--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A5407BF-8587-4F2F-98FA-DF8E64959BE1}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD70A2F-A7B7-4D46-A1FE-D10AD18B7BBA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22456,7 +22456,7 @@
         <v>75</v>
       </c>
       <c r="L363">
-        <v>5.65</v>
+        <v>6.1</v>
       </c>
       <c r="M363">
         <v>648</v>
@@ -31181,16 +31181,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31203,6 +31193,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52297,15 +52297,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
@@ -52318,14 +52309,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA071AA5-49F1-4442-BC42-9E2A4AB40C8C}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C24CFEE-BEAC-4E4D-A7E1-003CCD55EA2D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7874,6 +7874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R562"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
@@ -7953,7 +7954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" hidden="1">
       <c r="A2">
         <v>26712023</v>
       </c>
@@ -7991,7 +7992,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" hidden="1">
       <c r="A3">
         <v>26712123</v>
       </c>
@@ -8029,7 +8030,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" hidden="1">
       <c r="A4">
         <v>26712223</v>
       </c>
@@ -8067,7 +8068,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" hidden="1">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -8108,7 +8109,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" hidden="1">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -8190,7 +8191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" hidden="1">
       <c r="A8" t="s">
         <v>77</v>
       </c>
@@ -8319,7 +8320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" hidden="1">
       <c r="A11" t="s">
         <v>84</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" hidden="1">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -8395,7 +8396,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" hidden="1">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -8436,7 +8437,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" hidden="1">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -8477,7 +8478,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" hidden="1">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -8606,7 +8607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" hidden="1">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -8767,7 +8768,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" hidden="1">
       <c r="A22" t="s">
         <v>117</v>
       </c>
@@ -8805,7 +8806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" hidden="1">
       <c r="A23" t="s">
         <v>119</v>
       </c>
@@ -8843,7 +8844,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" hidden="1">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -8881,7 +8882,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" hidden="1">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -8919,7 +8920,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" hidden="1">
       <c r="A26" t="s">
         <v>128</v>
       </c>
@@ -8960,7 +8961,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" hidden="1">
       <c r="A27" t="s">
         <v>130</v>
       </c>
@@ -8998,7 +8999,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" hidden="1">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -9036,7 +9037,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" hidden="1">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -9074,7 +9075,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" hidden="1">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -9115,7 +9116,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" hidden="1">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -9156,7 +9157,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" hidden="1">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -9197,7 +9198,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" hidden="1">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -9238,7 +9239,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" hidden="1">
       <c r="A34" t="s">
         <v>152</v>
       </c>
@@ -9279,7 +9280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" hidden="1">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -9314,7 +9315,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:16" hidden="1">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -9355,7 +9356,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:16" hidden="1">
       <c r="A37" t="s">
         <v>159</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:16" hidden="1">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -9434,7 +9435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" hidden="1">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -9472,7 +9473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:16" hidden="1">
       <c r="A40" t="s">
         <v>168</v>
       </c>
@@ -9513,7 +9514,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" hidden="1">
       <c r="A41" t="s">
         <v>170</v>
       </c>
@@ -9557,7 +9558,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" hidden="1">
       <c r="A42" t="s">
         <v>174</v>
       </c>
@@ -9598,7 +9599,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:16" hidden="1">
       <c r="A43" t="s">
         <v>179</v>
       </c>
@@ -9642,7 +9643,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:16" hidden="1">
       <c r="A44">
         <v>26600424</v>
       </c>
@@ -9683,7 +9684,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
+    <row r="45" spans="1:16" hidden="1">
       <c r="A45" t="s">
         <v>186</v>
       </c>
@@ -9721,7 +9722,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="46" spans="1:16">
+    <row r="46" spans="1:16" hidden="1">
       <c r="A46" t="s">
         <v>190</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="47" spans="1:16">
+    <row r="47" spans="1:16" hidden="1">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -9797,7 +9798,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="48" spans="1:16">
+    <row r="48" spans="1:16" hidden="1">
       <c r="A48" t="s">
         <v>195</v>
       </c>
@@ -9838,7 +9839,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="49" spans="1:16">
+    <row r="49" spans="1:16" hidden="1">
       <c r="A49" t="s">
         <v>199</v>
       </c>
@@ -9879,7 +9880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="50" spans="1:16">
+    <row r="50" spans="1:16" hidden="1">
       <c r="A50" t="s">
         <v>202</v>
       </c>
@@ -9917,7 +9918,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="51" spans="1:16">
+    <row r="51" spans="1:16" hidden="1">
       <c r="A51" t="s">
         <v>204</v>
       </c>
@@ -9958,7 +9959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="52" spans="1:16">
+    <row r="52" spans="1:16" hidden="1">
       <c r="A52" t="s">
         <v>208</v>
       </c>
@@ -9996,7 +9997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="53" spans="1:16">
+    <row r="53" spans="1:16" hidden="1">
       <c r="A53" t="s">
         <v>210</v>
       </c>
@@ -10034,7 +10035,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="54" spans="1:16">
+    <row r="54" spans="1:16" hidden="1">
       <c r="A54" t="s">
         <v>211</v>
       </c>
@@ -10072,7 +10073,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="55" spans="1:16">
+    <row r="55" spans="1:16" hidden="1">
       <c r="A55" t="s">
         <v>215</v>
       </c>
@@ -10110,7 +10111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="56" spans="1:16">
+    <row r="56" spans="1:16" hidden="1">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -10154,7 +10155,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="57" spans="1:16">
+    <row r="57" spans="1:16" hidden="1">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -10192,7 +10193,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="58" spans="1:16">
+    <row r="58" spans="1:16" hidden="1">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -10233,7 +10234,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="59" spans="1:16">
+    <row r="59" spans="1:16" hidden="1">
       <c r="A59" t="s">
         <v>226</v>
       </c>
@@ -10271,7 +10272,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="60" spans="1:16">
+    <row r="60" spans="1:16" hidden="1">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -10312,7 +10313,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="61" spans="1:16">
+    <row r="61" spans="1:16" hidden="1">
       <c r="A61" t="s">
         <v>231</v>
       </c>
@@ -10347,7 +10348,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="62" spans="1:16">
+    <row r="62" spans="1:16" hidden="1">
       <c r="A62" t="s">
         <v>232</v>
       </c>
@@ -10388,7 +10389,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="63" spans="1:16">
+    <row r="63" spans="1:16" hidden="1">
       <c r="A63" t="s">
         <v>236</v>
       </c>
@@ -10426,7 +10427,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="64" spans="1:16">
+    <row r="64" spans="1:16" hidden="1">
       <c r="A64" t="s">
         <v>238</v>
       </c>
@@ -10470,7 +10471,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="65" spans="1:16">
+    <row r="65" spans="1:16" hidden="1">
       <c r="A65" t="s">
         <v>242</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="66" spans="1:16">
+    <row r="66" spans="1:16" hidden="1">
       <c r="A66" t="s">
         <v>245</v>
       </c>
@@ -10546,7 +10547,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="67" spans="1:16">
+    <row r="67" spans="1:16" hidden="1">
       <c r="A67" t="s">
         <v>248</v>
       </c>
@@ -10584,7 +10585,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="68" spans="1:16">
+    <row r="68" spans="1:16" hidden="1">
       <c r="A68" t="s">
         <v>249</v>
       </c>
@@ -10622,7 +10623,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="69" spans="1:16">
+    <row r="69" spans="1:16" hidden="1">
       <c r="A69" t="s">
         <v>252</v>
       </c>
@@ -10660,7 +10661,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="70" spans="1:16">
+    <row r="70" spans="1:16" hidden="1">
       <c r="A70" t="s">
         <v>255</v>
       </c>
@@ -10698,7 +10699,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="71" spans="1:16">
+    <row r="71" spans="1:16" hidden="1">
       <c r="A71" t="s">
         <v>258</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="72" spans="1:16">
+    <row r="72" spans="1:16" hidden="1">
       <c r="A72" t="s">
         <v>261</v>
       </c>
@@ -10777,7 +10778,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="73" spans="1:16">
+    <row r="73" spans="1:16" hidden="1">
       <c r="A73" t="s">
         <v>265</v>
       </c>
@@ -10821,7 +10822,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="74" spans="1:16">
+    <row r="74" spans="1:16" hidden="1">
       <c r="A74" t="s">
         <v>270</v>
       </c>
@@ -10862,7 +10863,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="75" spans="1:16">
+    <row r="75" spans="1:16" hidden="1">
       <c r="A75" t="s">
         <v>273</v>
       </c>
@@ -10900,7 +10901,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="76" spans="1:16">
+    <row r="76" spans="1:16" hidden="1">
       <c r="A76" t="s">
         <v>277</v>
       </c>
@@ -10938,7 +10939,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="77" spans="1:16">
+    <row r="77" spans="1:16" hidden="1">
       <c r="A77" t="s">
         <v>281</v>
       </c>
@@ -10976,7 +10977,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="78" spans="1:16">
+    <row r="78" spans="1:16" hidden="1">
       <c r="A78" t="s">
         <v>283</v>
       </c>
@@ -11011,7 +11012,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="79" spans="1:16">
+    <row r="79" spans="1:16" hidden="1">
       <c r="A79" t="s">
         <v>286</v>
       </c>
@@ -11049,7 +11050,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="80" spans="1:16">
+    <row r="80" spans="1:16" hidden="1">
       <c r="A80" t="s">
         <v>289</v>
       </c>
@@ -11090,7 +11091,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:16" hidden="1">
       <c r="A81" t="s">
         <v>293</v>
       </c>
@@ -11128,7 +11129,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
+    <row r="82" spans="1:16" hidden="1">
       <c r="A82" t="s">
         <v>295</v>
       </c>
@@ -11166,7 +11167,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="83" spans="1:16">
+    <row r="83" spans="1:16" hidden="1">
       <c r="A83" t="s">
         <v>297</v>
       </c>
@@ -11204,7 +11205,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:16" hidden="1">
       <c r="A84" t="s">
         <v>301</v>
       </c>
@@ -11242,7 +11243,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="85" spans="1:16">
+    <row r="85" spans="1:16" hidden="1">
       <c r="A85" t="s">
         <v>305</v>
       </c>
@@ -11283,7 +11284,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:16" hidden="1">
       <c r="A86" t="s">
         <v>307</v>
       </c>
@@ -11321,7 +11322,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
+    <row r="87" spans="1:16" hidden="1">
       <c r="A87" t="s">
         <v>309</v>
       </c>
@@ -11359,7 +11360,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="88" spans="1:16">
+    <row r="88" spans="1:16" hidden="1">
       <c r="A88" t="s">
         <v>312</v>
       </c>
@@ -11394,7 +11395,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
+    <row r="89" spans="1:16" hidden="1">
       <c r="A89">
         <v>10902324</v>
       </c>
@@ -11432,7 +11433,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="90" spans="1:16">
+    <row r="90" spans="1:16" hidden="1">
       <c r="A90" t="s">
         <v>318</v>
       </c>
@@ -11464,7 +11465,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="91" spans="1:16">
+    <row r="91" spans="1:16" hidden="1">
       <c r="A91" t="s">
         <v>321</v>
       </c>
@@ -11502,7 +11503,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="92" spans="1:16">
+    <row r="92" spans="1:16" hidden="1">
       <c r="A92">
         <v>15401623</v>
       </c>
@@ -11537,7 +11538,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="93" spans="1:16">
+    <row r="93" spans="1:16" hidden="1">
       <c r="A93" t="s">
         <v>325</v>
       </c>
@@ -11578,7 +11579,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="94" spans="1:16">
+    <row r="94" spans="1:16" hidden="1">
       <c r="A94" t="s">
         <v>328</v>
       </c>
@@ -11619,7 +11620,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="95" spans="1:16">
+    <row r="95" spans="1:16" hidden="1">
       <c r="A95" t="s">
         <v>330</v>
       </c>
@@ -11660,7 +11661,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="1:16">
+    <row r="96" spans="1:16" hidden="1">
       <c r="A96" t="s">
         <v>336</v>
       </c>
@@ -11701,7 +11702,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="97" spans="1:16">
+    <row r="97" spans="1:16" hidden="1">
       <c r="A97">
         <v>35800325</v>
       </c>
@@ -11742,7 +11743,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="98" spans="1:16">
+    <row r="98" spans="1:16" hidden="1">
       <c r="A98" t="s">
         <v>341</v>
       </c>
@@ -11786,7 +11787,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="99" spans="1:16">
+    <row r="99" spans="1:16" hidden="1">
       <c r="A99">
         <v>28500125</v>
       </c>
@@ -11827,7 +11828,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="100" spans="1:16">
+    <row r="100" spans="1:16" hidden="1">
       <c r="A100">
         <v>60502223</v>
       </c>
@@ -11868,7 +11869,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="101" spans="1:16">
+    <row r="101" spans="1:16" hidden="1">
       <c r="A101" t="s">
         <v>345</v>
       </c>
@@ -11909,7 +11910,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="102" spans="1:16">
+    <row r="102" spans="1:16" hidden="1">
       <c r="A102">
         <v>25000124</v>
       </c>
@@ -11950,7 +11951,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="103" spans="1:16">
+    <row r="103" spans="1:16" hidden="1">
       <c r="A103" t="s">
         <v>351</v>
       </c>
@@ -11991,7 +11992,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="104" spans="1:16">
+    <row r="104" spans="1:16" hidden="1">
       <c r="A104" t="s">
         <v>353</v>
       </c>
@@ -12032,7 +12033,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="105" spans="1:16">
+    <row r="105" spans="1:16" hidden="1">
       <c r="A105" t="s">
         <v>355</v>
       </c>
@@ -12073,7 +12074,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="106" spans="1:16">
+    <row r="106" spans="1:16" hidden="1">
       <c r="A106" t="s">
         <v>358</v>
       </c>
@@ -12114,7 +12115,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="107" spans="1:16">
+    <row r="107" spans="1:16" hidden="1">
       <c r="A107" t="s">
         <v>361</v>
       </c>
@@ -12155,7 +12156,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="108" spans="1:16">
+    <row r="108" spans="1:16" hidden="1">
       <c r="A108" t="s">
         <v>362</v>
       </c>
@@ -12196,7 +12197,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="109" spans="1:16">
+    <row r="109" spans="1:16" hidden="1">
       <c r="A109" t="s">
         <v>365</v>
       </c>
@@ -12234,7 +12235,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="110" spans="1:16">
+    <row r="110" spans="1:16" hidden="1">
       <c r="A110">
         <v>35800125</v>
       </c>
@@ -12269,7 +12270,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="111" spans="1:16">
+    <row r="111" spans="1:16" hidden="1">
       <c r="A111">
         <v>35800224</v>
       </c>
@@ -12304,7 +12305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="112" spans="1:16">
+    <row r="112" spans="1:16" hidden="1">
       <c r="A112" t="s">
         <v>372</v>
       </c>
@@ -12342,7 +12343,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="113" spans="1:16">
+    <row r="113" spans="1:16" hidden="1">
       <c r="A113">
         <v>27202325</v>
       </c>
@@ -12380,7 +12381,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" hidden="1">
       <c r="A114">
         <v>35800624</v>
       </c>
@@ -12424,7 +12425,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="115" spans="1:16">
+    <row r="115" spans="1:16" hidden="1">
       <c r="A115" t="s">
         <v>377</v>
       </c>
@@ -12465,7 +12466,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="116" spans="1:16">
+    <row r="116" spans="1:16" hidden="1">
       <c r="A116" t="s">
         <v>380</v>
       </c>
@@ -12509,7 +12510,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="117" spans="1:16">
+    <row r="117" spans="1:16" hidden="1">
       <c r="A117" t="s">
         <v>382</v>
       </c>
@@ -12547,7 +12548,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" hidden="1">
       <c r="A118" t="s">
         <v>384</v>
       </c>
@@ -12585,7 +12586,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" hidden="1">
       <c r="A119" t="s">
         <v>386</v>
       </c>
@@ -12629,7 +12630,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" hidden="1">
       <c r="A120" t="s">
         <v>390</v>
       </c>
@@ -12673,7 +12674,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" hidden="1">
       <c r="A121" t="s">
         <v>393</v>
       </c>
@@ -12708,7 +12709,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" hidden="1">
       <c r="A122" t="s">
         <v>396</v>
       </c>
@@ -12743,7 +12744,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" hidden="1">
       <c r="A123" t="s">
         <v>398</v>
       </c>
@@ -12784,7 +12785,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" hidden="1">
       <c r="A124" t="s">
         <v>400</v>
       </c>
@@ -12825,7 +12826,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" hidden="1">
       <c r="A125" t="s">
         <v>402</v>
       </c>
@@ -12863,7 +12864,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" hidden="1">
       <c r="A126" t="s">
         <v>403</v>
       </c>
@@ -12901,7 +12902,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" hidden="1">
       <c r="A127" t="s">
         <v>406</v>
       </c>
@@ -12942,7 +12943,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" hidden="1">
       <c r="A128" t="s">
         <v>409</v>
       </c>
@@ -12983,7 +12984,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" hidden="1">
       <c r="A129" t="s">
         <v>413</v>
       </c>
@@ -13024,7 +13025,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" hidden="1">
       <c r="A130" t="s">
         <v>415</v>
       </c>
@@ -13065,7 +13066,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" hidden="1">
       <c r="A131" t="s">
         <v>418</v>
       </c>
@@ -13106,7 +13107,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" hidden="1">
       <c r="A132">
         <v>65000724</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" hidden="1">
       <c r="A133" t="s">
         <v>425</v>
       </c>
@@ -13188,7 +13189,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" hidden="1">
       <c r="A134" t="s">
         <v>428</v>
       </c>
@@ -13232,7 +13233,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" hidden="1">
       <c r="A135" t="s">
         <v>431</v>
       </c>
@@ -13273,7 +13274,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" hidden="1">
       <c r="A136" t="s">
         <v>434</v>
       </c>
@@ -13311,7 +13312,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" hidden="1">
       <c r="A137" t="s">
         <v>436</v>
       </c>
@@ -13352,7 +13353,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" hidden="1">
       <c r="A138" t="s">
         <v>438</v>
       </c>
@@ -13390,7 +13391,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" hidden="1">
       <c r="A139" t="s">
         <v>441</v>
       </c>
@@ -13431,7 +13432,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" hidden="1">
       <c r="A140" t="s">
         <v>443</v>
       </c>
@@ -13472,7 +13473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" hidden="1">
       <c r="A141" t="s">
         <v>444</v>
       </c>
@@ -13513,7 +13514,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" hidden="1">
       <c r="A142">
         <v>35900524</v>
       </c>
@@ -13554,7 +13555,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" hidden="1">
       <c r="A143" t="s">
         <v>448</v>
       </c>
@@ -13595,7 +13596,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" hidden="1">
       <c r="A144" t="s">
         <v>452</v>
       </c>
@@ -13639,7 +13640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="145" spans="1:16">
+    <row r="145" spans="1:16" hidden="1">
       <c r="A145" t="s">
         <v>455</v>
       </c>
@@ -13680,7 +13681,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="146" spans="1:16">
+    <row r="146" spans="1:16" hidden="1">
       <c r="A146" t="s">
         <v>456</v>
       </c>
@@ -13718,7 +13719,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="147" spans="1:16">
+    <row r="147" spans="1:16" hidden="1">
       <c r="A147" t="s">
         <v>459</v>
       </c>
@@ -13759,7 +13760,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="148" spans="1:16">
+    <row r="148" spans="1:16" hidden="1">
       <c r="A148" t="s">
         <v>462</v>
       </c>
@@ -13794,7 +13795,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="149" spans="1:16">
+    <row r="149" spans="1:16" hidden="1">
       <c r="A149" t="s">
         <v>464</v>
       </c>
@@ -13835,7 +13836,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="150" spans="1:16">
+    <row r="150" spans="1:16" hidden="1">
       <c r="A150" t="s">
         <v>466</v>
       </c>
@@ -13879,7 +13880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="151" spans="1:16">
+    <row r="151" spans="1:16" hidden="1">
       <c r="A151" t="s">
         <v>469</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="152" spans="1:16">
+    <row r="152" spans="1:16" hidden="1">
       <c r="A152" t="s">
         <v>473</v>
       </c>
@@ -13955,7 +13956,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="153" spans="1:16">
+    <row r="153" spans="1:16" hidden="1">
       <c r="A153" t="s">
         <v>477</v>
       </c>
@@ -13996,7 +13997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="154" spans="1:16">
+    <row r="154" spans="1:16" hidden="1">
       <c r="A154" t="s">
         <v>480</v>
       </c>
@@ -14037,7 +14038,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="155" spans="1:16">
+    <row r="155" spans="1:16" hidden="1">
       <c r="A155" t="s">
         <v>483</v>
       </c>
@@ -14078,7 +14079,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="156" spans="1:16">
+    <row r="156" spans="1:16" hidden="1">
       <c r="A156" t="s">
         <v>486</v>
       </c>
@@ -14119,7 +14120,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="157" spans="1:16">
+    <row r="157" spans="1:16" hidden="1">
       <c r="A157" t="s">
         <v>488</v>
       </c>
@@ -14160,7 +14161,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="158" spans="1:16">
+    <row r="158" spans="1:16" hidden="1">
       <c r="A158" t="s">
         <v>491</v>
       </c>
@@ -14204,7 +14205,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="159" spans="1:16">
+    <row r="159" spans="1:16" hidden="1">
       <c r="A159" t="s">
         <v>495</v>
       </c>
@@ -14245,7 +14246,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="160" spans="1:16">
+    <row r="160" spans="1:16" hidden="1">
       <c r="A160" t="s">
         <v>496</v>
       </c>
@@ -14286,7 +14287,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="161" spans="1:16">
+    <row r="161" spans="1:16" hidden="1">
       <c r="A161" t="s">
         <v>499</v>
       </c>
@@ -14327,7 +14328,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="162" spans="1:16">
+    <row r="162" spans="1:16" hidden="1">
       <c r="A162" t="s">
         <v>503</v>
       </c>
@@ -14368,7 +14369,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="163" spans="1:16">
+    <row r="163" spans="1:16" hidden="1">
       <c r="A163" t="s">
         <v>506</v>
       </c>
@@ -14409,7 +14410,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="164" spans="1:16">
+    <row r="164" spans="1:16" hidden="1">
       <c r="A164" t="s">
         <v>509</v>
       </c>
@@ -14453,7 +14454,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="165" spans="1:16">
+    <row r="165" spans="1:16" hidden="1">
       <c r="A165">
         <v>12100124</v>
       </c>
@@ -14488,7 +14489,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="166" spans="1:16">
+    <row r="166" spans="1:16" hidden="1">
       <c r="A166" t="s">
         <v>512</v>
       </c>
@@ -14523,7 +14524,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="167" spans="1:16">
+    <row r="167" spans="1:16" hidden="1">
       <c r="A167" t="s">
         <v>514</v>
       </c>
@@ -14561,7 +14562,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="168" spans="1:16">
+    <row r="168" spans="1:16" hidden="1">
       <c r="A168" t="s">
         <v>515</v>
       </c>
@@ -14602,7 +14603,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="169" spans="1:16">
+    <row r="169" spans="1:16" hidden="1">
       <c r="A169" t="s">
         <v>517</v>
       </c>
@@ -14643,7 +14644,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="170" spans="1:16">
+    <row r="170" spans="1:16" hidden="1">
       <c r="A170" t="s">
         <v>520</v>
       </c>
@@ -14681,7 +14682,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="171" spans="1:16">
+    <row r="171" spans="1:16" hidden="1">
       <c r="A171" t="s">
         <v>522</v>
       </c>
@@ -14722,7 +14723,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="172" spans="1:16">
+    <row r="172" spans="1:16" hidden="1">
       <c r="A172" t="s">
         <v>525</v>
       </c>
@@ -14757,7 +14758,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="173" spans="1:16">
+    <row r="173" spans="1:16" hidden="1">
       <c r="A173" t="s">
         <v>527</v>
       </c>
@@ -14801,7 +14802,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" hidden="1">
       <c r="A174" t="s">
         <v>529</v>
       </c>
@@ -14842,7 +14843,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="175" spans="1:16">
+    <row r="175" spans="1:16" hidden="1">
       <c r="A175" t="s">
         <v>532</v>
       </c>
@@ -14883,7 +14884,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="176" spans="1:16">
+    <row r="176" spans="1:16" hidden="1">
       <c r="A176" t="s">
         <v>534</v>
       </c>
@@ -14924,7 +14925,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="177" spans="1:16">
+    <row r="177" spans="1:16" hidden="1">
       <c r="A177" t="s">
         <v>535</v>
       </c>
@@ -14968,7 +14969,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" hidden="1">
       <c r="A178" t="s">
         <v>539</v>
       </c>
@@ -15009,7 +15010,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="179" spans="1:16">
+    <row r="179" spans="1:16" hidden="1">
       <c r="A179" t="s">
         <v>541</v>
       </c>
@@ -15053,7 +15054,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" hidden="1">
       <c r="A180">
         <v>25002122</v>
       </c>
@@ -15091,7 +15092,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" hidden="1">
       <c r="A181" t="s">
         <v>544</v>
       </c>
@@ -15132,7 +15133,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" hidden="1">
       <c r="A182" t="s">
         <v>548</v>
       </c>
@@ -15173,7 +15174,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" hidden="1">
       <c r="A183" t="s">
         <v>550</v>
       </c>
@@ -15214,7 +15215,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" hidden="1">
       <c r="A184" t="s">
         <v>553</v>
       </c>
@@ -15255,7 +15256,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" hidden="1">
       <c r="A185">
         <v>28700625</v>
       </c>
@@ -15296,7 +15297,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" hidden="1">
       <c r="A186" t="s">
         <v>560</v>
       </c>
@@ -15337,7 +15338,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" hidden="1">
       <c r="A187" t="s">
         <v>562</v>
       </c>
@@ -15378,7 +15379,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" hidden="1">
       <c r="A188">
         <v>28701025</v>
       </c>
@@ -15419,7 +15420,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" hidden="1">
       <c r="A189" t="s">
         <v>567</v>
       </c>
@@ -15460,7 +15461,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" hidden="1">
       <c r="A190" t="s">
         <v>569</v>
       </c>
@@ -15501,7 +15502,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" hidden="1">
       <c r="A191" t="s">
         <v>572</v>
       </c>
@@ -15542,7 +15543,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" hidden="1">
       <c r="A192" t="s">
         <v>574</v>
       </c>
@@ -15583,7 +15584,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="193" spans="1:16">
+    <row r="193" spans="1:16" hidden="1">
       <c r="A193" t="s">
         <v>577</v>
       </c>
@@ -15627,7 +15628,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="194" spans="1:16">
+    <row r="194" spans="1:16" hidden="1">
       <c r="A194" t="s">
         <v>579</v>
       </c>
@@ -15668,7 +15669,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="195" spans="1:16">
+    <row r="195" spans="1:16" hidden="1">
       <c r="A195" t="s">
         <v>582</v>
       </c>
@@ -15712,7 +15713,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="196" spans="1:16">
+    <row r="196" spans="1:16" hidden="1">
       <c r="A196" t="s">
         <v>585</v>
       </c>
@@ -15753,7 +15754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="197" spans="1:16">
+    <row r="197" spans="1:16" hidden="1">
       <c r="A197" t="s">
         <v>588</v>
       </c>
@@ -15794,7 +15795,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="198" spans="1:16">
+    <row r="198" spans="1:16" hidden="1">
       <c r="A198">
         <v>43902124</v>
       </c>
@@ -15832,7 +15833,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="199" spans="1:16">
+    <row r="199" spans="1:16" hidden="1">
       <c r="A199" t="s">
         <v>594</v>
       </c>
@@ -15873,7 +15874,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="200" spans="1:16">
+    <row r="200" spans="1:16" hidden="1">
       <c r="A200" t="s">
         <v>596</v>
       </c>
@@ -15917,7 +15918,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="201" spans="1:16">
+    <row r="201" spans="1:16" hidden="1">
       <c r="A201" t="s">
         <v>600</v>
       </c>
@@ -15958,7 +15959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="202" spans="1:16">
+    <row r="202" spans="1:16" hidden="1">
       <c r="A202" t="s">
         <v>602</v>
       </c>
@@ -15999,7 +16000,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="203" spans="1:16">
+    <row r="203" spans="1:16" hidden="1">
       <c r="A203" t="s">
         <v>604</v>
       </c>
@@ -16043,7 +16044,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="204" spans="1:16">
+    <row r="204" spans="1:16" hidden="1">
       <c r="A204" t="s">
         <v>606</v>
       </c>
@@ -16084,7 +16085,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="205" spans="1:16">
+    <row r="205" spans="1:16" hidden="1">
       <c r="A205" t="s">
         <v>608</v>
       </c>
@@ -16128,7 +16129,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="206" spans="1:16">
+    <row r="206" spans="1:16" hidden="1">
       <c r="A206" t="s">
         <v>610</v>
       </c>
@@ -16169,7 +16170,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="207" spans="1:16">
+    <row r="207" spans="1:16" hidden="1">
       <c r="A207" t="s">
         <v>612</v>
       </c>
@@ -16210,7 +16211,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="208" spans="1:16">
+    <row r="208" spans="1:16" hidden="1">
       <c r="A208">
         <v>28400124</v>
       </c>
@@ -16251,7 +16252,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="209" spans="1:16">
+    <row r="209" spans="1:16" hidden="1">
       <c r="A209" t="s">
         <v>614</v>
       </c>
@@ -16292,7 +16293,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="210" spans="1:16">
+    <row r="210" spans="1:16" hidden="1">
       <c r="A210">
         <v>31901625</v>
       </c>
@@ -16330,7 +16331,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="211" spans="1:16">
+    <row r="211" spans="1:16" hidden="1">
       <c r="A211" t="s">
         <v>619</v>
       </c>
@@ -16371,7 +16372,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="212" spans="1:16">
+    <row r="212" spans="1:16" hidden="1">
       <c r="A212" t="s">
         <v>622</v>
       </c>
@@ -16412,7 +16413,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="213" spans="1:16">
+    <row r="213" spans="1:16" hidden="1">
       <c r="A213" t="s">
         <v>624</v>
       </c>
@@ -16453,7 +16454,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="214" spans="1:16">
+    <row r="214" spans="1:16" hidden="1">
       <c r="A214" t="s">
         <v>627</v>
       </c>
@@ -16494,7 +16495,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="215" spans="1:16">
+    <row r="215" spans="1:16" hidden="1">
       <c r="A215" t="s">
         <v>630</v>
       </c>
@@ -16535,7 +16536,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="216" spans="1:16">
+    <row r="216" spans="1:16" hidden="1">
       <c r="A216" t="s">
         <v>633</v>
       </c>
@@ -16576,7 +16577,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="217" spans="1:16">
+    <row r="217" spans="1:16" hidden="1">
       <c r="A217" t="s">
         <v>634</v>
       </c>
@@ -16617,7 +16618,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="218" spans="1:16">
+    <row r="218" spans="1:16" hidden="1">
       <c r="A218" t="s">
         <v>637</v>
       </c>
@@ -16658,7 +16659,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="219" spans="1:16">
+    <row r="219" spans="1:16" hidden="1">
       <c r="A219" t="s">
         <v>640</v>
       </c>
@@ -16699,7 +16700,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="220" spans="1:16">
+    <row r="220" spans="1:16" hidden="1">
       <c r="A220" t="s">
         <v>641</v>
       </c>
@@ -16740,7 +16741,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="221" spans="1:16">
+    <row r="221" spans="1:16" hidden="1">
       <c r="A221" t="s">
         <v>642</v>
       </c>
@@ -16781,7 +16782,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="222" spans="1:16">
+    <row r="222" spans="1:16" hidden="1">
       <c r="A222" t="s">
         <v>644</v>
       </c>
@@ -16822,7 +16823,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="223" spans="1:16">
+    <row r="223" spans="1:16" hidden="1">
       <c r="A223">
         <v>51600124</v>
       </c>
@@ -16866,7 +16867,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="224" spans="1:16">
+    <row r="224" spans="1:16" hidden="1">
       <c r="A224">
         <v>51600225</v>
       </c>
@@ -16910,7 +16911,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="225" spans="1:16">
+    <row r="225" spans="1:16" hidden="1">
       <c r="A225">
         <v>51600324</v>
       </c>
@@ -16954,7 +16955,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="226" spans="1:16">
+    <row r="226" spans="1:16" hidden="1">
       <c r="A226">
         <v>51600424</v>
       </c>
@@ -16998,7 +16999,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="227" spans="1:16">
+    <row r="227" spans="1:16" hidden="1">
       <c r="A227">
         <v>51600523</v>
       </c>
@@ -17042,7 +17043,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="228" spans="1:16">
+    <row r="228" spans="1:16" hidden="1">
       <c r="A228">
         <v>51600625</v>
       </c>
@@ -17086,7 +17087,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="229" spans="1:16">
+    <row r="229" spans="1:16" hidden="1">
       <c r="A229" t="s">
         <v>655</v>
       </c>
@@ -17127,7 +17128,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="230" spans="1:16">
+    <row r="230" spans="1:16" hidden="1">
       <c r="A230" t="s">
         <v>658</v>
       </c>
@@ -17168,7 +17169,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="231" spans="1:16">
+    <row r="231" spans="1:16" hidden="1">
       <c r="A231" t="s">
         <v>660</v>
       </c>
@@ -17209,7 +17210,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="232" spans="1:16">
+    <row r="232" spans="1:16" hidden="1">
       <c r="A232" t="s">
         <v>662</v>
       </c>
@@ -17250,7 +17251,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="233" spans="1:16">
+    <row r="233" spans="1:16" hidden="1">
       <c r="A233" t="s">
         <v>665</v>
       </c>
@@ -17291,7 +17292,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="234" spans="1:16">
+    <row r="234" spans="1:16" hidden="1">
       <c r="A234" t="s">
         <v>667</v>
       </c>
@@ -17335,7 +17336,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="235" spans="1:16">
+    <row r="235" spans="1:16" hidden="1">
       <c r="A235" t="s">
         <v>670</v>
       </c>
@@ -17376,7 +17377,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="236" spans="1:16">
+    <row r="236" spans="1:16" hidden="1">
       <c r="A236" t="s">
         <v>672</v>
       </c>
@@ -17417,7 +17418,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="237" spans="1:16">
+    <row r="237" spans="1:16" hidden="1">
       <c r="A237" t="s">
         <v>674</v>
       </c>
@@ -17458,7 +17459,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="238" spans="1:16">
+    <row r="238" spans="1:16" hidden="1">
       <c r="A238" t="s">
         <v>677</v>
       </c>
@@ -17502,7 +17503,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="239" spans="1:16">
+    <row r="239" spans="1:16" hidden="1">
       <c r="A239" t="s">
         <v>680</v>
       </c>
@@ -17543,7 +17544,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="240" spans="1:16">
+    <row r="240" spans="1:16" hidden="1">
       <c r="A240" t="s">
         <v>682</v>
       </c>
@@ -17584,7 +17585,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="241" spans="1:16">
+    <row r="241" spans="1:16" hidden="1">
       <c r="A241">
         <v>11001923</v>
       </c>
@@ -17622,7 +17623,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="242" spans="1:16">
+    <row r="242" spans="1:16" hidden="1">
       <c r="A242" t="s">
         <v>687</v>
       </c>
@@ -17663,7 +17664,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="243" spans="1:16">
+    <row r="243" spans="1:16" hidden="1">
       <c r="A243" t="s">
         <v>691</v>
       </c>
@@ -17704,7 +17705,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="244" spans="1:16">
+    <row r="244" spans="1:16" hidden="1">
       <c r="A244" t="s">
         <v>693</v>
       </c>
@@ -17745,7 +17746,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="245" spans="1:16">
+    <row r="245" spans="1:16" hidden="1">
       <c r="A245" t="s">
         <v>696</v>
       </c>
@@ -17786,7 +17787,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="246" spans="1:16">
+    <row r="246" spans="1:16" hidden="1">
       <c r="A246" t="s">
         <v>698</v>
       </c>
@@ -17827,7 +17828,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="247" spans="1:16">
+    <row r="247" spans="1:16" hidden="1">
       <c r="A247" t="s">
         <v>701</v>
       </c>
@@ -17868,7 +17869,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="248" spans="1:16">
+    <row r="248" spans="1:16" hidden="1">
       <c r="A248" t="s">
         <v>702</v>
       </c>
@@ -17912,7 +17913,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="249" spans="1:16">
+    <row r="249" spans="1:16" hidden="1">
       <c r="A249">
         <v>11003123</v>
       </c>
@@ -17953,7 +17954,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="250" spans="1:16">
+    <row r="250" spans="1:16" hidden="1">
       <c r="A250" t="s">
         <v>703</v>
       </c>
@@ -17997,7 +17998,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="251" spans="1:16">
+    <row r="251" spans="1:16" hidden="1">
       <c r="A251" t="s">
         <v>706</v>
       </c>
@@ -18038,7 +18039,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="252" spans="1:16">
+    <row r="252" spans="1:16" hidden="1">
       <c r="A252" t="s">
         <v>708</v>
       </c>
@@ -18079,7 +18080,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="253" spans="1:16">
+    <row r="253" spans="1:16" hidden="1">
       <c r="A253" t="s">
         <v>710</v>
       </c>
@@ -18120,7 +18121,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="254" spans="1:16">
+    <row r="254" spans="1:16" hidden="1">
       <c r="A254">
         <v>15000820</v>
       </c>
@@ -18161,7 +18162,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="255" spans="1:16">
+    <row r="255" spans="1:16" hidden="1">
       <c r="A255" t="s">
         <v>713</v>
       </c>
@@ -18202,7 +18203,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="256" spans="1:16">
+    <row r="256" spans="1:16" hidden="1">
       <c r="A256">
         <v>11002824</v>
       </c>
@@ -18243,7 +18244,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="257" spans="1:16">
+    <row r="257" spans="1:16" hidden="1">
       <c r="A257" t="s">
         <v>716</v>
       </c>
@@ -18284,7 +18285,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="258" spans="1:16">
+    <row r="258" spans="1:16" hidden="1">
       <c r="A258">
         <v>13800524</v>
       </c>
@@ -18325,7 +18326,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="259" spans="1:16">
+    <row r="259" spans="1:16" hidden="1">
       <c r="A259" t="s">
         <v>718</v>
       </c>
@@ -18366,7 +18367,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="260" spans="1:16">
+    <row r="260" spans="1:16" hidden="1">
       <c r="A260" t="s">
         <v>720</v>
       </c>
@@ -18407,7 +18408,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="261" spans="1:16">
+    <row r="261" spans="1:16" hidden="1">
       <c r="A261" t="s">
         <v>722</v>
       </c>
@@ -18448,7 +18449,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="262" spans="1:16">
+    <row r="262" spans="1:16" hidden="1">
       <c r="A262" t="s">
         <v>723</v>
       </c>
@@ -18486,7 +18487,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="263" spans="1:16">
+    <row r="263" spans="1:16" hidden="1">
       <c r="A263" t="s">
         <v>727</v>
       </c>
@@ -18524,7 +18525,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="264" spans="1:16">
+    <row r="264" spans="1:16" hidden="1">
       <c r="A264">
         <v>10700325</v>
       </c>
@@ -18562,7 +18563,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="265" spans="1:16">
+    <row r="265" spans="1:16" hidden="1">
       <c r="A265" t="s">
         <v>732</v>
       </c>
@@ -18600,7 +18601,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="266" spans="1:16">
+    <row r="266" spans="1:16" hidden="1">
       <c r="A266" t="s">
         <v>736</v>
       </c>
@@ -18641,7 +18642,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="267" spans="1:16">
+    <row r="267" spans="1:16" hidden="1">
       <c r="A267" t="s">
         <v>739</v>
       </c>
@@ -18682,7 +18683,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="268" spans="1:16">
+    <row r="268" spans="1:16" hidden="1">
       <c r="A268" t="s">
         <v>742</v>
       </c>
@@ -18723,7 +18724,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="269" spans="1:16">
+    <row r="269" spans="1:16" hidden="1">
       <c r="A269" t="s">
         <v>746</v>
       </c>
@@ -18764,7 +18765,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="270" spans="1:16">
+    <row r="270" spans="1:16" hidden="1">
       <c r="A270" t="s">
         <v>750</v>
       </c>
@@ -18805,7 +18806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="271" spans="1:16">
+    <row r="271" spans="1:16" hidden="1">
       <c r="A271" t="s">
         <v>754</v>
       </c>
@@ -18846,7 +18847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="272" spans="1:16">
+    <row r="272" spans="1:16" hidden="1">
       <c r="A272" t="s">
         <v>759</v>
       </c>
@@ -18931,7 +18932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="274" spans="1:18">
+    <row r="274" spans="1:18" hidden="1">
       <c r="A274" t="s">
         <v>765</v>
       </c>
@@ -18972,7 +18973,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="275" spans="1:18">
+    <row r="275" spans="1:18" hidden="1">
       <c r="A275" t="s">
         <v>769</v>
       </c>
@@ -19013,7 +19014,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="276" spans="1:18">
+    <row r="276" spans="1:18" hidden="1">
       <c r="A276" t="s">
         <v>772</v>
       </c>
@@ -19054,7 +19055,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="277" spans="1:18">
+    <row r="277" spans="1:18" hidden="1">
       <c r="A277" t="s">
         <v>777</v>
       </c>
@@ -19092,7 +19093,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="278" spans="1:18">
+    <row r="278" spans="1:18" hidden="1">
       <c r="A278">
         <v>14700423</v>
       </c>
@@ -19133,7 +19134,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="279" spans="1:18">
+    <row r="279" spans="1:18" hidden="1">
       <c r="A279" t="s">
         <v>781</v>
       </c>
@@ -19171,7 +19172,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="280" spans="1:18">
+    <row r="280" spans="1:18" hidden="1">
       <c r="A280" t="s">
         <v>783</v>
       </c>
@@ -19209,7 +19210,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="281" spans="1:18">
+    <row r="281" spans="1:18" hidden="1">
       <c r="A281" t="s">
         <v>786</v>
       </c>
@@ -19241,7 +19242,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="282" spans="1:18">
+    <row r="282" spans="1:18" hidden="1">
       <c r="A282" t="s">
         <v>789</v>
       </c>
@@ -19279,7 +19280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="283" spans="1:18">
+    <row r="283" spans="1:18" hidden="1">
       <c r="A283">
         <v>43800825</v>
       </c>
@@ -19320,7 +19321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="284" spans="1:18">
+    <row r="284" spans="1:18" hidden="1">
       <c r="A284" t="s">
         <v>795</v>
       </c>
@@ -19358,7 +19359,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="285" spans="1:18">
+    <row r="285" spans="1:18" hidden="1">
       <c r="A285" t="s">
         <v>798</v>
       </c>
@@ -19393,7 +19394,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="286" spans="1:18">
+    <row r="286" spans="1:18" hidden="1">
       <c r="A286" t="s">
         <v>800</v>
       </c>
@@ -19428,7 +19429,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="287" spans="1:18">
+    <row r="287" spans="1:18" hidden="1">
       <c r="A287" t="s">
         <v>802</v>
       </c>
@@ -19466,7 +19467,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="288" spans="1:18">
+    <row r="288" spans="1:18" hidden="1">
       <c r="A288" t="s">
         <v>805</v>
       </c>
@@ -19504,7 +19505,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="289" spans="1:18">
+    <row r="289" spans="1:18" hidden="1">
       <c r="A289">
         <v>14805225</v>
       </c>
@@ -19542,7 +19543,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="290" spans="1:18">
+    <row r="290" spans="1:18" hidden="1">
       <c r="A290" t="s">
         <v>810</v>
       </c>
@@ -19577,7 +19578,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="291" spans="1:18">
+    <row r="291" spans="1:18" hidden="1">
       <c r="A291" t="s">
         <v>813</v>
       </c>
@@ -19656,7 +19657,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:18">
+    <row r="293" spans="1:18" hidden="1">
       <c r="A293" t="s">
         <v>817</v>
       </c>
@@ -19691,7 +19692,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="294" spans="1:18">
+    <row r="294" spans="1:18" hidden="1">
       <c r="A294" t="s">
         <v>818</v>
       </c>
@@ -19729,7 +19730,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="295" spans="1:18">
+    <row r="295" spans="1:18" hidden="1">
       <c r="A295" t="s">
         <v>820</v>
       </c>
@@ -19767,7 +19768,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="296" spans="1:18">
+    <row r="296" spans="1:18" hidden="1">
       <c r="A296" t="s">
         <v>822</v>
       </c>
@@ -19805,7 +19806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="297" spans="1:18">
+    <row r="297" spans="1:18" hidden="1">
       <c r="A297" t="s">
         <v>824</v>
       </c>
@@ -19846,7 +19847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="298" spans="1:18">
+    <row r="298" spans="1:18" hidden="1">
       <c r="A298" t="s">
         <v>827</v>
       </c>
@@ -19887,7 +19888,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="299" spans="1:18">
+    <row r="299" spans="1:18" hidden="1">
       <c r="A299" t="s">
         <v>831</v>
       </c>
@@ -19925,7 +19926,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="300" spans="1:18">
+    <row r="300" spans="1:18" hidden="1">
       <c r="A300" t="s">
         <v>834</v>
       </c>
@@ -19963,7 +19964,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="301" spans="1:18">
+    <row r="301" spans="1:18" hidden="1">
       <c r="A301">
         <v>14800921</v>
       </c>
@@ -20001,7 +20002,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="302" spans="1:18">
+    <row r="302" spans="1:18" hidden="1">
       <c r="A302" t="s">
         <v>838</v>
       </c>
@@ -20042,7 +20043,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="303" spans="1:18">
+    <row r="303" spans="1:18" hidden="1">
       <c r="A303" t="s">
         <v>840</v>
       </c>
@@ -20083,7 +20084,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="304" spans="1:18">
+    <row r="304" spans="1:18" hidden="1">
       <c r="A304" t="s">
         <v>842</v>
       </c>
@@ -20124,7 +20125,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="305" spans="1:16">
+    <row r="305" spans="1:16" hidden="1">
       <c r="A305" t="s">
         <v>844</v>
       </c>
@@ -20162,7 +20163,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="306" spans="1:16">
+    <row r="306" spans="1:16" hidden="1">
       <c r="A306" t="s">
         <v>845</v>
       </c>
@@ -20203,7 +20204,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="307" spans="1:16">
+    <row r="307" spans="1:16" hidden="1">
       <c r="A307">
         <v>14700123</v>
       </c>
@@ -20241,7 +20242,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="308" spans="1:16">
+    <row r="308" spans="1:16" hidden="1">
       <c r="A308" t="s">
         <v>848</v>
       </c>
@@ -20279,7 +20280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="309" spans="1:16">
+    <row r="309" spans="1:16" hidden="1">
       <c r="A309" t="s">
         <v>850</v>
       </c>
@@ -20317,7 +20318,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="310" spans="1:16">
+    <row r="310" spans="1:16" hidden="1">
       <c r="A310" t="s">
         <v>852</v>
       </c>
@@ -20352,7 +20353,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="311" spans="1:16">
+    <row r="311" spans="1:16" hidden="1">
       <c r="A311" t="s">
         <v>853</v>
       </c>
@@ -20393,7 +20394,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="312" spans="1:16">
+    <row r="312" spans="1:16" hidden="1">
       <c r="A312" t="s">
         <v>855</v>
       </c>
@@ -20431,7 +20432,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="313" spans="1:16">
+    <row r="313" spans="1:16" hidden="1">
       <c r="A313">
         <v>10701525</v>
       </c>
@@ -20469,7 +20470,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="314" spans="1:16">
+    <row r="314" spans="1:16" hidden="1">
       <c r="A314" t="s">
         <v>862</v>
       </c>
@@ -20507,7 +20508,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="315" spans="1:16">
+    <row r="315" spans="1:16" hidden="1">
       <c r="A315" t="s">
         <v>865</v>
       </c>
@@ -20548,7 +20549,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="316" spans="1:16">
+    <row r="316" spans="1:16" hidden="1">
       <c r="A316" t="s">
         <v>867</v>
       </c>
@@ -20589,7 +20590,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="317" spans="1:16">
+    <row r="317" spans="1:16" hidden="1">
       <c r="A317" t="s">
         <v>869</v>
       </c>
@@ -20627,7 +20628,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="318" spans="1:16">
+    <row r="318" spans="1:16" hidden="1">
       <c r="A318" t="s">
         <v>873</v>
       </c>
@@ -20668,7 +20669,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="319" spans="1:16">
+    <row r="319" spans="1:16" hidden="1">
       <c r="A319" t="s">
         <v>876</v>
       </c>
@@ -20706,7 +20707,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="320" spans="1:16">
+    <row r="320" spans="1:16" hidden="1">
       <c r="A320" t="s">
         <v>877</v>
       </c>
@@ -20744,7 +20745,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="321" spans="1:16">
+    <row r="321" spans="1:16" hidden="1">
       <c r="A321" t="s">
         <v>880</v>
       </c>
@@ -20785,7 +20786,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="322" spans="1:16">
+    <row r="322" spans="1:16" hidden="1">
       <c r="A322" t="s">
         <v>883</v>
       </c>
@@ -20817,7 +20818,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="323" spans="1:16">
+    <row r="323" spans="1:16" hidden="1">
       <c r="A323" t="s">
         <v>885</v>
       </c>
@@ -20852,7 +20853,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="324" spans="1:16">
+    <row r="324" spans="1:16" hidden="1">
       <c r="A324" t="s">
         <v>887</v>
       </c>
@@ -20893,7 +20894,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="325" spans="1:16">
+    <row r="325" spans="1:16" hidden="1">
       <c r="A325">
         <v>66700924</v>
       </c>
@@ -20934,7 +20935,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="326" spans="1:16">
+    <row r="326" spans="1:16" hidden="1">
       <c r="A326">
         <v>66700820</v>
       </c>
@@ -20975,7 +20976,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="327" spans="1:16">
+    <row r="327" spans="1:16" hidden="1">
       <c r="A327">
         <v>66700815</v>
       </c>
@@ -21016,7 +21017,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="328" spans="1:16">
+    <row r="328" spans="1:16" hidden="1">
       <c r="A328">
         <v>66700217</v>
       </c>
@@ -21057,7 +21058,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="329" spans="1:16">
+    <row r="329" spans="1:16" hidden="1">
       <c r="A329" t="s">
         <v>892</v>
       </c>
@@ -21098,7 +21099,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="330" spans="1:16">
+    <row r="330" spans="1:16" hidden="1">
       <c r="A330">
         <v>66700711</v>
       </c>
@@ -21139,7 +21140,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="331" spans="1:16">
+    <row r="331" spans="1:16" hidden="1">
       <c r="A331" t="s">
         <v>894</v>
       </c>
@@ -21171,7 +21172,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="332" spans="1:16">
+    <row r="332" spans="1:16" hidden="1">
       <c r="A332" t="s">
         <v>896</v>
       </c>
@@ -21206,7 +21207,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="333" spans="1:16">
+    <row r="333" spans="1:16" hidden="1">
       <c r="A333" t="s">
         <v>897</v>
       </c>
@@ -21244,7 +21245,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="334" spans="1:16">
+    <row r="334" spans="1:16" hidden="1">
       <c r="A334" t="s">
         <v>898</v>
       </c>
@@ -21282,7 +21283,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="335" spans="1:16">
+    <row r="335" spans="1:16" hidden="1">
       <c r="A335" t="s">
         <v>899</v>
       </c>
@@ -21320,7 +21321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="336" spans="1:16">
+    <row r="336" spans="1:16" hidden="1">
       <c r="A336" t="s">
         <v>900</v>
       </c>
@@ -21399,7 +21400,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="338" spans="1:18">
+    <row r="338" spans="1:18" hidden="1">
       <c r="A338" t="s">
         <v>903</v>
       </c>
@@ -21434,7 +21435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="339" spans="1:18">
+    <row r="339" spans="1:18" hidden="1">
       <c r="A339" t="s">
         <v>904</v>
       </c>
@@ -21475,7 +21476,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="340" spans="1:18">
+    <row r="340" spans="1:18" hidden="1">
       <c r="A340" t="s">
         <v>906</v>
       </c>
@@ -21516,7 +21517,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="341" spans="1:18">
+    <row r="341" spans="1:18" hidden="1">
       <c r="A341" t="s">
         <v>910</v>
       </c>
@@ -21560,7 +21561,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="342" spans="1:18">
+    <row r="342" spans="1:18" hidden="1">
       <c r="A342" t="s">
         <v>917</v>
       </c>
@@ -21595,7 +21596,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="343" spans="1:18">
+    <row r="343" spans="1:18" hidden="1">
       <c r="A343" t="s">
         <v>921</v>
       </c>
@@ -21639,7 +21640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="344" spans="1:18">
+    <row r="344" spans="1:18" hidden="1">
       <c r="A344" t="s">
         <v>922</v>
       </c>
@@ -21683,7 +21684,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="345" spans="1:18">
+    <row r="345" spans="1:18" hidden="1">
       <c r="A345" t="s">
         <v>926</v>
       </c>
@@ -21718,7 +21719,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="346" spans="1:18">
+    <row r="346" spans="1:18" hidden="1">
       <c r="A346" t="s">
         <v>927</v>
       </c>
@@ -21753,7 +21754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="347" spans="1:18">
+    <row r="347" spans="1:18" hidden="1">
       <c r="A347" t="s">
         <v>930</v>
       </c>
@@ -21791,7 +21792,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="348" spans="1:18">
+    <row r="348" spans="1:18" hidden="1">
       <c r="A348" t="s">
         <v>932</v>
       </c>
@@ -21835,7 +21836,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="349" spans="1:18">
+    <row r="349" spans="1:18" hidden="1">
       <c r="A349">
         <v>72400122</v>
       </c>
@@ -21879,7 +21880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="350" spans="1:18">
+    <row r="350" spans="1:18" hidden="1">
       <c r="A350">
         <v>72400223</v>
       </c>
@@ -21923,7 +21924,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="351" spans="1:18">
+    <row r="351" spans="1:18" hidden="1">
       <c r="A351">
         <v>72400324</v>
       </c>
@@ -21967,7 +21968,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="352" spans="1:18">
+    <row r="352" spans="1:18" hidden="1">
       <c r="A352">
         <v>72400424</v>
       </c>
@@ -22011,7 +22012,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="353" spans="1:16">
+    <row r="353" spans="1:16" hidden="1">
       <c r="A353">
         <v>72400524</v>
       </c>
@@ -22055,7 +22056,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="354" spans="1:16">
+    <row r="354" spans="1:16" hidden="1">
       <c r="A354">
         <v>72400625</v>
       </c>
@@ -22099,7 +22100,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="355" spans="1:16">
+    <row r="355" spans="1:16" hidden="1">
       <c r="A355">
         <v>72300125</v>
       </c>
@@ -22143,7 +22144,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="356" spans="1:16">
+    <row r="356" spans="1:16" hidden="1">
       <c r="A356">
         <v>72300223</v>
       </c>
@@ -22187,7 +22188,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="357" spans="1:16">
+    <row r="357" spans="1:16" hidden="1">
       <c r="A357">
         <v>72300223</v>
       </c>
@@ -22231,7 +22232,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="358" spans="1:16">
+    <row r="358" spans="1:16" hidden="1">
       <c r="A358" t="s">
         <v>946</v>
       </c>
@@ -22266,7 +22267,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="359" spans="1:16">
+    <row r="359" spans="1:16" hidden="1">
       <c r="A359" t="s">
         <v>949</v>
       </c>
@@ -22304,7 +22305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="360" spans="1:16">
+    <row r="360" spans="1:16" hidden="1">
       <c r="A360" t="s">
         <v>953</v>
       </c>
@@ -22342,7 +22343,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="361" spans="1:16">
+    <row r="361" spans="1:16" hidden="1">
       <c r="A361" t="s">
         <v>956</v>
       </c>
@@ -22386,7 +22387,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="362" spans="1:16">
+    <row r="362" spans="1:16" hidden="1">
       <c r="A362">
         <v>10300525</v>
       </c>
@@ -22430,7 +22431,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="363" spans="1:16">
+    <row r="363" spans="1:16" hidden="1">
       <c r="A363" t="s">
         <v>961</v>
       </c>
@@ -22471,7 +22472,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="364" spans="1:16">
+    <row r="364" spans="1:16" hidden="1">
       <c r="A364" t="s">
         <v>964</v>
       </c>
@@ -22512,7 +22513,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="365" spans="1:16">
+    <row r="365" spans="1:16" hidden="1">
       <c r="A365" t="s">
         <v>966</v>
       </c>
@@ -22556,7 +22557,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="366" spans="1:16">
+    <row r="366" spans="1:16" hidden="1">
       <c r="A366" t="s">
         <v>969</v>
       </c>
@@ -22597,7 +22598,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="367" spans="1:16">
+    <row r="367" spans="1:16" hidden="1">
       <c r="A367" t="s">
         <v>971</v>
       </c>
@@ -22638,7 +22639,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="368" spans="1:16">
+    <row r="368" spans="1:16" hidden="1">
       <c r="A368" t="s">
         <v>973</v>
       </c>
@@ -22682,7 +22683,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="369" spans="1:16">
+    <row r="369" spans="1:16" hidden="1">
       <c r="A369" t="s">
         <v>975</v>
       </c>
@@ -22726,7 +22727,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="370" spans="1:16">
+    <row r="370" spans="1:16" hidden="1">
       <c r="A370" t="s">
         <v>978</v>
       </c>
@@ -22764,7 +22765,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="371" spans="1:16">
+    <row r="371" spans="1:16" hidden="1">
       <c r="A371" t="s">
         <v>980</v>
       </c>
@@ -22805,7 +22806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="372" spans="1:16">
+    <row r="372" spans="1:16" hidden="1">
       <c r="A372" t="s">
         <v>981</v>
       </c>
@@ -22846,7 +22847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="373" spans="1:16">
+    <row r="373" spans="1:16" hidden="1">
       <c r="A373" t="s">
         <v>982</v>
       </c>
@@ -22887,7 +22888,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="374" spans="1:16">
+    <row r="374" spans="1:16" hidden="1">
       <c r="A374" t="s">
         <v>988</v>
       </c>
@@ -22928,7 +22929,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="375" spans="1:16">
+    <row r="375" spans="1:16" hidden="1">
       <c r="A375" t="s">
         <v>991</v>
       </c>
@@ -22969,7 +22970,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="376" spans="1:16">
+    <row r="376" spans="1:16" hidden="1">
       <c r="A376" t="s">
         <v>995</v>
       </c>
@@ -23010,7 +23011,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="377" spans="1:16">
+    <row r="377" spans="1:16" hidden="1">
       <c r="A377" t="s">
         <v>998</v>
       </c>
@@ -23051,7 +23052,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="378" spans="1:16">
+    <row r="378" spans="1:16" hidden="1">
       <c r="A378" t="s">
         <v>1000</v>
       </c>
@@ -23092,7 +23093,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="379" spans="1:16">
+    <row r="379" spans="1:16" hidden="1">
       <c r="A379" t="s">
         <v>1002</v>
       </c>
@@ -23133,7 +23134,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="380" spans="1:16">
+    <row r="380" spans="1:16" hidden="1">
       <c r="A380" t="s">
         <v>1004</v>
       </c>
@@ -23174,7 +23175,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="381" spans="1:16">
+    <row r="381" spans="1:16" hidden="1">
       <c r="A381" t="s">
         <v>1007</v>
       </c>
@@ -23215,7 +23216,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="382" spans="1:16">
+    <row r="382" spans="1:16" hidden="1">
       <c r="A382" t="s">
         <v>1009</v>
       </c>
@@ -23256,7 +23257,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="383" spans="1:16">
+    <row r="383" spans="1:16" hidden="1">
       <c r="A383" t="s">
         <v>1012</v>
       </c>
@@ -23297,7 +23298,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="384" spans="1:16">
+    <row r="384" spans="1:16" hidden="1">
       <c r="A384" t="s">
         <v>1015</v>
       </c>
@@ -23341,7 +23342,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="385" spans="1:16">
+    <row r="385" spans="1:16" hidden="1">
       <c r="A385" t="s">
         <v>1018</v>
       </c>
@@ -23382,7 +23383,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="386" spans="1:16">
+    <row r="386" spans="1:16" hidden="1">
       <c r="A386" t="s">
         <v>1023</v>
       </c>
@@ -23426,7 +23427,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="387" spans="1:16">
+    <row r="387" spans="1:16" hidden="1">
       <c r="A387" t="s">
         <v>1027</v>
       </c>
@@ -23467,7 +23468,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="388" spans="1:16">
+    <row r="388" spans="1:16" hidden="1">
       <c r="A388">
         <v>13003025</v>
       </c>
@@ -23511,7 +23512,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="389" spans="1:16">
+    <row r="389" spans="1:16" hidden="1">
       <c r="A389" t="s">
         <v>1030</v>
       </c>
@@ -23552,7 +23553,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="390" spans="1:16">
+    <row r="390" spans="1:16" hidden="1">
       <c r="A390" t="s">
         <v>1032</v>
       </c>
@@ -23590,7 +23591,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="391" spans="1:16">
+    <row r="391" spans="1:16" hidden="1">
       <c r="A391">
         <v>43700425</v>
       </c>
@@ -23628,7 +23629,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="392" spans="1:16">
+    <row r="392" spans="1:16" hidden="1">
       <c r="A392" t="s">
         <v>1037</v>
       </c>
@@ -23669,7 +23670,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="393" spans="1:16">
+    <row r="393" spans="1:16" hidden="1">
       <c r="A393">
         <v>13300125</v>
       </c>
@@ -23710,7 +23711,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="394" spans="1:16">
+    <row r="394" spans="1:16" hidden="1">
       <c r="A394" t="s">
         <v>1043</v>
       </c>
@@ -23751,7 +23752,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="395" spans="1:16">
+    <row r="395" spans="1:16" hidden="1">
       <c r="A395">
         <v>24003025</v>
       </c>
@@ -23792,7 +23793,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="396" spans="1:16">
+    <row r="396" spans="1:16" hidden="1">
       <c r="A396" t="s">
         <v>1049</v>
       </c>
@@ -23833,7 +23834,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="397" spans="1:16">
+    <row r="397" spans="1:16" hidden="1">
       <c r="A397" t="s">
         <v>1052</v>
       </c>
@@ -23874,7 +23875,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="398" spans="1:16">
+    <row r="398" spans="1:16" hidden="1">
       <c r="A398" t="s">
         <v>1055</v>
       </c>
@@ -23915,7 +23916,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="399" spans="1:16">
+    <row r="399" spans="1:16" hidden="1">
       <c r="A399" t="s">
         <v>1058</v>
       </c>
@@ -23959,7 +23960,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="400" spans="1:16">
+    <row r="400" spans="1:16" hidden="1">
       <c r="A400" t="s">
         <v>1062</v>
       </c>
@@ -24000,7 +24001,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="401" spans="1:16">
+    <row r="401" spans="1:16" hidden="1">
       <c r="A401" t="s">
         <v>1066</v>
       </c>
@@ -24041,7 +24042,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="402" spans="1:16">
+    <row r="402" spans="1:16" hidden="1">
       <c r="A402" t="s">
         <v>1068</v>
       </c>
@@ -24082,7 +24083,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="403" spans="1:16">
+    <row r="403" spans="1:16" hidden="1">
       <c r="A403" t="s">
         <v>1071</v>
       </c>
@@ -24123,7 +24124,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="404" spans="1:16">
+    <row r="404" spans="1:16" hidden="1">
       <c r="A404">
         <v>68002225</v>
       </c>
@@ -24164,7 +24165,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="405" spans="1:16">
+    <row r="405" spans="1:16" hidden="1">
       <c r="A405">
         <v>68002325</v>
       </c>
@@ -24205,7 +24206,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="406" spans="1:16">
+    <row r="406" spans="1:16" hidden="1">
       <c r="A406">
         <v>68002424</v>
       </c>
@@ -24246,7 +24247,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="407" spans="1:16">
+    <row r="407" spans="1:16" hidden="1">
       <c r="A407" t="s">
         <v>1081</v>
       </c>
@@ -24287,7 +24288,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="408" spans="1:16">
+    <row r="408" spans="1:16" hidden="1">
       <c r="A408">
         <v>68002623</v>
       </c>
@@ -24331,7 +24332,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="409" spans="1:16">
+    <row r="409" spans="1:16" hidden="1">
       <c r="A409">
         <v>68002825</v>
       </c>
@@ -24375,7 +24376,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="410" spans="1:16">
+    <row r="410" spans="1:16" hidden="1">
       <c r="A410" t="s">
         <v>1089</v>
       </c>
@@ -24416,7 +24417,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="411" spans="1:16">
+    <row r="411" spans="1:16" hidden="1">
       <c r="A411">
         <v>68003025</v>
       </c>
@@ -24457,7 +24458,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="412" spans="1:16">
+    <row r="412" spans="1:16" hidden="1">
       <c r="A412">
         <v>680031225</v>
       </c>
@@ -24498,7 +24499,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="413" spans="1:16">
+    <row r="413" spans="1:16" hidden="1">
       <c r="A413" t="s">
         <v>1095</v>
       </c>
@@ -24539,7 +24540,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="414" spans="1:16">
+    <row r="414" spans="1:16" hidden="1">
       <c r="A414" t="s">
         <v>1097</v>
       </c>
@@ -24580,7 +24581,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="415" spans="1:16">
+    <row r="415" spans="1:16" hidden="1">
       <c r="A415" t="s">
         <v>1100</v>
       </c>
@@ -24621,7 +24622,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="416" spans="1:16">
+    <row r="416" spans="1:16" hidden="1">
       <c r="A416" t="s">
         <v>1102</v>
       </c>
@@ -24662,7 +24663,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="417" spans="1:16">
+    <row r="417" spans="1:16" hidden="1">
       <c r="A417" t="s">
         <v>1104</v>
       </c>
@@ -24700,7 +24701,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="418" spans="1:16">
+    <row r="418" spans="1:16" hidden="1">
       <c r="A418" t="s">
         <v>1108</v>
       </c>
@@ -24738,7 +24739,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="419" spans="1:16">
+    <row r="419" spans="1:16" hidden="1">
       <c r="A419">
         <v>53800623</v>
       </c>
@@ -24779,7 +24780,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="420" spans="1:16">
+    <row r="420" spans="1:16" hidden="1">
       <c r="A420" t="s">
         <v>1113</v>
       </c>
@@ -24820,7 +24821,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="421" spans="1:16">
+    <row r="421" spans="1:16" hidden="1">
       <c r="A421" t="s">
         <v>1115</v>
       </c>
@@ -24861,7 +24862,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="422" spans="1:16">
+    <row r="422" spans="1:16" hidden="1">
       <c r="A422" t="s">
         <v>1117</v>
       </c>
@@ -24902,7 +24903,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="423" spans="1:16">
+    <row r="423" spans="1:16" hidden="1">
       <c r="A423">
         <v>71501125</v>
       </c>
@@ -24946,7 +24947,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="424" spans="1:16">
+    <row r="424" spans="1:16" hidden="1">
       <c r="A424">
         <v>71500125</v>
       </c>
@@ -24987,7 +24988,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="425" spans="1:16">
+    <row r="425" spans="1:16" hidden="1">
       <c r="A425">
         <v>71500225</v>
       </c>
@@ -25028,7 +25029,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="426" spans="1:16">
+    <row r="426" spans="1:16" hidden="1">
       <c r="A426">
         <v>71500325</v>
       </c>
@@ -25069,7 +25070,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="427" spans="1:16">
+    <row r="427" spans="1:16" hidden="1">
       <c r="A427">
         <v>71500425</v>
       </c>
@@ -25110,7 +25111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="428" spans="1:16">
+    <row r="428" spans="1:16" hidden="1">
       <c r="A428">
         <v>71500525</v>
       </c>
@@ -25151,7 +25152,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="429" spans="1:16">
+    <row r="429" spans="1:16" hidden="1">
       <c r="A429">
         <v>71500625</v>
       </c>
@@ -25192,7 +25193,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="430" spans="1:16">
+    <row r="430" spans="1:16" hidden="1">
       <c r="A430">
         <v>71500725</v>
       </c>
@@ -25233,7 +25234,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="431" spans="1:16">
+    <row r="431" spans="1:16" hidden="1">
       <c r="A431">
         <v>71500825</v>
       </c>
@@ -25277,7 +25278,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="432" spans="1:16">
+    <row r="432" spans="1:16" hidden="1">
       <c r="A432">
         <v>71500925</v>
       </c>
@@ -25321,7 +25322,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="433" spans="1:16">
+    <row r="433" spans="1:16" hidden="1">
       <c r="A433">
         <v>71501025</v>
       </c>
@@ -25365,7 +25366,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="434" spans="1:16">
+    <row r="434" spans="1:16" hidden="1">
       <c r="A434" t="s">
         <v>1131</v>
       </c>
@@ -25406,7 +25407,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="435" spans="1:16">
+    <row r="435" spans="1:16" hidden="1">
       <c r="A435" t="s">
         <v>1132</v>
       </c>
@@ -25447,7 +25448,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="436" spans="1:16">
+    <row r="436" spans="1:16" hidden="1">
       <c r="A436" t="s">
         <v>1133</v>
       </c>
@@ -25488,7 +25489,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="437" spans="1:16">
+    <row r="437" spans="1:16" hidden="1">
       <c r="A437" t="s">
         <v>1135</v>
       </c>
@@ -25529,7 +25530,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="438" spans="1:16">
+    <row r="438" spans="1:16" hidden="1">
       <c r="A438" t="s">
         <v>1137</v>
       </c>
@@ -25570,7 +25571,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="439" spans="1:16">
+    <row r="439" spans="1:16" hidden="1">
       <c r="A439" t="s">
         <v>1139</v>
       </c>
@@ -25611,7 +25612,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="440" spans="1:16">
+    <row r="440" spans="1:16" hidden="1">
       <c r="A440" t="s">
         <v>1141</v>
       </c>
@@ -25652,7 +25653,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="441" spans="1:16">
+    <row r="441" spans="1:16" hidden="1">
       <c r="A441" t="s">
         <v>1144</v>
       </c>
@@ -25696,7 +25697,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="442" spans="1:16">
+    <row r="442" spans="1:16" hidden="1">
       <c r="A442" t="s">
         <v>1146</v>
       </c>
@@ -25740,7 +25741,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="443" spans="1:16">
+    <row r="443" spans="1:16" hidden="1">
       <c r="A443" t="s">
         <v>1148</v>
       </c>
@@ -25781,7 +25782,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="444" spans="1:16">
+    <row r="444" spans="1:16" hidden="1">
       <c r="A444" t="s">
         <v>1150</v>
       </c>
@@ -25822,7 +25823,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="445" spans="1:16">
+    <row r="445" spans="1:16" hidden="1">
       <c r="A445" t="s">
         <v>1153</v>
       </c>
@@ -25863,7 +25864,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="446" spans="1:16">
+    <row r="446" spans="1:16" hidden="1">
       <c r="A446" t="s">
         <v>1157</v>
       </c>
@@ -25904,7 +25905,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="447" spans="1:16">
+    <row r="447" spans="1:16" hidden="1">
       <c r="A447" t="s">
         <v>1159</v>
       </c>
@@ -25942,7 +25943,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="448" spans="1:16">
+    <row r="448" spans="1:16" hidden="1">
       <c r="A448" t="s">
         <v>1162</v>
       </c>
@@ -25983,7 +25984,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="449" spans="1:16">
+    <row r="449" spans="1:16" hidden="1">
       <c r="A449" t="s">
         <v>1164</v>
       </c>
@@ -26024,7 +26025,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="450" spans="1:16">
+    <row r="450" spans="1:16" hidden="1">
       <c r="A450" t="s">
         <v>1166</v>
       </c>
@@ -26065,7 +26066,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="451" spans="1:16">
+    <row r="451" spans="1:16" hidden="1">
       <c r="A451" t="s">
         <v>1169</v>
       </c>
@@ -26106,7 +26107,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="452" spans="1:16">
+    <row r="452" spans="1:16" hidden="1">
       <c r="A452" t="s">
         <v>1171</v>
       </c>
@@ -26150,7 +26151,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="453" spans="1:16">
+    <row r="453" spans="1:16" hidden="1">
       <c r="A453" t="s">
         <v>1173</v>
       </c>
@@ -26191,7 +26192,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="454" spans="1:16">
+    <row r="454" spans="1:16" hidden="1">
       <c r="A454" t="s">
         <v>1175</v>
       </c>
@@ -26235,7 +26236,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="455" spans="1:16">
+    <row r="455" spans="1:16" hidden="1">
       <c r="A455" t="s">
         <v>1177</v>
       </c>
@@ -26279,7 +26280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="456" spans="1:16">
+    <row r="456" spans="1:16" hidden="1">
       <c r="A456" t="s">
         <v>1179</v>
       </c>
@@ -26323,7 +26324,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="457" spans="1:16">
+    <row r="457" spans="1:16" hidden="1">
       <c r="A457" t="s">
         <v>1182</v>
       </c>
@@ -26364,7 +26365,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="458" spans="1:16">
+    <row r="458" spans="1:16" hidden="1">
       <c r="A458" t="s">
         <v>1186</v>
       </c>
@@ -26402,7 +26403,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="459" spans="1:16">
+    <row r="459" spans="1:16" hidden="1">
       <c r="A459" t="s">
         <v>1188</v>
       </c>
@@ -26446,7 +26447,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="460" spans="1:16">
+    <row r="460" spans="1:16" hidden="1">
       <c r="A460" t="s">
         <v>1192</v>
       </c>
@@ -26487,7 +26488,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="461" spans="1:16">
+    <row r="461" spans="1:16" hidden="1">
       <c r="A461" t="s">
         <v>1195</v>
       </c>
@@ -26528,7 +26529,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="462" spans="1:16">
+    <row r="462" spans="1:16" hidden="1">
       <c r="A462" t="s">
         <v>1197</v>
       </c>
@@ -26569,7 +26570,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="463" spans="1:16">
+    <row r="463" spans="1:16" hidden="1">
       <c r="A463" t="s">
         <v>1200</v>
       </c>
@@ -26610,7 +26611,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="464" spans="1:16">
+    <row r="464" spans="1:16" hidden="1">
       <c r="A464" t="s">
         <v>1203</v>
       </c>
@@ -26651,7 +26652,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="465" spans="1:16">
+    <row r="465" spans="1:16" hidden="1">
       <c r="A465" t="s">
         <v>1205</v>
       </c>
@@ -26692,7 +26693,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="466" spans="1:16">
+    <row r="466" spans="1:16" hidden="1">
       <c r="A466" t="s">
         <v>1208</v>
       </c>
@@ -26736,7 +26737,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="467" spans="1:16">
+    <row r="467" spans="1:16" hidden="1">
       <c r="A467" t="s">
         <v>1210</v>
       </c>
@@ -26777,7 +26778,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="468" spans="1:16">
+    <row r="468" spans="1:16" hidden="1">
       <c r="A468">
         <v>16003124</v>
       </c>
@@ -26818,7 +26819,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="469" spans="1:16">
+    <row r="469" spans="1:16" hidden="1">
       <c r="A469" t="s">
         <v>1214</v>
       </c>
@@ -26862,7 +26863,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="470" spans="1:16">
+    <row r="470" spans="1:16" hidden="1">
       <c r="A470" t="s">
         <v>1216</v>
       </c>
@@ -26906,7 +26907,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="471" spans="1:16">
+    <row r="471" spans="1:16" hidden="1">
       <c r="A471" t="s">
         <v>1218</v>
       </c>
@@ -26950,7 +26951,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="472" spans="1:16">
+    <row r="472" spans="1:16" hidden="1">
       <c r="A472" t="s">
         <v>1220</v>
       </c>
@@ -26988,7 +26989,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="473" spans="1:16">
+    <row r="473" spans="1:16" hidden="1">
       <c r="A473" t="s">
         <v>1223</v>
       </c>
@@ -27032,7 +27033,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="474" spans="1:16">
+    <row r="474" spans="1:16" hidden="1">
       <c r="A474" t="s">
         <v>1225</v>
       </c>
@@ -27067,7 +27068,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="475" spans="1:16">
+    <row r="475" spans="1:16" hidden="1">
       <c r="A475" t="s">
         <v>1228</v>
       </c>
@@ -27105,7 +27106,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="476" spans="1:16">
+    <row r="476" spans="1:16" hidden="1">
       <c r="A476">
         <v>27100522</v>
       </c>
@@ -27146,7 +27147,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="477" spans="1:16">
+    <row r="477" spans="1:16" hidden="1">
       <c r="A477" t="s">
         <v>1232</v>
       </c>
@@ -27184,7 +27185,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="478" spans="1:16">
+    <row r="478" spans="1:16" hidden="1">
       <c r="A478" t="s">
         <v>1236</v>
       </c>
@@ -27225,7 +27226,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="479" spans="1:16">
+    <row r="479" spans="1:16" hidden="1">
       <c r="B479" t="s">
         <v>55</v>
       </c>
@@ -27263,7 +27264,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="480" spans="1:16">
+    <row r="480" spans="1:16" hidden="1">
       <c r="A480" t="s">
         <v>1240</v>
       </c>
@@ -27304,7 +27305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="481" spans="1:18">
+    <row r="481" spans="1:18" hidden="1">
       <c r="A481" t="s">
         <v>1242</v>
       </c>
@@ -27348,7 +27349,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="482" spans="1:18">
+    <row r="482" spans="1:18" hidden="1">
       <c r="A482" t="s">
         <v>1246</v>
       </c>
@@ -27386,7 +27387,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="483" spans="1:18">
+    <row r="483" spans="1:18" hidden="1">
       <c r="A483" t="s">
         <v>1249</v>
       </c>
@@ -27427,7 +27428,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="484" spans="1:18">
+    <row r="484" spans="1:18" hidden="1">
       <c r="A484" t="s">
         <v>1252</v>
       </c>
@@ -27465,7 +27466,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="485" spans="1:18">
+    <row r="485" spans="1:18" hidden="1">
       <c r="A485">
         <v>43700325</v>
       </c>
@@ -27503,7 +27504,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="486" spans="1:18">
+    <row r="486" spans="1:18" hidden="1">
       <c r="A486">
         <v>43700524</v>
       </c>
@@ -27541,7 +27542,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="487" spans="1:18">
+    <row r="487" spans="1:18" hidden="1">
       <c r="A487" t="s">
         <v>1255</v>
       </c>
@@ -27582,7 +27583,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="488" spans="1:18">
+    <row r="488" spans="1:18" hidden="1">
       <c r="A488" t="s">
         <v>1256</v>
       </c>
@@ -27623,7 +27624,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="489" spans="1:18">
+    <row r="489" spans="1:18" hidden="1">
       <c r="A489" t="s">
         <v>1257</v>
       </c>
@@ -27664,7 +27665,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="490" spans="1:18">
+    <row r="490" spans="1:18" hidden="1">
       <c r="A490" t="s">
         <v>1259</v>
       </c>
@@ -27705,7 +27706,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="491" spans="1:18">
+    <row r="491" spans="1:18" hidden="1">
       <c r="A491" t="s">
         <v>1261</v>
       </c>
@@ -27746,7 +27747,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="492" spans="1:18">
+    <row r="492" spans="1:18" hidden="1">
       <c r="A492" t="s">
         <v>1262</v>
       </c>
@@ -27787,7 +27788,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="493" spans="1:18">
+    <row r="493" spans="1:18" hidden="1">
       <c r="A493" t="s">
         <v>1264</v>
       </c>
@@ -27872,7 +27873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="495" spans="1:18">
+    <row r="495" spans="1:18" hidden="1">
       <c r="A495">
         <v>24000925</v>
       </c>
@@ -27913,7 +27914,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="496" spans="1:18">
+    <row r="496" spans="1:18" hidden="1">
       <c r="A496" t="s">
         <v>1274</v>
       </c>
@@ -27954,7 +27955,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="497" spans="1:16">
+    <row r="497" spans="1:16" hidden="1">
       <c r="A497" t="s">
         <v>1278</v>
       </c>
@@ -27995,7 +27996,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="498" spans="1:16">
+    <row r="498" spans="1:16" hidden="1">
       <c r="A498">
         <v>24001825</v>
       </c>
@@ -28036,7 +28037,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="499" spans="1:16">
+    <row r="499" spans="1:16" hidden="1">
       <c r="A499" t="s">
         <v>1283</v>
       </c>
@@ -28074,7 +28075,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="500" spans="1:16">
+    <row r="500" spans="1:16" hidden="1">
       <c r="A500" t="s">
         <v>1286</v>
       </c>
@@ -28118,7 +28119,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="501" spans="1:16">
+    <row r="501" spans="1:16" hidden="1">
       <c r="A501" t="s">
         <v>1290</v>
       </c>
@@ -28156,7 +28157,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="502" spans="1:16">
+    <row r="502" spans="1:16" hidden="1">
       <c r="A502" t="s">
         <v>1295</v>
       </c>
@@ -28197,7 +28198,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="503" spans="1:16">
+    <row r="503" spans="1:16" hidden="1">
       <c r="A503" t="s">
         <v>1298</v>
       </c>
@@ -28238,7 +28239,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="504" spans="1:16">
+    <row r="504" spans="1:16" hidden="1">
       <c r="A504" t="s">
         <v>1301</v>
       </c>
@@ -28279,7 +28280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="505" spans="1:16">
+    <row r="505" spans="1:16" hidden="1">
       <c r="A505" t="s">
         <v>1303</v>
       </c>
@@ -28320,7 +28321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="506" spans="1:16">
+    <row r="506" spans="1:16" hidden="1">
       <c r="A506" t="s">
         <v>1306</v>
       </c>
@@ -28361,7 +28362,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="507" spans="1:16">
+    <row r="507" spans="1:16" hidden="1">
       <c r="A507" t="s">
         <v>1309</v>
       </c>
@@ -28402,7 +28403,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="508" spans="1:16">
+    <row r="508" spans="1:16" hidden="1">
       <c r="A508" t="s">
         <v>1314</v>
       </c>
@@ -28443,7 +28444,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="509" spans="1:16">
+    <row r="509" spans="1:16" hidden="1">
       <c r="A509" t="s">
         <v>1316</v>
       </c>
@@ -28484,7 +28485,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="510" spans="1:16">
+    <row r="510" spans="1:16" hidden="1">
       <c r="A510" t="s">
         <v>1318</v>
       </c>
@@ -28525,7 +28526,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="511" spans="1:16">
+    <row r="511" spans="1:16" hidden="1">
       <c r="A511" t="s">
         <v>1319</v>
       </c>
@@ -28566,7 +28567,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="512" spans="1:16">
+    <row r="512" spans="1:16" hidden="1">
       <c r="A512" t="s">
         <v>1321</v>
       </c>
@@ -28607,7 +28608,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="513" spans="1:16">
+    <row r="513" spans="1:16" hidden="1">
       <c r="A513" t="s">
         <v>1323</v>
       </c>
@@ -28648,7 +28649,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="514" spans="1:16">
+    <row r="514" spans="1:16" hidden="1">
       <c r="A514" t="s">
         <v>1325</v>
       </c>
@@ -28689,7 +28690,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="515" spans="1:16">
+    <row r="515" spans="1:16" hidden="1">
       <c r="A515" t="s">
         <v>1327</v>
       </c>
@@ -28730,7 +28731,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="516" spans="1:16">
+    <row r="516" spans="1:16" hidden="1">
       <c r="A516" t="s">
         <v>1329</v>
       </c>
@@ -28771,7 +28772,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="517" spans="1:16">
+    <row r="517" spans="1:16" hidden="1">
       <c r="A517" t="s">
         <v>1330</v>
       </c>
@@ -28812,7 +28813,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="518" spans="1:16">
+    <row r="518" spans="1:16" hidden="1">
       <c r="A518" t="s">
         <v>1334</v>
       </c>
@@ -28847,7 +28848,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="519" spans="1:16">
+    <row r="519" spans="1:16" hidden="1">
       <c r="A519" t="s">
         <v>1336</v>
       </c>
@@ -28882,7 +28883,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="520" spans="1:16">
+    <row r="520" spans="1:16" hidden="1">
       <c r="A520" t="s">
         <v>1339</v>
       </c>
@@ -28920,7 +28921,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="521" spans="1:16">
+    <row r="521" spans="1:16" hidden="1">
       <c r="A521" t="s">
         <v>1343</v>
       </c>
@@ -28958,7 +28959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="522" spans="1:16">
+    <row r="522" spans="1:16" hidden="1">
       <c r="A522" t="s">
         <v>1346</v>
       </c>
@@ -28996,7 +28997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="523" spans="1:16">
+    <row r="523" spans="1:16" hidden="1">
       <c r="A523" t="s">
         <v>1349</v>
       </c>
@@ -29031,7 +29032,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="524" spans="1:16">
+    <row r="524" spans="1:16" hidden="1">
       <c r="A524" t="s">
         <v>1352</v>
       </c>
@@ -29069,7 +29070,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="525" spans="1:16">
+    <row r="525" spans="1:16" hidden="1">
       <c r="A525" t="s">
         <v>1355</v>
       </c>
@@ -29107,7 +29108,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="526" spans="1:16">
+    <row r="526" spans="1:16" hidden="1">
       <c r="A526" t="s">
         <v>1358</v>
       </c>
@@ -29145,7 +29146,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="527" spans="1:16">
+    <row r="527" spans="1:16" hidden="1">
       <c r="A527" t="s">
         <v>1361</v>
       </c>
@@ -29183,7 +29184,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="528" spans="1:16">
+    <row r="528" spans="1:16" hidden="1">
       <c r="A528" t="s">
         <v>1363</v>
       </c>
@@ -29221,7 +29222,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="529" spans="1:16">
+    <row r="529" spans="1:16" hidden="1">
       <c r="A529" t="s">
         <v>1365</v>
       </c>
@@ -29259,7 +29260,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="530" spans="1:16">
+    <row r="530" spans="1:16" hidden="1">
       <c r="A530" t="s">
         <v>1367</v>
       </c>
@@ -29297,7 +29298,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="531" spans="1:16">
+    <row r="531" spans="1:16" hidden="1">
       <c r="A531" t="s">
         <v>1369</v>
       </c>
@@ -29335,7 +29336,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="532" spans="1:16">
+    <row r="532" spans="1:16" hidden="1">
       <c r="A532" t="s">
         <v>1371</v>
       </c>
@@ -29373,7 +29374,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="533" spans="1:16">
+    <row r="533" spans="1:16" hidden="1">
       <c r="A533" t="s">
         <v>1372</v>
       </c>
@@ -29411,7 +29412,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="534" spans="1:16">
+    <row r="534" spans="1:16" hidden="1">
       <c r="A534" t="s">
         <v>1375</v>
       </c>
@@ -29449,7 +29450,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="535" spans="1:16">
+    <row r="535" spans="1:16" hidden="1">
       <c r="A535" t="s">
         <v>1378</v>
       </c>
@@ -29487,7 +29488,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="536" spans="1:16">
+    <row r="536" spans="1:16" hidden="1">
       <c r="A536" t="s">
         <v>1381</v>
       </c>
@@ -29525,7 +29526,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="537" spans="1:16">
+    <row r="537" spans="1:16" hidden="1">
       <c r="A537" t="s">
         <v>1383</v>
       </c>
@@ -29563,7 +29564,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="538" spans="1:16">
+    <row r="538" spans="1:16" hidden="1">
       <c r="A538" t="s">
         <v>1386</v>
       </c>
@@ -29601,7 +29602,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="539" spans="1:16">
+    <row r="539" spans="1:16" hidden="1">
       <c r="A539" t="s">
         <v>1388</v>
       </c>
@@ -29639,7 +29640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="540" spans="1:16">
+    <row r="540" spans="1:16" hidden="1">
       <c r="A540" t="s">
         <v>1390</v>
       </c>
@@ -29677,7 +29678,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="541" spans="1:16">
+    <row r="541" spans="1:16" hidden="1">
       <c r="A541" t="s">
         <v>1392</v>
       </c>
@@ -29715,7 +29716,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="542" spans="1:16">
+    <row r="542" spans="1:16" hidden="1">
       <c r="A542" t="s">
         <v>1395</v>
       </c>
@@ -29753,7 +29754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="543" spans="1:16">
+    <row r="543" spans="1:16" hidden="1">
       <c r="A543" t="s">
         <v>1398</v>
       </c>
@@ -29791,7 +29792,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="544" spans="1:16">
+    <row r="544" spans="1:16" hidden="1">
       <c r="A544" t="s">
         <v>1400</v>
       </c>
@@ -29829,7 +29830,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="545" spans="1:16">
+    <row r="545" spans="1:16" hidden="1">
       <c r="A545" t="s">
         <v>1402</v>
       </c>
@@ -29870,7 +29871,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="546" spans="1:16">
+    <row r="546" spans="1:16" hidden="1">
       <c r="A546" t="s">
         <v>1404</v>
       </c>
@@ -29911,7 +29912,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="547" spans="1:16">
+    <row r="547" spans="1:16" hidden="1">
       <c r="A547" t="s">
         <v>1406</v>
       </c>
@@ -29952,7 +29953,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="548" spans="1:16">
+    <row r="548" spans="1:16" hidden="1">
       <c r="A548" t="s">
         <v>1408</v>
       </c>
@@ -29993,7 +29994,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="549" spans="1:16">
+    <row r="549" spans="1:16" hidden="1">
       <c r="A549" t="s">
         <v>1410</v>
       </c>
@@ -30034,7 +30035,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="550" spans="1:16">
+    <row r="550" spans="1:16" hidden="1">
       <c r="A550" t="s">
         <v>1412</v>
       </c>
@@ -30072,7 +30073,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="551" spans="1:16">
+    <row r="551" spans="1:16" hidden="1">
       <c r="A551" t="s">
         <v>1418</v>
       </c>
@@ -30110,7 +30111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="552" spans="1:16">
+    <row r="552" spans="1:16" hidden="1">
       <c r="A552" t="s">
         <v>1420</v>
       </c>
@@ -30145,7 +30146,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="553" spans="1:16">
+    <row r="553" spans="1:16" hidden="1">
       <c r="A553" t="s">
         <v>1424</v>
       </c>
@@ -30180,7 +30181,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="554" spans="1:16">
+    <row r="554" spans="1:16" hidden="1">
       <c r="A554" t="s">
         <v>1428</v>
       </c>
@@ -30215,7 +30216,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="555" spans="1:16">
+    <row r="555" spans="1:16" hidden="1">
       <c r="A555" t="s">
         <v>1431</v>
       </c>
@@ -30250,7 +30251,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="556" spans="1:16">
+    <row r="556" spans="1:16" hidden="1">
       <c r="A556" t="s">
         <v>1435</v>
       </c>
@@ -30288,7 +30289,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="557" spans="1:16">
+    <row r="557" spans="1:16" hidden="1">
       <c r="A557" t="s">
         <v>1438</v>
       </c>
@@ -30323,7 +30324,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="558" spans="1:16">
+    <row r="558" spans="1:16" hidden="1">
       <c r="A558" t="s">
         <v>1442</v>
       </c>
@@ -30358,7 +30359,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="559" spans="1:16">
+    <row r="559" spans="1:16" hidden="1">
       <c r="A559" t="s">
         <v>1445</v>
       </c>
@@ -30396,7 +30397,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="560" spans="1:16">
+    <row r="560" spans="1:16" hidden="1">
       <c r="A560" t="s">
         <v>1448</v>
       </c>
@@ -30434,7 +30435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="561" spans="1:16">
+    <row r="561" spans="1:16" hidden="1">
       <c r="A561" t="s">
         <v>1452</v>
       </c>
@@ -30472,7 +30473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="562" spans="1:16">
+    <row r="562" spans="1:16" hidden="1">
       <c r="A562" t="s">
         <v>1457</v>
       </c>
@@ -30511,7 +30512,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R562" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R562" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="17">
+      <filters>
+        <filter val="Oui"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -31187,16 +31194,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31209,6 +31206,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52031,19 +52038,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -52324,14 +52318,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C24CFEE-BEAC-4E4D-A7E1-003CCD55EA2D}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13395235-6B7E-4FBA-BA06-F85BF3A036E9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7954,7 +7954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>26712023</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>26712123</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>26712223</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>77</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:18" hidden="1">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>84</v>
       </c>
@@ -8358,7 +8358,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="12" spans="1:18" hidden="1">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>88</v>
       </c>
@@ -8396,7 +8396,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="13" spans="1:18" hidden="1">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -8437,7 +8437,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="14" spans="1:18" hidden="1">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>94</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="15" spans="1:18" hidden="1">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -8607,7 +8607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:18" hidden="1">
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:18" hidden="1">
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
         <v>117</v>
       </c>
@@ -8806,7 +8806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="23" spans="1:18" hidden="1">
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
         <v>119</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="24" spans="1:18" hidden="1">
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="25" spans="1:18" hidden="1">
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -8920,7 +8920,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="26" spans="1:18" hidden="1">
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
         <v>128</v>
       </c>
@@ -8961,7 +8961,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="27" spans="1:18" hidden="1">
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
         <v>130</v>
       </c>
@@ -8999,7 +8999,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="28" spans="1:18" hidden="1">
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="29" spans="1:18" hidden="1">
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
         <v>135</v>
       </c>
@@ -9075,7 +9075,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="30" spans="1:18" hidden="1">
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="31" spans="1:18" hidden="1">
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -9157,7 +9157,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="32" spans="1:18" hidden="1">
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -9198,7 +9198,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="33" spans="1:16" hidden="1">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>149</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="34" spans="1:16" hidden="1">
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
         <v>152</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="35" spans="1:16" hidden="1">
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
         <v>155</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="36" spans="1:16" hidden="1">
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
         <v>157</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="37" spans="1:16" hidden="1">
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
         <v>159</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="38" spans="1:16" hidden="1">
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="39" spans="1:16" hidden="1">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="40" spans="1:16" hidden="1">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>168</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="41" spans="1:16" hidden="1">
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
         <v>170</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="42" spans="1:16" hidden="1">
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
         <v>174</v>
       </c>
@@ -9599,7 +9599,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="43" spans="1:16" hidden="1">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>179</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="44" spans="1:16" hidden="1">
+    <row r="44" spans="1:16">
       <c r="A44">
         <v>26600424</v>
       </c>
@@ -9684,7 +9684,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="45" spans="1:16" hidden="1">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>186</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="46" spans="1:16" hidden="1">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>190</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="47" spans="1:16" hidden="1">
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
         <v>193</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="48" spans="1:16" hidden="1">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>195</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="49" spans="1:16" hidden="1">
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
         <v>199</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="50" spans="1:16" hidden="1">
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
         <v>202</v>
       </c>
@@ -9918,7 +9918,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="51" spans="1:16" hidden="1">
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
         <v>204</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="52" spans="1:16" hidden="1">
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
         <v>208</v>
       </c>
@@ -9997,7 +9997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="53" spans="1:16" hidden="1">
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
         <v>210</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="54" spans="1:16" hidden="1">
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
         <v>211</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="55" spans="1:16" hidden="1">
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
         <v>215</v>
       </c>
@@ -10111,7 +10111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="56" spans="1:16" hidden="1">
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -10155,7 +10155,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="57" spans="1:16" hidden="1">
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
         <v>222</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="58" spans="1:16" hidden="1">
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
         <v>224</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="59" spans="1:16" hidden="1">
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
         <v>226</v>
       </c>
@@ -10272,7 +10272,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="60" spans="1:16" hidden="1">
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
         <v>228</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="61" spans="1:16" hidden="1">
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
         <v>231</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="62" spans="1:16" hidden="1">
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
         <v>232</v>
       </c>
@@ -10389,7 +10389,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="63" spans="1:16" hidden="1">
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
         <v>236</v>
       </c>
@@ -10427,7 +10427,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="64" spans="1:16" hidden="1">
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
         <v>238</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="65" spans="1:16" hidden="1">
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
         <v>242</v>
       </c>
@@ -10509,7 +10509,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="66" spans="1:16" hidden="1">
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
         <v>245</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="67" spans="1:16" hidden="1">
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
         <v>248</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="68" spans="1:16" hidden="1">
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
         <v>249</v>
       </c>
@@ -10623,7 +10623,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="69" spans="1:16" hidden="1">
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
         <v>252</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="70" spans="1:16" hidden="1">
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
         <v>255</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="71" spans="1:16" hidden="1">
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
         <v>258</v>
       </c>
@@ -10737,7 +10737,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="72" spans="1:16" hidden="1">
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
         <v>261</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="73" spans="1:16" hidden="1">
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
         <v>265</v>
       </c>
@@ -10822,7 +10822,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="74" spans="1:16" hidden="1">
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
         <v>270</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="75" spans="1:16" hidden="1">
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
         <v>273</v>
       </c>
@@ -10901,7 +10901,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="76" spans="1:16" hidden="1">
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
         <v>277</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="77" spans="1:16" hidden="1">
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
         <v>281</v>
       </c>
@@ -10977,7 +10977,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="78" spans="1:16" hidden="1">
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
         <v>283</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="79" spans="1:16" hidden="1">
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
         <v>286</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="80" spans="1:16" hidden="1">
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
         <v>289</v>
       </c>
@@ -11091,7 +11091,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="81" spans="1:16" hidden="1">
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
         <v>293</v>
       </c>
@@ -11129,7 +11129,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="82" spans="1:16" hidden="1">
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
         <v>295</v>
       </c>
@@ -11167,7 +11167,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="83" spans="1:16" hidden="1">
+    <row r="83" spans="1:16">
       <c r="A83" t="s">
         <v>297</v>
       </c>
@@ -11205,7 +11205,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="84" spans="1:16" hidden="1">
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
         <v>301</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="85" spans="1:16" hidden="1">
+    <row r="85" spans="1:16">
       <c r="A85" t="s">
         <v>305</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="86" spans="1:16" hidden="1">
+    <row r="86" spans="1:16">
       <c r="A86" t="s">
         <v>307</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="87" spans="1:16" hidden="1">
+    <row r="87" spans="1:16">
       <c r="A87" t="s">
         <v>309</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="88" spans="1:16" hidden="1">
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
         <v>312</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="89" spans="1:16" hidden="1">
+    <row r="89" spans="1:16">
       <c r="A89">
         <v>10902324</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="90" spans="1:16" hidden="1">
+    <row r="90" spans="1:16">
       <c r="A90" t="s">
         <v>318</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="91" spans="1:16" hidden="1">
+    <row r="91" spans="1:16">
       <c r="A91" t="s">
         <v>321</v>
       </c>
@@ -11503,7 +11503,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="92" spans="1:16" hidden="1">
+    <row r="92" spans="1:16">
       <c r="A92">
         <v>15401623</v>
       </c>
@@ -11538,7 +11538,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="93" spans="1:16" hidden="1">
+    <row r="93" spans="1:16">
       <c r="A93" t="s">
         <v>325</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="94" spans="1:16" hidden="1">
+    <row r="94" spans="1:16">
       <c r="A94" t="s">
         <v>328</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="95" spans="1:16" hidden="1">
+    <row r="95" spans="1:16">
       <c r="A95" t="s">
         <v>330</v>
       </c>
@@ -11661,7 +11661,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="96" spans="1:16" hidden="1">
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
         <v>336</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="97" spans="1:16" hidden="1">
+    <row r="97" spans="1:16">
       <c r="A97">
         <v>35800325</v>
       </c>
@@ -11743,7 +11743,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="98" spans="1:16" hidden="1">
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
         <v>341</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="99" spans="1:16" hidden="1">
+    <row r="99" spans="1:16">
       <c r="A99">
         <v>28500125</v>
       </c>
@@ -11828,7 +11828,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="100" spans="1:16" hidden="1">
+    <row r="100" spans="1:16">
       <c r="A100">
         <v>60502223</v>
       </c>
@@ -11869,7 +11869,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="101" spans="1:16" hidden="1">
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
         <v>345</v>
       </c>
@@ -11910,7 +11910,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="102" spans="1:16" hidden="1">
+    <row r="102" spans="1:16">
       <c r="A102">
         <v>25000124</v>
       </c>
@@ -11951,7 +11951,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="103" spans="1:16" hidden="1">
+    <row r="103" spans="1:16">
       <c r="A103" t="s">
         <v>351</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="104" spans="1:16" hidden="1">
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
         <v>353</v>
       </c>
@@ -12033,7 +12033,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="105" spans="1:16" hidden="1">
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
         <v>355</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="106" spans="1:16" hidden="1">
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
         <v>358</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="107" spans="1:16" hidden="1">
+    <row r="107" spans="1:16">
       <c r="A107" t="s">
         <v>361</v>
       </c>
@@ -12156,7 +12156,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="108" spans="1:16" hidden="1">
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
         <v>362</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="109" spans="1:16" hidden="1">
+    <row r="109" spans="1:16">
       <c r="A109" t="s">
         <v>365</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="110" spans="1:16" hidden="1">
+    <row r="110" spans="1:16">
       <c r="A110">
         <v>35800125</v>
       </c>
@@ -12270,7 +12270,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="111" spans="1:16" hidden="1">
+    <row r="111" spans="1:16">
       <c r="A111">
         <v>35800224</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="112" spans="1:16" hidden="1">
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
         <v>372</v>
       </c>
@@ -12343,7 +12343,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="113" spans="1:16" hidden="1">
+    <row r="113" spans="1:16">
       <c r="A113">
         <v>27202325</v>
       </c>
@@ -12381,7 +12381,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="114" spans="1:16" hidden="1">
+    <row r="114" spans="1:16">
       <c r="A114">
         <v>35800624</v>
       </c>
@@ -12425,7 +12425,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="115" spans="1:16" hidden="1">
+    <row r="115" spans="1:16">
       <c r="A115" t="s">
         <v>377</v>
       </c>
@@ -12466,7 +12466,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="116" spans="1:16" hidden="1">
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
         <v>380</v>
       </c>
@@ -12510,7 +12510,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="117" spans="1:16" hidden="1">
+    <row r="117" spans="1:16">
       <c r="A117" t="s">
         <v>382</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="118" spans="1:16" hidden="1">
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
         <v>384</v>
       </c>
@@ -12586,7 +12586,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="119" spans="1:16" hidden="1">
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
         <v>386</v>
       </c>
@@ -12630,7 +12630,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="120" spans="1:16" hidden="1">
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
         <v>390</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="121" spans="1:16" hidden="1">
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
         <v>393</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="122" spans="1:16" hidden="1">
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
         <v>396</v>
       </c>
@@ -12744,7 +12744,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="123" spans="1:16" hidden="1">
+    <row r="123" spans="1:16">
       <c r="A123" t="s">
         <v>398</v>
       </c>
@@ -12785,7 +12785,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="124" spans="1:16" hidden="1">
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
         <v>400</v>
       </c>
@@ -12826,7 +12826,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="125" spans="1:16" hidden="1">
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
         <v>402</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="126" spans="1:16" hidden="1">
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
         <v>403</v>
       </c>
@@ -12902,7 +12902,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="127" spans="1:16" hidden="1">
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
         <v>406</v>
       </c>
@@ -12943,7 +12943,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="128" spans="1:16" hidden="1">
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
         <v>409</v>
       </c>
@@ -12984,7 +12984,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="129" spans="1:16" hidden="1">
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
         <v>413</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="130" spans="1:16" hidden="1">
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
         <v>415</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="131" spans="1:16" hidden="1">
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
         <v>418</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="132" spans="1:16" hidden="1">
+    <row r="132" spans="1:16">
       <c r="A132">
         <v>65000724</v>
       </c>
@@ -13148,7 +13148,7 @@
         <v>46182</v>
       </c>
     </row>
-    <row r="133" spans="1:16" hidden="1">
+    <row r="133" spans="1:16">
       <c r="A133" t="s">
         <v>425</v>
       </c>
@@ -13189,7 +13189,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="134" spans="1:16" hidden="1">
+    <row r="134" spans="1:16">
       <c r="A134" t="s">
         <v>428</v>
       </c>
@@ -13233,7 +13233,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="135" spans="1:16" hidden="1">
+    <row r="135" spans="1:16">
       <c r="A135" t="s">
         <v>431</v>
       </c>
@@ -13274,7 +13274,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="136" spans="1:16" hidden="1">
+    <row r="136" spans="1:16">
       <c r="A136" t="s">
         <v>434</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="137" spans="1:16" hidden="1">
+    <row r="137" spans="1:16">
       <c r="A137" t="s">
         <v>436</v>
       </c>
@@ -13353,7 +13353,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="138" spans="1:16" hidden="1">
+    <row r="138" spans="1:16">
       <c r="A138" t="s">
         <v>438</v>
       </c>
@@ -13391,7 +13391,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="139" spans="1:16" hidden="1">
+    <row r="139" spans="1:16">
       <c r="A139" t="s">
         <v>441</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="140" spans="1:16" hidden="1">
+    <row r="140" spans="1:16">
       <c r="A140" t="s">
         <v>443</v>
       </c>
@@ -13473,7 +13473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="141" spans="1:16" hidden="1">
+    <row r="141" spans="1:16">
       <c r="A141" t="s">
         <v>444</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="142" spans="1:16" hidden="1">
+    <row r="142" spans="1:16">
       <c r="A142">
         <v>35900524</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="143" spans="1:16" hidden="1">
+    <row r="143" spans="1:16">
       <c r="A143" t="s">
         <v>448</v>
       </c>
@@ -13596,7 +13596,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="144" spans="1:16" hidden="1">
+    <row r="144" spans="1:16">
       <c r="A144" t="s">
         <v>452</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="145" spans="1:16" hidden="1">
+    <row r="145" spans="1:16">
       <c r="A145" t="s">
         <v>455</v>
       </c>
@@ -13681,7 +13681,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="146" spans="1:16" hidden="1">
+    <row r="146" spans="1:16">
       <c r="A146" t="s">
         <v>456</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="147" spans="1:16" hidden="1">
+    <row r="147" spans="1:16">
       <c r="A147" t="s">
         <v>459</v>
       </c>
@@ -13760,7 +13760,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="148" spans="1:16" hidden="1">
+    <row r="148" spans="1:16">
       <c r="A148" t="s">
         <v>462</v>
       </c>
@@ -13795,7 +13795,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="149" spans="1:16" hidden="1">
+    <row r="149" spans="1:16">
       <c r="A149" t="s">
         <v>464</v>
       </c>
@@ -13836,7 +13836,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="150" spans="1:16" hidden="1">
+    <row r="150" spans="1:16">
       <c r="A150" t="s">
         <v>466</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="151" spans="1:16" hidden="1">
+    <row r="151" spans="1:16">
       <c r="A151" t="s">
         <v>469</v>
       </c>
@@ -13915,7 +13915,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="152" spans="1:16" hidden="1">
+    <row r="152" spans="1:16">
       <c r="A152" t="s">
         <v>473</v>
       </c>
@@ -13956,7 +13956,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="153" spans="1:16" hidden="1">
+    <row r="153" spans="1:16">
       <c r="A153" t="s">
         <v>477</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="154" spans="1:16" hidden="1">
+    <row r="154" spans="1:16">
       <c r="A154" t="s">
         <v>480</v>
       </c>
@@ -14038,7 +14038,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="155" spans="1:16" hidden="1">
+    <row r="155" spans="1:16">
       <c r="A155" t="s">
         <v>483</v>
       </c>
@@ -14079,7 +14079,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="156" spans="1:16" hidden="1">
+    <row r="156" spans="1:16">
       <c r="A156" t="s">
         <v>486</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="157" spans="1:16" hidden="1">
+    <row r="157" spans="1:16">
       <c r="A157" t="s">
         <v>488</v>
       </c>
@@ -14161,7 +14161,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="158" spans="1:16" hidden="1">
+    <row r="158" spans="1:16">
       <c r="A158" t="s">
         <v>491</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="159" spans="1:16" hidden="1">
+    <row r="159" spans="1:16">
       <c r="A159" t="s">
         <v>495</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="160" spans="1:16" hidden="1">
+    <row r="160" spans="1:16">
       <c r="A160" t="s">
         <v>496</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1">
+    <row r="161" spans="1:16">
       <c r="A161" t="s">
         <v>499</v>
       </c>
@@ -14328,7 +14328,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1">
+    <row r="162" spans="1:16">
       <c r="A162" t="s">
         <v>503</v>
       </c>
@@ -14369,7 +14369,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1">
+    <row r="163" spans="1:16">
       <c r="A163" t="s">
         <v>506</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1">
+    <row r="164" spans="1:16">
       <c r="A164" t="s">
         <v>509</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1">
+    <row r="165" spans="1:16">
       <c r="A165">
         <v>12100124</v>
       </c>
@@ -14489,7 +14489,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1">
+    <row r="166" spans="1:16">
       <c r="A166" t="s">
         <v>512</v>
       </c>
@@ -14524,7 +14524,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1">
+    <row r="167" spans="1:16">
       <c r="A167" t="s">
         <v>514</v>
       </c>
@@ -14562,7 +14562,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1">
+    <row r="168" spans="1:16">
       <c r="A168" t="s">
         <v>515</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1">
+    <row r="169" spans="1:16">
       <c r="A169" t="s">
         <v>517</v>
       </c>
@@ -14644,7 +14644,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1">
+    <row r="170" spans="1:16">
       <c r="A170" t="s">
         <v>520</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1">
+    <row r="171" spans="1:16">
       <c r="A171" t="s">
         <v>522</v>
       </c>
@@ -14723,7 +14723,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1">
+    <row r="172" spans="1:16">
       <c r="A172" t="s">
         <v>525</v>
       </c>
@@ -14758,7 +14758,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1">
+    <row r="173" spans="1:16">
       <c r="A173" t="s">
         <v>527</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1">
+    <row r="174" spans="1:16">
       <c r="A174" t="s">
         <v>529</v>
       </c>
@@ -14843,7 +14843,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1">
+    <row r="175" spans="1:16">
       <c r="A175" t="s">
         <v>532</v>
       </c>
@@ -14884,7 +14884,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1">
+    <row r="176" spans="1:16">
       <c r="A176" t="s">
         <v>534</v>
       </c>
@@ -14925,7 +14925,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1">
+    <row r="177" spans="1:16">
       <c r="A177" t="s">
         <v>535</v>
       </c>
@@ -14969,7 +14969,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1">
+    <row r="178" spans="1:16">
       <c r="A178" t="s">
         <v>539</v>
       </c>
@@ -15010,7 +15010,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1">
+    <row r="179" spans="1:16">
       <c r="A179" t="s">
         <v>541</v>
       </c>
@@ -15054,7 +15054,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1">
+    <row r="180" spans="1:16">
       <c r="A180">
         <v>25002122</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1">
+    <row r="181" spans="1:16">
       <c r="A181" t="s">
         <v>544</v>
       </c>
@@ -15133,7 +15133,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1">
+    <row r="182" spans="1:16">
       <c r="A182" t="s">
         <v>548</v>
       </c>
@@ -15174,7 +15174,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1">
+    <row r="183" spans="1:16">
       <c r="A183" t="s">
         <v>550</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1">
+    <row r="184" spans="1:16">
       <c r="A184" t="s">
         <v>553</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1">
+    <row r="185" spans="1:16">
       <c r="A185">
         <v>28700625</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1">
+    <row r="186" spans="1:16">
       <c r="A186" t="s">
         <v>560</v>
       </c>
@@ -15338,7 +15338,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1">
+    <row r="187" spans="1:16">
       <c r="A187" t="s">
         <v>562</v>
       </c>
@@ -15379,7 +15379,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1">
+    <row r="188" spans="1:16">
       <c r="A188">
         <v>28701025</v>
       </c>
@@ -15420,7 +15420,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1">
+    <row r="189" spans="1:16">
       <c r="A189" t="s">
         <v>567</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1">
+    <row r="190" spans="1:16">
       <c r="A190" t="s">
         <v>569</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1">
+    <row r="191" spans="1:16">
       <c r="A191" t="s">
         <v>572</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1">
+    <row r="192" spans="1:16">
       <c r="A192" t="s">
         <v>574</v>
       </c>
@@ -15584,7 +15584,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1">
+    <row r="193" spans="1:16">
       <c r="A193" t="s">
         <v>577</v>
       </c>
@@ -15628,7 +15628,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1">
+    <row r="194" spans="1:16">
       <c r="A194" t="s">
         <v>579</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1">
+    <row r="195" spans="1:16">
       <c r="A195" t="s">
         <v>582</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1">
+    <row r="196" spans="1:16">
       <c r="A196" t="s">
         <v>585</v>
       </c>
@@ -15754,7 +15754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1">
+    <row r="197" spans="1:16">
       <c r="A197" t="s">
         <v>588</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1">
+    <row r="198" spans="1:16">
       <c r="A198">
         <v>43902124</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1">
+    <row r="199" spans="1:16">
       <c r="A199" t="s">
         <v>594</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1">
+    <row r="200" spans="1:16">
       <c r="A200" t="s">
         <v>596</v>
       </c>
@@ -15918,7 +15918,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1">
+    <row r="201" spans="1:16">
       <c r="A201" t="s">
         <v>600</v>
       </c>
@@ -15959,7 +15959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1">
+    <row r="202" spans="1:16">
       <c r="A202" t="s">
         <v>602</v>
       </c>
@@ -16000,7 +16000,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1">
+    <row r="203" spans="1:16">
       <c r="A203" t="s">
         <v>604</v>
       </c>
@@ -16044,7 +16044,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1">
+    <row r="204" spans="1:16">
       <c r="A204" t="s">
         <v>606</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1">
+    <row r="205" spans="1:16">
       <c r="A205" t="s">
         <v>608</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1">
+    <row r="206" spans="1:16">
       <c r="A206" t="s">
         <v>610</v>
       </c>
@@ -16170,7 +16170,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1">
+    <row r="207" spans="1:16">
       <c r="A207" t="s">
         <v>612</v>
       </c>
@@ -16211,7 +16211,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1">
+    <row r="208" spans="1:16">
       <c r="A208">
         <v>28400124</v>
       </c>
@@ -16252,7 +16252,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1">
+    <row r="209" spans="1:16">
       <c r="A209" t="s">
         <v>614</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1">
+    <row r="210" spans="1:16">
       <c r="A210">
         <v>31901625</v>
       </c>
@@ -16331,7 +16331,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1">
+    <row r="211" spans="1:16">
       <c r="A211" t="s">
         <v>619</v>
       </c>
@@ -16372,7 +16372,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1">
+    <row r="212" spans="1:16">
       <c r="A212" t="s">
         <v>622</v>
       </c>
@@ -16413,7 +16413,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1">
+    <row r="213" spans="1:16">
       <c r="A213" t="s">
         <v>624</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1">
+    <row r="214" spans="1:16">
       <c r="A214" t="s">
         <v>627</v>
       </c>
@@ -16495,7 +16495,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1">
+    <row r="215" spans="1:16">
       <c r="A215" t="s">
         <v>630</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1">
+    <row r="216" spans="1:16">
       <c r="A216" t="s">
         <v>633</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1">
+    <row r="217" spans="1:16">
       <c r="A217" t="s">
         <v>634</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1">
+    <row r="218" spans="1:16">
       <c r="A218" t="s">
         <v>637</v>
       </c>
@@ -16659,7 +16659,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1">
+    <row r="219" spans="1:16">
       <c r="A219" t="s">
         <v>640</v>
       </c>
@@ -16700,7 +16700,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1">
+    <row r="220" spans="1:16">
       <c r="A220" t="s">
         <v>641</v>
       </c>
@@ -16741,7 +16741,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1">
+    <row r="221" spans="1:16">
       <c r="A221" t="s">
         <v>642</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1">
+    <row r="222" spans="1:16">
       <c r="A222" t="s">
         <v>644</v>
       </c>
@@ -16823,7 +16823,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1">
+    <row r="223" spans="1:16">
       <c r="A223">
         <v>51600124</v>
       </c>
@@ -16867,7 +16867,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1">
+    <row r="224" spans="1:16">
       <c r="A224">
         <v>51600225</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1">
+    <row r="225" spans="1:16">
       <c r="A225">
         <v>51600324</v>
       </c>
@@ -16955,7 +16955,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1">
+    <row r="226" spans="1:16">
       <c r="A226">
         <v>51600424</v>
       </c>
@@ -16999,7 +16999,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1">
+    <row r="227" spans="1:16">
       <c r="A227">
         <v>51600523</v>
       </c>
@@ -17043,7 +17043,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1">
+    <row r="228" spans="1:16">
       <c r="A228">
         <v>51600625</v>
       </c>
@@ -17087,7 +17087,7 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1">
+    <row r="229" spans="1:16">
       <c r="A229" t="s">
         <v>655</v>
       </c>
@@ -17128,7 +17128,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1">
+    <row r="230" spans="1:16">
       <c r="A230" t="s">
         <v>658</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1">
+    <row r="231" spans="1:16">
       <c r="A231" t="s">
         <v>660</v>
       </c>
@@ -17210,7 +17210,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1">
+    <row r="232" spans="1:16">
       <c r="A232" t="s">
         <v>662</v>
       </c>
@@ -17251,7 +17251,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1">
+    <row r="233" spans="1:16">
       <c r="A233" t="s">
         <v>665</v>
       </c>
@@ -17292,7 +17292,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1">
+    <row r="234" spans="1:16">
       <c r="A234" t="s">
         <v>667</v>
       </c>
@@ -17336,7 +17336,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1">
+    <row r="235" spans="1:16">
       <c r="A235" t="s">
         <v>670</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1">
+    <row r="236" spans="1:16">
       <c r="A236" t="s">
         <v>672</v>
       </c>
@@ -17418,7 +17418,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1">
+    <row r="237" spans="1:16">
       <c r="A237" t="s">
         <v>674</v>
       </c>
@@ -17459,7 +17459,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1">
+    <row r="238" spans="1:16">
       <c r="A238" t="s">
         <v>677</v>
       </c>
@@ -17503,7 +17503,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1">
+    <row r="239" spans="1:16">
       <c r="A239" t="s">
         <v>680</v>
       </c>
@@ -17544,7 +17544,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1">
+    <row r="240" spans="1:16">
       <c r="A240" t="s">
         <v>682</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1">
+    <row r="241" spans="1:16">
       <c r="A241">
         <v>11001923</v>
       </c>
@@ -17623,7 +17623,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1">
+    <row r="242" spans="1:16">
       <c r="A242" t="s">
         <v>687</v>
       </c>
@@ -17664,7 +17664,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1">
+    <row r="243" spans="1:16">
       <c r="A243" t="s">
         <v>691</v>
       </c>
@@ -17705,7 +17705,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1">
+    <row r="244" spans="1:16">
       <c r="A244" t="s">
         <v>693</v>
       </c>
@@ -17746,7 +17746,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1">
+    <row r="245" spans="1:16">
       <c r="A245" t="s">
         <v>696</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1">
+    <row r="246" spans="1:16">
       <c r="A246" t="s">
         <v>698</v>
       </c>
@@ -17828,7 +17828,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1">
+    <row r="247" spans="1:16">
       <c r="A247" t="s">
         <v>701</v>
       </c>
@@ -17869,7 +17869,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1">
+    <row r="248" spans="1:16">
       <c r="A248" t="s">
         <v>702</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1">
+    <row r="249" spans="1:16">
       <c r="A249">
         <v>11003123</v>
       </c>
@@ -17954,7 +17954,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1">
+    <row r="250" spans="1:16">
       <c r="A250" t="s">
         <v>703</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1">
+    <row r="251" spans="1:16">
       <c r="A251" t="s">
         <v>706</v>
       </c>
@@ -18039,7 +18039,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1">
+    <row r="252" spans="1:16">
       <c r="A252" t="s">
         <v>708</v>
       </c>
@@ -18080,7 +18080,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1">
+    <row r="253" spans="1:16">
       <c r="A253" t="s">
         <v>710</v>
       </c>
@@ -18121,7 +18121,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1">
+    <row r="254" spans="1:16">
       <c r="A254">
         <v>15000820</v>
       </c>
@@ -18162,7 +18162,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1">
+    <row r="255" spans="1:16">
       <c r="A255" t="s">
         <v>713</v>
       </c>
@@ -18203,7 +18203,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1">
+    <row r="256" spans="1:16">
       <c r="A256">
         <v>11002824</v>
       </c>
@@ -18244,7 +18244,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1">
+    <row r="257" spans="1:16">
       <c r="A257" t="s">
         <v>716</v>
       </c>
@@ -18285,7 +18285,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1">
+    <row r="258" spans="1:16">
       <c r="A258">
         <v>13800524</v>
       </c>
@@ -18326,7 +18326,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1">
+    <row r="259" spans="1:16">
       <c r="A259" t="s">
         <v>718</v>
       </c>
@@ -18367,7 +18367,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1">
+    <row r="260" spans="1:16">
       <c r="A260" t="s">
         <v>720</v>
       </c>
@@ -18408,7 +18408,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1">
+    <row r="261" spans="1:16">
       <c r="A261" t="s">
         <v>722</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1">
+    <row r="262" spans="1:16">
       <c r="A262" t="s">
         <v>723</v>
       </c>
@@ -18487,7 +18487,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1">
+    <row r="263" spans="1:16">
       <c r="A263" t="s">
         <v>727</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1">
+    <row r="264" spans="1:16">
       <c r="A264">
         <v>10700325</v>
       </c>
@@ -18563,7 +18563,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1">
+    <row r="265" spans="1:16">
       <c r="A265" t="s">
         <v>732</v>
       </c>
@@ -18601,7 +18601,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1">
+    <row r="266" spans="1:16">
       <c r="A266" t="s">
         <v>736</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1">
+    <row r="267" spans="1:16">
       <c r="A267" t="s">
         <v>739</v>
       </c>
@@ -18683,7 +18683,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1">
+    <row r="268" spans="1:16">
       <c r="A268" t="s">
         <v>742</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1">
+    <row r="269" spans="1:16">
       <c r="A269" t="s">
         <v>746</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1">
+    <row r="270" spans="1:16">
       <c r="A270" t="s">
         <v>750</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1">
+    <row r="271" spans="1:16">
       <c r="A271" t="s">
         <v>754</v>
       </c>
@@ -18847,7 +18847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1">
+    <row r="272" spans="1:16">
       <c r="A272" t="s">
         <v>759</v>
       </c>
@@ -18932,7 +18932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="274" spans="1:18" hidden="1">
+    <row r="274" spans="1:18">
       <c r="A274" t="s">
         <v>765</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="275" spans="1:18" hidden="1">
+    <row r="275" spans="1:18">
       <c r="A275" t="s">
         <v>769</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="276" spans="1:18" hidden="1">
+    <row r="276" spans="1:18">
       <c r="A276" t="s">
         <v>772</v>
       </c>
@@ -19055,7 +19055,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="277" spans="1:18" hidden="1">
+    <row r="277" spans="1:18">
       <c r="A277" t="s">
         <v>777</v>
       </c>
@@ -19093,7 +19093,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="278" spans="1:18" hidden="1">
+    <row r="278" spans="1:18">
       <c r="A278">
         <v>14700423</v>
       </c>
@@ -19134,7 +19134,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="279" spans="1:18" hidden="1">
+    <row r="279" spans="1:18">
       <c r="A279" t="s">
         <v>781</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="280" spans="1:18" hidden="1">
+    <row r="280" spans="1:18">
       <c r="A280" t="s">
         <v>783</v>
       </c>
@@ -19210,7 +19210,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="281" spans="1:18" hidden="1">
+    <row r="281" spans="1:18">
       <c r="A281" t="s">
         <v>786</v>
       </c>
@@ -19242,7 +19242,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="282" spans="1:18" hidden="1">
+    <row r="282" spans="1:18">
       <c r="A282" t="s">
         <v>789</v>
       </c>
@@ -19280,7 +19280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="283" spans="1:18" hidden="1">
+    <row r="283" spans="1:18">
       <c r="A283">
         <v>43800825</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="284" spans="1:18" hidden="1">
+    <row r="284" spans="1:18">
       <c r="A284" t="s">
         <v>795</v>
       </c>
@@ -19359,7 +19359,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="285" spans="1:18" hidden="1">
+    <row r="285" spans="1:18">
       <c r="A285" t="s">
         <v>798</v>
       </c>
@@ -19394,7 +19394,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="286" spans="1:18" hidden="1">
+    <row r="286" spans="1:18">
       <c r="A286" t="s">
         <v>800</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="287" spans="1:18" hidden="1">
+    <row r="287" spans="1:18">
       <c r="A287" t="s">
         <v>802</v>
       </c>
@@ -19467,7 +19467,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="288" spans="1:18" hidden="1">
+    <row r="288" spans="1:18">
       <c r="A288" t="s">
         <v>805</v>
       </c>
@@ -19505,7 +19505,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="289" spans="1:18" hidden="1">
+    <row r="289" spans="1:18">
       <c r="A289">
         <v>14805225</v>
       </c>
@@ -19543,7 +19543,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="290" spans="1:18" hidden="1">
+    <row r="290" spans="1:18">
       <c r="A290" t="s">
         <v>810</v>
       </c>
@@ -19578,7 +19578,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="291" spans="1:18" hidden="1">
+    <row r="291" spans="1:18">
       <c r="A291" t="s">
         <v>813</v>
       </c>
@@ -19657,7 +19657,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="293" spans="1:18" hidden="1">
+    <row r="293" spans="1:18">
       <c r="A293" t="s">
         <v>817</v>
       </c>
@@ -19692,7 +19692,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="294" spans="1:18" hidden="1">
+    <row r="294" spans="1:18">
       <c r="A294" t="s">
         <v>818</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="295" spans="1:18" hidden="1">
+    <row r="295" spans="1:18">
       <c r="A295" t="s">
         <v>820</v>
       </c>
@@ -19768,7 +19768,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="296" spans="1:18" hidden="1">
+    <row r="296" spans="1:18">
       <c r="A296" t="s">
         <v>822</v>
       </c>
@@ -19806,7 +19806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="297" spans="1:18" hidden="1">
+    <row r="297" spans="1:18">
       <c r="A297" t="s">
         <v>824</v>
       </c>
@@ -19847,7 +19847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="298" spans="1:18" hidden="1">
+    <row r="298" spans="1:18">
       <c r="A298" t="s">
         <v>827</v>
       </c>
@@ -19888,7 +19888,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="299" spans="1:18" hidden="1">
+    <row r="299" spans="1:18">
       <c r="A299" t="s">
         <v>831</v>
       </c>
@@ -19926,7 +19926,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="300" spans="1:18" hidden="1">
+    <row r="300" spans="1:18">
       <c r="A300" t="s">
         <v>834</v>
       </c>
@@ -19964,7 +19964,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="301" spans="1:18" hidden="1">
+    <row r="301" spans="1:18">
       <c r="A301">
         <v>14800921</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="302" spans="1:18" hidden="1">
+    <row r="302" spans="1:18">
       <c r="A302" t="s">
         <v>838</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="303" spans="1:18" hidden="1">
+    <row r="303" spans="1:18">
       <c r="A303" t="s">
         <v>840</v>
       </c>
@@ -20084,7 +20084,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="304" spans="1:18" hidden="1">
+    <row r="304" spans="1:18">
       <c r="A304" t="s">
         <v>842</v>
       </c>
@@ -20125,7 +20125,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1">
+    <row r="305" spans="1:16">
       <c r="A305" t="s">
         <v>844</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1">
+    <row r="306" spans="1:16">
       <c r="A306" t="s">
         <v>845</v>
       </c>
@@ -20204,7 +20204,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1">
+    <row r="307" spans="1:16">
       <c r="A307">
         <v>14700123</v>
       </c>
@@ -20242,7 +20242,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1">
+    <row r="308" spans="1:16">
       <c r="A308" t="s">
         <v>848</v>
       </c>
@@ -20280,7 +20280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1">
+    <row r="309" spans="1:16">
       <c r="A309" t="s">
         <v>850</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1">
+    <row r="310" spans="1:16">
       <c r="A310" t="s">
         <v>852</v>
       </c>
@@ -20353,7 +20353,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1">
+    <row r="311" spans="1:16">
       <c r="A311" t="s">
         <v>853</v>
       </c>
@@ -20394,7 +20394,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1">
+    <row r="312" spans="1:16">
       <c r="A312" t="s">
         <v>855</v>
       </c>
@@ -20432,7 +20432,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1">
+    <row r="313" spans="1:16">
       <c r="A313">
         <v>10701525</v>
       </c>
@@ -20470,7 +20470,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1">
+    <row r="314" spans="1:16">
       <c r="A314" t="s">
         <v>862</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1">
+    <row r="315" spans="1:16">
       <c r="A315" t="s">
         <v>865</v>
       </c>
@@ -20549,7 +20549,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1">
+    <row r="316" spans="1:16">
       <c r="A316" t="s">
         <v>867</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1">
+    <row r="317" spans="1:16">
       <c r="A317" t="s">
         <v>869</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1">
+    <row r="318" spans="1:16">
       <c r="A318" t="s">
         <v>873</v>
       </c>
@@ -20669,7 +20669,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1">
+    <row r="319" spans="1:16">
       <c r="A319" t="s">
         <v>876</v>
       </c>
@@ -20707,7 +20707,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1">
+    <row r="320" spans="1:16">
       <c r="A320" t="s">
         <v>877</v>
       </c>
@@ -20745,7 +20745,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1">
+    <row r="321" spans="1:16">
       <c r="A321" t="s">
         <v>880</v>
       </c>
@@ -20786,7 +20786,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1">
+    <row r="322" spans="1:16">
       <c r="A322" t="s">
         <v>883</v>
       </c>
@@ -20818,7 +20818,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1">
+    <row r="323" spans="1:16">
       <c r="A323" t="s">
         <v>885</v>
       </c>
@@ -20853,7 +20853,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1">
+    <row r="324" spans="1:16">
       <c r="A324" t="s">
         <v>887</v>
       </c>
@@ -20894,7 +20894,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1">
+    <row r="325" spans="1:16">
       <c r="A325">
         <v>66700924</v>
       </c>
@@ -20935,7 +20935,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1">
+    <row r="326" spans="1:16">
       <c r="A326">
         <v>66700820</v>
       </c>
@@ -20976,7 +20976,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1">
+    <row r="327" spans="1:16">
       <c r="A327">
         <v>66700815</v>
       </c>
@@ -21017,7 +21017,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1">
+    <row r="328" spans="1:16">
       <c r="A328">
         <v>66700217</v>
       </c>
@@ -21058,7 +21058,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1">
+    <row r="329" spans="1:16">
       <c r="A329" t="s">
         <v>892</v>
       </c>
@@ -21099,7 +21099,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1">
+    <row r="330" spans="1:16">
       <c r="A330">
         <v>66700711</v>
       </c>
@@ -21140,7 +21140,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1">
+    <row r="331" spans="1:16">
       <c r="A331" t="s">
         <v>894</v>
       </c>
@@ -21172,7 +21172,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1">
+    <row r="332" spans="1:16">
       <c r="A332" t="s">
         <v>896</v>
       </c>
@@ -21207,7 +21207,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1">
+    <row r="333" spans="1:16">
       <c r="A333" t="s">
         <v>897</v>
       </c>
@@ -21245,7 +21245,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1">
+    <row r="334" spans="1:16">
       <c r="A334" t="s">
         <v>898</v>
       </c>
@@ -21283,7 +21283,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1">
+    <row r="335" spans="1:16">
       <c r="A335" t="s">
         <v>899</v>
       </c>
@@ -21321,7 +21321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1">
+    <row r="336" spans="1:16">
       <c r="A336" t="s">
         <v>900</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="338" spans="1:18" hidden="1">
+    <row r="338" spans="1:18">
       <c r="A338" t="s">
         <v>903</v>
       </c>
@@ -21435,7 +21435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="339" spans="1:18" hidden="1">
+    <row r="339" spans="1:18">
       <c r="A339" t="s">
         <v>904</v>
       </c>
@@ -21476,7 +21476,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="340" spans="1:18" hidden="1">
+    <row r="340" spans="1:18">
       <c r="A340" t="s">
         <v>906</v>
       </c>
@@ -21517,7 +21517,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="341" spans="1:18" hidden="1">
+    <row r="341" spans="1:18">
       <c r="A341" t="s">
         <v>910</v>
       </c>
@@ -21561,7 +21561,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="342" spans="1:18" hidden="1">
+    <row r="342" spans="1:18">
       <c r="A342" t="s">
         <v>917</v>
       </c>
@@ -21596,7 +21596,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="343" spans="1:18" hidden="1">
+    <row r="343" spans="1:18">
       <c r="A343" t="s">
         <v>921</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="344" spans="1:18" hidden="1">
+    <row r="344" spans="1:18">
       <c r="A344" t="s">
         <v>922</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="345" spans="1:18" hidden="1">
+    <row r="345" spans="1:18">
       <c r="A345" t="s">
         <v>926</v>
       </c>
@@ -21719,7 +21719,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="346" spans="1:18" hidden="1">
+    <row r="346" spans="1:18">
       <c r="A346" t="s">
         <v>927</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="347" spans="1:18" hidden="1">
+    <row r="347" spans="1:18">
       <c r="A347" t="s">
         <v>930</v>
       </c>
@@ -21792,7 +21792,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="348" spans="1:18" hidden="1">
+    <row r="348" spans="1:18">
       <c r="A348" t="s">
         <v>932</v>
       </c>
@@ -21836,7 +21836,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="349" spans="1:18" hidden="1">
+    <row r="349" spans="1:18">
       <c r="A349">
         <v>72400122</v>
       </c>
@@ -21880,7 +21880,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="350" spans="1:18" hidden="1">
+    <row r="350" spans="1:18">
       <c r="A350">
         <v>72400223</v>
       </c>
@@ -21924,7 +21924,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="351" spans="1:18" hidden="1">
+    <row r="351" spans="1:18">
       <c r="A351">
         <v>72400324</v>
       </c>
@@ -21968,7 +21968,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="352" spans="1:18" hidden="1">
+    <row r="352" spans="1:18">
       <c r="A352">
         <v>72400424</v>
       </c>
@@ -22012,7 +22012,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1">
+    <row r="353" spans="1:16">
       <c r="A353">
         <v>72400524</v>
       </c>
@@ -22056,7 +22056,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1">
+    <row r="354" spans="1:16">
       <c r="A354">
         <v>72400625</v>
       </c>
@@ -22100,7 +22100,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1">
+    <row r="355" spans="1:16">
       <c r="A355">
         <v>72300125</v>
       </c>
@@ -22144,7 +22144,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1">
+    <row r="356" spans="1:16">
       <c r="A356">
         <v>72300223</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1">
+    <row r="357" spans="1:16">
       <c r="A357">
         <v>72300223</v>
       </c>
@@ -22232,7 +22232,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1">
+    <row r="358" spans="1:16">
       <c r="A358" t="s">
         <v>946</v>
       </c>
@@ -22267,7 +22267,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1">
+    <row r="359" spans="1:16">
       <c r="A359" t="s">
         <v>949</v>
       </c>
@@ -22305,7 +22305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1">
+    <row r="360" spans="1:16">
       <c r="A360" t="s">
         <v>953</v>
       </c>
@@ -22343,7 +22343,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1">
+    <row r="361" spans="1:16">
       <c r="A361" t="s">
         <v>956</v>
       </c>
@@ -22387,7 +22387,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1">
+    <row r="362" spans="1:16">
       <c r="A362">
         <v>10300525</v>
       </c>
@@ -22431,7 +22431,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1">
+    <row r="363" spans="1:16">
       <c r="A363" t="s">
         <v>961</v>
       </c>
@@ -22472,7 +22472,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1">
+    <row r="364" spans="1:16">
       <c r="A364" t="s">
         <v>964</v>
       </c>
@@ -22513,7 +22513,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1">
+    <row r="365" spans="1:16">
       <c r="A365" t="s">
         <v>966</v>
       </c>
@@ -22557,7 +22557,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1">
+    <row r="366" spans="1:16">
       <c r="A366" t="s">
         <v>969</v>
       </c>
@@ -22598,7 +22598,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1">
+    <row r="367" spans="1:16">
       <c r="A367" t="s">
         <v>971</v>
       </c>
@@ -22639,7 +22639,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1">
+    <row r="368" spans="1:16">
       <c r="A368" t="s">
         <v>973</v>
       </c>
@@ -22683,7 +22683,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1">
+    <row r="369" spans="1:16">
       <c r="A369" t="s">
         <v>975</v>
       </c>
@@ -22727,7 +22727,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1">
+    <row r="370" spans="1:16">
       <c r="A370" t="s">
         <v>978</v>
       </c>
@@ -22765,7 +22765,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1">
+    <row r="371" spans="1:16">
       <c r="A371" t="s">
         <v>980</v>
       </c>
@@ -22806,7 +22806,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1">
+    <row r="372" spans="1:16">
       <c r="A372" t="s">
         <v>981</v>
       </c>
@@ -22847,7 +22847,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1">
+    <row r="373" spans="1:16">
       <c r="A373" t="s">
         <v>982</v>
       </c>
@@ -22888,7 +22888,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1">
+    <row r="374" spans="1:16">
       <c r="A374" t="s">
         <v>988</v>
       </c>
@@ -22929,7 +22929,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1">
+    <row r="375" spans="1:16">
       <c r="A375" t="s">
         <v>991</v>
       </c>
@@ -22970,7 +22970,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1">
+    <row r="376" spans="1:16">
       <c r="A376" t="s">
         <v>995</v>
       </c>
@@ -23011,7 +23011,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1">
+    <row r="377" spans="1:16">
       <c r="A377" t="s">
         <v>998</v>
       </c>
@@ -23052,7 +23052,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1">
+    <row r="378" spans="1:16">
       <c r="A378" t="s">
         <v>1000</v>
       </c>
@@ -23093,7 +23093,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1">
+    <row r="379" spans="1:16">
       <c r="A379" t="s">
         <v>1002</v>
       </c>
@@ -23134,7 +23134,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1">
+    <row r="380" spans="1:16">
       <c r="A380" t="s">
         <v>1004</v>
       </c>
@@ -23175,7 +23175,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1">
+    <row r="381" spans="1:16">
       <c r="A381" t="s">
         <v>1007</v>
       </c>
@@ -23216,7 +23216,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1">
+    <row r="382" spans="1:16">
       <c r="A382" t="s">
         <v>1009</v>
       </c>
@@ -23257,7 +23257,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1">
+    <row r="383" spans="1:16">
       <c r="A383" t="s">
         <v>1012</v>
       </c>
@@ -23298,7 +23298,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1">
+    <row r="384" spans="1:16">
       <c r="A384" t="s">
         <v>1015</v>
       </c>
@@ -23342,7 +23342,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1">
+    <row r="385" spans="1:16">
       <c r="A385" t="s">
         <v>1018</v>
       </c>
@@ -23383,7 +23383,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1">
+    <row r="386" spans="1:16">
       <c r="A386" t="s">
         <v>1023</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1">
+    <row r="387" spans="1:16">
       <c r="A387" t="s">
         <v>1027</v>
       </c>
@@ -23468,7 +23468,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1">
+    <row r="388" spans="1:16">
       <c r="A388">
         <v>13003025</v>
       </c>
@@ -23512,7 +23512,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1">
+    <row r="389" spans="1:16">
       <c r="A389" t="s">
         <v>1030</v>
       </c>
@@ -23553,7 +23553,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1">
+    <row r="390" spans="1:16">
       <c r="A390" t="s">
         <v>1032</v>
       </c>
@@ -23591,7 +23591,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1">
+    <row r="391" spans="1:16">
       <c r="A391">
         <v>43700425</v>
       </c>
@@ -23629,7 +23629,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1">
+    <row r="392" spans="1:16">
       <c r="A392" t="s">
         <v>1037</v>
       </c>
@@ -23670,7 +23670,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1">
+    <row r="393" spans="1:16">
       <c r="A393">
         <v>13300125</v>
       </c>
@@ -23711,7 +23711,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1">
+    <row r="394" spans="1:16">
       <c r="A394" t="s">
         <v>1043</v>
       </c>
@@ -23752,7 +23752,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1">
+    <row r="395" spans="1:16">
       <c r="A395">
         <v>24003025</v>
       </c>
@@ -23793,7 +23793,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1">
+    <row r="396" spans="1:16">
       <c r="A396" t="s">
         <v>1049</v>
       </c>
@@ -23834,7 +23834,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1">
+    <row r="397" spans="1:16">
       <c r="A397" t="s">
         <v>1052</v>
       </c>
@@ -23875,7 +23875,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1">
+    <row r="398" spans="1:16">
       <c r="A398" t="s">
         <v>1055</v>
       </c>
@@ -23916,7 +23916,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1">
+    <row r="399" spans="1:16">
       <c r="A399" t="s">
         <v>1058</v>
       </c>
@@ -23960,7 +23960,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1">
+    <row r="400" spans="1:16">
       <c r="A400" t="s">
         <v>1062</v>
       </c>
@@ -24001,7 +24001,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1">
+    <row r="401" spans="1:16">
       <c r="A401" t="s">
         <v>1066</v>
       </c>
@@ -24042,7 +24042,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1">
+    <row r="402" spans="1:16">
       <c r="A402" t="s">
         <v>1068</v>
       </c>
@@ -24083,7 +24083,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1">
+    <row r="403" spans="1:16">
       <c r="A403" t="s">
         <v>1071</v>
       </c>
@@ -24124,7 +24124,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1">
+    <row r="404" spans="1:16">
       <c r="A404">
         <v>68002225</v>
       </c>
@@ -24165,7 +24165,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1">
+    <row r="405" spans="1:16">
       <c r="A405">
         <v>68002325</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1">
+    <row r="406" spans="1:16">
       <c r="A406">
         <v>68002424</v>
       </c>
@@ -24247,7 +24247,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1">
+    <row r="407" spans="1:16">
       <c r="A407" t="s">
         <v>1081</v>
       </c>
@@ -24288,7 +24288,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1">
+    <row r="408" spans="1:16">
       <c r="A408">
         <v>68002623</v>
       </c>
@@ -24332,7 +24332,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1">
+    <row r="409" spans="1:16">
       <c r="A409">
         <v>68002825</v>
       </c>
@@ -24376,7 +24376,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1">
+    <row r="410" spans="1:16">
       <c r="A410" t="s">
         <v>1089</v>
       </c>
@@ -24417,7 +24417,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1">
+    <row r="411" spans="1:16">
       <c r="A411">
         <v>68003025</v>
       </c>
@@ -24458,7 +24458,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1">
+    <row r="412" spans="1:16">
       <c r="A412">
         <v>680031225</v>
       </c>
@@ -24499,7 +24499,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1">
+    <row r="413" spans="1:16">
       <c r="A413" t="s">
         <v>1095</v>
       </c>
@@ -24540,7 +24540,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1">
+    <row r="414" spans="1:16">
       <c r="A414" t="s">
         <v>1097</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1">
+    <row r="415" spans="1:16">
       <c r="A415" t="s">
         <v>1100</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1">
+    <row r="416" spans="1:16">
       <c r="A416" t="s">
         <v>1102</v>
       </c>
@@ -24663,7 +24663,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1">
+    <row r="417" spans="1:16">
       <c r="A417" t="s">
         <v>1104</v>
       </c>
@@ -24701,7 +24701,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1">
+    <row r="418" spans="1:16">
       <c r="A418" t="s">
         <v>1108</v>
       </c>
@@ -24739,7 +24739,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1">
+    <row r="419" spans="1:16">
       <c r="A419">
         <v>53800623</v>
       </c>
@@ -24780,7 +24780,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1">
+    <row r="420" spans="1:16">
       <c r="A420" t="s">
         <v>1113</v>
       </c>
@@ -24821,7 +24821,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1">
+    <row r="421" spans="1:16">
       <c r="A421" t="s">
         <v>1115</v>
       </c>
@@ -24862,7 +24862,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1">
+    <row r="422" spans="1:16">
       <c r="A422" t="s">
         <v>1117</v>
       </c>
@@ -24903,7 +24903,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1">
+    <row r="423" spans="1:16">
       <c r="A423">
         <v>71501125</v>
       </c>
@@ -24947,7 +24947,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1">
+    <row r="424" spans="1:16">
       <c r="A424">
         <v>71500125</v>
       </c>
@@ -24988,7 +24988,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1">
+    <row r="425" spans="1:16">
       <c r="A425">
         <v>71500225</v>
       </c>
@@ -25029,7 +25029,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1">
+    <row r="426" spans="1:16">
       <c r="A426">
         <v>71500325</v>
       </c>
@@ -25070,7 +25070,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1">
+    <row r="427" spans="1:16">
       <c r="A427">
         <v>71500425</v>
       </c>
@@ -25111,7 +25111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1">
+    <row r="428" spans="1:16">
       <c r="A428">
         <v>71500525</v>
       </c>
@@ -25152,7 +25152,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1">
+    <row r="429" spans="1:16">
       <c r="A429">
         <v>71500625</v>
       </c>
@@ -25193,7 +25193,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1">
+    <row r="430" spans="1:16">
       <c r="A430">
         <v>71500725</v>
       </c>
@@ -25234,7 +25234,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1">
+    <row r="431" spans="1:16">
       <c r="A431">
         <v>71500825</v>
       </c>
@@ -25278,7 +25278,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1">
+    <row r="432" spans="1:16">
       <c r="A432">
         <v>71500925</v>
       </c>
@@ -25322,7 +25322,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1">
+    <row r="433" spans="1:16">
       <c r="A433">
         <v>71501025</v>
       </c>
@@ -25366,7 +25366,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1">
+    <row r="434" spans="1:16">
       <c r="A434" t="s">
         <v>1131</v>
       </c>
@@ -25407,7 +25407,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1">
+    <row r="435" spans="1:16">
       <c r="A435" t="s">
         <v>1132</v>
       </c>
@@ -25448,7 +25448,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1">
+    <row r="436" spans="1:16">
       <c r="A436" t="s">
         <v>1133</v>
       </c>
@@ -25489,7 +25489,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1">
+    <row r="437" spans="1:16">
       <c r="A437" t="s">
         <v>1135</v>
       </c>
@@ -25530,7 +25530,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1">
+    <row r="438" spans="1:16">
       <c r="A438" t="s">
         <v>1137</v>
       </c>
@@ -25571,7 +25571,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1">
+    <row r="439" spans="1:16">
       <c r="A439" t="s">
         <v>1139</v>
       </c>
@@ -25612,7 +25612,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1">
+    <row r="440" spans="1:16">
       <c r="A440" t="s">
         <v>1141</v>
       </c>
@@ -25653,7 +25653,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1">
+    <row r="441" spans="1:16">
       <c r="A441" t="s">
         <v>1144</v>
       </c>
@@ -25697,7 +25697,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1">
+    <row r="442" spans="1:16">
       <c r="A442" t="s">
         <v>1146</v>
       </c>
@@ -25741,7 +25741,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1">
+    <row r="443" spans="1:16">
       <c r="A443" t="s">
         <v>1148</v>
       </c>
@@ -25782,7 +25782,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1">
+    <row r="444" spans="1:16">
       <c r="A444" t="s">
         <v>1150</v>
       </c>
@@ -25823,7 +25823,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1">
+    <row r="445" spans="1:16">
       <c r="A445" t="s">
         <v>1153</v>
       </c>
@@ -25864,7 +25864,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="446" spans="1:16" hidden="1">
+    <row r="446" spans="1:16">
       <c r="A446" t="s">
         <v>1157</v>
       </c>
@@ -25905,7 +25905,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="447" spans="1:16" hidden="1">
+    <row r="447" spans="1:16">
       <c r="A447" t="s">
         <v>1159</v>
       </c>
@@ -25943,7 +25943,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="448" spans="1:16" hidden="1">
+    <row r="448" spans="1:16">
       <c r="A448" t="s">
         <v>1162</v>
       </c>
@@ -25984,7 +25984,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="449" spans="1:16" hidden="1">
+    <row r="449" spans="1:16">
       <c r="A449" t="s">
         <v>1164</v>
       </c>
@@ -26025,7 +26025,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="450" spans="1:16" hidden="1">
+    <row r="450" spans="1:16">
       <c r="A450" t="s">
         <v>1166</v>
       </c>
@@ -26066,7 +26066,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="451" spans="1:16" hidden="1">
+    <row r="451" spans="1:16">
       <c r="A451" t="s">
         <v>1169</v>
       </c>
@@ -26107,7 +26107,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="452" spans="1:16" hidden="1">
+    <row r="452" spans="1:16">
       <c r="A452" t="s">
         <v>1171</v>
       </c>
@@ -26151,7 +26151,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="453" spans="1:16" hidden="1">
+    <row r="453" spans="1:16">
       <c r="A453" t="s">
         <v>1173</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="454" spans="1:16" hidden="1">
+    <row r="454" spans="1:16">
       <c r="A454" t="s">
         <v>1175</v>
       </c>
@@ -26236,7 +26236,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="455" spans="1:16" hidden="1">
+    <row r="455" spans="1:16">
       <c r="A455" t="s">
         <v>1177</v>
       </c>
@@ -26280,7 +26280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="456" spans="1:16" hidden="1">
+    <row r="456" spans="1:16">
       <c r="A456" t="s">
         <v>1179</v>
       </c>
@@ -26324,7 +26324,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="457" spans="1:16" hidden="1">
+    <row r="457" spans="1:16">
       <c r="A457" t="s">
         <v>1182</v>
       </c>
@@ -26365,7 +26365,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="458" spans="1:16" hidden="1">
+    <row r="458" spans="1:16">
       <c r="A458" t="s">
         <v>1186</v>
       </c>
@@ -26403,7 +26403,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="459" spans="1:16" hidden="1">
+    <row r="459" spans="1:16">
       <c r="A459" t="s">
         <v>1188</v>
       </c>
@@ -26447,7 +26447,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="460" spans="1:16" hidden="1">
+    <row r="460" spans="1:16">
       <c r="A460" t="s">
         <v>1192</v>
       </c>
@@ -26488,7 +26488,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="461" spans="1:16" hidden="1">
+    <row r="461" spans="1:16">
       <c r="A461" t="s">
         <v>1195</v>
       </c>
@@ -26529,7 +26529,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="462" spans="1:16" hidden="1">
+    <row r="462" spans="1:16">
       <c r="A462" t="s">
         <v>1197</v>
       </c>
@@ -26570,7 +26570,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="463" spans="1:16" hidden="1">
+    <row r="463" spans="1:16">
       <c r="A463" t="s">
         <v>1200</v>
       </c>
@@ -26611,7 +26611,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="464" spans="1:16" hidden="1">
+    <row r="464" spans="1:16">
       <c r="A464" t="s">
         <v>1203</v>
       </c>
@@ -26652,7 +26652,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="465" spans="1:16" hidden="1">
+    <row r="465" spans="1:16">
       <c r="A465" t="s">
         <v>1205</v>
       </c>
@@ -26693,7 +26693,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="466" spans="1:16" hidden="1">
+    <row r="466" spans="1:16">
       <c r="A466" t="s">
         <v>1208</v>
       </c>
@@ -26737,7 +26737,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="467" spans="1:16" hidden="1">
+    <row r="467" spans="1:16">
       <c r="A467" t="s">
         <v>1210</v>
       </c>
@@ -26778,7 +26778,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="468" spans="1:16" hidden="1">
+    <row r="468" spans="1:16">
       <c r="A468">
         <v>16003124</v>
       </c>
@@ -26819,7 +26819,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="469" spans="1:16" hidden="1">
+    <row r="469" spans="1:16">
       <c r="A469" t="s">
         <v>1214</v>
       </c>
@@ -26863,7 +26863,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="470" spans="1:16" hidden="1">
+    <row r="470" spans="1:16">
       <c r="A470" t="s">
         <v>1216</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="471" spans="1:16" hidden="1">
+    <row r="471" spans="1:16">
       <c r="A471" t="s">
         <v>1218</v>
       </c>
@@ -26951,7 +26951,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="472" spans="1:16" hidden="1">
+    <row r="472" spans="1:16">
       <c r="A472" t="s">
         <v>1220</v>
       </c>
@@ -26989,7 +26989,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="473" spans="1:16" hidden="1">
+    <row r="473" spans="1:16">
       <c r="A473" t="s">
         <v>1223</v>
       </c>
@@ -27033,7 +27033,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="474" spans="1:16" hidden="1">
+    <row r="474" spans="1:16">
       <c r="A474" t="s">
         <v>1225</v>
       </c>
@@ -27068,7 +27068,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="475" spans="1:16" hidden="1">
+    <row r="475" spans="1:16">
       <c r="A475" t="s">
         <v>1228</v>
       </c>
@@ -27106,7 +27106,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="476" spans="1:16" hidden="1">
+    <row r="476" spans="1:16">
       <c r="A476">
         <v>27100522</v>
       </c>
@@ -27147,7 +27147,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="477" spans="1:16" hidden="1">
+    <row r="477" spans="1:16">
       <c r="A477" t="s">
         <v>1232</v>
       </c>
@@ -27185,7 +27185,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="478" spans="1:16" hidden="1">
+    <row r="478" spans="1:16">
       <c r="A478" t="s">
         <v>1236</v>
       </c>
@@ -27226,7 +27226,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="479" spans="1:16" hidden="1">
+    <row r="479" spans="1:16">
       <c r="B479" t="s">
         <v>55</v>
       </c>
@@ -27264,7 +27264,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="480" spans="1:16" hidden="1">
+    <row r="480" spans="1:16">
       <c r="A480" t="s">
         <v>1240</v>
       </c>
@@ -27305,7 +27305,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="481" spans="1:18" hidden="1">
+    <row r="481" spans="1:18">
       <c r="A481" t="s">
         <v>1242</v>
       </c>
@@ -27349,7 +27349,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="482" spans="1:18" hidden="1">
+    <row r="482" spans="1:18">
       <c r="A482" t="s">
         <v>1246</v>
       </c>
@@ -27387,7 +27387,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="483" spans="1:18" hidden="1">
+    <row r="483" spans="1:18">
       <c r="A483" t="s">
         <v>1249</v>
       </c>
@@ -27428,7 +27428,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="484" spans="1:18" hidden="1">
+    <row r="484" spans="1:18">
       <c r="A484" t="s">
         <v>1252</v>
       </c>
@@ -27466,7 +27466,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="485" spans="1:18" hidden="1">
+    <row r="485" spans="1:18">
       <c r="A485">
         <v>43700325</v>
       </c>
@@ -27504,7 +27504,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="486" spans="1:18" hidden="1">
+    <row r="486" spans="1:18">
       <c r="A486">
         <v>43700524</v>
       </c>
@@ -27542,7 +27542,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="487" spans="1:18" hidden="1">
+    <row r="487" spans="1:18">
       <c r="A487" t="s">
         <v>1255</v>
       </c>
@@ -27583,7 +27583,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="488" spans="1:18" hidden="1">
+    <row r="488" spans="1:18">
       <c r="A488" t="s">
         <v>1256</v>
       </c>
@@ -27624,7 +27624,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="489" spans="1:18" hidden="1">
+    <row r="489" spans="1:18">
       <c r="A489" t="s">
         <v>1257</v>
       </c>
@@ -27665,7 +27665,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="490" spans="1:18" hidden="1">
+    <row r="490" spans="1:18">
       <c r="A490" t="s">
         <v>1259</v>
       </c>
@@ -27706,7 +27706,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="491" spans="1:18" hidden="1">
+    <row r="491" spans="1:18">
       <c r="A491" t="s">
         <v>1261</v>
       </c>
@@ -27747,7 +27747,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="492" spans="1:18" hidden="1">
+    <row r="492" spans="1:18">
       <c r="A492" t="s">
         <v>1262</v>
       </c>
@@ -27788,7 +27788,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="493" spans="1:18" hidden="1">
+    <row r="493" spans="1:18">
       <c r="A493" t="s">
         <v>1264</v>
       </c>
@@ -27873,7 +27873,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="495" spans="1:18" hidden="1">
+    <row r="495" spans="1:18">
       <c r="A495">
         <v>24000925</v>
       </c>
@@ -27914,7 +27914,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="496" spans="1:18" hidden="1">
+    <row r="496" spans="1:18">
       <c r="A496" t="s">
         <v>1274</v>
       </c>
@@ -27955,7 +27955,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="497" spans="1:16" hidden="1">
+    <row r="497" spans="1:16">
       <c r="A497" t="s">
         <v>1278</v>
       </c>
@@ -27996,7 +27996,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="498" spans="1:16" hidden="1">
+    <row r="498" spans="1:16">
       <c r="A498">
         <v>24001825</v>
       </c>
@@ -28037,7 +28037,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="499" spans="1:16" hidden="1">
+    <row r="499" spans="1:16">
       <c r="A499" t="s">
         <v>1283</v>
       </c>
@@ -28075,7 +28075,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="500" spans="1:16" hidden="1">
+    <row r="500" spans="1:16">
       <c r="A500" t="s">
         <v>1286</v>
       </c>
@@ -28119,7 +28119,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="501" spans="1:16" hidden="1">
+    <row r="501" spans="1:16">
       <c r="A501" t="s">
         <v>1290</v>
       </c>
@@ -28157,7 +28157,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="502" spans="1:16" hidden="1">
+    <row r="502" spans="1:16">
       <c r="A502" t="s">
         <v>1295</v>
       </c>
@@ -28198,7 +28198,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="503" spans="1:16" hidden="1">
+    <row r="503" spans="1:16">
       <c r="A503" t="s">
         <v>1298</v>
       </c>
@@ -28239,7 +28239,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="504" spans="1:16" hidden="1">
+    <row r="504" spans="1:16">
       <c r="A504" t="s">
         <v>1301</v>
       </c>
@@ -28280,7 +28280,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="505" spans="1:16" hidden="1">
+    <row r="505" spans="1:16">
       <c r="A505" t="s">
         <v>1303</v>
       </c>
@@ -28321,7 +28321,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="506" spans="1:16" hidden="1">
+    <row r="506" spans="1:16">
       <c r="A506" t="s">
         <v>1306</v>
       </c>
@@ -28362,7 +28362,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="507" spans="1:16" hidden="1">
+    <row r="507" spans="1:16">
       <c r="A507" t="s">
         <v>1309</v>
       </c>
@@ -28403,7 +28403,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="508" spans="1:16" hidden="1">
+    <row r="508" spans="1:16">
       <c r="A508" t="s">
         <v>1314</v>
       </c>
@@ -28444,7 +28444,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="509" spans="1:16" hidden="1">
+    <row r="509" spans="1:16">
       <c r="A509" t="s">
         <v>1316</v>
       </c>
@@ -28485,7 +28485,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="510" spans="1:16" hidden="1">
+    <row r="510" spans="1:16">
       <c r="A510" t="s">
         <v>1318</v>
       </c>
@@ -28526,7 +28526,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="511" spans="1:16" hidden="1">
+    <row r="511" spans="1:16">
       <c r="A511" t="s">
         <v>1319</v>
       </c>
@@ -28567,7 +28567,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="512" spans="1:16" hidden="1">
+    <row r="512" spans="1:16">
       <c r="A512" t="s">
         <v>1321</v>
       </c>
@@ -28608,7 +28608,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="513" spans="1:16" hidden="1">
+    <row r="513" spans="1:16">
       <c r="A513" t="s">
         <v>1323</v>
       </c>
@@ -28649,7 +28649,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="514" spans="1:16" hidden="1">
+    <row r="514" spans="1:16">
       <c r="A514" t="s">
         <v>1325</v>
       </c>
@@ -28690,7 +28690,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="515" spans="1:16" hidden="1">
+    <row r="515" spans="1:16">
       <c r="A515" t="s">
         <v>1327</v>
       </c>
@@ -28731,7 +28731,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="516" spans="1:16" hidden="1">
+    <row r="516" spans="1:16">
       <c r="A516" t="s">
         <v>1329</v>
       </c>
@@ -28772,7 +28772,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="517" spans="1:16" hidden="1">
+    <row r="517" spans="1:16">
       <c r="A517" t="s">
         <v>1330</v>
       </c>
@@ -28813,7 +28813,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="518" spans="1:16" hidden="1">
+    <row r="518" spans="1:16">
       <c r="A518" t="s">
         <v>1334</v>
       </c>
@@ -28848,7 +28848,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="519" spans="1:16" hidden="1">
+    <row r="519" spans="1:16">
       <c r="A519" t="s">
         <v>1336</v>
       </c>
@@ -28883,7 +28883,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="520" spans="1:16" hidden="1">
+    <row r="520" spans="1:16">
       <c r="A520" t="s">
         <v>1339</v>
       </c>
@@ -28921,7 +28921,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="521" spans="1:16" hidden="1">
+    <row r="521" spans="1:16">
       <c r="A521" t="s">
         <v>1343</v>
       </c>
@@ -28959,7 +28959,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="522" spans="1:16" hidden="1">
+    <row r="522" spans="1:16">
       <c r="A522" t="s">
         <v>1346</v>
       </c>
@@ -28997,7 +28997,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="523" spans="1:16" hidden="1">
+    <row r="523" spans="1:16">
       <c r="A523" t="s">
         <v>1349</v>
       </c>
@@ -29032,7 +29032,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="524" spans="1:16" hidden="1">
+    <row r="524" spans="1:16">
       <c r="A524" t="s">
         <v>1352</v>
       </c>
@@ -29070,7 +29070,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="525" spans="1:16" hidden="1">
+    <row r="525" spans="1:16">
       <c r="A525" t="s">
         <v>1355</v>
       </c>
@@ -29108,7 +29108,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="526" spans="1:16" hidden="1">
+    <row r="526" spans="1:16">
       <c r="A526" t="s">
         <v>1358</v>
       </c>
@@ -29146,7 +29146,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="527" spans="1:16" hidden="1">
+    <row r="527" spans="1:16">
       <c r="A527" t="s">
         <v>1361</v>
       </c>
@@ -29184,7 +29184,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="528" spans="1:16" hidden="1">
+    <row r="528" spans="1:16">
       <c r="A528" t="s">
         <v>1363</v>
       </c>
@@ -29222,7 +29222,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="529" spans="1:16" hidden="1">
+    <row r="529" spans="1:16">
       <c r="A529" t="s">
         <v>1365</v>
       </c>
@@ -29260,7 +29260,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="530" spans="1:16" hidden="1">
+    <row r="530" spans="1:16">
       <c r="A530" t="s">
         <v>1367</v>
       </c>
@@ -29298,7 +29298,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="531" spans="1:16" hidden="1">
+    <row r="531" spans="1:16">
       <c r="A531" t="s">
         <v>1369</v>
       </c>
@@ -29336,7 +29336,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="532" spans="1:16" hidden="1">
+    <row r="532" spans="1:16">
       <c r="A532" t="s">
         <v>1371</v>
       </c>
@@ -29374,7 +29374,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="533" spans="1:16" hidden="1">
+    <row r="533" spans="1:16">
       <c r="A533" t="s">
         <v>1372</v>
       </c>
@@ -29412,7 +29412,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="534" spans="1:16" hidden="1">
+    <row r="534" spans="1:16">
       <c r="A534" t="s">
         <v>1375</v>
       </c>
@@ -29450,7 +29450,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="535" spans="1:16" hidden="1">
+    <row r="535" spans="1:16">
       <c r="A535" t="s">
         <v>1378</v>
       </c>
@@ -29488,7 +29488,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="536" spans="1:16" hidden="1">
+    <row r="536" spans="1:16">
       <c r="A536" t="s">
         <v>1381</v>
       </c>
@@ -29526,7 +29526,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="537" spans="1:16" hidden="1">
+    <row r="537" spans="1:16">
       <c r="A537" t="s">
         <v>1383</v>
       </c>
@@ -29564,7 +29564,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="538" spans="1:16" hidden="1">
+    <row r="538" spans="1:16">
       <c r="A538" t="s">
         <v>1386</v>
       </c>
@@ -29602,7 +29602,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="539" spans="1:16" hidden="1">
+    <row r="539" spans="1:16">
       <c r="A539" t="s">
         <v>1388</v>
       </c>
@@ -29640,7 +29640,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="540" spans="1:16" hidden="1">
+    <row r="540" spans="1:16">
       <c r="A540" t="s">
         <v>1390</v>
       </c>
@@ -29678,7 +29678,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="541" spans="1:16" hidden="1">
+    <row r="541" spans="1:16">
       <c r="A541" t="s">
         <v>1392</v>
       </c>
@@ -29716,7 +29716,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="542" spans="1:16" hidden="1">
+    <row r="542" spans="1:16">
       <c r="A542" t="s">
         <v>1395</v>
       </c>
@@ -29754,7 +29754,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="543" spans="1:16" hidden="1">
+    <row r="543" spans="1:16">
       <c r="A543" t="s">
         <v>1398</v>
       </c>
@@ -29792,7 +29792,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="544" spans="1:16" hidden="1">
+    <row r="544" spans="1:16">
       <c r="A544" t="s">
         <v>1400</v>
       </c>
@@ -29830,7 +29830,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1">
+    <row r="545" spans="1:16">
       <c r="A545" t="s">
         <v>1402</v>
       </c>
@@ -29871,7 +29871,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1">
+    <row r="546" spans="1:16">
       <c r="A546" t="s">
         <v>1404</v>
       </c>
@@ -29912,7 +29912,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1">
+    <row r="547" spans="1:16">
       <c r="A547" t="s">
         <v>1406</v>
       </c>
@@ -29953,7 +29953,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1">
+    <row r="548" spans="1:16">
       <c r="A548" t="s">
         <v>1408</v>
       </c>
@@ -29994,7 +29994,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="549" spans="1:16" hidden="1">
+    <row r="549" spans="1:16">
       <c r="A549" t="s">
         <v>1410</v>
       </c>
@@ -30035,7 +30035,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1">
+    <row r="550" spans="1:16">
       <c r="A550" t="s">
         <v>1412</v>
       </c>
@@ -30073,7 +30073,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="551" spans="1:16" hidden="1">
+    <row r="551" spans="1:16">
       <c r="A551" t="s">
         <v>1418</v>
       </c>
@@ -30111,7 +30111,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="552" spans="1:16" hidden="1">
+    <row r="552" spans="1:16">
       <c r="A552" t="s">
         <v>1420</v>
       </c>
@@ -30146,7 +30146,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="553" spans="1:16" hidden="1">
+    <row r="553" spans="1:16">
       <c r="A553" t="s">
         <v>1424</v>
       </c>
@@ -30181,7 +30181,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1">
+    <row r="554" spans="1:16">
       <c r="A554" t="s">
         <v>1428</v>
       </c>
@@ -30216,7 +30216,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="555" spans="1:16" hidden="1">
+    <row r="555" spans="1:16">
       <c r="A555" t="s">
         <v>1431</v>
       </c>
@@ -30251,7 +30251,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1">
+    <row r="556" spans="1:16">
       <c r="A556" t="s">
         <v>1435</v>
       </c>
@@ -30289,7 +30289,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1">
+    <row r="557" spans="1:16">
       <c r="A557" t="s">
         <v>1438</v>
       </c>
@@ -30324,7 +30324,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1">
+    <row r="558" spans="1:16">
       <c r="A558" t="s">
         <v>1442</v>
       </c>
@@ -30359,7 +30359,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="559" spans="1:16" hidden="1">
+    <row r="559" spans="1:16">
       <c r="A559" t="s">
         <v>1445</v>
       </c>
@@ -30397,7 +30397,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1">
+    <row r="560" spans="1:16">
       <c r="A560" t="s">
         <v>1448</v>
       </c>
@@ -30435,7 +30435,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="561" spans="1:16" hidden="1">
+    <row r="561" spans="1:16">
       <c r="A561" t="s">
         <v>1452</v>
       </c>
@@ -30473,7 +30473,7 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1">
+    <row r="562" spans="1:16">
       <c r="A562" t="s">
         <v>1457</v>
       </c>
@@ -31194,6 +31194,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31206,16 +31216,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52029,12 +52029,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52319,20 +52323,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -52340,5 +52340,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}"/>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13395235-6B7E-4FBA-BA06-F85BF3A036E9}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{622E7F39-2813-4114-87E9-79E142B10638}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10400" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10399" uniqueCount="2355">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -13091,8 +13091,8 @@
       <c r="H131" t="s">
         <v>422</v>
       </c>
-      <c r="J131" t="s">
-        <v>61</v>
+      <c r="J131">
+        <v>2024</v>
       </c>
       <c r="K131">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C09D531-9E06-4476-A9A9-AEBE5AEC2629}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F57A8AB0-7BAF-45E4-A438-34EA8AA86247}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28236,7 +28236,7 @@
         <v>6.1</v>
       </c>
       <c r="P503" s="8">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="504" spans="1:16">

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F57A8AB0-7BAF-45E4-A438-34EA8AA86247}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1165C9E-F311-4112-BBC8-EA2B52F2116F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7119,8 +7119,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -7338,10 +7339,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7373,6 +7370,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -7896,7 +7897,7 @@
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="12" style="8" customWidth="1"/>
+    <col min="16" max="16" width="12" style="19" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
     <col min="18" max="18" width="8" customWidth="1"/>
   </cols>
@@ -7947,7 +7948,7 @@
       <c r="O1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="18" t="s">
         <v>52</v>
       </c>
       <c r="Q1" s="2" t="s">
@@ -7991,7 +7992,7 @@
       <c r="M2">
         <v>180</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8029,7 +8030,7 @@
       <c r="M3">
         <v>180</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8067,7 +8068,7 @@
       <c r="M4">
         <v>180</v>
       </c>
-      <c r="P4" s="8">
+      <c r="P4" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8108,7 +8109,7 @@
       <c r="M5">
         <v>191</v>
       </c>
-      <c r="P5" s="8">
+      <c r="P5" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8146,7 +8147,7 @@
       <c r="M6">
         <v>7</v>
       </c>
-      <c r="P6" s="8">
+      <c r="P6" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8187,7 +8188,7 @@
       <c r="M7">
         <v>564</v>
       </c>
-      <c r="P7" s="8">
+      <c r="P7" s="19">
         <v>46155</v>
       </c>
       <c r="R7" t="s">
@@ -8231,7 +8232,7 @@
       <c r="M8">
         <v>411</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8272,7 +8273,7 @@
       <c r="M9">
         <v>7</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="19">
         <v>46155</v>
       </c>
       <c r="R9" t="s">
@@ -8316,7 +8317,7 @@
       <c r="M10">
         <v>10</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="19">
         <v>46155</v>
       </c>
       <c r="R10" t="s">
@@ -8357,7 +8358,7 @@
       <c r="M11">
         <v>153</v>
       </c>
-      <c r="P11" s="8">
+      <c r="P11" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8395,7 +8396,7 @@
       <c r="M12">
         <v>381</v>
       </c>
-      <c r="P12" s="8">
+      <c r="P12" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8436,7 +8437,7 @@
       <c r="M13">
         <v>13</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8477,7 +8478,7 @@
       <c r="M14">
         <v>29</v>
       </c>
-      <c r="P14" s="8">
+      <c r="P14" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8518,7 +8519,7 @@
       <c r="M15">
         <v>37</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P15" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8559,7 +8560,7 @@
       <c r="M16">
         <v>13</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="19">
         <v>46155</v>
       </c>
       <c r="R16" t="s">
@@ -8603,7 +8604,7 @@
       <c r="M17">
         <v>5</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="19">
         <v>46155</v>
       </c>
       <c r="R17" t="s">
@@ -8644,7 +8645,7 @@
       <c r="M18">
         <v>33</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P18" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8682,7 +8683,7 @@
       <c r="M19">
         <v>6</v>
       </c>
-      <c r="P19" s="8">
+      <c r="P19" s="19">
         <v>46155</v>
       </c>
       <c r="R19" t="s">
@@ -8723,7 +8724,7 @@
       <c r="M20">
         <v>110</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="19">
         <v>46155</v>
       </c>
       <c r="R20" t="s">
@@ -8764,7 +8765,7 @@
       <c r="M21">
         <v>30</v>
       </c>
-      <c r="P21" s="8">
+      <c r="P21" s="19">
         <v>46155</v>
       </c>
       <c r="R21" t="s">
@@ -8805,7 +8806,7 @@
       <c r="M22">
         <v>37</v>
       </c>
-      <c r="P22" s="8">
+      <c r="P22" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8843,7 +8844,7 @@
       <c r="M23">
         <v>0</v>
       </c>
-      <c r="P23" s="8">
+      <c r="P23" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8881,7 +8882,7 @@
       <c r="M24">
         <v>0</v>
       </c>
-      <c r="P24" s="8">
+      <c r="P24" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8919,7 +8920,7 @@
       <c r="M25">
         <v>233</v>
       </c>
-      <c r="P25" s="8">
+      <c r="P25" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8960,7 +8961,7 @@
       <c r="M26">
         <v>93</v>
       </c>
-      <c r="P26" s="8">
+      <c r="P26" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -8998,7 +8999,7 @@
       <c r="M27">
         <v>45</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P27" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9036,7 +9037,7 @@
       <c r="M28">
         <v>60</v>
       </c>
-      <c r="P28" s="8">
+      <c r="P28" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9074,7 +9075,7 @@
       <c r="M29">
         <v>35</v>
       </c>
-      <c r="P29" s="8">
+      <c r="P29" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9115,7 +9116,7 @@
       <c r="M30">
         <v>43</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P30" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9156,7 +9157,7 @@
       <c r="M31">
         <v>164</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P31" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9197,7 +9198,7 @@
       <c r="M32">
         <v>72</v>
       </c>
-      <c r="P32" s="8">
+      <c r="P32" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9238,7 +9239,7 @@
       <c r="M33">
         <v>596</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P33" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9279,7 +9280,7 @@
       <c r="M34">
         <v>881</v>
       </c>
-      <c r="P34" s="8">
+      <c r="P34" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9314,7 +9315,7 @@
       <c r="L35">
         <v>5.25</v>
       </c>
-      <c r="P35" s="8">
+      <c r="P35" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9355,7 +9356,7 @@
       <c r="M36">
         <v>497</v>
       </c>
-      <c r="P36" s="8">
+      <c r="P36" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9396,7 +9397,7 @@
       <c r="M37">
         <v>0</v>
       </c>
-      <c r="P37" s="8">
+      <c r="P37" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9434,7 +9435,7 @@
       <c r="L38">
         <v>16.649999999999999</v>
       </c>
-      <c r="P38" s="8">
+      <c r="P38" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9472,7 +9473,7 @@
       <c r="M39">
         <v>117</v>
       </c>
-      <c r="P39" s="8">
+      <c r="P39" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9513,7 +9514,7 @@
       <c r="M40">
         <v>27</v>
       </c>
-      <c r="P40" s="8">
+      <c r="P40" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9557,7 +9558,7 @@
       <c r="M41">
         <v>102</v>
       </c>
-      <c r="P41" s="8">
+      <c r="P41" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9598,7 +9599,7 @@
       <c r="M42">
         <v>63</v>
       </c>
-      <c r="P42" s="8">
+      <c r="P42" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9642,7 +9643,7 @@
       <c r="M43">
         <v>126</v>
       </c>
-      <c r="P43" s="8">
+      <c r="P43" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9683,7 +9684,7 @@
       <c r="M44">
         <v>216</v>
       </c>
-      <c r="P44" s="8">
+      <c r="P44" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9721,7 +9722,7 @@
       <c r="M45">
         <v>72</v>
       </c>
-      <c r="P45" s="8">
+      <c r="P45" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9759,7 +9760,7 @@
       <c r="M46">
         <v>248</v>
       </c>
-      <c r="P46" s="8">
+      <c r="P46" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9797,7 +9798,7 @@
       <c r="M47">
         <v>138</v>
       </c>
-      <c r="P47" s="8">
+      <c r="P47" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9838,7 +9839,7 @@
       <c r="M48">
         <v>332</v>
       </c>
-      <c r="P48" s="8">
+      <c r="P48" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9879,7 +9880,7 @@
       <c r="M49">
         <v>346</v>
       </c>
-      <c r="P49" s="8">
+      <c r="P49" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9917,7 +9918,7 @@
       <c r="M50">
         <v>180</v>
       </c>
-      <c r="P50" s="8">
+      <c r="P50" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9958,7 +9959,7 @@
       <c r="M51">
         <v>257</v>
       </c>
-      <c r="P51" s="8">
+      <c r="P51" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -9996,7 +9997,7 @@
       <c r="M52">
         <v>48</v>
       </c>
-      <c r="P52" s="8">
+      <c r="P52" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10034,7 +10035,7 @@
       <c r="M53">
         <v>15</v>
       </c>
-      <c r="P53" s="8">
+      <c r="P53" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10072,7 +10073,7 @@
       <c r="M54">
         <v>92</v>
       </c>
-      <c r="P54" s="8">
+      <c r="P54" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10110,7 +10111,7 @@
       <c r="M55">
         <v>9</v>
       </c>
-      <c r="P55" s="8">
+      <c r="P55" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10154,7 +10155,7 @@
       <c r="M56">
         <v>902</v>
       </c>
-      <c r="P56" s="8">
+      <c r="P56" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10192,7 +10193,7 @@
       <c r="M57">
         <v>87</v>
       </c>
-      <c r="P57" s="8">
+      <c r="P57" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10233,7 +10234,7 @@
       <c r="M58">
         <v>46</v>
       </c>
-      <c r="P58" s="8">
+      <c r="P58" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10271,7 +10272,7 @@
       <c r="M59">
         <v>45</v>
       </c>
-      <c r="P59" s="8">
+      <c r="P59" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10312,7 +10313,7 @@
       <c r="M60">
         <v>0</v>
       </c>
-      <c r="P60" s="8">
+      <c r="P60" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10347,7 +10348,7 @@
       <c r="L61">
         <v>31</v>
       </c>
-      <c r="P61" s="8">
+      <c r="P61" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10388,7 +10389,7 @@
       <c r="M62">
         <v>165</v>
       </c>
-      <c r="P62" s="8">
+      <c r="P62" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10426,7 +10427,7 @@
       <c r="M63">
         <v>162</v>
       </c>
-      <c r="P63" s="8">
+      <c r="P63" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10470,7 +10471,7 @@
       <c r="M64">
         <v>0</v>
       </c>
-      <c r="P64" s="8">
+      <c r="P64" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10508,7 +10509,7 @@
       <c r="M65">
         <v>702</v>
       </c>
-      <c r="P65" s="8">
+      <c r="P65" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10546,7 +10547,7 @@
       <c r="M66">
         <v>12</v>
       </c>
-      <c r="P66" s="8">
+      <c r="P66" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10584,7 +10585,7 @@
       <c r="M67">
         <v>36</v>
       </c>
-      <c r="P67" s="8">
+      <c r="P67" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10622,7 +10623,7 @@
       <c r="M68">
         <v>69</v>
       </c>
-      <c r="P68" s="8">
+      <c r="P68" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10660,7 +10661,7 @@
       <c r="M69">
         <v>0</v>
       </c>
-      <c r="P69" s="8">
+      <c r="P69" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10698,7 +10699,7 @@
       <c r="M70">
         <v>213</v>
       </c>
-      <c r="P70" s="8">
+      <c r="P70" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10736,7 +10737,7 @@
       <c r="M71">
         <v>57</v>
       </c>
-      <c r="P71" s="8">
+      <c r="P71" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10777,7 +10778,7 @@
       <c r="M72">
         <v>102</v>
       </c>
-      <c r="P72" s="8">
+      <c r="P72" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10821,7 +10822,7 @@
       <c r="M73">
         <v>0</v>
       </c>
-      <c r="P73" s="8">
+      <c r="P73" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10862,7 +10863,7 @@
       <c r="M74">
         <v>15</v>
       </c>
-      <c r="P74" s="8">
+      <c r="P74" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10900,7 +10901,7 @@
       <c r="M75">
         <v>210</v>
       </c>
-      <c r="P75" s="8">
+      <c r="P75" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10938,7 +10939,7 @@
       <c r="M76">
         <v>114</v>
       </c>
-      <c r="P76" s="8">
+      <c r="P76" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -10976,7 +10977,7 @@
       <c r="M77">
         <v>264</v>
       </c>
-      <c r="P77" s="8">
+      <c r="P77" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11011,7 +11012,7 @@
       <c r="M78">
         <v>828</v>
       </c>
-      <c r="P78" s="8">
+      <c r="P78" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11049,7 +11050,7 @@
       <c r="M79">
         <v>6122</v>
       </c>
-      <c r="P79" s="8">
+      <c r="P79" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11090,7 +11091,7 @@
       <c r="M80">
         <v>726</v>
       </c>
-      <c r="P80" s="8">
+      <c r="P80" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11128,7 +11129,7 @@
       <c r="M81">
         <v>310</v>
       </c>
-      <c r="P81" s="8">
+      <c r="P81" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11166,7 +11167,7 @@
       <c r="M82">
         <v>81</v>
       </c>
-      <c r="P82" s="8">
+      <c r="P82" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11204,7 +11205,7 @@
       <c r="L83">
         <v>8</v>
       </c>
-      <c r="P83" s="8">
+      <c r="P83" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11242,7 +11243,7 @@
       <c r="M84">
         <v>237</v>
       </c>
-      <c r="P84" s="8">
+      <c r="P84" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11283,7 +11284,7 @@
       <c r="M85">
         <v>581</v>
       </c>
-      <c r="P85" s="8">
+      <c r="P85" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11321,7 +11322,7 @@
       <c r="M86">
         <v>9</v>
       </c>
-      <c r="P86" s="8">
+      <c r="P86" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11359,7 +11360,7 @@
       <c r="M87">
         <v>6</v>
       </c>
-      <c r="P87" s="8">
+      <c r="P87" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11394,7 +11395,7 @@
       <c r="M88">
         <v>6</v>
       </c>
-      <c r="P88" s="8">
+      <c r="P88" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11432,7 +11433,7 @@
       <c r="M89">
         <v>902</v>
       </c>
-      <c r="P89" s="8">
+      <c r="P89" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11464,7 +11465,7 @@
       <c r="L90">
         <v>13.85</v>
       </c>
-      <c r="P90" s="8">
+      <c r="P90" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11502,7 +11503,7 @@
       <c r="M91">
         <v>780</v>
       </c>
-      <c r="P91" s="8">
+      <c r="P91" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11537,7 +11538,7 @@
       <c r="M92">
         <v>342</v>
       </c>
-      <c r="P92" s="8">
+      <c r="P92" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11578,7 +11579,7 @@
       <c r="M93">
         <v>342</v>
       </c>
-      <c r="P93" s="8">
+      <c r="P93" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11619,7 +11620,7 @@
       <c r="M94">
         <v>342</v>
       </c>
-      <c r="P94" s="8">
+      <c r="P94" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11660,7 +11661,7 @@
       <c r="M95">
         <v>66</v>
       </c>
-      <c r="P95" s="8">
+      <c r="P95" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11701,7 +11702,7 @@
       <c r="M96">
         <v>12</v>
       </c>
-      <c r="P96" s="8">
+      <c r="P96" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11742,7 +11743,7 @@
       <c r="M97">
         <v>108</v>
       </c>
-      <c r="P97" s="8">
+      <c r="P97" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11786,7 +11787,7 @@
       <c r="M98">
         <v>856</v>
       </c>
-      <c r="P98" s="8">
+      <c r="P98" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11827,7 +11828,7 @@
       <c r="M99">
         <v>132</v>
       </c>
-      <c r="P99" s="8">
+      <c r="P99" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11868,7 +11869,7 @@
       <c r="M100">
         <v>120</v>
       </c>
-      <c r="P100" s="8">
+      <c r="P100" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11909,7 +11910,7 @@
       <c r="M101">
         <v>187</v>
       </c>
-      <c r="P101" s="8">
+      <c r="P101" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11950,7 +11951,7 @@
       <c r="M102">
         <v>36</v>
       </c>
-      <c r="P102" s="8">
+      <c r="P102" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -11991,7 +11992,7 @@
       <c r="M103">
         <v>0</v>
       </c>
-      <c r="P103" s="8">
+      <c r="P103" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12032,7 +12033,7 @@
       <c r="M104">
         <v>156</v>
       </c>
-      <c r="P104" s="8">
+      <c r="P104" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12073,7 +12074,7 @@
       <c r="M105">
         <v>28</v>
       </c>
-      <c r="P105" s="8">
+      <c r="P105" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12114,7 +12115,7 @@
       <c r="M106">
         <v>206</v>
       </c>
-      <c r="P106" s="8">
+      <c r="P106" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12155,7 +12156,7 @@
       <c r="M107">
         <v>63</v>
       </c>
-      <c r="P107" s="8">
+      <c r="P107" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12196,7 +12197,7 @@
       <c r="M108">
         <v>78</v>
       </c>
-      <c r="P108" s="8">
+      <c r="P108" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12234,7 +12235,7 @@
       <c r="M109">
         <v>36</v>
       </c>
-      <c r="P109" s="8">
+      <c r="P109" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12269,7 +12270,7 @@
       <c r="L110">
         <v>10.65</v>
       </c>
-      <c r="P110" s="8">
+      <c r="P110" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12304,7 +12305,7 @@
       <c r="L111">
         <v>11.95</v>
       </c>
-      <c r="P111" s="8">
+      <c r="P111" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12342,7 +12343,7 @@
       <c r="M112">
         <v>152</v>
       </c>
-      <c r="P112" s="8">
+      <c r="P112" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12380,7 +12381,7 @@
       <c r="M113">
         <v>108</v>
       </c>
-      <c r="P113" s="8">
+      <c r="P113" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12424,7 +12425,7 @@
       <c r="M114">
         <v>0</v>
       </c>
-      <c r="P114" s="8">
+      <c r="P114" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12465,7 +12466,7 @@
       <c r="M115">
         <v>138</v>
       </c>
-      <c r="P115" s="8">
+      <c r="P115" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12509,7 +12510,7 @@
       <c r="M116">
         <v>0</v>
       </c>
-      <c r="P116" s="8">
+      <c r="P116" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12547,7 +12548,7 @@
       <c r="M117">
         <v>87</v>
       </c>
-      <c r="P117" s="8">
+      <c r="P117" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12585,7 +12586,7 @@
       <c r="M118">
         <v>36</v>
       </c>
-      <c r="P118" s="8">
+      <c r="P118" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12629,7 +12630,7 @@
       <c r="M119">
         <v>0</v>
       </c>
-      <c r="P119" s="8">
+      <c r="P119" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12673,7 +12674,7 @@
       <c r="M120">
         <v>0</v>
       </c>
-      <c r="P120" s="8">
+      <c r="P120" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12708,7 +12709,7 @@
       <c r="L121">
         <v>12.5</v>
       </c>
-      <c r="P121" s="8">
+      <c r="P121" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12743,7 +12744,7 @@
       <c r="L122">
         <v>14.9</v>
       </c>
-      <c r="P122" s="8">
+      <c r="P122" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12784,7 +12785,7 @@
       <c r="M123">
         <v>68</v>
       </c>
-      <c r="P123" s="8">
+      <c r="P123" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12825,7 +12826,7 @@
       <c r="M124">
         <v>68</v>
       </c>
-      <c r="P124" s="8">
+      <c r="P124" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12863,7 +12864,7 @@
       <c r="M125">
         <v>68</v>
       </c>
-      <c r="P125" s="8">
+      <c r="P125" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12901,7 +12902,7 @@
       <c r="M126">
         <v>137</v>
       </c>
-      <c r="P126" s="8">
+      <c r="P126" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12942,7 +12943,7 @@
       <c r="M127">
         <v>539</v>
       </c>
-      <c r="P127" s="8">
+      <c r="P127" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -12983,7 +12984,7 @@
       <c r="M128">
         <v>9</v>
       </c>
-      <c r="P128" s="8">
+      <c r="P128" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13024,7 +13025,7 @@
       <c r="M129">
         <v>87</v>
       </c>
-      <c r="P129" s="8">
+      <c r="P129" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13065,7 +13066,7 @@
       <c r="M130">
         <v>0</v>
       </c>
-      <c r="P130" s="8">
+      <c r="P130" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13106,7 +13107,7 @@
       <c r="M131">
         <v>174</v>
       </c>
-      <c r="P131" s="8">
+      <c r="P131" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13147,7 +13148,7 @@
       <c r="M132">
         <v>3</v>
       </c>
-      <c r="P132" s="8">
+      <c r="P132" s="19">
         <v>46182</v>
       </c>
     </row>
@@ -13188,7 +13189,7 @@
       <c r="M133">
         <v>15</v>
       </c>
-      <c r="P133" s="8">
+      <c r="P133" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13232,7 +13233,7 @@
       <c r="M134">
         <v>677</v>
       </c>
-      <c r="P134" s="8">
+      <c r="P134" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13273,7 +13274,7 @@
       <c r="M135">
         <v>3</v>
       </c>
-      <c r="P135" s="8">
+      <c r="P135" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13311,7 +13312,7 @@
       <c r="M136">
         <v>15</v>
       </c>
-      <c r="P136" s="8">
+      <c r="P136" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13352,7 +13353,7 @@
       <c r="M137">
         <v>51</v>
       </c>
-      <c r="P137" s="8">
+      <c r="P137" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13390,7 +13391,7 @@
       <c r="M138">
         <v>0</v>
       </c>
-      <c r="P138" s="8">
+      <c r="P138" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13426,13 +13427,13 @@
         <v>75</v>
       </c>
       <c r="L139">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="M139">
         <v>9</v>
       </c>
-      <c r="P139" s="8">
-        <v>46155</v>
+      <c r="P139" s="19">
+        <v>46275</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -13472,7 +13473,7 @@
       <c r="M140">
         <v>3</v>
       </c>
-      <c r="P140" s="8">
+      <c r="P140" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13513,7 +13514,7 @@
       <c r="M141">
         <v>69</v>
       </c>
-      <c r="P141" s="8">
+      <c r="P141" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13554,7 +13555,7 @@
       <c r="M142">
         <v>135</v>
       </c>
-      <c r="P142" s="8">
+      <c r="P142" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13595,7 +13596,7 @@
       <c r="M143">
         <v>305</v>
       </c>
-      <c r="P143" s="8">
+      <c r="P143" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13639,7 +13640,7 @@
       <c r="M144">
         <v>1282</v>
       </c>
-      <c r="P144" s="8">
+      <c r="P144" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13680,7 +13681,7 @@
       <c r="M145">
         <v>377</v>
       </c>
-      <c r="P145" s="8">
+      <c r="P145" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13718,7 +13719,7 @@
       <c r="M146">
         <v>9</v>
       </c>
-      <c r="P146" s="8">
+      <c r="P146" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13759,7 +13760,7 @@
       <c r="M147">
         <v>9</v>
       </c>
-      <c r="P147" s="8">
+      <c r="P147" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13794,7 +13795,7 @@
       <c r="L148">
         <v>45.2</v>
       </c>
-      <c r="P148" s="8">
+      <c r="P148" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13835,7 +13836,7 @@
       <c r="M149">
         <v>9</v>
       </c>
-      <c r="P149" s="8">
+      <c r="P149" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13879,7 +13880,7 @@
       <c r="M150">
         <v>19</v>
       </c>
-      <c r="P150" s="8">
+      <c r="P150" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13914,7 +13915,7 @@
       <c r="L151">
         <v>17.2</v>
       </c>
-      <c r="P151" s="8">
+      <c r="P151" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13955,7 +13956,7 @@
       <c r="M152">
         <v>3</v>
       </c>
-      <c r="P152" s="8">
+      <c r="P152" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -13996,7 +13997,7 @@
       <c r="M153">
         <v>1</v>
       </c>
-      <c r="P153" s="8">
+      <c r="P153" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14037,7 +14038,7 @@
       <c r="M154">
         <v>116</v>
       </c>
-      <c r="P154" s="8">
+      <c r="P154" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14078,7 +14079,7 @@
       <c r="M155">
         <v>116</v>
       </c>
-      <c r="P155" s="8">
+      <c r="P155" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14119,7 +14120,7 @@
       <c r="M156">
         <v>3</v>
       </c>
-      <c r="P156" s="8">
+      <c r="P156" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14160,7 +14161,7 @@
       <c r="M157">
         <v>38</v>
       </c>
-      <c r="P157" s="8">
+      <c r="P157" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14204,7 +14205,7 @@
       <c r="M158">
         <v>102</v>
       </c>
-      <c r="P158" s="8">
+      <c r="P158" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14245,7 +14246,7 @@
       <c r="M159">
         <v>6</v>
       </c>
-      <c r="P159" s="8">
+      <c r="P159" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14286,7 +14287,7 @@
       <c r="M160">
         <v>0</v>
       </c>
-      <c r="P160" s="8">
+      <c r="P160" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14327,7 +14328,7 @@
       <c r="M161">
         <v>6</v>
       </c>
-      <c r="P161" s="8">
+      <c r="P161" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14368,7 +14369,7 @@
       <c r="M162">
         <v>3</v>
       </c>
-      <c r="P162" s="8">
+      <c r="P162" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14409,7 +14410,7 @@
       <c r="M163">
         <v>378</v>
       </c>
-      <c r="P163" s="8">
+      <c r="P163" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14453,7 +14454,7 @@
       <c r="M164">
         <v>462</v>
       </c>
-      <c r="P164" s="8">
+      <c r="P164" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14488,7 +14489,7 @@
       <c r="L165">
         <v>16.7</v>
       </c>
-      <c r="P165" s="8">
+      <c r="P165" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14523,7 +14524,7 @@
       <c r="L166">
         <v>19</v>
       </c>
-      <c r="P166" s="8">
+      <c r="P166" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14561,7 +14562,7 @@
       <c r="M167">
         <v>474</v>
       </c>
-      <c r="P167" s="8">
+      <c r="P167" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14602,7 +14603,7 @@
       <c r="M168">
         <v>0</v>
       </c>
-      <c r="P168" s="8">
+      <c r="P168" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14643,7 +14644,7 @@
       <c r="M169">
         <v>6</v>
       </c>
-      <c r="P169" s="8">
+      <c r="P169" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14681,7 +14682,7 @@
       <c r="M170">
         <v>51</v>
       </c>
-      <c r="P170" s="8">
+      <c r="P170" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14722,7 +14723,7 @@
       <c r="M171">
         <v>17</v>
       </c>
-      <c r="P171" s="8">
+      <c r="P171" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14757,7 +14758,7 @@
       <c r="L172">
         <v>26</v>
       </c>
-      <c r="P172" s="8">
+      <c r="P172" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14801,7 +14802,7 @@
       <c r="M173">
         <v>84</v>
       </c>
-      <c r="P173" s="8">
+      <c r="P173" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14842,7 +14843,7 @@
       <c r="M174">
         <v>67</v>
       </c>
-      <c r="P174" s="8">
+      <c r="P174" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14883,7 +14884,7 @@
       <c r="M175">
         <v>3</v>
       </c>
-      <c r="P175" s="8">
+      <c r="P175" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14924,7 +14925,7 @@
       <c r="M176">
         <v>0</v>
       </c>
-      <c r="P176" s="8">
+      <c r="P176" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -14968,7 +14969,7 @@
       <c r="M177">
         <v>149</v>
       </c>
-      <c r="P177" s="8">
+      <c r="P177" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15009,7 +15010,7 @@
       <c r="M178">
         <v>6</v>
       </c>
-      <c r="P178" s="8">
+      <c r="P178" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15053,7 +15054,7 @@
       <c r="M179">
         <v>95</v>
       </c>
-      <c r="P179" s="8">
+      <c r="P179" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15091,7 +15092,7 @@
       <c r="M180">
         <v>18</v>
       </c>
-      <c r="P180" s="8">
+      <c r="P180" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15132,7 +15133,7 @@
       <c r="M181">
         <v>811</v>
       </c>
-      <c r="P181" s="8">
+      <c r="P181" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15173,7 +15174,7 @@
       <c r="M182">
         <v>811</v>
       </c>
-      <c r="P182" s="8">
+      <c r="P182" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15214,7 +15215,7 @@
       <c r="M183">
         <v>292</v>
       </c>
-      <c r="P183" s="8">
+      <c r="P183" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15255,7 +15256,7 @@
       <c r="M184">
         <v>432</v>
       </c>
-      <c r="P184" s="8">
+      <c r="P184" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15296,7 +15297,7 @@
       <c r="M185">
         <v>9</v>
       </c>
-      <c r="P185" s="8">
+      <c r="P185" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15337,7 +15338,7 @@
       <c r="M186">
         <v>18</v>
       </c>
-      <c r="P186" s="8">
+      <c r="P186" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15378,7 +15379,7 @@
       <c r="M187">
         <v>145</v>
       </c>
-      <c r="P187" s="8">
+      <c r="P187" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15419,7 +15420,7 @@
       <c r="M188">
         <v>24</v>
       </c>
-      <c r="P188" s="8">
+      <c r="P188" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15460,7 +15461,7 @@
       <c r="M189">
         <v>0</v>
       </c>
-      <c r="P189" s="8">
+      <c r="P189" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15501,7 +15502,7 @@
       <c r="M190">
         <v>944</v>
       </c>
-      <c r="P190" s="8">
+      <c r="P190" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15542,7 +15543,7 @@
       <c r="M191">
         <v>561</v>
       </c>
-      <c r="P191" s="8">
+      <c r="P191" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15583,7 +15584,7 @@
       <c r="M192">
         <v>1399</v>
       </c>
-      <c r="P192" s="8">
+      <c r="P192" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15627,7 +15628,7 @@
       <c r="M193">
         <v>1599</v>
       </c>
-      <c r="P193" s="8">
+      <c r="P193" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15668,7 +15669,7 @@
       <c r="M194">
         <v>0</v>
       </c>
-      <c r="P194" s="8">
+      <c r="P194" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15712,7 +15713,7 @@
       <c r="M195">
         <v>85</v>
       </c>
-      <c r="P195" s="8">
+      <c r="P195" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15753,7 +15754,7 @@
       <c r="M196">
         <v>75</v>
       </c>
-      <c r="P196" s="8">
+      <c r="P196" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15794,7 +15795,7 @@
       <c r="M197">
         <v>96</v>
       </c>
-      <c r="P197" s="8">
+      <c r="P197" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15832,7 +15833,7 @@
       <c r="L198">
         <v>6.9</v>
       </c>
-      <c r="P198" s="8">
+      <c r="P198" s="19">
         <v>46176</v>
       </c>
     </row>
@@ -15873,7 +15874,7 @@
       <c r="M199">
         <v>60</v>
       </c>
-      <c r="P199" s="8">
+      <c r="P199" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15917,7 +15918,7 @@
       <c r="M200">
         <v>246</v>
       </c>
-      <c r="P200" s="8">
+      <c r="P200" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15958,7 +15959,7 @@
       <c r="M201">
         <v>6</v>
       </c>
-      <c r="P201" s="8">
+      <c r="P201" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -15999,7 +16000,7 @@
       <c r="M202">
         <v>145</v>
       </c>
-      <c r="P202" s="8">
+      <c r="P202" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16043,7 +16044,7 @@
       <c r="M203">
         <v>70</v>
       </c>
-      <c r="P203" s="8">
+      <c r="P203" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16084,7 +16085,7 @@
       <c r="M204">
         <v>53</v>
       </c>
-      <c r="P204" s="8">
+      <c r="P204" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16128,7 +16129,7 @@
       <c r="M205">
         <v>81</v>
       </c>
-      <c r="P205" s="8">
+      <c r="P205" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16169,7 +16170,7 @@
       <c r="M206">
         <v>66</v>
       </c>
-      <c r="P206" s="8">
+      <c r="P206" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16210,7 +16211,7 @@
       <c r="M207">
         <v>196</v>
       </c>
-      <c r="P207" s="8">
+      <c r="P207" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16251,7 +16252,7 @@
       <c r="M208">
         <v>145</v>
       </c>
-      <c r="P208" s="8">
+      <c r="P208" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16292,7 +16293,7 @@
       <c r="M209">
         <v>9</v>
       </c>
-      <c r="P209" s="8">
+      <c r="P209" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16330,7 +16331,7 @@
       <c r="L210">
         <v>6.6</v>
       </c>
-      <c r="P210" s="8">
+      <c r="P210" s="19">
         <v>46181</v>
       </c>
     </row>
@@ -16371,7 +16372,7 @@
       <c r="M211">
         <v>120</v>
       </c>
-      <c r="P211" s="8">
+      <c r="P211" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16412,7 +16413,7 @@
       <c r="M212">
         <v>21</v>
       </c>
-      <c r="P212" s="8">
+      <c r="P212" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16453,7 +16454,7 @@
       <c r="M213">
         <v>356</v>
       </c>
-      <c r="P213" s="8">
+      <c r="P213" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16494,7 +16495,7 @@
       <c r="M214">
         <v>93</v>
       </c>
-      <c r="P214" s="8">
+      <c r="P214" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16535,7 +16536,7 @@
       <c r="M215">
         <v>93</v>
       </c>
-      <c r="P215" s="8">
+      <c r="P215" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16576,7 +16577,7 @@
       <c r="M216">
         <v>87</v>
       </c>
-      <c r="P216" s="8">
+      <c r="P216" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16617,7 +16618,7 @@
       <c r="M217">
         <v>60</v>
       </c>
-      <c r="P217" s="8">
+      <c r="P217" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16658,7 +16659,7 @@
       <c r="M218">
         <v>2</v>
       </c>
-      <c r="P218" s="8">
+      <c r="P218" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16699,7 +16700,7 @@
       <c r="M219">
         <v>85</v>
       </c>
-      <c r="P219" s="8">
+      <c r="P219" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16740,7 +16741,7 @@
       <c r="M220">
         <v>216</v>
       </c>
-      <c r="P220" s="8">
+      <c r="P220" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16781,7 +16782,7 @@
       <c r="M221">
         <v>22</v>
       </c>
-      <c r="P221" s="8">
+      <c r="P221" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16822,7 +16823,7 @@
       <c r="M222">
         <v>87</v>
       </c>
-      <c r="P222" s="8">
+      <c r="P222" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -16866,7 +16867,7 @@
       <c r="M223">
         <v>24</v>
       </c>
-      <c r="P223" s="8">
+      <c r="P223" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -16910,7 +16911,7 @@
       <c r="M224">
         <v>24</v>
       </c>
-      <c r="P224" s="8">
+      <c r="P224" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -16954,7 +16955,7 @@
       <c r="M225">
         <v>24</v>
       </c>
-      <c r="P225" s="8">
+      <c r="P225" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -16998,7 +16999,7 @@
       <c r="M226">
         <v>24</v>
       </c>
-      <c r="P226" s="8">
+      <c r="P226" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -17042,7 +17043,7 @@
       <c r="M227">
         <v>24</v>
       </c>
-      <c r="P227" s="8">
+      <c r="P227" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -17086,7 +17087,7 @@
       <c r="M228">
         <v>24</v>
       </c>
-      <c r="P228" s="8">
+      <c r="P228" s="19">
         <v>46268</v>
       </c>
     </row>
@@ -17127,7 +17128,7 @@
       <c r="M229">
         <v>42</v>
       </c>
-      <c r="P229" s="8">
+      <c r="P229" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17168,7 +17169,7 @@
       <c r="M230">
         <v>6</v>
       </c>
-      <c r="P230" s="8">
+      <c r="P230" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17209,7 +17210,7 @@
       <c r="M231">
         <v>6</v>
       </c>
-      <c r="P231" s="8">
+      <c r="P231" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17250,7 +17251,7 @@
       <c r="M232">
         <v>24</v>
       </c>
-      <c r="P232" s="8">
+      <c r="P232" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17291,7 +17292,7 @@
       <c r="M233">
         <v>65</v>
       </c>
-      <c r="P233" s="8">
+      <c r="P233" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17335,7 +17336,7 @@
       <c r="M234">
         <v>228</v>
       </c>
-      <c r="P234" s="8">
+      <c r="P234" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17376,7 +17377,7 @@
       <c r="M235">
         <v>146</v>
       </c>
-      <c r="P235" s="8">
+      <c r="P235" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17417,7 +17418,7 @@
       <c r="M236">
         <v>0</v>
       </c>
-      <c r="P236" s="8">
+      <c r="P236" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17458,7 +17459,7 @@
       <c r="M237">
         <v>12</v>
       </c>
-      <c r="P237" s="8">
+      <c r="P237" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17502,7 +17503,7 @@
       <c r="M238">
         <v>219</v>
       </c>
-      <c r="P238" s="8">
+      <c r="P238" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17543,7 +17544,7 @@
       <c r="M239">
         <v>47</v>
       </c>
-      <c r="P239" s="8">
+      <c r="P239" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17584,7 +17585,7 @@
       <c r="M240">
         <v>232</v>
       </c>
-      <c r="P240" s="8">
+      <c r="P240" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17622,7 +17623,7 @@
       <c r="M241">
         <v>12</v>
       </c>
-      <c r="P241" s="8">
+      <c r="P241" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17663,7 +17664,7 @@
       <c r="M242">
         <v>18</v>
       </c>
-      <c r="P242" s="8">
+      <c r="P242" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17704,7 +17705,7 @@
       <c r="M243">
         <v>54</v>
       </c>
-      <c r="P243" s="8">
+      <c r="P243" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17745,7 +17746,7 @@
       <c r="M244">
         <v>138</v>
       </c>
-      <c r="P244" s="8">
+      <c r="P244" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17786,7 +17787,7 @@
       <c r="M245">
         <v>138</v>
       </c>
-      <c r="P245" s="8">
+      <c r="P245" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17827,7 +17828,7 @@
       <c r="M246">
         <v>6</v>
       </c>
-      <c r="P246" s="8">
+      <c r="P246" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17868,7 +17869,7 @@
       <c r="M247">
         <v>0</v>
       </c>
-      <c r="P247" s="8">
+      <c r="P247" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17912,7 +17913,7 @@
       <c r="M248">
         <v>219</v>
       </c>
-      <c r="P248" s="8">
+      <c r="P248" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17953,7 +17954,7 @@
       <c r="M249">
         <v>47</v>
       </c>
-      <c r="P249" s="8">
+      <c r="P249" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -17997,7 +17998,7 @@
       <c r="M250">
         <v>120</v>
       </c>
-      <c r="P250" s="8">
+      <c r="P250" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18038,7 +18039,7 @@
       <c r="M251">
         <v>81</v>
       </c>
-      <c r="P251" s="8">
+      <c r="P251" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18079,7 +18080,7 @@
       <c r="M252">
         <v>36</v>
       </c>
-      <c r="P252" s="8">
+      <c r="P252" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18120,7 +18121,7 @@
       <c r="M253">
         <v>59</v>
       </c>
-      <c r="P253" s="8">
+      <c r="P253" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18161,7 +18162,7 @@
       <c r="M254">
         <v>118</v>
       </c>
-      <c r="P254" s="8">
+      <c r="P254" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18202,7 +18203,7 @@
       <c r="M255">
         <v>0</v>
       </c>
-      <c r="P255" s="8">
+      <c r="P255" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18243,7 +18244,7 @@
       <c r="M256">
         <v>427</v>
       </c>
-      <c r="P256" s="8">
+      <c r="P256" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18284,7 +18285,7 @@
       <c r="M257">
         <v>24</v>
       </c>
-      <c r="P257" s="8">
+      <c r="P257" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18325,7 +18326,7 @@
       <c r="M258">
         <v>24</v>
       </c>
-      <c r="P258" s="8">
+      <c r="P258" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18366,7 +18367,7 @@
       <c r="M259">
         <v>24</v>
       </c>
-      <c r="P259" s="8">
+      <c r="P259" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18407,7 +18408,7 @@
       <c r="M260">
         <v>84</v>
       </c>
-      <c r="P260" s="8">
+      <c r="P260" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18448,7 +18449,7 @@
       <c r="M261">
         <v>186</v>
       </c>
-      <c r="P261" s="8">
+      <c r="P261" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18486,7 +18487,7 @@
       <c r="M262">
         <v>363</v>
       </c>
-      <c r="P262" s="8">
+      <c r="P262" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18524,7 +18525,7 @@
       <c r="M263">
         <v>186</v>
       </c>
-      <c r="P263" s="8">
+      <c r="P263" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18562,7 +18563,7 @@
       <c r="M264">
         <v>442</v>
       </c>
-      <c r="P264" s="8">
+      <c r="P264" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18600,7 +18601,7 @@
       <c r="M265">
         <v>671</v>
       </c>
-      <c r="P265" s="8">
+      <c r="P265" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18641,7 +18642,7 @@
       <c r="M266">
         <v>33</v>
       </c>
-      <c r="P266" s="8">
+      <c r="P266" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18682,7 +18683,7 @@
       <c r="M267">
         <v>111</v>
       </c>
-      <c r="P267" s="8">
+      <c r="P267" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18723,7 +18724,7 @@
       <c r="M268">
         <v>174</v>
       </c>
-      <c r="P268" s="8">
+      <c r="P268" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18764,7 +18765,7 @@
       <c r="M269">
         <v>1180</v>
       </c>
-      <c r="P269" s="8">
+      <c r="P269" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18805,7 +18806,7 @@
       <c r="M270">
         <v>78</v>
       </c>
-      <c r="P270" s="8">
+      <c r="P270" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18846,7 +18847,7 @@
       <c r="M271">
         <v>0</v>
       </c>
-      <c r="P271" s="8">
+      <c r="P271" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18887,7 +18888,7 @@
       <c r="M272">
         <v>6</v>
       </c>
-      <c r="P272" s="8">
+      <c r="P272" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -18928,7 +18929,7 @@
       <c r="M273">
         <v>296</v>
       </c>
-      <c r="P273" s="8">
+      <c r="P273" s="19">
         <v>46155</v>
       </c>
       <c r="R273" t="s">
@@ -18972,7 +18973,7 @@
       <c r="M274">
         <v>165</v>
       </c>
-      <c r="P274" s="8">
+      <c r="P274" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19013,7 +19014,7 @@
       <c r="M275">
         <v>0</v>
       </c>
-      <c r="P275" s="8">
+      <c r="P275" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19054,7 +19055,7 @@
       <c r="M276">
         <v>1159</v>
       </c>
-      <c r="P276" s="8">
+      <c r="P276" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19092,7 +19093,7 @@
       <c r="M277">
         <v>30</v>
       </c>
-      <c r="P277" s="8">
+      <c r="P277" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19133,7 +19134,7 @@
       <c r="M278">
         <v>3</v>
       </c>
-      <c r="P278" s="8">
+      <c r="P278" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19171,7 +19172,7 @@
       <c r="M279">
         <v>0</v>
       </c>
-      <c r="P279" s="8">
+      <c r="P279" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19209,7 +19210,7 @@
       <c r="L280">
         <v>33.9</v>
       </c>
-      <c r="P280" s="8">
+      <c r="P280" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19241,7 +19242,7 @@
       <c r="L281">
         <v>8.9</v>
       </c>
-      <c r="P281" s="8">
+      <c r="P281" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19279,7 +19280,7 @@
       <c r="M282">
         <v>24</v>
       </c>
-      <c r="P282" s="8">
+      <c r="P282" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19320,7 +19321,7 @@
       <c r="M283">
         <v>120</v>
       </c>
-      <c r="P283" s="8">
+      <c r="P283" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19358,7 +19359,7 @@
       <c r="M284">
         <v>528</v>
       </c>
-      <c r="P284" s="8">
+      <c r="P284" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19393,7 +19394,7 @@
       <c r="M285">
         <v>9</v>
       </c>
-      <c r="P285" s="8">
+      <c r="P285" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19428,7 +19429,7 @@
       <c r="M286">
         <v>9</v>
       </c>
-      <c r="P286" s="8">
+      <c r="P286" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19466,7 +19467,7 @@
       <c r="M287">
         <v>393</v>
       </c>
-      <c r="P287" s="8">
+      <c r="P287" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19504,7 +19505,7 @@
       <c r="M288">
         <v>0</v>
       </c>
-      <c r="P288" s="8">
+      <c r="P288" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19542,7 +19543,7 @@
       <c r="M289">
         <v>0</v>
       </c>
-      <c r="P289" s="8">
+      <c r="P289" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19577,7 +19578,7 @@
       <c r="M290">
         <v>299</v>
       </c>
-      <c r="P290" s="8">
+      <c r="P290" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19615,7 +19616,7 @@
       <c r="M291">
         <v>76</v>
       </c>
-      <c r="P291" s="8">
+      <c r="P291" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19653,7 +19654,7 @@
       <c r="M292">
         <v>442</v>
       </c>
-      <c r="P292" s="8">
+      <c r="P292" s="19">
         <v>46155</v>
       </c>
       <c r="R292" t="s">
@@ -19691,7 +19692,7 @@
       <c r="M293">
         <v>1181</v>
       </c>
-      <c r="P293" s="8">
+      <c r="P293" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19729,7 +19730,7 @@
       <c r="M294">
         <v>12</v>
       </c>
-      <c r="P294" s="8">
+      <c r="P294" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19767,7 +19768,7 @@
       <c r="M295">
         <v>169</v>
       </c>
-      <c r="P295" s="8">
+      <c r="P295" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19805,7 +19806,7 @@
       <c r="M296">
         <v>63</v>
       </c>
-      <c r="P296" s="8">
+      <c r="P296" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19846,7 +19847,7 @@
       <c r="M297">
         <v>31</v>
       </c>
-      <c r="P297" s="8">
+      <c r="P297" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19887,7 +19888,7 @@
       <c r="M298">
         <v>219</v>
       </c>
-      <c r="P298" s="8">
+      <c r="P298" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19925,7 +19926,7 @@
       <c r="M299">
         <v>38</v>
       </c>
-      <c r="P299" s="8">
+      <c r="P299" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -19963,7 +19964,7 @@
       <c r="M300">
         <v>0</v>
       </c>
-      <c r="P300" s="8">
+      <c r="P300" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20001,7 +20002,7 @@
       <c r="M301">
         <v>0</v>
       </c>
-      <c r="P301" s="8">
+      <c r="P301" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20042,7 +20043,7 @@
       <c r="M302">
         <v>0</v>
       </c>
-      <c r="P302" s="8">
+      <c r="P302" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20083,7 +20084,7 @@
       <c r="M303">
         <v>0</v>
       </c>
-      <c r="P303" s="8">
+      <c r="P303" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20124,7 +20125,7 @@
       <c r="M304">
         <v>940</v>
       </c>
-      <c r="P304" s="8">
+      <c r="P304" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20162,7 +20163,7 @@
       <c r="M305">
         <v>66</v>
       </c>
-      <c r="P305" s="8">
+      <c r="P305" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20203,7 +20204,7 @@
       <c r="M306">
         <v>0</v>
       </c>
-      <c r="P306" s="8">
+      <c r="P306" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20241,7 +20242,7 @@
       <c r="M307">
         <v>180</v>
       </c>
-      <c r="P307" s="8">
+      <c r="P307" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20279,7 +20280,7 @@
       <c r="M308">
         <v>0</v>
       </c>
-      <c r="P308" s="8">
+      <c r="P308" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20317,7 +20318,7 @@
       <c r="M309">
         <v>3</v>
       </c>
-      <c r="P309" s="8">
+      <c r="P309" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20352,7 +20353,7 @@
       <c r="M310">
         <v>6</v>
       </c>
-      <c r="P310" s="8">
+      <c r="P310" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20393,7 +20394,7 @@
       <c r="M311">
         <v>35</v>
       </c>
-      <c r="P311" s="8">
+      <c r="P311" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20431,7 +20432,7 @@
       <c r="M312">
         <v>787</v>
       </c>
-      <c r="P312" s="8">
+      <c r="P312" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20469,7 +20470,7 @@
       <c r="M313">
         <v>787</v>
       </c>
-      <c r="P313" s="8">
+      <c r="P313" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20507,7 +20508,7 @@
       <c r="M314">
         <v>12</v>
       </c>
-      <c r="P314" s="8">
+      <c r="P314" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20548,7 +20549,7 @@
       <c r="M315">
         <v>274</v>
       </c>
-      <c r="P315" s="8">
+      <c r="P315" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20589,7 +20590,7 @@
       <c r="M316">
         <v>21</v>
       </c>
-      <c r="P316" s="8">
+      <c r="P316" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20627,7 +20628,7 @@
       <c r="M317">
         <v>99</v>
       </c>
-      <c r="P317" s="8">
+      <c r="P317" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20668,7 +20669,7 @@
       <c r="M318">
         <v>12</v>
       </c>
-      <c r="P318" s="8">
+      <c r="P318" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20706,7 +20707,7 @@
       <c r="M319">
         <v>102</v>
       </c>
-      <c r="P319" s="8">
+      <c r="P319" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20744,7 +20745,7 @@
       <c r="M320">
         <v>327</v>
       </c>
-      <c r="P320" s="8">
+      <c r="P320" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20785,7 +20786,7 @@
       <c r="M321">
         <v>120</v>
       </c>
-      <c r="P321" s="8">
+      <c r="P321" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20817,7 +20818,7 @@
       <c r="L322">
         <v>15</v>
       </c>
-      <c r="P322" s="8">
+      <c r="P322" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20852,7 +20853,7 @@
       <c r="M323">
         <v>54</v>
       </c>
-      <c r="P323" s="8">
+      <c r="P323" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20893,7 +20894,7 @@
       <c r="M324">
         <v>27</v>
       </c>
-      <c r="P324" s="8">
+      <c r="P324" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20934,7 +20935,7 @@
       <c r="M325">
         <v>0</v>
       </c>
-      <c r="P325" s="8">
+      <c r="P325" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -20975,7 +20976,7 @@
       <c r="M326">
         <v>0</v>
       </c>
-      <c r="P326" s="8">
+      <c r="P326" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21016,7 +21017,7 @@
       <c r="M327">
         <v>0</v>
       </c>
-      <c r="P327" s="8">
+      <c r="P327" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21057,7 +21058,7 @@
       <c r="M328">
         <v>0</v>
       </c>
-      <c r="P328" s="8">
+      <c r="P328" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21098,7 +21099,7 @@
       <c r="M329">
         <v>0</v>
       </c>
-      <c r="P329" s="8">
+      <c r="P329" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21139,7 +21140,7 @@
       <c r="M330">
         <v>0</v>
       </c>
-      <c r="P330" s="8">
+      <c r="P330" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21171,7 +21172,7 @@
       <c r="L331">
         <v>8.3000000000000007</v>
       </c>
-      <c r="P331" s="8">
+      <c r="P331" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21206,7 +21207,7 @@
       <c r="M332">
         <v>231</v>
       </c>
-      <c r="P332" s="8">
+      <c r="P332" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21244,7 +21245,7 @@
       <c r="M333">
         <v>12</v>
       </c>
-      <c r="P333" s="8">
+      <c r="P333" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21282,7 +21283,7 @@
       <c r="M334">
         <v>63</v>
       </c>
-      <c r="P334" s="8">
+      <c r="P334" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21320,7 +21321,7 @@
       <c r="M335">
         <v>0</v>
       </c>
-      <c r="P335" s="8">
+      <c r="P335" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21358,7 +21359,7 @@
       <c r="M336">
         <v>263</v>
       </c>
-      <c r="P336" s="8">
+      <c r="P336" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21396,7 +21397,7 @@
       <c r="M337">
         <v>102</v>
       </c>
-      <c r="P337" s="8">
+      <c r="P337" s="19">
         <v>46155</v>
       </c>
       <c r="R337" t="s">
@@ -21434,7 +21435,7 @@
       <c r="M338">
         <v>456</v>
       </c>
-      <c r="P338" s="8">
+      <c r="P338" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21475,7 +21476,7 @@
       <c r="M339">
         <v>12</v>
       </c>
-      <c r="P339" s="8">
+      <c r="P339" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21516,7 +21517,7 @@
       <c r="M340">
         <v>12</v>
       </c>
-      <c r="P340" s="8">
+      <c r="P340" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21560,7 +21561,7 @@
       <c r="M341">
         <v>10955</v>
       </c>
-      <c r="P341" s="8">
+      <c r="P341" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21595,7 +21596,7 @@
       <c r="L342">
         <v>17.3</v>
       </c>
-      <c r="P342" s="8">
+      <c r="P342" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21639,7 +21640,7 @@
       <c r="M343">
         <v>390</v>
       </c>
-      <c r="P343" s="8">
+      <c r="P343" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21683,7 +21684,7 @@
       <c r="M344">
         <v>97</v>
       </c>
-      <c r="P344" s="8">
+      <c r="P344" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21718,7 +21719,7 @@
       <c r="L345">
         <v>18.850000000000001</v>
       </c>
-      <c r="P345" s="8">
+      <c r="P345" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21753,7 +21754,7 @@
       <c r="L346">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P346" s="8">
+      <c r="P346" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21791,7 +21792,7 @@
       <c r="M347">
         <v>0</v>
       </c>
-      <c r="P347" s="8">
+      <c r="P347" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21835,7 +21836,7 @@
       <c r="M348">
         <v>10955</v>
       </c>
-      <c r="P348" s="8">
+      <c r="P348" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21879,7 +21880,7 @@
       <c r="M349">
         <v>24</v>
       </c>
-      <c r="P349" s="8">
+      <c r="P349" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21923,7 +21924,7 @@
       <c r="M350">
         <v>24</v>
       </c>
-      <c r="P350" s="8">
+      <c r="P350" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -21967,7 +21968,7 @@
       <c r="M351">
         <v>24</v>
       </c>
-      <c r="P351" s="8">
+      <c r="P351" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22011,7 +22012,7 @@
       <c r="M352">
         <v>24</v>
       </c>
-      <c r="P352" s="8">
+      <c r="P352" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22055,7 +22056,7 @@
       <c r="M353">
         <v>24</v>
       </c>
-      <c r="P353" s="8">
+      <c r="P353" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22099,7 +22100,7 @@
       <c r="M354">
         <v>24</v>
       </c>
-      <c r="P354" s="8">
+      <c r="P354" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22143,7 +22144,7 @@
       <c r="M355">
         <v>24</v>
       </c>
-      <c r="P355" s="8">
+      <c r="P355" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22187,7 +22188,7 @@
       <c r="M356">
         <v>24</v>
       </c>
-      <c r="P356" s="8">
+      <c r="P356" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22231,7 +22232,7 @@
       <c r="M357">
         <v>48</v>
       </c>
-      <c r="P357" s="8">
+      <c r="P357" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22266,7 +22267,7 @@
       <c r="M358">
         <v>324</v>
       </c>
-      <c r="P358" s="8">
+      <c r="P358" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22304,7 +22305,7 @@
       <c r="M359">
         <v>483</v>
       </c>
-      <c r="P359" s="8">
+      <c r="P359" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22342,7 +22343,7 @@
       <c r="M360">
         <v>0</v>
       </c>
-      <c r="P360" s="8">
+      <c r="P360" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22386,7 +22387,7 @@
       <c r="M361">
         <v>501</v>
       </c>
-      <c r="P361" s="8">
+      <c r="P361" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22430,7 +22431,7 @@
       <c r="M362">
         <v>741</v>
       </c>
-      <c r="P362" s="8">
+      <c r="P362" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22471,7 +22472,7 @@
       <c r="M363">
         <v>648</v>
       </c>
-      <c r="P363" s="8">
+      <c r="P363" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22512,7 +22513,7 @@
       <c r="M364">
         <v>574</v>
       </c>
-      <c r="P364" s="8">
+      <c r="P364" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22556,7 +22557,7 @@
       <c r="M365">
         <v>66</v>
       </c>
-      <c r="P365" s="8">
+      <c r="P365" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22597,7 +22598,7 @@
       <c r="M366">
         <v>253</v>
       </c>
-      <c r="P366" s="8">
+      <c r="P366" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22638,7 +22639,7 @@
       <c r="M367">
         <v>575</v>
       </c>
-      <c r="P367" s="8">
+      <c r="P367" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22682,7 +22683,7 @@
       <c r="M368">
         <v>12</v>
       </c>
-      <c r="P368" s="8">
+      <c r="P368" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22726,7 +22727,7 @@
       <c r="M369">
         <v>341</v>
       </c>
-      <c r="P369" s="8">
+      <c r="P369" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22764,7 +22765,7 @@
       <c r="M370">
         <v>394</v>
       </c>
-      <c r="P370" s="8">
+      <c r="P370" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22805,7 +22806,7 @@
       <c r="M371">
         <v>281</v>
       </c>
-      <c r="P371" s="8">
+      <c r="P371" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22846,7 +22847,7 @@
       <c r="M372">
         <v>27</v>
       </c>
-      <c r="P372" s="8">
+      <c r="P372" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22887,7 +22888,7 @@
       <c r="M373">
         <v>60</v>
       </c>
-      <c r="P373" s="8">
+      <c r="P373" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22928,7 +22929,7 @@
       <c r="M374">
         <v>368</v>
       </c>
-      <c r="P374" s="8">
+      <c r="P374" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -22969,7 +22970,7 @@
       <c r="M375">
         <v>152</v>
       </c>
-      <c r="P375" s="8">
+      <c r="P375" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23010,7 +23011,7 @@
       <c r="M376">
         <v>693</v>
       </c>
-      <c r="P376" s="8">
+      <c r="P376" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23051,7 +23052,7 @@
       <c r="M377">
         <v>363</v>
       </c>
-      <c r="P377" s="8">
+      <c r="P377" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23092,7 +23093,7 @@
       <c r="M378">
         <v>1425</v>
       </c>
-      <c r="P378" s="8">
+      <c r="P378" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23133,7 +23134,7 @@
       <c r="M379">
         <v>84</v>
       </c>
-      <c r="P379" s="8">
+      <c r="P379" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23174,7 +23175,7 @@
       <c r="M380">
         <v>42</v>
       </c>
-      <c r="P380" s="8">
+      <c r="P380" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23215,7 +23216,7 @@
       <c r="M381">
         <v>165</v>
       </c>
-      <c r="P381" s="8">
+      <c r="P381" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23256,7 +23257,7 @@
       <c r="M382">
         <v>3214</v>
       </c>
-      <c r="P382" s="8">
+      <c r="P382" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23297,7 +23298,7 @@
       <c r="M383">
         <v>0</v>
       </c>
-      <c r="P383" s="8">
+      <c r="P383" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23341,7 +23342,7 @@
       <c r="M384">
         <v>165</v>
       </c>
-      <c r="P384" s="8">
+      <c r="P384" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23382,7 +23383,7 @@
       <c r="M385">
         <v>24</v>
       </c>
-      <c r="P385" s="8">
+      <c r="P385" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23426,7 +23427,7 @@
       <c r="M386">
         <v>182</v>
       </c>
-      <c r="P386" s="8">
+      <c r="P386" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23467,7 +23468,7 @@
       <c r="M387">
         <v>357</v>
       </c>
-      <c r="P387" s="8">
+      <c r="P387" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23511,7 +23512,7 @@
       <c r="M388">
         <v>474</v>
       </c>
-      <c r="P388" s="8">
+      <c r="P388" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23552,7 +23553,7 @@
       <c r="M389">
         <v>321</v>
       </c>
-      <c r="P389" s="8">
+      <c r="P389" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23590,7 +23591,7 @@
       <c r="L390">
         <v>37</v>
       </c>
-      <c r="P390" s="8">
+      <c r="P390" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23628,7 +23629,7 @@
       <c r="L391">
         <v>10.5</v>
       </c>
-      <c r="P391" s="8">
+      <c r="P391" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23669,7 +23670,7 @@
       <c r="M392">
         <v>351</v>
       </c>
-      <c r="P392" s="8">
+      <c r="P392" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23710,7 +23711,7 @@
       <c r="M393">
         <v>14790</v>
       </c>
-      <c r="P393" s="8">
+      <c r="P393" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23751,7 +23752,7 @@
       <c r="M394">
         <v>0</v>
       </c>
-      <c r="P394" s="8">
+      <c r="P394" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23792,7 +23793,7 @@
       <c r="L395">
         <v>6.2</v>
       </c>
-      <c r="P395" s="8">
+      <c r="P395" s="19">
         <v>46177</v>
       </c>
     </row>
@@ -23833,7 +23834,7 @@
       <c r="M396">
         <v>0</v>
       </c>
-      <c r="P396" s="8">
+      <c r="P396" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23874,7 +23875,7 @@
       <c r="M397">
         <v>0</v>
       </c>
-      <c r="P397" s="8">
+      <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23915,7 +23916,7 @@
       <c r="M398">
         <v>0</v>
       </c>
-      <c r="P398" s="8">
+      <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -23959,7 +23960,7 @@
       <c r="M399">
         <v>6</v>
       </c>
-      <c r="P399" s="8">
+      <c r="P399" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24000,7 +24001,7 @@
       <c r="M400">
         <v>0</v>
       </c>
-      <c r="P400" s="8">
+      <c r="P400" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24041,7 +24042,7 @@
       <c r="M401">
         <v>0</v>
       </c>
-      <c r="P401" s="8">
+      <c r="P401" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24082,7 +24083,7 @@
       <c r="M402">
         <v>0</v>
       </c>
-      <c r="P402" s="8">
+      <c r="P402" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24123,7 +24124,7 @@
       <c r="M403">
         <v>0</v>
       </c>
-      <c r="P403" s="8">
+      <c r="P403" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24164,7 +24165,7 @@
       <c r="M404">
         <v>0</v>
       </c>
-      <c r="P404" s="8">
+      <c r="P404" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24205,7 +24206,7 @@
       <c r="M405">
         <v>0</v>
       </c>
-      <c r="P405" s="8">
+      <c r="P405" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24246,7 +24247,7 @@
       <c r="M406">
         <v>0</v>
       </c>
-      <c r="P406" s="8">
+      <c r="P406" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24287,7 +24288,7 @@
       <c r="M407">
         <v>0</v>
       </c>
-      <c r="P407" s="8">
+      <c r="P407" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24331,7 +24332,7 @@
       <c r="M408">
         <v>0</v>
       </c>
-      <c r="P408" s="8">
+      <c r="P408" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24375,7 +24376,7 @@
       <c r="M409">
         <v>0</v>
       </c>
-      <c r="P409" s="8">
+      <c r="P409" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24416,7 +24417,7 @@
       <c r="M410">
         <v>0</v>
       </c>
-      <c r="P410" s="8">
+      <c r="P410" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24457,7 +24458,7 @@
       <c r="M411">
         <v>0</v>
       </c>
-      <c r="P411" s="8">
+      <c r="P411" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24498,7 +24499,7 @@
       <c r="M412">
         <v>0</v>
       </c>
-      <c r="P412" s="8">
+      <c r="P412" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24539,7 +24540,7 @@
       <c r="M413">
         <v>0</v>
       </c>
-      <c r="P413" s="8">
+      <c r="P413" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24580,7 +24581,7 @@
       <c r="M414">
         <v>37</v>
       </c>
-      <c r="P414" s="8">
+      <c r="P414" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24621,7 +24622,7 @@
       <c r="M415">
         <v>539</v>
       </c>
-      <c r="P415" s="8">
+      <c r="P415" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24662,7 +24663,7 @@
       <c r="M416">
         <v>264</v>
       </c>
-      <c r="P416" s="8">
+      <c r="P416" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24700,7 +24701,7 @@
       <c r="L417">
         <v>7.1</v>
       </c>
-      <c r="P417" s="8">
+      <c r="P417" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24738,7 +24739,7 @@
       <c r="L418">
         <v>8.1999999999999993</v>
       </c>
-      <c r="P418" s="8">
+      <c r="P418" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24779,7 +24780,7 @@
       <c r="M419">
         <v>0</v>
       </c>
-      <c r="P419" s="8">
+      <c r="P419" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24820,7 +24821,7 @@
       <c r="M420">
         <v>113</v>
       </c>
-      <c r="P420" s="8">
+      <c r="P420" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24861,7 +24862,7 @@
       <c r="M421">
         <v>71</v>
       </c>
-      <c r="P421" s="8">
+      <c r="P421" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24902,7 +24903,7 @@
       <c r="M422">
         <v>152</v>
       </c>
-      <c r="P422" s="8">
+      <c r="P422" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24946,7 +24947,7 @@
       <c r="M423">
         <v>324</v>
       </c>
-      <c r="P423" s="8">
+      <c r="P423" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -24987,7 +24988,7 @@
       <c r="M424">
         <v>324</v>
       </c>
-      <c r="P424" s="8">
+      <c r="P424" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25028,7 +25029,7 @@
       <c r="M425">
         <v>324</v>
       </c>
-      <c r="P425" s="8">
+      <c r="P425" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25069,7 +25070,7 @@
       <c r="M426">
         <v>324</v>
       </c>
-      <c r="P426" s="8">
+      <c r="P426" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25110,7 +25111,7 @@
       <c r="M427">
         <v>324</v>
       </c>
-      <c r="P427" s="8">
+      <c r="P427" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25151,7 +25152,7 @@
       <c r="M428">
         <v>324</v>
       </c>
-      <c r="P428" s="8">
+      <c r="P428" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25192,7 +25193,7 @@
       <c r="M429">
         <v>324</v>
       </c>
-      <c r="P429" s="8">
+      <c r="P429" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25233,7 +25234,7 @@
       <c r="M430">
         <v>324</v>
       </c>
-      <c r="P430" s="8">
+      <c r="P430" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25277,7 +25278,7 @@
       <c r="M431">
         <v>324</v>
       </c>
-      <c r="P431" s="8">
+      <c r="P431" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25321,7 +25322,7 @@
       <c r="M432">
         <v>324</v>
       </c>
-      <c r="P432" s="8">
+      <c r="P432" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25365,7 +25366,7 @@
       <c r="M433">
         <v>324</v>
       </c>
-      <c r="P433" s="8">
+      <c r="P433" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25406,7 +25407,7 @@
       <c r="M434">
         <v>324</v>
       </c>
-      <c r="P434" s="8">
+      <c r="P434" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25447,7 +25448,7 @@
       <c r="M435">
         <v>99</v>
       </c>
-      <c r="P435" s="8">
+      <c r="P435" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25488,7 +25489,7 @@
       <c r="M436">
         <v>915</v>
       </c>
-      <c r="P436" s="8">
+      <c r="P436" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25529,7 +25530,7 @@
       <c r="M437">
         <v>219</v>
       </c>
-      <c r="P437" s="8">
+      <c r="P437" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25570,7 +25571,7 @@
       <c r="M438">
         <v>96</v>
       </c>
-      <c r="P438" s="8">
+      <c r="P438" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25611,7 +25612,7 @@
       <c r="M439">
         <v>219</v>
       </c>
-      <c r="P439" s="8">
+      <c r="P439" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25652,7 +25653,7 @@
       <c r="M440">
         <v>27</v>
       </c>
-      <c r="P440" s="8">
+      <c r="P440" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25696,7 +25697,7 @@
       <c r="M441">
         <v>303</v>
       </c>
-      <c r="P441" s="8">
+      <c r="P441" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25740,7 +25741,7 @@
       <c r="M442">
         <v>187</v>
       </c>
-      <c r="P442" s="8">
+      <c r="P442" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25781,7 +25782,7 @@
       <c r="M443">
         <v>340</v>
       </c>
-      <c r="P443" s="8">
+      <c r="P443" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25822,7 +25823,7 @@
       <c r="M444">
         <v>46</v>
       </c>
-      <c r="P444" s="8">
+      <c r="P444" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25863,7 +25864,7 @@
       <c r="M445">
         <v>78</v>
       </c>
-      <c r="P445" s="8">
+      <c r="P445" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25904,7 +25905,7 @@
       <c r="M446">
         <v>36</v>
       </c>
-      <c r="P446" s="8">
+      <c r="P446" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25942,7 +25943,7 @@
       <c r="L447">
         <v>11.4</v>
       </c>
-      <c r="P447" s="8">
+      <c r="P447" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -25983,7 +25984,7 @@
       <c r="M448">
         <v>0</v>
       </c>
-      <c r="P448" s="8">
+      <c r="P448" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26024,7 +26025,7 @@
       <c r="M449">
         <v>0</v>
       </c>
-      <c r="P449" s="8">
+      <c r="P449" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26065,7 +26066,7 @@
       <c r="M450">
         <v>0</v>
       </c>
-      <c r="P450" s="8">
+      <c r="P450" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26106,7 +26107,7 @@
       <c r="M451">
         <v>177</v>
       </c>
-      <c r="P451" s="8">
+      <c r="P451" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26150,7 +26151,7 @@
       <c r="M452">
         <v>0</v>
       </c>
-      <c r="P452" s="8">
+      <c r="P452" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26191,7 +26192,7 @@
       <c r="M453">
         <v>0</v>
       </c>
-      <c r="P453" s="8">
+      <c r="P453" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26235,7 +26236,7 @@
       <c r="M454">
         <v>0</v>
       </c>
-      <c r="P454" s="8">
+      <c r="P454" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26279,7 +26280,7 @@
       <c r="M455">
         <v>42</v>
       </c>
-      <c r="P455" s="8">
+      <c r="P455" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26323,7 +26324,7 @@
       <c r="M456">
         <v>65</v>
       </c>
-      <c r="P456" s="8">
+      <c r="P456" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26364,7 +26365,7 @@
       <c r="M457">
         <v>0</v>
       </c>
-      <c r="P457" s="8">
+      <c r="P457" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26402,7 +26403,7 @@
       <c r="L458">
         <v>31</v>
       </c>
-      <c r="P458" s="8">
+      <c r="P458" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26446,7 +26447,7 @@
       <c r="M459">
         <v>270.39999999999998</v>
       </c>
-      <c r="P459" s="8">
+      <c r="P459" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26487,7 +26488,7 @@
       <c r="M460">
         <v>18</v>
       </c>
-      <c r="P460" s="8">
+      <c r="P460" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26528,7 +26529,7 @@
       <c r="M461">
         <v>6</v>
       </c>
-      <c r="P461" s="8">
+      <c r="P461" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26569,7 +26570,7 @@
       <c r="M462">
         <v>49</v>
       </c>
-      <c r="P462" s="8">
+      <c r="P462" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26610,7 +26611,7 @@
       <c r="L463">
         <v>17.8</v>
       </c>
-      <c r="P463" s="8">
+      <c r="P463" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26651,7 +26652,7 @@
       <c r="M464">
         <v>53</v>
       </c>
-      <c r="P464" s="8">
+      <c r="P464" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26692,7 +26693,7 @@
       <c r="L465">
         <v>22.3</v>
       </c>
-      <c r="P465" s="8">
+      <c r="P465" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26736,7 +26737,7 @@
       <c r="M466">
         <v>42</v>
       </c>
-      <c r="P466" s="8">
+      <c r="P466" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26777,7 +26778,7 @@
       <c r="M467">
         <v>171</v>
       </c>
-      <c r="P467" s="8">
+      <c r="P467" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26818,7 +26819,7 @@
       <c r="M468">
         <v>171</v>
       </c>
-      <c r="P468" s="8">
+      <c r="P468" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26862,7 +26863,7 @@
       <c r="M469">
         <v>12</v>
       </c>
-      <c r="P469" s="8">
+      <c r="P469" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26906,7 +26907,7 @@
       <c r="M470">
         <v>171</v>
       </c>
-      <c r="P470" s="8">
+      <c r="P470" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26950,7 +26951,7 @@
       <c r="M471">
         <v>171</v>
       </c>
-      <c r="P471" s="8">
+      <c r="P471" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -26988,7 +26989,7 @@
       <c r="L472">
         <v>18.3</v>
       </c>
-      <c r="P472" s="8">
+      <c r="P472" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27032,7 +27033,7 @@
       <c r="M473">
         <v>12</v>
       </c>
-      <c r="P473" s="8">
+      <c r="P473" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27067,7 +27068,7 @@
       <c r="L474">
         <v>31.7</v>
       </c>
-      <c r="P474" s="8">
+      <c r="P474" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27105,7 +27106,7 @@
       <c r="M475">
         <v>30</v>
       </c>
-      <c r="P475" s="8">
+      <c r="P475" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27146,7 +27147,7 @@
       <c r="L476">
         <v>17.8</v>
       </c>
-      <c r="P476" s="8">
+      <c r="P476" s="19">
         <v>46178</v>
       </c>
     </row>
@@ -27184,7 +27185,7 @@
       <c r="L477">
         <v>95</v>
       </c>
-      <c r="P477" s="8">
+      <c r="P477" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27225,7 +27226,7 @@
       <c r="M478">
         <v>2215</v>
       </c>
-      <c r="P478" s="8">
+      <c r="P478" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27263,7 +27264,7 @@
       <c r="M479">
         <v>2215</v>
       </c>
-      <c r="P479" s="8">
+      <c r="P479" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27304,7 +27305,7 @@
       <c r="M480">
         <v>279</v>
       </c>
-      <c r="P480" s="8">
+      <c r="P480" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27348,7 +27349,7 @@
       <c r="M481">
         <v>205</v>
       </c>
-      <c r="P481" s="8">
+      <c r="P481" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27386,7 +27387,7 @@
       <c r="L482">
         <v>14.5</v>
       </c>
-      <c r="P482" s="8">
+      <c r="P482" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27427,7 +27428,7 @@
       <c r="M483">
         <v>0</v>
       </c>
-      <c r="P483" s="8">
+      <c r="P483" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27465,7 +27466,7 @@
       <c r="L484">
         <v>37</v>
       </c>
-      <c r="P484" s="8">
+      <c r="P484" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27503,7 +27504,7 @@
       <c r="L485">
         <v>7.9</v>
       </c>
-      <c r="P485" s="8">
+      <c r="P485" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27541,7 +27542,7 @@
       <c r="L486">
         <v>14.5</v>
       </c>
-      <c r="P486" s="8">
+      <c r="P486" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27582,7 +27583,7 @@
       <c r="M487">
         <v>324</v>
       </c>
-      <c r="P487" s="8">
+      <c r="P487" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27623,7 +27624,7 @@
       <c r="M488">
         <v>368</v>
       </c>
-      <c r="P488" s="8">
+      <c r="P488" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27664,7 +27665,7 @@
       <c r="M489">
         <v>969</v>
       </c>
-      <c r="P489" s="8">
+      <c r="P489" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27705,7 +27706,7 @@
       <c r="M490">
         <v>0</v>
       </c>
-      <c r="P490" s="8">
+      <c r="P490" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27746,7 +27747,7 @@
       <c r="M491">
         <v>113</v>
       </c>
-      <c r="P491" s="8">
+      <c r="P491" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27787,7 +27788,7 @@
       <c r="M492">
         <v>71</v>
       </c>
-      <c r="P492" s="8">
+      <c r="P492" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27828,7 +27829,7 @@
       <c r="M493">
         <v>240</v>
       </c>
-      <c r="P493" s="8">
+      <c r="P493" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27869,7 +27870,7 @@
       <c r="M494">
         <v>66</v>
       </c>
-      <c r="P494" s="8">
+      <c r="P494" s="19">
         <v>46155</v>
       </c>
       <c r="R494" t="s">
@@ -27913,7 +27914,7 @@
       <c r="M495">
         <v>549</v>
       </c>
-      <c r="P495" s="8">
+      <c r="P495" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27954,7 +27955,7 @@
       <c r="M496">
         <v>3</v>
       </c>
-      <c r="P496" s="8">
+      <c r="P496" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -27995,7 +27996,7 @@
       <c r="M497">
         <v>288</v>
       </c>
-      <c r="P497" s="8">
+      <c r="P497" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28036,7 +28037,7 @@
       <c r="M498">
         <v>54</v>
       </c>
-      <c r="P498" s="8">
+      <c r="P498" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28074,7 +28075,7 @@
       <c r="M499">
         <v>666</v>
       </c>
-      <c r="P499" s="8">
+      <c r="P499" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28118,7 +28119,7 @@
       <c r="M500">
         <v>318</v>
       </c>
-      <c r="P500" s="8">
+      <c r="P500" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28156,7 +28157,7 @@
       <c r="L501">
         <v>4.95</v>
       </c>
-      <c r="P501" s="8">
+      <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28197,7 +28198,7 @@
       <c r="M502">
         <v>133</v>
       </c>
-      <c r="P502" s="8">
+      <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28235,7 +28236,7 @@
       <c r="L503">
         <v>6.1</v>
       </c>
-      <c r="P503" s="8">
+      <c r="P503" s="19">
         <v>46275</v>
       </c>
     </row>
@@ -28276,7 +28277,7 @@
       <c r="M504">
         <v>0</v>
       </c>
-      <c r="P504" s="8">
+      <c r="P504" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28317,7 +28318,7 @@
       <c r="M505">
         <v>0</v>
       </c>
-      <c r="P505" s="8">
+      <c r="P505" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28358,7 +28359,7 @@
       <c r="M506">
         <v>0</v>
       </c>
-      <c r="P506" s="8">
+      <c r="P506" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28399,7 +28400,7 @@
       <c r="M507">
         <v>1327</v>
       </c>
-      <c r="P507" s="8">
+      <c r="P507" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28440,7 +28441,7 @@
       <c r="M508">
         <v>6</v>
       </c>
-      <c r="P508" s="8">
+      <c r="P508" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28481,7 +28482,7 @@
       <c r="M509">
         <v>30</v>
       </c>
-      <c r="P509" s="8">
+      <c r="P509" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28522,7 +28523,7 @@
       <c r="M510">
         <v>36</v>
       </c>
-      <c r="P510" s="8">
+      <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28563,7 +28564,7 @@
       <c r="M511">
         <v>18</v>
       </c>
-      <c r="P511" s="8">
+      <c r="P511" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28604,7 +28605,7 @@
       <c r="M512">
         <v>662</v>
       </c>
-      <c r="P512" s="8">
+      <c r="P512" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28645,7 +28646,7 @@
       <c r="M513">
         <v>64</v>
       </c>
-      <c r="P513" s="8">
+      <c r="P513" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28686,7 +28687,7 @@
       <c r="M514">
         <v>0</v>
       </c>
-      <c r="P514" s="8">
+      <c r="P514" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28727,7 +28728,7 @@
       <c r="M515">
         <v>36</v>
       </c>
-      <c r="P515" s="8">
+      <c r="P515" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28768,7 +28769,7 @@
       <c r="M516">
         <v>36</v>
       </c>
-      <c r="P516" s="8">
+      <c r="P516" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28809,7 +28810,7 @@
       <c r="M517">
         <v>55</v>
       </c>
-      <c r="P517" s="8">
+      <c r="P517" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28850,7 +28851,7 @@
       <c r="M518">
         <v>4411</v>
       </c>
-      <c r="P518" s="8">
+      <c r="P518" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28885,7 +28886,7 @@
       <c r="L519">
         <v>6.2</v>
       </c>
-      <c r="P519" s="8">
+      <c r="P519" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28920,7 +28921,7 @@
       <c r="L520">
         <v>8.99</v>
       </c>
-      <c r="P520" s="8">
+      <c r="P520" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28958,7 +28959,7 @@
       <c r="M521">
         <v>5</v>
       </c>
-      <c r="P521" s="8">
+      <c r="P521" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -28996,7 +28997,7 @@
       <c r="M522">
         <v>6532</v>
       </c>
-      <c r="P522" s="8">
+      <c r="P522" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29034,7 +29035,7 @@
       <c r="M523">
         <v>418</v>
       </c>
-      <c r="P523" s="8">
+      <c r="P523" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29069,7 +29070,7 @@
       <c r="L524">
         <v>23.9</v>
       </c>
-      <c r="P524" s="8">
+      <c r="P524" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29107,7 +29108,7 @@
       <c r="M525">
         <v>34</v>
       </c>
-      <c r="P525" s="8">
+      <c r="P525" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29145,7 +29146,7 @@
       <c r="M526">
         <v>995</v>
       </c>
-      <c r="P526" s="8">
+      <c r="P526" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29183,7 +29184,7 @@
       <c r="M527">
         <v>31</v>
       </c>
-      <c r="P527" s="8">
+      <c r="P527" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29221,7 +29222,7 @@
       <c r="M528">
         <v>5</v>
       </c>
-      <c r="P528" s="8">
+      <c r="P528" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29259,7 +29260,7 @@
       <c r="M529">
         <v>60</v>
       </c>
-      <c r="P529" s="8">
+      <c r="P529" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29297,7 +29298,7 @@
       <c r="M530">
         <v>60</v>
       </c>
-      <c r="P530" s="8">
+      <c r="P530" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29335,7 +29336,7 @@
       <c r="M531">
         <v>60</v>
       </c>
-      <c r="P531" s="8">
+      <c r="P531" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29373,7 +29374,7 @@
       <c r="M532">
         <v>60</v>
       </c>
-      <c r="P532" s="8">
+      <c r="P532" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29411,7 +29412,7 @@
       <c r="M533">
         <v>417</v>
       </c>
-      <c r="P533" s="8">
+      <c r="P533" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29449,7 +29450,7 @@
       <c r="M534">
         <v>777</v>
       </c>
-      <c r="P534" s="8">
+      <c r="P534" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29487,7 +29488,7 @@
       <c r="M535">
         <v>428</v>
       </c>
-      <c r="P535" s="8">
+      <c r="P535" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29525,7 +29526,7 @@
       <c r="M536">
         <v>0</v>
       </c>
-      <c r="P536" s="8">
+      <c r="P536" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29563,7 +29564,7 @@
       <c r="M537">
         <v>36</v>
       </c>
-      <c r="P537" s="8">
+      <c r="P537" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29601,7 +29602,7 @@
       <c r="M538">
         <v>0</v>
       </c>
-      <c r="P538" s="8">
+      <c r="P538" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29639,7 +29640,7 @@
       <c r="M539">
         <v>0</v>
       </c>
-      <c r="P539" s="8">
+      <c r="P539" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29677,7 +29678,7 @@
       <c r="M540">
         <v>31</v>
       </c>
-      <c r="P540" s="8">
+      <c r="P540" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29715,7 +29716,7 @@
       <c r="M541">
         <v>41</v>
       </c>
-      <c r="P541" s="8">
+      <c r="P541" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29753,7 +29754,7 @@
       <c r="M542">
         <v>0</v>
       </c>
-      <c r="P542" s="8">
+      <c r="P542" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29791,7 +29792,7 @@
       <c r="M543">
         <v>0</v>
       </c>
-      <c r="P543" s="8">
+      <c r="P543" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29829,7 +29830,7 @@
       <c r="M544">
         <v>3</v>
       </c>
-      <c r="P544" s="8">
+      <c r="P544" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29867,7 +29868,7 @@
       <c r="M545">
         <v>23</v>
       </c>
-      <c r="P545" s="8">
+      <c r="P545" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29908,7 +29909,7 @@
       <c r="M546">
         <v>3</v>
       </c>
-      <c r="P546" s="8">
+      <c r="P546" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29949,7 +29950,7 @@
       <c r="M547">
         <v>31</v>
       </c>
-      <c r="P547" s="8">
+      <c r="P547" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -29990,7 +29991,7 @@
       <c r="M548">
         <v>5</v>
       </c>
-      <c r="P548" s="8">
+      <c r="P548" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30031,7 +30032,7 @@
       <c r="M549">
         <v>5</v>
       </c>
-      <c r="P549" s="8">
+      <c r="P549" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30072,7 +30073,7 @@
       <c r="M550">
         <v>5</v>
       </c>
-      <c r="P550" s="8">
+      <c r="P550" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30110,7 +30111,7 @@
       <c r="M551">
         <v>6</v>
       </c>
-      <c r="P551" s="8">
+      <c r="P551" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30148,7 +30149,7 @@
       <c r="M552">
         <v>6</v>
       </c>
-      <c r="P552" s="8">
+      <c r="P552" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30183,7 +30184,7 @@
       <c r="L553">
         <v>14.85</v>
       </c>
-      <c r="P553" s="8">
+      <c r="P553" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30218,7 +30219,7 @@
       <c r="L554">
         <v>38.1</v>
       </c>
-      <c r="P554" s="8">
+      <c r="P554" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30253,7 +30254,7 @@
       <c r="L555">
         <v>35.5</v>
       </c>
-      <c r="P555" s="8">
+      <c r="P555" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30288,7 +30289,7 @@
       <c r="L556">
         <v>16.149999999999999</v>
       </c>
-      <c r="P556" s="8">
+      <c r="P556" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30326,7 +30327,7 @@
       <c r="L557">
         <v>112</v>
       </c>
-      <c r="P557" s="8">
+      <c r="P557" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30361,7 +30362,7 @@
       <c r="M558">
         <v>45</v>
       </c>
-      <c r="P558" s="8">
+      <c r="P558" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30396,7 +30397,7 @@
       <c r="M559">
         <v>45</v>
       </c>
-      <c r="P559" s="8">
+      <c r="P559" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30434,7 +30435,7 @@
       <c r="M560">
         <v>68</v>
       </c>
-      <c r="P560" s="8">
+      <c r="P560" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30472,7 +30473,7 @@
       <c r="M561">
         <v>155</v>
       </c>
-      <c r="P561" s="8">
+      <c r="P561" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30510,7 +30511,7 @@
       <c r="M562">
         <v>7</v>
       </c>
-      <c r="P562" s="8">
+      <c r="P562" s="19">
         <v>46155</v>
       </c>
     </row>
@@ -30548,7 +30549,7 @@
       <c r="M563">
         <v>5</v>
       </c>
-      <c r="P563" s="8">
+      <c r="P563" s="19">
         <v>46175</v>
       </c>
     </row>
@@ -30578,316 +30579,316 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="32.1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>1460</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>1461</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>1462</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>1463</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>1464</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>1465</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>1466</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>1467</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>2024</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>1468</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="11">
         <v>6.25</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="11">
         <v>4.9000000000000004</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="10">
         <v>820</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="12">
         <v>46143</v>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="12">
         <v>46203</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>1469</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="13" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1466</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>1471</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="14">
         <v>2025</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="14" t="s">
         <v>1468</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3" s="15">
         <v>7.99</v>
       </c>
-      <c r="G3" s="17">
+      <c r="G3" s="15">
         <v>6.5</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="14">
         <v>1240</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="16">
         <v>46143</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="16">
         <v>46203</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="K3" s="14" t="s">
         <v>1472</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="13" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>1466</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>2023</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>1468</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>7</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="11">
         <v>5.8</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>340</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="12">
         <v>46143</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="12">
         <v>46188</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>1473</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="13" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>1466</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="14" t="s">
         <v>1474</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>1475</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>1476</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>66</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="15">
         <v>58</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="14">
         <v>5</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="16">
         <v>46143</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="16">
         <v>46387</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="14" t="s">
         <v>1477</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="13" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>1466</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>1478</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>915</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>1468</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="11">
         <v>5.05</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="11">
         <v>4.2</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="10">
         <v>2880</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <v>46143</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <v>46234</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="10" t="s">
         <v>1479</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="13" t="s">
         <v>1470</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="15.95">
       <c r="A13" s="20" t="s">

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC5E7D90-2303-45D1-BEBA-B09C8868FF09}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2616D3-6BFD-424E-929C-52F89683924A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10405" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10404" uniqueCount="2358">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -9192,8 +9192,8 @@
       <c r="H32" t="s">
         <v>148</v>
       </c>
-      <c r="J32" t="s">
-        <v>61</v>
+      <c r="J32">
+        <v>2024</v>
       </c>
       <c r="K32">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2616D3-6BFD-424E-929C-52F89683924A}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E5CD351-1135-4791-99AE-4B48B9640A1B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10404" uniqueCount="2358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10403" uniqueCount="2358">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -13549,8 +13549,8 @@
       <c r="H142" t="s">
         <v>422</v>
       </c>
-      <c r="J142" t="s">
-        <v>61</v>
+      <c r="J142">
+        <v>2024</v>
       </c>
       <c r="K142">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C400BDA6-F33E-401E-A6F8-0D2354C7095B}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E333EF-B313-4289-B62F-531FD39106D5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,6 +575,9 @@
     <t>HVE</t>
   </si>
   <si>
+    <t>2021/22</t>
+  </si>
+  <si>
     <t>13702123</t>
   </si>
   <si>
@@ -618,9 +621,6 @@
   </si>
   <si>
     <t>Château La Croix de Mission</t>
-  </si>
-  <si>
-    <t>2021/22</t>
   </si>
   <si>
     <t>26600622</t>
@@ -9354,7 +9354,7 @@
         <v>145</v>
       </c>
       <c r="J36" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K36">
         <v>75</v>
@@ -9556,7 +9556,7 @@
         <v>175</v>
       </c>
       <c r="J41" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="K41">
         <v>75</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s">
         <v>66</v>
@@ -9582,19 +9582,19 @@
         <v>141</v>
       </c>
       <c r="D42" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E42" t="s">
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J42" t="s">
         <v>61</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
         <v>66</v>
@@ -9623,22 +9623,22 @@
         <v>141</v>
       </c>
       <c r="D43" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E43" t="s">
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G43" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H43" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I43" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J43" t="s">
         <v>109</v>
@@ -9667,16 +9667,16 @@
         <v>141</v>
       </c>
       <c r="D44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E44" t="s">
         <v>63</v>
       </c>
       <c r="F44" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I44" t="s">
         <v>175</v>
@@ -9699,7 +9699,7 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
         <v>66</v>
@@ -9708,19 +9708,19 @@
         <v>141</v>
       </c>
       <c r="D45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E45" t="s">
         <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J45" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="K45">
         <v>75</v>
@@ -9746,7 +9746,7 @@
         <v>141</v>
       </c>
       <c r="D46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E46" t="s">
         <v>63</v>
@@ -9784,7 +9784,7 @@
         <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E47" t="s">
         <v>63</v>
@@ -9822,7 +9822,7 @@
         <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E48" t="s">
         <v>63</v>
@@ -9863,7 +9863,7 @@
         <v>141</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E49" t="s">
         <v>63</v>
@@ -9904,7 +9904,7 @@
         <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E50" t="s">
         <v>63</v>
@@ -9942,7 +9942,7 @@
         <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E51" t="s">
         <v>63</v>
@@ -9983,7 +9983,7 @@
         <v>141</v>
       </c>
       <c r="D52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E52" t="s">
         <v>63</v>
@@ -10021,7 +10021,7 @@
         <v>141</v>
       </c>
       <c r="D53" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E53" t="s">
         <v>63</v>
@@ -11990,7 +11990,7 @@
         <v>342</v>
       </c>
       <c r="J103" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="K103">
         <v>75</v>
@@ -15957,7 +15957,7 @@
         <v>565</v>
       </c>
       <c r="J201" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="K201">
         <v>75</v>
@@ -17993,7 +17993,7 @@
         <v>706</v>
       </c>
       <c r="I250" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J250" t="s">
         <v>98</v>
@@ -27031,7 +27031,7 @@
         <v>175</v>
       </c>
       <c r="J473" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="K473">
         <v>75</v>
@@ -33059,10 +33059,10 @@
         <v>63</v>
       </c>
       <c r="C39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D39" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E39" t="s">
         <v>61</v>
@@ -33071,13 +33071,13 @@
         <v>1603</v>
       </c>
       <c r="G39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H39" t="s">
         <v>1603</v>
       </c>
       <c r="I39" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J39" t="s">
         <v>1566</v>
@@ -33100,10 +33100,10 @@
         <v>63</v>
       </c>
       <c r="C40" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E40" t="s">
         <v>109</v>
@@ -33112,13 +33112,13 @@
         <v>1604</v>
       </c>
       <c r="G40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
         <v>1604</v>
       </c>
       <c r="I40" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J40" t="s">
         <v>1566</v>
@@ -33141,7 +33141,7 @@
         <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E41" t="s">
         <v>61</v>
@@ -33156,7 +33156,7 @@
         <v>1605</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J41" t="s">
         <v>1566</v>
@@ -33179,22 +33179,22 @@
         <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E42" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F42" t="s">
         <v>1607</v>
       </c>
       <c r="G42" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H42" t="s">
         <v>1607</v>
       </c>
       <c r="I42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J42" t="s">
         <v>1566</v>
@@ -35454,7 +35454,7 @@
         <v>342</v>
       </c>
       <c r="E100" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F100" t="s">
         <v>1688</v>
@@ -39508,7 +39508,7 @@
         <v>565</v>
       </c>
       <c r="E202" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F202" t="s">
         <v>1854</v>
@@ -48715,7 +48715,7 @@
         <v>1012</v>
       </c>
       <c r="E430" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F430" t="s">
         <v>2219</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A746E1E9-7DD9-49DB-964A-BA25B2B07E88}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E225C829-0E12-4878-BA8E-C23C7B371408}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10270,7 +10270,7 @@
         <v>230</v>
       </c>
       <c r="J59" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K59">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E225C829-0E12-4878-BA8E-C23C7B371408}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C98B04-434E-4FF2-9C7F-302933F7FE1B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10403" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10402" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -10348,8 +10348,8 @@
       <c r="H61" t="s">
         <v>220</v>
       </c>
-      <c r="J61" t="s">
-        <v>109</v>
+      <c r="J61">
+        <v>2021</v>
       </c>
       <c r="K61">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C98B04-434E-4FF2-9C7F-302933F7FE1B}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09B17393-76F0-4532-AE54-AD7AA89C40F2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10402" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10401" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -10776,7 +10776,7 @@
         <v>267</v>
       </c>
       <c r="J72">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="K72">
         <v>75</v>
@@ -10819,8 +10819,8 @@
       <c r="I73" t="s">
         <v>69</v>
       </c>
-      <c r="J73" t="s">
-        <v>61</v>
+      <c r="J73">
+        <v>2024</v>
       </c>
       <c r="K73">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AA4B5CD-3ED7-4837-A084-14AE1D88FCDD}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F149E1-ABDF-42CD-9405-E46B3015C6D5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10400" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10399" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -11392,8 +11392,8 @@
       <c r="H88" t="s">
         <v>318</v>
       </c>
-      <c r="J88" t="s">
-        <v>87</v>
+      <c r="J88">
+        <v>2023</v>
       </c>
       <c r="K88">
         <v>75</v>
@@ -11577,7 +11577,7 @@
         <v>296</v>
       </c>
       <c r="J93" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K93">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F149E1-ABDF-42CD-9405-E46B3015C6D5}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCFB3874-551B-47F8-A1A8-415F12193B80}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11785,7 +11785,7 @@
         <v>69</v>
       </c>
       <c r="J98" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K98">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F4C0C4-BF1A-4519-B18C-C1B9F7701BDD}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9092D935-8BB6-4735-842D-1B1C811A17F2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12824,7 +12824,7 @@
         <v>292</v>
       </c>
       <c r="J124" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K124">
         <v>75</v>
@@ -13064,7 +13064,7 @@
         <v>324</v>
       </c>
       <c r="J130" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K130">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C91B9A9-0B4B-4AD9-AE2C-077EFD4C44C7}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC4021DB-CC71-4F20-B08C-79552A4CB02C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15172,7 +15172,7 @@
         <v>354</v>
       </c>
       <c r="J182" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K182">
         <v>75</v>
@@ -15213,7 +15213,7 @@
         <v>551</v>
       </c>
       <c r="J183" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K183">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC4021DB-CC71-4F20-B08C-79552A4CB02C}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5291855-8C86-40FD-94C6-AA82CA5268A5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10390" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10389" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -16127,7 +16127,7 @@
         <v>69</v>
       </c>
       <c r="J205" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K205">
         <v>75</v>
@@ -16410,8 +16410,8 @@
       <c r="H212" t="s">
         <v>555</v>
       </c>
-      <c r="J212" t="s">
-        <v>87</v>
+      <c r="J212">
+        <v>2023</v>
       </c>
       <c r="K212">
         <v>75</v>
@@ -16657,7 +16657,7 @@
         <v>637</v>
       </c>
       <c r="J218" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K218">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5291855-8C86-40FD-94C6-AA82CA5268A5}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCF62501-D0E3-46EC-A085-47F39ABFADF7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16698,7 +16698,7 @@
         <v>69</v>
       </c>
       <c r="J219" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K219">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCF62501-D0E3-46EC-A085-47F39ABFADF7}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2235DCE-306E-4FC2-87CC-AE44212DBF0F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16926,7 +16926,7 @@
     </row>
     <row r="225" spans="1:16">
       <c r="A225">
-        <v>51600324</v>
+        <v>51600323</v>
       </c>
       <c r="B225" t="s">
         <v>55</v>
@@ -16953,7 +16953,7 @@
         <v>69</v>
       </c>
       <c r="J225">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="K225">
         <v>75</v>
@@ -17167,7 +17167,7 @@
         <v>558</v>
       </c>
       <c r="J230" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K230">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2235DCE-306E-4FC2-87CC-AE44212DBF0F}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81BE59B7-41FF-427F-A65A-629081F9DFFA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17375,7 +17375,7 @@
         <v>616</v>
       </c>
       <c r="J235" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K235">
         <v>75</v>
@@ -17583,7 +17583,7 @@
         <v>682</v>
       </c>
       <c r="J240" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K240">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81BE59B7-41FF-427F-A65A-629081F9DFFA}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB2CB24-8AE5-48A7-A491-06087E087DFD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10389" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10388" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -17911,7 +17911,7 @@
         <v>69</v>
       </c>
       <c r="J248" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K248">
         <v>75</v>
@@ -17996,7 +17996,7 @@
         <v>186</v>
       </c>
       <c r="J250" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K250">
         <v>75</v>
@@ -18036,8 +18036,8 @@
       <c r="H251" t="s">
         <v>616</v>
       </c>
-      <c r="J251" t="s">
-        <v>61</v>
+      <c r="J251">
+        <v>2024</v>
       </c>
       <c r="K251">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEB2CB24-8AE5-48A7-A491-06087E087DFD}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D320327F-88CC-42C6-A036-65516C9EB5C7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10388" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10387" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -18405,8 +18405,8 @@
       <c r="H260" t="s">
         <v>589</v>
       </c>
-      <c r="J260" t="s">
-        <v>87</v>
+      <c r="J260">
+        <v>2023</v>
       </c>
       <c r="K260">
         <v>75</v>
@@ -18763,7 +18763,7 @@
         <v>69</v>
       </c>
       <c r="J269" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K269">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D320327F-88CC-42C6-A036-65516C9EB5C7}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB9A89EE-12CB-46D7-B954-67D0A6AB48E8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18804,7 +18804,7 @@
         <v>69</v>
       </c>
       <c r="J270" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K270">
         <v>75</v>
@@ -19614,7 +19614,7 @@
         <v>792</v>
       </c>
       <c r="J291" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K291">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1F4C8F-4007-405D-9736-AA23468F32FC}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C6DBEE-A2F4-404B-A92B-3FA2483253B2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10385" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10384" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -20081,8 +20081,8 @@
       <c r="I303" t="s">
         <v>756</v>
       </c>
-      <c r="J303" t="s">
-        <v>87</v>
+      <c r="J303">
+        <v>2025</v>
       </c>
       <c r="K303">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48C6DBEE-A2F4-404B-A92B-3FA2483253B2}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7100FDC6-BA57-4A21-B9DF-1B82014629F1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20123,7 +20123,7 @@
         <v>774</v>
       </c>
       <c r="J304" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K304">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7100FDC6-BA57-4A21-B9DF-1B82014629F1}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C03D8D4-0C83-4287-AB83-46B6E1923F0A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20547,7 +20547,7 @@
         <v>69</v>
       </c>
       <c r="J315" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K315">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C03D8D4-0C83-4287-AB83-46B6E1923F0A}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68346487-1510-4597-84AA-5F52503C0D03}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10384" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10383" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -20891,8 +20891,8 @@
       <c r="I324" t="s">
         <v>774</v>
       </c>
-      <c r="J324" t="s">
-        <v>109</v>
+      <c r="J324">
+        <v>2019</v>
       </c>
       <c r="K324">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68346487-1510-4597-84AA-5F52503C0D03}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87953E75-B562-46B7-A816-C67429EF28EF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10383" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10382" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -21137,8 +21137,8 @@
       <c r="I330" t="s">
         <v>756</v>
       </c>
-      <c r="J330" t="s">
-        <v>132</v>
+      <c r="J330">
+        <v>2011</v>
       </c>
       <c r="K330">
         <v>150</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87953E75-B562-46B7-A816-C67429EF28EF}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3BE8D70-E2F2-401B-8D10-AEB48F2559CA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10382" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10381" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -21280,8 +21280,8 @@
       <c r="I334" t="s">
         <v>69</v>
       </c>
-      <c r="J334" t="s">
-        <v>61</v>
+      <c r="J334">
+        <v>2023</v>
       </c>
       <c r="K334">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E2C0BA4-91D2-477B-9CAC-8B9A4D95F016}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE82ACDD-970E-4E70-B78A-73D546171B9E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21682,7 +21682,7 @@
         <v>175</v>
       </c>
       <c r="J344" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K344">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE82ACDD-970E-4E70-B78A-73D546171B9E}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1191B9-42C7-4A5A-850E-ECE092EB27D4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22159,7 +22159,7 @@
     </row>
     <row r="356" spans="1:16">
       <c r="A356">
-        <v>72300223</v>
+        <v>72300222</v>
       </c>
       <c r="B356" t="s">
         <v>55</v>
@@ -22186,7 +22186,7 @@
         <v>69</v>
       </c>
       <c r="J356">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="K356">
         <v>75</v>
@@ -22596,7 +22596,7 @@
         <v>920</v>
       </c>
       <c r="J366" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K366">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C1191B9-42C7-4A5A-850E-ECE092EB27D4}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A530F3DA-0470-4284-A7BC-4E3BEA2269E6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10377" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10376" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -22637,7 +22637,7 @@
         <v>947</v>
       </c>
       <c r="J367" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K367">
         <v>75</v>
@@ -22926,8 +22926,8 @@
       <c r="H374" t="s">
         <v>985</v>
       </c>
-      <c r="J374" t="s">
-        <v>98</v>
+      <c r="J374">
+        <v>2025</v>
       </c>
       <c r="K374">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A530F3DA-0470-4284-A7BC-4E3BEA2269E6}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81167A8-0DBC-47E0-8E2B-364F9CA7C847}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10376" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10375" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -23009,7 +23009,7 @@
         <v>992</v>
       </c>
       <c r="J376" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K376">
         <v>75</v>
@@ -23090,8 +23090,8 @@
       <c r="H378" t="s">
         <v>292</v>
       </c>
-      <c r="J378" t="s">
-        <v>98</v>
+      <c r="J378">
+        <v>2025</v>
       </c>
       <c r="K378">
         <v>75</v>
@@ -23381,7 +23381,7 @@
         <v>1017</v>
       </c>
       <c r="J385" t="s">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="K385">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A81167A8-0DBC-47E0-8E2B-364F9CA7C847}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C8B4D86-8B0E-4565-9AAF-7AAD127B434A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23425,7 +23425,7 @@
         <v>777</v>
       </c>
       <c r="J386" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K386">
         <v>75</v>
@@ -23592,7 +23592,7 @@
         <v>1029</v>
       </c>
       <c r="J390" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K390">
         <v>75</v>
@@ -23958,7 +23958,7 @@
         <v>1056</v>
       </c>
       <c r="J399" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K399">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BF9ED24-1E5D-4216-8AF0-40CEDC8B0E14}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E16621C8-AFD7-4C76-9F5B-B0988E0CC574}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10373" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10371" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -24578,8 +24578,8 @@
       <c r="H414" t="s">
         <v>1093</v>
       </c>
-      <c r="J414" t="s">
-        <v>98</v>
+      <c r="J414">
+        <v>2025</v>
       </c>
       <c r="K414">
         <v>75</v>
@@ -24660,8 +24660,8 @@
       <c r="H416" t="s">
         <v>1037</v>
       </c>
-      <c r="J416" t="s">
-        <v>98</v>
+      <c r="J416">
+        <v>2025</v>
       </c>
       <c r="K416">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86556CF2-8012-429E-994E-626B7CD21E72}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A89386E-6FC2-46E0-878C-DD4711E6A044}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10368" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10367" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -25487,7 +25487,7 @@
         <v>292</v>
       </c>
       <c r="J436" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K436">
         <v>75</v>
@@ -25527,8 +25527,8 @@
       <c r="H437" t="s">
         <v>985</v>
       </c>
-      <c r="J437" t="s">
-        <v>98</v>
+      <c r="J437">
+        <v>2025</v>
       </c>
       <c r="K437">
         <v>75</v>
@@ -25780,7 +25780,7 @@
         <v>1017</v>
       </c>
       <c r="J443" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K443">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A89386E-6FC2-46E0-878C-DD4711E6A044}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50CE8F4E-BA73-461C-B029-984837996839}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10367" uniqueCount="2359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10366" uniqueCount="2359">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -25821,7 +25821,7 @@
         <v>1101</v>
       </c>
       <c r="J444" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K444">
         <v>75</v>
@@ -26063,8 +26063,8 @@
       <c r="H450" t="s">
         <v>1161</v>
       </c>
-      <c r="J450" t="s">
-        <v>98</v>
+      <c r="J450">
+        <v>2014</v>
       </c>
       <c r="K450">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F7D42A9-7AF6-44DF-A9BB-41F2EA8E65E1}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFFDCFE2-FEE7-4C0D-BA8C-C48D43F7ED56}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26861,7 +26861,7 @@
         <v>175</v>
       </c>
       <c r="J469" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K469">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E60C5C9-17CC-4AC3-9BE4-1B001F8F5976}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F77CC1E5-1A74-499C-B253-C629CE655599}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10364" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10362" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27124,7 +27124,7 @@
     </row>
     <row r="476" spans="1:16">
       <c r="A476">
-        <v>27100522</v>
+        <v>27100523</v>
       </c>
       <c r="B476" t="s">
         <v>66</v>
@@ -27151,7 +27151,7 @@
         <v>777</v>
       </c>
       <c r="J476">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K476">
         <v>75</v>
@@ -27305,8 +27305,8 @@
       <c r="H480" t="s">
         <v>1231</v>
       </c>
-      <c r="J480" t="s">
-        <v>87</v>
+      <c r="J480">
+        <v>2023</v>
       </c>
       <c r="K480">
         <v>75</v>
@@ -27469,8 +27469,8 @@
       <c r="H484" t="s">
         <v>1029</v>
       </c>
-      <c r="J484" t="s">
-        <v>61</v>
+      <c r="J484">
+        <v>2024</v>
       </c>
       <c r="K484">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviermouton/Library/CloudStorage/OneDrive-Bibliothèquespartagées-VINOM/Vinom - Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CFD19E3-20F8-4BFF-A5AF-6DF12830247A}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE8AAF0B-85C6-4C1F-8245-5934C772C7C3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="26580" windowHeight="12460" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10360" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10359" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -27665,8 +27665,8 @@
       <c r="H489" t="s">
         <v>292</v>
       </c>
-      <c r="J489" t="s">
-        <v>98</v>
+      <c r="J489">
+        <v>2025</v>
       </c>
       <c r="K489">
         <v>75</v>
@@ -28161,7 +28161,7 @@
         <v>1286</v>
       </c>
       <c r="J501" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K501">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="136" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{402CD7DD-C76C-C54D-B7EA-0BDF0477CA8E}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF122D63-AAEA-414A-9931-EBECA8BD55F5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$563</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$562</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10356" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10348" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7894,7 +7894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R563"/>
+  <dimension ref="A1:R562"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -29433,7 +29433,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="B534" t="s">
         <v>66</v>
@@ -29448,10 +29448,10 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="H534" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="J534" t="s">
         <v>564</v>
@@ -29460,10 +29460,10 @@
         <v>75</v>
       </c>
       <c r="L534">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M534">
-        <v>777</v>
+        <v>428</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29471,7 +29471,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29486,10 +29486,10 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="H535" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="J535" t="s">
         <v>564</v>
@@ -29498,10 +29498,10 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M535">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29509,7 +29509,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29524,10 +29524,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="H536" t="s">
-        <v>1372</v>
+        <v>1349</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29536,10 +29536,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>33</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M536">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29547,7 +29547,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29562,10 +29562,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H537" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29574,10 +29574,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>34.200000000000003</v>
+        <v>39</v>
       </c>
       <c r="M537">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29585,10 +29585,10 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B538" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C538" t="s">
         <v>1323</v>
@@ -29600,10 +29600,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="H538" t="s">
-        <v>1377</v>
+        <v>1334</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29612,7 +29612,7 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M538">
         <v>0</v>
@@ -29623,10 +29623,10 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B539" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C539" t="s">
         <v>1323</v>
@@ -29638,10 +29638,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="H539" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29650,10 +29650,10 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M539">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
@@ -29661,7 +29661,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29676,7 +29676,7 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="H540" t="s">
         <v>1352</v>
@@ -29688,10 +29688,10 @@
         <v>75</v>
       </c>
       <c r="L540">
+        <v>47.3</v>
+      </c>
+      <c r="M540">
         <v>41</v>
-      </c>
-      <c r="M540">
-        <v>31</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29699,7 +29699,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29714,10 +29714,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H541" t="s">
-        <v>1352</v>
+        <v>1386</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29726,10 +29726,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M541">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29737,7 +29737,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29752,10 +29752,10 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="H542" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="J542" t="s">
         <v>564</v>
@@ -29775,7 +29775,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29790,22 +29790,22 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="H543" t="s">
-        <v>1389</v>
+        <v>1334</v>
       </c>
       <c r="J543" t="s">
-        <v>564</v>
+        <v>167</v>
       </c>
       <c r="K543">
         <v>75</v>
       </c>
       <c r="L543">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="M543">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29813,7 +29813,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29828,22 +29828,22 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H544" t="s">
-        <v>1334</v>
-      </c>
-      <c r="J544" t="s">
-        <v>167</v>
+        <v>1372</v>
+      </c>
+      <c r="J544">
+        <v>2017</v>
       </c>
       <c r="K544">
         <v>75</v>
       </c>
       <c r="L544">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="M544">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29851,7 +29851,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29859,6 +29859,9 @@
       <c r="C545" t="s">
         <v>1323</v>
       </c>
+      <c r="D545" t="s">
+        <v>1008</v>
+      </c>
       <c r="E545" t="s">
         <v>1323</v>
       </c>
@@ -29866,22 +29869,22 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H545" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J545">
-        <v>2017</v>
+        <v>1352</v>
+      </c>
+      <c r="J545" t="s">
+        <v>564</v>
       </c>
       <c r="K545">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L545">
-        <v>199</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M545">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29889,7 +29892,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29907,7 +29910,7 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="H546" t="s">
         <v>1352</v>
@@ -29919,10 +29922,10 @@
         <v>150</v>
       </c>
       <c r="L546">
-        <v>65.900000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="M546">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29930,10 +29933,10 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B547" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C547" t="s">
         <v>1323</v>
@@ -29948,10 +29951,10 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="H547" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J547" t="s">
         <v>564</v>
@@ -29960,10 +29963,10 @@
         <v>150</v>
       </c>
       <c r="L547">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="M547">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29971,7 +29974,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B548" t="s">
         <v>55</v>
@@ -29989,7 +29992,7 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="H548" t="s">
         <v>1334</v>
@@ -29998,10 +30001,10 @@
         <v>564</v>
       </c>
       <c r="K548">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L548">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M548">
         <v>5</v>
@@ -30012,7 +30015,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B549" t="s">
         <v>55</v>
@@ -30030,7 +30033,7 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="H549" t="s">
         <v>1334</v>
@@ -30039,10 +30042,10 @@
         <v>564</v>
       </c>
       <c r="K549">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L549">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="M549">
         <v>5</v>
@@ -30053,40 +30056,37 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B550" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C550" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D550" t="s">
-        <v>1008</v>
+        <v>1405</v>
       </c>
       <c r="E550" t="s">
-        <v>1323</v>
+        <v>1405</v>
       </c>
       <c r="F550" t="s">
-        <v>1332</v>
+        <v>1406</v>
       </c>
       <c r="G550" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="H550" t="s">
-        <v>1334</v>
+        <v>1408</v>
       </c>
       <c r="J550" t="s">
-        <v>564</v>
+        <v>1409</v>
       </c>
       <c r="K550">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="L550">
-        <v>359</v>
+        <v>13.8</v>
       </c>
       <c r="M550">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30094,7 +30094,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30109,7 +30109,7 @@
         <v>1406</v>
       </c>
       <c r="G551" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="H551" t="s">
         <v>1408</v>
@@ -30121,7 +30121,7 @@
         <v>70</v>
       </c>
       <c r="L551">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M551">
         <v>6</v>
@@ -30132,7 +30132,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30147,22 +30147,19 @@
         <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="H552" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J552" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="K552">
         <v>70</v>
       </c>
       <c r="L552">
-        <v>14.3</v>
-      </c>
-      <c r="M552">
-        <v>6</v>
+        <v>14.85</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30170,7 +30167,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30185,19 +30182,19 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="H553" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="J553" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="K553">
         <v>70</v>
       </c>
       <c r="L553">
-        <v>14.85</v>
+        <v>38.1</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30205,7 +30202,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30220,19 +30217,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="H554" t="s">
         <v>1418</v>
       </c>
       <c r="J554" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30240,7 +30237,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30255,19 +30252,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="H555" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="J555" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>35.5</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30275,7 +30272,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30283,6 +30280,9 @@
       <c r="C556" t="s">
         <v>1405</v>
       </c>
+      <c r="D556" t="s">
+        <v>1008</v>
+      </c>
       <c r="E556" t="s">
         <v>1405</v>
       </c>
@@ -30290,19 +30290,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="H556" t="s">
         <v>1425</v>
       </c>
       <c r="J556" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="K556">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L556">
-        <v>16.149999999999999</v>
+        <v>112</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30310,7 +30310,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30318,29 +30318,26 @@
       <c r="C557" t="s">
         <v>1405</v>
       </c>
-      <c r="D557" t="s">
-        <v>1008</v>
-      </c>
       <c r="E557" t="s">
         <v>1405</v>
       </c>
       <c r="F557" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G557" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="H557" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="J557" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="K557">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L557">
-        <v>112</v>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M557">
+        <v>45</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30348,10 +30345,10 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B558" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C558" t="s">
         <v>1405</v>
@@ -30362,17 +30359,17 @@
       <c r="F558" t="s">
         <v>1431</v>
       </c>
+      <c r="G558" t="s">
+        <v>1435</v>
+      </c>
       <c r="H558" t="s">
-        <v>1432</v>
-      </c>
-      <c r="J558" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="K558">
         <v>70</v>
       </c>
       <c r="L558">
-        <v>16.850000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M558">
         <v>45</v>
@@ -30383,10 +30380,10 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B559" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C559" t="s">
         <v>1405</v>
@@ -30398,19 +30395,22 @@
         <v>1431</v>
       </c>
       <c r="G559" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="H559" t="s">
-        <v>1436</v>
+        <v>1006</v>
+      </c>
+      <c r="J559" t="s">
+        <v>1439</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>17.95</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M559">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30418,7 +30418,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30433,22 +30433,22 @@
         <v>1431</v>
       </c>
       <c r="G560" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="H560" t="s">
-        <v>1006</v>
+        <v>1442</v>
       </c>
       <c r="J560" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="M560">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30456,7 +30456,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30468,25 +30468,25 @@
         <v>1405</v>
       </c>
       <c r="F561" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="G561" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="H561" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="J561" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="M561">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30494,7 +30494,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30509,7 +30509,7 @@
         <v>1445</v>
       </c>
       <c r="G562" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="H562" t="s">
         <v>1447</v>
@@ -30521,55 +30521,17 @@
         <v>70</v>
       </c>
       <c r="L562">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="M562">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P562" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A563" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B563" t="s">
-        <v>66</v>
-      </c>
-      <c r="C563" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E563" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F563" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G563" t="s">
-        <v>1450</v>
-      </c>
-      <c r="H563" t="s">
-        <v>1447</v>
-      </c>
-      <c r="J563" t="s">
-        <v>1448</v>
-      </c>
-      <c r="K563">
-        <v>70</v>
-      </c>
-      <c r="L563">
-        <v>40.5</v>
-      </c>
-      <c r="M563">
-        <v>5</v>
-      </c>
-      <c r="P563" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R563" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R562" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DF122D63-AAEA-414A-9931-EBECA8BD55F5}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B372A813-D8AA-9740-A233-941A43428208}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10348" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10347" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7386,10 +7386,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7405,10 +7405,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16214,8 +16210,8 @@
       <c r="H207" t="s">
         <v>586</v>
       </c>
-      <c r="J207" t="s">
-        <v>61</v>
+      <c r="J207">
+        <v>2024</v>
       </c>
       <c r="K207">
         <v>75</v>
@@ -30862,361 +30858,351 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>1471</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>1472</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>1473</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>1475</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>1476</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>1477</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1478</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>1479</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="22" t="s">
         <v>1480</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>1481</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>1482</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1483</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>1484</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>1485</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>1486</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>1487</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>1488</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31229,6 +31215,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52042,6 +52038,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -52322,29 +52340,33 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52362,30 +52384,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B372A813-D8AA-9740-A233-941A43428208}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7AC465D-CD29-884E-9645-4BBD9DFF8D31}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10347" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -16186,8 +16186,8 @@
       </c>
     </row>
     <row r="207" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A207" t="s">
-        <v>610</v>
+      <c r="A207">
+        <v>13800124</v>
       </c>
       <c r="B207" t="s">
         <v>66</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7AC465D-CD29-884E-9645-4BBD9DFF8D31}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{268389EE-5020-0540-B75A-A7870E26215F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$561</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10338" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7890,7 +7890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R562"/>
+  <dimension ref="A1:R561"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -29657,7 +29657,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29672,10 +29672,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H540" t="s">
-        <v>1352</v>
+        <v>1386</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29684,10 +29684,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M540">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29695,7 +29695,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29710,10 +29710,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="H541" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29733,7 +29733,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29748,22 +29748,22 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="H542" t="s">
-        <v>1389</v>
+        <v>1334</v>
       </c>
       <c r="J542" t="s">
-        <v>564</v>
+        <v>167</v>
       </c>
       <c r="K542">
         <v>75</v>
       </c>
       <c r="L542">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="M542">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29771,7 +29771,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29786,22 +29786,22 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H543" t="s">
-        <v>1334</v>
-      </c>
-      <c r="J543" t="s">
-        <v>167</v>
+        <v>1372</v>
+      </c>
+      <c r="J543">
+        <v>2017</v>
       </c>
       <c r="K543">
         <v>75</v>
       </c>
       <c r="L543">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="M543">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29809,7 +29809,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29817,6 +29817,9 @@
       <c r="C544" t="s">
         <v>1323</v>
       </c>
+      <c r="D544" t="s">
+        <v>1008</v>
+      </c>
       <c r="E544" t="s">
         <v>1323</v>
       </c>
@@ -29824,22 +29827,22 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H544" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J544">
-        <v>2017</v>
+        <v>1352</v>
+      </c>
+      <c r="J544" t="s">
+        <v>564</v>
       </c>
       <c r="K544">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L544">
-        <v>199</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M544">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29847,7 +29850,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29865,7 +29868,7 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="H545" t="s">
         <v>1352</v>
@@ -29877,10 +29880,10 @@
         <v>150</v>
       </c>
       <c r="L545">
-        <v>65.900000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="M545">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29888,10 +29891,10 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B546" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C546" t="s">
         <v>1323</v>
@@ -29906,10 +29909,10 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="H546" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J546" t="s">
         <v>564</v>
@@ -29918,10 +29921,10 @@
         <v>150</v>
       </c>
       <c r="L546">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="M546">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29929,7 +29932,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B547" t="s">
         <v>55</v>
@@ -29947,7 +29950,7 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="H547" t="s">
         <v>1334</v>
@@ -29956,10 +29959,10 @@
         <v>564</v>
       </c>
       <c r="K547">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L547">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M547">
         <v>5</v>
@@ -29970,7 +29973,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B548" t="s">
         <v>55</v>
@@ -29988,7 +29991,7 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="H548" t="s">
         <v>1334</v>
@@ -29997,10 +30000,10 @@
         <v>564</v>
       </c>
       <c r="K548">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L548">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="M548">
         <v>5</v>
@@ -30011,40 +30014,37 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B549" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C549" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1008</v>
+        <v>1405</v>
       </c>
       <c r="E549" t="s">
-        <v>1323</v>
+        <v>1405</v>
       </c>
       <c r="F549" t="s">
-        <v>1332</v>
+        <v>1406</v>
       </c>
       <c r="G549" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="H549" t="s">
-        <v>1334</v>
+        <v>1408</v>
       </c>
       <c r="J549" t="s">
-        <v>564</v>
+        <v>1409</v>
       </c>
       <c r="K549">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="L549">
-        <v>359</v>
+        <v>13.8</v>
       </c>
       <c r="M549">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30052,7 +30052,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30067,7 +30067,7 @@
         <v>1406</v>
       </c>
       <c r="G550" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="H550" t="s">
         <v>1408</v>
@@ -30079,7 +30079,7 @@
         <v>70</v>
       </c>
       <c r="L550">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M550">
         <v>6</v>
@@ -30090,7 +30090,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30105,22 +30105,19 @@
         <v>1406</v>
       </c>
       <c r="G551" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="H551" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J551" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="K551">
         <v>70</v>
       </c>
       <c r="L551">
-        <v>14.3</v>
-      </c>
-      <c r="M551">
-        <v>6</v>
+        <v>14.85</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30128,7 +30125,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30143,19 +30140,19 @@
         <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="H552" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="J552" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="K552">
         <v>70</v>
       </c>
       <c r="L552">
-        <v>14.85</v>
+        <v>38.1</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30163,7 +30160,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30178,19 +30175,19 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="H553" t="s">
         <v>1418</v>
       </c>
       <c r="J553" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="K553">
         <v>70</v>
       </c>
       <c r="L553">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30198,7 +30195,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30213,19 +30210,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="H554" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="J554" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>35.5</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30233,7 +30230,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30241,6 +30238,9 @@
       <c r="C555" t="s">
         <v>1405</v>
       </c>
+      <c r="D555" t="s">
+        <v>1008</v>
+      </c>
       <c r="E555" t="s">
         <v>1405</v>
       </c>
@@ -30248,19 +30248,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="H555" t="s">
         <v>1425</v>
       </c>
       <c r="J555" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="K555">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L555">
-        <v>16.149999999999999</v>
+        <v>112</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30268,7 +30268,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30276,29 +30276,26 @@
       <c r="C556" t="s">
         <v>1405</v>
       </c>
-      <c r="D556" t="s">
-        <v>1008</v>
-      </c>
       <c r="E556" t="s">
         <v>1405</v>
       </c>
       <c r="F556" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G556" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="H556" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="J556" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="K556">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L556">
-        <v>112</v>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M556">
+        <v>45</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30306,10 +30303,10 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B557" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C557" t="s">
         <v>1405</v>
@@ -30320,17 +30317,17 @@
       <c r="F557" t="s">
         <v>1431</v>
       </c>
+      <c r="G557" t="s">
+        <v>1435</v>
+      </c>
       <c r="H557" t="s">
-        <v>1432</v>
-      </c>
-      <c r="J557" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>16.850000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M557">
         <v>45</v>
@@ -30341,10 +30338,10 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B558" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C558" t="s">
         <v>1405</v>
@@ -30356,19 +30353,22 @@
         <v>1431</v>
       </c>
       <c r="G558" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="H558" t="s">
-        <v>1436</v>
+        <v>1006</v>
+      </c>
+      <c r="J558" t="s">
+        <v>1439</v>
       </c>
       <c r="K558">
         <v>70</v>
       </c>
       <c r="L558">
-        <v>17.95</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M558">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30376,7 +30376,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30391,22 +30391,22 @@
         <v>1431</v>
       </c>
       <c r="G559" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="H559" t="s">
-        <v>1006</v>
+        <v>1442</v>
       </c>
       <c r="J559" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="M559">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30414,7 +30414,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30426,25 +30426,25 @@
         <v>1405</v>
       </c>
       <c r="F560" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="G560" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="H560" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="J560" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="M560">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30452,7 +30452,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30467,7 +30467,7 @@
         <v>1445</v>
       </c>
       <c r="G561" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="H561" t="s">
         <v>1447</v>
@@ -30479,55 +30479,17 @@
         <v>70</v>
       </c>
       <c r="L561">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="M561">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P561" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A562" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B562" t="s">
-        <v>66</v>
-      </c>
-      <c r="C562" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E562" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F562" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G562" t="s">
-        <v>1450</v>
-      </c>
-      <c r="H562" t="s">
-        <v>1447</v>
-      </c>
-      <c r="J562" t="s">
-        <v>1448</v>
-      </c>
-      <c r="K562">
-        <v>70</v>
-      </c>
-      <c r="L562">
-        <v>40.5</v>
-      </c>
-      <c r="M562">
-        <v>5</v>
-      </c>
-      <c r="P562" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R562" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R561" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{268389EE-5020-0540-B75A-A7870E26215F}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{836702D9-9616-BF46-92FF-DF12232D96FA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$561</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$562</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10338" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7890,7 +7890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R561"/>
+  <dimension ref="A1:R562"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -29657,7 +29657,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29672,10 +29672,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H540" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29684,10 +29684,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M540">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29695,7 +29695,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29710,10 +29710,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H541" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29733,7 +29733,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29748,22 +29748,22 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H542" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J542" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K542">
         <v>75</v>
       </c>
       <c r="L542">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M542">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29771,7 +29771,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29786,22 +29786,22 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H543" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J543">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J543" t="s">
+        <v>167</v>
       </c>
       <c r="K543">
         <v>75</v>
       </c>
       <c r="L543">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M543">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29809,7 +29809,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29817,9 +29817,6 @@
       <c r="C544" t="s">
         <v>1323</v>
       </c>
-      <c r="D544" t="s">
-        <v>1008</v>
-      </c>
       <c r="E544" t="s">
         <v>1323</v>
       </c>
@@ -29827,22 +29824,22 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H544" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J544" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J544">
+        <v>2017</v>
       </c>
       <c r="K544">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L544">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M544">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29850,7 +29847,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29868,7 +29865,7 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H545" t="s">
         <v>1352</v>
@@ -29880,10 +29877,10 @@
         <v>150</v>
       </c>
       <c r="L545">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M545">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29891,10 +29888,10 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B546" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C546" t="s">
         <v>1323</v>
@@ -29909,10 +29906,10 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H546" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J546" t="s">
         <v>564</v>
@@ -29921,10 +29918,10 @@
         <v>150</v>
       </c>
       <c r="L546">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M546">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29932,7 +29929,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B547" t="s">
         <v>55</v>
@@ -29950,7 +29947,7 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H547" t="s">
         <v>1334</v>
@@ -29959,10 +29956,10 @@
         <v>564</v>
       </c>
       <c r="K547">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L547">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M547">
         <v>5</v>
@@ -29973,7 +29970,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B548" t="s">
         <v>55</v>
@@ -29991,7 +29988,7 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H548" t="s">
         <v>1334</v>
@@ -30000,10 +29997,10 @@
         <v>564</v>
       </c>
       <c r="K548">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L548">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M548">
         <v>5</v>
@@ -30014,37 +30011,40 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B549" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C549" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1008</v>
       </c>
       <c r="E549" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F549" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H549" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J549" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K549">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L549">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M549">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30052,7 +30052,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30067,7 +30067,7 @@
         <v>1406</v>
       </c>
       <c r="G550" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H550" t="s">
         <v>1408</v>
@@ -30079,7 +30079,7 @@
         <v>70</v>
       </c>
       <c r="L550">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M550">
         <v>6</v>
@@ -30090,7 +30090,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30105,19 +30105,22 @@
         <v>1406</v>
       </c>
       <c r="G551" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H551" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J551" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K551">
         <v>70</v>
       </c>
       <c r="L551">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M551">
+        <v>6</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30125,7 +30128,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30140,19 +30143,19 @@
         <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H552" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J552" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K552">
         <v>70</v>
       </c>
       <c r="L552">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30160,7 +30163,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30175,19 +30178,19 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H553" t="s">
         <v>1418</v>
       </c>
       <c r="J553" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K553">
         <v>70</v>
       </c>
       <c r="L553">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30195,7 +30198,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30210,19 +30213,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H554" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J554" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30230,7 +30233,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30238,9 +30241,6 @@
       <c r="C555" t="s">
         <v>1405</v>
       </c>
-      <c r="D555" t="s">
-        <v>1008</v>
-      </c>
       <c r="E555" t="s">
         <v>1405</v>
       </c>
@@ -30248,19 +30248,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H555" t="s">
         <v>1425</v>
       </c>
       <c r="J555" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K555">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L555">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30268,7 +30268,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30276,26 +30276,29 @@
       <c r="C556" t="s">
         <v>1405</v>
       </c>
+      <c r="D556" t="s">
+        <v>1008</v>
+      </c>
       <c r="E556" t="s">
         <v>1405</v>
       </c>
       <c r="F556" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G556" t="s">
+        <v>1428</v>
       </c>
       <c r="H556" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J556" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K556">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L556">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M556">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30303,10 +30306,10 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B557" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C557" t="s">
         <v>1405</v>
@@ -30317,17 +30320,17 @@
       <c r="F557" t="s">
         <v>1431</v>
       </c>
-      <c r="G557" t="s">
-        <v>1435</v>
-      </c>
       <c r="H557" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J557" t="s">
+        <v>1433</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M557">
         <v>45</v>
@@ -30338,10 +30341,10 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B558" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C558" t="s">
         <v>1405</v>
@@ -30353,22 +30356,19 @@
         <v>1431</v>
       </c>
       <c r="G558" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H558" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J558" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K558">
         <v>70</v>
       </c>
       <c r="L558">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M558">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30376,7 +30376,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30391,22 +30391,22 @@
         <v>1431</v>
       </c>
       <c r="G559" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H559" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J559" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M559">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30414,7 +30414,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30426,25 +30426,25 @@
         <v>1405</v>
       </c>
       <c r="F560" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G560" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H560" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J560" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M560">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30452,7 +30452,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30467,7 +30467,7 @@
         <v>1445</v>
       </c>
       <c r="G561" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H561" t="s">
         <v>1447</v>
@@ -30479,17 +30479,55 @@
         <v>70</v>
       </c>
       <c r="L561">
+        <v>36.5</v>
+      </c>
+      <c r="M561">
+        <v>7</v>
+      </c>
+      <c r="P561" s="19">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A562" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B562" t="s">
+        <v>66</v>
+      </c>
+      <c r="C562" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E562" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F562" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G562" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H562" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J562" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K562">
+        <v>70</v>
+      </c>
+      <c r="L562">
         <v>40.5</v>
       </c>
-      <c r="M561">
+      <c r="M562">
         <v>5</v>
       </c>
-      <c r="P561" s="19">
+      <c r="P562" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R561" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R562" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{706EBB09-E000-8D4F-93CA-B236678A506A}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEFA6529-8C97-0345-9F73-280D2FEFF42E}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10356" uniqueCount="2360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10354" uniqueCount="2360">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -18004,7 +18004,7 @@
         <v>75</v>
       </c>
       <c r="L250">
-        <v>13</v>
+        <v>13.35</v>
       </c>
       <c r="M250">
         <v>120</v>
@@ -18014,8 +18014,8 @@
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A251" t="s">
-        <v>701</v>
+      <c r="A251">
+        <v>26200425</v>
       </c>
       <c r="B251" t="s">
         <v>66</v>
@@ -18027,7 +18027,7 @@
         <v>590</v>
       </c>
       <c r="E251" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F251" t="s">
         <v>676</v>
@@ -18041,14 +18041,14 @@
       <c r="I251" t="s">
         <v>186</v>
       </c>
-      <c r="J251" t="s">
-        <v>286</v>
+      <c r="J251">
+        <v>2025</v>
       </c>
       <c r="K251">
         <v>75</v>
       </c>
       <c r="L251">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="M251">
         <v>120</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A42924-9973-7444-B29E-3815F1633D1F}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{668ACC61-BDF6-9C41-A15C-545ABF96147C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$565</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$564</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10366" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="2361">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7893,7 +7893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R565"/>
+  <dimension ref="A1:R564"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -29210,7 +29210,7 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29225,10 +29225,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="H528" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29237,10 +29237,10 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="M528">
-        <v>34</v>
+        <v>995</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29248,7 +29248,7 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29263,10 +29263,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="H529" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29275,10 +29275,10 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>25.8</v>
+        <v>27.5</v>
       </c>
       <c r="M529">
-        <v>995</v>
+        <v>31</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29286,7 +29286,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29301,10 +29301,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="H530" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29313,10 +29313,10 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="M530">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29324,7 +29324,7 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29339,10 +29339,10 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="H531" t="s">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="J531" t="s">
         <v>564</v>
@@ -29351,10 +29351,10 @@
         <v>75</v>
       </c>
       <c r="L531">
-        <v>29</v>
+        <v>29.35</v>
       </c>
       <c r="M531">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29362,10 +29362,10 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B532" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C532" t="s">
         <v>1323</v>
@@ -29377,7 +29377,7 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="H532" t="s">
         <v>1349</v>
@@ -29386,10 +29386,10 @@
         <v>564</v>
       </c>
       <c r="K532">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L532">
-        <v>29.35</v>
+        <v>63</v>
       </c>
       <c r="M532">
         <v>60</v>
@@ -29400,7 +29400,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B533" t="s">
         <v>55</v>
@@ -29415,7 +29415,7 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="H533" t="s">
         <v>1349</v>
@@ -29424,10 +29424,10 @@
         <v>564</v>
       </c>
       <c r="K533">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L533">
-        <v>63</v>
+        <v>34.5</v>
       </c>
       <c r="M533">
         <v>60</v>
@@ -29438,7 +29438,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B534" t="s">
         <v>55</v>
@@ -29453,7 +29453,7 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="H534" t="s">
         <v>1349</v>
@@ -29465,7 +29465,7 @@
         <v>75</v>
       </c>
       <c r="L534">
-        <v>34.5</v>
+        <v>30.4</v>
       </c>
       <c r="M534">
         <v>60</v>
@@ -29476,10 +29476,10 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B535" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C535" t="s">
         <v>1323</v>
@@ -29491,10 +29491,10 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>1362</v>
+        <v>919</v>
       </c>
       <c r="H535" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J535" t="s">
         <v>564</v>
@@ -29503,10 +29503,10 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>30.4</v>
+        <v>29.8</v>
       </c>
       <c r="M535">
-        <v>60</v>
+        <v>417</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29514,7 +29514,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29529,10 +29529,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>919</v>
+        <v>1368</v>
       </c>
       <c r="H536" t="s">
-        <v>1352</v>
+        <v>1369</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29541,10 +29541,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>29.8</v>
+        <v>31</v>
       </c>
       <c r="M536">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29552,7 +29552,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29567,10 +29567,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="H537" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29579,10 +29579,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M537">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29590,7 +29590,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29605,10 +29605,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="H538" t="s">
-        <v>1372</v>
+        <v>1349</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29617,10 +29617,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>33</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M538">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29628,7 +29628,7 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B539" t="s">
         <v>66</v>
@@ -29643,10 +29643,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H539" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29655,10 +29655,10 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>34.200000000000003</v>
+        <v>39</v>
       </c>
       <c r="M539">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
@@ -29666,10 +29666,10 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B540" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C540" t="s">
         <v>1323</v>
@@ -29681,10 +29681,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="H540" t="s">
-        <v>1377</v>
+        <v>1334</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29693,7 +29693,7 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -29704,10 +29704,10 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B541" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C541" t="s">
         <v>1323</v>
@@ -29719,10 +29719,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="H541" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29731,10 +29731,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M541">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29742,7 +29742,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29757,7 +29757,7 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="H542" t="s">
         <v>1352</v>
@@ -29769,10 +29769,10 @@
         <v>75</v>
       </c>
       <c r="L542">
+        <v>47.3</v>
+      </c>
+      <c r="M542">
         <v>41</v>
-      </c>
-      <c r="M542">
-        <v>31</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29780,7 +29780,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29795,10 +29795,10 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H543" t="s">
-        <v>1352</v>
+        <v>1386</v>
       </c>
       <c r="J543" t="s">
         <v>564</v>
@@ -29807,10 +29807,10 @@
         <v>75</v>
       </c>
       <c r="L543">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M543">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29818,7 +29818,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29833,10 +29833,10 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="H544" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="J544" t="s">
         <v>564</v>
@@ -29856,7 +29856,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29871,22 +29871,22 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="H545" t="s">
-        <v>1389</v>
+        <v>1334</v>
       </c>
       <c r="J545" t="s">
-        <v>564</v>
+        <v>167</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="M545">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29894,7 +29894,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29909,22 +29909,22 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H546" t="s">
-        <v>1334</v>
-      </c>
-      <c r="J546" t="s">
-        <v>167</v>
+        <v>1372</v>
+      </c>
+      <c r="J546">
+        <v>2017</v>
       </c>
       <c r="K546">
         <v>75</v>
       </c>
       <c r="L546">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="M546">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29932,7 +29932,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29940,6 +29940,9 @@
       <c r="C547" t="s">
         <v>1323</v>
       </c>
+      <c r="D547" t="s">
+        <v>1008</v>
+      </c>
       <c r="E547" t="s">
         <v>1323</v>
       </c>
@@ -29947,22 +29950,22 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H547" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J547">
-        <v>2017</v>
+        <v>1352</v>
+      </c>
+      <c r="J547" t="s">
+        <v>564</v>
       </c>
       <c r="K547">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L547">
-        <v>199</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M547">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29970,7 +29973,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -29988,7 +29991,7 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="H548" t="s">
         <v>1352</v>
@@ -30000,10 +30003,10 @@
         <v>150</v>
       </c>
       <c r="L548">
-        <v>65.900000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="M548">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30011,10 +30014,10 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B549" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C549" t="s">
         <v>1323</v>
@@ -30029,10 +30032,10 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="H549" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J549" t="s">
         <v>564</v>
@@ -30041,10 +30044,10 @@
         <v>150</v>
       </c>
       <c r="L549">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="M549">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30052,7 +30055,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B550" t="s">
         <v>55</v>
@@ -30070,7 +30073,7 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="H550" t="s">
         <v>1334</v>
@@ -30079,10 +30082,10 @@
         <v>564</v>
       </c>
       <c r="K550">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L550">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M550">
         <v>5</v>
@@ -30093,7 +30096,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B551" t="s">
         <v>55</v>
@@ -30111,7 +30114,7 @@
         <v>1332</v>
       </c>
       <c r="G551" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="H551" t="s">
         <v>1334</v>
@@ -30120,10 +30123,10 @@
         <v>564</v>
       </c>
       <c r="K551">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L551">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="M551">
         <v>5</v>
@@ -30134,40 +30137,37 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B552" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C552" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D552" t="s">
-        <v>1008</v>
+        <v>1405</v>
       </c>
       <c r="E552" t="s">
-        <v>1323</v>
+        <v>1405</v>
       </c>
       <c r="F552" t="s">
-        <v>1332</v>
+        <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="H552" t="s">
-        <v>1334</v>
+        <v>1408</v>
       </c>
       <c r="J552" t="s">
-        <v>564</v>
+        <v>1409</v>
       </c>
       <c r="K552">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="L552">
-        <v>359</v>
+        <v>13.8</v>
       </c>
       <c r="M552">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30175,7 +30175,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30190,7 +30190,7 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="H553" t="s">
         <v>1408</v>
@@ -30202,7 +30202,7 @@
         <v>70</v>
       </c>
       <c r="L553">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M553">
         <v>6</v>
@@ -30213,7 +30213,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30228,22 +30228,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="H554" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J554" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>14.3</v>
-      </c>
-      <c r="M554">
-        <v>6</v>
+        <v>14.85</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30251,7 +30248,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30266,19 +30263,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="H555" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="J555" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>14.85</v>
+        <v>38.1</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30286,7 +30283,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30301,19 +30298,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="H556" t="s">
         <v>1418</v>
       </c>
       <c r="J556" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30321,7 +30318,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30336,19 +30333,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="H557" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="J557" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>35.5</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30356,7 +30353,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30364,6 +30361,9 @@
       <c r="C558" t="s">
         <v>1405</v>
       </c>
+      <c r="D558" t="s">
+        <v>1008</v>
+      </c>
       <c r="E558" t="s">
         <v>1405</v>
       </c>
@@ -30371,19 +30371,19 @@
         <v>1406</v>
       </c>
       <c r="G558" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="H558" t="s">
         <v>1425</v>
       </c>
       <c r="J558" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="K558">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L558">
-        <v>16.149999999999999</v>
+        <v>112</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30391,7 +30391,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30399,29 +30399,26 @@
       <c r="C559" t="s">
         <v>1405</v>
       </c>
-      <c r="D559" t="s">
-        <v>1008</v>
-      </c>
       <c r="E559" t="s">
         <v>1405</v>
       </c>
       <c r="F559" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G559" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="H559" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="J559" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="K559">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L559">
-        <v>112</v>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M559">
+        <v>45</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30429,10 +30426,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B560" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C560" t="s">
         <v>1405</v>
@@ -30443,17 +30440,17 @@
       <c r="F560" t="s">
         <v>1431</v>
       </c>
+      <c r="G560" t="s">
+        <v>1435</v>
+      </c>
       <c r="H560" t="s">
-        <v>1432</v>
-      </c>
-      <c r="J560" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>16.850000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M560">
         <v>45</v>
@@ -30464,10 +30461,10 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B561" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C561" t="s">
         <v>1405</v>
@@ -30479,19 +30476,22 @@
         <v>1431</v>
       </c>
       <c r="G561" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="H561" t="s">
-        <v>1436</v>
+        <v>1006</v>
+      </c>
+      <c r="J561" t="s">
+        <v>1439</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>17.95</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M561">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30499,7 +30499,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30514,22 +30514,22 @@
         <v>1431</v>
       </c>
       <c r="G562" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="H562" t="s">
-        <v>1006</v>
+        <v>1442</v>
       </c>
       <c r="J562" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="M562">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30537,7 +30537,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30549,25 +30549,25 @@
         <v>1405</v>
       </c>
       <c r="F563" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="G563" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="H563" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="J563" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="K563">
         <v>70</v>
       </c>
       <c r="L563">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="M563">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30575,7 +30575,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="B564" t="s">
         <v>66</v>
@@ -30590,7 +30590,7 @@
         <v>1445</v>
       </c>
       <c r="G564" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="H564" t="s">
         <v>1447</v>
@@ -30602,55 +30602,17 @@
         <v>70</v>
       </c>
       <c r="L564">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="M564">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P564" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A565" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B565" t="s">
-        <v>66</v>
-      </c>
-      <c r="C565" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E565" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F565" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G565" t="s">
-        <v>1450</v>
-      </c>
-      <c r="H565" t="s">
-        <v>1447</v>
-      </c>
-      <c r="J565" t="s">
-        <v>1448</v>
-      </c>
-      <c r="K565">
-        <v>70</v>
-      </c>
-      <c r="L565">
-        <v>40.5</v>
-      </c>
-      <c r="M565">
-        <v>5</v>
-      </c>
-      <c r="P565" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R565" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R564" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{668ACC61-BDF6-9C41-A15C-545ABF96147C}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C073842-4E22-5C41-B2CD-3AE87E1C4056}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$564</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$563</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10358" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10349" uniqueCount="2361">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7893,7 +7893,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R564"/>
+  <dimension ref="A1:R563"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -26669,7 +26669,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="B465" t="s">
         <v>66</v>
@@ -26684,13 +26684,16 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G465" t="s">
-        <v>1190</v>
+        <v>165</v>
       </c>
       <c r="H465" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I465" t="s">
+        <v>777</v>
       </c>
       <c r="J465" t="s">
         <v>87</v>
@@ -26699,10 +26702,7 @@
         <v>75</v>
       </c>
       <c r="L465">
-        <v>15.9</v>
-      </c>
-      <c r="M465">
-        <v>49</v>
+        <v>17.8</v>
       </c>
       <c r="P465" s="19">
         <v>46155</v>
@@ -26710,7 +26710,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="B466" t="s">
         <v>66</v>
@@ -26725,25 +26725,25 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G466" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H466" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I466" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J466" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>17.8</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M466">
+        <v>53</v>
       </c>
       <c r="P466" s="19">
         <v>46155</v>
@@ -26751,7 +26751,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="B467" t="s">
         <v>66</v>
@@ -26766,25 +26766,25 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1185</v>
+        <v>1198</v>
       </c>
       <c r="G467" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H467" t="s">
-        <v>1191</v>
+        <v>1199</v>
+      </c>
+      <c r="I467" t="s">
+        <v>777</v>
       </c>
       <c r="J467" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M467">
-        <v>53</v>
+        <v>22.3</v>
       </c>
       <c r="P467" s="19">
         <v>46155</v>
@@ -26792,7 +26792,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1197</v>
+        <v>1200</v>
       </c>
       <c r="B468" t="s">
         <v>66</v>
@@ -26807,25 +26807,28 @@
         <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1198</v>
+        <v>1122</v>
       </c>
       <c r="G468" t="s">
-        <v>165</v>
+        <v>1201</v>
       </c>
       <c r="H468" t="s">
-        <v>1199</v>
+        <v>1006</v>
       </c>
       <c r="I468" t="s">
-        <v>777</v>
+        <v>175</v>
       </c>
       <c r="J468" t="s">
-        <v>87</v>
+        <v>286</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>22.3</v>
+        <v>6.5</v>
+      </c>
+      <c r="M468">
+        <v>42</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26833,10 +26836,10 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B469" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C469" t="s">
         <v>978</v>
@@ -26851,33 +26854,30 @@
         <v>1122</v>
       </c>
       <c r="G469" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="H469" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I469" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J469" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="M469">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A470" t="s">
-        <v>1202</v>
+      <c r="A470">
+        <v>16003124</v>
       </c>
       <c r="B470" t="s">
         <v>55</v>
@@ -26889,19 +26889,19 @@
         <v>979</v>
       </c>
       <c r="E470" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F470" t="s">
         <v>1122</v>
       </c>
       <c r="G470" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="H470" t="s">
         <v>1204</v>
       </c>
       <c r="J470" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K470">
         <v>75</v>
@@ -26917,11 +26917,11 @@
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A471">
-        <v>16003124</v>
+      <c r="A471" t="s">
+        <v>1206</v>
       </c>
       <c r="B471" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C471" t="s">
         <v>978</v>
@@ -26930,28 +26930,31 @@
         <v>979</v>
       </c>
       <c r="E471" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F471" t="s">
         <v>1122</v>
       </c>
       <c r="G471" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="H471" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I471" t="s">
+        <v>175</v>
       </c>
       <c r="J471" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>8.4</v>
+        <v>8.61</v>
       </c>
       <c r="M471">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -26959,10 +26962,10 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B472" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C472" t="s">
         <v>978</v>
@@ -26977,25 +26980,25 @@
         <v>1122</v>
       </c>
       <c r="G472" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="H472" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I472" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J472" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>8.61</v>
+        <v>9.6</v>
       </c>
       <c r="M472">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27003,10 +27006,10 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B473" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C473" t="s">
         <v>978</v>
@@ -27021,13 +27024,13 @@
         <v>1122</v>
       </c>
       <c r="G473" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="H473" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I473" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J473" t="s">
         <v>61</v>
@@ -27036,7 +27039,7 @@
         <v>75</v>
       </c>
       <c r="L473">
-        <v>9.6</v>
+        <v>13.82</v>
       </c>
       <c r="M473">
         <v>171</v>
@@ -27047,10 +27050,10 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B474" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C474" t="s">
         <v>978</v>
@@ -27065,25 +27068,19 @@
         <v>1122</v>
       </c>
       <c r="G474" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="H474" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I474" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J474" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>13.82</v>
-      </c>
-      <c r="M474">
-        <v>171</v>
+        <v>18.3</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27091,10 +27088,10 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B475" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C475" t="s">
         <v>978</v>
@@ -27106,22 +27103,28 @@
         <v>63</v>
       </c>
       <c r="F475" t="s">
-        <v>1122</v>
+        <v>58</v>
       </c>
       <c r="G475" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="H475" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I475" t="s">
+        <v>175</v>
       </c>
       <c r="J475" t="s">
-        <v>87</v>
+        <v>1217</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>18.3</v>
+        <v>24.08</v>
+      </c>
+      <c r="M475">
+        <v>12</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27129,10 +27132,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B476" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C476" t="s">
         <v>978</v>
@@ -27144,28 +27147,19 @@
         <v>63</v>
       </c>
       <c r="F476" t="s">
-        <v>58</v>
-      </c>
-      <c r="G476" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="H476" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I476" t="s">
-        <v>175</v>
+        <v>1220</v>
       </c>
       <c r="J476" t="s">
-        <v>1217</v>
+        <v>61</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>24.08</v>
-      </c>
-      <c r="M476">
-        <v>12</v>
+        <v>31.7</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27173,10 +27167,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B477" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C477" t="s">
         <v>978</v>
@@ -27188,27 +27182,30 @@
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>1219</v>
+        <v>1121</v>
       </c>
       <c r="H477" t="s">
-        <v>1220</v>
+        <v>982</v>
       </c>
       <c r="J477" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>31.7</v>
+        <v>7.05</v>
+      </c>
+      <c r="M477">
+        <v>30</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A478" t="s">
-        <v>1221</v>
+      <c r="A478">
+        <v>27100523</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27223,33 +27220,36 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1121</v>
+        <v>1222</v>
+      </c>
+      <c r="G478" t="s">
+        <v>1223</v>
       </c>
       <c r="H478" t="s">
-        <v>982</v>
-      </c>
-      <c r="J478" t="s">
-        <v>217</v>
+        <v>1224</v>
+      </c>
+      <c r="I478" t="s">
+        <v>777</v>
+      </c>
+      <c r="J478">
+        <v>2023</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>7.05</v>
-      </c>
-      <c r="M478">
-        <v>30</v>
+        <v>17.8</v>
       </c>
       <c r="P478" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A479">
-        <v>27100523</v>
+      <c r="A479" t="s">
+        <v>1225</v>
       </c>
       <c r="B479" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C479" t="s">
         <v>978</v>
@@ -27261,36 +27261,33 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1222</v>
+        <v>58</v>
       </c>
       <c r="G479" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="H479" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I479" t="s">
-        <v>777</v>
-      </c>
-      <c r="J479">
-        <v>2023</v>
+        <v>1227</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1228</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>17.8</v>
+        <v>95</v>
       </c>
       <c r="P479" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1225</v>
+        <v>1229</v>
       </c>
       <c r="B480" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C480" t="s">
         <v>978</v>
@@ -27302,33 +27299,33 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>58</v>
+        <v>1119</v>
       </c>
       <c r="G480" t="s">
-        <v>1226</v>
+        <v>1230</v>
       </c>
       <c r="H480" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
       <c r="J480" t="s">
-        <v>1228</v>
+        <v>98</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>95</v>
+        <v>7.35</v>
+      </c>
+      <c r="M480">
+        <v>2215</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A481" t="s">
-        <v>1229</v>
-      </c>
+    <row r="481" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B481" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C481" t="s">
         <v>978</v>
@@ -27343,19 +27340,19 @@
         <v>1119</v>
       </c>
       <c r="G481" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="H481" t="s">
         <v>1231</v>
       </c>
       <c r="J481" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K481">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L481">
-        <v>7.35</v>
+        <v>15.95</v>
       </c>
       <c r="M481">
         <v>2215</v>
@@ -27364,9 +27361,12 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>1233</v>
+      </c>
       <c r="B482" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
@@ -27381,30 +27381,30 @@
         <v>1119</v>
       </c>
       <c r="G482" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="H482" t="s">
         <v>1231</v>
       </c>
-      <c r="J482" t="s">
-        <v>61</v>
+      <c r="J482">
+        <v>2023</v>
       </c>
       <c r="K482">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L482">
-        <v>15.95</v>
+        <v>8.35</v>
       </c>
       <c r="M482">
-        <v>2215</v>
+        <v>279</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B483" t="s">
         <v>66</v>
@@ -27422,33 +27422,36 @@
         <v>1119</v>
       </c>
       <c r="G483" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="H483" t="s">
-        <v>1231</v>
-      </c>
-      <c r="J483">
-        <v>2023</v>
+        <v>1237</v>
+      </c>
+      <c r="I483" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J483" t="s">
+        <v>61</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>8.35</v>
+        <v>13.5</v>
       </c>
       <c r="M483">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
       <c r="B484" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C484" t="s">
         <v>978</v>
@@ -27463,33 +27466,27 @@
         <v>1119</v>
       </c>
       <c r="G484" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="H484" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I484" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="J484" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>13.5</v>
-      </c>
-      <c r="M484">
-        <v>205</v>
+        <v>14.5</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="B485" t="s">
         <v>55</v>
@@ -27507,10 +27504,10 @@
         <v>1119</v>
       </c>
       <c r="G485" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="H485" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="J485" t="s">
         <v>98</v>
@@ -27519,18 +27516,21 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>14.5</v>
+        <v>14.6</v>
+      </c>
+      <c r="M485">
+        <v>0</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A486" t="s">
-        <v>1242</v>
+    <row r="486" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>43700124</v>
       </c>
       <c r="B486" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C486" t="s">
         <v>978</v>
@@ -27542,36 +27542,33 @@
         <v>63</v>
       </c>
       <c r="F486" t="s">
-        <v>1119</v>
+        <v>1028</v>
       </c>
       <c r="G486" t="s">
-        <v>1243</v>
+        <v>165</v>
       </c>
       <c r="H486" t="s">
-        <v>1244</v>
-      </c>
-      <c r="J486" t="s">
-        <v>98</v>
+        <v>1029</v>
+      </c>
+      <c r="J486">
+        <v>2024</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>14.6</v>
-      </c>
-      <c r="M486">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A487">
-        <v>43700124</v>
+        <v>43700325</v>
       </c>
       <c r="B487" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27586,27 +27583,27 @@
         <v>1028</v>
       </c>
       <c r="G487" t="s">
-        <v>165</v>
+        <v>1245</v>
       </c>
       <c r="H487" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="J487">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>37</v>
+        <v>7.9</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A488">
-        <v>43700325</v>
+        <v>43700524</v>
       </c>
       <c r="B488" t="s">
         <v>55</v>
@@ -27624,30 +27621,30 @@
         <v>1028</v>
       </c>
       <c r="G488" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="H488" t="s">
         <v>1031</v>
       </c>
       <c r="J488">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>7.9</v>
+        <v>14.5</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A489">
-        <v>43700524</v>
+    <row r="489" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>1247</v>
       </c>
       <c r="B489" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C489" t="s">
         <v>978</v>
@@ -27656,33 +27653,36 @@
         <v>979</v>
       </c>
       <c r="E489" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F489" t="s">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="G489" t="s">
-        <v>1246</v>
+        <v>981</v>
       </c>
       <c r="H489" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J489">
-        <v>2024</v>
+        <v>982</v>
+      </c>
+      <c r="J489" t="s">
+        <v>98</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>14.5</v>
+        <v>3.8</v>
+      </c>
+      <c r="M489">
+        <v>324</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B490" t="s">
         <v>66</v>
@@ -27700,30 +27700,30 @@
         <v>980</v>
       </c>
       <c r="G490" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="H490" t="s">
-        <v>982</v>
-      </c>
-      <c r="J490" t="s">
-        <v>98</v>
+        <v>985</v>
+      </c>
+      <c r="J490">
+        <v>2025</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="M490">
-        <v>324</v>
+        <v>368</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B491" t="s">
         <v>66</v>
@@ -27741,10 +27741,10 @@
         <v>980</v>
       </c>
       <c r="G491" t="s">
-        <v>984</v>
+        <v>1250</v>
       </c>
       <c r="H491" t="s">
-        <v>985</v>
+        <v>292</v>
       </c>
       <c r="J491">
         <v>2025</v>
@@ -27753,21 +27753,21 @@
         <v>75</v>
       </c>
       <c r="L491">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="M491">
-        <v>368</v>
+        <v>969</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B492" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C492" t="s">
         <v>978</v>
@@ -27782,33 +27782,33 @@
         <v>980</v>
       </c>
       <c r="G492" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="H492" t="s">
-        <v>292</v>
-      </c>
-      <c r="J492">
-        <v>2025</v>
+        <v>1224</v>
+      </c>
+      <c r="J492" t="s">
+        <v>339</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>3.99</v>
+        <v>7.2</v>
       </c>
       <c r="M492">
-        <v>969</v>
+        <v>0</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B493" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27823,30 +27823,30 @@
         <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>1252</v>
+        <v>1108</v>
       </c>
       <c r="H493" t="s">
-        <v>1224</v>
+        <v>982</v>
       </c>
       <c r="J493" t="s">
-        <v>339</v>
+        <v>564</v>
       </c>
       <c r="K493">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="L493">
-        <v>7.2</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M493">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B494" t="s">
         <v>66</v>
@@ -27864,71 +27864,71 @@
         <v>980</v>
       </c>
       <c r="G494" t="s">
-        <v>1108</v>
+        <v>1255</v>
       </c>
       <c r="H494" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="J494" t="s">
-        <v>564</v>
+        <v>98</v>
       </c>
       <c r="K494">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L494">
-        <v>16.399999999999999</v>
+        <v>25.5</v>
       </c>
       <c r="M494">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B495" t="s">
         <v>66</v>
       </c>
       <c r="C495" t="s">
-        <v>978</v>
+        <v>1257</v>
       </c>
       <c r="D495" t="s">
-        <v>979</v>
+        <v>1258</v>
       </c>
       <c r="E495" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F495" t="s">
-        <v>980</v>
+        <v>1259</v>
       </c>
       <c r="G495" t="s">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="H495" t="s">
-        <v>985</v>
+        <v>1261</v>
       </c>
       <c r="J495" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K495">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="L495">
-        <v>25.5</v>
+        <v>5</v>
       </c>
       <c r="M495">
-        <v>71</v>
+        <v>240</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1256</v>
+        <v>1262</v>
       </c>
       <c r="B496" t="s">
         <v>66</v>
@@ -27943,13 +27943,13 @@
         <v>57</v>
       </c>
       <c r="F496" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G496" t="s">
-        <v>1260</v>
+        <v>113</v>
       </c>
       <c r="H496" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="J496" t="s">
         <v>339</v>
@@ -27958,18 +27958,21 @@
         <v>75</v>
       </c>
       <c r="L496">
-        <v>5</v>
+        <v>9.1</v>
       </c>
       <c r="M496">
-        <v>240</v>
+        <v>66</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
       </c>
-    </row>
-    <row r="497" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A497" t="s">
-        <v>1262</v>
+      <c r="R496" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="497" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A497">
+        <v>24000925</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -27981,39 +27984,36 @@
         <v>1258</v>
       </c>
       <c r="E497" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F497" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G497" t="s">
-        <v>113</v>
+        <v>1265</v>
       </c>
       <c r="H497" t="s">
-        <v>1264</v>
-      </c>
-      <c r="J497" t="s">
-        <v>339</v>
+        <v>1261</v>
+      </c>
+      <c r="J497">
+        <v>2025</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>9.1</v>
+        <v>5.55</v>
       </c>
       <c r="M497">
-        <v>66</v>
+        <v>549</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
       </c>
-      <c r="R497" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="498" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A498">
-        <v>24000925</v>
+    </row>
+    <row r="498" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A498" t="s">
+        <v>1266</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28025,36 +28025,36 @@
         <v>1258</v>
       </c>
       <c r="E498" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F498" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="G498" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="H498" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J498">
-        <v>2025</v>
+        <v>1269</v>
+      </c>
+      <c r="J498" t="s">
+        <v>87</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>5.55</v>
+        <v>4.5</v>
       </c>
       <c r="M498">
-        <v>549</v>
+        <v>3</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="499" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28069,33 +28069,33 @@
         <v>63</v>
       </c>
       <c r="F499" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
       <c r="G499" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
       <c r="H499" t="s">
-        <v>1269</v>
+        <v>1273</v>
       </c>
       <c r="J499" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="M499">
-        <v>3</v>
+        <v>288</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="500" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A500" t="s">
-        <v>1270</v>
+    <row r="500" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A500">
+        <v>24001825</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28110,33 +28110,33 @@
         <v>63</v>
       </c>
       <c r="F500" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="G500" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="H500" t="s">
-        <v>1273</v>
-      </c>
-      <c r="J500" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J500">
+        <v>2025</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="M500">
-        <v>288</v>
+        <v>54</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="501" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A501">
-        <v>24001825</v>
+    <row r="501" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A501" t="s">
+        <v>1275</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28151,33 +28151,30 @@
         <v>63</v>
       </c>
       <c r="F501" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G501" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="H501" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J501">
-        <v>2025</v>
+        <v>1277</v>
+      </c>
+      <c r="J501" t="s">
+        <v>98</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>6.75</v>
+        <v>6.85</v>
       </c>
       <c r="M501">
-        <v>54</v>
+        <v>666</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="502" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="B502" t="s">
         <v>66</v>
@@ -28192,30 +28189,36 @@
         <v>63</v>
       </c>
       <c r="F502" t="s">
-        <v>1276</v>
+        <v>1279</v>
+      </c>
+      <c r="G502" t="s">
+        <v>1280</v>
       </c>
       <c r="H502" t="s">
-        <v>1277</v>
+        <v>1281</v>
+      </c>
+      <c r="I502" t="s">
+        <v>69</v>
       </c>
       <c r="J502" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>6.85</v>
+        <v>8.25</v>
       </c>
       <c r="M502">
-        <v>666</v>
+        <v>318</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="503" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="B503" t="s">
         <v>66</v>
@@ -28224,42 +28227,36 @@
         <v>1257</v>
       </c>
       <c r="D503" t="s">
-        <v>1258</v>
+        <v>1283</v>
       </c>
       <c r="E503" t="s">
         <v>63</v>
       </c>
       <c r="F503" t="s">
-        <v>1279</v>
+        <v>1284</v>
       </c>
       <c r="G503" t="s">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="H503" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I503" t="s">
-        <v>69</v>
+        <v>1286</v>
       </c>
       <c r="J503" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>8.25</v>
-      </c>
-      <c r="M503">
-        <v>318</v>
+        <v>4.95</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="504" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="B504" t="s">
         <v>66</v>
@@ -28277,27 +28274,30 @@
         <v>1284</v>
       </c>
       <c r="G504" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="H504" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="J504" t="s">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>4.95</v>
+        <v>6.1</v>
+      </c>
+      <c r="M504">
+        <v>133</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="505" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B505" t="s">
         <v>66</v>
@@ -28320,8 +28320,8 @@
       <c r="H505" t="s">
         <v>1289</v>
       </c>
-      <c r="J505" t="s">
-        <v>87</v>
+      <c r="J505">
+        <v>2024</v>
       </c>
       <c r="K505">
         <v>75</v>
@@ -28329,19 +28329,16 @@
       <c r="L505">
         <v>6.1</v>
       </c>
-      <c r="M505">
-        <v>133</v>
-      </c>
       <c r="P505" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="506" spans="1:18" x14ac:dyDescent="0.2">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B506" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C506" t="s">
         <v>1257</v>
@@ -28356,27 +28353,30 @@
         <v>1284</v>
       </c>
       <c r="G506" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="H506" t="s">
-        <v>1289</v>
-      </c>
-      <c r="J506">
-        <v>2024</v>
+        <v>1293</v>
+      </c>
+      <c r="J506" t="s">
+        <v>109</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>6.1</v>
+        <v>13.2</v>
+      </c>
+      <c r="M506">
+        <v>0</v>
       </c>
       <c r="P506" s="19">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B507" t="s">
         <v>55</v>
@@ -28394,19 +28394,19 @@
         <v>1284</v>
       </c>
       <c r="G507" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="H507" t="s">
         <v>1293</v>
       </c>
       <c r="J507" t="s">
-        <v>109</v>
+        <v>1228</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>13.2</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M507">
         <v>0</v>
@@ -28415,9 +28415,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="508" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B508" t="s">
         <v>55</v>
@@ -28432,22 +28432,22 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="G508" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="H508" t="s">
         <v>1293</v>
       </c>
       <c r="J508" t="s">
-        <v>1228</v>
+        <v>61</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>16.350000000000001</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M508">
         <v>0</v>
@@ -28456,50 +28456,50 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A509" t="s">
-        <v>1296</v>
+    <row r="509" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A509">
+        <v>10702526</v>
       </c>
       <c r="B509" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C509" t="s">
         <v>1257</v>
       </c>
       <c r="D509" t="s">
-        <v>1283</v>
+        <v>1299</v>
       </c>
       <c r="E509" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F509" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="G509" t="s">
-        <v>1298</v>
+        <v>726</v>
       </c>
       <c r="H509" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J509" t="s">
-        <v>61</v>
+        <v>1300</v>
+      </c>
+      <c r="J509">
+        <v>2026</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>5.0999999999999996</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M509">
-        <v>0</v>
+        <v>1327</v>
       </c>
       <c r="P509" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="510" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A510">
-        <v>10702526</v>
+    <row r="510" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A510" t="s">
+        <v>1301</v>
       </c>
       <c r="B510" t="s">
         <v>66</v>
@@ -28508,39 +28508,39 @@
         <v>1257</v>
       </c>
       <c r="D510" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="E510" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="G510" t="s">
-        <v>726</v>
+        <v>1304</v>
       </c>
       <c r="H510" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J510">
-        <v>2026</v>
+        <v>1305</v>
+      </c>
+      <c r="J510" t="s">
+        <v>109</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>4.6500000000000004</v>
+        <v>8.5</v>
       </c>
       <c r="M510">
-        <v>1327</v>
+        <v>6</v>
       </c>
       <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="511" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1301</v>
+        <v>1306</v>
       </c>
       <c r="B511" t="s">
         <v>66</v>
@@ -28558,7 +28558,7 @@
         <v>1303</v>
       </c>
       <c r="G511" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="H511" t="s">
         <v>1305</v>
@@ -28570,18 +28570,18 @@
         <v>75</v>
       </c>
       <c r="L511">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="M511">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="P511" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="512" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B512" t="s">
         <v>66</v>
@@ -28599,7 +28599,7 @@
         <v>1303</v>
       </c>
       <c r="G512" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="H512" t="s">
         <v>1305</v>
@@ -28614,7 +28614,7 @@
         <v>8.6</v>
       </c>
       <c r="M512">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
@@ -28622,7 +28622,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28640,13 +28640,13 @@
         <v>1303</v>
       </c>
       <c r="G513" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="H513" t="s">
         <v>1305</v>
       </c>
       <c r="J513" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="K513">
         <v>75</v>
@@ -28655,7 +28655,7 @@
         <v>8.6</v>
       </c>
       <c r="M513">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28663,7 +28663,7 @@
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28681,7 +28681,7 @@
         <v>1303</v>
       </c>
       <c r="G514" t="s">
-        <v>1304</v>
+        <v>1312</v>
       </c>
       <c r="H514" t="s">
         <v>1305</v>
@@ -28696,7 +28696,7 @@
         <v>8.6</v>
       </c>
       <c r="M514">
-        <v>18</v>
+        <v>662</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28704,7 +28704,7 @@
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28722,22 +28722,22 @@
         <v>1303</v>
       </c>
       <c r="G515" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="H515" t="s">
         <v>1305</v>
       </c>
       <c r="J515" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K515">
         <v>75</v>
       </c>
       <c r="L515">
-        <v>8.6</v>
+        <v>12.05</v>
       </c>
       <c r="M515">
-        <v>662</v>
+        <v>64</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28745,7 +28745,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28763,22 +28763,22 @@
         <v>1303</v>
       </c>
       <c r="G516" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="H516" t="s">
         <v>1305</v>
       </c>
-      <c r="J516" t="s">
-        <v>127</v>
+      <c r="J516">
+        <v>2021</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>12.05</v>
+        <v>13</v>
       </c>
       <c r="M516">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28786,7 +28786,7 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B517" t="s">
         <v>66</v>
@@ -28804,13 +28804,13 @@
         <v>1303</v>
       </c>
       <c r="G517" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="H517" t="s">
         <v>1305</v>
       </c>
-      <c r="J517">
-        <v>2021</v>
+      <c r="J517" t="s">
+        <v>109</v>
       </c>
       <c r="K517">
         <v>75</v>
@@ -28819,7 +28819,7 @@
         <v>13</v>
       </c>
       <c r="M517">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28827,7 +28827,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="B518" t="s">
         <v>66</v>
@@ -28845,7 +28845,7 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="H518" t="s">
         <v>1305</v>
@@ -28857,7 +28857,7 @@
         <v>75</v>
       </c>
       <c r="L518">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M518">
         <v>36</v>
@@ -28868,7 +28868,7 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="B519" t="s">
         <v>66</v>
@@ -28880,28 +28880,28 @@
         <v>1302</v>
       </c>
       <c r="E519" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F519" t="s">
         <v>1303</v>
       </c>
       <c r="G519" t="s">
-        <v>1320</v>
+        <v>1042</v>
       </c>
       <c r="H519" t="s">
         <v>1305</v>
       </c>
       <c r="J519" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>16</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M519">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -28909,40 +28909,40 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
       </c>
       <c r="C520" t="s">
-        <v>1257</v>
+        <v>1323</v>
       </c>
       <c r="D520" t="s">
-        <v>1302</v>
+        <v>1258</v>
       </c>
       <c r="E520" t="s">
-        <v>57</v>
+        <v>1323</v>
       </c>
       <c r="F520" t="s">
-        <v>1303</v>
+        <v>1324</v>
       </c>
       <c r="G520" t="s">
-        <v>1042</v>
+        <v>1325</v>
       </c>
       <c r="H520" t="s">
-        <v>1305</v>
+        <v>1261</v>
       </c>
       <c r="J520" t="s">
-        <v>87</v>
+        <v>564</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>8.0500000000000007</v>
+        <v>6.2</v>
       </c>
       <c r="M520">
-        <v>55</v>
+        <v>4411</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -28950,7 +28950,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1322</v>
+        <v>1326</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -28958,20 +28958,17 @@
       <c r="C521" t="s">
         <v>1323</v>
       </c>
-      <c r="D521" t="s">
-        <v>1258</v>
-      </c>
       <c r="E521" t="s">
         <v>1323</v>
       </c>
       <c r="F521" t="s">
-        <v>1324</v>
+        <v>58</v>
       </c>
       <c r="G521" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="H521" t="s">
-        <v>1261</v>
+        <v>1001</v>
       </c>
       <c r="J521" t="s">
         <v>564</v>
@@ -28982,16 +28979,13 @@
       <c r="L521">
         <v>6.2</v>
       </c>
-      <c r="M521">
-        <v>4411</v>
-      </c>
       <c r="P521" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29006,10 +29000,10 @@
         <v>58</v>
       </c>
       <c r="G522" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="H522" t="s">
-        <v>1001</v>
+        <v>1330</v>
       </c>
       <c r="J522" t="s">
         <v>564</v>
@@ -29018,7 +29012,7 @@
         <v>75</v>
       </c>
       <c r="L522">
-        <v>6.2</v>
+        <v>8.99</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29026,7 +29020,7 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29038,22 +29032,25 @@
         <v>1323</v>
       </c>
       <c r="F523" t="s">
-        <v>58</v>
+        <v>1332</v>
       </c>
       <c r="G523" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
       <c r="H523" t="s">
-        <v>1330</v>
+        <v>1334</v>
       </c>
       <c r="J523" t="s">
         <v>564</v>
       </c>
       <c r="K523">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L523">
-        <v>8.99</v>
+        <v>16.899999999999999</v>
+      </c>
+      <c r="M523">
+        <v>5</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29061,7 +29058,7 @@
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1331</v>
+        <v>1335</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29076,22 +29073,22 @@
         <v>1332</v>
       </c>
       <c r="G524" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="H524" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="J524" t="s">
         <v>564</v>
       </c>
       <c r="K524">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L524">
-        <v>16.899999999999999</v>
+        <v>16.45</v>
       </c>
       <c r="M524">
-        <v>5</v>
+        <v>6532</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29099,7 +29096,7 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29114,10 +29111,10 @@
         <v>1332</v>
       </c>
       <c r="G525" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="H525" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="J525" t="s">
         <v>564</v>
@@ -29126,10 +29123,10 @@
         <v>75</v>
       </c>
       <c r="L525">
-        <v>16.45</v>
+        <v>23.5</v>
       </c>
       <c r="M525">
-        <v>6532</v>
+        <v>418</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29137,10 +29134,10 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B526" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C526" t="s">
         <v>1323</v>
@@ -29152,10 +29149,10 @@
         <v>1332</v>
       </c>
       <c r="G526" t="s">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="H526" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="J526" t="s">
         <v>564</v>
@@ -29164,10 +29161,7 @@
         <v>75</v>
       </c>
       <c r="L526">
-        <v>23.5</v>
-      </c>
-      <c r="M526">
-        <v>418</v>
+        <v>23.9</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29175,10 +29169,10 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1341</v>
+        <v>1347</v>
       </c>
       <c r="B527" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C527" t="s">
         <v>1323</v>
@@ -29190,10 +29184,10 @@
         <v>1332</v>
       </c>
       <c r="G527" t="s">
-        <v>1342</v>
+        <v>1348</v>
       </c>
       <c r="H527" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="J527" t="s">
         <v>564</v>
@@ -29202,7 +29196,10 @@
         <v>75</v>
       </c>
       <c r="L527">
-        <v>23.9</v>
+        <v>25.8</v>
+      </c>
+      <c r="M527">
+        <v>995</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29210,7 +29207,7 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29225,10 +29222,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="H528" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29237,10 +29234,10 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>25.8</v>
+        <v>27.5</v>
       </c>
       <c r="M528">
-        <v>995</v>
+        <v>31</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29248,7 +29245,7 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29263,10 +29260,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="H529" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29275,10 +29272,10 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>27.5</v>
+        <v>29</v>
       </c>
       <c r="M529">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29286,7 +29283,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29301,10 +29298,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="H530" t="s">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29313,10 +29310,10 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>29</v>
+        <v>29.35</v>
       </c>
       <c r="M530">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29324,10 +29321,10 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B531" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C531" t="s">
         <v>1323</v>
@@ -29339,7 +29336,7 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="H531" t="s">
         <v>1349</v>
@@ -29348,10 +29345,10 @@
         <v>564</v>
       </c>
       <c r="K531">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L531">
-        <v>29.35</v>
+        <v>63</v>
       </c>
       <c r="M531">
         <v>60</v>
@@ -29362,7 +29359,7 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B532" t="s">
         <v>55</v>
@@ -29377,7 +29374,7 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="H532" t="s">
         <v>1349</v>
@@ -29386,10 +29383,10 @@
         <v>564</v>
       </c>
       <c r="K532">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L532">
-        <v>63</v>
+        <v>34.5</v>
       </c>
       <c r="M532">
         <v>60</v>
@@ -29400,7 +29397,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B533" t="s">
         <v>55</v>
@@ -29415,7 +29412,7 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="H533" t="s">
         <v>1349</v>
@@ -29427,7 +29424,7 @@
         <v>75</v>
       </c>
       <c r="L533">
-        <v>34.5</v>
+        <v>30.4</v>
       </c>
       <c r="M533">
         <v>60</v>
@@ -29438,10 +29435,10 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="B534" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C534" t="s">
         <v>1323</v>
@@ -29453,10 +29450,10 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1362</v>
+        <v>919</v>
       </c>
       <c r="H534" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J534" t="s">
         <v>564</v>
@@ -29465,10 +29462,10 @@
         <v>75</v>
       </c>
       <c r="L534">
-        <v>30.4</v>
+        <v>29.8</v>
       </c>
       <c r="M534">
-        <v>60</v>
+        <v>417</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29476,7 +29473,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29491,10 +29488,10 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>919</v>
+        <v>1368</v>
       </c>
       <c r="H535" t="s">
-        <v>1352</v>
+        <v>1369</v>
       </c>
       <c r="J535" t="s">
         <v>564</v>
@@ -29503,10 +29500,10 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>29.8</v>
+        <v>31</v>
       </c>
       <c r="M535">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29514,7 +29511,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29529,10 +29526,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="H536" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29541,10 +29538,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M536">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29552,7 +29549,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29567,10 +29564,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="H537" t="s">
-        <v>1372</v>
+        <v>1349</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29579,10 +29576,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>33</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M537">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29590,7 +29587,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29605,10 +29602,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H538" t="s">
-        <v>1349</v>
+        <v>1377</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29617,10 +29614,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>34.200000000000003</v>
+        <v>39</v>
       </c>
       <c r="M538">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29628,10 +29625,10 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="B539" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C539" t="s">
         <v>1323</v>
@@ -29643,10 +29640,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="H539" t="s">
-        <v>1377</v>
+        <v>1334</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29655,7 +29652,7 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M539">
         <v>0</v>
@@ -29666,10 +29663,10 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B540" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C540" t="s">
         <v>1323</v>
@@ -29681,10 +29678,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="H540" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29693,10 +29690,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="M540">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29704,7 +29701,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29719,7 +29716,7 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="H541" t="s">
         <v>1352</v>
@@ -29731,10 +29728,10 @@
         <v>75</v>
       </c>
       <c r="L541">
+        <v>47.3</v>
+      </c>
+      <c r="M541">
         <v>41</v>
-      </c>
-      <c r="M541">
-        <v>31</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29742,7 +29739,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29757,10 +29754,10 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="H542" t="s">
-        <v>1352</v>
+        <v>1386</v>
       </c>
       <c r="J542" t="s">
         <v>564</v>
@@ -29769,10 +29766,10 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>47.3</v>
+        <v>49</v>
       </c>
       <c r="M542">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29780,7 +29777,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29795,10 +29792,10 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="H543" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="J543" t="s">
         <v>564</v>
@@ -29818,7 +29815,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29833,22 +29830,22 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="H544" t="s">
-        <v>1389</v>
+        <v>1334</v>
       </c>
       <c r="J544" t="s">
-        <v>564</v>
+        <v>167</v>
       </c>
       <c r="K544">
         <v>75</v>
       </c>
       <c r="L544">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="M544">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29856,7 +29853,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29871,22 +29868,22 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="H545" t="s">
-        <v>1334</v>
-      </c>
-      <c r="J545" t="s">
-        <v>167</v>
+        <v>1372</v>
+      </c>
+      <c r="J545">
+        <v>2017</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="M545">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29894,7 +29891,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29902,6 +29899,9 @@
       <c r="C546" t="s">
         <v>1323</v>
       </c>
+      <c r="D546" t="s">
+        <v>1008</v>
+      </c>
       <c r="E546" t="s">
         <v>1323</v>
       </c>
@@ -29909,22 +29909,22 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H546" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J546">
-        <v>2017</v>
+        <v>1352</v>
+      </c>
+      <c r="J546" t="s">
+        <v>564</v>
       </c>
       <c r="K546">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L546">
-        <v>199</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M546">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29932,7 +29932,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29950,7 +29950,7 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="H547" t="s">
         <v>1352</v>
@@ -29962,10 +29962,10 @@
         <v>150</v>
       </c>
       <c r="L547">
-        <v>65.900000000000006</v>
+        <v>54.5</v>
       </c>
       <c r="M547">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29973,10 +29973,10 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B548" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C548" t="s">
         <v>1323</v>
@@ -29991,10 +29991,10 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="H548" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J548" t="s">
         <v>564</v>
@@ -30003,10 +30003,10 @@
         <v>150</v>
       </c>
       <c r="L548">
-        <v>54.5</v>
+        <v>59</v>
       </c>
       <c r="M548">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30014,7 +30014,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B549" t="s">
         <v>55</v>
@@ -30032,7 +30032,7 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="H549" t="s">
         <v>1334</v>
@@ -30041,10 +30041,10 @@
         <v>564</v>
       </c>
       <c r="K549">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L549">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M549">
         <v>5</v>
@@ -30055,7 +30055,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B550" t="s">
         <v>55</v>
@@ -30073,7 +30073,7 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="H550" t="s">
         <v>1334</v>
@@ -30082,10 +30082,10 @@
         <v>564</v>
       </c>
       <c r="K550">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="L550">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="M550">
         <v>5</v>
@@ -30096,40 +30096,37 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B551" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C551" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D551" t="s">
-        <v>1008</v>
+        <v>1405</v>
       </c>
       <c r="E551" t="s">
-        <v>1323</v>
+        <v>1405</v>
       </c>
       <c r="F551" t="s">
-        <v>1332</v>
+        <v>1406</v>
       </c>
       <c r="G551" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="H551" t="s">
-        <v>1334</v>
+        <v>1408</v>
       </c>
       <c r="J551" t="s">
-        <v>564</v>
+        <v>1409</v>
       </c>
       <c r="K551">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="L551">
-        <v>359</v>
+        <v>13.8</v>
       </c>
       <c r="M551">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30137,7 +30134,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30152,7 +30149,7 @@
         <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="H552" t="s">
         <v>1408</v>
@@ -30164,7 +30161,7 @@
         <v>70</v>
       </c>
       <c r="L552">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="M552">
         <v>6</v>
@@ -30175,7 +30172,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30190,22 +30187,19 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="H553" t="s">
-        <v>1408</v>
+        <v>1414</v>
       </c>
       <c r="J553" t="s">
-        <v>1409</v>
+        <v>1415</v>
       </c>
       <c r="K553">
         <v>70</v>
       </c>
       <c r="L553">
-        <v>14.3</v>
-      </c>
-      <c r="M553">
-        <v>6</v>
+        <v>14.85</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30213,7 +30207,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1412</v>
+        <v>1416</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30228,19 +30222,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1413</v>
+        <v>1417</v>
       </c>
       <c r="H554" t="s">
-        <v>1414</v>
+        <v>1418</v>
       </c>
       <c r="J554" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>14.85</v>
+        <v>38.1</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30248,7 +30242,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30263,19 +30257,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1417</v>
+        <v>1421</v>
       </c>
       <c r="H555" t="s">
         <v>1418</v>
       </c>
       <c r="J555" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30283,7 +30277,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30298,19 +30292,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="H556" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="J556" t="s">
-        <v>1422</v>
+        <v>1426</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>35.5</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30318,7 +30312,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1423</v>
+        <v>1427</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30326,6 +30320,9 @@
       <c r="C557" t="s">
         <v>1405</v>
       </c>
+      <c r="D557" t="s">
+        <v>1008</v>
+      </c>
       <c r="E557" t="s">
         <v>1405</v>
       </c>
@@ -30333,19 +30330,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1424</v>
+        <v>1428</v>
       </c>
       <c r="H557" t="s">
         <v>1425</v>
       </c>
       <c r="J557" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="K557">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L557">
-        <v>16.149999999999999</v>
+        <v>112</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30353,7 +30350,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30361,29 +30358,26 @@
       <c r="C558" t="s">
         <v>1405</v>
       </c>
-      <c r="D558" t="s">
-        <v>1008</v>
-      </c>
       <c r="E558" t="s">
         <v>1405</v>
       </c>
       <c r="F558" t="s">
-        <v>1406</v>
-      </c>
-      <c r="G558" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="H558" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="J558" t="s">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="K558">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L558">
-        <v>112</v>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="M558">
+        <v>45</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30391,10 +30385,10 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B559" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C559" t="s">
         <v>1405</v>
@@ -30405,17 +30399,17 @@
       <c r="F559" t="s">
         <v>1431</v>
       </c>
+      <c r="G559" t="s">
+        <v>1435</v>
+      </c>
       <c r="H559" t="s">
-        <v>1432</v>
-      </c>
-      <c r="J559" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>16.850000000000001</v>
+        <v>17.95</v>
       </c>
       <c r="M559">
         <v>45</v>
@@ -30426,10 +30420,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B560" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C560" t="s">
         <v>1405</v>
@@ -30441,19 +30435,22 @@
         <v>1431</v>
       </c>
       <c r="G560" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="H560" t="s">
-        <v>1436</v>
+        <v>1006</v>
+      </c>
+      <c r="J560" t="s">
+        <v>1439</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>17.95</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M560">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30461,7 +30458,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30476,22 +30473,22 @@
         <v>1431</v>
       </c>
       <c r="G561" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="H561" t="s">
-        <v>1006</v>
+        <v>1442</v>
       </c>
       <c r="J561" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>20.399999999999999</v>
+        <v>40</v>
       </c>
       <c r="M561">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30499,7 +30496,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30511,25 +30508,25 @@
         <v>1405</v>
       </c>
       <c r="F562" t="s">
-        <v>1431</v>
+        <v>1445</v>
       </c>
       <c r="G562" t="s">
-        <v>1441</v>
+        <v>1446</v>
       </c>
       <c r="H562" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="J562" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>40</v>
+        <v>36.5</v>
       </c>
       <c r="M562">
-        <v>155</v>
+        <v>7</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30537,7 +30534,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30552,7 +30549,7 @@
         <v>1445</v>
       </c>
       <c r="G563" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="H563" t="s">
         <v>1447</v>
@@ -30564,55 +30561,17 @@
         <v>70</v>
       </c>
       <c r="L563">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="M563">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P563" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A564" t="s">
-        <v>1449</v>
-      </c>
-      <c r="B564" t="s">
-        <v>66</v>
-      </c>
-      <c r="C564" t="s">
-        <v>1405</v>
-      </c>
-      <c r="E564" t="s">
-        <v>1405</v>
-      </c>
-      <c r="F564" t="s">
-        <v>1445</v>
-      </c>
-      <c r="G564" t="s">
-        <v>1450</v>
-      </c>
-      <c r="H564" t="s">
-        <v>1447</v>
-      </c>
-      <c r="J564" t="s">
-        <v>1448</v>
-      </c>
-      <c r="K564">
-        <v>70</v>
-      </c>
-      <c r="L564">
-        <v>40.5</v>
-      </c>
-      <c r="M564">
-        <v>5</v>
-      </c>
-      <c r="P564" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R564" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R563" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C073842-4E22-5C41-B2CD-3AE87E1C4056}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94CDF081-9E10-1C40-9466-FCBE634B4A6A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10349" uniqueCount="2361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10348" uniqueCount="2362">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7128,6 +7128,9 @@
   </si>
   <si>
     <t>Château Latour Martillac</t>
+  </si>
+  <si>
+    <t>Mézardières - Grolleau</t>
   </si>
 </sst>
 </file>
@@ -20182,8 +20185,8 @@
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A306" t="s">
-        <v>836</v>
+      <c r="A306">
+        <v>66701025</v>
       </c>
       <c r="B306" t="s">
         <v>55</v>
@@ -20198,7 +20201,7 @@
         <v>58</v>
       </c>
       <c r="G306" t="s">
-        <v>837</v>
+        <v>2361</v>
       </c>
       <c r="H306" t="s">
         <v>755</v>
@@ -20213,7 +20216,7 @@
         <v>75</v>
       </c>
       <c r="L306">
-        <v>14.95</v>
+        <v>11.75</v>
       </c>
       <c r="M306">
         <v>0</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94CDF081-9E10-1C40-9466-FCBE634B4A6A}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D081530-DB5A-A041-B5EC-F53E9620C266}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7392,10 +7392,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14679,7 +14679,7 @@
         <v>512</v>
       </c>
       <c r="G170" t="s">
-        <v>515</v>
+        <v>431</v>
       </c>
       <c r="H170" t="s">
         <v>398</v>
@@ -30905,351 +30905,361 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1471</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1472</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1473</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1475</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1476</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1477</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1478</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1479</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1480</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1481</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1482</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1483</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1484</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1485</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1486</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1487</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1488</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31262,16 +31272,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52085,28 +52085,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -52387,33 +52365,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="8b06e530-ed80-4ff0-be41-2806c2470479" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TypeDocument xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+    <Statut xmlns="3ee8e01a-5661-48eb-b75f-361470a34d5b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52431,4 +52405,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D081530-DB5A-A041-B5EC-F53E9620C266}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D775E16-ECD7-BC4B-90F0-C6199B04BBA4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7392,10 +7392,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13561,7 +13561,7 @@
         <v>75</v>
       </c>
       <c r="L142">
-        <v>23.3</v>
+        <v>21.9</v>
       </c>
       <c r="M142">
         <v>3</v>
@@ -30905,361 +30905,351 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>1471</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>1472</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="20" t="s">
         <v>1473</v>
       </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="20" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="20" t="s">
         <v>1475</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="20" t="s">
         <v>1476</v>
       </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="20" t="s">
         <v>1477</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="20" t="s">
         <v>1478</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="20" t="s">
         <v>1479</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="22"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="22" t="s">
         <v>1480</v>
       </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="20" t="s">
         <v>1481</v>
       </c>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="20" t="s">
         <v>1482</v>
       </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1483</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
+      <c r="A29" s="20" t="s">
         <v>1484</v>
       </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
+      <c r="A30" s="20" t="s">
         <v>1485</v>
       </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="20" t="s">
         <v>1486</v>
       </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>1487</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
-      <c r="L33" s="23"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="20" t="s">
         <v>1488</v>
       </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31272,6 +31262,16 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52085,6 +52085,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -52365,15 +52374,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -52388,6 +52388,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52407,28 +52415,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
     <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -7392,10 +7392,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -30905,351 +30905,361 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>1471</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="20" t="s">
         <v>1472</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="22" t="s">
         <v>1473</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="22" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="20"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="22" t="s">
         <v>1475</v>
       </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>1476</v>
       </c>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="22" t="s">
         <v>1477</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="22" t="s">
         <v>1478</v>
       </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="22" t="s">
         <v>1479</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="20" t="s">
         <v>1480</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="22" t="s">
         <v>1481</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="22" t="s">
         <v>1482</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="23" t="s">
         <v>1483</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="22" t="s">
         <v>1484</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="22" t="s">
         <v>1485</v>
       </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="22" t="s">
         <v>1486</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="23" t="s">
         <v>1487</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="22" t="s">
         <v>1488</v>
       </c>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A31:L31"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A25:L25"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A30:L30"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="A14:L14"/>
@@ -31262,16 +31272,6 @@
     <mergeCell ref="A21:L21"/>
     <mergeCell ref="A22:L22"/>
     <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:L32"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A30:L30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -52085,15 +52085,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010002F00E183A222D47876A51DABA610BDE" ma:contentTypeVersion="26" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a17b2b7e63fcc2703c51012434bdcd89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ee8e01a-5661-48eb-b75f-361470a34d5b" xmlns:ns3="a1e62e11-0de7-4d84-85a0-444df097221b" xmlns:ns4="8b06e530-ed80-4ff0-be41-2806c2470479" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3eb9c2be522d359ee908948911399945" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
@@ -52374,6 +52365,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -52388,14 +52388,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7553FD30-6571-495C-A9F0-180AD16AA241}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -52415,20 +52407,28 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0FE2C01-6340-45D6-8526-0AB30AB8259E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DE35E19-146F-4A5C-934B-8F843242C74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8b06e530-ed80-4ff0-be41-2806c2470479"/>
     <ds:schemaRef ds:uri="a1e62e11-0de7-4d84-85a0-444df097221b"/>
     <ds:schemaRef ds:uri="3ee8e01a-5661-48eb-b75f-361470a34d5b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D775E16-ECD7-BC4B-90F0-C6199B04BBA4}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67A874-3630-A24E-B1FC-62028CF639BC}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10348" uniqueCount="2362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="2362">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -9220,8 +9220,8 @@
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>150</v>
+      <c r="A33">
+        <v>13700223</v>
       </c>
       <c r="B33" t="s">
         <v>66</v>
@@ -9244,8 +9244,8 @@
       <c r="H33" t="s">
         <v>152</v>
       </c>
-      <c r="J33" t="s">
-        <v>153</v>
+      <c r="J33">
+        <v>2023</v>
       </c>
       <c r="K33">
         <v>75</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="170" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC67A874-3630-A24E-B1FC-62028CF639BC}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D797866-2A7E-2544-A095-39795CCDFDA9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$563</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$564</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10346" uniqueCount="2362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10355" uniqueCount="2362">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7896,7 +7896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R563"/>
+  <dimension ref="A1:R564"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23812,8 +23812,8 @@
       </c>
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A396">
-        <v>13300125</v>
+      <c r="A396" t="s">
+        <v>1032</v>
       </c>
       <c r="B396" t="s">
         <v>66</v>
@@ -23831,33 +23831,33 @@
         <v>1033</v>
       </c>
       <c r="G396" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H396" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J396">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J396" t="s">
+        <v>98</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M396">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>1038</v>
+      <c r="A397">
+        <v>13300125</v>
       </c>
       <c r="B397" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C397" t="s">
         <v>978</v>
@@ -23869,33 +23869,33 @@
         <v>57</v>
       </c>
       <c r="F397" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G397" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H397" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J397" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J397">
+        <v>2025</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M397">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398">
-        <v>24003025</v>
+      <c r="A398" t="s">
+        <v>1038</v>
       </c>
       <c r="B398" t="s">
         <v>55</v>
@@ -23904,7 +23904,7 @@
         <v>978</v>
       </c>
       <c r="D398" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E398" t="s">
         <v>57</v>
@@ -23913,16 +23913,13 @@
         <v>58</v>
       </c>
       <c r="G398" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H398" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I398" t="s">
-        <v>69</v>
-      </c>
-      <c r="J398">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J398" t="s">
+        <v>339</v>
       </c>
       <c r="K398">
         <v>75</v>
@@ -23930,13 +23927,16 @@
       <c r="L398">
         <v>6.2</v>
       </c>
+      <c r="M398">
+        <v>0</v>
+      </c>
       <c r="P398" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>1044</v>
+      <c r="A399">
+        <v>24003025</v>
       </c>
       <c r="B399" t="s">
         <v>55</v>
@@ -23945,39 +23945,39 @@
         <v>978</v>
       </c>
       <c r="D399" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E399" t="s">
         <v>57</v>
       </c>
       <c r="F399" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G399" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H399" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J399" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I399" t="s">
+        <v>69</v>
+      </c>
+      <c r="J399">
+        <v>2025</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>7.55</v>
-      </c>
-      <c r="M399">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P399" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B400" t="s">
         <v>55</v>
@@ -23986,28 +23986,28 @@
         <v>978</v>
       </c>
       <c r="D400" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E400" t="s">
         <v>57</v>
       </c>
       <c r="F400" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G400" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H400" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J400" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M400">
         <v>0</v>
@@ -24018,7 +24018,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B401" t="s">
         <v>55</v>
@@ -24027,28 +24027,28 @@
         <v>978</v>
       </c>
       <c r="D401" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E401" t="s">
         <v>57</v>
       </c>
       <c r="F401" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G401" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H401" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J401" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M401">
         <v>0</v>
@@ -24059,7 +24059,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B402" t="s">
         <v>55</v>
@@ -24068,42 +24068,39 @@
         <v>978</v>
       </c>
       <c r="D402" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E402" t="s">
         <v>57</v>
       </c>
       <c r="F402" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G402" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H402" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I402" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J402" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M402">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P402" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A403">
-        <v>27701225</v>
+      <c r="A403" t="s">
+        <v>1053</v>
       </c>
       <c r="B403" t="s">
         <v>55</v>
@@ -24112,39 +24109,42 @@
         <v>978</v>
       </c>
       <c r="D403" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E403" t="s">
         <v>57</v>
       </c>
       <c r="F403" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G403" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H403" t="s">
         <v>1055</v>
       </c>
-      <c r="J403">
-        <v>2025</v>
+      <c r="I403" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J403" t="s">
+        <v>286</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M403">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A404" t="s">
-        <v>1060</v>
+      <c r="A404">
+        <v>27701225</v>
       </c>
       <c r="B404" t="s">
         <v>55</v>
@@ -24153,28 +24153,28 @@
         <v>978</v>
       </c>
       <c r="D404" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E404" t="s">
         <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G404" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H404" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J404" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J404">
+        <v>2025</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M404">
         <v>0</v>
@@ -24185,7 +24185,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B405" t="s">
         <v>55</v>
@@ -24194,28 +24194,28 @@
         <v>978</v>
       </c>
       <c r="D405" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E405" t="s">
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G405" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H405" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J405" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M405">
         <v>0</v>
@@ -24226,7 +24226,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B406" t="s">
         <v>55</v>
@@ -24241,22 +24241,22 @@
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G406" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H406" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J406" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M406">
         <v>0</v>
@@ -24266,8 +24266,8 @@
       </c>
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A407">
-        <v>68002225</v>
+      <c r="A407" t="s">
+        <v>1065</v>
       </c>
       <c r="B407" t="s">
         <v>55</v>
@@ -24279,13 +24279,13 @@
         <v>1057</v>
       </c>
       <c r="E407" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F407" t="s">
         <v>1066</v>
       </c>
       <c r="G407" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H407" t="s">
         <v>1068</v>
@@ -24297,7 +24297,7 @@
         <v>75</v>
       </c>
       <c r="L407">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M407">
         <v>0</v>
@@ -24308,7 +24308,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B408" t="s">
         <v>55</v>
@@ -24323,13 +24323,13 @@
         <v>63</v>
       </c>
       <c r="F408" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G408" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H408" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J408" t="s">
         <v>339</v>
@@ -24338,7 +24338,7 @@
         <v>75</v>
       </c>
       <c r="L408">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M408">
         <v>0</v>
@@ -24349,7 +24349,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B409" t="s">
         <v>55</v>
@@ -24367,13 +24367,13 @@
         <v>1070</v>
       </c>
       <c r="G409" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H409" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J409">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J409" t="s">
+        <v>339</v>
       </c>
       <c r="K409">
         <v>75</v>
@@ -24389,8 +24389,8 @@
       </c>
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A410" t="s">
-        <v>1075</v>
+      <c r="A410">
+        <v>68002424</v>
       </c>
       <c r="B410" t="s">
         <v>55</v>
@@ -24408,19 +24408,19 @@
         <v>1070</v>
       </c>
       <c r="G410" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H410" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J410" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J410">
+        <v>2024</v>
       </c>
       <c r="K410">
         <v>75</v>
       </c>
       <c r="L410">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M410">
         <v>0</v>
@@ -24430,8 +24430,8 @@
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A411">
-        <v>68002623</v>
+      <c r="A411" t="s">
+        <v>1075</v>
       </c>
       <c r="B411" t="s">
         <v>55</v>
@@ -24446,25 +24446,22 @@
         <v>63</v>
       </c>
       <c r="F411" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G411" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H411" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I411" t="s">
-        <v>69</v>
-      </c>
-      <c r="J411">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J411" t="s">
+        <v>564</v>
       </c>
       <c r="K411">
         <v>75</v>
       </c>
       <c r="L411">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M411">
         <v>0</v>
@@ -24475,7 +24472,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B412" t="s">
         <v>55</v>
@@ -24487,28 +24484,28 @@
         <v>1057</v>
       </c>
       <c r="E412" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F412" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G412" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H412" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I412" t="s">
         <v>69</v>
       </c>
       <c r="J412">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M412">
         <v>0</v>
@@ -24518,8 +24515,8 @@
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A413" t="s">
-        <v>1083</v>
+      <c r="A413">
+        <v>68002825</v>
       </c>
       <c r="B413" t="s">
         <v>55</v>
@@ -24534,22 +24531,25 @@
         <v>57</v>
       </c>
       <c r="F413" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G413" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H413" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J413" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I413" t="s">
+        <v>69</v>
+      </c>
+      <c r="J413">
+        <v>2025</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M413">
         <v>0</v>
@@ -24559,8 +24559,8 @@
       </c>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A414">
-        <v>68003025</v>
+      <c r="A414" t="s">
+        <v>1083</v>
       </c>
       <c r="B414" t="s">
         <v>55</v>
@@ -24572,13 +24572,13 @@
         <v>1057</v>
       </c>
       <c r="E414" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F414" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G414" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H414" t="s">
         <v>1085</v>
@@ -24601,7 +24601,7 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B415" t="s">
         <v>55</v>
@@ -24619,10 +24619,10 @@
         <v>1078</v>
       </c>
       <c r="G415" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H415" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J415" t="s">
         <v>339</v>
@@ -24631,7 +24631,7 @@
         <v>75</v>
       </c>
       <c r="L415">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M415">
         <v>0</v>
@@ -24641,8 +24641,8 @@
       </c>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
-        <v>1089</v>
+      <c r="A416">
+        <v>680031225</v>
       </c>
       <c r="B416" t="s">
         <v>55</v>
@@ -24654,25 +24654,25 @@
         <v>1057</v>
       </c>
       <c r="E416" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F416" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G416" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H416" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J416" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M416">
         <v>0</v>
@@ -24683,10 +24683,10 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B417" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C417" t="s">
         <v>978</v>
@@ -24701,22 +24701,22 @@
         <v>1066</v>
       </c>
       <c r="G417" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H417" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J417">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J417" t="s">
+        <v>98</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M417">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P417" s="19">
         <v>46155</v>
@@ -24724,7 +24724,7 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B418" t="s">
         <v>66</v>
@@ -24733,31 +24733,31 @@
         <v>978</v>
       </c>
       <c r="D418" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E418" t="s">
         <v>57</v>
       </c>
       <c r="F418" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G418" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H418" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J418" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J418">
+        <v>2025</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M418">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
@@ -24765,7 +24765,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24783,22 +24783,22 @@
         <v>1033</v>
       </c>
       <c r="G419" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H419" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J419">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J419" t="s">
+        <v>98</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M419">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
@@ -24806,7 +24806,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24821,22 +24821,25 @@
         <v>57</v>
       </c>
       <c r="F420" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G420" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H420" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J420" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J420">
+        <v>2025</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M420">
+        <v>264</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24844,7 +24847,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24859,104 +24862,101 @@
         <v>57</v>
       </c>
       <c r="F421" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G421" t="s">
         <v>1100</v>
       </c>
       <c r="H421" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J421" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A422">
-        <v>53800623</v>
+      <c r="A422" t="s">
+        <v>1102</v>
       </c>
       <c r="B422" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C422" t="s">
         <v>978</v>
       </c>
       <c r="D422" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E422" t="s">
         <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G422" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H422" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J422" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>11</v>
-      </c>
-      <c r="M422">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A423" t="s">
-        <v>1107</v>
+      <c r="A423">
+        <v>53800623</v>
       </c>
       <c r="B423" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C423" t="s">
         <v>978</v>
       </c>
       <c r="D423" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E423" t="s">
         <v>57</v>
       </c>
       <c r="F423" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G423" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H423" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J423" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K423">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L423">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M423">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
@@ -24964,7 +24964,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B424" t="s">
         <v>66</v>
@@ -24982,22 +24982,22 @@
         <v>980</v>
       </c>
       <c r="G424" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H424" t="s">
-        <v>985</v>
-      </c>
-      <c r="J424">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J424" t="s">
+        <v>564</v>
       </c>
       <c r="K424">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L424">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M424">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P424" s="19">
         <v>46155</v>
@@ -25005,7 +25005,7 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B425" t="s">
         <v>66</v>
@@ -25014,75 +25014,72 @@
         <v>978</v>
       </c>
       <c r="D425" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E425" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F425" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G425" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H425" t="s">
-        <v>989</v>
-      </c>
-      <c r="J425" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J425">
+        <v>2025</v>
       </c>
       <c r="K425">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L425">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M425">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P425" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A426">
-        <v>71501125</v>
+      <c r="A426" t="s">
+        <v>1111</v>
       </c>
       <c r="B426" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C426" t="s">
         <v>978</v>
       </c>
       <c r="D426" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E426" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F426" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G426" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H426" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I426" t="s">
-        <v>69</v>
-      </c>
-      <c r="J426">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J426" t="s">
+        <v>564</v>
       </c>
       <c r="K426">
         <v>75</v>
       </c>
       <c r="L426">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M426">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
@@ -25090,7 +25087,7 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B427" t="s">
         <v>55</v>
@@ -25102,17 +25099,20 @@
         <v>979</v>
       </c>
       <c r="E427" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F427" t="s">
         <v>980</v>
       </c>
       <c r="G427" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H427" t="s">
         <v>1113</v>
       </c>
+      <c r="I427" t="s">
+        <v>69</v>
+      </c>
       <c r="J427">
         <v>2025</v>
       </c>
@@ -25120,7 +25120,7 @@
         <v>75</v>
       </c>
       <c r="L427">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M427">
         <v>324</v>
@@ -25131,7 +25131,7 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B428" t="s">
         <v>55</v>
@@ -25149,7 +25149,7 @@
         <v>980</v>
       </c>
       <c r="G428" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H428" t="s">
         <v>1113</v>
@@ -25172,7 +25172,7 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B429" t="s">
         <v>55</v>
@@ -25187,10 +25187,10 @@
         <v>63</v>
       </c>
       <c r="F429" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G429" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H429" t="s">
         <v>1113</v>
@@ -25213,7 +25213,7 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25225,13 +25225,13 @@
         <v>979</v>
       </c>
       <c r="E430" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F430" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G430" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H430" t="s">
         <v>1113</v>
@@ -25254,7 +25254,7 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25269,10 +25269,10 @@
         <v>57</v>
       </c>
       <c r="F431" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G431" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H431" t="s">
         <v>1113</v>
@@ -25295,7 +25295,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25307,13 +25307,13 @@
         <v>979</v>
       </c>
       <c r="E432" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G432" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H432" t="s">
         <v>1113</v>
@@ -25325,7 +25325,7 @@
         <v>75</v>
       </c>
       <c r="L432">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M432">
         <v>324</v>
@@ -25336,7 +25336,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25351,7 +25351,7 @@
         <v>63</v>
       </c>
       <c r="F433" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G433" t="s">
         <v>1120</v>
@@ -25366,7 +25366,7 @@
         <v>75</v>
       </c>
       <c r="L433">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M433">
         <v>324</v>
@@ -25377,7 +25377,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25392,7 +25392,7 @@
         <v>63</v>
       </c>
       <c r="F434" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G434" t="s">
         <v>1120</v>
@@ -25400,9 +25400,6 @@
       <c r="H434" t="s">
         <v>1113</v>
       </c>
-      <c r="I434" t="s">
-        <v>69</v>
-      </c>
       <c r="J434">
         <v>2025</v>
       </c>
@@ -25421,7 +25418,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25433,10 +25430,10 @@
         <v>979</v>
       </c>
       <c r="E435" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F435" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G435" t="s">
         <v>1120</v>
@@ -25445,7 +25442,7 @@
         <v>1113</v>
       </c>
       <c r="I435" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J435">
         <v>2025</v>
@@ -25454,7 +25451,7 @@
         <v>75</v>
       </c>
       <c r="L435">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M435">
         <v>324</v>
@@ -25465,7 +25462,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25480,7 +25477,7 @@
         <v>57</v>
       </c>
       <c r="F436" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G436" t="s">
         <v>1120</v>
@@ -25498,7 +25495,7 @@
         <v>75</v>
       </c>
       <c r="L436">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M436">
         <v>324</v>
@@ -25509,10 +25506,10 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B437" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C437" t="s">
         <v>978</v>
@@ -25521,16 +25518,19 @@
         <v>979</v>
       </c>
       <c r="E437" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F437" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G437" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H437" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I437" t="s">
+        <v>175</v>
       </c>
       <c r="J437">
         <v>2025</v>
@@ -25539,7 +25539,7 @@
         <v>75</v>
       </c>
       <c r="L437">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M437">
         <v>324</v>
@@ -25549,8 +25549,8 @@
       </c>
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A438" t="s">
-        <v>1125</v>
+      <c r="A438">
+        <v>16000125</v>
       </c>
       <c r="B438" t="s">
         <v>66</v>
@@ -25568,22 +25568,22 @@
         <v>980</v>
       </c>
       <c r="G438" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H438" t="s">
-        <v>985</v>
-      </c>
-      <c r="J438" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J438">
+        <v>2025</v>
       </c>
       <c r="K438">
         <v>75</v>
       </c>
       <c r="L438">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M438">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P438" s="19">
         <v>46155</v>
@@ -25591,7 +25591,7 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B439" t="s">
         <v>66</v>
@@ -25609,22 +25609,22 @@
         <v>980</v>
       </c>
       <c r="G439" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H439" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J439" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K439">
         <v>75</v>
       </c>
       <c r="L439">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M439">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P439" s="19">
         <v>46155</v>
@@ -25632,7 +25632,7 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B440" t="s">
         <v>66</v>
@@ -25650,22 +25650,22 @@
         <v>980</v>
       </c>
       <c r="G440" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H440" t="s">
-        <v>985</v>
-      </c>
-      <c r="J440">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J440" t="s">
+        <v>286</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M440">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P440" s="19">
         <v>46155</v>
@@ -25673,7 +25673,7 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B441" t="s">
         <v>66</v>
@@ -25688,25 +25688,25 @@
         <v>63</v>
       </c>
       <c r="F441" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G441" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H441" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J441" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J441">
+        <v>2025</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M441">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P441" s="19">
         <v>46155</v>
@@ -25714,7 +25714,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B442" t="s">
         <v>66</v>
@@ -25729,25 +25729,25 @@
         <v>63</v>
       </c>
       <c r="F442" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G442" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H442" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J442" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M442">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P442" s="19">
         <v>46155</v>
@@ -25755,7 +25755,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B443" t="s">
         <v>66</v>
@@ -25773,22 +25773,22 @@
         <v>980</v>
       </c>
       <c r="G443" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H443" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J443" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M443">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P443" s="19">
         <v>46155</v>
@@ -25796,7 +25796,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B444" t="s">
         <v>66</v>
@@ -25814,25 +25814,22 @@
         <v>980</v>
       </c>
       <c r="G444" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H444" t="s">
-        <v>982</v>
-      </c>
-      <c r="I444" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J444" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M444">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P444" s="19">
         <v>46155</v>
@@ -25840,7 +25837,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B445" t="s">
         <v>66</v>
@@ -25858,13 +25855,13 @@
         <v>980</v>
       </c>
       <c r="G445" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H445" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I445" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J445" t="s">
         <v>61</v>
@@ -25873,10 +25870,10 @@
         <v>75</v>
       </c>
       <c r="L445">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M445">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P445" s="19">
         <v>46155</v>
@@ -25884,7 +25881,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B446" t="s">
         <v>66</v>
@@ -25899,25 +25896,28 @@
         <v>63</v>
       </c>
       <c r="F446" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G446" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H446" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I446" t="s">
+        <v>1012</v>
       </c>
       <c r="J446" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K446">
         <v>75</v>
       </c>
       <c r="L446">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M446">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P446" s="19">
         <v>46155</v>
@@ -25925,7 +25925,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B447" t="s">
         <v>66</v>
@@ -25934,19 +25934,19 @@
         <v>978</v>
       </c>
       <c r="D447" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E447" t="s">
         <v>63</v>
       </c>
       <c r="F447" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G447" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H447" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J447" t="s">
         <v>217</v>
@@ -25955,10 +25955,10 @@
         <v>75</v>
       </c>
       <c r="L447">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M447">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P447" s="19">
         <v>46155</v>
@@ -25966,7 +25966,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B448" t="s">
         <v>66</v>
@@ -25981,25 +25981,25 @@
         <v>63</v>
       </c>
       <c r="F448" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G448" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H448" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J448" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M448">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26007,7 +26007,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26025,22 +26025,22 @@
         <v>1147</v>
       </c>
       <c r="G449" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H449" t="s">
         <v>1149</v>
       </c>
       <c r="J449" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M449">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26048,37 +26048,40 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B450" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C450" t="s">
         <v>978</v>
       </c>
       <c r="D450" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E450" t="s">
         <v>63</v>
       </c>
       <c r="F450" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G450" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H450" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J450" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M450">
+        <v>36</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26086,7 +26089,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B451" t="s">
         <v>55</v>
@@ -26101,25 +26104,22 @@
         <v>63</v>
       </c>
       <c r="F451" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G451" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H451" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J451" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>12.5</v>
-      </c>
-      <c r="M451">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26127,7 +26127,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B452" t="s">
         <v>55</v>
@@ -26142,22 +26142,22 @@
         <v>63</v>
       </c>
       <c r="F452" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G452" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H452" t="s">
         <v>1064</v>
       </c>
       <c r="J452" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M452">
         <v>0</v>
@@ -26168,7 +26168,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B453" t="s">
         <v>55</v>
@@ -26186,19 +26186,19 @@
         <v>1078</v>
       </c>
       <c r="G453" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H453" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J453">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J453" t="s">
+        <v>209</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M453">
         <v>0</v>
@@ -26209,10 +26209,10 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B454" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C454" t="s">
         <v>978</v>
@@ -26224,25 +26224,25 @@
         <v>63</v>
       </c>
       <c r="F454" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G454" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H454" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J454" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J454">
+        <v>2014</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M454">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
@@ -26250,10 +26250,10 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B455" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C455" t="s">
         <v>978</v>
@@ -26268,13 +26268,10 @@
         <v>1066</v>
       </c>
       <c r="G455" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H455" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I455" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J455" t="s">
         <v>61</v>
@@ -26283,18 +26280,18 @@
         <v>75</v>
       </c>
       <c r="L455">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M455">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A456">
-        <v>27701324</v>
+      <c r="A456" t="s">
+        <v>1164</v>
       </c>
       <c r="B456" t="s">
         <v>55</v>
@@ -26312,19 +26309,22 @@
         <v>1066</v>
       </c>
       <c r="G456" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H456" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J456">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I456" t="s">
+        <v>69</v>
+      </c>
+      <c r="J456" t="s">
+        <v>61</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M456">
         <v>0</v>
@@ -26334,8 +26334,8 @@
       </c>
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A457" t="s">
-        <v>1167</v>
+      <c r="A457">
+        <v>27701324</v>
       </c>
       <c r="B457" t="s">
         <v>55</v>
@@ -26353,22 +26353,19 @@
         <v>1066</v>
       </c>
       <c r="G457" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H457" t="s">
         <v>1055</v>
       </c>
-      <c r="I457" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J457" t="s">
-        <v>98</v>
+      <c r="J457">
+        <v>2024</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M457">
         <v>0</v>
@@ -26379,31 +26376,31 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B458" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C458" t="s">
         <v>978</v>
       </c>
       <c r="D458" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E458" t="s">
         <v>63</v>
       </c>
       <c r="F458" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G458" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H458" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I458" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J458" t="s">
         <v>98</v>
@@ -26412,10 +26409,10 @@
         <v>75</v>
       </c>
       <c r="L458">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M458">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P458" s="19">
         <v>46155</v>
@@ -26423,7 +26420,7 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B459" t="s">
         <v>66</v>
@@ -26438,28 +26435,28 @@
         <v>63</v>
       </c>
       <c r="F459" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G459" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H459" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I459" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J459" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M459">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P459" s="19">
         <v>46155</v>
@@ -26467,10 +26464,10 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B460" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C460" t="s">
         <v>978</v>
@@ -26482,25 +26479,28 @@
         <v>63</v>
       </c>
       <c r="F460" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G460" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H460" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I460" t="s">
+        <v>69</v>
       </c>
       <c r="J460" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M460">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P460" s="19">
         <v>46155</v>
@@ -26508,7 +26508,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B461" t="s">
         <v>55</v>
@@ -26526,19 +26526,22 @@
         <v>1175</v>
       </c>
       <c r="G461" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H461" t="s">
         <v>1177</v>
       </c>
       <c r="J461" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K461">
         <v>75</v>
       </c>
       <c r="L461">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M461">
+        <v>0</v>
       </c>
       <c r="P461" s="19">
         <v>46155</v>
@@ -26546,10 +26549,10 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B462" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C462" t="s">
         <v>978</v>
@@ -26561,28 +26564,22 @@
         <v>63</v>
       </c>
       <c r="F462" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G462" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H462" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I462" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J462" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K462">
         <v>75</v>
       </c>
       <c r="L462">
-        <v>7.6</v>
-      </c>
-      <c r="M462">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P462" s="19">
         <v>46155</v>
@@ -26590,10 +26587,10 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B463" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C463" t="s">
         <v>978</v>
@@ -26605,25 +26602,28 @@
         <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G463" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H463" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I463" t="s">
+        <v>69</v>
       </c>
       <c r="J463" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K463">
         <v>75</v>
       </c>
       <c r="L463">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M463">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P463" s="19">
         <v>46155</v>
@@ -26631,7 +26631,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26649,22 +26649,22 @@
         <v>1185</v>
       </c>
       <c r="G464" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H464" t="s">
         <v>1049</v>
       </c>
       <c r="J464" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K464">
         <v>75</v>
       </c>
       <c r="L464">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M464">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P464" s="19">
         <v>46155</v>
@@ -26672,10 +26672,10 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B465" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C465" t="s">
         <v>978</v>
@@ -26687,25 +26687,25 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G465" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H465" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I465" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J465" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K465">
         <v>75</v>
       </c>
       <c r="L465">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M465">
+        <v>6</v>
       </c>
       <c r="P465" s="19">
         <v>46155</v>
@@ -26713,7 +26713,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B466" t="s">
         <v>66</v>
@@ -26728,25 +26728,25 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G466" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H466" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I466" t="s">
+        <v>777</v>
       </c>
       <c r="J466" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M466">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P466" s="19">
         <v>46155</v>
@@ -26754,7 +26754,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B467" t="s">
         <v>66</v>
@@ -26769,25 +26769,25 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G467" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H467" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I467" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J467" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M467">
+        <v>53</v>
       </c>
       <c r="P467" s="19">
         <v>46155</v>
@@ -26795,7 +26795,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B468" t="s">
         <v>66</v>
@@ -26810,28 +26810,25 @@
         <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G468" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H468" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I468" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J468" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>6.5</v>
-      </c>
-      <c r="M468">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26839,10 +26836,10 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B469" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C469" t="s">
         <v>978</v>
@@ -26857,30 +26854,33 @@
         <v>1122</v>
       </c>
       <c r="G469" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H469" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I469" t="s">
+        <v>175</v>
       </c>
       <c r="J469" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M469">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A470">
-        <v>16003124</v>
+      <c r="A470" t="s">
+        <v>1202</v>
       </c>
       <c r="B470" t="s">
         <v>55</v>
@@ -26892,19 +26892,19 @@
         <v>979</v>
       </c>
       <c r="E470" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F470" t="s">
         <v>1122</v>
       </c>
       <c r="G470" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H470" t="s">
         <v>1204</v>
       </c>
       <c r="J470" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K470">
         <v>75</v>
@@ -26920,11 +26920,11 @@
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A471" t="s">
-        <v>1206</v>
+      <c r="A471">
+        <v>16003124</v>
       </c>
       <c r="B471" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C471" t="s">
         <v>978</v>
@@ -26933,31 +26933,28 @@
         <v>979</v>
       </c>
       <c r="E471" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F471" t="s">
         <v>1122</v>
       </c>
       <c r="G471" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H471" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I471" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J471" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M471">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -26965,10 +26962,10 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B472" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C472" t="s">
         <v>978</v>
@@ -26983,25 +26980,25 @@
         <v>1122</v>
       </c>
       <c r="G472" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H472" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I472" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J472" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M472">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27009,10 +27006,10 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B473" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C473" t="s">
         <v>978</v>
@@ -27027,13 +27024,13 @@
         <v>1122</v>
       </c>
       <c r="G473" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H473" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I473" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J473" t="s">
         <v>61</v>
@@ -27042,7 +27039,7 @@
         <v>75</v>
       </c>
       <c r="L473">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M473">
         <v>171</v>
@@ -27053,10 +27050,10 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B474" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C474" t="s">
         <v>978</v>
@@ -27071,19 +27068,25 @@
         <v>1122</v>
       </c>
       <c r="G474" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H474" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I474" t="s">
+        <v>175</v>
       </c>
       <c r="J474" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M474">
+        <v>171</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27091,10 +27094,10 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B475" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C475" t="s">
         <v>978</v>
@@ -27106,28 +27109,22 @@
         <v>63</v>
       </c>
       <c r="F475" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G475" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H475" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I475" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J475" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>24.08</v>
-      </c>
-      <c r="M475">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27135,10 +27132,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B476" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C476" t="s">
         <v>978</v>
@@ -27150,19 +27147,28 @@
         <v>63</v>
       </c>
       <c r="F476" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G476" t="s">
+        <v>1216</v>
       </c>
       <c r="H476" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I476" t="s">
+        <v>175</v>
       </c>
       <c r="J476" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M476">
+        <v>12</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27170,10 +27176,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B477" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C477" t="s">
         <v>978</v>
@@ -27185,30 +27191,27 @@
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H477" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J477" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>7.05</v>
-      </c>
-      <c r="M477">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A478">
-        <v>27100523</v>
+      <c r="A478" t="s">
+        <v>1221</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27223,36 +27226,33 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G478" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H478" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I478" t="s">
-        <v>777</v>
-      </c>
-      <c r="J478">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J478" t="s">
+        <v>217</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M478">
+        <v>30</v>
       </c>
       <c r="P478" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A479" t="s">
-        <v>1225</v>
+      <c r="A479">
+        <v>27100523</v>
       </c>
       <c r="B479" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C479" t="s">
         <v>978</v>
@@ -27264,33 +27264,36 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G479" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H479" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J479" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I479" t="s">
+        <v>777</v>
+      </c>
+      <c r="J479">
+        <v>2023</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P479" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B480" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C480" t="s">
         <v>978</v>
@@ -27302,33 +27305,33 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G480" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H480" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J480" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>7.35</v>
-      </c>
-      <c r="M480">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="481" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>1229</v>
+      </c>
       <c r="B481" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C481" t="s">
         <v>978</v>
@@ -27343,19 +27346,19 @@
         <v>1119</v>
       </c>
       <c r="G481" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H481" t="s">
         <v>1231</v>
       </c>
       <c r="J481" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K481">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L481">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M481">
         <v>2215</v>
@@ -27364,12 +27367,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="482" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A482" t="s">
-        <v>1233</v>
-      </c>
+    <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B482" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
@@ -27384,30 +27384,30 @@
         <v>1119</v>
       </c>
       <c r="G482" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H482" t="s">
         <v>1231</v>
       </c>
-      <c r="J482">
-        <v>2023</v>
+      <c r="J482" t="s">
+        <v>61</v>
       </c>
       <c r="K482">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L482">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M482">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="483" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B483" t="s">
         <v>66</v>
@@ -27425,36 +27425,33 @@
         <v>1119</v>
       </c>
       <c r="G483" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H483" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I483" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J483" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J483">
+        <v>2023</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M483">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="484" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B484" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C484" t="s">
         <v>978</v>
@@ -27469,27 +27466,33 @@
         <v>1119</v>
       </c>
       <c r="G484" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H484" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I484" t="s">
+        <v>1238</v>
       </c>
       <c r="J484" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M484">
+        <v>205</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="485" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B485" t="s">
         <v>55</v>
@@ -27507,10 +27510,10 @@
         <v>1119</v>
       </c>
       <c r="G485" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H485" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J485" t="s">
         <v>98</v>
@@ -27519,21 +27522,18 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>14.6</v>
-      </c>
-      <c r="M485">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="486" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A486">
-        <v>43700124</v>
+    <row r="486" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>1242</v>
       </c>
       <c r="B486" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C486" t="s">
         <v>978</v>
@@ -27545,33 +27545,36 @@
         <v>63</v>
       </c>
       <c r="F486" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G486" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H486" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J486">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J486" t="s">
+        <v>98</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M486">
+        <v>0</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="487" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B487" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27586,27 +27589,27 @@
         <v>1028</v>
       </c>
       <c r="G487" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H487" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J487">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="488" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B488" t="s">
         <v>55</v>
@@ -27624,30 +27627,30 @@
         <v>1028</v>
       </c>
       <c r="G488" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H488" t="s">
         <v>1031</v>
       </c>
       <c r="J488">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="489" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A489" t="s">
-        <v>1247</v>
+    <row r="489" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>43700524</v>
       </c>
       <c r="B489" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C489" t="s">
         <v>978</v>
@@ -27656,36 +27659,33 @@
         <v>979</v>
       </c>
       <c r="E489" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F489" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G489" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H489" t="s">
-        <v>982</v>
-      </c>
-      <c r="J489" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J489">
+        <v>2024</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>3.8</v>
-      </c>
-      <c r="M489">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="490" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B490" t="s">
         <v>66</v>
@@ -27703,30 +27703,30 @@
         <v>980</v>
       </c>
       <c r="G490" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H490" t="s">
-        <v>985</v>
-      </c>
-      <c r="J490">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J490" t="s">
+        <v>98</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M490">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="491" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B491" t="s">
         <v>66</v>
@@ -27744,10 +27744,10 @@
         <v>980</v>
       </c>
       <c r="G491" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H491" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J491">
         <v>2025</v>
@@ -27756,21 +27756,21 @@
         <v>75</v>
       </c>
       <c r="L491">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M491">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="492" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B492" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C492" t="s">
         <v>978</v>
@@ -27785,33 +27785,33 @@
         <v>980</v>
       </c>
       <c r="G492" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H492" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J492" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J492">
+        <v>2025</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M492">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="493" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B493" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27826,30 +27826,30 @@
         <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H493" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J493" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K493">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L493">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M493">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="494" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B494" t="s">
         <v>66</v>
@@ -27867,71 +27867,71 @@
         <v>980</v>
       </c>
       <c r="G494" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H494" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J494" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K494">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L494">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M494">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="495" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B495" t="s">
         <v>66</v>
       </c>
       <c r="C495" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D495" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E495" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F495" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G495" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H495" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J495" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K495">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L495">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M495">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="496" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B496" t="s">
         <v>66</v>
@@ -27946,13 +27946,13 @@
         <v>57</v>
       </c>
       <c r="F496" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G496" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H496" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J496" t="s">
         <v>339</v>
@@ -27961,21 +27961,18 @@
         <v>75</v>
       </c>
       <c r="L496">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M496">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
       </c>
-      <c r="R496" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A497">
-        <v>24000925</v>
+    </row>
+    <row r="497" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A497" t="s">
+        <v>1262</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -27987,36 +27984,39 @@
         <v>1258</v>
       </c>
       <c r="E497" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F497" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G497" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H497" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J497">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J497" t="s">
+        <v>339</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M497">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
       </c>
-    </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A498" t="s">
-        <v>1266</v>
+      <c r="R497" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="498" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A498">
+        <v>24000925</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28028,36 +28028,36 @@
         <v>1258</v>
       </c>
       <c r="E498" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F498" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G498" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H498" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J498" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J498">
+        <v>2025</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M498">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28072,33 +28072,33 @@
         <v>63</v>
       </c>
       <c r="F499" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G499" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H499" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J499" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M499">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A500">
-        <v>24001825</v>
+    <row r="500" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A500" t="s">
+        <v>1270</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28113,33 +28113,33 @@
         <v>63</v>
       </c>
       <c r="F500" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G500" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H500" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J500">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J500" t="s">
+        <v>98</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M500">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A501" t="s">
-        <v>1275</v>
+    <row r="501" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A501">
+        <v>24001825</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28154,30 +28154,33 @@
         <v>63</v>
       </c>
       <c r="F501" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G501" t="s">
+        <v>1274</v>
       </c>
       <c r="H501" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J501" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J501">
+        <v>2025</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M501">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B502" t="s">
         <v>66</v>
@@ -28192,36 +28195,30 @@
         <v>63</v>
       </c>
       <c r="F502" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G502" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H502" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I502" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J502" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M502">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B503" t="s">
         <v>66</v>
@@ -28230,36 +28227,42 @@
         <v>1257</v>
       </c>
       <c r="D503" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E503" t="s">
         <v>63</v>
       </c>
       <c r="F503" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G503" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H503" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I503" t="s">
+        <v>69</v>
       </c>
       <c r="J503" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M503">
+        <v>318</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B504" t="s">
         <v>66</v>
@@ -28277,30 +28280,27 @@
         <v>1284</v>
       </c>
       <c r="G504" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H504" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J504" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>6.1</v>
-      </c>
-      <c r="M504">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B505" t="s">
         <v>66</v>
@@ -28323,8 +28323,8 @@
       <c r="H505" t="s">
         <v>1289</v>
       </c>
-      <c r="J505">
-        <v>2024</v>
+      <c r="J505" t="s">
+        <v>87</v>
       </c>
       <c r="K505">
         <v>75</v>
@@ -28332,16 +28332,19 @@
       <c r="L505">
         <v>6.1</v>
       </c>
+      <c r="M505">
+        <v>133</v>
+      </c>
       <c r="P505" s="19">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="506" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B506" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C506" t="s">
         <v>1257</v>
@@ -28356,30 +28359,27 @@
         <v>1284</v>
       </c>
       <c r="G506" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H506" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J506" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J506">
+        <v>2024</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>13.2</v>
-      </c>
-      <c r="M506">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P506" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="507" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B507" t="s">
         <v>55</v>
@@ -28397,19 +28397,19 @@
         <v>1284</v>
       </c>
       <c r="G507" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H507" t="s">
         <v>1293</v>
       </c>
       <c r="J507" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M507">
         <v>0</v>
@@ -28418,9 +28418,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B508" t="s">
         <v>55</v>
@@ -28435,22 +28435,22 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G508" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H508" t="s">
         <v>1293</v>
       </c>
       <c r="J508" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M508">
         <v>0</v>
@@ -28459,50 +28459,50 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A509">
-        <v>10702526</v>
+    <row r="509" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A509" t="s">
+        <v>1296</v>
       </c>
       <c r="B509" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C509" t="s">
         <v>1257</v>
       </c>
       <c r="D509" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E509" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G509" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H509" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J509">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J509" t="s">
+        <v>61</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M509">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P509" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A510" t="s">
-        <v>1301</v>
+    <row r="510" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A510">
+        <v>10702526</v>
       </c>
       <c r="B510" t="s">
         <v>66</v>
@@ -28511,39 +28511,39 @@
         <v>1257</v>
       </c>
       <c r="D510" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E510" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F510" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G510" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H510" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J510" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J510">
+        <v>2026</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M510">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B511" t="s">
         <v>66</v>
@@ -28561,7 +28561,7 @@
         <v>1303</v>
       </c>
       <c r="G511" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H511" t="s">
         <v>1305</v>
@@ -28573,18 +28573,18 @@
         <v>75</v>
       </c>
       <c r="L511">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M511">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P511" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B512" t="s">
         <v>66</v>
@@ -28602,7 +28602,7 @@
         <v>1303</v>
       </c>
       <c r="G512" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H512" t="s">
         <v>1305</v>
@@ -28617,7 +28617,7 @@
         <v>8.6</v>
       </c>
       <c r="M512">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
@@ -28625,7 +28625,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28643,13 +28643,13 @@
         <v>1303</v>
       </c>
       <c r="G513" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H513" t="s">
         <v>1305</v>
       </c>
       <c r="J513" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K513">
         <v>75</v>
@@ -28658,7 +28658,7 @@
         <v>8.6</v>
       </c>
       <c r="M513">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28666,7 +28666,7 @@
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28684,7 +28684,7 @@
         <v>1303</v>
       </c>
       <c r="G514" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H514" t="s">
         <v>1305</v>
@@ -28699,7 +28699,7 @@
         <v>8.6</v>
       </c>
       <c r="M514">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28707,7 +28707,7 @@
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28725,22 +28725,22 @@
         <v>1303</v>
       </c>
       <c r="G515" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H515" t="s">
         <v>1305</v>
       </c>
       <c r="J515" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K515">
         <v>75</v>
       </c>
       <c r="L515">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M515">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28748,7 +28748,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28766,22 +28766,22 @@
         <v>1303</v>
       </c>
       <c r="G516" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H516" t="s">
         <v>1305</v>
       </c>
-      <c r="J516">
-        <v>2021</v>
+      <c r="J516" t="s">
+        <v>127</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M516">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28789,7 +28789,7 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B517" t="s">
         <v>66</v>
@@ -28807,13 +28807,13 @@
         <v>1303</v>
       </c>
       <c r="G517" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H517" t="s">
         <v>1305</v>
       </c>
-      <c r="J517" t="s">
-        <v>109</v>
+      <c r="J517">
+        <v>2021</v>
       </c>
       <c r="K517">
         <v>75</v>
@@ -28822,7 +28822,7 @@
         <v>13</v>
       </c>
       <c r="M517">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28830,7 +28830,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B518" t="s">
         <v>66</v>
@@ -28848,7 +28848,7 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H518" t="s">
         <v>1305</v>
@@ -28860,7 +28860,7 @@
         <v>75</v>
       </c>
       <c r="L518">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M518">
         <v>36</v>
@@ -28871,7 +28871,7 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B519" t="s">
         <v>66</v>
@@ -28883,28 +28883,28 @@
         <v>1302</v>
       </c>
       <c r="E519" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F519" t="s">
         <v>1303</v>
       </c>
       <c r="G519" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H519" t="s">
         <v>1305</v>
       </c>
       <c r="J519" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M519">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -28912,40 +28912,40 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
       </c>
       <c r="C520" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D520" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E520" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F520" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G520" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H520" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J520" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M520">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -28953,7 +28953,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -28961,17 +28961,20 @@
       <c r="C521" t="s">
         <v>1323</v>
       </c>
+      <c r="D521" t="s">
+        <v>1258</v>
+      </c>
       <c r="E521" t="s">
         <v>1323</v>
       </c>
       <c r="F521" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G521" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H521" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J521" t="s">
         <v>564</v>
@@ -28982,13 +28985,16 @@
       <c r="L521">
         <v>6.2</v>
       </c>
+      <c r="M521">
+        <v>4411</v>
+      </c>
       <c r="P521" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29003,10 +29009,10 @@
         <v>58</v>
       </c>
       <c r="G522" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H522" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J522" t="s">
         <v>564</v>
@@ -29015,7 +29021,7 @@
         <v>75</v>
       </c>
       <c r="L522">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29023,7 +29029,7 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29035,25 +29041,22 @@
         <v>1323</v>
       </c>
       <c r="F523" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G523" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H523" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J523" t="s">
         <v>564</v>
       </c>
       <c r="K523">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L523">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M523">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29061,7 +29064,7 @@
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29076,22 +29079,22 @@
         <v>1332</v>
       </c>
       <c r="G524" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H524" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J524" t="s">
         <v>564</v>
       </c>
       <c r="K524">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L524">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M524">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29099,7 +29102,7 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29114,10 +29117,10 @@
         <v>1332</v>
       </c>
       <c r="G525" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H525" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J525" t="s">
         <v>564</v>
@@ -29126,10 +29129,10 @@
         <v>75</v>
       </c>
       <c r="L525">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M525">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29137,10 +29140,10 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B526" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C526" t="s">
         <v>1323</v>
@@ -29152,10 +29155,10 @@
         <v>1332</v>
       </c>
       <c r="G526" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H526" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J526" t="s">
         <v>564</v>
@@ -29164,7 +29167,10 @@
         <v>75</v>
       </c>
       <c r="L526">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M526">
+        <v>418</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29172,10 +29178,10 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B527" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C527" t="s">
         <v>1323</v>
@@ -29187,10 +29193,10 @@
         <v>1332</v>
       </c>
       <c r="G527" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H527" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J527" t="s">
         <v>564</v>
@@ -29199,10 +29205,7 @@
         <v>75</v>
       </c>
       <c r="L527">
-        <v>25.8</v>
-      </c>
-      <c r="M527">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29210,7 +29213,7 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29225,10 +29228,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H528" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29237,10 +29240,10 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M528">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29248,7 +29251,7 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29263,10 +29266,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H529" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29275,10 +29278,10 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M529">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29286,7 +29289,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29301,10 +29304,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H530" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29313,10 +29316,10 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M530">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29324,10 +29327,10 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B531" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C531" t="s">
         <v>1323</v>
@@ -29339,7 +29342,7 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H531" t="s">
         <v>1349</v>
@@ -29348,10 +29351,10 @@
         <v>564</v>
       </c>
       <c r="K531">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L531">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M531">
         <v>60</v>
@@ -29362,7 +29365,7 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B532" t="s">
         <v>55</v>
@@ -29377,7 +29380,7 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H532" t="s">
         <v>1349</v>
@@ -29386,10 +29389,10 @@
         <v>564</v>
       </c>
       <c r="K532">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L532">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M532">
         <v>60</v>
@@ -29400,7 +29403,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B533" t="s">
         <v>55</v>
@@ -29415,7 +29418,7 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H533" t="s">
         <v>1349</v>
@@ -29427,7 +29430,7 @@
         <v>75</v>
       </c>
       <c r="L533">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M533">
         <v>60</v>
@@ -29438,10 +29441,10 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B534" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C534" t="s">
         <v>1323</v>
@@ -29453,10 +29456,10 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H534" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J534" t="s">
         <v>564</v>
@@ -29465,10 +29468,10 @@
         <v>75</v>
       </c>
       <c r="L534">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M534">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29476,7 +29479,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29491,10 +29494,10 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H535" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J535" t="s">
         <v>564</v>
@@ -29503,10 +29506,10 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M535">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29514,7 +29517,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29529,10 +29532,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H536" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29541,10 +29544,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M536">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29552,7 +29555,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29567,10 +29570,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H537" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29579,10 +29582,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M537">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29590,7 +29593,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29605,10 +29608,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H538" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29617,10 +29620,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M538">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29628,10 +29631,10 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B539" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C539" t="s">
         <v>1323</v>
@@ -29643,10 +29646,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H539" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29655,7 +29658,7 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M539">
         <v>0</v>
@@ -29666,10 +29669,10 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B540" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C540" t="s">
         <v>1323</v>
@@ -29681,10 +29684,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H540" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29693,10 +29696,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M540">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29704,7 +29707,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29719,7 +29722,7 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H541" t="s">
         <v>1352</v>
@@ -29731,10 +29734,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M541">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29742,7 +29745,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29757,10 +29760,10 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H542" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J542" t="s">
         <v>564</v>
@@ -29769,10 +29772,10 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M542">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29780,7 +29783,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29795,10 +29798,10 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H543" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J543" t="s">
         <v>564</v>
@@ -29818,7 +29821,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29833,22 +29836,22 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H544" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J544" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K544">
         <v>75</v>
       </c>
       <c r="L544">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M544">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29856,7 +29859,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29871,22 +29874,22 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H545" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J545">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J545" t="s">
+        <v>167</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M545">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29894,7 +29897,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29902,9 +29905,6 @@
       <c r="C546" t="s">
         <v>1323</v>
       </c>
-      <c r="D546" t="s">
-        <v>1008</v>
-      </c>
       <c r="E546" t="s">
         <v>1323</v>
       </c>
@@ -29912,22 +29912,22 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H546" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J546" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J546">
+        <v>2017</v>
       </c>
       <c r="K546">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L546">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M546">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29935,7 +29935,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29953,7 +29953,7 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H547" t="s">
         <v>1352</v>
@@ -29965,10 +29965,10 @@
         <v>150</v>
       </c>
       <c r="L547">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M547">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29976,10 +29976,10 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B548" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C548" t="s">
         <v>1323</v>
@@ -29994,10 +29994,10 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H548" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J548" t="s">
         <v>564</v>
@@ -30006,10 +30006,10 @@
         <v>150</v>
       </c>
       <c r="L548">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M548">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30017,7 +30017,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B549" t="s">
         <v>55</v>
@@ -30035,7 +30035,7 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H549" t="s">
         <v>1334</v>
@@ -30044,10 +30044,10 @@
         <v>564</v>
       </c>
       <c r="K549">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L549">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M549">
         <v>5</v>
@@ -30058,7 +30058,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B550" t="s">
         <v>55</v>
@@ -30076,7 +30076,7 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H550" t="s">
         <v>1334</v>
@@ -30085,10 +30085,10 @@
         <v>564</v>
       </c>
       <c r="K550">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L550">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M550">
         <v>5</v>
@@ -30099,37 +30099,40 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B551" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C551" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D551" t="s">
+        <v>1008</v>
       </c>
       <c r="E551" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F551" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G551" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H551" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J551" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K551">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L551">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M551">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30137,7 +30140,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30152,7 +30155,7 @@
         <v>1406</v>
       </c>
       <c r="G552" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H552" t="s">
         <v>1408</v>
@@ -30164,7 +30167,7 @@
         <v>70</v>
       </c>
       <c r="L552">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M552">
         <v>6</v>
@@ -30175,7 +30178,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30190,19 +30193,22 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H553" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J553" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K553">
         <v>70</v>
       </c>
       <c r="L553">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M553">
+        <v>6</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30210,7 +30216,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30225,19 +30231,19 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H554" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J554" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30245,7 +30251,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30260,19 +30266,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H555" t="s">
         <v>1418</v>
       </c>
       <c r="J555" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30280,7 +30286,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30295,19 +30301,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H556" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J556" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30315,7 +30321,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30323,9 +30329,6 @@
       <c r="C557" t="s">
         <v>1405</v>
       </c>
-      <c r="D557" t="s">
-        <v>1008</v>
-      </c>
       <c r="E557" t="s">
         <v>1405</v>
       </c>
@@ -30333,19 +30336,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H557" t="s">
         <v>1425</v>
       </c>
       <c r="J557" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K557">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L557">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30353,7 +30356,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30361,26 +30364,29 @@
       <c r="C558" t="s">
         <v>1405</v>
       </c>
+      <c r="D558" t="s">
+        <v>1008</v>
+      </c>
       <c r="E558" t="s">
         <v>1405</v>
       </c>
       <c r="F558" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G558" t="s">
+        <v>1428</v>
       </c>
       <c r="H558" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J558" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K558">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L558">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M558">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30388,10 +30394,10 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B559" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C559" t="s">
         <v>1405</v>
@@ -30402,17 +30408,17 @@
       <c r="F559" t="s">
         <v>1431</v>
       </c>
-      <c r="G559" t="s">
-        <v>1435</v>
-      </c>
       <c r="H559" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J559" t="s">
+        <v>1433</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M559">
         <v>45</v>
@@ -30423,10 +30429,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B560" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C560" t="s">
         <v>1405</v>
@@ -30438,22 +30444,19 @@
         <v>1431</v>
       </c>
       <c r="G560" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H560" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J560" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M560">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30461,7 +30464,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30476,22 +30479,22 @@
         <v>1431</v>
       </c>
       <c r="G561" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H561" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J561" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M561">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30499,7 +30502,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30511,25 +30514,25 @@
         <v>1405</v>
       </c>
       <c r="F562" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G562" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H562" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J562" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M562">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30537,7 +30540,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30552,7 +30555,7 @@
         <v>1445</v>
       </c>
       <c r="G563" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H563" t="s">
         <v>1447</v>
@@ -30564,17 +30567,55 @@
         <v>70</v>
       </c>
       <c r="L563">
+        <v>36.5</v>
+      </c>
+      <c r="M563">
+        <v>7</v>
+      </c>
+      <c r="P563" s="19">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A564" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B564" t="s">
+        <v>66</v>
+      </c>
+      <c r="C564" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E564" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F564" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G564" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H564" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J564" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K564">
+        <v>70</v>
+      </c>
+      <c r="L564">
         <v>40.5</v>
       </c>
-      <c r="M563">
+      <c r="M564">
         <v>5</v>
       </c>
-      <c r="P563" s="19">
+      <c r="P564" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R563" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R564" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="171" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D797866-2A7E-2544-A095-39795CCDFDA9}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B157939-DB6D-364E-A316-F911F53C5909}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$564</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$565</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10355" uniqueCount="2362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10360" uniqueCount="2364">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7131,6 +7131,12 @@
   </si>
   <si>
     <t>Mézardières - Grolleau</t>
+  </si>
+  <si>
+    <t>Domaine Saint-Aubin</t>
+  </si>
+  <si>
+    <t>Petit Manseng - moelleux</t>
   </si>
 </sst>
 </file>
@@ -7896,7 +7902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R564"/>
+  <dimension ref="A1:R565"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23771,11 +23777,11 @@
       </c>
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
-        <v>1032</v>
+      <c r="A395">
+        <v>73300125</v>
       </c>
       <c r="B395" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C395" t="s">
         <v>978</v>
@@ -23790,33 +23796,33 @@
         <v>1033</v>
       </c>
       <c r="G395" t="s">
-        <v>1034</v>
+        <v>113</v>
       </c>
       <c r="H395" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J395" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J395">
+        <v>2025</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M395">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P395" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A396" t="s">
-        <v>1032</v>
+      <c r="A396">
+        <v>73300325</v>
       </c>
       <c r="B396" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C396" t="s">
         <v>978</v>
@@ -23831,30 +23837,30 @@
         <v>1033</v>
       </c>
       <c r="G396" t="s">
-        <v>1034</v>
+        <v>2363</v>
       </c>
       <c r="H396" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J396" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J396">
+        <v>2025</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>3.95</v>
+        <v>5.59</v>
       </c>
       <c r="M396">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A397">
-        <v>13300125</v>
+      <c r="A397" t="s">
+        <v>1032</v>
       </c>
       <c r="B397" t="s">
         <v>66</v>
@@ -23872,33 +23878,33 @@
         <v>1033</v>
       </c>
       <c r="G397" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H397" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J397">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J397" t="s">
+        <v>98</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M397">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
-        <v>1038</v>
+      <c r="A398">
+        <v>13300125</v>
       </c>
       <c r="B398" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C398" t="s">
         <v>978</v>
@@ -23910,33 +23916,33 @@
         <v>57</v>
       </c>
       <c r="F398" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G398" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H398" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J398" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J398">
+        <v>2025</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M398">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399">
-        <v>24003025</v>
+      <c r="A399" t="s">
+        <v>1038</v>
       </c>
       <c r="B399" t="s">
         <v>55</v>
@@ -23945,7 +23951,7 @@
         <v>978</v>
       </c>
       <c r="D399" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E399" t="s">
         <v>57</v>
@@ -23954,16 +23960,13 @@
         <v>58</v>
       </c>
       <c r="G399" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H399" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I399" t="s">
-        <v>69</v>
-      </c>
-      <c r="J399">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J399" t="s">
+        <v>339</v>
       </c>
       <c r="K399">
         <v>75</v>
@@ -23971,13 +23974,16 @@
       <c r="L399">
         <v>6.2</v>
       </c>
+      <c r="M399">
+        <v>0</v>
+      </c>
       <c r="P399" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>1044</v>
+      <c r="A400">
+        <v>24003025</v>
       </c>
       <c r="B400" t="s">
         <v>55</v>
@@ -23986,39 +23992,39 @@
         <v>978</v>
       </c>
       <c r="D400" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E400" t="s">
         <v>57</v>
       </c>
       <c r="F400" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G400" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H400" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J400" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I400" t="s">
+        <v>69</v>
+      </c>
+      <c r="J400">
+        <v>2025</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>7.55</v>
-      </c>
-      <c r="M400">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P400" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B401" t="s">
         <v>55</v>
@@ -24027,28 +24033,28 @@
         <v>978</v>
       </c>
       <c r="D401" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E401" t="s">
         <v>57</v>
       </c>
       <c r="F401" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G401" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H401" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J401" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M401">
         <v>0</v>
@@ -24059,7 +24065,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B402" t="s">
         <v>55</v>
@@ -24068,28 +24074,28 @@
         <v>978</v>
       </c>
       <c r="D402" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E402" t="s">
         <v>57</v>
       </c>
       <c r="F402" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G402" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H402" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J402" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M402">
         <v>0</v>
@@ -24100,7 +24106,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B403" t="s">
         <v>55</v>
@@ -24109,42 +24115,39 @@
         <v>978</v>
       </c>
       <c r="D403" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E403" t="s">
         <v>57</v>
       </c>
       <c r="F403" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G403" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H403" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I403" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J403" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M403">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A404">
-        <v>27701225</v>
+      <c r="A404" t="s">
+        <v>1053</v>
       </c>
       <c r="B404" t="s">
         <v>55</v>
@@ -24153,39 +24156,42 @@
         <v>978</v>
       </c>
       <c r="D404" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E404" t="s">
         <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G404" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H404" t="s">
         <v>1055</v>
       </c>
-      <c r="J404">
-        <v>2025</v>
+      <c r="I404" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J404" t="s">
+        <v>286</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M404">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A405" t="s">
-        <v>1060</v>
+      <c r="A405">
+        <v>27701225</v>
       </c>
       <c r="B405" t="s">
         <v>55</v>
@@ -24194,28 +24200,28 @@
         <v>978</v>
       </c>
       <c r="D405" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E405" t="s">
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G405" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H405" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J405" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J405">
+        <v>2025</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M405">
         <v>0</v>
@@ -24226,7 +24232,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B406" t="s">
         <v>55</v>
@@ -24235,28 +24241,28 @@
         <v>978</v>
       </c>
       <c r="D406" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E406" t="s">
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G406" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H406" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J406" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M406">
         <v>0</v>
@@ -24267,7 +24273,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B407" t="s">
         <v>55</v>
@@ -24282,22 +24288,22 @@
         <v>57</v>
       </c>
       <c r="F407" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G407" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H407" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J407" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M407">
         <v>0</v>
@@ -24307,8 +24313,8 @@
       </c>
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A408">
-        <v>68002225</v>
+      <c r="A408" t="s">
+        <v>1065</v>
       </c>
       <c r="B408" t="s">
         <v>55</v>
@@ -24320,13 +24326,13 @@
         <v>1057</v>
       </c>
       <c r="E408" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F408" t="s">
         <v>1066</v>
       </c>
       <c r="G408" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H408" t="s">
         <v>1068</v>
@@ -24338,7 +24344,7 @@
         <v>75</v>
       </c>
       <c r="L408">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M408">
         <v>0</v>
@@ -24349,7 +24355,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B409" t="s">
         <v>55</v>
@@ -24364,13 +24370,13 @@
         <v>63</v>
       </c>
       <c r="F409" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G409" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H409" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J409" t="s">
         <v>339</v>
@@ -24379,7 +24385,7 @@
         <v>75</v>
       </c>
       <c r="L409">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24390,7 +24396,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B410" t="s">
         <v>55</v>
@@ -24408,13 +24414,13 @@
         <v>1070</v>
       </c>
       <c r="G410" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H410" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J410">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J410" t="s">
+        <v>339</v>
       </c>
       <c r="K410">
         <v>75</v>
@@ -24430,8 +24436,8 @@
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A411" t="s">
-        <v>1075</v>
+      <c r="A411">
+        <v>68002424</v>
       </c>
       <c r="B411" t="s">
         <v>55</v>
@@ -24449,19 +24455,19 @@
         <v>1070</v>
       </c>
       <c r="G411" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H411" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J411" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J411">
+        <v>2024</v>
       </c>
       <c r="K411">
         <v>75</v>
       </c>
       <c r="L411">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M411">
         <v>0</v>
@@ -24471,8 +24477,8 @@
       </c>
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A412">
-        <v>68002623</v>
+      <c r="A412" t="s">
+        <v>1075</v>
       </c>
       <c r="B412" t="s">
         <v>55</v>
@@ -24487,25 +24493,22 @@
         <v>63</v>
       </c>
       <c r="F412" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G412" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H412" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I412" t="s">
-        <v>69</v>
-      </c>
-      <c r="J412">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J412" t="s">
+        <v>564</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M412">
         <v>0</v>
@@ -24516,7 +24519,7 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B413" t="s">
         <v>55</v>
@@ -24528,28 +24531,28 @@
         <v>1057</v>
       </c>
       <c r="E413" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F413" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G413" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H413" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I413" t="s">
         <v>69</v>
       </c>
       <c r="J413">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M413">
         <v>0</v>
@@ -24559,8 +24562,8 @@
       </c>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A414" t="s">
-        <v>1083</v>
+      <c r="A414">
+        <v>68002825</v>
       </c>
       <c r="B414" t="s">
         <v>55</v>
@@ -24575,22 +24578,25 @@
         <v>57</v>
       </c>
       <c r="F414" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G414" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H414" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J414" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I414" t="s">
+        <v>69</v>
+      </c>
+      <c r="J414">
+        <v>2025</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M414">
         <v>0</v>
@@ -24600,8 +24606,8 @@
       </c>
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A415">
-        <v>68003025</v>
+      <c r="A415" t="s">
+        <v>1083</v>
       </c>
       <c r="B415" t="s">
         <v>55</v>
@@ -24613,13 +24619,13 @@
         <v>1057</v>
       </c>
       <c r="E415" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F415" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G415" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H415" t="s">
         <v>1085</v>
@@ -24642,7 +24648,7 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B416" t="s">
         <v>55</v>
@@ -24660,10 +24666,10 @@
         <v>1078</v>
       </c>
       <c r="G416" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H416" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J416" t="s">
         <v>339</v>
@@ -24672,7 +24678,7 @@
         <v>75</v>
       </c>
       <c r="L416">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M416">
         <v>0</v>
@@ -24682,8 +24688,8 @@
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A417" t="s">
-        <v>1089</v>
+      <c r="A417">
+        <v>680031225</v>
       </c>
       <c r="B417" t="s">
         <v>55</v>
@@ -24695,25 +24701,25 @@
         <v>1057</v>
       </c>
       <c r="E417" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F417" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G417" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H417" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J417" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M417">
         <v>0</v>
@@ -24724,10 +24730,10 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B418" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C418" t="s">
         <v>978</v>
@@ -24742,22 +24748,22 @@
         <v>1066</v>
       </c>
       <c r="G418" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H418" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J418">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J418" t="s">
+        <v>98</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M418">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
@@ -24765,7 +24771,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24774,31 +24780,31 @@
         <v>978</v>
       </c>
       <c r="D419" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E419" t="s">
         <v>57</v>
       </c>
       <c r="F419" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G419" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H419" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J419" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J419">
+        <v>2025</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M419">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
@@ -24806,7 +24812,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24824,22 +24830,22 @@
         <v>1033</v>
       </c>
       <c r="G420" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H420" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J420">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J420" t="s">
+        <v>98</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M420">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24847,7 +24853,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24862,22 +24868,25 @@
         <v>57</v>
       </c>
       <c r="F421" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G421" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H421" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J421" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J421">
+        <v>2025</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M421">
+        <v>264</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24885,7 +24894,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B422" t="s">
         <v>66</v>
@@ -24900,104 +24909,101 @@
         <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G422" t="s">
         <v>1100</v>
       </c>
       <c r="H422" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J422" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A423">
-        <v>53800623</v>
+      <c r="A423" t="s">
+        <v>1102</v>
       </c>
       <c r="B423" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C423" t="s">
         <v>978</v>
       </c>
       <c r="D423" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E423" t="s">
         <v>57</v>
       </c>
       <c r="F423" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G423" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H423" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J423" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K423">
         <v>75</v>
       </c>
       <c r="L423">
-        <v>11</v>
-      </c>
-      <c r="M423">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A424" t="s">
-        <v>1107</v>
+      <c r="A424">
+        <v>53800623</v>
       </c>
       <c r="B424" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C424" t="s">
         <v>978</v>
       </c>
       <c r="D424" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E424" t="s">
         <v>57</v>
       </c>
       <c r="F424" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G424" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H424" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J424" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K424">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L424">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M424">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P424" s="19">
         <v>46155</v>
@@ -25005,7 +25011,7 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B425" t="s">
         <v>66</v>
@@ -25023,22 +25029,22 @@
         <v>980</v>
       </c>
       <c r="G425" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H425" t="s">
-        <v>985</v>
-      </c>
-      <c r="J425">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J425" t="s">
+        <v>564</v>
       </c>
       <c r="K425">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L425">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M425">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P425" s="19">
         <v>46155</v>
@@ -25046,7 +25052,7 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B426" t="s">
         <v>66</v>
@@ -25055,75 +25061,72 @@
         <v>978</v>
       </c>
       <c r="D426" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E426" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F426" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G426" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H426" t="s">
-        <v>989</v>
-      </c>
-      <c r="J426" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J426">
+        <v>2025</v>
       </c>
       <c r="K426">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L426">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M426">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A427">
-        <v>71501125</v>
+      <c r="A427" t="s">
+        <v>1111</v>
       </c>
       <c r="B427" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C427" t="s">
         <v>978</v>
       </c>
       <c r="D427" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E427" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F427" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G427" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H427" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I427" t="s">
-        <v>69</v>
-      </c>
-      <c r="J427">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J427" t="s">
+        <v>564</v>
       </c>
       <c r="K427">
         <v>75</v>
       </c>
       <c r="L427">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M427">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
@@ -25131,7 +25134,7 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B428" t="s">
         <v>55</v>
@@ -25143,17 +25146,20 @@
         <v>979</v>
       </c>
       <c r="E428" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F428" t="s">
         <v>980</v>
       </c>
       <c r="G428" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H428" t="s">
         <v>1113</v>
       </c>
+      <c r="I428" t="s">
+        <v>69</v>
+      </c>
       <c r="J428">
         <v>2025</v>
       </c>
@@ -25161,7 +25167,7 @@
         <v>75</v>
       </c>
       <c r="L428">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M428">
         <v>324</v>
@@ -25172,7 +25178,7 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B429" t="s">
         <v>55</v>
@@ -25190,7 +25196,7 @@
         <v>980</v>
       </c>
       <c r="G429" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H429" t="s">
         <v>1113</v>
@@ -25213,7 +25219,7 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25228,10 +25234,10 @@
         <v>63</v>
       </c>
       <c r="F430" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G430" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H430" t="s">
         <v>1113</v>
@@ -25254,7 +25260,7 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25266,13 +25272,13 @@
         <v>979</v>
       </c>
       <c r="E431" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F431" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G431" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H431" t="s">
         <v>1113</v>
@@ -25295,7 +25301,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25310,10 +25316,10 @@
         <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G432" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H432" t="s">
         <v>1113</v>
@@ -25336,7 +25342,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25348,13 +25354,13 @@
         <v>979</v>
       </c>
       <c r="E433" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G433" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H433" t="s">
         <v>1113</v>
@@ -25366,7 +25372,7 @@
         <v>75</v>
       </c>
       <c r="L433">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M433">
         <v>324</v>
@@ -25377,7 +25383,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25392,7 +25398,7 @@
         <v>63</v>
       </c>
       <c r="F434" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G434" t="s">
         <v>1120</v>
@@ -25407,7 +25413,7 @@
         <v>75</v>
       </c>
       <c r="L434">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M434">
         <v>324</v>
@@ -25418,7 +25424,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25433,7 +25439,7 @@
         <v>63</v>
       </c>
       <c r="F435" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G435" t="s">
         <v>1120</v>
@@ -25441,9 +25447,6 @@
       <c r="H435" t="s">
         <v>1113</v>
       </c>
-      <c r="I435" t="s">
-        <v>69</v>
-      </c>
       <c r="J435">
         <v>2025</v>
       </c>
@@ -25462,7 +25465,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25474,10 +25477,10 @@
         <v>979</v>
       </c>
       <c r="E436" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F436" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G436" t="s">
         <v>1120</v>
@@ -25486,7 +25489,7 @@
         <v>1113</v>
       </c>
       <c r="I436" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J436">
         <v>2025</v>
@@ -25495,7 +25498,7 @@
         <v>75</v>
       </c>
       <c r="L436">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M436">
         <v>324</v>
@@ -25506,7 +25509,7 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25521,7 +25524,7 @@
         <v>57</v>
       </c>
       <c r="F437" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G437" t="s">
         <v>1120</v>
@@ -25539,7 +25542,7 @@
         <v>75</v>
       </c>
       <c r="L437">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M437">
         <v>324</v>
@@ -25550,10 +25553,10 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B438" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C438" t="s">
         <v>978</v>
@@ -25562,16 +25565,19 @@
         <v>979</v>
       </c>
       <c r="E438" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F438" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G438" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H438" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I438" t="s">
+        <v>175</v>
       </c>
       <c r="J438">
         <v>2025</v>
@@ -25580,7 +25586,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M438">
         <v>324</v>
@@ -25590,8 +25596,8 @@
       </c>
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A439" t="s">
-        <v>1125</v>
+      <c r="A439">
+        <v>16000125</v>
       </c>
       <c r="B439" t="s">
         <v>66</v>
@@ -25609,22 +25615,22 @@
         <v>980</v>
       </c>
       <c r="G439" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H439" t="s">
-        <v>985</v>
-      </c>
-      <c r="J439" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J439">
+        <v>2025</v>
       </c>
       <c r="K439">
         <v>75</v>
       </c>
       <c r="L439">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M439">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P439" s="19">
         <v>46155</v>
@@ -25632,7 +25638,7 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B440" t="s">
         <v>66</v>
@@ -25650,22 +25656,22 @@
         <v>980</v>
       </c>
       <c r="G440" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H440" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J440" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M440">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P440" s="19">
         <v>46155</v>
@@ -25673,7 +25679,7 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B441" t="s">
         <v>66</v>
@@ -25691,22 +25697,22 @@
         <v>980</v>
       </c>
       <c r="G441" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H441" t="s">
-        <v>985</v>
-      </c>
-      <c r="J441">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J441" t="s">
+        <v>286</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M441">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P441" s="19">
         <v>46155</v>
@@ -25714,7 +25720,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B442" t="s">
         <v>66</v>
@@ -25729,25 +25735,25 @@
         <v>63</v>
       </c>
       <c r="F442" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G442" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H442" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J442" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J442">
+        <v>2025</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M442">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P442" s="19">
         <v>46155</v>
@@ -25755,7 +25761,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B443" t="s">
         <v>66</v>
@@ -25770,25 +25776,25 @@
         <v>63</v>
       </c>
       <c r="F443" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G443" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H443" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J443" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M443">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P443" s="19">
         <v>46155</v>
@@ -25796,7 +25802,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B444" t="s">
         <v>66</v>
@@ -25814,22 +25820,22 @@
         <v>980</v>
       </c>
       <c r="G444" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H444" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J444" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M444">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P444" s="19">
         <v>46155</v>
@@ -25837,7 +25843,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B445" t="s">
         <v>66</v>
@@ -25855,25 +25861,22 @@
         <v>980</v>
       </c>
       <c r="G445" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H445" t="s">
-        <v>982</v>
-      </c>
-      <c r="I445" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J445" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K445">
         <v>75</v>
       </c>
       <c r="L445">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M445">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P445" s="19">
         <v>46155</v>
@@ -25881,7 +25884,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B446" t="s">
         <v>66</v>
@@ -25899,13 +25902,13 @@
         <v>980</v>
       </c>
       <c r="G446" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H446" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I446" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J446" t="s">
         <v>61</v>
@@ -25914,10 +25917,10 @@
         <v>75</v>
       </c>
       <c r="L446">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M446">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P446" s="19">
         <v>46155</v>
@@ -25925,7 +25928,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B447" t="s">
         <v>66</v>
@@ -25940,25 +25943,28 @@
         <v>63</v>
       </c>
       <c r="F447" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G447" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H447" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I447" t="s">
+        <v>1012</v>
       </c>
       <c r="J447" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K447">
         <v>75</v>
       </c>
       <c r="L447">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M447">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P447" s="19">
         <v>46155</v>
@@ -25966,7 +25972,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B448" t="s">
         <v>66</v>
@@ -25975,19 +25981,19 @@
         <v>978</v>
       </c>
       <c r="D448" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E448" t="s">
         <v>63</v>
       </c>
       <c r="F448" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G448" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H448" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J448" t="s">
         <v>217</v>
@@ -25996,10 +26002,10 @@
         <v>75</v>
       </c>
       <c r="L448">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M448">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26007,7 +26013,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26022,25 +26028,25 @@
         <v>63</v>
       </c>
       <c r="F449" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G449" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H449" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J449" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M449">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26048,7 +26054,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26066,22 +26072,22 @@
         <v>1147</v>
       </c>
       <c r="G450" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H450" t="s">
         <v>1149</v>
       </c>
       <c r="J450" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M450">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26089,37 +26095,40 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B451" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C451" t="s">
         <v>978</v>
       </c>
       <c r="D451" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E451" t="s">
         <v>63</v>
       </c>
       <c r="F451" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G451" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H451" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J451" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M451">
+        <v>36</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26127,7 +26136,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B452" t="s">
         <v>55</v>
@@ -26142,25 +26151,22 @@
         <v>63</v>
       </c>
       <c r="F452" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G452" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H452" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J452" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>12.5</v>
-      </c>
-      <c r="M452">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
@@ -26168,7 +26174,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B453" t="s">
         <v>55</v>
@@ -26183,22 +26189,22 @@
         <v>63</v>
       </c>
       <c r="F453" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G453" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H453" t="s">
         <v>1064</v>
       </c>
       <c r="J453" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M453">
         <v>0</v>
@@ -26209,7 +26215,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B454" t="s">
         <v>55</v>
@@ -26227,19 +26233,19 @@
         <v>1078</v>
       </c>
       <c r="G454" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H454" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J454">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J454" t="s">
+        <v>209</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M454">
         <v>0</v>
@@ -26250,10 +26256,10 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B455" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C455" t="s">
         <v>978</v>
@@ -26265,25 +26271,25 @@
         <v>63</v>
       </c>
       <c r="F455" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G455" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H455" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J455" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J455">
+        <v>2014</v>
       </c>
       <c r="K455">
         <v>75</v>
       </c>
       <c r="L455">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M455">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
@@ -26291,10 +26297,10 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B456" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C456" t="s">
         <v>978</v>
@@ -26309,13 +26315,10 @@
         <v>1066</v>
       </c>
       <c r="G456" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H456" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I456" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J456" t="s">
         <v>61</v>
@@ -26324,18 +26327,18 @@
         <v>75</v>
       </c>
       <c r="L456">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M456">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A457">
-        <v>27701324</v>
+      <c r="A457" t="s">
+        <v>1164</v>
       </c>
       <c r="B457" t="s">
         <v>55</v>
@@ -26353,19 +26356,22 @@
         <v>1066</v>
       </c>
       <c r="G457" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H457" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J457">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I457" t="s">
+        <v>69</v>
+      </c>
+      <c r="J457" t="s">
+        <v>61</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M457">
         <v>0</v>
@@ -26375,8 +26381,8 @@
       </c>
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A458" t="s">
-        <v>1167</v>
+      <c r="A458">
+        <v>27701324</v>
       </c>
       <c r="B458" t="s">
         <v>55</v>
@@ -26394,22 +26400,19 @@
         <v>1066</v>
       </c>
       <c r="G458" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H458" t="s">
         <v>1055</v>
       </c>
-      <c r="I458" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J458" t="s">
-        <v>98</v>
+      <c r="J458">
+        <v>2024</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -26420,31 +26423,31 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B459" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C459" t="s">
         <v>978</v>
       </c>
       <c r="D459" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E459" t="s">
         <v>63</v>
       </c>
       <c r="F459" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G459" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H459" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I459" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J459" t="s">
         <v>98</v>
@@ -26453,10 +26456,10 @@
         <v>75</v>
       </c>
       <c r="L459">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M459">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P459" s="19">
         <v>46155</v>
@@ -26464,7 +26467,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B460" t="s">
         <v>66</v>
@@ -26479,28 +26482,28 @@
         <v>63</v>
       </c>
       <c r="F460" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G460" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H460" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I460" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J460" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M460">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P460" s="19">
         <v>46155</v>
@@ -26508,10 +26511,10 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B461" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C461" t="s">
         <v>978</v>
@@ -26523,25 +26526,28 @@
         <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G461" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H461" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I461" t="s">
+        <v>69</v>
       </c>
       <c r="J461" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K461">
         <v>75</v>
       </c>
       <c r="L461">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M461">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P461" s="19">
         <v>46155</v>
@@ -26549,7 +26555,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B462" t="s">
         <v>55</v>
@@ -26567,19 +26573,22 @@
         <v>1175</v>
       </c>
       <c r="G462" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H462" t="s">
         <v>1177</v>
       </c>
       <c r="J462" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K462">
         <v>75</v>
       </c>
       <c r="L462">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M462">
+        <v>0</v>
       </c>
       <c r="P462" s="19">
         <v>46155</v>
@@ -26587,10 +26596,10 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B463" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C463" t="s">
         <v>978</v>
@@ -26602,28 +26611,22 @@
         <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G463" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H463" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I463" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J463" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K463">
         <v>75</v>
       </c>
       <c r="L463">
-        <v>7.6</v>
-      </c>
-      <c r="M463">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P463" s="19">
         <v>46155</v>
@@ -26631,10 +26634,10 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B464" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C464" t="s">
         <v>978</v>
@@ -26646,25 +26649,28 @@
         <v>63</v>
       </c>
       <c r="F464" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G464" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H464" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I464" t="s">
+        <v>69</v>
       </c>
       <c r="J464" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K464">
         <v>75</v>
       </c>
       <c r="L464">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M464">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P464" s="19">
         <v>46155</v>
@@ -26672,7 +26678,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B465" t="s">
         <v>55</v>
@@ -26690,22 +26696,22 @@
         <v>1185</v>
       </c>
       <c r="G465" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H465" t="s">
         <v>1049</v>
       </c>
       <c r="J465" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K465">
         <v>75</v>
       </c>
       <c r="L465">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M465">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P465" s="19">
         <v>46155</v>
@@ -26713,10 +26719,10 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B466" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C466" t="s">
         <v>978</v>
@@ -26728,25 +26734,25 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G466" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H466" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I466" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J466" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M466">
+        <v>6</v>
       </c>
       <c r="P466" s="19">
         <v>46155</v>
@@ -26754,7 +26760,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B467" t="s">
         <v>66</v>
@@ -26769,25 +26775,25 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G467" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H467" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I467" t="s">
+        <v>777</v>
       </c>
       <c r="J467" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M467">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P467" s="19">
         <v>46155</v>
@@ -26795,7 +26801,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B468" t="s">
         <v>66</v>
@@ -26810,25 +26816,25 @@
         <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G468" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H468" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I468" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J468" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M468">
+        <v>53</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26836,7 +26842,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B469" t="s">
         <v>66</v>
@@ -26851,28 +26857,25 @@
         <v>63</v>
       </c>
       <c r="F469" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G469" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H469" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I469" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J469" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>6.5</v>
-      </c>
-      <c r="M469">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
@@ -26880,10 +26883,10 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B470" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C470" t="s">
         <v>978</v>
@@ -26898,30 +26901,33 @@
         <v>1122</v>
       </c>
       <c r="G470" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H470" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I470" t="s">
+        <v>175</v>
       </c>
       <c r="J470" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M470">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A471">
-        <v>16003124</v>
+      <c r="A471" t="s">
+        <v>1202</v>
       </c>
       <c r="B471" t="s">
         <v>55</v>
@@ -26933,19 +26939,19 @@
         <v>979</v>
       </c>
       <c r="E471" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F471" t="s">
         <v>1122</v>
       </c>
       <c r="G471" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H471" t="s">
         <v>1204</v>
       </c>
       <c r="J471" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K471">
         <v>75</v>
@@ -26961,11 +26967,11 @@
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A472" t="s">
-        <v>1206</v>
+      <c r="A472">
+        <v>16003124</v>
       </c>
       <c r="B472" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C472" t="s">
         <v>978</v>
@@ -26974,31 +26980,28 @@
         <v>979</v>
       </c>
       <c r="E472" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F472" t="s">
         <v>1122</v>
       </c>
       <c r="G472" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H472" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I472" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J472" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M472">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27006,10 +27009,10 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B473" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C473" t="s">
         <v>978</v>
@@ -27024,25 +27027,25 @@
         <v>1122</v>
       </c>
       <c r="G473" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H473" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I473" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J473" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M473">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27050,10 +27053,10 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B474" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C474" t="s">
         <v>978</v>
@@ -27068,13 +27071,13 @@
         <v>1122</v>
       </c>
       <c r="G474" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H474" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I474" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J474" t="s">
         <v>61</v>
@@ -27083,7 +27086,7 @@
         <v>75</v>
       </c>
       <c r="L474">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M474">
         <v>171</v>
@@ -27094,10 +27097,10 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B475" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C475" t="s">
         <v>978</v>
@@ -27112,19 +27115,25 @@
         <v>1122</v>
       </c>
       <c r="G475" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H475" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I475" t="s">
+        <v>175</v>
       </c>
       <c r="J475" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M475">
+        <v>171</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27132,10 +27141,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B476" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C476" t="s">
         <v>978</v>
@@ -27147,28 +27156,22 @@
         <v>63</v>
       </c>
       <c r="F476" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G476" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H476" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I476" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J476" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>24.08</v>
-      </c>
-      <c r="M476">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27176,10 +27179,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B477" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C477" t="s">
         <v>978</v>
@@ -27191,19 +27194,28 @@
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G477" t="s">
+        <v>1216</v>
       </c>
       <c r="H477" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I477" t="s">
+        <v>175</v>
       </c>
       <c r="J477" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M477">
+        <v>12</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27211,10 +27223,10 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B478" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C478" t="s">
         <v>978</v>
@@ -27226,30 +27238,27 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H478" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J478" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>7.05</v>
-      </c>
-      <c r="M478">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A479">
-        <v>27100523</v>
+      <c r="A479" t="s">
+        <v>1221</v>
       </c>
       <c r="B479" t="s">
         <v>66</v>
@@ -27264,36 +27273,33 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G479" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H479" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I479" t="s">
-        <v>777</v>
-      </c>
-      <c r="J479">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J479" t="s">
+        <v>217</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M479">
+        <v>30</v>
       </c>
       <c r="P479" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A480" t="s">
-        <v>1225</v>
+      <c r="A480">
+        <v>27100523</v>
       </c>
       <c r="B480" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C480" t="s">
         <v>978</v>
@@ -27305,33 +27311,36 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G480" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H480" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J480" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I480" t="s">
+        <v>777</v>
+      </c>
+      <c r="J480">
+        <v>2023</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P480" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B481" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C481" t="s">
         <v>978</v>
@@ -27343,33 +27352,33 @@
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G481" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H481" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J481" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>7.35</v>
-      </c>
-      <c r="M481">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P481" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>1229</v>
+      </c>
       <c r="B482" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
@@ -27384,19 +27393,19 @@
         <v>1119</v>
       </c>
       <c r="G482" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H482" t="s">
         <v>1231</v>
       </c>
       <c r="J482" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K482">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L482">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M482">
         <v>2215</v>
@@ -27406,11 +27415,8 @@
       </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A483" t="s">
-        <v>1233</v>
-      </c>
       <c r="B483" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C483" t="s">
         <v>978</v>
@@ -27425,22 +27431,22 @@
         <v>1119</v>
       </c>
       <c r="G483" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H483" t="s">
         <v>1231</v>
       </c>
-      <c r="J483">
-        <v>2023</v>
+      <c r="J483" t="s">
+        <v>61</v>
       </c>
       <c r="K483">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L483">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M483">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
@@ -27448,7 +27454,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B484" t="s">
         <v>66</v>
@@ -27466,25 +27472,22 @@
         <v>1119</v>
       </c>
       <c r="G484" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H484" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I484" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J484" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J484">
+        <v>2023</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M484">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
@@ -27492,10 +27495,10 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B485" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C485" t="s">
         <v>978</v>
@@ -27510,19 +27513,25 @@
         <v>1119</v>
       </c>
       <c r="G485" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H485" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I485" t="s">
+        <v>1238</v>
       </c>
       <c r="J485" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K485">
         <v>75</v>
       </c>
       <c r="L485">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M485">
+        <v>205</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
@@ -27530,7 +27539,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B486" t="s">
         <v>55</v>
@@ -27548,10 +27557,10 @@
         <v>1119</v>
       </c>
       <c r="G486" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H486" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J486" t="s">
         <v>98</v>
@@ -27560,21 +27569,18 @@
         <v>75</v>
       </c>
       <c r="L486">
-        <v>14.6</v>
-      </c>
-      <c r="M486">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A487">
-        <v>43700124</v>
+      <c r="A487" t="s">
+        <v>1242</v>
       </c>
       <c r="B487" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27586,22 +27592,25 @@
         <v>63</v>
       </c>
       <c r="F487" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G487" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H487" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J487">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J487" t="s">
+        <v>98</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M487">
+        <v>0</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
@@ -27609,10 +27618,10 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B488" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C488" t="s">
         <v>978</v>
@@ -27627,19 +27636,19 @@
         <v>1028</v>
       </c>
       <c r="G488" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H488" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J488">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
@@ -27647,7 +27656,7 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B489" t="s">
         <v>55</v>
@@ -27665,30 +27674,30 @@
         <v>1028</v>
       </c>
       <c r="G489" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H489" t="s">
         <v>1031</v>
       </c>
       <c r="J489">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A490" t="s">
-        <v>1247</v>
+      <c r="A490">
+        <v>43700524</v>
       </c>
       <c r="B490" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C490" t="s">
         <v>978</v>
@@ -27697,28 +27706,25 @@
         <v>979</v>
       </c>
       <c r="E490" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F490" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G490" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H490" t="s">
-        <v>982</v>
-      </c>
-      <c r="J490" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J490">
+        <v>2024</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>3.8</v>
-      </c>
-      <c r="M490">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
@@ -27726,7 +27732,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B491" t="s">
         <v>66</v>
@@ -27744,22 +27750,22 @@
         <v>980</v>
       </c>
       <c r="G491" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H491" t="s">
-        <v>985</v>
-      </c>
-      <c r="J491">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J491" t="s">
+        <v>98</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M491">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27767,7 +27773,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B492" t="s">
         <v>66</v>
@@ -27785,10 +27791,10 @@
         <v>980</v>
       </c>
       <c r="G492" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H492" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J492">
         <v>2025</v>
@@ -27797,10 +27803,10 @@
         <v>75</v>
       </c>
       <c r="L492">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M492">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27808,10 +27814,10 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B493" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27826,22 +27832,22 @@
         <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H493" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J493" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J493">
+        <v>2025</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M493">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27849,10 +27855,10 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B494" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C494" t="s">
         <v>978</v>
@@ -27867,22 +27873,22 @@
         <v>980</v>
       </c>
       <c r="G494" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H494" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J494" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K494">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L494">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M494">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -27890,7 +27896,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B495" t="s">
         <v>66</v>
@@ -27908,22 +27914,22 @@
         <v>980</v>
       </c>
       <c r="G495" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H495" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J495" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K495">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L495">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M495">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -27931,40 +27937,40 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B496" t="s">
         <v>66</v>
       </c>
       <c r="C496" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D496" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E496" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F496" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G496" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H496" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J496" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K496">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L496">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M496">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -27972,7 +27978,7 @@
     </row>
     <row r="497" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -27987,13 +27993,13 @@
         <v>57</v>
       </c>
       <c r="F497" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G497" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H497" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J497" t="s">
         <v>339</v>
@@ -28002,21 +28008,18 @@
         <v>75</v>
       </c>
       <c r="L497">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M497">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
       </c>
-      <c r="R497" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="498" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A498">
-        <v>24000925</v>
+      <c r="A498" t="s">
+        <v>1262</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28028,36 +28031,39 @@
         <v>1258</v>
       </c>
       <c r="E498" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F498" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G498" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H498" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J498">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J498" t="s">
+        <v>339</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M498">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
       </c>
+      <c r="R498" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="499" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A499" t="s">
-        <v>1266</v>
+      <c r="A499">
+        <v>24000925</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28069,28 +28075,28 @@
         <v>1258</v>
       </c>
       <c r="E499" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F499" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G499" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H499" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J499" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J499">
+        <v>2025</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M499">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
@@ -28098,7 +28104,7 @@
     </row>
     <row r="500" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28113,33 +28119,33 @@
         <v>63</v>
       </c>
       <c r="F500" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G500" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H500" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J500" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M500">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A501">
-        <v>24001825</v>
+      <c r="A501" t="s">
+        <v>1270</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28154,33 +28160,33 @@
         <v>63</v>
       </c>
       <c r="F501" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G501" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H501" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J501">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J501" t="s">
+        <v>98</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M501">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A502" t="s">
-        <v>1275</v>
+      <c r="A502">
+        <v>24001825</v>
       </c>
       <c r="B502" t="s">
         <v>66</v>
@@ -28195,22 +28201,25 @@
         <v>63</v>
       </c>
       <c r="F502" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G502" t="s">
+        <v>1274</v>
       </c>
       <c r="H502" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J502" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J502">
+        <v>2025</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M502">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
@@ -28218,7 +28227,7 @@
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B503" t="s">
         <v>66</v>
@@ -28233,28 +28242,22 @@
         <v>63</v>
       </c>
       <c r="F503" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G503" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H503" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I503" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J503" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M503">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
@@ -28262,7 +28265,7 @@
     </row>
     <row r="504" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B504" t="s">
         <v>66</v>
@@ -28271,28 +28274,34 @@
         <v>1257</v>
       </c>
       <c r="D504" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E504" t="s">
         <v>63</v>
       </c>
       <c r="F504" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G504" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H504" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I504" t="s">
+        <v>69</v>
       </c>
       <c r="J504" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M504">
+        <v>318</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28300,7 +28309,7 @@
     </row>
     <row r="505" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B505" t="s">
         <v>66</v>
@@ -28318,22 +28327,19 @@
         <v>1284</v>
       </c>
       <c r="G505" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H505" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J505" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>6.1</v>
-      </c>
-      <c r="M505">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28341,7 +28347,7 @@
     </row>
     <row r="506" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B506" t="s">
         <v>66</v>
@@ -28364,8 +28370,8 @@
       <c r="H506" t="s">
         <v>1289</v>
       </c>
-      <c r="J506">
-        <v>2024</v>
+      <c r="J506" t="s">
+        <v>87</v>
       </c>
       <c r="K506">
         <v>75</v>
@@ -28373,16 +28379,19 @@
       <c r="L506">
         <v>6.1</v>
       </c>
+      <c r="M506">
+        <v>133</v>
+      </c>
       <c r="P506" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="507" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B507" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C507" t="s">
         <v>1257</v>
@@ -28397,30 +28406,27 @@
         <v>1284</v>
       </c>
       <c r="G507" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H507" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J507" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J507">
+        <v>2024</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>13.2</v>
-      </c>
-      <c r="M507">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P507" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="508" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B508" t="s">
         <v>55</v>
@@ -28438,19 +28444,19 @@
         <v>1284</v>
       </c>
       <c r="G508" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H508" t="s">
         <v>1293</v>
       </c>
       <c r="J508" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M508">
         <v>0</v>
@@ -28461,7 +28467,7 @@
     </row>
     <row r="509" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B509" t="s">
         <v>55</v>
@@ -28476,22 +28482,22 @@
         <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G509" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H509" t="s">
         <v>1293</v>
       </c>
       <c r="J509" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M509">
         <v>0</v>
@@ -28501,49 +28507,49 @@
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A510">
-        <v>10702526</v>
+      <c r="A510" t="s">
+        <v>1296</v>
       </c>
       <c r="B510" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C510" t="s">
         <v>1257</v>
       </c>
       <c r="D510" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E510" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G510" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H510" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J510">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J510" t="s">
+        <v>61</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M510">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A511" t="s">
-        <v>1301</v>
+      <c r="A511">
+        <v>10702526</v>
       </c>
       <c r="B511" t="s">
         <v>66</v>
@@ -28552,31 +28558,31 @@
         <v>1257</v>
       </c>
       <c r="D511" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E511" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F511" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G511" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H511" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J511" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J511">
+        <v>2026</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M511">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P511" s="19">
         <v>46155</v>
@@ -28584,7 +28590,7 @@
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B512" t="s">
         <v>66</v>
@@ -28602,7 +28608,7 @@
         <v>1303</v>
       </c>
       <c r="G512" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H512" t="s">
         <v>1305</v>
@@ -28614,10 +28620,10 @@
         <v>75</v>
       </c>
       <c r="L512">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M512">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
@@ -28625,7 +28631,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28643,7 +28649,7 @@
         <v>1303</v>
       </c>
       <c r="G513" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H513" t="s">
         <v>1305</v>
@@ -28658,7 +28664,7 @@
         <v>8.6</v>
       </c>
       <c r="M513">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28666,7 +28672,7 @@
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28684,13 +28690,13 @@
         <v>1303</v>
       </c>
       <c r="G514" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H514" t="s">
         <v>1305</v>
       </c>
       <c r="J514" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K514">
         <v>75</v>
@@ -28699,7 +28705,7 @@
         <v>8.6</v>
       </c>
       <c r="M514">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28707,7 +28713,7 @@
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28725,7 +28731,7 @@
         <v>1303</v>
       </c>
       <c r="G515" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H515" t="s">
         <v>1305</v>
@@ -28740,7 +28746,7 @@
         <v>8.6</v>
       </c>
       <c r="M515">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28748,7 +28754,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28766,22 +28772,22 @@
         <v>1303</v>
       </c>
       <c r="G516" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H516" t="s">
         <v>1305</v>
       </c>
       <c r="J516" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M516">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28789,7 +28795,7 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B517" t="s">
         <v>66</v>
@@ -28807,22 +28813,22 @@
         <v>1303</v>
       </c>
       <c r="G517" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H517" t="s">
         <v>1305</v>
       </c>
-      <c r="J517">
-        <v>2021</v>
+      <c r="J517" t="s">
+        <v>127</v>
       </c>
       <c r="K517">
         <v>75</v>
       </c>
       <c r="L517">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M517">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28830,7 +28836,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B518" t="s">
         <v>66</v>
@@ -28848,13 +28854,13 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H518" t="s">
         <v>1305</v>
       </c>
-      <c r="J518" t="s">
-        <v>109</v>
+      <c r="J518">
+        <v>2021</v>
       </c>
       <c r="K518">
         <v>75</v>
@@ -28863,7 +28869,7 @@
         <v>13</v>
       </c>
       <c r="M518">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
@@ -28871,7 +28877,7 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B519" t="s">
         <v>66</v>
@@ -28889,7 +28895,7 @@
         <v>1303</v>
       </c>
       <c r="G519" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H519" t="s">
         <v>1305</v>
@@ -28901,7 +28907,7 @@
         <v>75</v>
       </c>
       <c r="L519">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M519">
         <v>36</v>
@@ -28912,7 +28918,7 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
@@ -28924,28 +28930,28 @@
         <v>1302</v>
       </c>
       <c r="E520" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F520" t="s">
         <v>1303</v>
       </c>
       <c r="G520" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H520" t="s">
         <v>1305</v>
       </c>
       <c r="J520" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M520">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -28953,40 +28959,40 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
       </c>
       <c r="C521" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D521" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E521" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F521" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G521" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H521" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J521" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K521">
         <v>75</v>
       </c>
       <c r="L521">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M521">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
@@ -28994,7 +29000,7 @@
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29002,17 +29008,20 @@
       <c r="C522" t="s">
         <v>1323</v>
       </c>
+      <c r="D522" t="s">
+        <v>1258</v>
+      </c>
       <c r="E522" t="s">
         <v>1323</v>
       </c>
       <c r="F522" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G522" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H522" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J522" t="s">
         <v>564</v>
@@ -29023,13 +29032,16 @@
       <c r="L522">
         <v>6.2</v>
       </c>
+      <c r="M522">
+        <v>4411</v>
+      </c>
       <c r="P522" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29044,10 +29056,10 @@
         <v>58</v>
       </c>
       <c r="G523" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H523" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J523" t="s">
         <v>564</v>
@@ -29056,7 +29068,7 @@
         <v>75</v>
       </c>
       <c r="L523">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29064,7 +29076,7 @@
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29076,25 +29088,22 @@
         <v>1323</v>
       </c>
       <c r="F524" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G524" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H524" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J524" t="s">
         <v>564</v>
       </c>
       <c r="K524">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L524">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M524">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29102,7 +29111,7 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29117,22 +29126,22 @@
         <v>1332</v>
       </c>
       <c r="G525" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H525" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J525" t="s">
         <v>564</v>
       </c>
       <c r="K525">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L525">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M525">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29140,7 +29149,7 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
@@ -29155,10 +29164,10 @@
         <v>1332</v>
       </c>
       <c r="G526" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H526" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J526" t="s">
         <v>564</v>
@@ -29167,10 +29176,10 @@
         <v>75</v>
       </c>
       <c r="L526">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M526">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29178,10 +29187,10 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B527" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C527" t="s">
         <v>1323</v>
@@ -29193,10 +29202,10 @@
         <v>1332</v>
       </c>
       <c r="G527" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H527" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J527" t="s">
         <v>564</v>
@@ -29205,7 +29214,10 @@
         <v>75</v>
       </c>
       <c r="L527">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M527">
+        <v>418</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29213,10 +29225,10 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B528" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C528" t="s">
         <v>1323</v>
@@ -29228,10 +29240,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H528" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29240,10 +29252,7 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>25.8</v>
-      </c>
-      <c r="M528">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29251,7 +29260,7 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29266,10 +29275,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H529" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29278,10 +29287,10 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M529">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29289,7 +29298,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29304,10 +29313,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H530" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29316,10 +29325,10 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M530">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29327,7 +29336,7 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29342,10 +29351,10 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H531" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J531" t="s">
         <v>564</v>
@@ -29354,10 +29363,10 @@
         <v>75</v>
       </c>
       <c r="L531">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M531">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29365,10 +29374,10 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B532" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C532" t="s">
         <v>1323</v>
@@ -29380,7 +29389,7 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H532" t="s">
         <v>1349</v>
@@ -29389,10 +29398,10 @@
         <v>564</v>
       </c>
       <c r="K532">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L532">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M532">
         <v>60</v>
@@ -29403,7 +29412,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B533" t="s">
         <v>55</v>
@@ -29418,7 +29427,7 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H533" t="s">
         <v>1349</v>
@@ -29427,10 +29436,10 @@
         <v>564</v>
       </c>
       <c r="K533">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L533">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M533">
         <v>60</v>
@@ -29441,7 +29450,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B534" t="s">
         <v>55</v>
@@ -29456,7 +29465,7 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H534" t="s">
         <v>1349</v>
@@ -29468,7 +29477,7 @@
         <v>75</v>
       </c>
       <c r="L534">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M534">
         <v>60</v>
@@ -29479,10 +29488,10 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B535" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C535" t="s">
         <v>1323</v>
@@ -29494,10 +29503,10 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H535" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J535" t="s">
         <v>564</v>
@@ -29506,10 +29515,10 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M535">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29517,7 +29526,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29532,10 +29541,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H536" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29544,10 +29553,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M536">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29555,7 +29564,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29570,10 +29579,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H537" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29582,10 +29591,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M537">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29593,7 +29602,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29608,10 +29617,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H538" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29620,10 +29629,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M538">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29631,7 +29640,7 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B539" t="s">
         <v>66</v>
@@ -29646,10 +29655,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H539" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29658,10 +29667,10 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M539">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
@@ -29669,10 +29678,10 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B540" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C540" t="s">
         <v>1323</v>
@@ -29684,10 +29693,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H540" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29696,7 +29705,7 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -29707,10 +29716,10 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B541" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C541" t="s">
         <v>1323</v>
@@ -29722,10 +29731,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H541" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29734,10 +29743,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M541">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29745,7 +29754,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29760,7 +29769,7 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H542" t="s">
         <v>1352</v>
@@ -29772,10 +29781,10 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M542">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29783,7 +29792,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29798,10 +29807,10 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H543" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J543" t="s">
         <v>564</v>
@@ -29810,10 +29819,10 @@
         <v>75</v>
       </c>
       <c r="L543">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M543">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29821,7 +29830,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29836,10 +29845,10 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H544" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J544" t="s">
         <v>564</v>
@@ -29859,7 +29868,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29874,22 +29883,22 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H545" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J545" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M545">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29897,7 +29906,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29912,22 +29921,22 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H546" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J546">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J546" t="s">
+        <v>167</v>
       </c>
       <c r="K546">
         <v>75</v>
       </c>
       <c r="L546">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M546">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29935,7 +29944,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29943,9 +29952,6 @@
       <c r="C547" t="s">
         <v>1323</v>
       </c>
-      <c r="D547" t="s">
-        <v>1008</v>
-      </c>
       <c r="E547" t="s">
         <v>1323</v>
       </c>
@@ -29953,22 +29959,22 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H547" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J547" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J547">
+        <v>2017</v>
       </c>
       <c r="K547">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L547">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M547">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29976,7 +29982,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -29994,7 +30000,7 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H548" t="s">
         <v>1352</v>
@@ -30006,10 +30012,10 @@
         <v>150</v>
       </c>
       <c r="L548">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M548">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30017,10 +30023,10 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B549" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C549" t="s">
         <v>1323</v>
@@ -30035,10 +30041,10 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H549" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J549" t="s">
         <v>564</v>
@@ -30047,10 +30053,10 @@
         <v>150</v>
       </c>
       <c r="L549">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M549">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30058,7 +30064,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B550" t="s">
         <v>55</v>
@@ -30076,7 +30082,7 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H550" t="s">
         <v>1334</v>
@@ -30085,10 +30091,10 @@
         <v>564</v>
       </c>
       <c r="K550">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L550">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M550">
         <v>5</v>
@@ -30099,7 +30105,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B551" t="s">
         <v>55</v>
@@ -30117,7 +30123,7 @@
         <v>1332</v>
       </c>
       <c r="G551" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H551" t="s">
         <v>1334</v>
@@ -30126,10 +30132,10 @@
         <v>564</v>
       </c>
       <c r="K551">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L551">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M551">
         <v>5</v>
@@ -30140,37 +30146,40 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B552" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C552" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D552" t="s">
+        <v>1008</v>
       </c>
       <c r="E552" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F552" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G552" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H552" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J552" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K552">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L552">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M552">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30178,7 +30187,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30193,7 +30202,7 @@
         <v>1406</v>
       </c>
       <c r="G553" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H553" t="s">
         <v>1408</v>
@@ -30205,7 +30214,7 @@
         <v>70</v>
       </c>
       <c r="L553">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M553">
         <v>6</v>
@@ -30216,7 +30225,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30231,19 +30240,22 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H554" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J554" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K554">
         <v>70</v>
       </c>
       <c r="L554">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M554">
+        <v>6</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30251,7 +30263,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30266,19 +30278,19 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H555" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J555" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30286,7 +30298,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30301,19 +30313,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H556" t="s">
         <v>1418</v>
       </c>
       <c r="J556" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30321,7 +30333,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30336,19 +30348,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H557" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J557" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30356,7 +30368,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30364,9 +30376,6 @@
       <c r="C558" t="s">
         <v>1405</v>
       </c>
-      <c r="D558" t="s">
-        <v>1008</v>
-      </c>
       <c r="E558" t="s">
         <v>1405</v>
       </c>
@@ -30374,19 +30383,19 @@
         <v>1406</v>
       </c>
       <c r="G558" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H558" t="s">
         <v>1425</v>
       </c>
       <c r="J558" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K558">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L558">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30394,7 +30403,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30402,26 +30411,29 @@
       <c r="C559" t="s">
         <v>1405</v>
       </c>
+      <c r="D559" t="s">
+        <v>1008</v>
+      </c>
       <c r="E559" t="s">
         <v>1405</v>
       </c>
       <c r="F559" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G559" t="s">
+        <v>1428</v>
       </c>
       <c r="H559" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J559" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K559">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L559">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M559">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30429,10 +30441,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B560" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C560" t="s">
         <v>1405</v>
@@ -30443,17 +30455,17 @@
       <c r="F560" t="s">
         <v>1431</v>
       </c>
-      <c r="G560" t="s">
-        <v>1435</v>
-      </c>
       <c r="H560" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J560" t="s">
+        <v>1433</v>
       </c>
       <c r="K560">
         <v>70</v>
       </c>
       <c r="L560">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M560">
         <v>45</v>
@@ -30464,10 +30476,10 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B561" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C561" t="s">
         <v>1405</v>
@@ -30479,22 +30491,19 @@
         <v>1431</v>
       </c>
       <c r="G561" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H561" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J561" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M561">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30502,7 +30511,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30517,22 +30526,22 @@
         <v>1431</v>
       </c>
       <c r="G562" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H562" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J562" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M562">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30540,7 +30549,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30552,25 +30561,25 @@
         <v>1405</v>
       </c>
       <c r="F563" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G563" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H563" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J563" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K563">
         <v>70</v>
       </c>
       <c r="L563">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M563">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30578,7 +30587,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B564" t="s">
         <v>66</v>
@@ -30593,7 +30602,7 @@
         <v>1445</v>
       </c>
       <c r="G564" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H564" t="s">
         <v>1447</v>
@@ -30605,17 +30614,55 @@
         <v>70</v>
       </c>
       <c r="L564">
+        <v>36.5</v>
+      </c>
+      <c r="M564">
+        <v>7</v>
+      </c>
+      <c r="P564" s="19">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="565" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A565" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B565" t="s">
+        <v>66</v>
+      </c>
+      <c r="C565" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E565" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F565" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G565" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H565" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J565" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K565">
+        <v>70</v>
+      </c>
+      <c r="L565">
         <v>40.5</v>
       </c>
-      <c r="M564">
+      <c r="M565">
         <v>5</v>
       </c>
-      <c r="P564" s="19">
+      <c r="P565" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R564" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R565" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="182" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B157939-DB6D-364E-A316-F911F53C5909}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D800C6B5-F5B0-DB4B-BE21-DB734E65053B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$565</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$566</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10360" uniqueCount="2364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10367" uniqueCount="2365">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7137,6 +7137,9 @@
   </si>
   <si>
     <t>Petit Manseng - moelleux</t>
+  </si>
+  <si>
+    <t>Sauvignon Blanc - Colombard</t>
   </si>
 </sst>
 </file>
@@ -7902,7 +7905,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R565"/>
+  <dimension ref="A1:R566"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23819,7 +23822,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396">
-        <v>73300325</v>
+        <v>73300225</v>
       </c>
       <c r="B396" t="s">
         <v>55</v>
@@ -23837,7 +23840,7 @@
         <v>1033</v>
       </c>
       <c r="G396" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H396" t="s">
         <v>2362</v>
@@ -23849,7 +23852,7 @@
         <v>75</v>
       </c>
       <c r="L396">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="M396">
         <v>12</v>
@@ -23859,11 +23862,11 @@
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>1032</v>
+      <c r="A397">
+        <v>73300325</v>
       </c>
       <c r="B397" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C397" t="s">
         <v>978</v>
@@ -23878,30 +23881,30 @@
         <v>1033</v>
       </c>
       <c r="G397" t="s">
-        <v>1034</v>
+        <v>2363</v>
       </c>
       <c r="H397" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J397" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J397">
+        <v>2025</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>3.95</v>
+        <v>5.59</v>
       </c>
       <c r="M397">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398">
-        <v>13300125</v>
+      <c r="A398" t="s">
+        <v>1032</v>
       </c>
       <c r="B398" t="s">
         <v>66</v>
@@ -23919,33 +23922,33 @@
         <v>1033</v>
       </c>
       <c r="G398" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H398" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J398">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J398" t="s">
+        <v>98</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M398">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>1038</v>
+      <c r="A399">
+        <v>13300125</v>
       </c>
       <c r="B399" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C399" t="s">
         <v>978</v>
@@ -23957,33 +23960,33 @@
         <v>57</v>
       </c>
       <c r="F399" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G399" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H399" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J399" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J399">
+        <v>2025</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M399">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A400">
-        <v>24003025</v>
+      <c r="A400" t="s">
+        <v>1038</v>
       </c>
       <c r="B400" t="s">
         <v>55</v>
@@ -23992,7 +23995,7 @@
         <v>978</v>
       </c>
       <c r="D400" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E400" t="s">
         <v>57</v>
@@ -24001,16 +24004,13 @@
         <v>58</v>
       </c>
       <c r="G400" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H400" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I400" t="s">
-        <v>69</v>
-      </c>
-      <c r="J400">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J400" t="s">
+        <v>339</v>
       </c>
       <c r="K400">
         <v>75</v>
@@ -24018,13 +24018,16 @@
       <c r="L400">
         <v>6.2</v>
       </c>
+      <c r="M400">
+        <v>0</v>
+      </c>
       <c r="P400" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>1044</v>
+      <c r="A401">
+        <v>24003025</v>
       </c>
       <c r="B401" t="s">
         <v>55</v>
@@ -24033,39 +24036,39 @@
         <v>978</v>
       </c>
       <c r="D401" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E401" t="s">
         <v>57</v>
       </c>
       <c r="F401" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G401" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H401" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J401" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I401" t="s">
+        <v>69</v>
+      </c>
+      <c r="J401">
+        <v>2025</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>7.55</v>
-      </c>
-      <c r="M401">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P401" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B402" t="s">
         <v>55</v>
@@ -24074,28 +24077,28 @@
         <v>978</v>
       </c>
       <c r="D402" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E402" t="s">
         <v>57</v>
       </c>
       <c r="F402" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G402" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H402" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J402" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M402">
         <v>0</v>
@@ -24106,7 +24109,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B403" t="s">
         <v>55</v>
@@ -24115,28 +24118,28 @@
         <v>978</v>
       </c>
       <c r="D403" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E403" t="s">
         <v>57</v>
       </c>
       <c r="F403" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G403" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H403" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J403" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M403">
         <v>0</v>
@@ -24147,7 +24150,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B404" t="s">
         <v>55</v>
@@ -24156,42 +24159,39 @@
         <v>978</v>
       </c>
       <c r="D404" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E404" t="s">
         <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G404" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H404" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I404" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J404" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M404">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A405">
-        <v>27701225</v>
+      <c r="A405" t="s">
+        <v>1053</v>
       </c>
       <c r="B405" t="s">
         <v>55</v>
@@ -24200,39 +24200,42 @@
         <v>978</v>
       </c>
       <c r="D405" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E405" t="s">
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G405" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H405" t="s">
         <v>1055</v>
       </c>
-      <c r="J405">
-        <v>2025</v>
+      <c r="I405" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J405" t="s">
+        <v>286</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M405">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A406" t="s">
-        <v>1060</v>
+      <c r="A406">
+        <v>27701225</v>
       </c>
       <c r="B406" t="s">
         <v>55</v>
@@ -24241,28 +24244,28 @@
         <v>978</v>
       </c>
       <c r="D406" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E406" t="s">
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G406" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H406" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J406" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J406">
+        <v>2025</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M406">
         <v>0</v>
@@ -24273,7 +24276,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B407" t="s">
         <v>55</v>
@@ -24282,28 +24285,28 @@
         <v>978</v>
       </c>
       <c r="D407" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E407" t="s">
         <v>57</v>
       </c>
       <c r="F407" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G407" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H407" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J407" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M407">
         <v>0</v>
@@ -24314,7 +24317,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B408" t="s">
         <v>55</v>
@@ -24329,22 +24332,22 @@
         <v>57</v>
       </c>
       <c r="F408" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G408" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H408" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J408" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M408">
         <v>0</v>
@@ -24354,8 +24357,8 @@
       </c>
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A409">
-        <v>68002225</v>
+      <c r="A409" t="s">
+        <v>1065</v>
       </c>
       <c r="B409" t="s">
         <v>55</v>
@@ -24367,13 +24370,13 @@
         <v>1057</v>
       </c>
       <c r="E409" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F409" t="s">
         <v>1066</v>
       </c>
       <c r="G409" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H409" t="s">
         <v>1068</v>
@@ -24385,7 +24388,7 @@
         <v>75</v>
       </c>
       <c r="L409">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24396,7 +24399,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B410" t="s">
         <v>55</v>
@@ -24411,13 +24414,13 @@
         <v>63</v>
       </c>
       <c r="F410" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G410" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H410" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J410" t="s">
         <v>339</v>
@@ -24426,7 +24429,7 @@
         <v>75</v>
       </c>
       <c r="L410">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M410">
         <v>0</v>
@@ -24437,7 +24440,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B411" t="s">
         <v>55</v>
@@ -24455,13 +24458,13 @@
         <v>1070</v>
       </c>
       <c r="G411" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H411" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J411">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J411" t="s">
+        <v>339</v>
       </c>
       <c r="K411">
         <v>75</v>
@@ -24477,8 +24480,8 @@
       </c>
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A412" t="s">
-        <v>1075</v>
+      <c r="A412">
+        <v>68002424</v>
       </c>
       <c r="B412" t="s">
         <v>55</v>
@@ -24496,19 +24499,19 @@
         <v>1070</v>
       </c>
       <c r="G412" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H412" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J412" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J412">
+        <v>2024</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M412">
         <v>0</v>
@@ -24518,8 +24521,8 @@
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A413">
-        <v>68002623</v>
+      <c r="A413" t="s">
+        <v>1075</v>
       </c>
       <c r="B413" t="s">
         <v>55</v>
@@ -24534,25 +24537,22 @@
         <v>63</v>
       </c>
       <c r="F413" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G413" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H413" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I413" t="s">
-        <v>69</v>
-      </c>
-      <c r="J413">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J413" t="s">
+        <v>564</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M413">
         <v>0</v>
@@ -24563,7 +24563,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B414" t="s">
         <v>55</v>
@@ -24575,28 +24575,28 @@
         <v>1057</v>
       </c>
       <c r="E414" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F414" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G414" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H414" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I414" t="s">
         <v>69</v>
       </c>
       <c r="J414">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M414">
         <v>0</v>
@@ -24606,8 +24606,8 @@
       </c>
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A415" t="s">
-        <v>1083</v>
+      <c r="A415">
+        <v>68002825</v>
       </c>
       <c r="B415" t="s">
         <v>55</v>
@@ -24622,22 +24622,25 @@
         <v>57</v>
       </c>
       <c r="F415" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G415" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H415" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J415" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I415" t="s">
+        <v>69</v>
+      </c>
+      <c r="J415">
+        <v>2025</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M415">
         <v>0</v>
@@ -24647,8 +24650,8 @@
       </c>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A416">
-        <v>68003025</v>
+      <c r="A416" t="s">
+        <v>1083</v>
       </c>
       <c r="B416" t="s">
         <v>55</v>
@@ -24660,13 +24663,13 @@
         <v>1057</v>
       </c>
       <c r="E416" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G416" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H416" t="s">
         <v>1085</v>
@@ -24689,7 +24692,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B417" t="s">
         <v>55</v>
@@ -24707,10 +24710,10 @@
         <v>1078</v>
       </c>
       <c r="G417" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H417" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J417" t="s">
         <v>339</v>
@@ -24719,7 +24722,7 @@
         <v>75</v>
       </c>
       <c r="L417">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M417">
         <v>0</v>
@@ -24729,8 +24732,8 @@
       </c>
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
-        <v>1089</v>
+      <c r="A418">
+        <v>680031225</v>
       </c>
       <c r="B418" t="s">
         <v>55</v>
@@ -24742,25 +24745,25 @@
         <v>1057</v>
       </c>
       <c r="E418" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F418" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G418" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H418" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J418" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M418">
         <v>0</v>
@@ -24771,10 +24774,10 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B419" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C419" t="s">
         <v>978</v>
@@ -24789,22 +24792,22 @@
         <v>1066</v>
       </c>
       <c r="G419" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H419" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J419">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J419" t="s">
+        <v>98</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M419">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
@@ -24812,7 +24815,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24821,31 +24824,31 @@
         <v>978</v>
       </c>
       <c r="D420" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E420" t="s">
         <v>57</v>
       </c>
       <c r="F420" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G420" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H420" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J420" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J420">
+        <v>2025</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M420">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24853,7 +24856,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24871,22 +24874,22 @@
         <v>1033</v>
       </c>
       <c r="G421" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H421" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J421">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J421" t="s">
+        <v>98</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M421">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24894,7 +24897,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B422" t="s">
         <v>66</v>
@@ -24909,22 +24912,25 @@
         <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G422" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H422" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J422" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J422">
+        <v>2025</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M422">
+        <v>264</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
@@ -24932,7 +24938,7 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B423" t="s">
         <v>66</v>
@@ -24947,104 +24953,101 @@
         <v>57</v>
       </c>
       <c r="F423" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G423" t="s">
         <v>1100</v>
       </c>
       <c r="H423" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J423" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K423">
         <v>75</v>
       </c>
       <c r="L423">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A424">
-        <v>53800623</v>
+      <c r="A424" t="s">
+        <v>1102</v>
       </c>
       <c r="B424" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C424" t="s">
         <v>978</v>
       </c>
       <c r="D424" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E424" t="s">
         <v>57</v>
       </c>
       <c r="F424" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G424" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H424" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J424" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K424">
         <v>75</v>
       </c>
       <c r="L424">
-        <v>11</v>
-      </c>
-      <c r="M424">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P424" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
-        <v>1107</v>
+      <c r="A425">
+        <v>53800623</v>
       </c>
       <c r="B425" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C425" t="s">
         <v>978</v>
       </c>
       <c r="D425" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E425" t="s">
         <v>57</v>
       </c>
       <c r="F425" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G425" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H425" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J425" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K425">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L425">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M425">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P425" s="19">
         <v>46155</v>
@@ -25052,7 +25055,7 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B426" t="s">
         <v>66</v>
@@ -25070,22 +25073,22 @@
         <v>980</v>
       </c>
       <c r="G426" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H426" t="s">
-        <v>985</v>
-      </c>
-      <c r="J426">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J426" t="s">
+        <v>564</v>
       </c>
       <c r="K426">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L426">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M426">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
@@ -25093,7 +25096,7 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B427" t="s">
         <v>66</v>
@@ -25102,75 +25105,72 @@
         <v>978</v>
       </c>
       <c r="D427" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E427" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F427" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G427" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H427" t="s">
-        <v>989</v>
-      </c>
-      <c r="J427" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J427">
+        <v>2025</v>
       </c>
       <c r="K427">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L427">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M427">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A428">
-        <v>71501125</v>
+      <c r="A428" t="s">
+        <v>1111</v>
       </c>
       <c r="B428" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C428" t="s">
         <v>978</v>
       </c>
       <c r="D428" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E428" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F428" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G428" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H428" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I428" t="s">
-        <v>69</v>
-      </c>
-      <c r="J428">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J428" t="s">
+        <v>564</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M428">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P428" s="19">
         <v>46155</v>
@@ -25178,7 +25178,7 @@
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A429">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B429" t="s">
         <v>55</v>
@@ -25190,17 +25190,20 @@
         <v>979</v>
       </c>
       <c r="E429" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F429" t="s">
         <v>980</v>
       </c>
       <c r="G429" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H429" t="s">
         <v>1113</v>
       </c>
+      <c r="I429" t="s">
+        <v>69</v>
+      </c>
       <c r="J429">
         <v>2025</v>
       </c>
@@ -25208,7 +25211,7 @@
         <v>75</v>
       </c>
       <c r="L429">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M429">
         <v>324</v>
@@ -25219,7 +25222,7 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25237,7 +25240,7 @@
         <v>980</v>
       </c>
       <c r="G430" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H430" t="s">
         <v>1113</v>
@@ -25260,7 +25263,7 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25275,10 +25278,10 @@
         <v>63</v>
       </c>
       <c r="F431" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G431" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H431" t="s">
         <v>1113</v>
@@ -25301,7 +25304,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25313,13 +25316,13 @@
         <v>979</v>
       </c>
       <c r="E432" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F432" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G432" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H432" t="s">
         <v>1113</v>
@@ -25342,7 +25345,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25357,10 +25360,10 @@
         <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G433" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H433" t="s">
         <v>1113</v>
@@ -25383,7 +25386,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25395,13 +25398,13 @@
         <v>979</v>
       </c>
       <c r="E434" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G434" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H434" t="s">
         <v>1113</v>
@@ -25413,7 +25416,7 @@
         <v>75</v>
       </c>
       <c r="L434">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M434">
         <v>324</v>
@@ -25424,7 +25427,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25439,7 +25442,7 @@
         <v>63</v>
       </c>
       <c r="F435" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G435" t="s">
         <v>1120</v>
@@ -25454,7 +25457,7 @@
         <v>75</v>
       </c>
       <c r="L435">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M435">
         <v>324</v>
@@ -25465,7 +25468,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25480,7 +25483,7 @@
         <v>63</v>
       </c>
       <c r="F436" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G436" t="s">
         <v>1120</v>
@@ -25488,9 +25491,6 @@
       <c r="H436" t="s">
         <v>1113</v>
       </c>
-      <c r="I436" t="s">
-        <v>69</v>
-      </c>
       <c r="J436">
         <v>2025</v>
       </c>
@@ -25509,7 +25509,7 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25521,10 +25521,10 @@
         <v>979</v>
       </c>
       <c r="E437" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F437" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G437" t="s">
         <v>1120</v>
@@ -25533,7 +25533,7 @@
         <v>1113</v>
       </c>
       <c r="I437" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J437">
         <v>2025</v>
@@ -25542,7 +25542,7 @@
         <v>75</v>
       </c>
       <c r="L437">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M437">
         <v>324</v>
@@ -25553,7 +25553,7 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25568,7 +25568,7 @@
         <v>57</v>
       </c>
       <c r="F438" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G438" t="s">
         <v>1120</v>
@@ -25586,7 +25586,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M438">
         <v>324</v>
@@ -25597,10 +25597,10 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B439" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C439" t="s">
         <v>978</v>
@@ -25609,16 +25609,19 @@
         <v>979</v>
       </c>
       <c r="E439" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F439" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G439" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H439" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I439" t="s">
+        <v>175</v>
       </c>
       <c r="J439">
         <v>2025</v>
@@ -25627,7 +25630,7 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M439">
         <v>324</v>
@@ -25637,8 +25640,8 @@
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>1125</v>
+      <c r="A440">
+        <v>16000125</v>
       </c>
       <c r="B440" t="s">
         <v>66</v>
@@ -25656,22 +25659,22 @@
         <v>980</v>
       </c>
       <c r="G440" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H440" t="s">
-        <v>985</v>
-      </c>
-      <c r="J440" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J440">
+        <v>2025</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M440">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P440" s="19">
         <v>46155</v>
@@ -25679,7 +25682,7 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B441" t="s">
         <v>66</v>
@@ -25697,22 +25700,22 @@
         <v>980</v>
       </c>
       <c r="G441" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H441" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J441" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M441">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P441" s="19">
         <v>46155</v>
@@ -25720,7 +25723,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B442" t="s">
         <v>66</v>
@@ -25738,22 +25741,22 @@
         <v>980</v>
       </c>
       <c r="G442" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H442" t="s">
-        <v>985</v>
-      </c>
-      <c r="J442">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J442" t="s">
+        <v>286</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M442">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P442" s="19">
         <v>46155</v>
@@ -25761,7 +25764,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B443" t="s">
         <v>66</v>
@@ -25776,25 +25779,25 @@
         <v>63</v>
       </c>
       <c r="F443" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G443" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H443" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J443" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J443">
+        <v>2025</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M443">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P443" s="19">
         <v>46155</v>
@@ -25802,7 +25805,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B444" t="s">
         <v>66</v>
@@ -25817,25 +25820,25 @@
         <v>63</v>
       </c>
       <c r="F444" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G444" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H444" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J444" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M444">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P444" s="19">
         <v>46155</v>
@@ -25843,7 +25846,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B445" t="s">
         <v>66</v>
@@ -25861,22 +25864,22 @@
         <v>980</v>
       </c>
       <c r="G445" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H445" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J445" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K445">
         <v>75</v>
       </c>
       <c r="L445">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M445">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P445" s="19">
         <v>46155</v>
@@ -25884,7 +25887,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B446" t="s">
         <v>66</v>
@@ -25902,25 +25905,22 @@
         <v>980</v>
       </c>
       <c r="G446" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H446" t="s">
-        <v>982</v>
-      </c>
-      <c r="I446" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J446" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K446">
         <v>75</v>
       </c>
       <c r="L446">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M446">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P446" s="19">
         <v>46155</v>
@@ -25928,7 +25928,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B447" t="s">
         <v>66</v>
@@ -25946,13 +25946,13 @@
         <v>980</v>
       </c>
       <c r="G447" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H447" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I447" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J447" t="s">
         <v>61</v>
@@ -25961,10 +25961,10 @@
         <v>75</v>
       </c>
       <c r="L447">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M447">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P447" s="19">
         <v>46155</v>
@@ -25972,7 +25972,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B448" t="s">
         <v>66</v>
@@ -25987,25 +25987,28 @@
         <v>63</v>
       </c>
       <c r="F448" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G448" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H448" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I448" t="s">
+        <v>1012</v>
       </c>
       <c r="J448" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M448">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26013,7 +26016,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26022,19 +26025,19 @@
         <v>978</v>
       </c>
       <c r="D449" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E449" t="s">
         <v>63</v>
       </c>
       <c r="F449" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G449" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H449" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J449" t="s">
         <v>217</v>
@@ -26043,10 +26046,10 @@
         <v>75</v>
       </c>
       <c r="L449">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M449">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26054,7 +26057,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26069,25 +26072,25 @@
         <v>63</v>
       </c>
       <c r="F450" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G450" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H450" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J450" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M450">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26095,7 +26098,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26113,22 +26116,22 @@
         <v>1147</v>
       </c>
       <c r="G451" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H451" t="s">
         <v>1149</v>
       </c>
       <c r="J451" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M451">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26136,37 +26139,40 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B452" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C452" t="s">
         <v>978</v>
       </c>
       <c r="D452" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E452" t="s">
         <v>63</v>
       </c>
       <c r="F452" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G452" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H452" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J452" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M452">
+        <v>36</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
@@ -26174,7 +26180,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B453" t="s">
         <v>55</v>
@@ -26189,25 +26195,22 @@
         <v>63</v>
       </c>
       <c r="F453" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G453" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H453" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J453" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>12.5</v>
-      </c>
-      <c r="M453">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
@@ -26215,7 +26218,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B454" t="s">
         <v>55</v>
@@ -26230,22 +26233,22 @@
         <v>63</v>
       </c>
       <c r="F454" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G454" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H454" t="s">
         <v>1064</v>
       </c>
       <c r="J454" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M454">
         <v>0</v>
@@ -26256,7 +26259,7 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B455" t="s">
         <v>55</v>
@@ -26274,19 +26277,19 @@
         <v>1078</v>
       </c>
       <c r="G455" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H455" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J455">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J455" t="s">
+        <v>209</v>
       </c>
       <c r="K455">
         <v>75</v>
       </c>
       <c r="L455">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M455">
         <v>0</v>
@@ -26297,10 +26300,10 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B456" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C456" t="s">
         <v>978</v>
@@ -26312,25 +26315,25 @@
         <v>63</v>
       </c>
       <c r="F456" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G456" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H456" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J456" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J456">
+        <v>2014</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M456">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
@@ -26338,10 +26341,10 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B457" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C457" t="s">
         <v>978</v>
@@ -26356,13 +26359,10 @@
         <v>1066</v>
       </c>
       <c r="G457" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H457" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I457" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J457" t="s">
         <v>61</v>
@@ -26371,18 +26371,18 @@
         <v>75</v>
       </c>
       <c r="L457">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M457">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P457" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A458">
-        <v>27701324</v>
+      <c r="A458" t="s">
+        <v>1164</v>
       </c>
       <c r="B458" t="s">
         <v>55</v>
@@ -26400,19 +26400,22 @@
         <v>1066</v>
       </c>
       <c r="G458" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H458" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J458">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I458" t="s">
+        <v>69</v>
+      </c>
+      <c r="J458" t="s">
+        <v>61</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M458">
         <v>0</v>
@@ -26422,8 +26425,8 @@
       </c>
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A459" t="s">
-        <v>1167</v>
+      <c r="A459">
+        <v>27701324</v>
       </c>
       <c r="B459" t="s">
         <v>55</v>
@@ -26441,22 +26444,19 @@
         <v>1066</v>
       </c>
       <c r="G459" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H459" t="s">
         <v>1055</v>
       </c>
-      <c r="I459" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J459" t="s">
-        <v>98</v>
+      <c r="J459">
+        <v>2024</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M459">
         <v>0</v>
@@ -26467,31 +26467,31 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B460" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C460" t="s">
         <v>978</v>
       </c>
       <c r="D460" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E460" t="s">
         <v>63</v>
       </c>
       <c r="F460" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G460" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H460" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I460" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J460" t="s">
         <v>98</v>
@@ -26500,10 +26500,10 @@
         <v>75</v>
       </c>
       <c r="L460">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M460">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P460" s="19">
         <v>46155</v>
@@ -26511,7 +26511,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B461" t="s">
         <v>66</v>
@@ -26526,28 +26526,28 @@
         <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G461" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H461" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I461" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J461" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K461">
         <v>75</v>
       </c>
       <c r="L461">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M461">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P461" s="19">
         <v>46155</v>
@@ -26555,10 +26555,10 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B462" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C462" t="s">
         <v>978</v>
@@ -26570,25 +26570,28 @@
         <v>63</v>
       </c>
       <c r="F462" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G462" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H462" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I462" t="s">
+        <v>69</v>
       </c>
       <c r="J462" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K462">
         <v>75</v>
       </c>
       <c r="L462">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M462">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P462" s="19">
         <v>46155</v>
@@ -26596,7 +26599,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B463" t="s">
         <v>55</v>
@@ -26614,19 +26617,22 @@
         <v>1175</v>
       </c>
       <c r="G463" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H463" t="s">
         <v>1177</v>
       </c>
       <c r="J463" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K463">
         <v>75</v>
       </c>
       <c r="L463">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M463">
+        <v>0</v>
       </c>
       <c r="P463" s="19">
         <v>46155</v>
@@ -26634,10 +26640,10 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B464" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C464" t="s">
         <v>978</v>
@@ -26649,28 +26655,22 @@
         <v>63</v>
       </c>
       <c r="F464" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G464" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H464" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I464" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J464" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K464">
         <v>75</v>
       </c>
       <c r="L464">
-        <v>7.6</v>
-      </c>
-      <c r="M464">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P464" s="19">
         <v>46155</v>
@@ -26678,10 +26678,10 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B465" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C465" t="s">
         <v>978</v>
@@ -26693,25 +26693,28 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G465" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H465" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I465" t="s">
+        <v>69</v>
       </c>
       <c r="J465" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K465">
         <v>75</v>
       </c>
       <c r="L465">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M465">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P465" s="19">
         <v>46155</v>
@@ -26719,7 +26722,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B466" t="s">
         <v>55</v>
@@ -26737,22 +26740,22 @@
         <v>1185</v>
       </c>
       <c r="G466" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H466" t="s">
         <v>1049</v>
       </c>
       <c r="J466" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M466">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P466" s="19">
         <v>46155</v>
@@ -26760,10 +26763,10 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B467" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C467" t="s">
         <v>978</v>
@@ -26775,25 +26778,25 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G467" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H467" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I467" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J467" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M467">
+        <v>6</v>
       </c>
       <c r="P467" s="19">
         <v>46155</v>
@@ -26801,7 +26804,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B468" t="s">
         <v>66</v>
@@ -26816,25 +26819,25 @@
         <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G468" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H468" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I468" t="s">
+        <v>777</v>
       </c>
       <c r="J468" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M468">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26842,7 +26845,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B469" t="s">
         <v>66</v>
@@ -26857,25 +26860,25 @@
         <v>63</v>
       </c>
       <c r="F469" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G469" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H469" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I469" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J469" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M469">
+        <v>53</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
@@ -26883,7 +26886,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B470" t="s">
         <v>66</v>
@@ -26898,28 +26901,25 @@
         <v>63</v>
       </c>
       <c r="F470" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G470" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H470" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I470" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J470" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>6.5</v>
-      </c>
-      <c r="M470">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
@@ -26927,10 +26927,10 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B471" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C471" t="s">
         <v>978</v>
@@ -26945,30 +26945,33 @@
         <v>1122</v>
       </c>
       <c r="G471" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H471" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I471" t="s">
+        <v>175</v>
       </c>
       <c r="J471" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M471">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A472">
-        <v>16003124</v>
+      <c r="A472" t="s">
+        <v>1202</v>
       </c>
       <c r="B472" t="s">
         <v>55</v>
@@ -26980,19 +26983,19 @@
         <v>979</v>
       </c>
       <c r="E472" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F472" t="s">
         <v>1122</v>
       </c>
       <c r="G472" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H472" t="s">
         <v>1204</v>
       </c>
       <c r="J472" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K472">
         <v>75</v>
@@ -27008,11 +27011,11 @@
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A473" t="s">
-        <v>1206</v>
+      <c r="A473">
+        <v>16003124</v>
       </c>
       <c r="B473" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C473" t="s">
         <v>978</v>
@@ -27021,31 +27024,28 @@
         <v>979</v>
       </c>
       <c r="E473" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F473" t="s">
         <v>1122</v>
       </c>
       <c r="G473" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H473" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I473" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J473" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M473">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27053,10 +27053,10 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B474" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C474" t="s">
         <v>978</v>
@@ -27071,25 +27071,25 @@
         <v>1122</v>
       </c>
       <c r="G474" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H474" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I474" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J474" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M474">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27097,10 +27097,10 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B475" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C475" t="s">
         <v>978</v>
@@ -27115,13 +27115,13 @@
         <v>1122</v>
       </c>
       <c r="G475" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H475" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I475" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J475" t="s">
         <v>61</v>
@@ -27130,7 +27130,7 @@
         <v>75</v>
       </c>
       <c r="L475">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M475">
         <v>171</v>
@@ -27141,10 +27141,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B476" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C476" t="s">
         <v>978</v>
@@ -27159,19 +27159,25 @@
         <v>1122</v>
       </c>
       <c r="G476" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H476" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I476" t="s">
+        <v>175</v>
       </c>
       <c r="J476" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M476">
+        <v>171</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27179,10 +27185,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B477" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C477" t="s">
         <v>978</v>
@@ -27194,28 +27200,22 @@
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G477" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H477" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I477" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J477" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>24.08</v>
-      </c>
-      <c r="M477">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27223,10 +27223,10 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B478" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C478" t="s">
         <v>978</v>
@@ -27238,19 +27238,28 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G478" t="s">
+        <v>1216</v>
       </c>
       <c r="H478" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I478" t="s">
+        <v>175</v>
       </c>
       <c r="J478" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M478">
+        <v>12</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27258,10 +27267,10 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B479" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C479" t="s">
         <v>978</v>
@@ -27273,30 +27282,27 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H479" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J479" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>7.05</v>
-      </c>
-      <c r="M479">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A480">
-        <v>27100523</v>
+      <c r="A480" t="s">
+        <v>1221</v>
       </c>
       <c r="B480" t="s">
         <v>66</v>
@@ -27311,36 +27317,33 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G480" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H480" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I480" t="s">
-        <v>777</v>
-      </c>
-      <c r="J480">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J480" t="s">
+        <v>217</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M480">
+        <v>30</v>
       </c>
       <c r="P480" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A481" t="s">
-        <v>1225</v>
+      <c r="A481">
+        <v>27100523</v>
       </c>
       <c r="B481" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C481" t="s">
         <v>978</v>
@@ -27352,33 +27355,36 @@
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G481" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H481" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J481" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I481" t="s">
+        <v>777</v>
+      </c>
+      <c r="J481">
+        <v>2023</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P481" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B482" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
@@ -27390,33 +27396,33 @@
         <v>63</v>
       </c>
       <c r="F482" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G482" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H482" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J482" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>7.35</v>
-      </c>
-      <c r="M482">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>1229</v>
+      </c>
       <c r="B483" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C483" t="s">
         <v>978</v>
@@ -27431,19 +27437,19 @@
         <v>1119</v>
       </c>
       <c r="G483" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H483" t="s">
         <v>1231</v>
       </c>
       <c r="J483" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K483">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L483">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M483">
         <v>2215</v>
@@ -27453,11 +27459,8 @@
       </c>
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A484" t="s">
-        <v>1233</v>
-      </c>
       <c r="B484" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C484" t="s">
         <v>978</v>
@@ -27472,22 +27475,22 @@
         <v>1119</v>
       </c>
       <c r="G484" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H484" t="s">
         <v>1231</v>
       </c>
-      <c r="J484">
-        <v>2023</v>
+      <c r="J484" t="s">
+        <v>61</v>
       </c>
       <c r="K484">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L484">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M484">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
@@ -27495,7 +27498,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B485" t="s">
         <v>66</v>
@@ -27513,25 +27516,22 @@
         <v>1119</v>
       </c>
       <c r="G485" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H485" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I485" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J485" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J485">
+        <v>2023</v>
       </c>
       <c r="K485">
         <v>75</v>
       </c>
       <c r="L485">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M485">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
@@ -27539,10 +27539,10 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B486" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C486" t="s">
         <v>978</v>
@@ -27557,19 +27557,25 @@
         <v>1119</v>
       </c>
       <c r="G486" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H486" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I486" t="s">
+        <v>1238</v>
       </c>
       <c r="J486" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M486">
+        <v>205</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
@@ -27577,7 +27583,7 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B487" t="s">
         <v>55</v>
@@ -27595,10 +27601,10 @@
         <v>1119</v>
       </c>
       <c r="G487" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H487" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J487" t="s">
         <v>98</v>
@@ -27607,21 +27613,18 @@
         <v>75</v>
       </c>
       <c r="L487">
-        <v>14.6</v>
-      </c>
-      <c r="M487">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A488">
-        <v>43700124</v>
+      <c r="A488" t="s">
+        <v>1242</v>
       </c>
       <c r="B488" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C488" t="s">
         <v>978</v>
@@ -27633,22 +27636,25 @@
         <v>63</v>
       </c>
       <c r="F488" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G488" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H488" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J488">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J488" t="s">
+        <v>98</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M488">
+        <v>0</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
@@ -27656,10 +27662,10 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B489" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C489" t="s">
         <v>978</v>
@@ -27674,19 +27680,19 @@
         <v>1028</v>
       </c>
       <c r="G489" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H489" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J489">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
@@ -27694,7 +27700,7 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B490" t="s">
         <v>55</v>
@@ -27712,30 +27718,30 @@
         <v>1028</v>
       </c>
       <c r="G490" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H490" t="s">
         <v>1031</v>
       </c>
       <c r="J490">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A491" t="s">
-        <v>1247</v>
+      <c r="A491">
+        <v>43700524</v>
       </c>
       <c r="B491" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C491" t="s">
         <v>978</v>
@@ -27744,28 +27750,25 @@
         <v>979</v>
       </c>
       <c r="E491" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F491" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G491" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H491" t="s">
-        <v>982</v>
-      </c>
-      <c r="J491" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J491">
+        <v>2024</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>3.8</v>
-      </c>
-      <c r="M491">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27773,7 +27776,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B492" t="s">
         <v>66</v>
@@ -27791,22 +27794,22 @@
         <v>980</v>
       </c>
       <c r="G492" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H492" t="s">
-        <v>985</v>
-      </c>
-      <c r="J492">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J492" t="s">
+        <v>98</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M492">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27814,7 +27817,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B493" t="s">
         <v>66</v>
@@ -27832,10 +27835,10 @@
         <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H493" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J493">
         <v>2025</v>
@@ -27844,10 +27847,10 @@
         <v>75</v>
       </c>
       <c r="L493">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M493">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27855,10 +27858,10 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B494" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C494" t="s">
         <v>978</v>
@@ -27873,22 +27876,22 @@
         <v>980</v>
       </c>
       <c r="G494" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H494" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J494" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J494">
+        <v>2025</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M494">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -27896,10 +27899,10 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B495" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C495" t="s">
         <v>978</v>
@@ -27914,22 +27917,22 @@
         <v>980</v>
       </c>
       <c r="G495" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H495" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J495" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K495">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L495">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M495">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -27937,7 +27940,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B496" t="s">
         <v>66</v>
@@ -27955,22 +27958,22 @@
         <v>980</v>
       </c>
       <c r="G496" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H496" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J496" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K496">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L496">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M496">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -27978,40 +27981,40 @@
     </row>
     <row r="497" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
       </c>
       <c r="C497" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D497" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E497" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F497" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G497" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H497" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J497" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K497">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L497">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M497">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28019,7 +28022,7 @@
     </row>
     <row r="498" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28034,13 +28037,13 @@
         <v>57</v>
       </c>
       <c r="F498" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G498" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H498" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J498" t="s">
         <v>339</v>
@@ -28049,21 +28052,18 @@
         <v>75</v>
       </c>
       <c r="L498">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M498">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
       </c>
-      <c r="R498" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="499" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A499">
-        <v>24000925</v>
+      <c r="A499" t="s">
+        <v>1262</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28075,36 +28075,39 @@
         <v>1258</v>
       </c>
       <c r="E499" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F499" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G499" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H499" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J499">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J499" t="s">
+        <v>339</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M499">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
       </c>
+      <c r="R499" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="500" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A500" t="s">
-        <v>1266</v>
+      <c r="A500">
+        <v>24000925</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28116,28 +28119,28 @@
         <v>1258</v>
       </c>
       <c r="E500" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F500" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G500" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H500" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J500" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J500">
+        <v>2025</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M500">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
@@ -28145,7 +28148,7 @@
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28160,33 +28163,33 @@
         <v>63</v>
       </c>
       <c r="F501" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G501" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H501" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J501" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M501">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A502">
-        <v>24001825</v>
+      <c r="A502" t="s">
+        <v>1270</v>
       </c>
       <c r="B502" t="s">
         <v>66</v>
@@ -28201,33 +28204,33 @@
         <v>63</v>
       </c>
       <c r="F502" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G502" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H502" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J502">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J502" t="s">
+        <v>98</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M502">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A503" t="s">
-        <v>1275</v>
+      <c r="A503">
+        <v>24001825</v>
       </c>
       <c r="B503" t="s">
         <v>66</v>
@@ -28242,22 +28245,25 @@
         <v>63</v>
       </c>
       <c r="F503" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G503" t="s">
+        <v>1274</v>
       </c>
       <c r="H503" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J503" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J503">
+        <v>2025</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M503">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
@@ -28265,7 +28271,7 @@
     </row>
     <row r="504" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B504" t="s">
         <v>66</v>
@@ -28280,28 +28286,22 @@
         <v>63</v>
       </c>
       <c r="F504" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G504" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H504" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I504" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J504" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M504">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28309,7 +28309,7 @@
     </row>
     <row r="505" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B505" t="s">
         <v>66</v>
@@ -28318,28 +28318,34 @@
         <v>1257</v>
       </c>
       <c r="D505" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E505" t="s">
         <v>63</v>
       </c>
       <c r="F505" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G505" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H505" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I505" t="s">
+        <v>69</v>
       </c>
       <c r="J505" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M505">
+        <v>318</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28347,7 +28353,7 @@
     </row>
     <row r="506" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B506" t="s">
         <v>66</v>
@@ -28365,22 +28371,19 @@
         <v>1284</v>
       </c>
       <c r="G506" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H506" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J506" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>6.1</v>
-      </c>
-      <c r="M506">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P506" s="19">
         <v>46155</v>
@@ -28388,7 +28391,7 @@
     </row>
     <row r="507" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B507" t="s">
         <v>66</v>
@@ -28411,8 +28414,8 @@
       <c r="H507" t="s">
         <v>1289</v>
       </c>
-      <c r="J507">
-        <v>2024</v>
+      <c r="J507" t="s">
+        <v>87</v>
       </c>
       <c r="K507">
         <v>75</v>
@@ -28420,16 +28423,19 @@
       <c r="L507">
         <v>6.1</v>
       </c>
+      <c r="M507">
+        <v>133</v>
+      </c>
       <c r="P507" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="508" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B508" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C508" t="s">
         <v>1257</v>
@@ -28444,30 +28450,27 @@
         <v>1284</v>
       </c>
       <c r="G508" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H508" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J508" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J508">
+        <v>2024</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>13.2</v>
-      </c>
-      <c r="M508">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P508" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="509" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B509" t="s">
         <v>55</v>
@@ -28485,19 +28488,19 @@
         <v>1284</v>
       </c>
       <c r="G509" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H509" t="s">
         <v>1293</v>
       </c>
       <c r="J509" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M509">
         <v>0</v>
@@ -28508,7 +28511,7 @@
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B510" t="s">
         <v>55</v>
@@ -28523,22 +28526,22 @@
         <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G510" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H510" t="s">
         <v>1293</v>
       </c>
       <c r="J510" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M510">
         <v>0</v>
@@ -28548,49 +28551,49 @@
       </c>
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A511">
-        <v>10702526</v>
+      <c r="A511" t="s">
+        <v>1296</v>
       </c>
       <c r="B511" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C511" t="s">
         <v>1257</v>
       </c>
       <c r="D511" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E511" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F511" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G511" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H511" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J511">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J511" t="s">
+        <v>61</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M511">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P511" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A512" t="s">
-        <v>1301</v>
+      <c r="A512">
+        <v>10702526</v>
       </c>
       <c r="B512" t="s">
         <v>66</v>
@@ -28599,31 +28602,31 @@
         <v>1257</v>
       </c>
       <c r="D512" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E512" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F512" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G512" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H512" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J512" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J512">
+        <v>2026</v>
       </c>
       <c r="K512">
         <v>75</v>
       </c>
       <c r="L512">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M512">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
@@ -28631,7 +28634,7 @@
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28649,7 +28652,7 @@
         <v>1303</v>
       </c>
       <c r="G513" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H513" t="s">
         <v>1305</v>
@@ -28661,10 +28664,10 @@
         <v>75</v>
       </c>
       <c r="L513">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M513">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28672,7 +28675,7 @@
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28690,7 +28693,7 @@
         <v>1303</v>
       </c>
       <c r="G514" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H514" t="s">
         <v>1305</v>
@@ -28705,7 +28708,7 @@
         <v>8.6</v>
       </c>
       <c r="M514">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28713,7 +28716,7 @@
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28731,13 +28734,13 @@
         <v>1303</v>
       </c>
       <c r="G515" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H515" t="s">
         <v>1305</v>
       </c>
       <c r="J515" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K515">
         <v>75</v>
@@ -28746,7 +28749,7 @@
         <v>8.6</v>
       </c>
       <c r="M515">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28754,7 +28757,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28772,7 +28775,7 @@
         <v>1303</v>
       </c>
       <c r="G516" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H516" t="s">
         <v>1305</v>
@@ -28787,7 +28790,7 @@
         <v>8.6</v>
       </c>
       <c r="M516">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28795,7 +28798,7 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B517" t="s">
         <v>66</v>
@@ -28813,22 +28816,22 @@
         <v>1303</v>
       </c>
       <c r="G517" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H517" t="s">
         <v>1305</v>
       </c>
       <c r="J517" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K517">
         <v>75</v>
       </c>
       <c r="L517">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M517">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28836,7 +28839,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B518" t="s">
         <v>66</v>
@@ -28854,22 +28857,22 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H518" t="s">
         <v>1305</v>
       </c>
-      <c r="J518">
-        <v>2021</v>
+      <c r="J518" t="s">
+        <v>127</v>
       </c>
       <c r="K518">
         <v>75</v>
       </c>
       <c r="L518">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M518">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
@@ -28877,7 +28880,7 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B519" t="s">
         <v>66</v>
@@ -28895,13 +28898,13 @@
         <v>1303</v>
       </c>
       <c r="G519" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H519" t="s">
         <v>1305</v>
       </c>
-      <c r="J519" t="s">
-        <v>109</v>
+      <c r="J519">
+        <v>2021</v>
       </c>
       <c r="K519">
         <v>75</v>
@@ -28910,7 +28913,7 @@
         <v>13</v>
       </c>
       <c r="M519">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -28918,7 +28921,7 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
@@ -28936,7 +28939,7 @@
         <v>1303</v>
       </c>
       <c r="G520" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H520" t="s">
         <v>1305</v>
@@ -28948,7 +28951,7 @@
         <v>75</v>
       </c>
       <c r="L520">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M520">
         <v>36</v>
@@ -28959,7 +28962,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -28971,28 +28974,28 @@
         <v>1302</v>
       </c>
       <c r="E521" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F521" t="s">
         <v>1303</v>
       </c>
       <c r="G521" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H521" t="s">
         <v>1305</v>
       </c>
       <c r="J521" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K521">
         <v>75</v>
       </c>
       <c r="L521">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M521">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
@@ -29000,40 +29003,40 @@
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
       </c>
       <c r="C522" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D522" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E522" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F522" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G522" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H522" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J522" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K522">
         <v>75</v>
       </c>
       <c r="L522">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M522">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29041,7 +29044,7 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29049,17 +29052,20 @@
       <c r="C523" t="s">
         <v>1323</v>
       </c>
+      <c r="D523" t="s">
+        <v>1258</v>
+      </c>
       <c r="E523" t="s">
         <v>1323</v>
       </c>
       <c r="F523" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G523" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H523" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J523" t="s">
         <v>564</v>
@@ -29070,13 +29076,16 @@
       <c r="L523">
         <v>6.2</v>
       </c>
+      <c r="M523">
+        <v>4411</v>
+      </c>
       <c r="P523" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29091,10 +29100,10 @@
         <v>58</v>
       </c>
       <c r="G524" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H524" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J524" t="s">
         <v>564</v>
@@ -29103,7 +29112,7 @@
         <v>75</v>
       </c>
       <c r="L524">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29111,7 +29120,7 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29123,25 +29132,22 @@
         <v>1323</v>
       </c>
       <c r="F525" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G525" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H525" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J525" t="s">
         <v>564</v>
       </c>
       <c r="K525">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L525">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M525">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29149,7 +29155,7 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
@@ -29164,22 +29170,22 @@
         <v>1332</v>
       </c>
       <c r="G526" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H526" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J526" t="s">
         <v>564</v>
       </c>
       <c r="K526">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L526">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M526">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29187,7 +29193,7 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
@@ -29202,10 +29208,10 @@
         <v>1332</v>
       </c>
       <c r="G527" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H527" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J527" t="s">
         <v>564</v>
@@ -29214,10 +29220,10 @@
         <v>75</v>
       </c>
       <c r="L527">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M527">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29225,10 +29231,10 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B528" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C528" t="s">
         <v>1323</v>
@@ -29240,10 +29246,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H528" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29252,7 +29258,10 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M528">
+        <v>418</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29260,10 +29269,10 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B529" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C529" t="s">
         <v>1323</v>
@@ -29275,10 +29284,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H529" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29287,10 +29296,7 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>25.8</v>
-      </c>
-      <c r="M529">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29298,7 +29304,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29313,10 +29319,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H530" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29325,10 +29331,10 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M530">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29336,7 +29342,7 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29351,10 +29357,10 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H531" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J531" t="s">
         <v>564</v>
@@ -29363,10 +29369,10 @@
         <v>75</v>
       </c>
       <c r="L531">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M531">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29374,7 +29380,7 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29389,10 +29395,10 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H532" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J532" t="s">
         <v>564</v>
@@ -29401,10 +29407,10 @@
         <v>75</v>
       </c>
       <c r="L532">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M532">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
@@ -29412,10 +29418,10 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B533" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C533" t="s">
         <v>1323</v>
@@ -29427,7 +29433,7 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H533" t="s">
         <v>1349</v>
@@ -29436,10 +29442,10 @@
         <v>564</v>
       </c>
       <c r="K533">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L533">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M533">
         <v>60</v>
@@ -29450,7 +29456,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B534" t="s">
         <v>55</v>
@@ -29465,7 +29471,7 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H534" t="s">
         <v>1349</v>
@@ -29474,10 +29480,10 @@
         <v>564</v>
       </c>
       <c r="K534">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L534">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M534">
         <v>60</v>
@@ -29488,7 +29494,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B535" t="s">
         <v>55</v>
@@ -29503,7 +29509,7 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H535" t="s">
         <v>1349</v>
@@ -29515,7 +29521,7 @@
         <v>75</v>
       </c>
       <c r="L535">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M535">
         <v>60</v>
@@ -29526,10 +29532,10 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B536" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C536" t="s">
         <v>1323</v>
@@ -29541,10 +29547,10 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H536" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J536" t="s">
         <v>564</v>
@@ -29553,10 +29559,10 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M536">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29564,7 +29570,7 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29579,10 +29585,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H537" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29591,10 +29597,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M537">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29602,7 +29608,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29617,10 +29623,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H538" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29629,10 +29635,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M538">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29640,7 +29646,7 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B539" t="s">
         <v>66</v>
@@ -29655,10 +29661,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H539" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29667,10 +29673,10 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M539">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
@@ -29678,7 +29684,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29693,10 +29699,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H540" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29705,10 +29711,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M540">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29716,10 +29722,10 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B541" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C541" t="s">
         <v>1323</v>
@@ -29731,10 +29737,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H541" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29743,7 +29749,7 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M541">
         <v>0</v>
@@ -29754,10 +29760,10 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B542" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C542" t="s">
         <v>1323</v>
@@ -29769,10 +29775,10 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H542" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J542" t="s">
         <v>564</v>
@@ -29781,10 +29787,10 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M542">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29792,7 +29798,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29807,7 +29813,7 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H543" t="s">
         <v>1352</v>
@@ -29819,10 +29825,10 @@
         <v>75</v>
       </c>
       <c r="L543">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M543">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29830,7 +29836,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29845,10 +29851,10 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H544" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J544" t="s">
         <v>564</v>
@@ -29857,10 +29863,10 @@
         <v>75</v>
       </c>
       <c r="L544">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M544">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29868,7 +29874,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29883,10 +29889,10 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H545" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J545" t="s">
         <v>564</v>
@@ -29906,7 +29912,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29921,22 +29927,22 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H546" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J546" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K546">
         <v>75</v>
       </c>
       <c r="L546">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M546">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -29944,7 +29950,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29959,22 +29965,22 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H547" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J547">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J547" t="s">
+        <v>167</v>
       </c>
       <c r="K547">
         <v>75</v>
       </c>
       <c r="L547">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M547">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29982,7 +29988,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -29990,9 +29996,6 @@
       <c r="C548" t="s">
         <v>1323</v>
       </c>
-      <c r="D548" t="s">
-        <v>1008</v>
-      </c>
       <c r="E548" t="s">
         <v>1323</v>
       </c>
@@ -30000,22 +30003,22 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H548" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J548" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J548">
+        <v>2017</v>
       </c>
       <c r="K548">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L548">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M548">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30023,7 +30026,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30041,7 +30044,7 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H549" t="s">
         <v>1352</v>
@@ -30053,10 +30056,10 @@
         <v>150</v>
       </c>
       <c r="L549">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M549">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30064,10 +30067,10 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B550" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C550" t="s">
         <v>1323</v>
@@ -30082,10 +30085,10 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H550" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J550" t="s">
         <v>564</v>
@@ -30094,10 +30097,10 @@
         <v>150</v>
       </c>
       <c r="L550">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M550">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30105,7 +30108,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B551" t="s">
         <v>55</v>
@@ -30123,7 +30126,7 @@
         <v>1332</v>
       </c>
       <c r="G551" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H551" t="s">
         <v>1334</v>
@@ -30132,10 +30135,10 @@
         <v>564</v>
       </c>
       <c r="K551">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L551">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M551">
         <v>5</v>
@@ -30146,7 +30149,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B552" t="s">
         <v>55</v>
@@ -30164,7 +30167,7 @@
         <v>1332</v>
       </c>
       <c r="G552" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H552" t="s">
         <v>1334</v>
@@ -30173,10 +30176,10 @@
         <v>564</v>
       </c>
       <c r="K552">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L552">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M552">
         <v>5</v>
@@ -30187,37 +30190,40 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B553" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C553" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1008</v>
       </c>
       <c r="E553" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F553" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G553" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H553" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J553" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K553">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L553">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M553">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30225,7 +30231,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30240,7 +30246,7 @@
         <v>1406</v>
       </c>
       <c r="G554" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H554" t="s">
         <v>1408</v>
@@ -30252,7 +30258,7 @@
         <v>70</v>
       </c>
       <c r="L554">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M554">
         <v>6</v>
@@ -30263,7 +30269,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30278,19 +30284,22 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H555" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J555" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K555">
         <v>70</v>
       </c>
       <c r="L555">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M555">
+        <v>6</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30298,7 +30307,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30313,19 +30322,19 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H556" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J556" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30333,7 +30342,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30348,19 +30357,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H557" t="s">
         <v>1418</v>
       </c>
       <c r="J557" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30368,7 +30377,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30383,19 +30392,19 @@
         <v>1406</v>
       </c>
       <c r="G558" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H558" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J558" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K558">
         <v>70</v>
       </c>
       <c r="L558">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30403,7 +30412,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30411,9 +30420,6 @@
       <c r="C559" t="s">
         <v>1405</v>
       </c>
-      <c r="D559" t="s">
-        <v>1008</v>
-      </c>
       <c r="E559" t="s">
         <v>1405</v>
       </c>
@@ -30421,19 +30427,19 @@
         <v>1406</v>
       </c>
       <c r="G559" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H559" t="s">
         <v>1425</v>
       </c>
       <c r="J559" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K559">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L559">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30441,7 +30447,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30449,26 +30455,29 @@
       <c r="C560" t="s">
         <v>1405</v>
       </c>
+      <c r="D560" t="s">
+        <v>1008</v>
+      </c>
       <c r="E560" t="s">
         <v>1405</v>
       </c>
       <c r="F560" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G560" t="s">
+        <v>1428</v>
       </c>
       <c r="H560" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J560" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K560">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L560">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M560">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30476,10 +30485,10 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B561" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C561" t="s">
         <v>1405</v>
@@ -30490,17 +30499,17 @@
       <c r="F561" t="s">
         <v>1431</v>
       </c>
-      <c r="G561" t="s">
-        <v>1435</v>
-      </c>
       <c r="H561" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J561" t="s">
+        <v>1433</v>
       </c>
       <c r="K561">
         <v>70</v>
       </c>
       <c r="L561">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M561">
         <v>45</v>
@@ -30511,10 +30520,10 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B562" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C562" t="s">
         <v>1405</v>
@@ -30526,22 +30535,19 @@
         <v>1431</v>
       </c>
       <c r="G562" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H562" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J562" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M562">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30549,7 +30555,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30564,22 +30570,22 @@
         <v>1431</v>
       </c>
       <c r="G563" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H563" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J563" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K563">
         <v>70</v>
       </c>
       <c r="L563">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M563">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30587,7 +30593,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B564" t="s">
         <v>66</v>
@@ -30599,25 +30605,25 @@
         <v>1405</v>
       </c>
       <c r="F564" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G564" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H564" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J564" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K564">
         <v>70</v>
       </c>
       <c r="L564">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M564">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P564" s="19">
         <v>46155</v>
@@ -30625,7 +30631,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B565" t="s">
         <v>66</v>
@@ -30640,7 +30646,7 @@
         <v>1445</v>
       </c>
       <c r="G565" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H565" t="s">
         <v>1447</v>
@@ -30652,17 +30658,55 @@
         <v>70</v>
       </c>
       <c r="L565">
+        <v>36.5</v>
+      </c>
+      <c r="M565">
+        <v>7</v>
+      </c>
+      <c r="P565" s="19">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="566" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A566" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B566" t="s">
+        <v>66</v>
+      </c>
+      <c r="C566" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E566" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F566" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G566" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H566" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J566" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K566">
+        <v>70</v>
+      </c>
+      <c r="L566">
         <v>40.5</v>
       </c>
-      <c r="M565">
+      <c r="M566">
         <v>5</v>
       </c>
-      <c r="P565" s="19">
+      <c r="P566" s="19">
         <v>46175</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R565" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R566" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D800C6B5-F5B0-DB4B-BE21-DB734E65053B}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{241DD28C-034F-F24A-AA74-B7C68B5074A7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$566</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$567</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10367" uniqueCount="2365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10381" uniqueCount="2368">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7140,6 +7140,15 @@
   </si>
   <si>
     <t>Sauvignon Blanc - Colombard</t>
+  </si>
+  <si>
+    <t>733005NM</t>
+  </si>
+  <si>
+    <t>Armagnac</t>
+  </si>
+  <si>
+    <t>VSOP</t>
   </si>
 </sst>
 </file>
@@ -7905,7 +7914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R566"/>
+  <dimension ref="A1:R568"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23903,11 +23912,11 @@
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
-        <v>1032</v>
+      <c r="A398">
+        <v>73300425</v>
       </c>
       <c r="B398" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C398" t="s">
         <v>978</v>
@@ -23916,36 +23925,36 @@
         <v>979</v>
       </c>
       <c r="E398" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F398" t="s">
         <v>1033</v>
       </c>
       <c r="G398" t="s">
-        <v>1034</v>
+        <v>1135</v>
       </c>
       <c r="H398" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J398" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J398">
+        <v>2025</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M398">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399">
-        <v>13300125</v>
+      <c r="A399" t="s">
+        <v>1032</v>
       </c>
       <c r="B399" t="s">
         <v>66</v>
@@ -23963,33 +23972,33 @@
         <v>1033</v>
       </c>
       <c r="G399" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H399" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J399">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J399" t="s">
+        <v>98</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M399">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>1038</v>
+      <c r="A400">
+        <v>13300125</v>
       </c>
       <c r="B400" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C400" t="s">
         <v>978</v>
@@ -24001,33 +24010,33 @@
         <v>57</v>
       </c>
       <c r="F400" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G400" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H400" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J400" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J400">
+        <v>2025</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M400">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P400" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A401">
-        <v>24003025</v>
+      <c r="A401" t="s">
+        <v>1038</v>
       </c>
       <c r="B401" t="s">
         <v>55</v>
@@ -24036,7 +24045,7 @@
         <v>978</v>
       </c>
       <c r="D401" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E401" t="s">
         <v>57</v>
@@ -24045,16 +24054,13 @@
         <v>58</v>
       </c>
       <c r="G401" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H401" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I401" t="s">
-        <v>69</v>
-      </c>
-      <c r="J401">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J401" t="s">
+        <v>339</v>
       </c>
       <c r="K401">
         <v>75</v>
@@ -24062,13 +24068,16 @@
       <c r="L401">
         <v>6.2</v>
       </c>
+      <c r="M401">
+        <v>0</v>
+      </c>
       <c r="P401" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A402" t="s">
-        <v>1044</v>
+      <c r="A402">
+        <v>24003025</v>
       </c>
       <c r="B402" t="s">
         <v>55</v>
@@ -24077,39 +24086,39 @@
         <v>978</v>
       </c>
       <c r="D402" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E402" t="s">
         <v>57</v>
       </c>
       <c r="F402" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G402" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H402" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J402" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I402" t="s">
+        <v>69</v>
+      </c>
+      <c r="J402">
+        <v>2025</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>7.55</v>
-      </c>
-      <c r="M402">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P402" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B403" t="s">
         <v>55</v>
@@ -24118,28 +24127,28 @@
         <v>978</v>
       </c>
       <c r="D403" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E403" t="s">
         <v>57</v>
       </c>
       <c r="F403" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G403" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H403" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J403" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M403">
         <v>0</v>
@@ -24150,7 +24159,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B404" t="s">
         <v>55</v>
@@ -24159,28 +24168,28 @@
         <v>978</v>
       </c>
       <c r="D404" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E404" t="s">
         <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G404" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H404" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J404" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M404">
         <v>0</v>
@@ -24191,7 +24200,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B405" t="s">
         <v>55</v>
@@ -24200,42 +24209,39 @@
         <v>978</v>
       </c>
       <c r="D405" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E405" t="s">
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G405" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H405" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I405" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J405" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M405">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A406">
-        <v>27701225</v>
+      <c r="A406" t="s">
+        <v>1053</v>
       </c>
       <c r="B406" t="s">
         <v>55</v>
@@ -24244,39 +24250,42 @@
         <v>978</v>
       </c>
       <c r="D406" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E406" t="s">
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G406" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H406" t="s">
         <v>1055</v>
       </c>
-      <c r="J406">
-        <v>2025</v>
+      <c r="I406" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J406" t="s">
+        <v>286</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M406">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P406" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A407" t="s">
-        <v>1060</v>
+      <c r="A407">
+        <v>27701225</v>
       </c>
       <c r="B407" t="s">
         <v>55</v>
@@ -24285,28 +24294,28 @@
         <v>978</v>
       </c>
       <c r="D407" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E407" t="s">
         <v>57</v>
       </c>
       <c r="F407" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G407" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H407" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J407" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J407">
+        <v>2025</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M407">
         <v>0</v>
@@ -24317,7 +24326,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B408" t="s">
         <v>55</v>
@@ -24326,28 +24335,28 @@
         <v>978</v>
       </c>
       <c r="D408" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E408" t="s">
         <v>57</v>
       </c>
       <c r="F408" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G408" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H408" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J408" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M408">
         <v>0</v>
@@ -24358,7 +24367,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B409" t="s">
         <v>55</v>
@@ -24373,22 +24382,22 @@
         <v>57</v>
       </c>
       <c r="F409" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G409" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H409" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J409" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K409">
         <v>75</v>
       </c>
       <c r="L409">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M409">
         <v>0</v>
@@ -24398,8 +24407,8 @@
       </c>
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A410">
-        <v>68002225</v>
+      <c r="A410" t="s">
+        <v>1065</v>
       </c>
       <c r="B410" t="s">
         <v>55</v>
@@ -24411,13 +24420,13 @@
         <v>1057</v>
       </c>
       <c r="E410" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F410" t="s">
         <v>1066</v>
       </c>
       <c r="G410" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H410" t="s">
         <v>1068</v>
@@ -24429,7 +24438,7 @@
         <v>75</v>
       </c>
       <c r="L410">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M410">
         <v>0</v>
@@ -24440,7 +24449,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B411" t="s">
         <v>55</v>
@@ -24455,13 +24464,13 @@
         <v>63</v>
       </c>
       <c r="F411" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G411" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H411" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J411" t="s">
         <v>339</v>
@@ -24470,7 +24479,7 @@
         <v>75</v>
       </c>
       <c r="L411">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M411">
         <v>0</v>
@@ -24481,7 +24490,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B412" t="s">
         <v>55</v>
@@ -24499,13 +24508,13 @@
         <v>1070</v>
       </c>
       <c r="G412" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H412" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J412">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J412" t="s">
+        <v>339</v>
       </c>
       <c r="K412">
         <v>75</v>
@@ -24521,8 +24530,8 @@
       </c>
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A413" t="s">
-        <v>1075</v>
+      <c r="A413">
+        <v>68002424</v>
       </c>
       <c r="B413" t="s">
         <v>55</v>
@@ -24540,19 +24549,19 @@
         <v>1070</v>
       </c>
       <c r="G413" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H413" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J413" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J413">
+        <v>2024</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M413">
         <v>0</v>
@@ -24562,8 +24571,8 @@
       </c>
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A414">
-        <v>68002623</v>
+      <c r="A414" t="s">
+        <v>1075</v>
       </c>
       <c r="B414" t="s">
         <v>55</v>
@@ -24578,25 +24587,22 @@
         <v>63</v>
       </c>
       <c r="F414" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G414" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H414" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I414" t="s">
-        <v>69</v>
-      </c>
-      <c r="J414">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J414" t="s">
+        <v>564</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M414">
         <v>0</v>
@@ -24607,7 +24613,7 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B415" t="s">
         <v>55</v>
@@ -24619,28 +24625,28 @@
         <v>1057</v>
       </c>
       <c r="E415" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F415" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G415" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H415" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I415" t="s">
         <v>69</v>
       </c>
       <c r="J415">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M415">
         <v>0</v>
@@ -24650,8 +24656,8 @@
       </c>
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A416" t="s">
-        <v>1083</v>
+      <c r="A416">
+        <v>68002825</v>
       </c>
       <c r="B416" t="s">
         <v>55</v>
@@ -24666,22 +24672,25 @@
         <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G416" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H416" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J416" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I416" t="s">
+        <v>69</v>
+      </c>
+      <c r="J416">
+        <v>2025</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M416">
         <v>0</v>
@@ -24691,8 +24700,8 @@
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A417">
-        <v>68003025</v>
+      <c r="A417" t="s">
+        <v>1083</v>
       </c>
       <c r="B417" t="s">
         <v>55</v>
@@ -24704,13 +24713,13 @@
         <v>1057</v>
       </c>
       <c r="E417" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F417" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G417" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H417" t="s">
         <v>1085</v>
@@ -24733,7 +24742,7 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B418" t="s">
         <v>55</v>
@@ -24751,10 +24760,10 @@
         <v>1078</v>
       </c>
       <c r="G418" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H418" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J418" t="s">
         <v>339</v>
@@ -24763,7 +24772,7 @@
         <v>75</v>
       </c>
       <c r="L418">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M418">
         <v>0</v>
@@ -24773,8 +24782,8 @@
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
-        <v>1089</v>
+      <c r="A419">
+        <v>680031225</v>
       </c>
       <c r="B419" t="s">
         <v>55</v>
@@ -24786,25 +24795,25 @@
         <v>1057</v>
       </c>
       <c r="E419" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F419" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G419" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H419" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J419" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M419">
         <v>0</v>
@@ -24815,10 +24824,10 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B420" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C420" t="s">
         <v>978</v>
@@ -24833,22 +24842,22 @@
         <v>1066</v>
       </c>
       <c r="G420" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H420" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J420">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J420" t="s">
+        <v>98</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M420">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24856,7 +24865,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24865,31 +24874,31 @@
         <v>978</v>
       </c>
       <c r="D421" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E421" t="s">
         <v>57</v>
       </c>
       <c r="F421" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G421" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H421" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J421" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J421">
+        <v>2025</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M421">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24897,7 +24906,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B422" t="s">
         <v>66</v>
@@ -24915,22 +24924,22 @@
         <v>1033</v>
       </c>
       <c r="G422" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H422" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J422">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J422" t="s">
+        <v>98</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M422">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
@@ -24938,7 +24947,7 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B423" t="s">
         <v>66</v>
@@ -24953,22 +24962,25 @@
         <v>57</v>
       </c>
       <c r="F423" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G423" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H423" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J423" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J423">
+        <v>2025</v>
       </c>
       <c r="K423">
         <v>75</v>
       </c>
       <c r="L423">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M423">
+        <v>264</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
@@ -24976,7 +24988,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B424" t="s">
         <v>66</v>
@@ -24991,104 +25003,101 @@
         <v>57</v>
       </c>
       <c r="F424" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G424" t="s">
         <v>1100</v>
       </c>
       <c r="H424" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J424" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K424">
         <v>75</v>
       </c>
       <c r="L424">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P424" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A425">
-        <v>53800623</v>
+      <c r="A425" t="s">
+        <v>1102</v>
       </c>
       <c r="B425" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C425" t="s">
         <v>978</v>
       </c>
       <c r="D425" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E425" t="s">
         <v>57</v>
       </c>
       <c r="F425" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G425" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H425" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J425" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K425">
         <v>75</v>
       </c>
       <c r="L425">
-        <v>11</v>
-      </c>
-      <c r="M425">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P425" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
-        <v>1107</v>
+      <c r="A426">
+        <v>53800623</v>
       </c>
       <c r="B426" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C426" t="s">
         <v>978</v>
       </c>
       <c r="D426" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E426" t="s">
         <v>57</v>
       </c>
       <c r="F426" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G426" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H426" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J426" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K426">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L426">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M426">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
@@ -25096,7 +25105,7 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B427" t="s">
         <v>66</v>
@@ -25114,22 +25123,22 @@
         <v>980</v>
       </c>
       <c r="G427" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H427" t="s">
-        <v>985</v>
-      </c>
-      <c r="J427">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J427" t="s">
+        <v>564</v>
       </c>
       <c r="K427">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L427">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M427">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
@@ -25137,7 +25146,7 @@
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B428" t="s">
         <v>66</v>
@@ -25146,75 +25155,72 @@
         <v>978</v>
       </c>
       <c r="D428" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E428" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F428" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G428" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H428" t="s">
-        <v>989</v>
-      </c>
-      <c r="J428" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J428">
+        <v>2025</v>
       </c>
       <c r="K428">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L428">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M428">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P428" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A429">
-        <v>71501125</v>
+      <c r="A429" t="s">
+        <v>1111</v>
       </c>
       <c r="B429" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C429" t="s">
         <v>978</v>
       </c>
       <c r="D429" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E429" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F429" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G429" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H429" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I429" t="s">
-        <v>69</v>
-      </c>
-      <c r="J429">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J429" t="s">
+        <v>564</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M429">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P429" s="19">
         <v>46155</v>
@@ -25222,7 +25228,7 @@
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25234,17 +25240,20 @@
         <v>979</v>
       </c>
       <c r="E430" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F430" t="s">
         <v>980</v>
       </c>
       <c r="G430" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H430" t="s">
         <v>1113</v>
       </c>
+      <c r="I430" t="s">
+        <v>69</v>
+      </c>
       <c r="J430">
         <v>2025</v>
       </c>
@@ -25252,7 +25261,7 @@
         <v>75</v>
       </c>
       <c r="L430">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M430">
         <v>324</v>
@@ -25263,7 +25272,7 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25281,7 +25290,7 @@
         <v>980</v>
       </c>
       <c r="G431" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H431" t="s">
         <v>1113</v>
@@ -25304,7 +25313,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25319,10 +25328,10 @@
         <v>63</v>
       </c>
       <c r="F432" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G432" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H432" t="s">
         <v>1113</v>
@@ -25345,7 +25354,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25357,13 +25366,13 @@
         <v>979</v>
       </c>
       <c r="E433" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F433" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G433" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H433" t="s">
         <v>1113</v>
@@ -25386,7 +25395,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25401,10 +25410,10 @@
         <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G434" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H434" t="s">
         <v>1113</v>
@@ -25427,7 +25436,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25439,13 +25448,13 @@
         <v>979</v>
       </c>
       <c r="E435" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F435" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G435" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H435" t="s">
         <v>1113</v>
@@ -25457,7 +25466,7 @@
         <v>75</v>
       </c>
       <c r="L435">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M435">
         <v>324</v>
@@ -25468,7 +25477,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25483,7 +25492,7 @@
         <v>63</v>
       </c>
       <c r="F436" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G436" t="s">
         <v>1120</v>
@@ -25498,7 +25507,7 @@
         <v>75</v>
       </c>
       <c r="L436">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M436">
         <v>324</v>
@@ -25509,7 +25518,7 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25524,7 +25533,7 @@
         <v>63</v>
       </c>
       <c r="F437" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G437" t="s">
         <v>1120</v>
@@ -25532,9 +25541,6 @@
       <c r="H437" t="s">
         <v>1113</v>
       </c>
-      <c r="I437" t="s">
-        <v>69</v>
-      </c>
       <c r="J437">
         <v>2025</v>
       </c>
@@ -25553,7 +25559,7 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25565,10 +25571,10 @@
         <v>979</v>
       </c>
       <c r="E438" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F438" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G438" t="s">
         <v>1120</v>
@@ -25577,7 +25583,7 @@
         <v>1113</v>
       </c>
       <c r="I438" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J438">
         <v>2025</v>
@@ -25586,7 +25592,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M438">
         <v>324</v>
@@ -25597,7 +25603,7 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B439" t="s">
         <v>55</v>
@@ -25612,7 +25618,7 @@
         <v>57</v>
       </c>
       <c r="F439" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G439" t="s">
         <v>1120</v>
@@ -25630,7 +25636,7 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M439">
         <v>324</v>
@@ -25641,10 +25647,10 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B440" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C440" t="s">
         <v>978</v>
@@ -25653,16 +25659,19 @@
         <v>979</v>
       </c>
       <c r="E440" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F440" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G440" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H440" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I440" t="s">
+        <v>175</v>
       </c>
       <c r="J440">
         <v>2025</v>
@@ -25671,7 +25680,7 @@
         <v>75</v>
       </c>
       <c r="L440">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M440">
         <v>324</v>
@@ -25681,8 +25690,8 @@
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>1125</v>
+      <c r="A441">
+        <v>16000125</v>
       </c>
       <c r="B441" t="s">
         <v>66</v>
@@ -25700,22 +25709,22 @@
         <v>980</v>
       </c>
       <c r="G441" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H441" t="s">
-        <v>985</v>
-      </c>
-      <c r="J441" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J441">
+        <v>2025</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M441">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P441" s="19">
         <v>46155</v>
@@ -25723,7 +25732,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B442" t="s">
         <v>66</v>
@@ -25741,22 +25750,22 @@
         <v>980</v>
       </c>
       <c r="G442" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H442" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J442" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M442">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P442" s="19">
         <v>46155</v>
@@ -25764,7 +25773,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B443" t="s">
         <v>66</v>
@@ -25782,22 +25791,22 @@
         <v>980</v>
       </c>
       <c r="G443" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H443" t="s">
-        <v>985</v>
-      </c>
-      <c r="J443">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J443" t="s">
+        <v>286</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M443">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P443" s="19">
         <v>46155</v>
@@ -25805,7 +25814,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B444" t="s">
         <v>66</v>
@@ -25820,25 +25829,25 @@
         <v>63</v>
       </c>
       <c r="F444" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G444" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H444" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J444" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J444">
+        <v>2025</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M444">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P444" s="19">
         <v>46155</v>
@@ -25846,7 +25855,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B445" t="s">
         <v>66</v>
@@ -25861,25 +25870,25 @@
         <v>63</v>
       </c>
       <c r="F445" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G445" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H445" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J445" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K445">
         <v>75</v>
       </c>
       <c r="L445">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M445">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P445" s="19">
         <v>46155</v>
@@ -25887,7 +25896,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B446" t="s">
         <v>66</v>
@@ -25905,22 +25914,22 @@
         <v>980</v>
       </c>
       <c r="G446" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H446" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J446" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K446">
         <v>75</v>
       </c>
       <c r="L446">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M446">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P446" s="19">
         <v>46155</v>
@@ -25928,7 +25937,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B447" t="s">
         <v>66</v>
@@ -25946,25 +25955,22 @@
         <v>980</v>
       </c>
       <c r="G447" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H447" t="s">
-        <v>982</v>
-      </c>
-      <c r="I447" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J447" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K447">
         <v>75</v>
       </c>
       <c r="L447">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M447">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P447" s="19">
         <v>46155</v>
@@ -25972,7 +25978,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B448" t="s">
         <v>66</v>
@@ -25990,13 +25996,13 @@
         <v>980</v>
       </c>
       <c r="G448" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H448" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I448" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J448" t="s">
         <v>61</v>
@@ -26005,10 +26011,10 @@
         <v>75</v>
       </c>
       <c r="L448">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M448">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26016,7 +26022,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26031,25 +26037,28 @@
         <v>63</v>
       </c>
       <c r="F449" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G449" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H449" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I449" t="s">
+        <v>1012</v>
       </c>
       <c r="J449" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M449">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26057,7 +26066,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26066,19 +26075,19 @@
         <v>978</v>
       </c>
       <c r="D450" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E450" t="s">
         <v>63</v>
       </c>
       <c r="F450" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G450" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H450" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J450" t="s">
         <v>217</v>
@@ -26087,10 +26096,10 @@
         <v>75</v>
       </c>
       <c r="L450">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M450">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26098,7 +26107,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26113,25 +26122,25 @@
         <v>63</v>
       </c>
       <c r="F451" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G451" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H451" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J451" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M451">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26139,7 +26148,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B452" t="s">
         <v>66</v>
@@ -26157,22 +26166,22 @@
         <v>1147</v>
       </c>
       <c r="G452" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H452" t="s">
         <v>1149</v>
       </c>
       <c r="J452" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M452">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
@@ -26180,37 +26189,40 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B453" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C453" t="s">
         <v>978</v>
       </c>
       <c r="D453" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E453" t="s">
         <v>63</v>
       </c>
       <c r="F453" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G453" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H453" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J453" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M453">
+        <v>36</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
@@ -26218,7 +26230,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B454" t="s">
         <v>55</v>
@@ -26233,25 +26245,22 @@
         <v>63</v>
       </c>
       <c r="F454" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G454" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H454" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J454" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>12.5</v>
-      </c>
-      <c r="M454">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
@@ -26259,7 +26268,7 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B455" t="s">
         <v>55</v>
@@ -26274,22 +26283,22 @@
         <v>63</v>
       </c>
       <c r="F455" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G455" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H455" t="s">
         <v>1064</v>
       </c>
       <c r="J455" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K455">
         <v>75</v>
       </c>
       <c r="L455">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M455">
         <v>0</v>
@@ -26300,7 +26309,7 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B456" t="s">
         <v>55</v>
@@ -26318,19 +26327,19 @@
         <v>1078</v>
       </c>
       <c r="G456" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H456" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J456">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J456" t="s">
+        <v>209</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M456">
         <v>0</v>
@@ -26341,10 +26350,10 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B457" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C457" t="s">
         <v>978</v>
@@ -26356,25 +26365,25 @@
         <v>63</v>
       </c>
       <c r="F457" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G457" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H457" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J457" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J457">
+        <v>2014</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M457">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P457" s="19">
         <v>46155</v>
@@ -26382,10 +26391,10 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B458" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C458" t="s">
         <v>978</v>
@@ -26400,13 +26409,10 @@
         <v>1066</v>
       </c>
       <c r="G458" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H458" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I458" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J458" t="s">
         <v>61</v>
@@ -26415,18 +26421,18 @@
         <v>75</v>
       </c>
       <c r="L458">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M458">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P458" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A459">
-        <v>27701324</v>
+      <c r="A459" t="s">
+        <v>1164</v>
       </c>
       <c r="B459" t="s">
         <v>55</v>
@@ -26444,19 +26450,22 @@
         <v>1066</v>
       </c>
       <c r="G459" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H459" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J459">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I459" t="s">
+        <v>69</v>
+      </c>
+      <c r="J459" t="s">
+        <v>61</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M459">
         <v>0</v>
@@ -26466,8 +26475,8 @@
       </c>
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A460" t="s">
-        <v>1167</v>
+      <c r="A460">
+        <v>27701324</v>
       </c>
       <c r="B460" t="s">
         <v>55</v>
@@ -26485,22 +26494,19 @@
         <v>1066</v>
       </c>
       <c r="G460" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H460" t="s">
         <v>1055</v>
       </c>
-      <c r="I460" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J460" t="s">
-        <v>98</v>
+      <c r="J460">
+        <v>2024</v>
       </c>
       <c r="K460">
         <v>75</v>
       </c>
       <c r="L460">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M460">
         <v>0</v>
@@ -26511,31 +26517,31 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B461" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C461" t="s">
         <v>978</v>
       </c>
       <c r="D461" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E461" t="s">
         <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G461" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H461" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I461" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J461" t="s">
         <v>98</v>
@@ -26544,10 +26550,10 @@
         <v>75</v>
       </c>
       <c r="L461">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M461">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P461" s="19">
         <v>46155</v>
@@ -26555,7 +26561,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B462" t="s">
         <v>66</v>
@@ -26570,28 +26576,28 @@
         <v>63</v>
       </c>
       <c r="F462" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G462" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H462" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I462" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J462" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K462">
         <v>75</v>
       </c>
       <c r="L462">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M462">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P462" s="19">
         <v>46155</v>
@@ -26599,10 +26605,10 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B463" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C463" t="s">
         <v>978</v>
@@ -26614,25 +26620,28 @@
         <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G463" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H463" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I463" t="s">
+        <v>69</v>
       </c>
       <c r="J463" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K463">
         <v>75</v>
       </c>
       <c r="L463">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M463">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P463" s="19">
         <v>46155</v>
@@ -26640,7 +26649,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26658,19 +26667,22 @@
         <v>1175</v>
       </c>
       <c r="G464" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H464" t="s">
         <v>1177</v>
       </c>
       <c r="J464" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K464">
         <v>75</v>
       </c>
       <c r="L464">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M464">
+        <v>0</v>
       </c>
       <c r="P464" s="19">
         <v>46155</v>
@@ -26678,10 +26690,10 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B465" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C465" t="s">
         <v>978</v>
@@ -26693,28 +26705,22 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G465" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H465" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I465" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J465" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K465">
         <v>75</v>
       </c>
       <c r="L465">
-        <v>7.6</v>
-      </c>
-      <c r="M465">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P465" s="19">
         <v>46155</v>
@@ -26722,10 +26728,10 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B466" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C466" t="s">
         <v>978</v>
@@ -26737,25 +26743,28 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G466" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H466" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I466" t="s">
+        <v>69</v>
       </c>
       <c r="J466" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K466">
         <v>75</v>
       </c>
       <c r="L466">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M466">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P466" s="19">
         <v>46155</v>
@@ -26763,7 +26772,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B467" t="s">
         <v>55</v>
@@ -26781,22 +26790,22 @@
         <v>1185</v>
       </c>
       <c r="G467" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H467" t="s">
         <v>1049</v>
       </c>
       <c r="J467" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K467">
         <v>75</v>
       </c>
       <c r="L467">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M467">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P467" s="19">
         <v>46155</v>
@@ -26804,10 +26813,10 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B468" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C468" t="s">
         <v>978</v>
@@ -26819,25 +26828,25 @@
         <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G468" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H468" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I468" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J468" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M468">
+        <v>6</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26845,7 +26854,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B469" t="s">
         <v>66</v>
@@ -26860,25 +26869,25 @@
         <v>63</v>
       </c>
       <c r="F469" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G469" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H469" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I469" t="s">
+        <v>777</v>
       </c>
       <c r="J469" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M469">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
@@ -26886,7 +26895,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B470" t="s">
         <v>66</v>
@@ -26901,25 +26910,25 @@
         <v>63</v>
       </c>
       <c r="F470" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G470" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H470" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I470" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J470" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M470">
+        <v>53</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
@@ -26927,7 +26936,7 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B471" t="s">
         <v>66</v>
@@ -26942,28 +26951,25 @@
         <v>63</v>
       </c>
       <c r="F471" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G471" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H471" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I471" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J471" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>6.5</v>
-      </c>
-      <c r="M471">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -26971,10 +26977,10 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B472" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C472" t="s">
         <v>978</v>
@@ -26989,30 +26995,33 @@
         <v>1122</v>
       </c>
       <c r="G472" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H472" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I472" t="s">
+        <v>175</v>
       </c>
       <c r="J472" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M472">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A473">
-        <v>16003124</v>
+      <c r="A473" t="s">
+        <v>1202</v>
       </c>
       <c r="B473" t="s">
         <v>55</v>
@@ -27024,19 +27033,19 @@
         <v>979</v>
       </c>
       <c r="E473" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F473" t="s">
         <v>1122</v>
       </c>
       <c r="G473" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H473" t="s">
         <v>1204</v>
       </c>
       <c r="J473" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K473">
         <v>75</v>
@@ -27052,11 +27061,11 @@
       </c>
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A474" t="s">
-        <v>1206</v>
+      <c r="A474">
+        <v>16003124</v>
       </c>
       <c r="B474" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C474" t="s">
         <v>978</v>
@@ -27065,31 +27074,28 @@
         <v>979</v>
       </c>
       <c r="E474" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F474" t="s">
         <v>1122</v>
       </c>
       <c r="G474" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H474" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I474" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J474" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M474">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27097,10 +27103,10 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B475" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C475" t="s">
         <v>978</v>
@@ -27115,25 +27121,25 @@
         <v>1122</v>
       </c>
       <c r="G475" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H475" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I475" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J475" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M475">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27141,10 +27147,10 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B476" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C476" t="s">
         <v>978</v>
@@ -27159,13 +27165,13 @@
         <v>1122</v>
       </c>
       <c r="G476" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H476" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I476" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J476" t="s">
         <v>61</v>
@@ -27174,7 +27180,7 @@
         <v>75</v>
       </c>
       <c r="L476">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M476">
         <v>171</v>
@@ -27185,10 +27191,10 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B477" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C477" t="s">
         <v>978</v>
@@ -27203,19 +27209,25 @@
         <v>1122</v>
       </c>
       <c r="G477" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H477" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I477" t="s">
+        <v>175</v>
       </c>
       <c r="J477" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M477">
+        <v>171</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27223,10 +27235,10 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B478" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C478" t="s">
         <v>978</v>
@@ -27238,28 +27250,22 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G478" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H478" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I478" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J478" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>24.08</v>
-      </c>
-      <c r="M478">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27267,10 +27273,10 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B479" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C479" t="s">
         <v>978</v>
@@ -27282,19 +27288,28 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G479" t="s">
+        <v>1216</v>
       </c>
       <c r="H479" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I479" t="s">
+        <v>175</v>
       </c>
       <c r="J479" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M479">
+        <v>12</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
@@ -27302,10 +27317,10 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B480" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C480" t="s">
         <v>978</v>
@@ -27317,30 +27332,27 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H480" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J480" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>7.05</v>
-      </c>
-      <c r="M480">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A481">
-        <v>27100523</v>
+      <c r="A481" t="s">
+        <v>1221</v>
       </c>
       <c r="B481" t="s">
         <v>66</v>
@@ -27355,36 +27367,33 @@
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G481" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H481" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I481" t="s">
-        <v>777</v>
-      </c>
-      <c r="J481">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J481" t="s">
+        <v>217</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M481">
+        <v>30</v>
       </c>
       <c r="P481" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A482" t="s">
-        <v>1225</v>
+      <c r="A482">
+        <v>27100523</v>
       </c>
       <c r="B482" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
@@ -27396,33 +27405,36 @@
         <v>63</v>
       </c>
       <c r="F482" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G482" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H482" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J482" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I482" t="s">
+        <v>777</v>
+      </c>
+      <c r="J482">
+        <v>2023</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P482" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B483" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C483" t="s">
         <v>978</v>
@@ -27434,33 +27446,33 @@
         <v>63</v>
       </c>
       <c r="F483" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G483" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H483" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J483" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>7.35</v>
-      </c>
-      <c r="M483">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>1229</v>
+      </c>
       <c r="B484" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C484" t="s">
         <v>978</v>
@@ -27475,19 +27487,19 @@
         <v>1119</v>
       </c>
       <c r="G484" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H484" t="s">
         <v>1231</v>
       </c>
       <c r="J484" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K484">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L484">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M484">
         <v>2215</v>
@@ -27497,11 +27509,8 @@
       </c>
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A485" t="s">
-        <v>1233</v>
-      </c>
       <c r="B485" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C485" t="s">
         <v>978</v>
@@ -27516,22 +27525,22 @@
         <v>1119</v>
       </c>
       <c r="G485" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H485" t="s">
         <v>1231</v>
       </c>
-      <c r="J485">
-        <v>2023</v>
+      <c r="J485" t="s">
+        <v>61</v>
       </c>
       <c r="K485">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L485">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M485">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
@@ -27539,7 +27548,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B486" t="s">
         <v>66</v>
@@ -27557,25 +27566,22 @@
         <v>1119</v>
       </c>
       <c r="G486" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H486" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I486" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J486" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J486">
+        <v>2023</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M486">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
@@ -27583,10 +27589,10 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B487" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27601,19 +27607,25 @@
         <v>1119</v>
       </c>
       <c r="G487" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H487" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I487" t="s">
+        <v>1238</v>
       </c>
       <c r="J487" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M487">
+        <v>205</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
@@ -27621,7 +27633,7 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B488" t="s">
         <v>55</v>
@@ -27639,10 +27651,10 @@
         <v>1119</v>
       </c>
       <c r="G488" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H488" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J488" t="s">
         <v>98</v>
@@ -27651,21 +27663,18 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>14.6</v>
-      </c>
-      <c r="M488">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A489">
-        <v>43700124</v>
+      <c r="A489" t="s">
+        <v>1242</v>
       </c>
       <c r="B489" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C489" t="s">
         <v>978</v>
@@ -27677,22 +27686,25 @@
         <v>63</v>
       </c>
       <c r="F489" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G489" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H489" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J489">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J489" t="s">
+        <v>98</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M489">
+        <v>0</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
@@ -27700,10 +27712,10 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B490" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C490" t="s">
         <v>978</v>
@@ -27718,19 +27730,19 @@
         <v>1028</v>
       </c>
       <c r="G490" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H490" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J490">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
@@ -27738,7 +27750,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B491" t="s">
         <v>55</v>
@@ -27756,30 +27768,30 @@
         <v>1028</v>
       </c>
       <c r="G491" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H491" t="s">
         <v>1031</v>
       </c>
       <c r="J491">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A492" t="s">
-        <v>1247</v>
+      <c r="A492">
+        <v>43700524</v>
       </c>
       <c r="B492" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C492" t="s">
         <v>978</v>
@@ -27788,28 +27800,25 @@
         <v>979</v>
       </c>
       <c r="E492" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F492" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G492" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H492" t="s">
-        <v>982</v>
-      </c>
-      <c r="J492" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J492">
+        <v>2024</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>3.8</v>
-      </c>
-      <c r="M492">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27817,7 +27826,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B493" t="s">
         <v>66</v>
@@ -27835,22 +27844,22 @@
         <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H493" t="s">
-        <v>985</v>
-      </c>
-      <c r="J493">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J493" t="s">
+        <v>98</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M493">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27858,7 +27867,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B494" t="s">
         <v>66</v>
@@ -27876,10 +27885,10 @@
         <v>980</v>
       </c>
       <c r="G494" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H494" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J494">
         <v>2025</v>
@@ -27888,10 +27897,10 @@
         <v>75</v>
       </c>
       <c r="L494">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M494">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -27899,10 +27908,10 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B495" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C495" t="s">
         <v>978</v>
@@ -27917,22 +27926,22 @@
         <v>980</v>
       </c>
       <c r="G495" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H495" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J495" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J495">
+        <v>2025</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M495">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -27940,10 +27949,10 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B496" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C496" t="s">
         <v>978</v>
@@ -27958,22 +27967,22 @@
         <v>980</v>
       </c>
       <c r="G496" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H496" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J496" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K496">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L496">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M496">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -27981,7 +27990,7 @@
     </row>
     <row r="497" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -27999,22 +28008,22 @@
         <v>980</v>
       </c>
       <c r="G497" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H497" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J497" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K497">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L497">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M497">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28022,40 +28031,40 @@
     </row>
     <row r="498" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
       </c>
       <c r="C498" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D498" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E498" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F498" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G498" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H498" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J498" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K498">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L498">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M498">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
@@ -28063,7 +28072,7 @@
     </row>
     <row r="499" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28078,13 +28087,13 @@
         <v>57</v>
       </c>
       <c r="F499" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G499" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H499" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J499" t="s">
         <v>339</v>
@@ -28093,21 +28102,18 @@
         <v>75</v>
       </c>
       <c r="L499">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M499">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
       </c>
-      <c r="R499" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="500" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A500">
-        <v>24000925</v>
+      <c r="A500" t="s">
+        <v>1262</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28119,36 +28125,39 @@
         <v>1258</v>
       </c>
       <c r="E500" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F500" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G500" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H500" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J500">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J500" t="s">
+        <v>339</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M500">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
       </c>
+      <c r="R500" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A501" t="s">
-        <v>1266</v>
+      <c r="A501">
+        <v>24000925</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28160,28 +28169,28 @@
         <v>1258</v>
       </c>
       <c r="E501" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F501" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G501" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H501" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J501" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J501">
+        <v>2025</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M501">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
@@ -28189,7 +28198,7 @@
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B502" t="s">
         <v>66</v>
@@ -28204,33 +28213,33 @@
         <v>63</v>
       </c>
       <c r="F502" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G502" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H502" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J502" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M502">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A503">
-        <v>24001825</v>
+      <c r="A503" t="s">
+        <v>1270</v>
       </c>
       <c r="B503" t="s">
         <v>66</v>
@@ -28245,33 +28254,33 @@
         <v>63</v>
       </c>
       <c r="F503" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G503" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H503" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J503">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J503" t="s">
+        <v>98</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M503">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="504" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A504" t="s">
-        <v>1275</v>
+      <c r="A504">
+        <v>24001825</v>
       </c>
       <c r="B504" t="s">
         <v>66</v>
@@ -28286,22 +28295,25 @@
         <v>63</v>
       </c>
       <c r="F504" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G504" t="s">
+        <v>1274</v>
       </c>
       <c r="H504" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J504" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J504">
+        <v>2025</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M504">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28309,7 +28321,7 @@
     </row>
     <row r="505" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B505" t="s">
         <v>66</v>
@@ -28324,28 +28336,22 @@
         <v>63</v>
       </c>
       <c r="F505" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G505" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H505" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I505" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J505" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M505">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28353,7 +28359,7 @@
     </row>
     <row r="506" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B506" t="s">
         <v>66</v>
@@ -28362,28 +28368,34 @@
         <v>1257</v>
       </c>
       <c r="D506" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E506" t="s">
         <v>63</v>
       </c>
       <c r="F506" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G506" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H506" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I506" t="s">
+        <v>69</v>
       </c>
       <c r="J506" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M506">
+        <v>318</v>
       </c>
       <c r="P506" s="19">
         <v>46155</v>
@@ -28391,7 +28403,7 @@
     </row>
     <row r="507" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B507" t="s">
         <v>66</v>
@@ -28409,22 +28421,19 @@
         <v>1284</v>
       </c>
       <c r="G507" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H507" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J507" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>6.1</v>
-      </c>
-      <c r="M507">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P507" s="19">
         <v>46155</v>
@@ -28432,7 +28441,7 @@
     </row>
     <row r="508" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B508" t="s">
         <v>66</v>
@@ -28455,8 +28464,8 @@
       <c r="H508" t="s">
         <v>1289</v>
       </c>
-      <c r="J508">
-        <v>2024</v>
+      <c r="J508" t="s">
+        <v>87</v>
       </c>
       <c r="K508">
         <v>75</v>
@@ -28464,16 +28473,19 @@
       <c r="L508">
         <v>6.1</v>
       </c>
+      <c r="M508">
+        <v>133</v>
+      </c>
       <c r="P508" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="509" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B509" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C509" t="s">
         <v>1257</v>
@@ -28488,30 +28500,27 @@
         <v>1284</v>
       </c>
       <c r="G509" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H509" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J509" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J509">
+        <v>2024</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>13.2</v>
-      </c>
-      <c r="M509">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P509" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B510" t="s">
         <v>55</v>
@@ -28529,19 +28538,19 @@
         <v>1284</v>
       </c>
       <c r="G510" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H510" t="s">
         <v>1293</v>
       </c>
       <c r="J510" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M510">
         <v>0</v>
@@ -28552,7 +28561,7 @@
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B511" t="s">
         <v>55</v>
@@ -28567,22 +28576,22 @@
         <v>63</v>
       </c>
       <c r="F511" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G511" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H511" t="s">
         <v>1293</v>
       </c>
       <c r="J511" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M511">
         <v>0</v>
@@ -28592,49 +28601,49 @@
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A512">
-        <v>10702526</v>
+      <c r="A512" t="s">
+        <v>1296</v>
       </c>
       <c r="B512" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C512" t="s">
         <v>1257</v>
       </c>
       <c r="D512" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E512" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F512" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G512" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H512" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J512">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J512" t="s">
+        <v>61</v>
       </c>
       <c r="K512">
         <v>75</v>
       </c>
       <c r="L512">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M512">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A513" t="s">
-        <v>1301</v>
+      <c r="A513">
+        <v>10702526</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28643,31 +28652,31 @@
         <v>1257</v>
       </c>
       <c r="D513" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E513" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F513" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G513" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H513" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J513" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J513">
+        <v>2026</v>
       </c>
       <c r="K513">
         <v>75</v>
       </c>
       <c r="L513">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M513">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28675,7 +28684,7 @@
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28693,7 +28702,7 @@
         <v>1303</v>
       </c>
       <c r="G514" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H514" t="s">
         <v>1305</v>
@@ -28705,10 +28714,10 @@
         <v>75</v>
       </c>
       <c r="L514">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M514">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28716,7 +28725,7 @@
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28734,7 +28743,7 @@
         <v>1303</v>
       </c>
       <c r="G515" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H515" t="s">
         <v>1305</v>
@@ -28749,7 +28758,7 @@
         <v>8.6</v>
       </c>
       <c r="M515">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28757,7 +28766,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28775,13 +28784,13 @@
         <v>1303</v>
       </c>
       <c r="G516" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H516" t="s">
         <v>1305</v>
       </c>
       <c r="J516" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K516">
         <v>75</v>
@@ -28790,7 +28799,7 @@
         <v>8.6</v>
       </c>
       <c r="M516">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28798,7 +28807,7 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B517" t="s">
         <v>66</v>
@@ -28816,7 +28825,7 @@
         <v>1303</v>
       </c>
       <c r="G517" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H517" t="s">
         <v>1305</v>
@@ -28831,7 +28840,7 @@
         <v>8.6</v>
       </c>
       <c r="M517">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28839,7 +28848,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B518" t="s">
         <v>66</v>
@@ -28857,22 +28866,22 @@
         <v>1303</v>
       </c>
       <c r="G518" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H518" t="s">
         <v>1305</v>
       </c>
       <c r="J518" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K518">
         <v>75</v>
       </c>
       <c r="L518">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M518">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
@@ -28880,7 +28889,7 @@
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B519" t="s">
         <v>66</v>
@@ -28898,22 +28907,22 @@
         <v>1303</v>
       </c>
       <c r="G519" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H519" t="s">
         <v>1305</v>
       </c>
-      <c r="J519">
-        <v>2021</v>
+      <c r="J519" t="s">
+        <v>127</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M519">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -28921,7 +28930,7 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
@@ -28939,13 +28948,13 @@
         <v>1303</v>
       </c>
       <c r="G520" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H520" t="s">
         <v>1305</v>
       </c>
-      <c r="J520" t="s">
-        <v>109</v>
+      <c r="J520">
+        <v>2021</v>
       </c>
       <c r="K520">
         <v>75</v>
@@ -28954,7 +28963,7 @@
         <v>13</v>
       </c>
       <c r="M520">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -28962,7 +28971,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -28980,7 +28989,7 @@
         <v>1303</v>
       </c>
       <c r="G521" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H521" t="s">
         <v>1305</v>
@@ -28992,7 +29001,7 @@
         <v>75</v>
       </c>
       <c r="L521">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M521">
         <v>36</v>
@@ -29003,7 +29012,7 @@
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29015,28 +29024,28 @@
         <v>1302</v>
       </c>
       <c r="E522" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F522" t="s">
         <v>1303</v>
       </c>
       <c r="G522" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H522" t="s">
         <v>1305</v>
       </c>
       <c r="J522" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K522">
         <v>75</v>
       </c>
       <c r="L522">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M522">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29044,40 +29053,40 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
       </c>
       <c r="C523" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D523" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E523" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F523" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G523" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H523" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J523" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K523">
         <v>75</v>
       </c>
       <c r="L523">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M523">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29085,7 +29094,7 @@
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29093,17 +29102,20 @@
       <c r="C524" t="s">
         <v>1323</v>
       </c>
+      <c r="D524" t="s">
+        <v>1258</v>
+      </c>
       <c r="E524" t="s">
         <v>1323</v>
       </c>
       <c r="F524" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G524" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H524" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J524" t="s">
         <v>564</v>
@@ -29114,13 +29126,16 @@
       <c r="L524">
         <v>6.2</v>
       </c>
+      <c r="M524">
+        <v>4411</v>
+      </c>
       <c r="P524" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29135,10 +29150,10 @@
         <v>58</v>
       </c>
       <c r="G525" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H525" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J525" t="s">
         <v>564</v>
@@ -29147,7 +29162,7 @@
         <v>75</v>
       </c>
       <c r="L525">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29155,7 +29170,7 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
@@ -29167,25 +29182,22 @@
         <v>1323</v>
       </c>
       <c r="F526" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G526" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H526" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J526" t="s">
         <v>564</v>
       </c>
       <c r="K526">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L526">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M526">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29193,7 +29205,7 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
@@ -29208,22 +29220,22 @@
         <v>1332</v>
       </c>
       <c r="G527" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H527" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J527" t="s">
         <v>564</v>
       </c>
       <c r="K527">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L527">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M527">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29231,7 +29243,7 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29246,10 +29258,10 @@
         <v>1332</v>
       </c>
       <c r="G528" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H528" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J528" t="s">
         <v>564</v>
@@ -29258,10 +29270,10 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M528">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29269,10 +29281,10 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B529" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C529" t="s">
         <v>1323</v>
@@ -29284,10 +29296,10 @@
         <v>1332</v>
       </c>
       <c r="G529" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H529" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J529" t="s">
         <v>564</v>
@@ -29296,7 +29308,10 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M529">
+        <v>418</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29304,10 +29319,10 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B530" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C530" t="s">
         <v>1323</v>
@@ -29319,10 +29334,10 @@
         <v>1332</v>
       </c>
       <c r="G530" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H530" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J530" t="s">
         <v>564</v>
@@ -29331,10 +29346,7 @@
         <v>75</v>
       </c>
       <c r="L530">
-        <v>25.8</v>
-      </c>
-      <c r="M530">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
@@ -29342,7 +29354,7 @@
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29357,10 +29369,10 @@
         <v>1332</v>
       </c>
       <c r="G531" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H531" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J531" t="s">
         <v>564</v>
@@ -29369,10 +29381,10 @@
         <v>75</v>
       </c>
       <c r="L531">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M531">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29380,7 +29392,7 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29395,10 +29407,10 @@
         <v>1332</v>
       </c>
       <c r="G532" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H532" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J532" t="s">
         <v>564</v>
@@ -29407,10 +29419,10 @@
         <v>75</v>
       </c>
       <c r="L532">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M532">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
@@ -29418,7 +29430,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B533" t="s">
         <v>66</v>
@@ -29433,10 +29445,10 @@
         <v>1332</v>
       </c>
       <c r="G533" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H533" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J533" t="s">
         <v>564</v>
@@ -29445,10 +29457,10 @@
         <v>75</v>
       </c>
       <c r="L533">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M533">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P533" s="19">
         <v>46155</v>
@@ -29456,10 +29468,10 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B534" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C534" t="s">
         <v>1323</v>
@@ -29471,7 +29483,7 @@
         <v>1332</v>
       </c>
       <c r="G534" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H534" t="s">
         <v>1349</v>
@@ -29480,10 +29492,10 @@
         <v>564</v>
       </c>
       <c r="K534">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L534">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M534">
         <v>60</v>
@@ -29494,7 +29506,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B535" t="s">
         <v>55</v>
@@ -29509,7 +29521,7 @@
         <v>1332</v>
       </c>
       <c r="G535" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H535" t="s">
         <v>1349</v>
@@ -29518,10 +29530,10 @@
         <v>564</v>
       </c>
       <c r="K535">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L535">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M535">
         <v>60</v>
@@ -29532,7 +29544,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B536" t="s">
         <v>55</v>
@@ -29547,7 +29559,7 @@
         <v>1332</v>
       </c>
       <c r="G536" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H536" t="s">
         <v>1349</v>
@@ -29559,7 +29571,7 @@
         <v>75</v>
       </c>
       <c r="L536">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M536">
         <v>60</v>
@@ -29570,10 +29582,10 @@
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B537" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C537" t="s">
         <v>1323</v>
@@ -29585,10 +29597,10 @@
         <v>1332</v>
       </c>
       <c r="G537" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H537" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J537" t="s">
         <v>564</v>
@@ -29597,10 +29609,10 @@
         <v>75</v>
       </c>
       <c r="L537">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M537">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29608,7 +29620,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29623,10 +29635,10 @@
         <v>1332</v>
       </c>
       <c r="G538" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H538" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J538" t="s">
         <v>564</v>
@@ -29635,10 +29647,10 @@
         <v>75</v>
       </c>
       <c r="L538">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M538">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P538" s="19">
         <v>46155</v>
@@ -29646,7 +29658,7 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B539" t="s">
         <v>66</v>
@@ -29661,10 +29673,10 @@
         <v>1332</v>
       </c>
       <c r="G539" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H539" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J539" t="s">
         <v>564</v>
@@ -29673,10 +29685,10 @@
         <v>75</v>
       </c>
       <c r="L539">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M539">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
@@ -29684,7 +29696,7 @@
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29699,10 +29711,10 @@
         <v>1332</v>
       </c>
       <c r="G540" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H540" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J540" t="s">
         <v>564</v>
@@ -29711,10 +29723,10 @@
         <v>75</v>
       </c>
       <c r="L540">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M540">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29722,7 +29734,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29737,10 +29749,10 @@
         <v>1332</v>
       </c>
       <c r="G541" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H541" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J541" t="s">
         <v>564</v>
@@ -29749,10 +29761,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M541">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29760,10 +29772,10 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B542" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C542" t="s">
         <v>1323</v>
@@ -29775,10 +29787,10 @@
         <v>1332</v>
       </c>
       <c r="G542" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H542" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J542" t="s">
         <v>564</v>
@@ -29787,7 +29799,7 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M542">
         <v>0</v>
@@ -29798,10 +29810,10 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B543" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C543" t="s">
         <v>1323</v>
@@ -29813,10 +29825,10 @@
         <v>1332</v>
       </c>
       <c r="G543" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H543" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J543" t="s">
         <v>564</v>
@@ -29825,10 +29837,10 @@
         <v>75</v>
       </c>
       <c r="L543">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M543">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29836,7 +29848,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -29851,7 +29863,7 @@
         <v>1332</v>
       </c>
       <c r="G544" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H544" t="s">
         <v>1352</v>
@@ -29863,10 +29875,10 @@
         <v>75</v>
       </c>
       <c r="L544">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M544">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -29874,7 +29886,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -29889,10 +29901,10 @@
         <v>1332</v>
       </c>
       <c r="G545" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H545" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J545" t="s">
         <v>564</v>
@@ -29901,10 +29913,10 @@
         <v>75</v>
       </c>
       <c r="L545">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M545">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -29912,7 +29924,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -29927,10 +29939,10 @@
         <v>1332</v>
       </c>
       <c r="G546" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H546" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J546" t="s">
         <v>564</v>
@@ -29950,7 +29962,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -29965,22 +29977,22 @@
         <v>1332</v>
       </c>
       <c r="G547" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H547" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J547" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K547">
         <v>75</v>
       </c>
       <c r="L547">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M547">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -29988,7 +30000,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30003,22 +30015,22 @@
         <v>1332</v>
       </c>
       <c r="G548" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H548" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J548">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J548" t="s">
+        <v>167</v>
       </c>
       <c r="K548">
         <v>75</v>
       </c>
       <c r="L548">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M548">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30026,7 +30038,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30034,9 +30046,6 @@
       <c r="C549" t="s">
         <v>1323</v>
       </c>
-      <c r="D549" t="s">
-        <v>1008</v>
-      </c>
       <c r="E549" t="s">
         <v>1323</v>
       </c>
@@ -30044,22 +30053,22 @@
         <v>1332</v>
       </c>
       <c r="G549" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H549" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J549" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J549">
+        <v>2017</v>
       </c>
       <c r="K549">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L549">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M549">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30067,7 +30076,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30085,7 +30094,7 @@
         <v>1332</v>
       </c>
       <c r="G550" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H550" t="s">
         <v>1352</v>
@@ -30097,10 +30106,10 @@
         <v>150</v>
       </c>
       <c r="L550">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M550">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30108,10 +30117,10 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B551" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C551" t="s">
         <v>1323</v>
@@ -30126,10 +30135,10 @@
         <v>1332</v>
       </c>
       <c r="G551" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H551" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J551" t="s">
         <v>564</v>
@@ -30138,10 +30147,10 @@
         <v>150</v>
       </c>
       <c r="L551">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M551">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30149,7 +30158,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B552" t="s">
         <v>55</v>
@@ -30167,7 +30176,7 @@
         <v>1332</v>
       </c>
       <c r="G552" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H552" t="s">
         <v>1334</v>
@@ -30176,10 +30185,10 @@
         <v>564</v>
       </c>
       <c r="K552">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L552">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M552">
         <v>5</v>
@@ -30190,7 +30199,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B553" t="s">
         <v>55</v>
@@ -30208,7 +30217,7 @@
         <v>1332</v>
       </c>
       <c r="G553" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H553" t="s">
         <v>1334</v>
@@ -30217,10 +30226,10 @@
         <v>564</v>
       </c>
       <c r="K553">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L553">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M553">
         <v>5</v>
@@ -30231,37 +30240,40 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B554" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C554" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D554" t="s">
+        <v>1008</v>
       </c>
       <c r="E554" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F554" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G554" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H554" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J554" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K554">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L554">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M554">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30269,7 +30281,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30284,7 +30296,7 @@
         <v>1406</v>
       </c>
       <c r="G555" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H555" t="s">
         <v>1408</v>
@@ -30296,7 +30308,7 @@
         <v>70</v>
       </c>
       <c r="L555">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M555">
         <v>6</v>
@@ -30307,7 +30319,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30322,19 +30334,22 @@
         <v>1406</v>
       </c>
       <c r="G556" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H556" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J556" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K556">
         <v>70</v>
       </c>
       <c r="L556">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M556">
+        <v>6</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30342,7 +30357,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30357,19 +30372,19 @@
         <v>1406</v>
       </c>
       <c r="G557" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H557" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J557" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K557">
         <v>70</v>
       </c>
       <c r="L557">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30377,7 +30392,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30392,19 +30407,19 @@
         <v>1406</v>
       </c>
       <c r="G558" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H558" t="s">
         <v>1418</v>
       </c>
       <c r="J558" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K558">
         <v>70</v>
       </c>
       <c r="L558">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30412,7 +30427,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30427,19 +30442,19 @@
         <v>1406</v>
       </c>
       <c r="G559" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H559" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J559" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K559">
         <v>70</v>
       </c>
       <c r="L559">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30447,7 +30462,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30455,9 +30470,6 @@
       <c r="C560" t="s">
         <v>1405</v>
       </c>
-      <c r="D560" t="s">
-        <v>1008</v>
-      </c>
       <c r="E560" t="s">
         <v>1405</v>
       </c>
@@ -30465,19 +30477,19 @@
         <v>1406</v>
       </c>
       <c r="G560" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H560" t="s">
         <v>1425</v>
       </c>
       <c r="J560" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K560">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L560">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30485,7 +30497,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30493,26 +30505,29 @@
       <c r="C561" t="s">
         <v>1405</v>
       </c>
+      <c r="D561" t="s">
+        <v>1008</v>
+      </c>
       <c r="E561" t="s">
         <v>1405</v>
       </c>
       <c r="F561" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G561" t="s">
+        <v>1428</v>
       </c>
       <c r="H561" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J561" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K561">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L561">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M561">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30520,10 +30535,10 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B562" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C562" t="s">
         <v>1405</v>
@@ -30534,17 +30549,17 @@
       <c r="F562" t="s">
         <v>1431</v>
       </c>
-      <c r="G562" t="s">
-        <v>1435</v>
-      </c>
       <c r="H562" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J562" t="s">
+        <v>1433</v>
       </c>
       <c r="K562">
         <v>70</v>
       </c>
       <c r="L562">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M562">
         <v>45</v>
@@ -30555,10 +30570,10 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B563" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C563" t="s">
         <v>1405</v>
@@ -30570,22 +30585,19 @@
         <v>1431</v>
       </c>
       <c r="G563" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H563" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J563" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K563">
         <v>70</v>
       </c>
       <c r="L563">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M563">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30593,7 +30605,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B564" t="s">
         <v>66</v>
@@ -30608,22 +30620,22 @@
         <v>1431</v>
       </c>
       <c r="G564" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H564" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J564" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K564">
         <v>70</v>
       </c>
       <c r="L564">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M564">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P564" s="19">
         <v>46155</v>
@@ -30631,7 +30643,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B565" t="s">
         <v>66</v>
@@ -30643,25 +30655,25 @@
         <v>1405</v>
       </c>
       <c r="F565" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G565" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H565" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J565" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K565">
         <v>70</v>
       </c>
       <c r="L565">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M565">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P565" s="19">
         <v>46155</v>
@@ -30669,7 +30681,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B566" t="s">
         <v>66</v>
@@ -30684,7 +30696,7 @@
         <v>1445</v>
       </c>
       <c r="G566" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H566" t="s">
         <v>1447</v>
@@ -30696,17 +30708,94 @@
         <v>70</v>
       </c>
       <c r="L566">
+        <v>36.5</v>
+      </c>
+      <c r="M566">
+        <v>7</v>
+      </c>
+      <c r="P566" s="19">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="567" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A567" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B567" t="s">
+        <v>66</v>
+      </c>
+      <c r="C567" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E567" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F567" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G567" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H567" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J567" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K567">
+        <v>70</v>
+      </c>
+      <c r="L567">
         <v>40.5</v>
       </c>
-      <c r="M566">
+      <c r="M567">
         <v>5</v>
       </c>
-      <c r="P566" s="19">
+      <c r="P567" s="19">
         <v>46175</v>
       </c>
     </row>
+    <row r="568" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A568" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B568" t="s">
+        <v>55</v>
+      </c>
+      <c r="C568" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E568" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F568" t="s">
+        <v>2366</v>
+      </c>
+      <c r="G568" t="s">
+        <v>2367</v>
+      </c>
+      <c r="H568" t="s">
+        <v>2362</v>
+      </c>
+      <c r="J568">
+        <f>5.41+1.74</f>
+        <v>7.15</v>
+      </c>
+      <c r="K568">
+        <v>70</v>
+      </c>
+      <c r="L568">
+        <v>21.95</v>
+      </c>
+      <c r="M568">
+        <v>6</v>
+      </c>
+      <c r="P568" s="19">
+        <v>46155</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R566" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R567" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB87EC5-E38D-1B45-BE90-705AA27D3632}"/>
+  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6964867-D9FB-A54E-8123-9588ECD87677}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23947,7 +23947,7 @@
         <v>968</v>
       </c>
       <c r="B397" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C397" t="s">
         <v>906</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="394" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6964867-D9FB-A54E-8123-9588ECD87677}"/>
+  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D090B3FA-16D1-7142-9F49-9676C8113BC7}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10559" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10558" uniqueCount="2398">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -23943,8 +23943,8 @@
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A397" t="s">
-        <v>968</v>
+      <c r="A397">
+        <v>43600225</v>
       </c>
       <c r="B397" t="s">
         <v>66</v>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="395" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D090B3FA-16D1-7142-9F49-9676C8113BC7}"/>
+  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25D5DF51-BA9F-414F-B22F-894B91CE64DA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$593</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$594</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10558" uniqueCount="2398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="2401">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7239,6 +7239,15 @@
   </si>
   <si>
     <t>Organic</t>
+  </si>
+  <si>
+    <t>IGP Alpilles</t>
+  </si>
+  <si>
+    <t>Iris</t>
+  </si>
+  <si>
+    <t>Domaine Oddo</t>
   </si>
 </sst>
 </file>
@@ -8004,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R594"/>
+  <dimension ref="A1:R595"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23545,6 +23554,9 @@
       <c r="C387" t="s">
         <v>906</v>
       </c>
+      <c r="D387" t="s">
+        <v>913</v>
+      </c>
       <c r="E387" t="s">
         <v>923</v>
       </c>
@@ -23580,6 +23592,9 @@
       <c r="C388" t="s">
         <v>906</v>
       </c>
+      <c r="D388" t="s">
+        <v>913</v>
+      </c>
       <c r="E388" t="s">
         <v>923</v>
       </c>
@@ -23618,6 +23633,9 @@
       <c r="C389" t="s">
         <v>906</v>
       </c>
+      <c r="D389" t="s">
+        <v>913</v>
+      </c>
       <c r="E389" t="s">
         <v>923</v>
       </c>
@@ -23647,11 +23665,11 @@
       </c>
     </row>
     <row r="390" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A390" t="s">
-        <v>951</v>
+      <c r="A390">
+        <v>73900225</v>
       </c>
       <c r="B390" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C390" t="s">
         <v>906</v>
@@ -23660,39 +23678,36 @@
         <v>913</v>
       </c>
       <c r="E390" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F390" t="s">
-        <v>952</v>
+        <v>2398</v>
       </c>
       <c r="G390" t="s">
-        <v>953</v>
+        <v>2399</v>
       </c>
       <c r="H390" t="s">
-        <v>954</v>
+        <v>2400</v>
       </c>
       <c r="I390" t="s">
         <v>69</v>
       </c>
-      <c r="J390" t="s">
-        <v>98</v>
+      <c r="J390">
+        <v>2025</v>
       </c>
       <c r="K390">
         <v>75</v>
       </c>
       <c r="L390">
-        <v>6.45</v>
+        <v>6.9</v>
       </c>
       <c r="M390">
-        <v>501</v>
-      </c>
-      <c r="P390" s="19">
-        <v>46155</v>
+        <v>12</v>
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A391">
-        <v>10300525</v>
+      <c r="A391" t="s">
+        <v>951</v>
       </c>
       <c r="B391" t="s">
         <v>66</v>
@@ -23710,7 +23725,7 @@
         <v>952</v>
       </c>
       <c r="G391" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H391" t="s">
         <v>954</v>
@@ -23718,25 +23733,25 @@
       <c r="I391" t="s">
         <v>69</v>
       </c>
-      <c r="J391">
-        <v>2025</v>
+      <c r="J391" t="s">
+        <v>98</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M391">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P391" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>956</v>
+      <c r="A392">
+        <v>10300525</v>
       </c>
       <c r="B392" t="s">
         <v>66</v>
@@ -23751,25 +23766,28 @@
         <v>923</v>
       </c>
       <c r="F392" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G392" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H392" t="s">
-        <v>292</v>
-      </c>
-      <c r="J392" t="s">
-        <v>98</v>
+        <v>954</v>
+      </c>
+      <c r="I392" t="s">
+        <v>69</v>
+      </c>
+      <c r="J392">
+        <v>2025</v>
       </c>
       <c r="K392">
         <v>75</v>
       </c>
       <c r="L392">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="M392">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P392" s="19">
         <v>46155</v>
@@ -23777,7 +23795,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B393" t="s">
         <v>66</v>
@@ -23794,11 +23812,11 @@
       <c r="F393" t="s">
         <v>957</v>
       </c>
+      <c r="G393" t="s">
+        <v>958</v>
+      </c>
       <c r="H393" t="s">
-        <v>960</v>
-      </c>
-      <c r="I393" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="J393" t="s">
         <v>98</v>
@@ -23807,10 +23825,10 @@
         <v>75</v>
       </c>
       <c r="L393">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="M393">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P393" s="19">
         <v>46155</v>
@@ -23818,10 +23836,10 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B394" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C394" t="s">
         <v>906</v>
@@ -23835,26 +23853,23 @@
       <c r="F394" t="s">
         <v>957</v>
       </c>
-      <c r="G394" t="s">
-        <v>962</v>
-      </c>
       <c r="H394" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I394" t="s">
         <v>69</v>
       </c>
       <c r="J394" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M394">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P394" s="19">
         <v>46155</v>
@@ -23862,10 +23877,10 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B395" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C395" t="s">
         <v>906</v>
@@ -23880,22 +23895,25 @@
         <v>957</v>
       </c>
       <c r="G395" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H395" t="s">
-        <v>920</v>
+        <v>963</v>
+      </c>
+      <c r="I395" t="s">
+        <v>69</v>
       </c>
       <c r="J395" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M395">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P395" s="19">
         <v>46155</v>
@@ -23903,7 +23921,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B396" t="s">
         <v>66</v>
@@ -23921,10 +23939,10 @@
         <v>957</v>
       </c>
       <c r="G396" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H396" t="s">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="J396" t="s">
         <v>286</v>
@@ -23936,15 +23954,15 @@
         <v>9.1</v>
       </c>
       <c r="M396">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A397">
-        <v>43600225</v>
+      <c r="A397" t="s">
+        <v>966</v>
       </c>
       <c r="B397" t="s">
         <v>66</v>
@@ -23962,33 +23980,30 @@
         <v>957</v>
       </c>
       <c r="G397" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H397" t="s">
-        <v>963</v>
-      </c>
-      <c r="I397" t="s">
-        <v>69</v>
+        <v>947</v>
       </c>
       <c r="J397" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M397">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398" t="s">
-        <v>970</v>
+      <c r="A398">
+        <v>43600225</v>
       </c>
       <c r="B398" t="s">
         <v>66</v>
@@ -24006,25 +24021,25 @@
         <v>957</v>
       </c>
       <c r="G398" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H398" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="I398" t="s">
         <v>69</v>
       </c>
       <c r="J398" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M398">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
@@ -24032,7 +24047,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B399" t="s">
         <v>66</v>
@@ -24049,8 +24064,14 @@
       <c r="F399" t="s">
         <v>957</v>
       </c>
+      <c r="G399" t="s">
+        <v>971</v>
+      </c>
       <c r="H399" t="s">
-        <v>974</v>
+        <v>972</v>
+      </c>
+      <c r="I399" t="s">
+        <v>69</v>
       </c>
       <c r="J399" t="s">
         <v>98</v>
@@ -24062,7 +24083,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M399">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
@@ -24070,7 +24091,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B400" t="s">
         <v>66</v>
@@ -24085,25 +24106,22 @@
         <v>923</v>
       </c>
       <c r="F400" t="s">
-        <v>918</v>
-      </c>
-      <c r="G400" t="s">
-        <v>919</v>
+        <v>957</v>
       </c>
       <c r="H400" t="s">
-        <v>920</v>
+        <v>974</v>
       </c>
       <c r="J400" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M400">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P400" s="19">
         <v>46155</v>
@@ -24111,7 +24129,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B401" t="s">
         <v>66</v>
@@ -24126,25 +24144,25 @@
         <v>923</v>
       </c>
       <c r="F401" t="s">
-        <v>957</v>
+        <v>918</v>
+      </c>
+      <c r="G401" t="s">
+        <v>919</v>
       </c>
       <c r="H401" t="s">
-        <v>972</v>
-      </c>
-      <c r="I401" t="s">
-        <v>69</v>
-      </c>
-      <c r="J401">
-        <v>2025</v>
+        <v>920</v>
+      </c>
+      <c r="J401" t="s">
+        <v>339</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M401">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P401" s="19">
         <v>46155</v>
@@ -24152,40 +24170,40 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B402" t="s">
         <v>66</v>
       </c>
       <c r="C402" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="D402" t="s">
-        <v>979</v>
+        <v>913</v>
       </c>
       <c r="E402" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F402" t="s">
-        <v>980</v>
-      </c>
-      <c r="G402" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="H402" t="s">
-        <v>982</v>
-      </c>
-      <c r="J402" t="s">
-        <v>339</v>
+        <v>972</v>
+      </c>
+      <c r="I402" t="s">
+        <v>69</v>
+      </c>
+      <c r="J402">
+        <v>2025</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M402">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P402" s="19">
         <v>46155</v>
@@ -24193,7 +24211,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B403" t="s">
         <v>66</v>
@@ -24211,22 +24229,22 @@
         <v>980</v>
       </c>
       <c r="G403" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H403" t="s">
-        <v>985</v>
-      </c>
-      <c r="J403">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J403" t="s">
+        <v>339</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M403">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
@@ -24234,7 +24252,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B404" t="s">
         <v>66</v>
@@ -24249,25 +24267,25 @@
         <v>57</v>
       </c>
       <c r="F404" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G404" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H404" t="s">
-        <v>989</v>
-      </c>
-      <c r="J404" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J404">
+        <v>2025</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M404">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
@@ -24275,7 +24293,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B405" t="s">
         <v>66</v>
@@ -24290,25 +24308,25 @@
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G405" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="H405" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="J405" t="s">
-        <v>286</v>
+        <v>564</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M405">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
@@ -24316,7 +24334,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B406" t="s">
         <v>66</v>
@@ -24334,22 +24352,22 @@
         <v>980</v>
       </c>
       <c r="G406" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H406" t="s">
-        <v>292</v>
+        <v>992</v>
       </c>
       <c r="J406" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M406">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P406" s="19">
         <v>46155</v>
@@ -24357,7 +24375,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B407" t="s">
         <v>66</v>
@@ -24375,22 +24393,22 @@
         <v>980</v>
       </c>
       <c r="G407" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H407" t="s">
         <v>292</v>
       </c>
-      <c r="J407">
-        <v>2025</v>
+      <c r="J407" t="s">
+        <v>98</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M407">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P407" s="19">
         <v>46155</v>
@@ -24398,7 +24416,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B408" t="s">
         <v>66</v>
@@ -24416,22 +24434,22 @@
         <v>980</v>
       </c>
       <c r="G408" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H408" t="s">
-        <v>992</v>
-      </c>
-      <c r="J408" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J408">
+        <v>2025</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M408">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P408" s="19">
         <v>46155</v>
@@ -24439,7 +24457,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B409" t="s">
         <v>66</v>
@@ -24454,13 +24472,13 @@
         <v>57</v>
       </c>
       <c r="F409" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G409" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H409" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="J409" t="s">
         <v>339</v>
@@ -24469,10 +24487,10 @@
         <v>75</v>
       </c>
       <c r="L409">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M409">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P409" s="19">
         <v>46155</v>
@@ -24480,7 +24498,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B410" t="s">
         <v>66</v>
@@ -24495,16 +24513,16 @@
         <v>57</v>
       </c>
       <c r="F410" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G410" t="s">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="H410" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J410" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K410">
         <v>75</v>
@@ -24513,7 +24531,7 @@
         <v>5.7</v>
       </c>
       <c r="M410">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P410" s="19">
         <v>46155</v>
@@ -24521,7 +24539,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B411" t="s">
         <v>66</v>
@@ -24539,22 +24557,22 @@
         <v>980</v>
       </c>
       <c r="G411" t="s">
-        <v>1005</v>
+        <v>113</v>
       </c>
       <c r="H411" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="J411" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K411">
         <v>75</v>
       </c>
       <c r="L411">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M411">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P411" s="19">
         <v>46155</v>
@@ -24562,16 +24580,16 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B412" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C412" t="s">
         <v>978</v>
       </c>
       <c r="D412" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E412" t="s">
         <v>57</v>
@@ -24580,7 +24598,7 @@
         <v>980</v>
       </c>
       <c r="G412" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="H412" t="s">
         <v>1006</v>
@@ -24589,13 +24607,13 @@
         <v>339</v>
       </c>
       <c r="K412">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L412">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M412">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P412" s="19">
         <v>46155</v>
@@ -24603,16 +24621,16 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B413" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C413" t="s">
         <v>978</v>
       </c>
       <c r="D413" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="E413" t="s">
         <v>57</v>
@@ -24621,25 +24639,22 @@
         <v>980</v>
       </c>
       <c r="G413" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H413" t="s">
-        <v>992</v>
-      </c>
-      <c r="I413" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="J413" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K413">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L413">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M413">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P413" s="19">
         <v>46155</v>
@@ -24647,7 +24662,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B414" t="s">
         <v>66</v>
@@ -24656,31 +24671,34 @@
         <v>978</v>
       </c>
       <c r="D414" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E414" t="s">
         <v>57</v>
       </c>
       <c r="F414" t="s">
-        <v>1015</v>
+        <v>980</v>
       </c>
       <c r="G414" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="H414" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I414" t="s">
+        <v>1012</v>
       </c>
       <c r="J414" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M414">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P414" s="19">
         <v>46155</v>
@@ -24688,7 +24706,7 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B415" t="s">
         <v>66</v>
@@ -24697,34 +24715,31 @@
         <v>978</v>
       </c>
       <c r="D415" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
       </c>
       <c r="F415" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G415" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H415" t="s">
-        <v>1021</v>
-      </c>
-      <c r="I415" t="s">
-        <v>777</v>
+        <v>1017</v>
       </c>
       <c r="J415" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M415">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P415" s="19">
         <v>46155</v>
@@ -24732,7 +24747,7 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B416" t="s">
         <v>66</v>
@@ -24747,33 +24762,36 @@
         <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="G416" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="H416" t="s">
-        <v>992</v>
+        <v>1021</v>
+      </c>
+      <c r="I416" t="s">
+        <v>777</v>
       </c>
       <c r="J416" t="s">
-        <v>339</v>
+        <v>217</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M416">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P416" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A417">
-        <v>13003025</v>
+      <c r="A417" t="s">
+        <v>1022</v>
       </c>
       <c r="B417" t="s">
         <v>66</v>
@@ -24791,33 +24809,30 @@
         <v>980</v>
       </c>
       <c r="G417" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H417" t="s">
         <v>992</v>
       </c>
-      <c r="I417" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J417">
-        <v>2025</v>
+      <c r="J417" t="s">
+        <v>339</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M417">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P417" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A418" t="s">
-        <v>1025</v>
+      <c r="A418">
+        <v>13003025</v>
       </c>
       <c r="B418" t="s">
         <v>66</v>
@@ -24835,22 +24850,25 @@
         <v>980</v>
       </c>
       <c r="G418" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H418" t="s">
-        <v>589</v>
-      </c>
-      <c r="J418" t="s">
-        <v>339</v>
+        <v>992</v>
+      </c>
+      <c r="I418" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J418">
+        <v>2025</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M418">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
@@ -24858,7 +24876,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24873,33 +24891,36 @@
         <v>57</v>
       </c>
       <c r="F419" t="s">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="G419" t="s">
-        <v>165</v>
+        <v>1026</v>
       </c>
       <c r="H419" t="s">
-        <v>1029</v>
+        <v>589</v>
       </c>
       <c r="J419" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M419">
+        <v>321</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A420">
-        <v>43700425</v>
+      <c r="A420" t="s">
+        <v>1027</v>
       </c>
       <c r="B420" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C420" t="s">
         <v>978</v>
@@ -24914,19 +24935,19 @@
         <v>1028</v>
       </c>
       <c r="G420" t="s">
-        <v>1030</v>
+        <v>165</v>
       </c>
       <c r="H420" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J420">
-        <v>2025</v>
+        <v>1029</v>
+      </c>
+      <c r="J420" t="s">
+        <v>286</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>10.5</v>
+        <v>37</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24934,7 +24955,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421">
-        <v>73300125</v>
+        <v>43700425</v>
       </c>
       <c r="B421" t="s">
         <v>55</v>
@@ -24949,13 +24970,13 @@
         <v>57</v>
       </c>
       <c r="F421" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G421" t="s">
-        <v>113</v>
+        <v>1030</v>
       </c>
       <c r="H421" t="s">
-        <v>2362</v>
+        <v>1031</v>
       </c>
       <c r="J421">
         <v>2025</v>
@@ -24964,10 +24985,7 @@
         <v>75</v>
       </c>
       <c r="L421">
-        <v>4.99</v>
-      </c>
-      <c r="M421">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24975,7 +24993,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422">
-        <v>73300225</v>
+        <v>73300125</v>
       </c>
       <c r="B422" t="s">
         <v>55</v>
@@ -24993,7 +25011,7 @@
         <v>1033</v>
       </c>
       <c r="G422" t="s">
-        <v>2364</v>
+        <v>113</v>
       </c>
       <c r="H422" t="s">
         <v>2362</v>
@@ -25016,7 +25034,7 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423">
-        <v>73300325</v>
+        <v>73300225</v>
       </c>
       <c r="B423" t="s">
         <v>55</v>
@@ -25034,7 +25052,7 @@
         <v>1033</v>
       </c>
       <c r="G423" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H423" t="s">
         <v>2362</v>
@@ -25046,7 +25064,7 @@
         <v>75</v>
       </c>
       <c r="L423">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="M423">
         <v>12</v>
@@ -25057,7 +25075,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
-        <v>73300425</v>
+        <v>73300325</v>
       </c>
       <c r="B424" t="s">
         <v>55</v>
@@ -25069,13 +25087,13 @@
         <v>979</v>
       </c>
       <c r="E424" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F424" t="s">
         <v>1033</v>
       </c>
       <c r="G424" t="s">
-        <v>1135</v>
+        <v>2363</v>
       </c>
       <c r="H424" t="s">
         <v>2362</v>
@@ -25087,7 +25105,7 @@
         <v>75</v>
       </c>
       <c r="L424">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="M424">
         <v>12</v>
@@ -25097,11 +25115,11 @@
       </c>
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A425" t="s">
-        <v>1032</v>
+      <c r="A425">
+        <v>73300425</v>
       </c>
       <c r="B425" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C425" t="s">
         <v>978</v>
@@ -25110,36 +25128,36 @@
         <v>979</v>
       </c>
       <c r="E425" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F425" t="s">
         <v>1033</v>
       </c>
       <c r="G425" t="s">
-        <v>1034</v>
+        <v>1135</v>
       </c>
       <c r="H425" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J425" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J425">
+        <v>2025</v>
       </c>
       <c r="K425">
         <v>75</v>
       </c>
       <c r="L425">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M425">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P425" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A426">
-        <v>13300125</v>
+      <c r="A426" t="s">
+        <v>1032</v>
       </c>
       <c r="B426" t="s">
         <v>66</v>
@@ -25157,33 +25175,33 @@
         <v>1033</v>
       </c>
       <c r="G426" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H426" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J426">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J426" t="s">
+        <v>98</v>
       </c>
       <c r="K426">
         <v>75</v>
       </c>
       <c r="L426">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M426">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
-        <v>1038</v>
+      <c r="A427">
+        <v>13300125</v>
       </c>
       <c r="B427" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C427" t="s">
         <v>978</v>
@@ -25195,33 +25213,33 @@
         <v>57</v>
       </c>
       <c r="F427" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G427" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H427" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J427" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J427">
+        <v>2025</v>
       </c>
       <c r="K427">
         <v>75</v>
       </c>
       <c r="L427">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M427">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A428">
-        <v>24003025</v>
+      <c r="A428" t="s">
+        <v>1038</v>
       </c>
       <c r="B428" t="s">
         <v>55</v>
@@ -25230,7 +25248,7 @@
         <v>978</v>
       </c>
       <c r="D428" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E428" t="s">
         <v>57</v>
@@ -25239,16 +25257,13 @@
         <v>58</v>
       </c>
       <c r="G428" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H428" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I428" t="s">
-        <v>69</v>
-      </c>
-      <c r="J428">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J428" t="s">
+        <v>339</v>
       </c>
       <c r="K428">
         <v>75</v>
@@ -25256,13 +25271,16 @@
       <c r="L428">
         <v>6.2</v>
       </c>
+      <c r="M428">
+        <v>0</v>
+      </c>
       <c r="P428" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A429" t="s">
-        <v>1044</v>
+      <c r="A429">
+        <v>24003025</v>
       </c>
       <c r="B429" t="s">
         <v>55</v>
@@ -25271,39 +25289,39 @@
         <v>978</v>
       </c>
       <c r="D429" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E429" t="s">
         <v>57</v>
       </c>
       <c r="F429" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G429" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H429" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J429" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I429" t="s">
+        <v>69</v>
+      </c>
+      <c r="J429">
+        <v>2025</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>7.55</v>
-      </c>
-      <c r="M429">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P429" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25312,28 +25330,28 @@
         <v>978</v>
       </c>
       <c r="D430" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E430" t="s">
         <v>57</v>
       </c>
       <c r="F430" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G430" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H430" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J430" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K430">
         <v>75</v>
       </c>
       <c r="L430">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M430">
         <v>0</v>
@@ -25344,7 +25362,7 @@
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25353,28 +25371,28 @@
         <v>978</v>
       </c>
       <c r="D431" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E431" t="s">
         <v>57</v>
       </c>
       <c r="F431" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G431" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H431" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J431" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K431">
         <v>75</v>
       </c>
       <c r="L431">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M431">
         <v>0</v>
@@ -25385,7 +25403,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25394,42 +25412,39 @@
         <v>978</v>
       </c>
       <c r="D432" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E432" t="s">
         <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G432" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H432" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I432" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J432" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M432">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P432" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A433">
-        <v>27701225</v>
+      <c r="A433" t="s">
+        <v>1053</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25438,39 +25453,42 @@
         <v>978</v>
       </c>
       <c r="D433" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E433" t="s">
         <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G433" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H433" t="s">
         <v>1055</v>
       </c>
-      <c r="J433">
-        <v>2025</v>
+      <c r="I433" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J433" t="s">
+        <v>286</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M433">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P433" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A434" t="s">
-        <v>1060</v>
+      <c r="A434">
+        <v>27701225</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25479,28 +25497,28 @@
         <v>978</v>
       </c>
       <c r="D434" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E434" t="s">
         <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G434" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H434" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J434" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J434">
+        <v>2025</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M434">
         <v>0</v>
@@ -25511,7 +25529,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25520,28 +25538,28 @@
         <v>978</v>
       </c>
       <c r="D435" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E435" t="s">
         <v>57</v>
       </c>
       <c r="F435" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G435" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H435" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J435" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K435">
         <v>75</v>
       </c>
       <c r="L435">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M435">
         <v>0</v>
@@ -25552,7 +25570,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25567,22 +25585,22 @@
         <v>57</v>
       </c>
       <c r="F436" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G436" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H436" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J436" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K436">
         <v>75</v>
       </c>
       <c r="L436">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -25592,8 +25610,8 @@
       </c>
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A437">
-        <v>68002225</v>
+      <c r="A437" t="s">
+        <v>1065</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25605,13 +25623,13 @@
         <v>1057</v>
       </c>
       <c r="E437" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F437" t="s">
         <v>1066</v>
       </c>
       <c r="G437" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H437" t="s">
         <v>1068</v>
@@ -25623,7 +25641,7 @@
         <v>75</v>
       </c>
       <c r="L437">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M437">
         <v>0</v>
@@ -25634,7 +25652,7 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25649,13 +25667,13 @@
         <v>63</v>
       </c>
       <c r="F438" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G438" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H438" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J438" t="s">
         <v>339</v>
@@ -25664,7 +25682,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M438">
         <v>0</v>
@@ -25675,7 +25693,7 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B439" t="s">
         <v>55</v>
@@ -25693,13 +25711,13 @@
         <v>1070</v>
       </c>
       <c r="G439" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H439" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J439">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J439" t="s">
+        <v>339</v>
       </c>
       <c r="K439">
         <v>75</v>
@@ -25715,8 +25733,8 @@
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A440" t="s">
-        <v>1075</v>
+      <c r="A440">
+        <v>68002424</v>
       </c>
       <c r="B440" t="s">
         <v>55</v>
@@ -25734,19 +25752,19 @@
         <v>1070</v>
       </c>
       <c r="G440" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H440" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J440" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J440">
+        <v>2024</v>
       </c>
       <c r="K440">
         <v>75</v>
       </c>
       <c r="L440">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M440">
         <v>0</v>
@@ -25756,8 +25774,8 @@
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A441">
-        <v>68002623</v>
+      <c r="A441" t="s">
+        <v>1075</v>
       </c>
       <c r="B441" t="s">
         <v>55</v>
@@ -25772,25 +25790,22 @@
         <v>63</v>
       </c>
       <c r="F441" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G441" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H441" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I441" t="s">
-        <v>69</v>
-      </c>
-      <c r="J441">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J441" t="s">
+        <v>564</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M441">
         <v>0</v>
@@ -25801,7 +25816,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B442" t="s">
         <v>55</v>
@@ -25813,28 +25828,28 @@
         <v>1057</v>
       </c>
       <c r="E442" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F442" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G442" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H442" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I442" t="s">
         <v>69</v>
       </c>
       <c r="J442">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -25844,8 +25859,8 @@
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>1083</v>
+      <c r="A443">
+        <v>68002825</v>
       </c>
       <c r="B443" t="s">
         <v>55</v>
@@ -25860,22 +25875,25 @@
         <v>57</v>
       </c>
       <c r="F443" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G443" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H443" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J443" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I443" t="s">
+        <v>69</v>
+      </c>
+      <c r="J443">
+        <v>2025</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -25885,8 +25903,8 @@
       </c>
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A444">
-        <v>68003025</v>
+      <c r="A444" t="s">
+        <v>1083</v>
       </c>
       <c r="B444" t="s">
         <v>55</v>
@@ -25898,13 +25916,13 @@
         <v>1057</v>
       </c>
       <c r="E444" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F444" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G444" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H444" t="s">
         <v>1085</v>
@@ -25927,7 +25945,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B445" t="s">
         <v>55</v>
@@ -25945,10 +25963,10 @@
         <v>1078</v>
       </c>
       <c r="G445" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H445" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J445" t="s">
         <v>339</v>
@@ -25957,7 +25975,7 @@
         <v>75</v>
       </c>
       <c r="L445">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M445">
         <v>0</v>
@@ -25967,8 +25985,8 @@
       </c>
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>1089</v>
+      <c r="A446">
+        <v>680031225</v>
       </c>
       <c r="B446" t="s">
         <v>55</v>
@@ -25980,25 +25998,25 @@
         <v>1057</v>
       </c>
       <c r="E446" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F446" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G446" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H446" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J446" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K446">
         <v>75</v>
       </c>
       <c r="L446">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M446">
         <v>0</v>
@@ -26009,10 +26027,10 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B447" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C447" t="s">
         <v>978</v>
@@ -26027,22 +26045,22 @@
         <v>1066</v>
       </c>
       <c r="G447" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H447" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J447">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J447" t="s">
+        <v>98</v>
       </c>
       <c r="K447">
         <v>75</v>
       </c>
       <c r="L447">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M447">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P447" s="19">
         <v>46155</v>
@@ -26050,7 +26068,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B448" t="s">
         <v>66</v>
@@ -26059,31 +26077,31 @@
         <v>978</v>
       </c>
       <c r="D448" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E448" t="s">
         <v>57</v>
       </c>
       <c r="F448" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G448" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H448" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J448" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J448">
+        <v>2025</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M448">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26091,7 +26109,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26109,22 +26127,22 @@
         <v>1033</v>
       </c>
       <c r="G449" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H449" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J449">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J449" t="s">
+        <v>98</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M449">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26132,7 +26150,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26147,22 +26165,25 @@
         <v>57</v>
       </c>
       <c r="F450" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G450" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H450" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J450" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J450">
+        <v>2025</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M450">
+        <v>264</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26170,7 +26191,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26185,104 +26206,101 @@
         <v>57</v>
       </c>
       <c r="F451" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G451" t="s">
         <v>1100</v>
       </c>
       <c r="H451" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J451" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A452">
-        <v>53800623</v>
+      <c r="A452" t="s">
+        <v>1102</v>
       </c>
       <c r="B452" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C452" t="s">
         <v>978</v>
       </c>
       <c r="D452" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E452" t="s">
         <v>57</v>
       </c>
       <c r="F452" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G452" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H452" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J452" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>11</v>
-      </c>
-      <c r="M452">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A453" t="s">
-        <v>1107</v>
+      <c r="A453">
+        <v>53800623</v>
       </c>
       <c r="B453" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C453" t="s">
         <v>978</v>
       </c>
       <c r="D453" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E453" t="s">
         <v>57</v>
       </c>
       <c r="F453" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G453" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H453" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J453" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K453">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L453">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M453">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
@@ -26290,7 +26308,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B454" t="s">
         <v>66</v>
@@ -26308,22 +26326,22 @@
         <v>980</v>
       </c>
       <c r="G454" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H454" t="s">
-        <v>985</v>
-      </c>
-      <c r="J454">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J454" t="s">
+        <v>564</v>
       </c>
       <c r="K454">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L454">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M454">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
@@ -26331,7 +26349,7 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B455" t="s">
         <v>66</v>
@@ -26340,75 +26358,72 @@
         <v>978</v>
       </c>
       <c r="D455" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E455" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F455" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G455" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H455" t="s">
-        <v>989</v>
-      </c>
-      <c r="J455" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J455">
+        <v>2025</v>
       </c>
       <c r="K455">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L455">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M455">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A456">
-        <v>71501125</v>
+      <c r="A456" t="s">
+        <v>1111</v>
       </c>
       <c r="B456" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C456" t="s">
         <v>978</v>
       </c>
       <c r="D456" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E456" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F456" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G456" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H456" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I456" t="s">
-        <v>69</v>
-      </c>
-      <c r="J456">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J456" t="s">
+        <v>564</v>
       </c>
       <c r="K456">
         <v>75</v>
       </c>
       <c r="L456">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M456">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
@@ -26416,7 +26431,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B457" t="s">
         <v>55</v>
@@ -26428,17 +26443,20 @@
         <v>979</v>
       </c>
       <c r="E457" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F457" t="s">
         <v>980</v>
       </c>
       <c r="G457" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H457" t="s">
         <v>1113</v>
       </c>
+      <c r="I457" t="s">
+        <v>69</v>
+      </c>
       <c r="J457">
         <v>2025</v>
       </c>
@@ -26446,7 +26464,7 @@
         <v>75</v>
       </c>
       <c r="L457">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M457">
         <v>324</v>
@@ -26457,7 +26475,7 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B458" t="s">
         <v>55</v>
@@ -26475,7 +26493,7 @@
         <v>980</v>
       </c>
       <c r="G458" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H458" t="s">
         <v>1113</v>
@@ -26498,7 +26516,7 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B459" t="s">
         <v>55</v>
@@ -26513,10 +26531,10 @@
         <v>63</v>
       </c>
       <c r="F459" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G459" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H459" t="s">
         <v>1113</v>
@@ -26539,7 +26557,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B460" t="s">
         <v>55</v>
@@ -26551,13 +26569,13 @@
         <v>979</v>
       </c>
       <c r="E460" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F460" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G460" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H460" t="s">
         <v>1113</v>
@@ -26580,7 +26598,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B461" t="s">
         <v>55</v>
@@ -26595,10 +26613,10 @@
         <v>57</v>
       </c>
       <c r="F461" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G461" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H461" t="s">
         <v>1113</v>
@@ -26621,7 +26639,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B462" t="s">
         <v>55</v>
@@ -26633,13 +26651,13 @@
         <v>979</v>
       </c>
       <c r="E462" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F462" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G462" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H462" t="s">
         <v>1113</v>
@@ -26651,7 +26669,7 @@
         <v>75</v>
       </c>
       <c r="L462">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M462">
         <v>324</v>
@@ -26662,7 +26680,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B463" t="s">
         <v>55</v>
@@ -26677,7 +26695,7 @@
         <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G463" t="s">
         <v>1120</v>
@@ -26692,7 +26710,7 @@
         <v>75</v>
       </c>
       <c r="L463">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M463">
         <v>324</v>
@@ -26703,7 +26721,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26718,7 +26736,7 @@
         <v>63</v>
       </c>
       <c r="F464" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G464" t="s">
         <v>1120</v>
@@ -26726,9 +26744,6 @@
       <c r="H464" t="s">
         <v>1113</v>
       </c>
-      <c r="I464" t="s">
-        <v>69</v>
-      </c>
       <c r="J464">
         <v>2025</v>
       </c>
@@ -26747,7 +26762,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B465" t="s">
         <v>55</v>
@@ -26759,10 +26774,10 @@
         <v>979</v>
       </c>
       <c r="E465" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G465" t="s">
         <v>1120</v>
@@ -26771,7 +26786,7 @@
         <v>1113</v>
       </c>
       <c r="I465" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J465">
         <v>2025</v>
@@ -26780,7 +26795,7 @@
         <v>75</v>
       </c>
       <c r="L465">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M465">
         <v>324</v>
@@ -26791,7 +26806,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B466" t="s">
         <v>55</v>
@@ -26806,7 +26821,7 @@
         <v>57</v>
       </c>
       <c r="F466" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G466" t="s">
         <v>1120</v>
@@ -26824,7 +26839,7 @@
         <v>75</v>
       </c>
       <c r="L466">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M466">
         <v>324</v>
@@ -26835,10 +26850,10 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B467" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C467" t="s">
         <v>978</v>
@@ -26847,16 +26862,19 @@
         <v>979</v>
       </c>
       <c r="E467" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F467" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G467" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H467" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I467" t="s">
+        <v>175</v>
       </c>
       <c r="J467">
         <v>2025</v>
@@ -26865,7 +26883,7 @@
         <v>75</v>
       </c>
       <c r="L467">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M467">
         <v>324</v>
@@ -26875,8 +26893,8 @@
       </c>
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A468" t="s">
-        <v>1125</v>
+      <c r="A468">
+        <v>16000125</v>
       </c>
       <c r="B468" t="s">
         <v>66</v>
@@ -26894,22 +26912,22 @@
         <v>980</v>
       </c>
       <c r="G468" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H468" t="s">
-        <v>985</v>
-      </c>
-      <c r="J468" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J468">
+        <v>2025</v>
       </c>
       <c r="K468">
         <v>75</v>
       </c>
       <c r="L468">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M468">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P468" s="19">
         <v>46155</v>
@@ -26917,7 +26935,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B469" t="s">
         <v>66</v>
@@ -26935,22 +26953,22 @@
         <v>980</v>
       </c>
       <c r="G469" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H469" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J469" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M469">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
@@ -26958,7 +26976,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B470" t="s">
         <v>66</v>
@@ -26976,22 +26994,22 @@
         <v>980</v>
       </c>
       <c r="G470" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H470" t="s">
-        <v>985</v>
-      </c>
-      <c r="J470">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J470" t="s">
+        <v>286</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M470">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
@@ -26999,7 +27017,7 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B471" t="s">
         <v>66</v>
@@ -27014,25 +27032,25 @@
         <v>63</v>
       </c>
       <c r="F471" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G471" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H471" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J471" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J471">
+        <v>2025</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M471">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -27040,7 +27058,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B472" t="s">
         <v>66</v>
@@ -27055,25 +27073,25 @@
         <v>63</v>
       </c>
       <c r="F472" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G472" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H472" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J472" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M472">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27081,7 +27099,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B473" t="s">
         <v>66</v>
@@ -27099,22 +27117,22 @@
         <v>980</v>
       </c>
       <c r="G473" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H473" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J473" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M473">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27122,7 +27140,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B474" t="s">
         <v>66</v>
@@ -27140,25 +27158,22 @@
         <v>980</v>
       </c>
       <c r="G474" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H474" t="s">
-        <v>982</v>
-      </c>
-      <c r="I474" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J474" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M474">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27166,7 +27181,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B475" t="s">
         <v>66</v>
@@ -27184,13 +27199,13 @@
         <v>980</v>
       </c>
       <c r="G475" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H475" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I475" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J475" t="s">
         <v>61</v>
@@ -27199,10 +27214,10 @@
         <v>75</v>
       </c>
       <c r="L475">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M475">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27210,7 +27225,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B476" t="s">
         <v>66</v>
@@ -27225,25 +27240,28 @@
         <v>63</v>
       </c>
       <c r="F476" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G476" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H476" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1012</v>
       </c>
       <c r="J476" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M476">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27251,7 +27269,7 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B477" t="s">
         <v>66</v>
@@ -27260,19 +27278,19 @@
         <v>978</v>
       </c>
       <c r="D477" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E477" t="s">
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G477" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H477" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J477" t="s">
         <v>217</v>
@@ -27281,10 +27299,10 @@
         <v>75</v>
       </c>
       <c r="L477">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M477">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27292,7 +27310,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27307,25 +27325,25 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G478" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H478" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J478" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M478">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27333,7 +27351,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B479" t="s">
         <v>66</v>
@@ -27351,22 +27369,22 @@
         <v>1147</v>
       </c>
       <c r="G479" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H479" t="s">
         <v>1149</v>
       </c>
       <c r="J479" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M479">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
@@ -27374,37 +27392,40 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B480" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C480" t="s">
         <v>978</v>
       </c>
       <c r="D480" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E480" t="s">
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G480" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H480" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J480" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M480">
+        <v>36</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
@@ -27412,7 +27433,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B481" t="s">
         <v>55</v>
@@ -27427,25 +27448,22 @@
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G481" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H481" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J481" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>12.5</v>
-      </c>
-      <c r="M481">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P481" s="19">
         <v>46155</v>
@@ -27453,7 +27471,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B482" t="s">
         <v>55</v>
@@ -27468,22 +27486,22 @@
         <v>63</v>
       </c>
       <c r="F482" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G482" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H482" t="s">
         <v>1064</v>
       </c>
       <c r="J482" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M482">
         <v>0</v>
@@ -27494,7 +27512,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B483" t="s">
         <v>55</v>
@@ -27512,19 +27530,19 @@
         <v>1078</v>
       </c>
       <c r="G483" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H483" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J483">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J483" t="s">
+        <v>209</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M483">
         <v>0</v>
@@ -27535,10 +27553,10 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B484" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C484" t="s">
         <v>978</v>
@@ -27550,25 +27568,25 @@
         <v>63</v>
       </c>
       <c r="F484" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G484" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H484" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J484" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J484">
+        <v>2014</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M484">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
@@ -27576,10 +27594,10 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B485" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C485" t="s">
         <v>978</v>
@@ -27594,13 +27612,10 @@
         <v>1066</v>
       </c>
       <c r="G485" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H485" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I485" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J485" t="s">
         <v>61</v>
@@ -27609,18 +27624,18 @@
         <v>75</v>
       </c>
       <c r="L485">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M485">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A486">
-        <v>27701324</v>
+      <c r="A486" t="s">
+        <v>1164</v>
       </c>
       <c r="B486" t="s">
         <v>55</v>
@@ -27638,19 +27653,22 @@
         <v>1066</v>
       </c>
       <c r="G486" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H486" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J486">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I486" t="s">
+        <v>69</v>
+      </c>
+      <c r="J486" t="s">
+        <v>61</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M486">
         <v>0</v>
@@ -27660,8 +27678,8 @@
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A487" t="s">
-        <v>1167</v>
+      <c r="A487">
+        <v>27701324</v>
       </c>
       <c r="B487" t="s">
         <v>55</v>
@@ -27679,22 +27697,19 @@
         <v>1066</v>
       </c>
       <c r="G487" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H487" t="s">
         <v>1055</v>
       </c>
-      <c r="I487" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J487" t="s">
-        <v>98</v>
+      <c r="J487">
+        <v>2024</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M487">
         <v>0</v>
@@ -27705,31 +27720,31 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B488" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C488" t="s">
         <v>978</v>
       </c>
       <c r="D488" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E488" t="s">
         <v>63</v>
       </c>
       <c r="F488" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G488" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H488" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I488" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J488" t="s">
         <v>98</v>
@@ -27738,10 +27753,10 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M488">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
@@ -27749,7 +27764,7 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B489" t="s">
         <v>66</v>
@@ -27764,28 +27779,28 @@
         <v>63</v>
       </c>
       <c r="F489" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G489" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H489" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I489" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J489" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M489">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
@@ -27793,10 +27808,10 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B490" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C490" t="s">
         <v>978</v>
@@ -27808,25 +27823,28 @@
         <v>63</v>
       </c>
       <c r="F490" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G490" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H490" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I490" t="s">
+        <v>69</v>
       </c>
       <c r="J490" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M490">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
@@ -27834,7 +27852,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B491" t="s">
         <v>55</v>
@@ -27852,19 +27870,22 @@
         <v>1175</v>
       </c>
       <c r="G491" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H491" t="s">
         <v>1177</v>
       </c>
       <c r="J491" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M491">
+        <v>0</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27872,10 +27893,10 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B492" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C492" t="s">
         <v>978</v>
@@ -27887,28 +27908,22 @@
         <v>63</v>
       </c>
       <c r="F492" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G492" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H492" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I492" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J492" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>7.6</v>
-      </c>
-      <c r="M492">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27916,10 +27931,10 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B493" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27931,25 +27946,28 @@
         <v>63</v>
       </c>
       <c r="F493" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G493" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H493" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I493" t="s">
+        <v>69</v>
       </c>
       <c r="J493" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M493">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27957,7 +27975,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B494" t="s">
         <v>55</v>
@@ -27975,22 +27993,22 @@
         <v>1185</v>
       </c>
       <c r="G494" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H494" t="s">
         <v>1049</v>
       </c>
       <c r="J494" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M494">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -27998,10 +28016,10 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B495" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C495" t="s">
         <v>978</v>
@@ -28013,25 +28031,25 @@
         <v>63</v>
       </c>
       <c r="F495" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G495" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H495" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I495" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J495" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M495">
+        <v>6</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -28039,7 +28057,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B496" t="s">
         <v>66</v>
@@ -28054,25 +28072,25 @@
         <v>63</v>
       </c>
       <c r="F496" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G496" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H496" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I496" t="s">
+        <v>777</v>
       </c>
       <c r="J496" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K496">
         <v>75</v>
       </c>
       <c r="L496">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M496">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -28080,7 +28098,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -28095,25 +28113,25 @@
         <v>63</v>
       </c>
       <c r="F497" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G497" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H497" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I497" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J497" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M497">
+        <v>53</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28121,7 +28139,7 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28136,28 +28154,25 @@
         <v>63</v>
       </c>
       <c r="F498" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G498" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H498" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I498" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J498" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>6.5</v>
-      </c>
-      <c r="M498">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
@@ -28165,10 +28180,10 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B499" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C499" t="s">
         <v>978</v>
@@ -28183,30 +28198,33 @@
         <v>1122</v>
       </c>
       <c r="G499" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H499" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I499" t="s">
+        <v>175</v>
       </c>
       <c r="J499" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M499">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A500">
-        <v>16003124</v>
+      <c r="A500" t="s">
+        <v>1202</v>
       </c>
       <c r="B500" t="s">
         <v>55</v>
@@ -28218,19 +28236,19 @@
         <v>979</v>
       </c>
       <c r="E500" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F500" t="s">
         <v>1122</v>
       </c>
       <c r="G500" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H500" t="s">
         <v>1204</v>
       </c>
       <c r="J500" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K500">
         <v>75</v>
@@ -28246,11 +28264,11 @@
       </c>
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A501" t="s">
-        <v>1206</v>
+      <c r="A501">
+        <v>16003124</v>
       </c>
       <c r="B501" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C501" t="s">
         <v>978</v>
@@ -28259,31 +28277,28 @@
         <v>979</v>
       </c>
       <c r="E501" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F501" t="s">
         <v>1122</v>
       </c>
       <c r="G501" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H501" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I501" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J501" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M501">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
@@ -28291,10 +28306,10 @@
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B502" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C502" t="s">
         <v>978</v>
@@ -28309,25 +28324,25 @@
         <v>1122</v>
       </c>
       <c r="G502" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H502" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I502" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J502" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M502">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
@@ -28335,10 +28350,10 @@
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B503" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C503" t="s">
         <v>978</v>
@@ -28353,13 +28368,13 @@
         <v>1122</v>
       </c>
       <c r="G503" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H503" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I503" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J503" t="s">
         <v>61</v>
@@ -28368,7 +28383,7 @@
         <v>75</v>
       </c>
       <c r="L503">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M503">
         <v>171</v>
@@ -28379,10 +28394,10 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B504" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C504" t="s">
         <v>978</v>
@@ -28397,19 +28412,25 @@
         <v>1122</v>
       </c>
       <c r="G504" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H504" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I504" t="s">
+        <v>175</v>
       </c>
       <c r="J504" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M504">
+        <v>171</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28417,10 +28438,10 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B505" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C505" t="s">
         <v>978</v>
@@ -28432,28 +28453,22 @@
         <v>63</v>
       </c>
       <c r="F505" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G505" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H505" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I505" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J505" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>24.08</v>
-      </c>
-      <c r="M505">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28461,10 +28476,10 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B506" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C506" t="s">
         <v>978</v>
@@ -28476,19 +28491,28 @@
         <v>63</v>
       </c>
       <c r="F506" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G506" t="s">
+        <v>1216</v>
       </c>
       <c r="H506" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I506" t="s">
+        <v>175</v>
       </c>
       <c r="J506" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M506">
+        <v>12</v>
       </c>
       <c r="P506" s="19">
         <v>46155</v>
@@ -28496,10 +28520,10 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B507" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C507" t="s">
         <v>978</v>
@@ -28511,30 +28535,27 @@
         <v>63</v>
       </c>
       <c r="F507" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H507" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J507" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>7.05</v>
-      </c>
-      <c r="M507">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P507" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A508">
-        <v>27100523</v>
+      <c r="A508" t="s">
+        <v>1221</v>
       </c>
       <c r="B508" t="s">
         <v>66</v>
@@ -28549,36 +28570,33 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G508" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H508" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I508" t="s">
-        <v>777</v>
-      </c>
-      <c r="J508">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J508" t="s">
+        <v>217</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M508">
+        <v>30</v>
       </c>
       <c r="P508" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A509" t="s">
-        <v>1225</v>
+      <c r="A509">
+        <v>27100523</v>
       </c>
       <c r="B509" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C509" t="s">
         <v>978</v>
@@ -28590,33 +28608,36 @@
         <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G509" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H509" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J509" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I509" t="s">
+        <v>777</v>
+      </c>
+      <c r="J509">
+        <v>2023</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P509" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B510" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C510" t="s">
         <v>978</v>
@@ -28628,33 +28649,33 @@
         <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G510" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H510" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J510" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>7.35</v>
-      </c>
-      <c r="M510">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A511" t="s">
+        <v>1229</v>
+      </c>
       <c r="B511" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C511" t="s">
         <v>978</v>
@@ -28669,19 +28690,19 @@
         <v>1119</v>
       </c>
       <c r="G511" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H511" t="s">
         <v>1231</v>
       </c>
       <c r="J511" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K511">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L511">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M511">
         <v>2215</v>
@@ -28691,11 +28712,8 @@
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A512" t="s">
-        <v>1233</v>
-      </c>
       <c r="B512" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C512" t="s">
         <v>978</v>
@@ -28710,22 +28728,22 @@
         <v>1119</v>
       </c>
       <c r="G512" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H512" t="s">
         <v>1231</v>
       </c>
-      <c r="J512">
-        <v>2023</v>
+      <c r="J512" t="s">
+        <v>61</v>
       </c>
       <c r="K512">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L512">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M512">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
@@ -28733,7 +28751,7 @@
     </row>
     <row r="513" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B513" t="s">
         <v>66</v>
@@ -28751,25 +28769,22 @@
         <v>1119</v>
       </c>
       <c r="G513" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H513" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I513" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J513" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J513">
+        <v>2023</v>
       </c>
       <c r="K513">
         <v>75</v>
       </c>
       <c r="L513">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M513">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28777,10 +28792,10 @@
     </row>
     <row r="514" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B514" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C514" t="s">
         <v>978</v>
@@ -28795,19 +28810,25 @@
         <v>1119</v>
       </c>
       <c r="G514" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H514" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I514" t="s">
+        <v>1238</v>
       </c>
       <c r="J514" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K514">
         <v>75</v>
       </c>
       <c r="L514">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M514">
+        <v>205</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28815,7 +28836,7 @@
     </row>
     <row r="515" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B515" t="s">
         <v>55</v>
@@ -28833,10 +28854,10 @@
         <v>1119</v>
       </c>
       <c r="G515" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H515" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J515" t="s">
         <v>98</v>
@@ -28845,21 +28866,18 @@
         <v>75</v>
       </c>
       <c r="L515">
-        <v>14.6</v>
-      </c>
-      <c r="M515">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="516" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A516">
-        <v>43700124</v>
+      <c r="A516" t="s">
+        <v>1242</v>
       </c>
       <c r="B516" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C516" t="s">
         <v>978</v>
@@ -28871,22 +28889,25 @@
         <v>63</v>
       </c>
       <c r="F516" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G516" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H516" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J516">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J516" t="s">
+        <v>98</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M516">
+        <v>0</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28894,10 +28915,10 @@
     </row>
     <row r="517" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A517">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B517" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C517" t="s">
         <v>978</v>
@@ -28912,19 +28933,19 @@
         <v>1028</v>
       </c>
       <c r="G517" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H517" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J517">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K517">
         <v>75</v>
       </c>
       <c r="L517">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28932,7 +28953,7 @@
     </row>
     <row r="518" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A518">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B518" t="s">
         <v>55</v>
@@ -28950,30 +28971,30 @@
         <v>1028</v>
       </c>
       <c r="G518" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H518" t="s">
         <v>1031</v>
       </c>
       <c r="J518">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K518">
         <v>75</v>
       </c>
       <c r="L518">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="519" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A519" t="s">
-        <v>1247</v>
+      <c r="A519">
+        <v>43700524</v>
       </c>
       <c r="B519" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C519" t="s">
         <v>978</v>
@@ -28982,28 +29003,25 @@
         <v>979</v>
       </c>
       <c r="E519" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F519" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G519" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H519" t="s">
-        <v>982</v>
-      </c>
-      <c r="J519" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J519">
+        <v>2024</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>3.8</v>
-      </c>
-      <c r="M519">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -29011,7 +29029,7 @@
     </row>
     <row r="520" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B520" t="s">
         <v>66</v>
@@ -29029,22 +29047,22 @@
         <v>980</v>
       </c>
       <c r="G520" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H520" t="s">
-        <v>985</v>
-      </c>
-      <c r="J520">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J520" t="s">
+        <v>98</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M520">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -29052,7 +29070,7 @@
     </row>
     <row r="521" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -29070,10 +29088,10 @@
         <v>980</v>
       </c>
       <c r="G521" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H521" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J521">
         <v>2025</v>
@@ -29082,10 +29100,10 @@
         <v>75</v>
       </c>
       <c r="L521">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M521">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
@@ -29093,10 +29111,10 @@
     </row>
     <row r="522" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B522" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C522" t="s">
         <v>978</v>
@@ -29111,22 +29129,22 @@
         <v>980</v>
       </c>
       <c r="G522" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H522" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J522" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J522">
+        <v>2025</v>
       </c>
       <c r="K522">
         <v>75</v>
       </c>
       <c r="L522">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M522">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29134,10 +29152,10 @@
     </row>
     <row r="523" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B523" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C523" t="s">
         <v>978</v>
@@ -29152,22 +29170,22 @@
         <v>980</v>
       </c>
       <c r="G523" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H523" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J523" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K523">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L523">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M523">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29175,7 +29193,7 @@
     </row>
     <row r="524" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29193,22 +29211,22 @@
         <v>980</v>
       </c>
       <c r="G524" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H524" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J524" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K524">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L524">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M524">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29216,40 +29234,40 @@
     </row>
     <row r="525" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
       </c>
       <c r="C525" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D525" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E525" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F525" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G525" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H525" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J525" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K525">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L525">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M525">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29257,7 +29275,7 @@
     </row>
     <row r="526" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
@@ -29272,13 +29290,13 @@
         <v>57</v>
       </c>
       <c r="F526" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G526" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H526" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J526" t="s">
         <v>339</v>
@@ -29287,21 +29305,18 @@
         <v>75</v>
       </c>
       <c r="L526">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M526">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
       </c>
-      <c r="R526" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="527" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A527">
-        <v>24000925</v>
+      <c r="A527" t="s">
+        <v>1262</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
@@ -29313,36 +29328,39 @@
         <v>1258</v>
       </c>
       <c r="E527" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F527" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G527" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H527" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J527">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J527" t="s">
+        <v>339</v>
       </c>
       <c r="K527">
         <v>75</v>
       </c>
       <c r="L527">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M527">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
       </c>
+      <c r="R527" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A528" t="s">
-        <v>1266</v>
+      <c r="A528">
+        <v>24000925</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29354,28 +29372,28 @@
         <v>1258</v>
       </c>
       <c r="E528" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F528" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G528" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H528" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J528" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J528">
+        <v>2025</v>
       </c>
       <c r="K528">
         <v>75</v>
       </c>
       <c r="L528">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M528">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29383,7 +29401,7 @@
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29398,33 +29416,33 @@
         <v>63</v>
       </c>
       <c r="F529" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G529" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H529" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J529" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K529">
         <v>75</v>
       </c>
       <c r="L529">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M529">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A530">
-        <v>24001825</v>
+      <c r="A530" t="s">
+        <v>1270</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29439,33 +29457,33 @@
         <v>63</v>
       </c>
       <c r="F530" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G530" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H530" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J530">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J530" t="s">
+        <v>98</v>
       </c>
       <c r="K530">
         <v>75</v>
       </c>
       <c r="L530">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M530">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A531" t="s">
-        <v>1275</v>
+      <c r="A531">
+        <v>24001825</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29480,22 +29498,25 @@
         <v>63</v>
       </c>
       <c r="F531" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G531" t="s">
+        <v>1274</v>
       </c>
       <c r="H531" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J531" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J531">
+        <v>2025</v>
       </c>
       <c r="K531">
         <v>75</v>
       </c>
       <c r="L531">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M531">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29503,7 +29524,7 @@
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29518,28 +29539,22 @@
         <v>63</v>
       </c>
       <c r="F532" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G532" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H532" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I532" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J532" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K532">
         <v>75</v>
       </c>
       <c r="L532">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M532">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
@@ -29547,7 +29562,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B533" t="s">
         <v>66</v>
@@ -29556,28 +29571,34 @@
         <v>1257</v>
       </c>
       <c r="D533" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E533" t="s">
         <v>63</v>
       </c>
       <c r="F533" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G533" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H533" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I533" t="s">
+        <v>69</v>
       </c>
       <c r="J533" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K533">
         <v>75</v>
       </c>
       <c r="L533">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M533">
+        <v>318</v>
       </c>
       <c r="P533" s="19">
         <v>46155</v>
@@ -29585,7 +29606,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B534" t="s">
         <v>66</v>
@@ -29603,22 +29624,19 @@
         <v>1284</v>
       </c>
       <c r="G534" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H534" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J534" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K534">
         <v>75</v>
       </c>
       <c r="L534">
-        <v>6.1</v>
-      </c>
-      <c r="M534">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29626,7 +29644,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29649,8 +29667,8 @@
       <c r="H535" t="s">
         <v>1289</v>
       </c>
-      <c r="J535">
-        <v>2024</v>
+      <c r="J535" t="s">
+        <v>87</v>
       </c>
       <c r="K535">
         <v>75</v>
@@ -29658,16 +29676,19 @@
       <c r="L535">
         <v>6.1</v>
       </c>
+      <c r="M535">
+        <v>133</v>
+      </c>
       <c r="P535" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B536" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C536" t="s">
         <v>1257</v>
@@ -29682,30 +29703,27 @@
         <v>1284</v>
       </c>
       <c r="G536" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H536" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J536" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J536">
+        <v>2024</v>
       </c>
       <c r="K536">
         <v>75</v>
       </c>
       <c r="L536">
-        <v>13.2</v>
-      </c>
-      <c r="M536">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P536" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B537" t="s">
         <v>55</v>
@@ -29723,19 +29741,19 @@
         <v>1284</v>
       </c>
       <c r="G537" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H537" t="s">
         <v>1293</v>
       </c>
       <c r="J537" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K537">
         <v>75</v>
       </c>
       <c r="L537">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M537">
         <v>0</v>
@@ -29746,7 +29764,7 @@
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B538" t="s">
         <v>55</v>
@@ -29761,22 +29779,22 @@
         <v>63</v>
       </c>
       <c r="F538" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G538" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H538" t="s">
         <v>1293</v>
       </c>
       <c r="J538" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K538">
         <v>75</v>
       </c>
       <c r="L538">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M538">
         <v>0</v>
@@ -29786,49 +29804,49 @@
       </c>
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A539">
-        <v>10702526</v>
+      <c r="A539" t="s">
+        <v>1296</v>
       </c>
       <c r="B539" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C539" t="s">
         <v>1257</v>
       </c>
       <c r="D539" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E539" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F539" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G539" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H539" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J539">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J539" t="s">
+        <v>61</v>
       </c>
       <c r="K539">
         <v>75</v>
       </c>
       <c r="L539">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M539">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P539" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A540" t="s">
-        <v>1301</v>
+      <c r="A540">
+        <v>10702526</v>
       </c>
       <c r="B540" t="s">
         <v>66</v>
@@ -29837,31 +29855,31 @@
         <v>1257</v>
       </c>
       <c r="D540" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E540" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F540" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G540" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H540" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J540" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J540">
+        <v>2026</v>
       </c>
       <c r="K540">
         <v>75</v>
       </c>
       <c r="L540">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M540">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29869,7 +29887,7 @@
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29887,7 +29905,7 @@
         <v>1303</v>
       </c>
       <c r="G541" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H541" t="s">
         <v>1305</v>
@@ -29899,10 +29917,10 @@
         <v>75</v>
       </c>
       <c r="L541">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M541">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29910,7 +29928,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29928,7 +29946,7 @@
         <v>1303</v>
       </c>
       <c r="G542" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H542" t="s">
         <v>1305</v>
@@ -29943,7 +29961,7 @@
         <v>8.6</v>
       </c>
       <c r="M542">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29951,7 +29969,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29969,13 +29987,13 @@
         <v>1303</v>
       </c>
       <c r="G543" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H543" t="s">
         <v>1305</v>
       </c>
       <c r="J543" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K543">
         <v>75</v>
@@ -29984,7 +30002,7 @@
         <v>8.6</v>
       </c>
       <c r="M543">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -29992,7 +30010,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -30010,7 +30028,7 @@
         <v>1303</v>
       </c>
       <c r="G544" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H544" t="s">
         <v>1305</v>
@@ -30025,7 +30043,7 @@
         <v>8.6</v>
       </c>
       <c r="M544">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -30033,7 +30051,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -30051,22 +30069,22 @@
         <v>1303</v>
       </c>
       <c r="G545" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H545" t="s">
         <v>1305</v>
       </c>
       <c r="J545" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M545">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -30074,7 +30092,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -30092,22 +30110,22 @@
         <v>1303</v>
       </c>
       <c r="G546" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H546" t="s">
         <v>1305</v>
       </c>
-      <c r="J546">
-        <v>2021</v>
+      <c r="J546" t="s">
+        <v>127</v>
       </c>
       <c r="K546">
         <v>75</v>
       </c>
       <c r="L546">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M546">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -30115,7 +30133,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -30133,13 +30151,13 @@
         <v>1303</v>
       </c>
       <c r="G547" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H547" t="s">
         <v>1305</v>
       </c>
-      <c r="J547" t="s">
-        <v>109</v>
+      <c r="J547">
+        <v>2021</v>
       </c>
       <c r="K547">
         <v>75</v>
@@ -30148,7 +30166,7 @@
         <v>13</v>
       </c>
       <c r="M547">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -30156,7 +30174,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30174,7 +30192,7 @@
         <v>1303</v>
       </c>
       <c r="G548" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H548" t="s">
         <v>1305</v>
@@ -30186,7 +30204,7 @@
         <v>75</v>
       </c>
       <c r="L548">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M548">
         <v>36</v>
@@ -30197,7 +30215,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30209,28 +30227,28 @@
         <v>1302</v>
       </c>
       <c r="E549" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F549" t="s">
         <v>1303</v>
       </c>
       <c r="G549" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H549" t="s">
         <v>1305</v>
       </c>
       <c r="J549" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K549">
         <v>75</v>
       </c>
       <c r="L549">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M549">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30238,40 +30256,40 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
       </c>
       <c r="C550" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D550" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E550" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F550" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G550" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H550" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J550" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K550">
         <v>75</v>
       </c>
       <c r="L550">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M550">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30279,7 +30297,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30287,17 +30305,20 @@
       <c r="C551" t="s">
         <v>1323</v>
       </c>
+      <c r="D551" t="s">
+        <v>1258</v>
+      </c>
       <c r="E551" t="s">
         <v>1323</v>
       </c>
       <c r="F551" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G551" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H551" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J551" t="s">
         <v>564</v>
@@ -30308,13 +30329,16 @@
       <c r="L551">
         <v>6.2</v>
       </c>
+      <c r="M551">
+        <v>4411</v>
+      </c>
       <c r="P551" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30329,10 +30353,10 @@
         <v>58</v>
       </c>
       <c r="G552" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H552" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J552" t="s">
         <v>564</v>
@@ -30341,7 +30365,7 @@
         <v>75</v>
       </c>
       <c r="L552">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30349,7 +30373,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30361,25 +30385,22 @@
         <v>1323</v>
       </c>
       <c r="F553" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G553" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H553" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J553" t="s">
         <v>564</v>
       </c>
       <c r="K553">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L553">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M553">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30387,7 +30408,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30402,22 +30423,22 @@
         <v>1332</v>
       </c>
       <c r="G554" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H554" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J554" t="s">
         <v>564</v>
       </c>
       <c r="K554">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L554">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M554">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30425,7 +30446,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30440,10 +30461,10 @@
         <v>1332</v>
       </c>
       <c r="G555" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H555" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J555" t="s">
         <v>564</v>
@@ -30452,10 +30473,10 @@
         <v>75</v>
       </c>
       <c r="L555">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M555">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30463,10 +30484,10 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B556" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C556" t="s">
         <v>1323</v>
@@ -30478,10 +30499,10 @@
         <v>1332</v>
       </c>
       <c r="G556" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H556" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J556" t="s">
         <v>564</v>
@@ -30490,7 +30511,10 @@
         <v>75</v>
       </c>
       <c r="L556">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M556">
+        <v>418</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30498,10 +30522,10 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B557" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C557" t="s">
         <v>1323</v>
@@ -30513,10 +30537,10 @@
         <v>1332</v>
       </c>
       <c r="G557" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H557" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J557" t="s">
         <v>564</v>
@@ -30525,10 +30549,7 @@
         <v>75</v>
       </c>
       <c r="L557">
-        <v>25.8</v>
-      </c>
-      <c r="M557">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30536,7 +30557,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30551,10 +30572,10 @@
         <v>1332</v>
       </c>
       <c r="G558" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H558" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J558" t="s">
         <v>564</v>
@@ -30563,10 +30584,10 @@
         <v>75</v>
       </c>
       <c r="L558">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M558">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30574,7 +30595,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30589,10 +30610,10 @@
         <v>1332</v>
       </c>
       <c r="G559" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H559" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J559" t="s">
         <v>564</v>
@@ -30601,10 +30622,10 @@
         <v>75</v>
       </c>
       <c r="L559">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M559">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30612,7 +30633,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30627,10 +30648,10 @@
         <v>1332</v>
       </c>
       <c r="G560" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H560" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J560" t="s">
         <v>564</v>
@@ -30639,10 +30660,10 @@
         <v>75</v>
       </c>
       <c r="L560">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M560">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30650,10 +30671,10 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B561" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C561" t="s">
         <v>1323</v>
@@ -30665,7 +30686,7 @@
         <v>1332</v>
       </c>
       <c r="G561" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H561" t="s">
         <v>1349</v>
@@ -30674,10 +30695,10 @@
         <v>564</v>
       </c>
       <c r="K561">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L561">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M561">
         <v>60</v>
@@ -30688,7 +30709,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B562" t="s">
         <v>55</v>
@@ -30703,7 +30724,7 @@
         <v>1332</v>
       </c>
       <c r="G562" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H562" t="s">
         <v>1349</v>
@@ -30712,10 +30733,10 @@
         <v>564</v>
       </c>
       <c r="K562">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L562">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M562">
         <v>60</v>
@@ -30726,7 +30747,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B563" t="s">
         <v>55</v>
@@ -30741,7 +30762,7 @@
         <v>1332</v>
       </c>
       <c r="G563" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H563" t="s">
         <v>1349</v>
@@ -30753,7 +30774,7 @@
         <v>75</v>
       </c>
       <c r="L563">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M563">
         <v>60</v>
@@ -30764,10 +30785,10 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B564" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C564" t="s">
         <v>1323</v>
@@ -30779,10 +30800,10 @@
         <v>1332</v>
       </c>
       <c r="G564" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H564" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J564" t="s">
         <v>564</v>
@@ -30791,10 +30812,10 @@
         <v>75</v>
       </c>
       <c r="L564">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M564">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P564" s="19">
         <v>46155</v>
@@ -30802,7 +30823,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B565" t="s">
         <v>66</v>
@@ -30817,10 +30838,10 @@
         <v>1332</v>
       </c>
       <c r="G565" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H565" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J565" t="s">
         <v>564</v>
@@ -30829,10 +30850,10 @@
         <v>75</v>
       </c>
       <c r="L565">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M565">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P565" s="19">
         <v>46155</v>
@@ -30840,7 +30861,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B566" t="s">
         <v>66</v>
@@ -30855,10 +30876,10 @@
         <v>1332</v>
       </c>
       <c r="G566" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H566" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J566" t="s">
         <v>564</v>
@@ -30867,10 +30888,10 @@
         <v>75</v>
       </c>
       <c r="L566">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M566">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P566" s="19">
         <v>46155</v>
@@ -30878,7 +30899,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B567" t="s">
         <v>66</v>
@@ -30893,10 +30914,10 @@
         <v>1332</v>
       </c>
       <c r="G567" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H567" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J567" t="s">
         <v>564</v>
@@ -30905,10 +30926,10 @@
         <v>75</v>
       </c>
       <c r="L567">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M567">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P567" s="19">
         <v>46155</v>
@@ -30916,7 +30937,7 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B568" t="s">
         <v>66</v>
@@ -30931,10 +30952,10 @@
         <v>1332</v>
       </c>
       <c r="G568" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H568" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J568" t="s">
         <v>564</v>
@@ -30943,10 +30964,10 @@
         <v>75</v>
       </c>
       <c r="L568">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M568">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P568" s="19">
         <v>46155</v>
@@ -30954,10 +30975,10 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B569" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C569" t="s">
         <v>1323</v>
@@ -30969,10 +30990,10 @@
         <v>1332</v>
       </c>
       <c r="G569" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H569" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J569" t="s">
         <v>564</v>
@@ -30981,7 +31002,7 @@
         <v>75</v>
       </c>
       <c r="L569">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M569">
         <v>0</v>
@@ -30992,10 +31013,10 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B570" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C570" t="s">
         <v>1323</v>
@@ -31007,10 +31028,10 @@
         <v>1332</v>
       </c>
       <c r="G570" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H570" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J570" t="s">
         <v>564</v>
@@ -31019,10 +31040,10 @@
         <v>75</v>
       </c>
       <c r="L570">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M570">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P570" s="19">
         <v>46155</v>
@@ -31030,7 +31051,7 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B571" t="s">
         <v>66</v>
@@ -31045,7 +31066,7 @@
         <v>1332</v>
       </c>
       <c r="G571" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H571" t="s">
         <v>1352</v>
@@ -31057,10 +31078,10 @@
         <v>75</v>
       </c>
       <c r="L571">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M571">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P571" s="19">
         <v>46155</v>
@@ -31068,7 +31089,7 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B572" t="s">
         <v>66</v>
@@ -31083,10 +31104,10 @@
         <v>1332</v>
       </c>
       <c r="G572" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H572" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J572" t="s">
         <v>564</v>
@@ -31095,10 +31116,10 @@
         <v>75</v>
       </c>
       <c r="L572">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M572">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P572" s="19">
         <v>46155</v>
@@ -31106,7 +31127,7 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B573" t="s">
         <v>66</v>
@@ -31121,10 +31142,10 @@
         <v>1332</v>
       </c>
       <c r="G573" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H573" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J573" t="s">
         <v>564</v>
@@ -31144,7 +31165,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B574" t="s">
         <v>66</v>
@@ -31159,22 +31180,22 @@
         <v>1332</v>
       </c>
       <c r="G574" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H574" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J574" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K574">
         <v>75</v>
       </c>
       <c r="L574">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M574">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P574" s="19">
         <v>46155</v>
@@ -31182,7 +31203,7 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B575" t="s">
         <v>66</v>
@@ -31197,22 +31218,22 @@
         <v>1332</v>
       </c>
       <c r="G575" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H575" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J575">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J575" t="s">
+        <v>167</v>
       </c>
       <c r="K575">
         <v>75</v>
       </c>
       <c r="L575">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M575">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P575" s="19">
         <v>46155</v>
@@ -31220,7 +31241,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -31228,9 +31249,6 @@
       <c r="C576" t="s">
         <v>1323</v>
       </c>
-      <c r="D576" t="s">
-        <v>1008</v>
-      </c>
       <c r="E576" t="s">
         <v>1323</v>
       </c>
@@ -31238,22 +31256,22 @@
         <v>1332</v>
       </c>
       <c r="G576" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H576" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J576" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J576">
+        <v>2017</v>
       </c>
       <c r="K576">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L576">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M576">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P576" s="19">
         <v>46155</v>
@@ -31261,7 +31279,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B577" t="s">
         <v>66</v>
@@ -31279,7 +31297,7 @@
         <v>1332</v>
       </c>
       <c r="G577" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H577" t="s">
         <v>1352</v>
@@ -31291,10 +31309,10 @@
         <v>150</v>
       </c>
       <c r="L577">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M577">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P577" s="19">
         <v>46155</v>
@@ -31302,10 +31320,10 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B578" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C578" t="s">
         <v>1323</v>
@@ -31320,10 +31338,10 @@
         <v>1332</v>
       </c>
       <c r="G578" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H578" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J578" t="s">
         <v>564</v>
@@ -31332,10 +31350,10 @@
         <v>150</v>
       </c>
       <c r="L578">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M578">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P578" s="19">
         <v>46155</v>
@@ -31343,7 +31361,7 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B579" t="s">
         <v>55</v>
@@ -31361,7 +31379,7 @@
         <v>1332</v>
       </c>
       <c r="G579" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H579" t="s">
         <v>1334</v>
@@ -31370,10 +31388,10 @@
         <v>564</v>
       </c>
       <c r="K579">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L579">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M579">
         <v>5</v>
@@ -31384,7 +31402,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B580" t="s">
         <v>55</v>
@@ -31402,7 +31420,7 @@
         <v>1332</v>
       </c>
       <c r="G580" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H580" t="s">
         <v>1334</v>
@@ -31411,10 +31429,10 @@
         <v>564</v>
       </c>
       <c r="K580">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L580">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M580">
         <v>5</v>
@@ -31425,37 +31443,40 @@
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B581" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C581" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D581" t="s">
+        <v>1008</v>
       </c>
       <c r="E581" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F581" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G581" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H581" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J581" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K581">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L581">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M581">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P581" s="19">
         <v>46155</v>
@@ -31463,7 +31484,7 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B582" t="s">
         <v>66</v>
@@ -31478,7 +31499,7 @@
         <v>1406</v>
       </c>
       <c r="G582" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H582" t="s">
         <v>1408</v>
@@ -31490,7 +31511,7 @@
         <v>70</v>
       </c>
       <c r="L582">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M582">
         <v>6</v>
@@ -31501,7 +31522,7 @@
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B583" t="s">
         <v>66</v>
@@ -31516,19 +31537,22 @@
         <v>1406</v>
       </c>
       <c r="G583" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H583" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J583" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K583">
         <v>70</v>
       </c>
       <c r="L583">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M583">
+        <v>6</v>
       </c>
       <c r="P583" s="19">
         <v>46155</v>
@@ -31536,7 +31560,7 @@
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B584" t="s">
         <v>66</v>
@@ -31551,19 +31575,19 @@
         <v>1406</v>
       </c>
       <c r="G584" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H584" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J584" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K584">
         <v>70</v>
       </c>
       <c r="L584">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P584" s="19">
         <v>46155</v>
@@ -31571,7 +31595,7 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B585" t="s">
         <v>66</v>
@@ -31586,19 +31610,19 @@
         <v>1406</v>
       </c>
       <c r="G585" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H585" t="s">
         <v>1418</v>
       </c>
       <c r="J585" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K585">
         <v>70</v>
       </c>
       <c r="L585">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P585" s="19">
         <v>46155</v>
@@ -31606,7 +31630,7 @@
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B586" t="s">
         <v>66</v>
@@ -31621,19 +31645,19 @@
         <v>1406</v>
       </c>
       <c r="G586" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H586" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J586" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K586">
         <v>70</v>
       </c>
       <c r="L586">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P586" s="19">
         <v>46155</v>
@@ -31641,7 +31665,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B587" t="s">
         <v>66</v>
@@ -31649,9 +31673,6 @@
       <c r="C587" t="s">
         <v>1405</v>
       </c>
-      <c r="D587" t="s">
-        <v>1008</v>
-      </c>
       <c r="E587" t="s">
         <v>1405</v>
       </c>
@@ -31659,19 +31680,19 @@
         <v>1406</v>
       </c>
       <c r="G587" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H587" t="s">
         <v>1425</v>
       </c>
       <c r="J587" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K587">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L587">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P587" s="19">
         <v>46155</v>
@@ -31679,7 +31700,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B588" t="s">
         <v>66</v>
@@ -31687,26 +31708,29 @@
       <c r="C588" t="s">
         <v>1405</v>
       </c>
+      <c r="D588" t="s">
+        <v>1008</v>
+      </c>
       <c r="E588" t="s">
         <v>1405</v>
       </c>
       <c r="F588" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G588" t="s">
+        <v>1428</v>
       </c>
       <c r="H588" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J588" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K588">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L588">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M588">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P588" s="19">
         <v>46155</v>
@@ -31714,10 +31738,10 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B589" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C589" t="s">
         <v>1405</v>
@@ -31728,17 +31752,17 @@
       <c r="F589" t="s">
         <v>1431</v>
       </c>
-      <c r="G589" t="s">
-        <v>1435</v>
-      </c>
       <c r="H589" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J589" t="s">
+        <v>1433</v>
       </c>
       <c r="K589">
         <v>70</v>
       </c>
       <c r="L589">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M589">
         <v>45</v>
@@ -31749,10 +31773,10 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B590" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C590" t="s">
         <v>1405</v>
@@ -31764,22 +31788,19 @@
         <v>1431</v>
       </c>
       <c r="G590" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H590" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J590" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K590">
         <v>70</v>
       </c>
       <c r="L590">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M590">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P590" s="19">
         <v>46155</v>
@@ -31787,7 +31808,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B591" t="s">
         <v>66</v>
@@ -31802,22 +31823,22 @@
         <v>1431</v>
       </c>
       <c r="G591" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H591" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J591" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K591">
         <v>70</v>
       </c>
       <c r="L591">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M591">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P591" s="19">
         <v>46155</v>
@@ -31825,7 +31846,7 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B592" t="s">
         <v>66</v>
@@ -31837,25 +31858,25 @@
         <v>1405</v>
       </c>
       <c r="F592" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G592" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H592" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J592" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K592">
         <v>70</v>
       </c>
       <c r="L592">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M592">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P592" s="19">
         <v>46155</v>
@@ -31863,7 +31884,7 @@
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B593" t="s">
         <v>66</v>
@@ -31878,7 +31899,7 @@
         <v>1445</v>
       </c>
       <c r="G593" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H593" t="s">
         <v>1447</v>
@@ -31890,21 +31911,21 @@
         <v>70</v>
       </c>
       <c r="L593">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
       <c r="M593">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P593" s="19">
-        <v>46175</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>2365</v>
+        <v>1449</v>
       </c>
       <c r="B594" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C594" t="s">
         <v>1405</v>
@@ -31913,33 +31934,71 @@
         <v>1405</v>
       </c>
       <c r="F594" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G594" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H594" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J594" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K594">
+        <v>70</v>
+      </c>
+      <c r="L594">
+        <v>40.5</v>
+      </c>
+      <c r="M594">
+        <v>5</v>
+      </c>
+      <c r="P594" s="19">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="595" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A595" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B595" t="s">
+        <v>55</v>
+      </c>
+      <c r="C595" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E595" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F595" t="s">
         <v>2366</v>
       </c>
-      <c r="G594" t="s">
+      <c r="G595" t="s">
         <v>2367</v>
       </c>
-      <c r="H594" t="s">
+      <c r="H595" t="s">
         <v>2362</v>
       </c>
-      <c r="J594">
+      <c r="J595">
         <f>5.41+1.74</f>
         <v>7.15</v>
       </c>
-      <c r="K594">
+      <c r="K595">
         <v>70</v>
       </c>
-      <c r="L594">
+      <c r="L595">
         <v>21.95</v>
       </c>
-      <c r="M594">
+      <c r="M595">
         <v>6</v>
       </c>
-      <c r="P594" s="19">
+      <c r="P595" s="19">
         <v>46155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R593" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R594" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="410" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25D5DF51-BA9F-414F-B22F-894B91CE64DA}"/>
+  <xr:revisionPtr revIDLastSave="414" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B783C902-2995-444B-A4D6-1CDDBC06936A}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$594</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$595</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10569" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10577" uniqueCount="2401">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -8013,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R595"/>
+  <dimension ref="A1:R596"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23706,11 +23706,11 @@
       </c>
     </row>
     <row r="391" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A391" t="s">
-        <v>951</v>
+      <c r="A391">
+        <v>73900324</v>
       </c>
       <c r="B391" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C391" t="s">
         <v>906</v>
@@ -23719,39 +23719,36 @@
         <v>913</v>
       </c>
       <c r="E391" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F391" t="s">
-        <v>952</v>
+        <v>2398</v>
       </c>
       <c r="G391" t="s">
-        <v>953</v>
+        <v>2399</v>
       </c>
       <c r="H391" t="s">
-        <v>954</v>
+        <v>2400</v>
       </c>
       <c r="I391" t="s">
         <v>69</v>
       </c>
-      <c r="J391" t="s">
-        <v>98</v>
+      <c r="J391">
+        <v>2024</v>
       </c>
       <c r="K391">
         <v>75</v>
       </c>
       <c r="L391">
-        <v>6.45</v>
+        <v>6.9</v>
       </c>
       <c r="M391">
-        <v>501</v>
-      </c>
-      <c r="P391" s="19">
-        <v>46155</v>
+        <v>12</v>
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A392">
-        <v>10300525</v>
+      <c r="A392" t="s">
+        <v>951</v>
       </c>
       <c r="B392" t="s">
         <v>66</v>
@@ -23769,7 +23766,7 @@
         <v>952</v>
       </c>
       <c r="G392" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H392" t="s">
         <v>954</v>
@@ -23777,25 +23774,25 @@
       <c r="I392" t="s">
         <v>69</v>
       </c>
-      <c r="J392">
-        <v>2025</v>
+      <c r="J392" t="s">
+        <v>98</v>
       </c>
       <c r="K392">
         <v>75</v>
       </c>
       <c r="L392">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M392">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P392" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>956</v>
+      <c r="A393">
+        <v>10300525</v>
       </c>
       <c r="B393" t="s">
         <v>66</v>
@@ -23810,25 +23807,28 @@
         <v>923</v>
       </c>
       <c r="F393" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G393" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H393" t="s">
-        <v>292</v>
-      </c>
-      <c r="J393" t="s">
-        <v>98</v>
+        <v>954</v>
+      </c>
+      <c r="I393" t="s">
+        <v>69</v>
+      </c>
+      <c r="J393">
+        <v>2025</v>
       </c>
       <c r="K393">
         <v>75</v>
       </c>
       <c r="L393">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="M393">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P393" s="19">
         <v>46155</v>
@@ -23836,7 +23836,7 @@
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B394" t="s">
         <v>66</v>
@@ -23853,11 +23853,11 @@
       <c r="F394" t="s">
         <v>957</v>
       </c>
+      <c r="G394" t="s">
+        <v>958</v>
+      </c>
       <c r="H394" t="s">
-        <v>960</v>
-      </c>
-      <c r="I394" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="J394" t="s">
         <v>98</v>
@@ -23866,10 +23866,10 @@
         <v>75</v>
       </c>
       <c r="L394">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="M394">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P394" s="19">
         <v>46155</v>
@@ -23877,10 +23877,10 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B395" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C395" t="s">
         <v>906</v>
@@ -23894,26 +23894,23 @@
       <c r="F395" t="s">
         <v>957</v>
       </c>
-      <c r="G395" t="s">
-        <v>962</v>
-      </c>
       <c r="H395" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I395" t="s">
         <v>69</v>
       </c>
       <c r="J395" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M395">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P395" s="19">
         <v>46155</v>
@@ -23921,10 +23918,10 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B396" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C396" t="s">
         <v>906</v>
@@ -23939,22 +23936,25 @@
         <v>957</v>
       </c>
       <c r="G396" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H396" t="s">
-        <v>920</v>
+        <v>963</v>
+      </c>
+      <c r="I396" t="s">
+        <v>69</v>
       </c>
       <c r="J396" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M396">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
@@ -23962,7 +23962,7 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B397" t="s">
         <v>66</v>
@@ -23980,10 +23980,10 @@
         <v>957</v>
       </c>
       <c r="G397" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H397" t="s">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="J397" t="s">
         <v>286</v>
@@ -23995,15 +23995,15 @@
         <v>9.1</v>
       </c>
       <c r="M397">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A398">
-        <v>43600225</v>
+      <c r="A398" t="s">
+        <v>966</v>
       </c>
       <c r="B398" t="s">
         <v>66</v>
@@ -24021,33 +24021,30 @@
         <v>957</v>
       </c>
       <c r="G398" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H398" t="s">
-        <v>963</v>
-      </c>
-      <c r="I398" t="s">
-        <v>69</v>
+        <v>947</v>
       </c>
       <c r="J398" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M398">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399" t="s">
-        <v>970</v>
+      <c r="A399">
+        <v>43600225</v>
       </c>
       <c r="B399" t="s">
         <v>66</v>
@@ -24065,25 +24062,25 @@
         <v>957</v>
       </c>
       <c r="G399" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H399" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="I399" t="s">
         <v>69</v>
       </c>
       <c r="J399" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M399">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
@@ -24091,7 +24088,7 @@
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B400" t="s">
         <v>66</v>
@@ -24108,8 +24105,14 @@
       <c r="F400" t="s">
         <v>957</v>
       </c>
+      <c r="G400" t="s">
+        <v>971</v>
+      </c>
       <c r="H400" t="s">
-        <v>974</v>
+        <v>972</v>
+      </c>
+      <c r="I400" t="s">
+        <v>69</v>
       </c>
       <c r="J400" t="s">
         <v>98</v>
@@ -24121,7 +24124,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M400">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P400" s="19">
         <v>46155</v>
@@ -24129,7 +24132,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B401" t="s">
         <v>66</v>
@@ -24144,25 +24147,22 @@
         <v>923</v>
       </c>
       <c r="F401" t="s">
-        <v>918</v>
-      </c>
-      <c r="G401" t="s">
-        <v>919</v>
+        <v>957</v>
       </c>
       <c r="H401" t="s">
-        <v>920</v>
+        <v>974</v>
       </c>
       <c r="J401" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M401">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P401" s="19">
         <v>46155</v>
@@ -24170,7 +24170,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B402" t="s">
         <v>66</v>
@@ -24185,25 +24185,25 @@
         <v>923</v>
       </c>
       <c r="F402" t="s">
-        <v>957</v>
+        <v>918</v>
+      </c>
+      <c r="G402" t="s">
+        <v>919</v>
       </c>
       <c r="H402" t="s">
-        <v>972</v>
-      </c>
-      <c r="I402" t="s">
-        <v>69</v>
-      </c>
-      <c r="J402">
-        <v>2025</v>
+        <v>920</v>
+      </c>
+      <c r="J402" t="s">
+        <v>339</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M402">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P402" s="19">
         <v>46155</v>
@@ -24211,40 +24211,40 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B403" t="s">
         <v>66</v>
       </c>
       <c r="C403" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="D403" t="s">
-        <v>979</v>
+        <v>913</v>
       </c>
       <c r="E403" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F403" t="s">
-        <v>980</v>
-      </c>
-      <c r="G403" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="H403" t="s">
-        <v>982</v>
-      </c>
-      <c r="J403" t="s">
-        <v>339</v>
+        <v>972</v>
+      </c>
+      <c r="I403" t="s">
+        <v>69</v>
+      </c>
+      <c r="J403">
+        <v>2025</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M403">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
@@ -24252,7 +24252,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B404" t="s">
         <v>66</v>
@@ -24270,22 +24270,22 @@
         <v>980</v>
       </c>
       <c r="G404" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H404" t="s">
-        <v>985</v>
-      </c>
-      <c r="J404">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J404" t="s">
+        <v>339</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M404">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
@@ -24293,7 +24293,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B405" t="s">
         <v>66</v>
@@ -24308,25 +24308,25 @@
         <v>57</v>
       </c>
       <c r="F405" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G405" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H405" t="s">
-        <v>989</v>
-      </c>
-      <c r="J405" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J405">
+        <v>2025</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M405">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
@@ -24334,7 +24334,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B406" t="s">
         <v>66</v>
@@ -24349,25 +24349,25 @@
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G406" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="H406" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="J406" t="s">
-        <v>286</v>
+        <v>564</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M406">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P406" s="19">
         <v>46155</v>
@@ -24375,7 +24375,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B407" t="s">
         <v>66</v>
@@ -24393,22 +24393,22 @@
         <v>980</v>
       </c>
       <c r="G407" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H407" t="s">
-        <v>292</v>
+        <v>992</v>
       </c>
       <c r="J407" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M407">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P407" s="19">
         <v>46155</v>
@@ -24416,7 +24416,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B408" t="s">
         <v>66</v>
@@ -24434,22 +24434,22 @@
         <v>980</v>
       </c>
       <c r="G408" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H408" t="s">
         <v>292</v>
       </c>
-      <c r="J408">
-        <v>2025</v>
+      <c r="J408" t="s">
+        <v>98</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M408">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P408" s="19">
         <v>46155</v>
@@ -24457,7 +24457,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B409" t="s">
         <v>66</v>
@@ -24475,22 +24475,22 @@
         <v>980</v>
       </c>
       <c r="G409" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H409" t="s">
-        <v>992</v>
-      </c>
-      <c r="J409" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J409">
+        <v>2025</v>
       </c>
       <c r="K409">
         <v>75</v>
       </c>
       <c r="L409">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M409">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P409" s="19">
         <v>46155</v>
@@ -24498,7 +24498,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B410" t="s">
         <v>66</v>
@@ -24513,13 +24513,13 @@
         <v>57</v>
       </c>
       <c r="F410" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G410" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H410" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="J410" t="s">
         <v>339</v>
@@ -24528,10 +24528,10 @@
         <v>75</v>
       </c>
       <c r="L410">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M410">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P410" s="19">
         <v>46155</v>
@@ -24539,7 +24539,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B411" t="s">
         <v>66</v>
@@ -24554,16 +24554,16 @@
         <v>57</v>
       </c>
       <c r="F411" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G411" t="s">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="H411" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J411" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K411">
         <v>75</v>
@@ -24572,7 +24572,7 @@
         <v>5.7</v>
       </c>
       <c r="M411">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P411" s="19">
         <v>46155</v>
@@ -24580,7 +24580,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B412" t="s">
         <v>66</v>
@@ -24598,22 +24598,22 @@
         <v>980</v>
       </c>
       <c r="G412" t="s">
-        <v>1005</v>
+        <v>113</v>
       </c>
       <c r="H412" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="J412" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K412">
         <v>75</v>
       </c>
       <c r="L412">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M412">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P412" s="19">
         <v>46155</v>
@@ -24621,16 +24621,16 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B413" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C413" t="s">
         <v>978</v>
       </c>
       <c r="D413" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E413" t="s">
         <v>57</v>
@@ -24639,7 +24639,7 @@
         <v>980</v>
       </c>
       <c r="G413" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="H413" t="s">
         <v>1006</v>
@@ -24648,13 +24648,13 @@
         <v>339</v>
       </c>
       <c r="K413">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L413">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M413">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P413" s="19">
         <v>46155</v>
@@ -24662,16 +24662,16 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B414" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C414" t="s">
         <v>978</v>
       </c>
       <c r="D414" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="E414" t="s">
         <v>57</v>
@@ -24680,25 +24680,22 @@
         <v>980</v>
       </c>
       <c r="G414" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H414" t="s">
-        <v>992</v>
-      </c>
-      <c r="I414" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="J414" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K414">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L414">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M414">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P414" s="19">
         <v>46155</v>
@@ -24706,7 +24703,7 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B415" t="s">
         <v>66</v>
@@ -24715,31 +24712,34 @@
         <v>978</v>
       </c>
       <c r="D415" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
       </c>
       <c r="F415" t="s">
-        <v>1015</v>
+        <v>980</v>
       </c>
       <c r="G415" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="H415" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I415" t="s">
+        <v>1012</v>
       </c>
       <c r="J415" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K415">
         <v>75</v>
       </c>
       <c r="L415">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M415">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P415" s="19">
         <v>46155</v>
@@ -24747,7 +24747,7 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B416" t="s">
         <v>66</v>
@@ -24756,34 +24756,31 @@
         <v>978</v>
       </c>
       <c r="D416" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E416" t="s">
         <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G416" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H416" t="s">
-        <v>1021</v>
-      </c>
-      <c r="I416" t="s">
-        <v>777</v>
+        <v>1017</v>
       </c>
       <c r="J416" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M416">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P416" s="19">
         <v>46155</v>
@@ -24791,7 +24788,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B417" t="s">
         <v>66</v>
@@ -24806,33 +24803,36 @@
         <v>57</v>
       </c>
       <c r="F417" t="s">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="G417" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="H417" t="s">
-        <v>992</v>
+        <v>1021</v>
+      </c>
+      <c r="I417" t="s">
+        <v>777</v>
       </c>
       <c r="J417" t="s">
-        <v>339</v>
+        <v>217</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M417">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P417" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A418">
-        <v>13003025</v>
+      <c r="A418" t="s">
+        <v>1022</v>
       </c>
       <c r="B418" t="s">
         <v>66</v>
@@ -24850,33 +24850,30 @@
         <v>980</v>
       </c>
       <c r="G418" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H418" t="s">
         <v>992</v>
       </c>
-      <c r="I418" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J418">
-        <v>2025</v>
+      <c r="J418" t="s">
+        <v>339</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M418">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A419" t="s">
-        <v>1025</v>
+      <c r="A419">
+        <v>13003025</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24894,22 +24891,25 @@
         <v>980</v>
       </c>
       <c r="G419" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H419" t="s">
-        <v>589</v>
-      </c>
-      <c r="J419" t="s">
-        <v>339</v>
+        <v>992</v>
+      </c>
+      <c r="I419" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J419">
+        <v>2025</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M419">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
@@ -24917,7 +24917,7 @@
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24932,33 +24932,36 @@
         <v>57</v>
       </c>
       <c r="F420" t="s">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="G420" t="s">
-        <v>165</v>
+        <v>1026</v>
       </c>
       <c r="H420" t="s">
-        <v>1029</v>
+        <v>589</v>
       </c>
       <c r="J420" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M420">
+        <v>321</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A421">
-        <v>43700425</v>
+      <c r="A421" t="s">
+        <v>1027</v>
       </c>
       <c r="B421" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C421" t="s">
         <v>978</v>
@@ -24973,19 +24976,19 @@
         <v>1028</v>
       </c>
       <c r="G421" t="s">
-        <v>1030</v>
+        <v>165</v>
       </c>
       <c r="H421" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J421">
-        <v>2025</v>
+        <v>1029</v>
+      </c>
+      <c r="J421" t="s">
+        <v>286</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>10.5</v>
+        <v>37</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24993,7 +24996,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422">
-        <v>73300125</v>
+        <v>43700425</v>
       </c>
       <c r="B422" t="s">
         <v>55</v>
@@ -25008,13 +25011,13 @@
         <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G422" t="s">
-        <v>113</v>
+        <v>1030</v>
       </c>
       <c r="H422" t="s">
-        <v>2362</v>
+        <v>1031</v>
       </c>
       <c r="J422">
         <v>2025</v>
@@ -25023,10 +25026,7 @@
         <v>75</v>
       </c>
       <c r="L422">
-        <v>4.99</v>
-      </c>
-      <c r="M422">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
@@ -25034,7 +25034,7 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423">
-        <v>73300225</v>
+        <v>73300125</v>
       </c>
       <c r="B423" t="s">
         <v>55</v>
@@ -25052,7 +25052,7 @@
         <v>1033</v>
       </c>
       <c r="G423" t="s">
-        <v>2364</v>
+        <v>113</v>
       </c>
       <c r="H423" t="s">
         <v>2362</v>
@@ -25075,7 +25075,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
-        <v>73300325</v>
+        <v>73300225</v>
       </c>
       <c r="B424" t="s">
         <v>55</v>
@@ -25093,7 +25093,7 @@
         <v>1033</v>
       </c>
       <c r="G424" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H424" t="s">
         <v>2362</v>
@@ -25105,7 +25105,7 @@
         <v>75</v>
       </c>
       <c r="L424">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="M424">
         <v>12</v>
@@ -25116,7 +25116,7 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425">
-        <v>73300425</v>
+        <v>73300325</v>
       </c>
       <c r="B425" t="s">
         <v>55</v>
@@ -25128,13 +25128,13 @@
         <v>979</v>
       </c>
       <c r="E425" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F425" t="s">
         <v>1033</v>
       </c>
       <c r="G425" t="s">
-        <v>1135</v>
+        <v>2363</v>
       </c>
       <c r="H425" t="s">
         <v>2362</v>
@@ -25146,7 +25146,7 @@
         <v>75</v>
       </c>
       <c r="L425">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="M425">
         <v>12</v>
@@ -25156,11 +25156,11 @@
       </c>
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A426" t="s">
-        <v>1032</v>
+      <c r="A426">
+        <v>73300425</v>
       </c>
       <c r="B426" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C426" t="s">
         <v>978</v>
@@ -25169,36 +25169,36 @@
         <v>979</v>
       </c>
       <c r="E426" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F426" t="s">
         <v>1033</v>
       </c>
       <c r="G426" t="s">
-        <v>1034</v>
+        <v>1135</v>
       </c>
       <c r="H426" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J426" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J426">
+        <v>2025</v>
       </c>
       <c r="K426">
         <v>75</v>
       </c>
       <c r="L426">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M426">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P426" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A427">
-        <v>13300125</v>
+      <c r="A427" t="s">
+        <v>1032</v>
       </c>
       <c r="B427" t="s">
         <v>66</v>
@@ -25216,33 +25216,33 @@
         <v>1033</v>
       </c>
       <c r="G427" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H427" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J427">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J427" t="s">
+        <v>98</v>
       </c>
       <c r="K427">
         <v>75</v>
       </c>
       <c r="L427">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M427">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
-        <v>1038</v>
+      <c r="A428">
+        <v>13300125</v>
       </c>
       <c r="B428" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C428" t="s">
         <v>978</v>
@@ -25254,33 +25254,33 @@
         <v>57</v>
       </c>
       <c r="F428" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G428" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H428" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J428" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J428">
+        <v>2025</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M428">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P428" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A429">
-        <v>24003025</v>
+      <c r="A429" t="s">
+        <v>1038</v>
       </c>
       <c r="B429" t="s">
         <v>55</v>
@@ -25289,7 +25289,7 @@
         <v>978</v>
       </c>
       <c r="D429" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E429" t="s">
         <v>57</v>
@@ -25298,16 +25298,13 @@
         <v>58</v>
       </c>
       <c r="G429" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H429" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I429" t="s">
-        <v>69</v>
-      </c>
-      <c r="J429">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J429" t="s">
+        <v>339</v>
       </c>
       <c r="K429">
         <v>75</v>
@@ -25315,13 +25312,16 @@
       <c r="L429">
         <v>6.2</v>
       </c>
+      <c r="M429">
+        <v>0</v>
+      </c>
       <c r="P429" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
-        <v>1044</v>
+      <c r="A430">
+        <v>24003025</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25330,39 +25330,39 @@
         <v>978</v>
       </c>
       <c r="D430" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E430" t="s">
         <v>57</v>
       </c>
       <c r="F430" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G430" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H430" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J430" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I430" t="s">
+        <v>69</v>
+      </c>
+      <c r="J430">
+        <v>2025</v>
       </c>
       <c r="K430">
         <v>75</v>
       </c>
       <c r="L430">
-        <v>7.55</v>
-      </c>
-      <c r="M430">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P430" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25371,28 +25371,28 @@
         <v>978</v>
       </c>
       <c r="D431" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E431" t="s">
         <v>57</v>
       </c>
       <c r="F431" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G431" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H431" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J431" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K431">
         <v>75</v>
       </c>
       <c r="L431">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M431">
         <v>0</v>
@@ -25403,7 +25403,7 @@
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25412,28 +25412,28 @@
         <v>978</v>
       </c>
       <c r="D432" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E432" t="s">
         <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G432" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H432" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J432" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M432">
         <v>0</v>
@@ -25444,7 +25444,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25453,42 +25453,39 @@
         <v>978</v>
       </c>
       <c r="D433" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E433" t="s">
         <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G433" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H433" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I433" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J433" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M433">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P433" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A434">
-        <v>27701225</v>
+      <c r="A434" t="s">
+        <v>1053</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25497,39 +25494,42 @@
         <v>978</v>
       </c>
       <c r="D434" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E434" t="s">
         <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G434" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H434" t="s">
         <v>1055</v>
       </c>
-      <c r="J434">
-        <v>2025</v>
+      <c r="I434" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J434" t="s">
+        <v>286</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M434">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P434" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A435" t="s">
-        <v>1060</v>
+      <c r="A435">
+        <v>27701225</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25538,28 +25538,28 @@
         <v>978</v>
       </c>
       <c r="D435" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E435" t="s">
         <v>57</v>
       </c>
       <c r="F435" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G435" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H435" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J435" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J435">
+        <v>2025</v>
       </c>
       <c r="K435">
         <v>75</v>
       </c>
       <c r="L435">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M435">
         <v>0</v>
@@ -25570,7 +25570,7 @@
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25579,28 +25579,28 @@
         <v>978</v>
       </c>
       <c r="D436" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E436" t="s">
         <v>57</v>
       </c>
       <c r="F436" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G436" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H436" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J436" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K436">
         <v>75</v>
       </c>
       <c r="L436">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -25611,7 +25611,7 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25626,22 +25626,22 @@
         <v>57</v>
       </c>
       <c r="F437" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G437" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H437" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J437" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M437">
         <v>0</v>
@@ -25651,8 +25651,8 @@
       </c>
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A438">
-        <v>68002225</v>
+      <c r="A438" t="s">
+        <v>1065</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25664,13 +25664,13 @@
         <v>1057</v>
       </c>
       <c r="E438" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F438" t="s">
         <v>1066</v>
       </c>
       <c r="G438" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H438" t="s">
         <v>1068</v>
@@ -25682,7 +25682,7 @@
         <v>75</v>
       </c>
       <c r="L438">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M438">
         <v>0</v>
@@ -25693,7 +25693,7 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B439" t="s">
         <v>55</v>
@@ -25708,13 +25708,13 @@
         <v>63</v>
       </c>
       <c r="F439" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G439" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H439" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J439" t="s">
         <v>339</v>
@@ -25723,7 +25723,7 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M439">
         <v>0</v>
@@ -25734,7 +25734,7 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B440" t="s">
         <v>55</v>
@@ -25752,13 +25752,13 @@
         <v>1070</v>
       </c>
       <c r="G440" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H440" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J440">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J440" t="s">
+        <v>339</v>
       </c>
       <c r="K440">
         <v>75</v>
@@ -25774,8 +25774,8 @@
       </c>
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A441" t="s">
-        <v>1075</v>
+      <c r="A441">
+        <v>68002424</v>
       </c>
       <c r="B441" t="s">
         <v>55</v>
@@ -25793,19 +25793,19 @@
         <v>1070</v>
       </c>
       <c r="G441" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H441" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J441" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J441">
+        <v>2024</v>
       </c>
       <c r="K441">
         <v>75</v>
       </c>
       <c r="L441">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M441">
         <v>0</v>
@@ -25815,8 +25815,8 @@
       </c>
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A442">
-        <v>68002623</v>
+      <c r="A442" t="s">
+        <v>1075</v>
       </c>
       <c r="B442" t="s">
         <v>55</v>
@@ -25831,25 +25831,22 @@
         <v>63</v>
       </c>
       <c r="F442" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G442" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H442" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I442" t="s">
-        <v>69</v>
-      </c>
-      <c r="J442">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J442" t="s">
+        <v>564</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -25860,7 +25857,7 @@
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A443">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B443" t="s">
         <v>55</v>
@@ -25872,28 +25869,28 @@
         <v>1057</v>
       </c>
       <c r="E443" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F443" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G443" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H443" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I443" t="s">
         <v>69</v>
       </c>
       <c r="J443">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -25903,8 +25900,8 @@
       </c>
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A444" t="s">
-        <v>1083</v>
+      <c r="A444">
+        <v>68002825</v>
       </c>
       <c r="B444" t="s">
         <v>55</v>
@@ -25919,22 +25916,25 @@
         <v>57</v>
       </c>
       <c r="F444" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G444" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H444" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J444" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I444" t="s">
+        <v>69</v>
+      </c>
+      <c r="J444">
+        <v>2025</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M444">
         <v>0</v>
@@ -25944,8 +25944,8 @@
       </c>
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A445">
-        <v>68003025</v>
+      <c r="A445" t="s">
+        <v>1083</v>
       </c>
       <c r="B445" t="s">
         <v>55</v>
@@ -25957,13 +25957,13 @@
         <v>1057</v>
       </c>
       <c r="E445" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F445" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G445" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H445" t="s">
         <v>1085</v>
@@ -25986,7 +25986,7 @@
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A446">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B446" t="s">
         <v>55</v>
@@ -26004,10 +26004,10 @@
         <v>1078</v>
       </c>
       <c r="G446" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H446" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J446" t="s">
         <v>339</v>
@@ -26016,7 +26016,7 @@
         <v>75</v>
       </c>
       <c r="L446">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M446">
         <v>0</v>
@@ -26026,8 +26026,8 @@
       </c>
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A447" t="s">
-        <v>1089</v>
+      <c r="A447">
+        <v>680031225</v>
       </c>
       <c r="B447" t="s">
         <v>55</v>
@@ -26039,25 +26039,25 @@
         <v>1057</v>
       </c>
       <c r="E447" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F447" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G447" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H447" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J447" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K447">
         <v>75</v>
       </c>
       <c r="L447">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M447">
         <v>0</v>
@@ -26068,10 +26068,10 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B448" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C448" t="s">
         <v>978</v>
@@ -26086,22 +26086,22 @@
         <v>1066</v>
       </c>
       <c r="G448" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H448" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J448">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J448" t="s">
+        <v>98</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M448">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P448" s="19">
         <v>46155</v>
@@ -26109,7 +26109,7 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B449" t="s">
         <v>66</v>
@@ -26118,31 +26118,31 @@
         <v>978</v>
       </c>
       <c r="D449" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E449" t="s">
         <v>57</v>
       </c>
       <c r="F449" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G449" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H449" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J449" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J449">
+        <v>2025</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M449">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26150,7 +26150,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26168,22 +26168,22 @@
         <v>1033</v>
       </c>
       <c r="G450" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H450" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J450">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J450" t="s">
+        <v>98</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M450">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26191,7 +26191,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26206,22 +26206,25 @@
         <v>57</v>
       </c>
       <c r="F451" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G451" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H451" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J451" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J451">
+        <v>2025</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M451">
+        <v>264</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26229,7 +26232,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B452" t="s">
         <v>66</v>
@@ -26244,104 +26247,101 @@
         <v>57</v>
       </c>
       <c r="F452" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G452" t="s">
         <v>1100</v>
       </c>
       <c r="H452" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J452" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A453">
-        <v>53800623</v>
+      <c r="A453" t="s">
+        <v>1102</v>
       </c>
       <c r="B453" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C453" t="s">
         <v>978</v>
       </c>
       <c r="D453" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E453" t="s">
         <v>57</v>
       </c>
       <c r="F453" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G453" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H453" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J453" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>11</v>
-      </c>
-      <c r="M453">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A454" t="s">
-        <v>1107</v>
+      <c r="A454">
+        <v>53800623</v>
       </c>
       <c r="B454" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C454" t="s">
         <v>978</v>
       </c>
       <c r="D454" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E454" t="s">
         <v>57</v>
       </c>
       <c r="F454" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G454" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H454" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J454" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K454">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L454">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M454">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
@@ -26349,7 +26349,7 @@
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B455" t="s">
         <v>66</v>
@@ -26367,22 +26367,22 @@
         <v>980</v>
       </c>
       <c r="G455" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H455" t="s">
-        <v>985</v>
-      </c>
-      <c r="J455">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J455" t="s">
+        <v>564</v>
       </c>
       <c r="K455">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L455">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M455">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
@@ -26390,7 +26390,7 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B456" t="s">
         <v>66</v>
@@ -26399,75 +26399,72 @@
         <v>978</v>
       </c>
       <c r="D456" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E456" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F456" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G456" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H456" t="s">
-        <v>989</v>
-      </c>
-      <c r="J456" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J456">
+        <v>2025</v>
       </c>
       <c r="K456">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L456">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M456">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A457">
-        <v>71501125</v>
+      <c r="A457" t="s">
+        <v>1111</v>
       </c>
       <c r="B457" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C457" t="s">
         <v>978</v>
       </c>
       <c r="D457" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E457" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F457" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G457" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H457" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I457" t="s">
-        <v>69</v>
-      </c>
-      <c r="J457">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J457" t="s">
+        <v>564</v>
       </c>
       <c r="K457">
         <v>75</v>
       </c>
       <c r="L457">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M457">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P457" s="19">
         <v>46155</v>
@@ -26475,7 +26472,7 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B458" t="s">
         <v>55</v>
@@ -26487,17 +26484,20 @@
         <v>979</v>
       </c>
       <c r="E458" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F458" t="s">
         <v>980</v>
       </c>
       <c r="G458" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H458" t="s">
         <v>1113</v>
       </c>
+      <c r="I458" t="s">
+        <v>69</v>
+      </c>
       <c r="J458">
         <v>2025</v>
       </c>
@@ -26505,7 +26505,7 @@
         <v>75</v>
       </c>
       <c r="L458">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M458">
         <v>324</v>
@@ -26516,7 +26516,7 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B459" t="s">
         <v>55</v>
@@ -26534,7 +26534,7 @@
         <v>980</v>
       </c>
       <c r="G459" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H459" t="s">
         <v>1113</v>
@@ -26557,7 +26557,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B460" t="s">
         <v>55</v>
@@ -26572,10 +26572,10 @@
         <v>63</v>
       </c>
       <c r="F460" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G460" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H460" t="s">
         <v>1113</v>
@@ -26598,7 +26598,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B461" t="s">
         <v>55</v>
@@ -26610,13 +26610,13 @@
         <v>979</v>
       </c>
       <c r="E461" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G461" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H461" t="s">
         <v>1113</v>
@@ -26639,7 +26639,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B462" t="s">
         <v>55</v>
@@ -26654,10 +26654,10 @@
         <v>57</v>
       </c>
       <c r="F462" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G462" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H462" t="s">
         <v>1113</v>
@@ -26680,7 +26680,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B463" t="s">
         <v>55</v>
@@ -26692,13 +26692,13 @@
         <v>979</v>
       </c>
       <c r="E463" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F463" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G463" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H463" t="s">
         <v>1113</v>
@@ -26710,7 +26710,7 @@
         <v>75</v>
       </c>
       <c r="L463">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M463">
         <v>324</v>
@@ -26721,7 +26721,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26736,7 +26736,7 @@
         <v>63</v>
       </c>
       <c r="F464" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G464" t="s">
         <v>1120</v>
@@ -26751,7 +26751,7 @@
         <v>75</v>
       </c>
       <c r="L464">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M464">
         <v>324</v>
@@ -26762,7 +26762,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B465" t="s">
         <v>55</v>
@@ -26777,7 +26777,7 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G465" t="s">
         <v>1120</v>
@@ -26785,9 +26785,6 @@
       <c r="H465" t="s">
         <v>1113</v>
       </c>
-      <c r="I465" t="s">
-        <v>69</v>
-      </c>
       <c r="J465">
         <v>2025</v>
       </c>
@@ -26806,7 +26803,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B466" t="s">
         <v>55</v>
@@ -26818,10 +26815,10 @@
         <v>979</v>
       </c>
       <c r="E466" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G466" t="s">
         <v>1120</v>
@@ -26830,7 +26827,7 @@
         <v>1113</v>
       </c>
       <c r="I466" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J466">
         <v>2025</v>
@@ -26839,7 +26836,7 @@
         <v>75</v>
       </c>
       <c r="L466">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M466">
         <v>324</v>
@@ -26850,7 +26847,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B467" t="s">
         <v>55</v>
@@ -26865,7 +26862,7 @@
         <v>57</v>
       </c>
       <c r="F467" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G467" t="s">
         <v>1120</v>
@@ -26883,7 +26880,7 @@
         <v>75</v>
       </c>
       <c r="L467">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M467">
         <v>324</v>
@@ -26894,10 +26891,10 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B468" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C468" t="s">
         <v>978</v>
@@ -26906,16 +26903,19 @@
         <v>979</v>
       </c>
       <c r="E468" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F468" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G468" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H468" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I468" t="s">
+        <v>175</v>
       </c>
       <c r="J468">
         <v>2025</v>
@@ -26924,7 +26924,7 @@
         <v>75</v>
       </c>
       <c r="L468">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M468">
         <v>324</v>
@@ -26934,8 +26934,8 @@
       </c>
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A469" t="s">
-        <v>1125</v>
+      <c r="A469">
+        <v>16000125</v>
       </c>
       <c r="B469" t="s">
         <v>66</v>
@@ -26953,22 +26953,22 @@
         <v>980</v>
       </c>
       <c r="G469" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H469" t="s">
-        <v>985</v>
-      </c>
-      <c r="J469" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J469">
+        <v>2025</v>
       </c>
       <c r="K469">
         <v>75</v>
       </c>
       <c r="L469">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M469">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P469" s="19">
         <v>46155</v>
@@ -26976,7 +26976,7 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B470" t="s">
         <v>66</v>
@@ -26994,22 +26994,22 @@
         <v>980</v>
       </c>
       <c r="G470" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H470" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J470" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M470">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
@@ -27017,7 +27017,7 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B471" t="s">
         <v>66</v>
@@ -27035,22 +27035,22 @@
         <v>980</v>
       </c>
       <c r="G471" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H471" t="s">
-        <v>985</v>
-      </c>
-      <c r="J471">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J471" t="s">
+        <v>286</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M471">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -27058,7 +27058,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B472" t="s">
         <v>66</v>
@@ -27073,25 +27073,25 @@
         <v>63</v>
       </c>
       <c r="F472" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G472" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H472" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J472" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J472">
+        <v>2025</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M472">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27099,7 +27099,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B473" t="s">
         <v>66</v>
@@ -27114,25 +27114,25 @@
         <v>63</v>
       </c>
       <c r="F473" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G473" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H473" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J473" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M473">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27140,7 +27140,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B474" t="s">
         <v>66</v>
@@ -27158,22 +27158,22 @@
         <v>980</v>
       </c>
       <c r="G474" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H474" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J474" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M474">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27181,7 +27181,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B475" t="s">
         <v>66</v>
@@ -27199,25 +27199,22 @@
         <v>980</v>
       </c>
       <c r="G475" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H475" t="s">
-        <v>982</v>
-      </c>
-      <c r="I475" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J475" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M475">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27225,7 +27222,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B476" t="s">
         <v>66</v>
@@ -27243,13 +27240,13 @@
         <v>980</v>
       </c>
       <c r="G476" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H476" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I476" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J476" t="s">
         <v>61</v>
@@ -27258,10 +27255,10 @@
         <v>75</v>
       </c>
       <c r="L476">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M476">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27269,7 +27266,7 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B477" t="s">
         <v>66</v>
@@ -27284,25 +27281,28 @@
         <v>63</v>
       </c>
       <c r="F477" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G477" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H477" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I477" t="s">
+        <v>1012</v>
       </c>
       <c r="J477" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M477">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27310,7 +27310,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27319,19 +27319,19 @@
         <v>978</v>
       </c>
       <c r="D478" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E478" t="s">
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G478" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H478" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J478" t="s">
         <v>217</v>
@@ -27340,10 +27340,10 @@
         <v>75</v>
       </c>
       <c r="L478">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M478">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27351,7 +27351,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B479" t="s">
         <v>66</v>
@@ -27366,25 +27366,25 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G479" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H479" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J479" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M479">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
@@ -27392,7 +27392,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B480" t="s">
         <v>66</v>
@@ -27410,22 +27410,22 @@
         <v>1147</v>
       </c>
       <c r="G480" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H480" t="s">
         <v>1149</v>
       </c>
       <c r="J480" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M480">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
@@ -27433,37 +27433,40 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B481" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C481" t="s">
         <v>978</v>
       </c>
       <c r="D481" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E481" t="s">
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G481" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H481" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J481" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M481">
+        <v>36</v>
       </c>
       <c r="P481" s="19">
         <v>46155</v>
@@ -27471,7 +27474,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B482" t="s">
         <v>55</v>
@@ -27486,25 +27489,22 @@
         <v>63</v>
       </c>
       <c r="F482" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G482" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H482" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J482" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>12.5</v>
-      </c>
-      <c r="M482">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
@@ -27512,7 +27512,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B483" t="s">
         <v>55</v>
@@ -27527,22 +27527,22 @@
         <v>63</v>
       </c>
       <c r="F483" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G483" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H483" t="s">
         <v>1064</v>
       </c>
       <c r="J483" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M483">
         <v>0</v>
@@ -27553,7 +27553,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B484" t="s">
         <v>55</v>
@@ -27571,19 +27571,19 @@
         <v>1078</v>
       </c>
       <c r="G484" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H484" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J484">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J484" t="s">
+        <v>209</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M484">
         <v>0</v>
@@ -27594,10 +27594,10 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B485" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C485" t="s">
         <v>978</v>
@@ -27609,25 +27609,25 @@
         <v>63</v>
       </c>
       <c r="F485" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G485" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H485" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J485" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J485">
+        <v>2014</v>
       </c>
       <c r="K485">
         <v>75</v>
       </c>
       <c r="L485">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M485">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P485" s="19">
         <v>46155</v>
@@ -27635,10 +27635,10 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B486" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C486" t="s">
         <v>978</v>
@@ -27653,13 +27653,10 @@
         <v>1066</v>
       </c>
       <c r="G486" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H486" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I486" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J486" t="s">
         <v>61</v>
@@ -27668,18 +27665,18 @@
         <v>75</v>
       </c>
       <c r="L486">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M486">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A487">
-        <v>27701324</v>
+      <c r="A487" t="s">
+        <v>1164</v>
       </c>
       <c r="B487" t="s">
         <v>55</v>
@@ -27697,19 +27694,22 @@
         <v>1066</v>
       </c>
       <c r="G487" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H487" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J487">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I487" t="s">
+        <v>69</v>
+      </c>
+      <c r="J487" t="s">
+        <v>61</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M487">
         <v>0</v>
@@ -27719,8 +27719,8 @@
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A488" t="s">
-        <v>1167</v>
+      <c r="A488">
+        <v>27701324</v>
       </c>
       <c r="B488" t="s">
         <v>55</v>
@@ -27738,22 +27738,19 @@
         <v>1066</v>
       </c>
       <c r="G488" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H488" t="s">
         <v>1055</v>
       </c>
-      <c r="I488" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J488" t="s">
-        <v>98</v>
+      <c r="J488">
+        <v>2024</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -27764,31 +27761,31 @@
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B489" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C489" t="s">
         <v>978</v>
       </c>
       <c r="D489" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E489" t="s">
         <v>63</v>
       </c>
       <c r="F489" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G489" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H489" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I489" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J489" t="s">
         <v>98</v>
@@ -27797,10 +27794,10 @@
         <v>75</v>
       </c>
       <c r="L489">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M489">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P489" s="19">
         <v>46155</v>
@@ -27808,7 +27805,7 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B490" t="s">
         <v>66</v>
@@ -27823,28 +27820,28 @@
         <v>63</v>
       </c>
       <c r="F490" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G490" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H490" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I490" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J490" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M490">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
@@ -27852,10 +27849,10 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B491" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C491" t="s">
         <v>978</v>
@@ -27867,25 +27864,28 @@
         <v>63</v>
       </c>
       <c r="F491" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G491" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H491" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I491" t="s">
+        <v>69</v>
       </c>
       <c r="J491" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M491">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27893,7 +27893,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B492" t="s">
         <v>55</v>
@@ -27911,19 +27911,22 @@
         <v>1175</v>
       </c>
       <c r="G492" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H492" t="s">
         <v>1177</v>
       </c>
       <c r="J492" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M492">
+        <v>0</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27931,10 +27934,10 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B493" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27946,28 +27949,22 @@
         <v>63</v>
       </c>
       <c r="F493" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G493" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H493" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I493" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J493" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>7.6</v>
-      </c>
-      <c r="M493">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27975,10 +27972,10 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B494" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C494" t="s">
         <v>978</v>
@@ -27990,25 +27987,28 @@
         <v>63</v>
       </c>
       <c r="F494" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G494" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H494" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I494" t="s">
+        <v>69</v>
       </c>
       <c r="J494" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M494">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -28016,7 +28016,7 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B495" t="s">
         <v>55</v>
@@ -28034,22 +28034,22 @@
         <v>1185</v>
       </c>
       <c r="G495" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H495" t="s">
         <v>1049</v>
       </c>
       <c r="J495" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M495">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -28057,10 +28057,10 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B496" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C496" t="s">
         <v>978</v>
@@ -28072,25 +28072,25 @@
         <v>63</v>
       </c>
       <c r="F496" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G496" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H496" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I496" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J496" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K496">
         <v>75</v>
       </c>
       <c r="L496">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M496">
+        <v>6</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -28098,7 +28098,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B497" t="s">
         <v>66</v>
@@ -28113,25 +28113,25 @@
         <v>63</v>
       </c>
       <c r="F497" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G497" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H497" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I497" t="s">
+        <v>777</v>
       </c>
       <c r="J497" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M497">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28139,7 +28139,7 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28154,25 +28154,25 @@
         <v>63</v>
       </c>
       <c r="F498" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G498" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H498" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I498" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J498" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M498">
+        <v>53</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
@@ -28180,7 +28180,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28195,28 +28195,25 @@
         <v>63</v>
       </c>
       <c r="F499" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G499" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H499" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I499" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J499" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>6.5</v>
-      </c>
-      <c r="M499">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
@@ -28224,10 +28221,10 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B500" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C500" t="s">
         <v>978</v>
@@ -28242,30 +28239,33 @@
         <v>1122</v>
       </c>
       <c r="G500" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H500" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I500" t="s">
+        <v>175</v>
       </c>
       <c r="J500" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M500">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A501">
-        <v>16003124</v>
+      <c r="A501" t="s">
+        <v>1202</v>
       </c>
       <c r="B501" t="s">
         <v>55</v>
@@ -28277,19 +28277,19 @@
         <v>979</v>
       </c>
       <c r="E501" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F501" t="s">
         <v>1122</v>
       </c>
       <c r="G501" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H501" t="s">
         <v>1204</v>
       </c>
       <c r="J501" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K501">
         <v>75</v>
@@ -28305,11 +28305,11 @@
       </c>
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A502" t="s">
-        <v>1206</v>
+      <c r="A502">
+        <v>16003124</v>
       </c>
       <c r="B502" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C502" t="s">
         <v>978</v>
@@ -28318,31 +28318,28 @@
         <v>979</v>
       </c>
       <c r="E502" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F502" t="s">
         <v>1122</v>
       </c>
       <c r="G502" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H502" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I502" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J502" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M502">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
@@ -28350,10 +28347,10 @@
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B503" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C503" t="s">
         <v>978</v>
@@ -28368,25 +28365,25 @@
         <v>1122</v>
       </c>
       <c r="G503" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H503" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I503" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J503" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M503">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
@@ -28394,10 +28391,10 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B504" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C504" t="s">
         <v>978</v>
@@ -28412,13 +28409,13 @@
         <v>1122</v>
       </c>
       <c r="G504" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H504" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I504" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J504" t="s">
         <v>61</v>
@@ -28427,7 +28424,7 @@
         <v>75</v>
       </c>
       <c r="L504">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M504">
         <v>171</v>
@@ -28438,10 +28435,10 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B505" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C505" t="s">
         <v>978</v>
@@ -28456,19 +28453,25 @@
         <v>1122</v>
       </c>
       <c r="G505" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H505" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I505" t="s">
+        <v>175</v>
       </c>
       <c r="J505" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M505">
+        <v>171</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28476,10 +28479,10 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B506" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C506" t="s">
         <v>978</v>
@@ -28491,28 +28494,22 @@
         <v>63</v>
       </c>
       <c r="F506" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G506" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H506" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I506" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J506" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>24.08</v>
-      </c>
-      <c r="M506">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P506" s="19">
         <v>46155</v>
@@ -28520,10 +28517,10 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B507" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C507" t="s">
         <v>978</v>
@@ -28535,19 +28532,28 @@
         <v>63</v>
       </c>
       <c r="F507" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G507" t="s">
+        <v>1216</v>
       </c>
       <c r="H507" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I507" t="s">
+        <v>175</v>
       </c>
       <c r="J507" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M507">
+        <v>12</v>
       </c>
       <c r="P507" s="19">
         <v>46155</v>
@@ -28555,10 +28561,10 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B508" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C508" t="s">
         <v>978</v>
@@ -28570,30 +28576,27 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H508" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J508" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>7.05</v>
-      </c>
-      <c r="M508">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P508" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A509">
-        <v>27100523</v>
+      <c r="A509" t="s">
+        <v>1221</v>
       </c>
       <c r="B509" t="s">
         <v>66</v>
@@ -28608,36 +28611,33 @@
         <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G509" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H509" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I509" t="s">
-        <v>777</v>
-      </c>
-      <c r="J509">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J509" t="s">
+        <v>217</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M509">
+        <v>30</v>
       </c>
       <c r="P509" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A510" t="s">
-        <v>1225</v>
+      <c r="A510">
+        <v>27100523</v>
       </c>
       <c r="B510" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C510" t="s">
         <v>978</v>
@@ -28649,33 +28649,36 @@
         <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G510" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H510" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J510" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I510" t="s">
+        <v>777</v>
+      </c>
+      <c r="J510">
+        <v>2023</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P510" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B511" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C511" t="s">
         <v>978</v>
@@ -28687,33 +28690,33 @@
         <v>63</v>
       </c>
       <c r="F511" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G511" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H511" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J511" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>7.35</v>
-      </c>
-      <c r="M511">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P511" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A512" t="s">
+        <v>1229</v>
+      </c>
       <c r="B512" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C512" t="s">
         <v>978</v>
@@ -28728,19 +28731,19 @@
         <v>1119</v>
       </c>
       <c r="G512" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H512" t="s">
         <v>1231</v>
       </c>
       <c r="J512" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K512">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L512">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M512">
         <v>2215</v>
@@ -28750,11 +28753,8 @@
       </c>
     </row>
     <row r="513" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A513" t="s">
-        <v>1233</v>
-      </c>
       <c r="B513" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C513" t="s">
         <v>978</v>
@@ -28769,22 +28769,22 @@
         <v>1119</v>
       </c>
       <c r="G513" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H513" t="s">
         <v>1231</v>
       </c>
-      <c r="J513">
-        <v>2023</v>
+      <c r="J513" t="s">
+        <v>61</v>
       </c>
       <c r="K513">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L513">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M513">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
@@ -28792,7 +28792,7 @@
     </row>
     <row r="514" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B514" t="s">
         <v>66</v>
@@ -28810,25 +28810,22 @@
         <v>1119</v>
       </c>
       <c r="G514" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H514" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I514" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J514" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J514">
+        <v>2023</v>
       </c>
       <c r="K514">
         <v>75</v>
       </c>
       <c r="L514">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M514">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
@@ -28836,10 +28833,10 @@
     </row>
     <row r="515" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B515" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C515" t="s">
         <v>978</v>
@@ -28854,19 +28851,25 @@
         <v>1119</v>
       </c>
       <c r="G515" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H515" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I515" t="s">
+        <v>1238</v>
       </c>
       <c r="J515" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K515">
         <v>75</v>
       </c>
       <c r="L515">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M515">
+        <v>205</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28874,7 +28877,7 @@
     </row>
     <row r="516" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B516" t="s">
         <v>55</v>
@@ -28892,10 +28895,10 @@
         <v>1119</v>
       </c>
       <c r="G516" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H516" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J516" t="s">
         <v>98</v>
@@ -28904,21 +28907,18 @@
         <v>75</v>
       </c>
       <c r="L516">
-        <v>14.6</v>
-      </c>
-      <c r="M516">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="517" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A517">
-        <v>43700124</v>
+      <c r="A517" t="s">
+        <v>1242</v>
       </c>
       <c r="B517" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C517" t="s">
         <v>978</v>
@@ -28930,22 +28930,25 @@
         <v>63</v>
       </c>
       <c r="F517" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G517" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H517" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J517">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J517" t="s">
+        <v>98</v>
       </c>
       <c r="K517">
         <v>75</v>
       </c>
       <c r="L517">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M517">
+        <v>0</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28953,10 +28956,10 @@
     </row>
     <row r="518" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A518">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B518" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C518" t="s">
         <v>978</v>
@@ -28971,19 +28974,19 @@
         <v>1028</v>
       </c>
       <c r="G518" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H518" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J518">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K518">
         <v>75</v>
       </c>
       <c r="L518">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
@@ -28991,7 +28994,7 @@
     </row>
     <row r="519" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A519">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B519" t="s">
         <v>55</v>
@@ -29009,30 +29012,30 @@
         <v>1028</v>
       </c>
       <c r="G519" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H519" t="s">
         <v>1031</v>
       </c>
       <c r="J519">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="520" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A520" t="s">
-        <v>1247</v>
+      <c r="A520">
+        <v>43700524</v>
       </c>
       <c r="B520" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C520" t="s">
         <v>978</v>
@@ -29041,28 +29044,25 @@
         <v>979</v>
       </c>
       <c r="E520" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F520" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G520" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H520" t="s">
-        <v>982</v>
-      </c>
-      <c r="J520" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J520">
+        <v>2024</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>3.8</v>
-      </c>
-      <c r="M520">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -29070,7 +29070,7 @@
     </row>
     <row r="521" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B521" t="s">
         <v>66</v>
@@ -29088,22 +29088,22 @@
         <v>980</v>
       </c>
       <c r="G521" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H521" t="s">
-        <v>985</v>
-      </c>
-      <c r="J521">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J521" t="s">
+        <v>98</v>
       </c>
       <c r="K521">
         <v>75</v>
       </c>
       <c r="L521">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M521">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
@@ -29111,7 +29111,7 @@
     </row>
     <row r="522" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29129,10 +29129,10 @@
         <v>980</v>
       </c>
       <c r="G522" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H522" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J522">
         <v>2025</v>
@@ -29141,10 +29141,10 @@
         <v>75</v>
       </c>
       <c r="L522">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M522">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29152,10 +29152,10 @@
     </row>
     <row r="523" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B523" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C523" t="s">
         <v>978</v>
@@ -29170,22 +29170,22 @@
         <v>980</v>
       </c>
       <c r="G523" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H523" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J523" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J523">
+        <v>2025</v>
       </c>
       <c r="K523">
         <v>75</v>
       </c>
       <c r="L523">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M523">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29193,10 +29193,10 @@
     </row>
     <row r="524" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B524" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C524" t="s">
         <v>978</v>
@@ -29211,22 +29211,22 @@
         <v>980</v>
       </c>
       <c r="G524" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H524" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J524" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K524">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L524">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M524">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29234,7 +29234,7 @@
     </row>
     <row r="525" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B525" t="s">
         <v>66</v>
@@ -29252,22 +29252,22 @@
         <v>980</v>
       </c>
       <c r="G525" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H525" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J525" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K525">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L525">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M525">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29275,40 +29275,40 @@
     </row>
     <row r="526" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
       </c>
       <c r="C526" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D526" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E526" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F526" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G526" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H526" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J526" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K526">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L526">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M526">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29316,7 +29316,7 @@
     </row>
     <row r="527" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
@@ -29331,13 +29331,13 @@
         <v>57</v>
       </c>
       <c r="F527" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G527" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H527" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J527" t="s">
         <v>339</v>
@@ -29346,21 +29346,18 @@
         <v>75</v>
       </c>
       <c r="L527">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M527">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
       </c>
-      <c r="R527" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A528">
-        <v>24000925</v>
+      <c r="A528" t="s">
+        <v>1262</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29372,36 +29369,39 @@
         <v>1258</v>
       </c>
       <c r="E528" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F528" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G528" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H528" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J528">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J528" t="s">
+        <v>339</v>
       </c>
       <c r="K528">
         <v>75</v>
       </c>
       <c r="L528">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M528">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
       </c>
+      <c r="R528" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="529" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A529" t="s">
-        <v>1266</v>
+      <c r="A529">
+        <v>24000925</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29413,28 +29413,28 @@
         <v>1258</v>
       </c>
       <c r="E529" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F529" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G529" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H529" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J529" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J529">
+        <v>2025</v>
       </c>
       <c r="K529">
         <v>75</v>
       </c>
       <c r="L529">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M529">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
@@ -29442,7 +29442,7 @@
     </row>
     <row r="530" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29457,33 +29457,33 @@
         <v>63</v>
       </c>
       <c r="F530" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G530" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H530" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J530" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K530">
         <v>75</v>
       </c>
       <c r="L530">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M530">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="531" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A531">
-        <v>24001825</v>
+      <c r="A531" t="s">
+        <v>1270</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29498,33 +29498,33 @@
         <v>63</v>
       </c>
       <c r="F531" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G531" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H531" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J531">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J531" t="s">
+        <v>98</v>
       </c>
       <c r="K531">
         <v>75</v>
       </c>
       <c r="L531">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M531">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="532" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A532" t="s">
-        <v>1275</v>
+      <c r="A532">
+        <v>24001825</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29539,22 +29539,25 @@
         <v>63</v>
       </c>
       <c r="F532" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G532" t="s">
+        <v>1274</v>
       </c>
       <c r="H532" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J532" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J532">
+        <v>2025</v>
       </c>
       <c r="K532">
         <v>75</v>
       </c>
       <c r="L532">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M532">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
@@ -29562,7 +29565,7 @@
     </row>
     <row r="533" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B533" t="s">
         <v>66</v>
@@ -29577,28 +29580,22 @@
         <v>63</v>
       </c>
       <c r="F533" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G533" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H533" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I533" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J533" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K533">
         <v>75</v>
       </c>
       <c r="L533">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M533">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P533" s="19">
         <v>46155</v>
@@ -29606,7 +29603,7 @@
     </row>
     <row r="534" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B534" t="s">
         <v>66</v>
@@ -29615,28 +29612,34 @@
         <v>1257</v>
       </c>
       <c r="D534" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E534" t="s">
         <v>63</v>
       </c>
       <c r="F534" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G534" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H534" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I534" t="s">
+        <v>69</v>
       </c>
       <c r="J534" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K534">
         <v>75</v>
       </c>
       <c r="L534">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M534">
+        <v>318</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29644,7 +29647,7 @@
     </row>
     <row r="535" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29662,22 +29665,19 @@
         <v>1284</v>
       </c>
       <c r="G535" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H535" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J535" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K535">
         <v>75</v>
       </c>
       <c r="L535">
-        <v>6.1</v>
-      </c>
-      <c r="M535">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29685,7 +29685,7 @@
     </row>
     <row r="536" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29708,8 +29708,8 @@
       <c r="H536" t="s">
         <v>1289</v>
       </c>
-      <c r="J536">
-        <v>2024</v>
+      <c r="J536" t="s">
+        <v>87</v>
       </c>
       <c r="K536">
         <v>75</v>
@@ -29717,16 +29717,19 @@
       <c r="L536">
         <v>6.1</v>
       </c>
+      <c r="M536">
+        <v>133</v>
+      </c>
       <c r="P536" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="537" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B537" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C537" t="s">
         <v>1257</v>
@@ -29741,30 +29744,27 @@
         <v>1284</v>
       </c>
       <c r="G537" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H537" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J537" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J537">
+        <v>2024</v>
       </c>
       <c r="K537">
         <v>75</v>
       </c>
       <c r="L537">
-        <v>13.2</v>
-      </c>
-      <c r="M537">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P537" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="538" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B538" t="s">
         <v>55</v>
@@ -29782,19 +29782,19 @@
         <v>1284</v>
       </c>
       <c r="G538" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H538" t="s">
         <v>1293</v>
       </c>
       <c r="J538" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K538">
         <v>75</v>
       </c>
       <c r="L538">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M538">
         <v>0</v>
@@ -29805,7 +29805,7 @@
     </row>
     <row r="539" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B539" t="s">
         <v>55</v>
@@ -29820,22 +29820,22 @@
         <v>63</v>
       </c>
       <c r="F539" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G539" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H539" t="s">
         <v>1293</v>
       </c>
       <c r="J539" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K539">
         <v>75</v>
       </c>
       <c r="L539">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M539">
         <v>0</v>
@@ -29845,49 +29845,49 @@
       </c>
     </row>
     <row r="540" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A540">
-        <v>10702526</v>
+      <c r="A540" t="s">
+        <v>1296</v>
       </c>
       <c r="B540" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C540" t="s">
         <v>1257</v>
       </c>
       <c r="D540" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E540" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F540" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G540" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H540" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J540">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J540" t="s">
+        <v>61</v>
       </c>
       <c r="K540">
         <v>75</v>
       </c>
       <c r="L540">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M540">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="541" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A541" t="s">
-        <v>1301</v>
+      <c r="A541">
+        <v>10702526</v>
       </c>
       <c r="B541" t="s">
         <v>66</v>
@@ -29896,31 +29896,31 @@
         <v>1257</v>
       </c>
       <c r="D541" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E541" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F541" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G541" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H541" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J541" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J541">
+        <v>2026</v>
       </c>
       <c r="K541">
         <v>75</v>
       </c>
       <c r="L541">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M541">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
@@ -29928,7 +29928,7 @@
     </row>
     <row r="542" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29946,7 +29946,7 @@
         <v>1303</v>
       </c>
       <c r="G542" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H542" t="s">
         <v>1305</v>
@@ -29958,10 +29958,10 @@
         <v>75</v>
       </c>
       <c r="L542">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M542">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
@@ -29969,7 +29969,7 @@
     </row>
     <row r="543" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29987,7 +29987,7 @@
         <v>1303</v>
       </c>
       <c r="G543" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H543" t="s">
         <v>1305</v>
@@ -30002,7 +30002,7 @@
         <v>8.6</v>
       </c>
       <c r="M543">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -30010,7 +30010,7 @@
     </row>
     <row r="544" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -30028,13 +30028,13 @@
         <v>1303</v>
       </c>
       <c r="G544" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H544" t="s">
         <v>1305</v>
       </c>
       <c r="J544" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K544">
         <v>75</v>
@@ -30043,7 +30043,7 @@
         <v>8.6</v>
       </c>
       <c r="M544">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -30051,7 +30051,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -30069,7 +30069,7 @@
         <v>1303</v>
       </c>
       <c r="G545" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H545" t="s">
         <v>1305</v>
@@ -30084,7 +30084,7 @@
         <v>8.6</v>
       </c>
       <c r="M545">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -30092,7 +30092,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -30110,22 +30110,22 @@
         <v>1303</v>
       </c>
       <c r="G546" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H546" t="s">
         <v>1305</v>
       </c>
       <c r="J546" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K546">
         <v>75</v>
       </c>
       <c r="L546">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M546">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -30133,7 +30133,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -30151,22 +30151,22 @@
         <v>1303</v>
       </c>
       <c r="G547" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H547" t="s">
         <v>1305</v>
       </c>
-      <c r="J547">
-        <v>2021</v>
+      <c r="J547" t="s">
+        <v>127</v>
       </c>
       <c r="K547">
         <v>75</v>
       </c>
       <c r="L547">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M547">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -30174,7 +30174,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30192,13 +30192,13 @@
         <v>1303</v>
       </c>
       <c r="G548" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H548" t="s">
         <v>1305</v>
       </c>
-      <c r="J548" t="s">
-        <v>109</v>
+      <c r="J548">
+        <v>2021</v>
       </c>
       <c r="K548">
         <v>75</v>
@@ -30207,7 +30207,7 @@
         <v>13</v>
       </c>
       <c r="M548">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30215,7 +30215,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30233,7 +30233,7 @@
         <v>1303</v>
       </c>
       <c r="G549" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H549" t="s">
         <v>1305</v>
@@ -30245,7 +30245,7 @@
         <v>75</v>
       </c>
       <c r="L549">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M549">
         <v>36</v>
@@ -30256,7 +30256,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30268,28 +30268,28 @@
         <v>1302</v>
       </c>
       <c r="E550" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F550" t="s">
         <v>1303</v>
       </c>
       <c r="G550" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H550" t="s">
         <v>1305</v>
       </c>
       <c r="J550" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K550">
         <v>75</v>
       </c>
       <c r="L550">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M550">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30297,40 +30297,40 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
       </c>
       <c r="C551" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D551" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E551" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F551" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G551" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H551" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J551" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K551">
         <v>75</v>
       </c>
       <c r="L551">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M551">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30338,7 +30338,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30346,17 +30346,20 @@
       <c r="C552" t="s">
         <v>1323</v>
       </c>
+      <c r="D552" t="s">
+        <v>1258</v>
+      </c>
       <c r="E552" t="s">
         <v>1323</v>
       </c>
       <c r="F552" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G552" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H552" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J552" t="s">
         <v>564</v>
@@ -30367,13 +30370,16 @@
       <c r="L552">
         <v>6.2</v>
       </c>
+      <c r="M552">
+        <v>4411</v>
+      </c>
       <c r="P552" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30388,10 +30394,10 @@
         <v>58</v>
       </c>
       <c r="G553" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H553" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J553" t="s">
         <v>564</v>
@@ -30400,7 +30406,7 @@
         <v>75</v>
       </c>
       <c r="L553">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30408,7 +30414,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30420,25 +30426,22 @@
         <v>1323</v>
       </c>
       <c r="F554" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G554" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H554" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J554" t="s">
         <v>564</v>
       </c>
       <c r="K554">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L554">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M554">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30446,7 +30449,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30461,22 +30464,22 @@
         <v>1332</v>
       </c>
       <c r="G555" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H555" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J555" t="s">
         <v>564</v>
       </c>
       <c r="K555">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L555">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M555">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30484,7 +30487,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30499,10 +30502,10 @@
         <v>1332</v>
       </c>
       <c r="G556" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H556" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J556" t="s">
         <v>564</v>
@@ -30511,10 +30514,10 @@
         <v>75</v>
       </c>
       <c r="L556">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M556">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30522,10 +30525,10 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B557" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C557" t="s">
         <v>1323</v>
@@ -30537,10 +30540,10 @@
         <v>1332</v>
       </c>
       <c r="G557" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H557" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J557" t="s">
         <v>564</v>
@@ -30549,7 +30552,10 @@
         <v>75</v>
       </c>
       <c r="L557">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M557">
+        <v>418</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30557,10 +30563,10 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B558" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C558" t="s">
         <v>1323</v>
@@ -30572,10 +30578,10 @@
         <v>1332</v>
       </c>
       <c r="G558" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H558" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J558" t="s">
         <v>564</v>
@@ -30584,10 +30590,7 @@
         <v>75</v>
       </c>
       <c r="L558">
-        <v>25.8</v>
-      </c>
-      <c r="M558">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30595,7 +30598,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30610,10 +30613,10 @@
         <v>1332</v>
       </c>
       <c r="G559" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H559" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J559" t="s">
         <v>564</v>
@@ -30622,10 +30625,10 @@
         <v>75</v>
       </c>
       <c r="L559">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M559">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30633,7 +30636,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30648,10 +30651,10 @@
         <v>1332</v>
       </c>
       <c r="G560" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H560" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J560" t="s">
         <v>564</v>
@@ -30660,10 +30663,10 @@
         <v>75</v>
       </c>
       <c r="L560">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M560">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30671,7 +30674,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30686,10 +30689,10 @@
         <v>1332</v>
       </c>
       <c r="G561" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H561" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J561" t="s">
         <v>564</v>
@@ -30698,10 +30701,10 @@
         <v>75</v>
       </c>
       <c r="L561">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M561">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30709,10 +30712,10 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B562" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C562" t="s">
         <v>1323</v>
@@ -30724,7 +30727,7 @@
         <v>1332</v>
       </c>
       <c r="G562" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H562" t="s">
         <v>1349</v>
@@ -30733,10 +30736,10 @@
         <v>564</v>
       </c>
       <c r="K562">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L562">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M562">
         <v>60</v>
@@ -30747,7 +30750,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B563" t="s">
         <v>55</v>
@@ -30762,7 +30765,7 @@
         <v>1332</v>
       </c>
       <c r="G563" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H563" t="s">
         <v>1349</v>
@@ -30771,10 +30774,10 @@
         <v>564</v>
       </c>
       <c r="K563">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L563">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M563">
         <v>60</v>
@@ -30785,7 +30788,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B564" t="s">
         <v>55</v>
@@ -30800,7 +30803,7 @@
         <v>1332</v>
       </c>
       <c r="G564" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H564" t="s">
         <v>1349</v>
@@ -30812,7 +30815,7 @@
         <v>75</v>
       </c>
       <c r="L564">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M564">
         <v>60</v>
@@ -30823,10 +30826,10 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B565" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C565" t="s">
         <v>1323</v>
@@ -30838,10 +30841,10 @@
         <v>1332</v>
       </c>
       <c r="G565" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H565" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J565" t="s">
         <v>564</v>
@@ -30850,10 +30853,10 @@
         <v>75</v>
       </c>
       <c r="L565">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M565">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P565" s="19">
         <v>46155</v>
@@ -30861,7 +30864,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B566" t="s">
         <v>66</v>
@@ -30876,10 +30879,10 @@
         <v>1332</v>
       </c>
       <c r="G566" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H566" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J566" t="s">
         <v>564</v>
@@ -30888,10 +30891,10 @@
         <v>75</v>
       </c>
       <c r="L566">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M566">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P566" s="19">
         <v>46155</v>
@@ -30899,7 +30902,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B567" t="s">
         <v>66</v>
@@ -30914,10 +30917,10 @@
         <v>1332</v>
       </c>
       <c r="G567" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H567" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J567" t="s">
         <v>564</v>
@@ -30926,10 +30929,10 @@
         <v>75</v>
       </c>
       <c r="L567">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M567">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P567" s="19">
         <v>46155</v>
@@ -30937,7 +30940,7 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B568" t="s">
         <v>66</v>
@@ -30952,10 +30955,10 @@
         <v>1332</v>
       </c>
       <c r="G568" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H568" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J568" t="s">
         <v>564</v>
@@ -30964,10 +30967,10 @@
         <v>75</v>
       </c>
       <c r="L568">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M568">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P568" s="19">
         <v>46155</v>
@@ -30975,7 +30978,7 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B569" t="s">
         <v>66</v>
@@ -30990,10 +30993,10 @@
         <v>1332</v>
       </c>
       <c r="G569" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H569" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J569" t="s">
         <v>564</v>
@@ -31002,10 +31005,10 @@
         <v>75</v>
       </c>
       <c r="L569">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M569">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P569" s="19">
         <v>46155</v>
@@ -31013,10 +31016,10 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B570" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C570" t="s">
         <v>1323</v>
@@ -31028,10 +31031,10 @@
         <v>1332</v>
       </c>
       <c r="G570" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H570" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J570" t="s">
         <v>564</v>
@@ -31040,7 +31043,7 @@
         <v>75</v>
       </c>
       <c r="L570">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M570">
         <v>0</v>
@@ -31051,10 +31054,10 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B571" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C571" t="s">
         <v>1323</v>
@@ -31066,10 +31069,10 @@
         <v>1332</v>
       </c>
       <c r="G571" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H571" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J571" t="s">
         <v>564</v>
@@ -31078,10 +31081,10 @@
         <v>75</v>
       </c>
       <c r="L571">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M571">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P571" s="19">
         <v>46155</v>
@@ -31089,7 +31092,7 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B572" t="s">
         <v>66</v>
@@ -31104,7 +31107,7 @@
         <v>1332</v>
       </c>
       <c r="G572" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H572" t="s">
         <v>1352</v>
@@ -31116,10 +31119,10 @@
         <v>75</v>
       </c>
       <c r="L572">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M572">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P572" s="19">
         <v>46155</v>
@@ -31127,7 +31130,7 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B573" t="s">
         <v>66</v>
@@ -31142,10 +31145,10 @@
         <v>1332</v>
       </c>
       <c r="G573" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H573" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J573" t="s">
         <v>564</v>
@@ -31154,10 +31157,10 @@
         <v>75</v>
       </c>
       <c r="L573">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M573">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P573" s="19">
         <v>46155</v>
@@ -31165,7 +31168,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B574" t="s">
         <v>66</v>
@@ -31180,10 +31183,10 @@
         <v>1332</v>
       </c>
       <c r="G574" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H574" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J574" t="s">
         <v>564</v>
@@ -31203,7 +31206,7 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B575" t="s">
         <v>66</v>
@@ -31218,22 +31221,22 @@
         <v>1332</v>
       </c>
       <c r="G575" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H575" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J575" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K575">
         <v>75</v>
       </c>
       <c r="L575">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M575">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P575" s="19">
         <v>46155</v>
@@ -31241,7 +31244,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -31256,22 +31259,22 @@
         <v>1332</v>
       </c>
       <c r="G576" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H576" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J576">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J576" t="s">
+        <v>167</v>
       </c>
       <c r="K576">
         <v>75</v>
       </c>
       <c r="L576">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M576">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P576" s="19">
         <v>46155</v>
@@ -31279,7 +31282,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B577" t="s">
         <v>66</v>
@@ -31287,9 +31290,6 @@
       <c r="C577" t="s">
         <v>1323</v>
       </c>
-      <c r="D577" t="s">
-        <v>1008</v>
-      </c>
       <c r="E577" t="s">
         <v>1323</v>
       </c>
@@ -31297,22 +31297,22 @@
         <v>1332</v>
       </c>
       <c r="G577" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H577" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J577" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J577">
+        <v>2017</v>
       </c>
       <c r="K577">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L577">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M577">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P577" s="19">
         <v>46155</v>
@@ -31320,7 +31320,7 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B578" t="s">
         <v>66</v>
@@ -31338,7 +31338,7 @@
         <v>1332</v>
       </c>
       <c r="G578" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H578" t="s">
         <v>1352</v>
@@ -31350,10 +31350,10 @@
         <v>150</v>
       </c>
       <c r="L578">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M578">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P578" s="19">
         <v>46155</v>
@@ -31361,10 +31361,10 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B579" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C579" t="s">
         <v>1323</v>
@@ -31379,10 +31379,10 @@
         <v>1332</v>
       </c>
       <c r="G579" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H579" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J579" t="s">
         <v>564</v>
@@ -31391,10 +31391,10 @@
         <v>150</v>
       </c>
       <c r="L579">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M579">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P579" s="19">
         <v>46155</v>
@@ -31402,7 +31402,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B580" t="s">
         <v>55</v>
@@ -31420,7 +31420,7 @@
         <v>1332</v>
       </c>
       <c r="G580" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H580" t="s">
         <v>1334</v>
@@ -31429,10 +31429,10 @@
         <v>564</v>
       </c>
       <c r="K580">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L580">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M580">
         <v>5</v>
@@ -31443,7 +31443,7 @@
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B581" t="s">
         <v>55</v>
@@ -31461,7 +31461,7 @@
         <v>1332</v>
       </c>
       <c r="G581" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H581" t="s">
         <v>1334</v>
@@ -31470,10 +31470,10 @@
         <v>564</v>
       </c>
       <c r="K581">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L581">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M581">
         <v>5</v>
@@ -31484,37 +31484,40 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B582" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C582" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D582" t="s">
+        <v>1008</v>
       </c>
       <c r="E582" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F582" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G582" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H582" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J582" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K582">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L582">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M582">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P582" s="19">
         <v>46155</v>
@@ -31522,7 +31525,7 @@
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B583" t="s">
         <v>66</v>
@@ -31537,7 +31540,7 @@
         <v>1406</v>
       </c>
       <c r="G583" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H583" t="s">
         <v>1408</v>
@@ -31549,7 +31552,7 @@
         <v>70</v>
       </c>
       <c r="L583">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M583">
         <v>6</v>
@@ -31560,7 +31563,7 @@
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B584" t="s">
         <v>66</v>
@@ -31575,19 +31578,22 @@
         <v>1406</v>
       </c>
       <c r="G584" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H584" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J584" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K584">
         <v>70</v>
       </c>
       <c r="L584">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M584">
+        <v>6</v>
       </c>
       <c r="P584" s="19">
         <v>46155</v>
@@ -31595,7 +31601,7 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B585" t="s">
         <v>66</v>
@@ -31610,19 +31616,19 @@
         <v>1406</v>
       </c>
       <c r="G585" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H585" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J585" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K585">
         <v>70</v>
       </c>
       <c r="L585">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P585" s="19">
         <v>46155</v>
@@ -31630,7 +31636,7 @@
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B586" t="s">
         <v>66</v>
@@ -31645,19 +31651,19 @@
         <v>1406</v>
       </c>
       <c r="G586" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H586" t="s">
         <v>1418</v>
       </c>
       <c r="J586" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K586">
         <v>70</v>
       </c>
       <c r="L586">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P586" s="19">
         <v>46155</v>
@@ -31665,7 +31671,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B587" t="s">
         <v>66</v>
@@ -31680,19 +31686,19 @@
         <v>1406</v>
       </c>
       <c r="G587" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H587" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J587" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K587">
         <v>70</v>
       </c>
       <c r="L587">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P587" s="19">
         <v>46155</v>
@@ -31700,7 +31706,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B588" t="s">
         <v>66</v>
@@ -31708,9 +31714,6 @@
       <c r="C588" t="s">
         <v>1405</v>
       </c>
-      <c r="D588" t="s">
-        <v>1008</v>
-      </c>
       <c r="E588" t="s">
         <v>1405</v>
       </c>
@@ -31718,19 +31721,19 @@
         <v>1406</v>
       </c>
       <c r="G588" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H588" t="s">
         <v>1425</v>
       </c>
       <c r="J588" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K588">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L588">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P588" s="19">
         <v>46155</v>
@@ -31738,7 +31741,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B589" t="s">
         <v>66</v>
@@ -31746,26 +31749,29 @@
       <c r="C589" t="s">
         <v>1405</v>
       </c>
+      <c r="D589" t="s">
+        <v>1008</v>
+      </c>
       <c r="E589" t="s">
         <v>1405</v>
       </c>
       <c r="F589" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G589" t="s">
+        <v>1428</v>
       </c>
       <c r="H589" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J589" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K589">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L589">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M589">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P589" s="19">
         <v>46155</v>
@@ -31773,10 +31779,10 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B590" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C590" t="s">
         <v>1405</v>
@@ -31787,17 +31793,17 @@
       <c r="F590" t="s">
         <v>1431</v>
       </c>
-      <c r="G590" t="s">
-        <v>1435</v>
-      </c>
       <c r="H590" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J590" t="s">
+        <v>1433</v>
       </c>
       <c r="K590">
         <v>70</v>
       </c>
       <c r="L590">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M590">
         <v>45</v>
@@ -31808,10 +31814,10 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B591" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C591" t="s">
         <v>1405</v>
@@ -31823,22 +31829,19 @@
         <v>1431</v>
       </c>
       <c r="G591" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H591" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J591" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K591">
         <v>70</v>
       </c>
       <c r="L591">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M591">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P591" s="19">
         <v>46155</v>
@@ -31846,7 +31849,7 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B592" t="s">
         <v>66</v>
@@ -31861,22 +31864,22 @@
         <v>1431</v>
       </c>
       <c r="G592" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H592" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J592" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K592">
         <v>70</v>
       </c>
       <c r="L592">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M592">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P592" s="19">
         <v>46155</v>
@@ -31884,7 +31887,7 @@
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B593" t="s">
         <v>66</v>
@@ -31896,25 +31899,25 @@
         <v>1405</v>
       </c>
       <c r="F593" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G593" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H593" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J593" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K593">
         <v>70</v>
       </c>
       <c r="L593">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M593">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P593" s="19">
         <v>46155</v>
@@ -31922,7 +31925,7 @@
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B594" t="s">
         <v>66</v>
@@ -31937,7 +31940,7 @@
         <v>1445</v>
       </c>
       <c r="G594" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H594" t="s">
         <v>1447</v>
@@ -31949,21 +31952,21 @@
         <v>70</v>
       </c>
       <c r="L594">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
       <c r="M594">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P594" s="19">
-        <v>46175</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>2365</v>
+        <v>1449</v>
       </c>
       <c r="B595" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C595" t="s">
         <v>1405</v>
@@ -31972,33 +31975,71 @@
         <v>1405</v>
       </c>
       <c r="F595" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G595" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H595" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J595" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K595">
+        <v>70</v>
+      </c>
+      <c r="L595">
+        <v>40.5</v>
+      </c>
+      <c r="M595">
+        <v>5</v>
+      </c>
+      <c r="P595" s="19">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="596" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A596" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B596" t="s">
+        <v>55</v>
+      </c>
+      <c r="C596" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E596" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F596" t="s">
         <v>2366</v>
       </c>
-      <c r="G595" t="s">
+      <c r="G596" t="s">
         <v>2367</v>
       </c>
-      <c r="H595" t="s">
+      <c r="H596" t="s">
         <v>2362</v>
       </c>
-      <c r="J595">
+      <c r="J596">
         <f>5.41+1.74</f>
         <v>7.15</v>
       </c>
-      <c r="K595">
+      <c r="K596">
         <v>70</v>
       </c>
-      <c r="L595">
+      <c r="L596">
         <v>21.95</v>
       </c>
-      <c r="M595">
+      <c r="M596">
         <v>6</v>
       </c>
-      <c r="P595" s="19">
+      <c r="P596" s="19">
         <v>46155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R594" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R595" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="414" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B783C902-2995-444B-A4D6-1CDDBC06936A}"/>
+  <xr:revisionPtr revIDLastSave="419" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DB21A4-B29A-E546-9253-39A885EDA494}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$595</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$596</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10577" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10584" uniqueCount="2401">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -8013,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R596"/>
+  <dimension ref="A1:R597"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23747,11 +23747,11 @@
       </c>
     </row>
     <row r="392" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A392" t="s">
-        <v>951</v>
+      <c r="A392">
+        <v>73900525</v>
       </c>
       <c r="B392" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C392" t="s">
         <v>906</v>
@@ -23760,39 +23760,33 @@
         <v>913</v>
       </c>
       <c r="E392" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F392" t="s">
         <v>952</v>
       </c>
-      <c r="G392" t="s">
-        <v>953</v>
-      </c>
       <c r="H392" t="s">
-        <v>954</v>
+        <v>2400</v>
       </c>
       <c r="I392" t="s">
         <v>69</v>
       </c>
-      <c r="J392" t="s">
-        <v>98</v>
+      <c r="J392">
+        <v>2025</v>
       </c>
       <c r="K392">
         <v>75</v>
       </c>
       <c r="L392">
-        <v>6.45</v>
+        <v>7.4</v>
       </c>
       <c r="M392">
-        <v>501</v>
-      </c>
-      <c r="P392" s="19">
-        <v>46155</v>
+        <v>12</v>
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A393">
-        <v>10300525</v>
+      <c r="A393" t="s">
+        <v>951</v>
       </c>
       <c r="B393" t="s">
         <v>66</v>
@@ -23810,7 +23804,7 @@
         <v>952</v>
       </c>
       <c r="G393" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H393" t="s">
         <v>954</v>
@@ -23818,25 +23812,25 @@
       <c r="I393" t="s">
         <v>69</v>
       </c>
-      <c r="J393">
-        <v>2025</v>
+      <c r="J393" t="s">
+        <v>98</v>
       </c>
       <c r="K393">
         <v>75</v>
       </c>
       <c r="L393">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M393">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P393" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A394" t="s">
-        <v>956</v>
+      <c r="A394">
+        <v>10300525</v>
       </c>
       <c r="B394" t="s">
         <v>66</v>
@@ -23851,25 +23845,28 @@
         <v>923</v>
       </c>
       <c r="F394" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G394" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H394" t="s">
-        <v>292</v>
-      </c>
-      <c r="J394" t="s">
-        <v>98</v>
+        <v>954</v>
+      </c>
+      <c r="I394" t="s">
+        <v>69</v>
+      </c>
+      <c r="J394">
+        <v>2025</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="M394">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P394" s="19">
         <v>46155</v>
@@ -23877,7 +23874,7 @@
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B395" t="s">
         <v>66</v>
@@ -23894,11 +23891,11 @@
       <c r="F395" t="s">
         <v>957</v>
       </c>
+      <c r="G395" t="s">
+        <v>958</v>
+      </c>
       <c r="H395" t="s">
-        <v>960</v>
-      </c>
-      <c r="I395" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="J395" t="s">
         <v>98</v>
@@ -23907,10 +23904,10 @@
         <v>75</v>
       </c>
       <c r="L395">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="M395">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P395" s="19">
         <v>46155</v>
@@ -23918,10 +23915,10 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B396" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C396" t="s">
         <v>906</v>
@@ -23935,26 +23932,23 @@
       <c r="F396" t="s">
         <v>957</v>
       </c>
-      <c r="G396" t="s">
-        <v>962</v>
-      </c>
       <c r="H396" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I396" t="s">
         <v>69</v>
       </c>
       <c r="J396" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K396">
         <v>75</v>
       </c>
       <c r="L396">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M396">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
@@ -23962,10 +23956,10 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B397" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C397" t="s">
         <v>906</v>
@@ -23980,22 +23974,25 @@
         <v>957</v>
       </c>
       <c r="G397" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H397" t="s">
-        <v>920</v>
+        <v>963</v>
+      </c>
+      <c r="I397" t="s">
+        <v>69</v>
       </c>
       <c r="J397" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M397">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
@@ -24003,7 +24000,7 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B398" t="s">
         <v>66</v>
@@ -24021,10 +24018,10 @@
         <v>957</v>
       </c>
       <c r="G398" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H398" t="s">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="J398" t="s">
         <v>286</v>
@@ -24036,15 +24033,15 @@
         <v>9.1</v>
       </c>
       <c r="M398">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A399">
-        <v>43600225</v>
+      <c r="A399" t="s">
+        <v>966</v>
       </c>
       <c r="B399" t="s">
         <v>66</v>
@@ -24062,33 +24059,30 @@
         <v>957</v>
       </c>
       <c r="G399" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H399" t="s">
-        <v>963</v>
-      </c>
-      <c r="I399" t="s">
-        <v>69</v>
+        <v>947</v>
       </c>
       <c r="J399" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="K399">
         <v>75</v>
       </c>
       <c r="L399">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M399">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A400" t="s">
-        <v>970</v>
+      <c r="A400">
+        <v>43600225</v>
       </c>
       <c r="B400" t="s">
         <v>66</v>
@@ -24106,25 +24100,25 @@
         <v>957</v>
       </c>
       <c r="G400" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H400" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="I400" t="s">
         <v>69</v>
       </c>
       <c r="J400" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M400">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P400" s="19">
         <v>46155</v>
@@ -24132,7 +24126,7 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B401" t="s">
         <v>66</v>
@@ -24149,8 +24143,14 @@
       <c r="F401" t="s">
         <v>957</v>
       </c>
+      <c r="G401" t="s">
+        <v>971</v>
+      </c>
       <c r="H401" t="s">
-        <v>974</v>
+        <v>972</v>
+      </c>
+      <c r="I401" t="s">
+        <v>69</v>
       </c>
       <c r="J401" t="s">
         <v>98</v>
@@ -24162,7 +24162,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M401">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P401" s="19">
         <v>46155</v>
@@ -24170,7 +24170,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B402" t="s">
         <v>66</v>
@@ -24185,25 +24185,22 @@
         <v>923</v>
       </c>
       <c r="F402" t="s">
-        <v>918</v>
-      </c>
-      <c r="G402" t="s">
-        <v>919</v>
+        <v>957</v>
       </c>
       <c r="H402" t="s">
-        <v>920</v>
+        <v>974</v>
       </c>
       <c r="J402" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K402">
         <v>75</v>
       </c>
       <c r="L402">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M402">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P402" s="19">
         <v>46155</v>
@@ -24211,7 +24208,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B403" t="s">
         <v>66</v>
@@ -24226,25 +24223,25 @@
         <v>923</v>
       </c>
       <c r="F403" t="s">
-        <v>957</v>
+        <v>918</v>
+      </c>
+      <c r="G403" t="s">
+        <v>919</v>
       </c>
       <c r="H403" t="s">
-        <v>972</v>
-      </c>
-      <c r="I403" t="s">
-        <v>69</v>
-      </c>
-      <c r="J403">
-        <v>2025</v>
+        <v>920</v>
+      </c>
+      <c r="J403" t="s">
+        <v>339</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M403">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
@@ -24252,40 +24249,40 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B404" t="s">
         <v>66</v>
       </c>
       <c r="C404" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="D404" t="s">
-        <v>979</v>
+        <v>913</v>
       </c>
       <c r="E404" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F404" t="s">
-        <v>980</v>
-      </c>
-      <c r="G404" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="H404" t="s">
-        <v>982</v>
-      </c>
-      <c r="J404" t="s">
-        <v>339</v>
+        <v>972</v>
+      </c>
+      <c r="I404" t="s">
+        <v>69</v>
+      </c>
+      <c r="J404">
+        <v>2025</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M404">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
@@ -24293,7 +24290,7 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B405" t="s">
         <v>66</v>
@@ -24311,22 +24308,22 @@
         <v>980</v>
       </c>
       <c r="G405" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H405" t="s">
-        <v>985</v>
-      </c>
-      <c r="J405">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J405" t="s">
+        <v>339</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M405">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
@@ -24334,7 +24331,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B406" t="s">
         <v>66</v>
@@ -24349,25 +24346,25 @@
         <v>57</v>
       </c>
       <c r="F406" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G406" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H406" t="s">
-        <v>989</v>
-      </c>
-      <c r="J406" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J406">
+        <v>2025</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M406">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P406" s="19">
         <v>46155</v>
@@ -24375,7 +24372,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B407" t="s">
         <v>66</v>
@@ -24390,25 +24387,25 @@
         <v>57</v>
       </c>
       <c r="F407" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G407" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="H407" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="J407" t="s">
-        <v>286</v>
+        <v>564</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M407">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P407" s="19">
         <v>46155</v>
@@ -24416,7 +24413,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B408" t="s">
         <v>66</v>
@@ -24434,22 +24431,22 @@
         <v>980</v>
       </c>
       <c r="G408" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H408" t="s">
-        <v>292</v>
+        <v>992</v>
       </c>
       <c r="J408" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M408">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P408" s="19">
         <v>46155</v>
@@ -24457,7 +24454,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B409" t="s">
         <v>66</v>
@@ -24475,22 +24472,22 @@
         <v>980</v>
       </c>
       <c r="G409" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H409" t="s">
         <v>292</v>
       </c>
-      <c r="J409">
-        <v>2025</v>
+      <c r="J409" t="s">
+        <v>98</v>
       </c>
       <c r="K409">
         <v>75</v>
       </c>
       <c r="L409">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M409">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P409" s="19">
         <v>46155</v>
@@ -24498,7 +24495,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B410" t="s">
         <v>66</v>
@@ -24516,22 +24513,22 @@
         <v>980</v>
       </c>
       <c r="G410" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H410" t="s">
-        <v>992</v>
-      </c>
-      <c r="J410" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J410">
+        <v>2025</v>
       </c>
       <c r="K410">
         <v>75</v>
       </c>
       <c r="L410">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M410">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P410" s="19">
         <v>46155</v>
@@ -24539,7 +24536,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B411" t="s">
         <v>66</v>
@@ -24554,13 +24551,13 @@
         <v>57</v>
       </c>
       <c r="F411" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G411" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H411" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="J411" t="s">
         <v>339</v>
@@ -24569,10 +24566,10 @@
         <v>75</v>
       </c>
       <c r="L411">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M411">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P411" s="19">
         <v>46155</v>
@@ -24580,7 +24577,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B412" t="s">
         <v>66</v>
@@ -24595,16 +24592,16 @@
         <v>57</v>
       </c>
       <c r="F412" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G412" t="s">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="H412" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J412" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K412">
         <v>75</v>
@@ -24613,7 +24610,7 @@
         <v>5.7</v>
       </c>
       <c r="M412">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P412" s="19">
         <v>46155</v>
@@ -24621,7 +24618,7 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B413" t="s">
         <v>66</v>
@@ -24639,22 +24636,22 @@
         <v>980</v>
       </c>
       <c r="G413" t="s">
-        <v>1005</v>
+        <v>113</v>
       </c>
       <c r="H413" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="J413" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K413">
         <v>75</v>
       </c>
       <c r="L413">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M413">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P413" s="19">
         <v>46155</v>
@@ -24662,16 +24659,16 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B414" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C414" t="s">
         <v>978</v>
       </c>
       <c r="D414" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E414" t="s">
         <v>57</v>
@@ -24680,7 +24677,7 @@
         <v>980</v>
       </c>
       <c r="G414" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="H414" t="s">
         <v>1006</v>
@@ -24689,13 +24686,13 @@
         <v>339</v>
       </c>
       <c r="K414">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L414">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M414">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P414" s="19">
         <v>46155</v>
@@ -24703,16 +24700,16 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B415" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C415" t="s">
         <v>978</v>
       </c>
       <c r="D415" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
@@ -24721,25 +24718,22 @@
         <v>980</v>
       </c>
       <c r="G415" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H415" t="s">
-        <v>992</v>
-      </c>
-      <c r="I415" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="J415" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K415">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L415">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M415">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P415" s="19">
         <v>46155</v>
@@ -24747,7 +24741,7 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B416" t="s">
         <v>66</v>
@@ -24756,31 +24750,34 @@
         <v>978</v>
       </c>
       <c r="D416" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E416" t="s">
         <v>57</v>
       </c>
       <c r="F416" t="s">
-        <v>1015</v>
+        <v>980</v>
       </c>
       <c r="G416" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="H416" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I416" t="s">
+        <v>1012</v>
       </c>
       <c r="J416" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K416">
         <v>75</v>
       </c>
       <c r="L416">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M416">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P416" s="19">
         <v>46155</v>
@@ -24788,7 +24785,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B417" t="s">
         <v>66</v>
@@ -24797,34 +24794,31 @@
         <v>978</v>
       </c>
       <c r="D417" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E417" t="s">
         <v>57</v>
       </c>
       <c r="F417" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G417" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H417" t="s">
-        <v>1021</v>
-      </c>
-      <c r="I417" t="s">
-        <v>777</v>
+        <v>1017</v>
       </c>
       <c r="J417" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M417">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P417" s="19">
         <v>46155</v>
@@ -24832,7 +24826,7 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B418" t="s">
         <v>66</v>
@@ -24847,33 +24841,36 @@
         <v>57</v>
       </c>
       <c r="F418" t="s">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="G418" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="H418" t="s">
-        <v>992</v>
+        <v>1021</v>
+      </c>
+      <c r="I418" t="s">
+        <v>777</v>
       </c>
       <c r="J418" t="s">
-        <v>339</v>
+        <v>217</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M418">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A419">
-        <v>13003025</v>
+      <c r="A419" t="s">
+        <v>1022</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24891,33 +24888,30 @@
         <v>980</v>
       </c>
       <c r="G419" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H419" t="s">
         <v>992</v>
       </c>
-      <c r="I419" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J419">
-        <v>2025</v>
+      <c r="J419" t="s">
+        <v>339</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M419">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A420" t="s">
-        <v>1025</v>
+      <c r="A420">
+        <v>13003025</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24935,22 +24929,25 @@
         <v>980</v>
       </c>
       <c r="G420" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H420" t="s">
-        <v>589</v>
-      </c>
-      <c r="J420" t="s">
-        <v>339</v>
+        <v>992</v>
+      </c>
+      <c r="I420" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J420">
+        <v>2025</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M420">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
@@ -24958,7 +24955,7 @@
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24973,33 +24970,36 @@
         <v>57</v>
       </c>
       <c r="F421" t="s">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="G421" t="s">
-        <v>165</v>
+        <v>1026</v>
       </c>
       <c r="H421" t="s">
-        <v>1029</v>
+        <v>589</v>
       </c>
       <c r="J421" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M421">
+        <v>321</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A422">
-        <v>43700425</v>
+      <c r="A422" t="s">
+        <v>1027</v>
       </c>
       <c r="B422" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C422" t="s">
         <v>978</v>
@@ -25014,19 +25014,19 @@
         <v>1028</v>
       </c>
       <c r="G422" t="s">
-        <v>1030</v>
+        <v>165</v>
       </c>
       <c r="H422" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J422">
-        <v>2025</v>
+        <v>1029</v>
+      </c>
+      <c r="J422" t="s">
+        <v>286</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>10.5</v>
+        <v>37</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
@@ -25034,7 +25034,7 @@
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A423">
-        <v>73300125</v>
+        <v>43700425</v>
       </c>
       <c r="B423" t="s">
         <v>55</v>
@@ -25049,13 +25049,13 @@
         <v>57</v>
       </c>
       <c r="F423" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G423" t="s">
-        <v>113</v>
+        <v>1030</v>
       </c>
       <c r="H423" t="s">
-        <v>2362</v>
+        <v>1031</v>
       </c>
       <c r="J423">
         <v>2025</v>
@@ -25064,10 +25064,7 @@
         <v>75</v>
       </c>
       <c r="L423">
-        <v>4.99</v>
-      </c>
-      <c r="M423">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
@@ -25075,7 +25072,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
-        <v>73300225</v>
+        <v>73300125</v>
       </c>
       <c r="B424" t="s">
         <v>55</v>
@@ -25093,7 +25090,7 @@
         <v>1033</v>
       </c>
       <c r="G424" t="s">
-        <v>2364</v>
+        <v>113</v>
       </c>
       <c r="H424" t="s">
         <v>2362</v>
@@ -25116,7 +25113,7 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425">
-        <v>73300325</v>
+        <v>73300225</v>
       </c>
       <c r="B425" t="s">
         <v>55</v>
@@ -25134,7 +25131,7 @@
         <v>1033</v>
       </c>
       <c r="G425" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H425" t="s">
         <v>2362</v>
@@ -25146,7 +25143,7 @@
         <v>75</v>
       </c>
       <c r="L425">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="M425">
         <v>12</v>
@@ -25157,7 +25154,7 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426">
-        <v>73300425</v>
+        <v>73300325</v>
       </c>
       <c r="B426" t="s">
         <v>55</v>
@@ -25169,13 +25166,13 @@
         <v>979</v>
       </c>
       <c r="E426" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F426" t="s">
         <v>1033</v>
       </c>
       <c r="G426" t="s">
-        <v>1135</v>
+        <v>2363</v>
       </c>
       <c r="H426" t="s">
         <v>2362</v>
@@ -25187,7 +25184,7 @@
         <v>75</v>
       </c>
       <c r="L426">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="M426">
         <v>12</v>
@@ -25197,11 +25194,11 @@
       </c>
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A427" t="s">
-        <v>1032</v>
+      <c r="A427">
+        <v>73300425</v>
       </c>
       <c r="B427" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C427" t="s">
         <v>978</v>
@@ -25210,36 +25207,36 @@
         <v>979</v>
       </c>
       <c r="E427" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F427" t="s">
         <v>1033</v>
       </c>
       <c r="G427" t="s">
-        <v>1034</v>
+        <v>1135</v>
       </c>
       <c r="H427" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J427" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J427">
+        <v>2025</v>
       </c>
       <c r="K427">
         <v>75</v>
       </c>
       <c r="L427">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M427">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P427" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A428">
-        <v>13300125</v>
+      <c r="A428" t="s">
+        <v>1032</v>
       </c>
       <c r="B428" t="s">
         <v>66</v>
@@ -25257,33 +25254,33 @@
         <v>1033</v>
       </c>
       <c r="G428" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H428" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J428">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J428" t="s">
+        <v>98</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M428">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P428" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A429" t="s">
-        <v>1038</v>
+      <c r="A429">
+        <v>13300125</v>
       </c>
       <c r="B429" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C429" t="s">
         <v>978</v>
@@ -25295,33 +25292,33 @@
         <v>57</v>
       </c>
       <c r="F429" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G429" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H429" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J429" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J429">
+        <v>2025</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M429">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P429" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A430">
-        <v>24003025</v>
+      <c r="A430" t="s">
+        <v>1038</v>
       </c>
       <c r="B430" t="s">
         <v>55</v>
@@ -25330,7 +25327,7 @@
         <v>978</v>
       </c>
       <c r="D430" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E430" t="s">
         <v>57</v>
@@ -25339,16 +25336,13 @@
         <v>58</v>
       </c>
       <c r="G430" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H430" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I430" t="s">
-        <v>69</v>
-      </c>
-      <c r="J430">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J430" t="s">
+        <v>339</v>
       </c>
       <c r="K430">
         <v>75</v>
@@ -25356,13 +25350,16 @@
       <c r="L430">
         <v>6.2</v>
       </c>
+      <c r="M430">
+        <v>0</v>
+      </c>
       <c r="P430" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>1044</v>
+      <c r="A431">
+        <v>24003025</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25371,39 +25368,39 @@
         <v>978</v>
       </c>
       <c r="D431" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E431" t="s">
         <v>57</v>
       </c>
       <c r="F431" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G431" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H431" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J431" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I431" t="s">
+        <v>69</v>
+      </c>
+      <c r="J431">
+        <v>2025</v>
       </c>
       <c r="K431">
         <v>75</v>
       </c>
       <c r="L431">
-        <v>7.55</v>
-      </c>
-      <c r="M431">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P431" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25412,28 +25409,28 @@
         <v>978</v>
       </c>
       <c r="D432" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E432" t="s">
         <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G432" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H432" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J432" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M432">
         <v>0</v>
@@ -25444,7 +25441,7 @@
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25453,28 +25450,28 @@
         <v>978</v>
       </c>
       <c r="D433" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E433" t="s">
         <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G433" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H433" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J433" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M433">
         <v>0</v>
@@ -25485,7 +25482,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25494,42 +25491,39 @@
         <v>978</v>
       </c>
       <c r="D434" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E434" t="s">
         <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G434" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H434" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I434" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J434" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M434">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P434" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A435">
-        <v>27701225</v>
+      <c r="A435" t="s">
+        <v>1053</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25538,39 +25532,42 @@
         <v>978</v>
       </c>
       <c r="D435" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E435" t="s">
         <v>57</v>
       </c>
       <c r="F435" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G435" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H435" t="s">
         <v>1055</v>
       </c>
-      <c r="J435">
-        <v>2025</v>
+      <c r="I435" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J435" t="s">
+        <v>286</v>
       </c>
       <c r="K435">
         <v>75</v>
       </c>
       <c r="L435">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M435">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P435" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A436" t="s">
-        <v>1060</v>
+      <c r="A436">
+        <v>27701225</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25579,28 +25576,28 @@
         <v>978</v>
       </c>
       <c r="D436" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E436" t="s">
         <v>57</v>
       </c>
       <c r="F436" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G436" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H436" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J436" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J436">
+        <v>2025</v>
       </c>
       <c r="K436">
         <v>75</v>
       </c>
       <c r="L436">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M436">
         <v>0</v>
@@ -25611,7 +25608,7 @@
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25620,28 +25617,28 @@
         <v>978</v>
       </c>
       <c r="D437" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E437" t="s">
         <v>57</v>
       </c>
       <c r="F437" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G437" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H437" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J437" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M437">
         <v>0</v>
@@ -25652,7 +25649,7 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25667,22 +25664,22 @@
         <v>57</v>
       </c>
       <c r="F438" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G438" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H438" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J438" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K438">
         <v>75</v>
       </c>
       <c r="L438">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M438">
         <v>0</v>
@@ -25692,8 +25689,8 @@
       </c>
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A439">
-        <v>68002225</v>
+      <c r="A439" t="s">
+        <v>1065</v>
       </c>
       <c r="B439" t="s">
         <v>55</v>
@@ -25705,13 +25702,13 @@
         <v>1057</v>
       </c>
       <c r="E439" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F439" t="s">
         <v>1066</v>
       </c>
       <c r="G439" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H439" t="s">
         <v>1068</v>
@@ -25723,7 +25720,7 @@
         <v>75</v>
       </c>
       <c r="L439">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M439">
         <v>0</v>
@@ -25734,7 +25731,7 @@
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A440">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B440" t="s">
         <v>55</v>
@@ -25749,13 +25746,13 @@
         <v>63</v>
       </c>
       <c r="F440" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G440" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H440" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J440" t="s">
         <v>339</v>
@@ -25764,7 +25761,7 @@
         <v>75</v>
       </c>
       <c r="L440">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M440">
         <v>0</v>
@@ -25775,7 +25772,7 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B441" t="s">
         <v>55</v>
@@ -25793,13 +25790,13 @@
         <v>1070</v>
       </c>
       <c r="G441" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H441" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J441">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J441" t="s">
+        <v>339</v>
       </c>
       <c r="K441">
         <v>75</v>
@@ -25815,8 +25812,8 @@
       </c>
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A442" t="s">
-        <v>1075</v>
+      <c r="A442">
+        <v>68002424</v>
       </c>
       <c r="B442" t="s">
         <v>55</v>
@@ -25834,19 +25831,19 @@
         <v>1070</v>
       </c>
       <c r="G442" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H442" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J442" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J442">
+        <v>2024</v>
       </c>
       <c r="K442">
         <v>75</v>
       </c>
       <c r="L442">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M442">
         <v>0</v>
@@ -25856,8 +25853,8 @@
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A443">
-        <v>68002623</v>
+      <c r="A443" t="s">
+        <v>1075</v>
       </c>
       <c r="B443" t="s">
         <v>55</v>
@@ -25872,25 +25869,22 @@
         <v>63</v>
       </c>
       <c r="F443" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G443" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H443" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I443" t="s">
-        <v>69</v>
-      </c>
-      <c r="J443">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J443" t="s">
+        <v>564</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -25901,7 +25895,7 @@
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A444">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B444" t="s">
         <v>55</v>
@@ -25913,28 +25907,28 @@
         <v>1057</v>
       </c>
       <c r="E444" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F444" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G444" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H444" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I444" t="s">
         <v>69</v>
       </c>
       <c r="J444">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M444">
         <v>0</v>
@@ -25944,8 +25938,8 @@
       </c>
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A445" t="s">
-        <v>1083</v>
+      <c r="A445">
+        <v>68002825</v>
       </c>
       <c r="B445" t="s">
         <v>55</v>
@@ -25960,22 +25954,25 @@
         <v>57</v>
       </c>
       <c r="F445" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G445" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H445" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J445" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I445" t="s">
+        <v>69</v>
+      </c>
+      <c r="J445">
+        <v>2025</v>
       </c>
       <c r="K445">
         <v>75</v>
       </c>
       <c r="L445">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M445">
         <v>0</v>
@@ -25985,8 +25982,8 @@
       </c>
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A446">
-        <v>68003025</v>
+      <c r="A446" t="s">
+        <v>1083</v>
       </c>
       <c r="B446" t="s">
         <v>55</v>
@@ -25998,13 +25995,13 @@
         <v>1057</v>
       </c>
       <c r="E446" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F446" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G446" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H446" t="s">
         <v>1085</v>
@@ -26027,7 +26024,7 @@
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A447">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B447" t="s">
         <v>55</v>
@@ -26045,10 +26042,10 @@
         <v>1078</v>
       </c>
       <c r="G447" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H447" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J447" t="s">
         <v>339</v>
@@ -26057,7 +26054,7 @@
         <v>75</v>
       </c>
       <c r="L447">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M447">
         <v>0</v>
@@ -26067,8 +26064,8 @@
       </c>
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A448" t="s">
-        <v>1089</v>
+      <c r="A448">
+        <v>680031225</v>
       </c>
       <c r="B448" t="s">
         <v>55</v>
@@ -26080,25 +26077,25 @@
         <v>1057</v>
       </c>
       <c r="E448" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F448" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G448" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H448" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J448" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K448">
         <v>75</v>
       </c>
       <c r="L448">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M448">
         <v>0</v>
@@ -26109,10 +26106,10 @@
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B449" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C449" t="s">
         <v>978</v>
@@ -26127,22 +26124,22 @@
         <v>1066</v>
       </c>
       <c r="G449" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H449" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J449">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J449" t="s">
+        <v>98</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M449">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P449" s="19">
         <v>46155</v>
@@ -26150,7 +26147,7 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B450" t="s">
         <v>66</v>
@@ -26159,31 +26156,31 @@
         <v>978</v>
       </c>
       <c r="D450" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E450" t="s">
         <v>57</v>
       </c>
       <c r="F450" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G450" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H450" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J450" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J450">
+        <v>2025</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M450">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26191,7 +26188,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26209,22 +26206,22 @@
         <v>1033</v>
       </c>
       <c r="G451" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H451" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J451">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J451" t="s">
+        <v>98</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M451">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26232,7 +26229,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B452" t="s">
         <v>66</v>
@@ -26247,22 +26244,25 @@
         <v>57</v>
       </c>
       <c r="F452" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G452" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H452" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J452" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J452">
+        <v>2025</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M452">
+        <v>264</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
@@ -26270,7 +26270,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B453" t="s">
         <v>66</v>
@@ -26285,104 +26285,101 @@
         <v>57</v>
       </c>
       <c r="F453" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G453" t="s">
         <v>1100</v>
       </c>
       <c r="H453" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J453" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A454">
-        <v>53800623</v>
+      <c r="A454" t="s">
+        <v>1102</v>
       </c>
       <c r="B454" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C454" t="s">
         <v>978</v>
       </c>
       <c r="D454" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E454" t="s">
         <v>57</v>
       </c>
       <c r="F454" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G454" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H454" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J454" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>11</v>
-      </c>
-      <c r="M454">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A455" t="s">
-        <v>1107</v>
+      <c r="A455">
+        <v>53800623</v>
       </c>
       <c r="B455" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C455" t="s">
         <v>978</v>
       </c>
       <c r="D455" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E455" t="s">
         <v>57</v>
       </c>
       <c r="F455" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G455" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H455" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J455" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K455">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L455">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M455">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
@@ -26390,7 +26387,7 @@
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B456" t="s">
         <v>66</v>
@@ -26408,22 +26405,22 @@
         <v>980</v>
       </c>
       <c r="G456" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H456" t="s">
-        <v>985</v>
-      </c>
-      <c r="J456">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J456" t="s">
+        <v>564</v>
       </c>
       <c r="K456">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L456">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M456">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
@@ -26431,7 +26428,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B457" t="s">
         <v>66</v>
@@ -26440,75 +26437,72 @@
         <v>978</v>
       </c>
       <c r="D457" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E457" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F457" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G457" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H457" t="s">
-        <v>989</v>
-      </c>
-      <c r="J457" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J457">
+        <v>2025</v>
       </c>
       <c r="K457">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L457">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M457">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P457" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A458">
-        <v>71501125</v>
+      <c r="A458" t="s">
+        <v>1111</v>
       </c>
       <c r="B458" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C458" t="s">
         <v>978</v>
       </c>
       <c r="D458" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E458" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F458" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G458" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H458" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I458" t="s">
-        <v>69</v>
-      </c>
-      <c r="J458">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J458" t="s">
+        <v>564</v>
       </c>
       <c r="K458">
         <v>75</v>
       </c>
       <c r="L458">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M458">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P458" s="19">
         <v>46155</v>
@@ -26516,7 +26510,7 @@
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A459">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B459" t="s">
         <v>55</v>
@@ -26528,17 +26522,20 @@
         <v>979</v>
       </c>
       <c r="E459" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F459" t="s">
         <v>980</v>
       </c>
       <c r="G459" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H459" t="s">
         <v>1113</v>
       </c>
+      <c r="I459" t="s">
+        <v>69</v>
+      </c>
       <c r="J459">
         <v>2025</v>
       </c>
@@ -26546,7 +26543,7 @@
         <v>75</v>
       </c>
       <c r="L459">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M459">
         <v>324</v>
@@ -26557,7 +26554,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B460" t="s">
         <v>55</v>
@@ -26575,7 +26572,7 @@
         <v>980</v>
       </c>
       <c r="G460" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H460" t="s">
         <v>1113</v>
@@ -26598,7 +26595,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B461" t="s">
         <v>55</v>
@@ -26613,10 +26610,10 @@
         <v>63</v>
       </c>
       <c r="F461" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G461" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H461" t="s">
         <v>1113</v>
@@ -26639,7 +26636,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B462" t="s">
         <v>55</v>
@@ -26651,13 +26648,13 @@
         <v>979</v>
       </c>
       <c r="E462" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F462" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G462" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H462" t="s">
         <v>1113</v>
@@ -26680,7 +26677,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B463" t="s">
         <v>55</v>
@@ -26695,10 +26692,10 @@
         <v>57</v>
       </c>
       <c r="F463" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G463" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H463" t="s">
         <v>1113</v>
@@ -26721,7 +26718,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26733,13 +26730,13 @@
         <v>979</v>
       </c>
       <c r="E464" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F464" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G464" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H464" t="s">
         <v>1113</v>
@@ -26751,7 +26748,7 @@
         <v>75</v>
       </c>
       <c r="L464">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M464">
         <v>324</v>
@@ -26762,7 +26759,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B465" t="s">
         <v>55</v>
@@ -26777,7 +26774,7 @@
         <v>63</v>
       </c>
       <c r="F465" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G465" t="s">
         <v>1120</v>
@@ -26792,7 +26789,7 @@
         <v>75</v>
       </c>
       <c r="L465">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M465">
         <v>324</v>
@@ -26803,7 +26800,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B466" t="s">
         <v>55</v>
@@ -26818,7 +26815,7 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G466" t="s">
         <v>1120</v>
@@ -26826,9 +26823,6 @@
       <c r="H466" t="s">
         <v>1113</v>
       </c>
-      <c r="I466" t="s">
-        <v>69</v>
-      </c>
       <c r="J466">
         <v>2025</v>
       </c>
@@ -26847,7 +26841,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B467" t="s">
         <v>55</v>
@@ -26859,10 +26853,10 @@
         <v>979</v>
       </c>
       <c r="E467" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G467" t="s">
         <v>1120</v>
@@ -26871,7 +26865,7 @@
         <v>1113</v>
       </c>
       <c r="I467" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J467">
         <v>2025</v>
@@ -26880,7 +26874,7 @@
         <v>75</v>
       </c>
       <c r="L467">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M467">
         <v>324</v>
@@ -26891,7 +26885,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B468" t="s">
         <v>55</v>
@@ -26906,7 +26900,7 @@
         <v>57</v>
       </c>
       <c r="F468" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G468" t="s">
         <v>1120</v>
@@ -26924,7 +26918,7 @@
         <v>75</v>
       </c>
       <c r="L468">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M468">
         <v>324</v>
@@ -26935,10 +26929,10 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B469" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C469" t="s">
         <v>978</v>
@@ -26947,16 +26941,19 @@
         <v>979</v>
       </c>
       <c r="E469" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F469" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G469" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H469" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I469" t="s">
+        <v>175</v>
       </c>
       <c r="J469">
         <v>2025</v>
@@ -26965,7 +26962,7 @@
         <v>75</v>
       </c>
       <c r="L469">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M469">
         <v>324</v>
@@ -26975,8 +26972,8 @@
       </c>
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A470" t="s">
-        <v>1125</v>
+      <c r="A470">
+        <v>16000125</v>
       </c>
       <c r="B470" t="s">
         <v>66</v>
@@ -26994,22 +26991,22 @@
         <v>980</v>
       </c>
       <c r="G470" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H470" t="s">
-        <v>985</v>
-      </c>
-      <c r="J470" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J470">
+        <v>2025</v>
       </c>
       <c r="K470">
         <v>75</v>
       </c>
       <c r="L470">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M470">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P470" s="19">
         <v>46155</v>
@@ -27017,7 +27014,7 @@
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B471" t="s">
         <v>66</v>
@@ -27035,22 +27032,22 @@
         <v>980</v>
       </c>
       <c r="G471" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H471" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J471" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M471">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -27058,7 +27055,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B472" t="s">
         <v>66</v>
@@ -27076,22 +27073,22 @@
         <v>980</v>
       </c>
       <c r="G472" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H472" t="s">
-        <v>985</v>
-      </c>
-      <c r="J472">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J472" t="s">
+        <v>286</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M472">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27099,7 +27096,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B473" t="s">
         <v>66</v>
@@ -27114,25 +27111,25 @@
         <v>63</v>
       </c>
       <c r="F473" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G473" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H473" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J473" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J473">
+        <v>2025</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M473">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27140,7 +27137,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B474" t="s">
         <v>66</v>
@@ -27155,25 +27152,25 @@
         <v>63</v>
       </c>
       <c r="F474" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G474" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H474" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J474" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M474">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27181,7 +27178,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B475" t="s">
         <v>66</v>
@@ -27199,22 +27196,22 @@
         <v>980</v>
       </c>
       <c r="G475" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H475" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J475" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M475">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27222,7 +27219,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B476" t="s">
         <v>66</v>
@@ -27240,25 +27237,22 @@
         <v>980</v>
       </c>
       <c r="G476" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H476" t="s">
-        <v>982</v>
-      </c>
-      <c r="I476" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J476" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M476">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27266,7 +27260,7 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B477" t="s">
         <v>66</v>
@@ -27284,13 +27278,13 @@
         <v>980</v>
       </c>
       <c r="G477" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H477" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I477" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J477" t="s">
         <v>61</v>
@@ -27299,10 +27293,10 @@
         <v>75</v>
       </c>
       <c r="L477">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M477">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27310,7 +27304,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27325,25 +27319,28 @@
         <v>63</v>
       </c>
       <c r="F478" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G478" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H478" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I478" t="s">
+        <v>1012</v>
       </c>
       <c r="J478" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K478">
         <v>75</v>
       </c>
       <c r="L478">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M478">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27351,7 +27348,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B479" t="s">
         <v>66</v>
@@ -27360,19 +27357,19 @@
         <v>978</v>
       </c>
       <c r="D479" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E479" t="s">
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G479" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H479" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J479" t="s">
         <v>217</v>
@@ -27381,10 +27378,10 @@
         <v>75</v>
       </c>
       <c r="L479">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M479">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
@@ -27392,7 +27389,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B480" t="s">
         <v>66</v>
@@ -27407,25 +27404,25 @@
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G480" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H480" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J480" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K480">
         <v>75</v>
       </c>
       <c r="L480">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M480">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
@@ -27433,7 +27430,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B481" t="s">
         <v>66</v>
@@ -27451,22 +27448,22 @@
         <v>1147</v>
       </c>
       <c r="G481" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H481" t="s">
         <v>1149</v>
       </c>
       <c r="J481" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M481">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P481" s="19">
         <v>46155</v>
@@ -27474,37 +27471,40 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B482" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C482" t="s">
         <v>978</v>
       </c>
       <c r="D482" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E482" t="s">
         <v>63</v>
       </c>
       <c r="F482" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G482" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H482" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J482" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M482">
+        <v>36</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
@@ -27512,7 +27512,7 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B483" t="s">
         <v>55</v>
@@ -27527,25 +27527,22 @@
         <v>63</v>
       </c>
       <c r="F483" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G483" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H483" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J483" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>12.5</v>
-      </c>
-      <c r="M483">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
@@ -27553,7 +27550,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B484" t="s">
         <v>55</v>
@@ -27568,22 +27565,22 @@
         <v>63</v>
       </c>
       <c r="F484" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G484" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H484" t="s">
         <v>1064</v>
       </c>
       <c r="J484" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M484">
         <v>0</v>
@@ -27594,7 +27591,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B485" t="s">
         <v>55</v>
@@ -27612,19 +27609,19 @@
         <v>1078</v>
       </c>
       <c r="G485" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H485" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J485">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J485" t="s">
+        <v>209</v>
       </c>
       <c r="K485">
         <v>75</v>
       </c>
       <c r="L485">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -27635,10 +27632,10 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B486" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C486" t="s">
         <v>978</v>
@@ -27650,25 +27647,25 @@
         <v>63</v>
       </c>
       <c r="F486" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G486" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H486" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J486" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J486">
+        <v>2014</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M486">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P486" s="19">
         <v>46155</v>
@@ -27676,10 +27673,10 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B487" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27694,13 +27691,10 @@
         <v>1066</v>
       </c>
       <c r="G487" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H487" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I487" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J487" t="s">
         <v>61</v>
@@ -27709,18 +27703,18 @@
         <v>75</v>
       </c>
       <c r="L487">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M487">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A488">
-        <v>27701324</v>
+      <c r="A488" t="s">
+        <v>1164</v>
       </c>
       <c r="B488" t="s">
         <v>55</v>
@@ -27738,19 +27732,22 @@
         <v>1066</v>
       </c>
       <c r="G488" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H488" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J488">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I488" t="s">
+        <v>69</v>
+      </c>
+      <c r="J488" t="s">
+        <v>61</v>
       </c>
       <c r="K488">
         <v>75</v>
       </c>
       <c r="L488">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M488">
         <v>0</v>
@@ -27760,8 +27757,8 @@
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A489" t="s">
-        <v>1167</v>
+      <c r="A489">
+        <v>27701324</v>
       </c>
       <c r="B489" t="s">
         <v>55</v>
@@ -27779,22 +27776,19 @@
         <v>1066</v>
       </c>
       <c r="G489" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H489" t="s">
         <v>1055</v>
       </c>
-      <c r="I489" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J489" t="s">
-        <v>98</v>
+      <c r="J489">
+        <v>2024</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M489">
         <v>0</v>
@@ -27805,31 +27799,31 @@
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B490" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C490" t="s">
         <v>978</v>
       </c>
       <c r="D490" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E490" t="s">
         <v>63</v>
       </c>
       <c r="F490" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G490" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H490" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I490" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J490" t="s">
         <v>98</v>
@@ -27838,10 +27832,10 @@
         <v>75</v>
       </c>
       <c r="L490">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M490">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P490" s="19">
         <v>46155</v>
@@ -27849,7 +27843,7 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B491" t="s">
         <v>66</v>
@@ -27864,28 +27858,28 @@
         <v>63</v>
       </c>
       <c r="F491" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G491" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H491" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I491" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J491" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K491">
         <v>75</v>
       </c>
       <c r="L491">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M491">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27893,10 +27887,10 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B492" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C492" t="s">
         <v>978</v>
@@ -27908,25 +27902,28 @@
         <v>63</v>
       </c>
       <c r="F492" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G492" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H492" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I492" t="s">
+        <v>69</v>
       </c>
       <c r="J492" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M492">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27934,7 +27931,7 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B493" t="s">
         <v>55</v>
@@ -27952,19 +27949,22 @@
         <v>1175</v>
       </c>
       <c r="G493" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H493" t="s">
         <v>1177</v>
       </c>
       <c r="J493" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M493">
+        <v>0</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27972,10 +27972,10 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B494" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C494" t="s">
         <v>978</v>
@@ -27987,28 +27987,22 @@
         <v>63</v>
       </c>
       <c r="F494" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G494" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H494" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I494" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J494" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>7.6</v>
-      </c>
-      <c r="M494">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -28016,10 +28010,10 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B495" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C495" t="s">
         <v>978</v>
@@ -28031,25 +28025,28 @@
         <v>63</v>
       </c>
       <c r="F495" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G495" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H495" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I495" t="s">
+        <v>69</v>
       </c>
       <c r="J495" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M495">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -28057,7 +28054,7 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B496" t="s">
         <v>55</v>
@@ -28075,22 +28072,22 @@
         <v>1185</v>
       </c>
       <c r="G496" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H496" t="s">
         <v>1049</v>
       </c>
       <c r="J496" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K496">
         <v>75</v>
       </c>
       <c r="L496">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M496">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -28098,10 +28095,10 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B497" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C497" t="s">
         <v>978</v>
@@ -28113,25 +28110,25 @@
         <v>63</v>
       </c>
       <c r="F497" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G497" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H497" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I497" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J497" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M497">
+        <v>6</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28139,7 +28136,7 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B498" t="s">
         <v>66</v>
@@ -28154,25 +28151,25 @@
         <v>63</v>
       </c>
       <c r="F498" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G498" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H498" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I498" t="s">
+        <v>777</v>
       </c>
       <c r="J498" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M498">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
@@ -28180,7 +28177,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28195,25 +28192,25 @@
         <v>63</v>
       </c>
       <c r="F499" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G499" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H499" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I499" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J499" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M499">
+        <v>53</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
@@ -28221,7 +28218,7 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28236,28 +28233,25 @@
         <v>63</v>
       </c>
       <c r="F500" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G500" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H500" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I500" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J500" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>6.5</v>
-      </c>
-      <c r="M500">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
@@ -28265,10 +28259,10 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B501" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C501" t="s">
         <v>978</v>
@@ -28283,30 +28277,33 @@
         <v>1122</v>
       </c>
       <c r="G501" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H501" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I501" t="s">
+        <v>175</v>
       </c>
       <c r="J501" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M501">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A502">
-        <v>16003124</v>
+      <c r="A502" t="s">
+        <v>1202</v>
       </c>
       <c r="B502" t="s">
         <v>55</v>
@@ -28318,19 +28315,19 @@
         <v>979</v>
       </c>
       <c r="E502" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F502" t="s">
         <v>1122</v>
       </c>
       <c r="G502" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H502" t="s">
         <v>1204</v>
       </c>
       <c r="J502" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K502">
         <v>75</v>
@@ -28346,11 +28343,11 @@
       </c>
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A503" t="s">
-        <v>1206</v>
+      <c r="A503">
+        <v>16003124</v>
       </c>
       <c r="B503" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C503" t="s">
         <v>978</v>
@@ -28359,31 +28356,28 @@
         <v>979</v>
       </c>
       <c r="E503" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F503" t="s">
         <v>1122</v>
       </c>
       <c r="G503" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H503" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I503" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J503" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K503">
         <v>75</v>
       </c>
       <c r="L503">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M503">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P503" s="19">
         <v>46155</v>
@@ -28391,10 +28385,10 @@
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B504" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C504" t="s">
         <v>978</v>
@@ -28409,25 +28403,25 @@
         <v>1122</v>
       </c>
       <c r="G504" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H504" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I504" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J504" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M504">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28435,10 +28429,10 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B505" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C505" t="s">
         <v>978</v>
@@ -28453,13 +28447,13 @@
         <v>1122</v>
       </c>
       <c r="G505" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H505" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I505" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J505" t="s">
         <v>61</v>
@@ -28468,7 +28462,7 @@
         <v>75</v>
       </c>
       <c r="L505">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M505">
         <v>171</v>
@@ -28479,10 +28473,10 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B506" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C506" t="s">
         <v>978</v>
@@ -28497,19 +28491,25 @@
         <v>1122</v>
       </c>
       <c r="G506" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H506" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I506" t="s">
+        <v>175</v>
       </c>
       <c r="J506" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K506">
         <v>75</v>
       </c>
       <c r="L506">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M506">
+        <v>171</v>
       </c>
       <c r="P506" s="19">
         <v>46155</v>
@@ -28517,10 +28517,10 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B507" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C507" t="s">
         <v>978</v>
@@ -28532,28 +28532,22 @@
         <v>63</v>
       </c>
       <c r="F507" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G507" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H507" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I507" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J507" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>24.08</v>
-      </c>
-      <c r="M507">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P507" s="19">
         <v>46155</v>
@@ -28561,10 +28555,10 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B508" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C508" t="s">
         <v>978</v>
@@ -28576,19 +28570,28 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G508" t="s">
+        <v>1216</v>
       </c>
       <c r="H508" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I508" t="s">
+        <v>175</v>
       </c>
       <c r="J508" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M508">
+        <v>12</v>
       </c>
       <c r="P508" s="19">
         <v>46155</v>
@@ -28596,10 +28599,10 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B509" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C509" t="s">
         <v>978</v>
@@ -28611,30 +28614,27 @@
         <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H509" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J509" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>7.05</v>
-      </c>
-      <c r="M509">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P509" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A510">
-        <v>27100523</v>
+      <c r="A510" t="s">
+        <v>1221</v>
       </c>
       <c r="B510" t="s">
         <v>66</v>
@@ -28649,36 +28649,33 @@
         <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G510" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H510" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I510" t="s">
-        <v>777</v>
-      </c>
-      <c r="J510">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J510" t="s">
+        <v>217</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M510">
+        <v>30</v>
       </c>
       <c r="P510" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A511" t="s">
-        <v>1225</v>
+      <c r="A511">
+        <v>27100523</v>
       </c>
       <c r="B511" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C511" t="s">
         <v>978</v>
@@ -28690,33 +28687,36 @@
         <v>63</v>
       </c>
       <c r="F511" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G511" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H511" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J511" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I511" t="s">
+        <v>777</v>
+      </c>
+      <c r="J511">
+        <v>2023</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P511" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B512" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C512" t="s">
         <v>978</v>
@@ -28728,33 +28728,33 @@
         <v>63</v>
       </c>
       <c r="F512" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G512" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H512" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J512" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K512">
         <v>75</v>
       </c>
       <c r="L512">
-        <v>7.35</v>
-      </c>
-      <c r="M512">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P512" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="513" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A513" t="s">
+        <v>1229</v>
+      </c>
       <c r="B513" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C513" t="s">
         <v>978</v>
@@ -28769,19 +28769,19 @@
         <v>1119</v>
       </c>
       <c r="G513" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H513" t="s">
         <v>1231</v>
       </c>
       <c r="J513" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K513">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L513">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M513">
         <v>2215</v>
@@ -28790,12 +28790,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="514" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A514" t="s">
-        <v>1233</v>
-      </c>
+    <row r="514" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B514" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C514" t="s">
         <v>978</v>
@@ -28810,30 +28807,30 @@
         <v>1119</v>
       </c>
       <c r="G514" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H514" t="s">
         <v>1231</v>
       </c>
-      <c r="J514">
-        <v>2023</v>
+      <c r="J514" t="s">
+        <v>61</v>
       </c>
       <c r="K514">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L514">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M514">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P514" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="515" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B515" t="s">
         <v>66</v>
@@ -28851,36 +28848,33 @@
         <v>1119</v>
       </c>
       <c r="G515" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H515" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I515" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J515" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J515">
+        <v>2023</v>
       </c>
       <c r="K515">
         <v>75</v>
       </c>
       <c r="L515">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M515">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="516" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B516" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C516" t="s">
         <v>978</v>
@@ -28895,27 +28889,33 @@
         <v>1119</v>
       </c>
       <c r="G516" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H516" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I516" t="s">
+        <v>1238</v>
       </c>
       <c r="J516" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M516">
+        <v>205</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="517" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B517" t="s">
         <v>55</v>
@@ -28933,10 +28933,10 @@
         <v>1119</v>
       </c>
       <c r="G517" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H517" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J517" t="s">
         <v>98</v>
@@ -28945,21 +28945,18 @@
         <v>75</v>
       </c>
       <c r="L517">
-        <v>14.6</v>
-      </c>
-      <c r="M517">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="518" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A518">
-        <v>43700124</v>
+    <row r="518" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A518" t="s">
+        <v>1242</v>
       </c>
       <c r="B518" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C518" t="s">
         <v>978</v>
@@ -28971,33 +28968,36 @@
         <v>63</v>
       </c>
       <c r="F518" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G518" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H518" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J518">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J518" t="s">
+        <v>98</v>
       </c>
       <c r="K518">
         <v>75</v>
       </c>
       <c r="L518">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M518">
+        <v>0</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="519" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A519">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B519" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C519" t="s">
         <v>978</v>
@@ -29012,27 +29012,27 @@
         <v>1028</v>
       </c>
       <c r="G519" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H519" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J519">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="520" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B520" t="s">
         <v>55</v>
@@ -29050,30 +29050,30 @@
         <v>1028</v>
       </c>
       <c r="G520" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H520" t="s">
         <v>1031</v>
       </c>
       <c r="J520">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="521" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A521" t="s">
-        <v>1247</v>
+    <row r="521" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A521">
+        <v>43700524</v>
       </c>
       <c r="B521" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C521" t="s">
         <v>978</v>
@@ -29082,36 +29082,33 @@
         <v>979</v>
       </c>
       <c r="E521" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F521" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G521" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H521" t="s">
-        <v>982</v>
-      </c>
-      <c r="J521" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J521">
+        <v>2024</v>
       </c>
       <c r="K521">
         <v>75</v>
       </c>
       <c r="L521">
-        <v>3.8</v>
-      </c>
-      <c r="M521">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="522" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B522" t="s">
         <v>66</v>
@@ -29129,30 +29126,30 @@
         <v>980</v>
       </c>
       <c r="G522" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H522" t="s">
-        <v>985</v>
-      </c>
-      <c r="J522">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J522" t="s">
+        <v>98</v>
       </c>
       <c r="K522">
         <v>75</v>
       </c>
       <c r="L522">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M522">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="523" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29170,10 +29167,10 @@
         <v>980</v>
       </c>
       <c r="G523" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H523" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J523">
         <v>2025</v>
@@ -29182,21 +29179,21 @@
         <v>75</v>
       </c>
       <c r="L523">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M523">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="524" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B524" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C524" t="s">
         <v>978</v>
@@ -29211,33 +29208,33 @@
         <v>980</v>
       </c>
       <c r="G524" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H524" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J524" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J524">
+        <v>2025</v>
       </c>
       <c r="K524">
         <v>75</v>
       </c>
       <c r="L524">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M524">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="525" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B525" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C525" t="s">
         <v>978</v>
@@ -29252,30 +29249,30 @@
         <v>980</v>
       </c>
       <c r="G525" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H525" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J525" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K525">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L525">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M525">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="526" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B526" t="s">
         <v>66</v>
@@ -29293,71 +29290,71 @@
         <v>980</v>
       </c>
       <c r="G526" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H526" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J526" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K526">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L526">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M526">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="527" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
       </c>
       <c r="C527" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D527" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E527" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F527" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G527" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H527" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J527" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K527">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L527">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M527">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="528" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
@@ -29372,13 +29369,13 @@
         <v>57</v>
       </c>
       <c r="F528" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G528" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H528" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J528" t="s">
         <v>339</v>
@@ -29387,21 +29384,18 @@
         <v>75</v>
       </c>
       <c r="L528">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M528">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
       </c>
-      <c r="R528" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A529">
-        <v>24000925</v>
+    </row>
+    <row r="529" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A529" t="s">
+        <v>1262</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29413,36 +29407,39 @@
         <v>1258</v>
       </c>
       <c r="E529" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F529" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G529" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H529" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J529">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J529" t="s">
+        <v>339</v>
       </c>
       <c r="K529">
         <v>75</v>
       </c>
       <c r="L529">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M529">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
       </c>
-    </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A530" t="s">
-        <v>1266</v>
+      <c r="R529" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="530" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A530">
+        <v>24000925</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29454,36 +29451,36 @@
         <v>1258</v>
       </c>
       <c r="E530" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F530" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G530" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H530" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J530" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J530">
+        <v>2025</v>
       </c>
       <c r="K530">
         <v>75</v>
       </c>
       <c r="L530">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M530">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29498,33 +29495,33 @@
         <v>63</v>
       </c>
       <c r="F531" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G531" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H531" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J531" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K531">
         <v>75</v>
       </c>
       <c r="L531">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M531">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A532">
-        <v>24001825</v>
+    <row r="532" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A532" t="s">
+        <v>1270</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29539,33 +29536,33 @@
         <v>63</v>
       </c>
       <c r="F532" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G532" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H532" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J532">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J532" t="s">
+        <v>98</v>
       </c>
       <c r="K532">
         <v>75</v>
       </c>
       <c r="L532">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M532">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A533" t="s">
-        <v>1275</v>
+    <row r="533" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A533">
+        <v>24001825</v>
       </c>
       <c r="B533" t="s">
         <v>66</v>
@@ -29580,30 +29577,33 @@
         <v>63</v>
       </c>
       <c r="F533" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G533" t="s">
+        <v>1274</v>
       </c>
       <c r="H533" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J533" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J533">
+        <v>2025</v>
       </c>
       <c r="K533">
         <v>75</v>
       </c>
       <c r="L533">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M533">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P533" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B534" t="s">
         <v>66</v>
@@ -29618,36 +29618,30 @@
         <v>63</v>
       </c>
       <c r="F534" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G534" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H534" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I534" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J534" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K534">
         <v>75</v>
       </c>
       <c r="L534">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M534">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29656,36 +29650,42 @@
         <v>1257</v>
       </c>
       <c r="D535" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E535" t="s">
         <v>63</v>
       </c>
       <c r="F535" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G535" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H535" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I535" t="s">
+        <v>69</v>
       </c>
       <c r="J535" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K535">
         <v>75</v>
       </c>
       <c r="L535">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M535">
+        <v>318</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29703,30 +29703,27 @@
         <v>1284</v>
       </c>
       <c r="G536" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H536" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J536" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K536">
         <v>75</v>
       </c>
       <c r="L536">
-        <v>6.1</v>
-      </c>
-      <c r="M536">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29749,8 +29746,8 @@
       <c r="H537" t="s">
         <v>1289</v>
       </c>
-      <c r="J537">
-        <v>2024</v>
+      <c r="J537" t="s">
+        <v>87</v>
       </c>
       <c r="K537">
         <v>75</v>
@@ -29758,16 +29755,19 @@
       <c r="L537">
         <v>6.1</v>
       </c>
+      <c r="M537">
+        <v>133</v>
+      </c>
       <c r="P537" s="19">
-        <v>46275</v>
-      </c>
-    </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="538" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B538" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C538" t="s">
         <v>1257</v>
@@ -29782,30 +29782,27 @@
         <v>1284</v>
       </c>
       <c r="G538" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H538" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J538" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J538">
+        <v>2024</v>
       </c>
       <c r="K538">
         <v>75</v>
       </c>
       <c r="L538">
-        <v>13.2</v>
-      </c>
-      <c r="M538">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P538" s="19">
-        <v>46155</v>
-      </c>
-    </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.2">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="539" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B539" t="s">
         <v>55</v>
@@ -29823,19 +29820,19 @@
         <v>1284</v>
       </c>
       <c r="G539" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H539" t="s">
         <v>1293</v>
       </c>
       <c r="J539" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K539">
         <v>75</v>
       </c>
       <c r="L539">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M539">
         <v>0</v>
@@ -29844,9 +29841,9 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B540" t="s">
         <v>55</v>
@@ -29861,22 +29858,22 @@
         <v>63</v>
       </c>
       <c r="F540" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G540" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H540" t="s">
         <v>1293</v>
       </c>
       <c r="J540" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K540">
         <v>75</v>
       </c>
       <c r="L540">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -29885,50 +29882,50 @@
         <v>46155</v>
       </c>
     </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A541">
-        <v>10702526</v>
+    <row r="541" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A541" t="s">
+        <v>1296</v>
       </c>
       <c r="B541" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C541" t="s">
         <v>1257</v>
       </c>
       <c r="D541" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E541" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F541" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G541" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H541" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J541">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J541" t="s">
+        <v>61</v>
       </c>
       <c r="K541">
         <v>75</v>
       </c>
       <c r="L541">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M541">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P541" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A542" t="s">
-        <v>1301</v>
+    <row r="542" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A542">
+        <v>10702526</v>
       </c>
       <c r="B542" t="s">
         <v>66</v>
@@ -29937,39 +29934,39 @@
         <v>1257</v>
       </c>
       <c r="D542" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E542" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F542" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G542" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H542" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J542" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J542">
+        <v>2026</v>
       </c>
       <c r="K542">
         <v>75</v>
       </c>
       <c r="L542">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M542">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29987,7 +29984,7 @@
         <v>1303</v>
       </c>
       <c r="G543" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H543" t="s">
         <v>1305</v>
@@ -29999,18 +29996,18 @@
         <v>75</v>
       </c>
       <c r="L543">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M543">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
       </c>
     </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -30028,7 +30025,7 @@
         <v>1303</v>
       </c>
       <c r="G544" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H544" t="s">
         <v>1305</v>
@@ -30043,7 +30040,7 @@
         <v>8.6</v>
       </c>
       <c r="M544">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -30051,7 +30048,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -30069,13 +30066,13 @@
         <v>1303</v>
       </c>
       <c r="G545" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H545" t="s">
         <v>1305</v>
       </c>
       <c r="J545" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K545">
         <v>75</v>
@@ -30084,7 +30081,7 @@
         <v>8.6</v>
       </c>
       <c r="M545">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -30092,7 +30089,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -30110,7 +30107,7 @@
         <v>1303</v>
       </c>
       <c r="G546" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H546" t="s">
         <v>1305</v>
@@ -30125,7 +30122,7 @@
         <v>8.6</v>
       </c>
       <c r="M546">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -30133,7 +30130,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -30151,22 +30148,22 @@
         <v>1303</v>
       </c>
       <c r="G547" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H547" t="s">
         <v>1305</v>
       </c>
       <c r="J547" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K547">
         <v>75</v>
       </c>
       <c r="L547">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M547">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -30174,7 +30171,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30192,22 +30189,22 @@
         <v>1303</v>
       </c>
       <c r="G548" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H548" t="s">
         <v>1305</v>
       </c>
-      <c r="J548">
-        <v>2021</v>
+      <c r="J548" t="s">
+        <v>127</v>
       </c>
       <c r="K548">
         <v>75</v>
       </c>
       <c r="L548">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M548">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30215,7 +30212,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30233,13 +30230,13 @@
         <v>1303</v>
       </c>
       <c r="G549" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H549" t="s">
         <v>1305</v>
       </c>
-      <c r="J549" t="s">
-        <v>109</v>
+      <c r="J549">
+        <v>2021</v>
       </c>
       <c r="K549">
         <v>75</v>
@@ -30248,7 +30245,7 @@
         <v>13</v>
       </c>
       <c r="M549">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30256,7 +30253,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30274,7 +30271,7 @@
         <v>1303</v>
       </c>
       <c r="G550" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H550" t="s">
         <v>1305</v>
@@ -30286,7 +30283,7 @@
         <v>75</v>
       </c>
       <c r="L550">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M550">
         <v>36</v>
@@ -30297,7 +30294,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30309,28 +30306,28 @@
         <v>1302</v>
       </c>
       <c r="E551" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F551" t="s">
         <v>1303</v>
       </c>
       <c r="G551" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H551" t="s">
         <v>1305</v>
       </c>
       <c r="J551" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K551">
         <v>75</v>
       </c>
       <c r="L551">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M551">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30338,40 +30335,40 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
       </c>
       <c r="C552" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D552" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E552" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F552" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G552" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H552" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J552" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K552">
         <v>75</v>
       </c>
       <c r="L552">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M552">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30379,7 +30376,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30387,17 +30384,20 @@
       <c r="C553" t="s">
         <v>1323</v>
       </c>
+      <c r="D553" t="s">
+        <v>1258</v>
+      </c>
       <c r="E553" t="s">
         <v>1323</v>
       </c>
       <c r="F553" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G553" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H553" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J553" t="s">
         <v>564</v>
@@ -30408,13 +30408,16 @@
       <c r="L553">
         <v>6.2</v>
       </c>
+      <c r="M553">
+        <v>4411</v>
+      </c>
       <c r="P553" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30429,10 +30432,10 @@
         <v>58</v>
       </c>
       <c r="G554" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H554" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J554" t="s">
         <v>564</v>
@@ -30441,7 +30444,7 @@
         <v>75</v>
       </c>
       <c r="L554">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30449,7 +30452,7 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30461,25 +30464,22 @@
         <v>1323</v>
       </c>
       <c r="F555" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G555" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H555" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J555" t="s">
         <v>564</v>
       </c>
       <c r="K555">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L555">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M555">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30487,7 +30487,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30502,22 +30502,22 @@
         <v>1332</v>
       </c>
       <c r="G556" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H556" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J556" t="s">
         <v>564</v>
       </c>
       <c r="K556">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L556">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M556">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30525,7 +30525,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30540,10 +30540,10 @@
         <v>1332</v>
       </c>
       <c r="G557" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H557" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J557" t="s">
         <v>564</v>
@@ -30552,10 +30552,10 @@
         <v>75</v>
       </c>
       <c r="L557">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M557">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30563,10 +30563,10 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B558" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C558" t="s">
         <v>1323</v>
@@ -30578,10 +30578,10 @@
         <v>1332</v>
       </c>
       <c r="G558" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H558" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J558" t="s">
         <v>564</v>
@@ -30590,7 +30590,10 @@
         <v>75</v>
       </c>
       <c r="L558">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M558">
+        <v>418</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30598,10 +30601,10 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B559" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C559" t="s">
         <v>1323</v>
@@ -30613,10 +30616,10 @@
         <v>1332</v>
       </c>
       <c r="G559" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H559" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J559" t="s">
         <v>564</v>
@@ -30625,10 +30628,7 @@
         <v>75</v>
       </c>
       <c r="L559">
-        <v>25.8</v>
-      </c>
-      <c r="M559">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30636,7 +30636,7 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B560" t="s">
         <v>66</v>
@@ -30651,10 +30651,10 @@
         <v>1332</v>
       </c>
       <c r="G560" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H560" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J560" t="s">
         <v>564</v>
@@ -30663,10 +30663,10 @@
         <v>75</v>
       </c>
       <c r="L560">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M560">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30674,7 +30674,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30689,10 +30689,10 @@
         <v>1332</v>
       </c>
       <c r="G561" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H561" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J561" t="s">
         <v>564</v>
@@ -30701,10 +30701,10 @@
         <v>75</v>
       </c>
       <c r="L561">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M561">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30712,7 +30712,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30727,10 +30727,10 @@
         <v>1332</v>
       </c>
       <c r="G562" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H562" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J562" t="s">
         <v>564</v>
@@ -30739,10 +30739,10 @@
         <v>75</v>
       </c>
       <c r="L562">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M562">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30750,10 +30750,10 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B563" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C563" t="s">
         <v>1323</v>
@@ -30765,7 +30765,7 @@
         <v>1332</v>
       </c>
       <c r="G563" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H563" t="s">
         <v>1349</v>
@@ -30774,10 +30774,10 @@
         <v>564</v>
       </c>
       <c r="K563">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L563">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M563">
         <v>60</v>
@@ -30788,7 +30788,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B564" t="s">
         <v>55</v>
@@ -30803,7 +30803,7 @@
         <v>1332</v>
       </c>
       <c r="G564" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H564" t="s">
         <v>1349</v>
@@ -30812,10 +30812,10 @@
         <v>564</v>
       </c>
       <c r="K564">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L564">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M564">
         <v>60</v>
@@ -30826,7 +30826,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B565" t="s">
         <v>55</v>
@@ -30841,7 +30841,7 @@
         <v>1332</v>
       </c>
       <c r="G565" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H565" t="s">
         <v>1349</v>
@@ -30853,7 +30853,7 @@
         <v>75</v>
       </c>
       <c r="L565">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M565">
         <v>60</v>
@@ -30864,10 +30864,10 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B566" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C566" t="s">
         <v>1323</v>
@@ -30879,10 +30879,10 @@
         <v>1332</v>
       </c>
       <c r="G566" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H566" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J566" t="s">
         <v>564</v>
@@ -30891,10 +30891,10 @@
         <v>75</v>
       </c>
       <c r="L566">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M566">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P566" s="19">
         <v>46155</v>
@@ -30902,7 +30902,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B567" t="s">
         <v>66</v>
@@ -30917,10 +30917,10 @@
         <v>1332</v>
       </c>
       <c r="G567" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H567" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J567" t="s">
         <v>564</v>
@@ -30929,10 +30929,10 @@
         <v>75</v>
       </c>
       <c r="L567">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M567">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P567" s="19">
         <v>46155</v>
@@ -30940,7 +30940,7 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B568" t="s">
         <v>66</v>
@@ -30955,10 +30955,10 @@
         <v>1332</v>
       </c>
       <c r="G568" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H568" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J568" t="s">
         <v>564</v>
@@ -30967,10 +30967,10 @@
         <v>75</v>
       </c>
       <c r="L568">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M568">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P568" s="19">
         <v>46155</v>
@@ -30978,7 +30978,7 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B569" t="s">
         <v>66</v>
@@ -30993,10 +30993,10 @@
         <v>1332</v>
       </c>
       <c r="G569" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H569" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J569" t="s">
         <v>564</v>
@@ -31005,10 +31005,10 @@
         <v>75</v>
       </c>
       <c r="L569">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M569">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P569" s="19">
         <v>46155</v>
@@ -31016,7 +31016,7 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B570" t="s">
         <v>66</v>
@@ -31031,10 +31031,10 @@
         <v>1332</v>
       </c>
       <c r="G570" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H570" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J570" t="s">
         <v>564</v>
@@ -31043,10 +31043,10 @@
         <v>75</v>
       </c>
       <c r="L570">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M570">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P570" s="19">
         <v>46155</v>
@@ -31054,10 +31054,10 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B571" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C571" t="s">
         <v>1323</v>
@@ -31069,10 +31069,10 @@
         <v>1332</v>
       </c>
       <c r="G571" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H571" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J571" t="s">
         <v>564</v>
@@ -31081,7 +31081,7 @@
         <v>75</v>
       </c>
       <c r="L571">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M571">
         <v>0</v>
@@ -31092,10 +31092,10 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B572" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C572" t="s">
         <v>1323</v>
@@ -31107,10 +31107,10 @@
         <v>1332</v>
       </c>
       <c r="G572" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H572" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J572" t="s">
         <v>564</v>
@@ -31119,10 +31119,10 @@
         <v>75</v>
       </c>
       <c r="L572">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M572">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P572" s="19">
         <v>46155</v>
@@ -31130,7 +31130,7 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B573" t="s">
         <v>66</v>
@@ -31145,7 +31145,7 @@
         <v>1332</v>
       </c>
       <c r="G573" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H573" t="s">
         <v>1352</v>
@@ -31157,10 +31157,10 @@
         <v>75</v>
       </c>
       <c r="L573">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M573">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P573" s="19">
         <v>46155</v>
@@ -31168,7 +31168,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B574" t="s">
         <v>66</v>
@@ -31183,10 +31183,10 @@
         <v>1332</v>
       </c>
       <c r="G574" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H574" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J574" t="s">
         <v>564</v>
@@ -31195,10 +31195,10 @@
         <v>75</v>
       </c>
       <c r="L574">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M574">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P574" s="19">
         <v>46155</v>
@@ -31206,7 +31206,7 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B575" t="s">
         <v>66</v>
@@ -31221,10 +31221,10 @@
         <v>1332</v>
       </c>
       <c r="G575" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H575" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J575" t="s">
         <v>564</v>
@@ -31244,7 +31244,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -31259,22 +31259,22 @@
         <v>1332</v>
       </c>
       <c r="G576" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H576" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J576" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K576">
         <v>75</v>
       </c>
       <c r="L576">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M576">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P576" s="19">
         <v>46155</v>
@@ -31282,7 +31282,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B577" t="s">
         <v>66</v>
@@ -31297,22 +31297,22 @@
         <v>1332</v>
       </c>
       <c r="G577" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H577" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J577">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J577" t="s">
+        <v>167</v>
       </c>
       <c r="K577">
         <v>75</v>
       </c>
       <c r="L577">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M577">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P577" s="19">
         <v>46155</v>
@@ -31320,7 +31320,7 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B578" t="s">
         <v>66</v>
@@ -31328,9 +31328,6 @@
       <c r="C578" t="s">
         <v>1323</v>
       </c>
-      <c r="D578" t="s">
-        <v>1008</v>
-      </c>
       <c r="E578" t="s">
         <v>1323</v>
       </c>
@@ -31338,22 +31335,22 @@
         <v>1332</v>
       </c>
       <c r="G578" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H578" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J578" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J578">
+        <v>2017</v>
       </c>
       <c r="K578">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L578">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M578">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P578" s="19">
         <v>46155</v>
@@ -31361,7 +31358,7 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B579" t="s">
         <v>66</v>
@@ -31379,7 +31376,7 @@
         <v>1332</v>
       </c>
       <c r="G579" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H579" t="s">
         <v>1352</v>
@@ -31391,10 +31388,10 @@
         <v>150</v>
       </c>
       <c r="L579">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M579">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P579" s="19">
         <v>46155</v>
@@ -31402,10 +31399,10 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B580" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C580" t="s">
         <v>1323</v>
@@ -31420,10 +31417,10 @@
         <v>1332</v>
       </c>
       <c r="G580" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H580" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J580" t="s">
         <v>564</v>
@@ -31432,10 +31429,10 @@
         <v>150</v>
       </c>
       <c r="L580">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M580">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P580" s="19">
         <v>46155</v>
@@ -31443,7 +31440,7 @@
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B581" t="s">
         <v>55</v>
@@ -31461,7 +31458,7 @@
         <v>1332</v>
       </c>
       <c r="G581" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H581" t="s">
         <v>1334</v>
@@ -31470,10 +31467,10 @@
         <v>564</v>
       </c>
       <c r="K581">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L581">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M581">
         <v>5</v>
@@ -31484,7 +31481,7 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B582" t="s">
         <v>55</v>
@@ -31502,7 +31499,7 @@
         <v>1332</v>
       </c>
       <c r="G582" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H582" t="s">
         <v>1334</v>
@@ -31511,10 +31508,10 @@
         <v>564</v>
       </c>
       <c r="K582">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L582">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M582">
         <v>5</v>
@@ -31525,37 +31522,40 @@
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B583" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C583" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D583" t="s">
+        <v>1008</v>
       </c>
       <c r="E583" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F583" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G583" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H583" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J583" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K583">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L583">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M583">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P583" s="19">
         <v>46155</v>
@@ -31563,7 +31563,7 @@
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B584" t="s">
         <v>66</v>
@@ -31578,7 +31578,7 @@
         <v>1406</v>
       </c>
       <c r="G584" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H584" t="s">
         <v>1408</v>
@@ -31590,7 +31590,7 @@
         <v>70</v>
       </c>
       <c r="L584">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M584">
         <v>6</v>
@@ -31601,7 +31601,7 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B585" t="s">
         <v>66</v>
@@ -31616,19 +31616,22 @@
         <v>1406</v>
       </c>
       <c r="G585" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H585" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J585" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K585">
         <v>70</v>
       </c>
       <c r="L585">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M585">
+        <v>6</v>
       </c>
       <c r="P585" s="19">
         <v>46155</v>
@@ -31636,7 +31639,7 @@
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B586" t="s">
         <v>66</v>
@@ -31651,19 +31654,19 @@
         <v>1406</v>
       </c>
       <c r="G586" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H586" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J586" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K586">
         <v>70</v>
       </c>
       <c r="L586">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P586" s="19">
         <v>46155</v>
@@ -31671,7 +31674,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B587" t="s">
         <v>66</v>
@@ -31686,19 +31689,19 @@
         <v>1406</v>
       </c>
       <c r="G587" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H587" t="s">
         <v>1418</v>
       </c>
       <c r="J587" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K587">
         <v>70</v>
       </c>
       <c r="L587">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P587" s="19">
         <v>46155</v>
@@ -31706,7 +31709,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B588" t="s">
         <v>66</v>
@@ -31721,19 +31724,19 @@
         <v>1406</v>
       </c>
       <c r="G588" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H588" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J588" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K588">
         <v>70</v>
       </c>
       <c r="L588">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P588" s="19">
         <v>46155</v>
@@ -31741,7 +31744,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B589" t="s">
         <v>66</v>
@@ -31749,9 +31752,6 @@
       <c r="C589" t="s">
         <v>1405</v>
       </c>
-      <c r="D589" t="s">
-        <v>1008</v>
-      </c>
       <c r="E589" t="s">
         <v>1405</v>
       </c>
@@ -31759,19 +31759,19 @@
         <v>1406</v>
       </c>
       <c r="G589" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H589" t="s">
         <v>1425</v>
       </c>
       <c r="J589" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K589">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L589">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P589" s="19">
         <v>46155</v>
@@ -31779,7 +31779,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B590" t="s">
         <v>66</v>
@@ -31787,26 +31787,29 @@
       <c r="C590" t="s">
         <v>1405</v>
       </c>
+      <c r="D590" t="s">
+        <v>1008</v>
+      </c>
       <c r="E590" t="s">
         <v>1405</v>
       </c>
       <c r="F590" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G590" t="s">
+        <v>1428</v>
       </c>
       <c r="H590" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J590" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K590">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L590">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M590">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P590" s="19">
         <v>46155</v>
@@ -31814,10 +31817,10 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B591" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C591" t="s">
         <v>1405</v>
@@ -31828,17 +31831,17 @@
       <c r="F591" t="s">
         <v>1431</v>
       </c>
-      <c r="G591" t="s">
-        <v>1435</v>
-      </c>
       <c r="H591" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J591" t="s">
+        <v>1433</v>
       </c>
       <c r="K591">
         <v>70</v>
       </c>
       <c r="L591">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M591">
         <v>45</v>
@@ -31849,10 +31852,10 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B592" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C592" t="s">
         <v>1405</v>
@@ -31864,22 +31867,19 @@
         <v>1431</v>
       </c>
       <c r="G592" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H592" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J592" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K592">
         <v>70</v>
       </c>
       <c r="L592">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M592">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P592" s="19">
         <v>46155</v>
@@ -31887,7 +31887,7 @@
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B593" t="s">
         <v>66</v>
@@ -31902,22 +31902,22 @@
         <v>1431</v>
       </c>
       <c r="G593" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H593" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J593" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K593">
         <v>70</v>
       </c>
       <c r="L593">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M593">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P593" s="19">
         <v>46155</v>
@@ -31925,7 +31925,7 @@
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B594" t="s">
         <v>66</v>
@@ -31937,25 +31937,25 @@
         <v>1405</v>
       </c>
       <c r="F594" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G594" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H594" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J594" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K594">
         <v>70</v>
       </c>
       <c r="L594">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M594">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P594" s="19">
         <v>46155</v>
@@ -31963,7 +31963,7 @@
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B595" t="s">
         <v>66</v>
@@ -31978,7 +31978,7 @@
         <v>1445</v>
       </c>
       <c r="G595" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H595" t="s">
         <v>1447</v>
@@ -31990,21 +31990,21 @@
         <v>70</v>
       </c>
       <c r="L595">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
       <c r="M595">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P595" s="19">
-        <v>46175</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="596" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>2365</v>
+        <v>1449</v>
       </c>
       <c r="B596" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C596" t="s">
         <v>1405</v>
@@ -32013,33 +32013,71 @@
         <v>1405</v>
       </c>
       <c r="F596" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G596" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H596" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J596" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K596">
+        <v>70</v>
+      </c>
+      <c r="L596">
+        <v>40.5</v>
+      </c>
+      <c r="M596">
+        <v>5</v>
+      </c>
+      <c r="P596" s="19">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="597" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A597" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B597" t="s">
+        <v>55</v>
+      </c>
+      <c r="C597" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E597" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F597" t="s">
         <v>2366</v>
       </c>
-      <c r="G596" t="s">
+      <c r="G597" t="s">
         <v>2367</v>
       </c>
-      <c r="H596" t="s">
+      <c r="H597" t="s">
         <v>2362</v>
       </c>
-      <c r="J596">
+      <c r="J597">
         <f>5.41+1.74</f>
         <v>7.15</v>
       </c>
-      <c r="K596">
+      <c r="K597">
         <v>70</v>
       </c>
-      <c r="L596">
+      <c r="L597">
         <v>21.95</v>
       </c>
-      <c r="M596">
+      <c r="M597">
         <v>6</v>
       </c>
-      <c r="P596" s="19">
+      <c r="P597" s="19">
         <v>46155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R595" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R596" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="419" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56DB21A4-B29A-E546-9253-39A885EDA494}"/>
+  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04391901-AF94-194B-A995-F72457E3C370}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$596</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$597</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10584" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10591" uniqueCount="2401">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -8013,7 +8013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R597"/>
+  <dimension ref="A1:R598"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23785,11 +23785,11 @@
       </c>
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A393" t="s">
-        <v>951</v>
+      <c r="A393">
+        <v>73900525</v>
       </c>
       <c r="B393" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C393" t="s">
         <v>906</v>
@@ -23798,39 +23798,33 @@
         <v>913</v>
       </c>
       <c r="E393" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F393" t="s">
         <v>952</v>
       </c>
-      <c r="G393" t="s">
-        <v>953</v>
-      </c>
       <c r="H393" t="s">
-        <v>954</v>
+        <v>2400</v>
       </c>
       <c r="I393" t="s">
         <v>69</v>
       </c>
-      <c r="J393" t="s">
-        <v>98</v>
+      <c r="J393">
+        <v>2025</v>
       </c>
       <c r="K393">
         <v>75</v>
       </c>
       <c r="L393">
-        <v>6.45</v>
+        <v>7.4</v>
       </c>
       <c r="M393">
-        <v>501</v>
-      </c>
-      <c r="P393" s="19">
-        <v>46155</v>
+        <v>12</v>
       </c>
     </row>
     <row r="394" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A394">
-        <v>10300525</v>
+      <c r="A394" t="s">
+        <v>951</v>
       </c>
       <c r="B394" t="s">
         <v>66</v>
@@ -23848,7 +23842,7 @@
         <v>952</v>
       </c>
       <c r="G394" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="H394" t="s">
         <v>954</v>
@@ -23856,25 +23850,25 @@
       <c r="I394" t="s">
         <v>69</v>
       </c>
-      <c r="J394">
-        <v>2025</v>
+      <c r="J394" t="s">
+        <v>98</v>
       </c>
       <c r="K394">
         <v>75</v>
       </c>
       <c r="L394">
-        <v>6.55</v>
+        <v>6.45</v>
       </c>
       <c r="M394">
-        <v>741</v>
+        <v>501</v>
       </c>
       <c r="P394" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="395" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A395" t="s">
-        <v>956</v>
+      <c r="A395">
+        <v>10300525</v>
       </c>
       <c r="B395" t="s">
         <v>66</v>
@@ -23889,25 +23883,28 @@
         <v>923</v>
       </c>
       <c r="F395" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="G395" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="H395" t="s">
-        <v>292</v>
-      </c>
-      <c r="J395" t="s">
-        <v>98</v>
+        <v>954</v>
+      </c>
+      <c r="I395" t="s">
+        <v>69</v>
+      </c>
+      <c r="J395">
+        <v>2025</v>
       </c>
       <c r="K395">
         <v>75</v>
       </c>
       <c r="L395">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="M395">
-        <v>648</v>
+        <v>741</v>
       </c>
       <c r="P395" s="19">
         <v>46155</v>
@@ -23915,7 +23912,7 @@
     </row>
     <row r="396" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B396" t="s">
         <v>66</v>
@@ -23932,11 +23929,11 @@
       <c r="F396" t="s">
         <v>957</v>
       </c>
+      <c r="G396" t="s">
+        <v>958</v>
+      </c>
       <c r="H396" t="s">
-        <v>960</v>
-      </c>
-      <c r="I396" t="s">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="J396" t="s">
         <v>98</v>
@@ -23945,10 +23942,10 @@
         <v>75</v>
       </c>
       <c r="L396">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="M396">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="P396" s="19">
         <v>46155</v>
@@ -23956,10 +23953,10 @@
     </row>
     <row r="397" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B397" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C397" t="s">
         <v>906</v>
@@ -23973,26 +23970,23 @@
       <c r="F397" t="s">
         <v>957</v>
       </c>
-      <c r="G397" t="s">
-        <v>962</v>
-      </c>
       <c r="H397" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="I397" t="s">
         <v>69</v>
       </c>
       <c r="J397" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K397">
         <v>75</v>
       </c>
       <c r="L397">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="M397">
-        <v>66</v>
+        <v>574</v>
       </c>
       <c r="P397" s="19">
         <v>46155</v>
@@ -24000,10 +23994,10 @@
     </row>
     <row r="398" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B398" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C398" t="s">
         <v>906</v>
@@ -24018,22 +24012,25 @@
         <v>957</v>
       </c>
       <c r="G398" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="H398" t="s">
-        <v>920</v>
+        <v>963</v>
+      </c>
+      <c r="I398" t="s">
+        <v>69</v>
       </c>
       <c r="J398" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K398">
         <v>75</v>
       </c>
       <c r="L398">
-        <v>9.1</v>
+        <v>7.5</v>
       </c>
       <c r="M398">
-        <v>253</v>
+        <v>66</v>
       </c>
       <c r="P398" s="19">
         <v>46155</v>
@@ -24041,7 +24038,7 @@
     </row>
     <row r="399" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B399" t="s">
         <v>66</v>
@@ -24059,10 +24056,10 @@
         <v>957</v>
       </c>
       <c r="G399" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H399" t="s">
-        <v>947</v>
+        <v>920</v>
       </c>
       <c r="J399" t="s">
         <v>286</v>
@@ -24074,15 +24071,15 @@
         <v>9.1</v>
       </c>
       <c r="M399">
-        <v>575</v>
+        <v>253</v>
       </c>
       <c r="P399" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="400" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A400">
-        <v>43600225</v>
+      <c r="A400" t="s">
+        <v>966</v>
       </c>
       <c r="B400" t="s">
         <v>66</v>
@@ -24100,33 +24097,30 @@
         <v>957</v>
       </c>
       <c r="G400" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H400" t="s">
-        <v>963</v>
-      </c>
-      <c r="I400" t="s">
-        <v>69</v>
+        <v>947</v>
       </c>
       <c r="J400" t="s">
-        <v>339</v>
+        <v>286</v>
       </c>
       <c r="K400">
         <v>75</v>
       </c>
       <c r="L400">
-        <v>9.3000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="M400">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="P400" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A401" t="s">
-        <v>970</v>
+      <c r="A401">
+        <v>43600225</v>
       </c>
       <c r="B401" t="s">
         <v>66</v>
@@ -24144,25 +24138,25 @@
         <v>957</v>
       </c>
       <c r="G401" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="H401" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="I401" t="s">
         <v>69</v>
       </c>
       <c r="J401" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K401">
         <v>75</v>
       </c>
       <c r="L401">
-        <v>9.9499999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="M401">
-        <v>341</v>
+        <v>12</v>
       </c>
       <c r="P401" s="19">
         <v>46155</v>
@@ -24170,7 +24164,7 @@
     </row>
     <row r="402" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B402" t="s">
         <v>66</v>
@@ -24187,8 +24181,14 @@
       <c r="F402" t="s">
         <v>957</v>
       </c>
+      <c r="G402" t="s">
+        <v>971</v>
+      </c>
       <c r="H402" t="s">
-        <v>974</v>
+        <v>972</v>
+      </c>
+      <c r="I402" t="s">
+        <v>69</v>
       </c>
       <c r="J402" t="s">
         <v>98</v>
@@ -24200,7 +24200,7 @@
         <v>9.9499999999999993</v>
       </c>
       <c r="M402">
-        <v>394</v>
+        <v>341</v>
       </c>
       <c r="P402" s="19">
         <v>46155</v>
@@ -24208,7 +24208,7 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B403" t="s">
         <v>66</v>
@@ -24223,25 +24223,22 @@
         <v>923</v>
       </c>
       <c r="F403" t="s">
-        <v>918</v>
-      </c>
-      <c r="G403" t="s">
-        <v>919</v>
+        <v>957</v>
       </c>
       <c r="H403" t="s">
-        <v>920</v>
+        <v>974</v>
       </c>
       <c r="J403" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K403">
         <v>75</v>
       </c>
       <c r="L403">
-        <v>11.8</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M403">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="P403" s="19">
         <v>46155</v>
@@ -24249,7 +24246,7 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B404" t="s">
         <v>66</v>
@@ -24264,25 +24261,25 @@
         <v>923</v>
       </c>
       <c r="F404" t="s">
-        <v>957</v>
+        <v>918</v>
+      </c>
+      <c r="G404" t="s">
+        <v>919</v>
       </c>
       <c r="H404" t="s">
-        <v>972</v>
-      </c>
-      <c r="I404" t="s">
-        <v>69</v>
-      </c>
-      <c r="J404">
-        <v>2025</v>
+        <v>920</v>
+      </c>
+      <c r="J404" t="s">
+        <v>339</v>
       </c>
       <c r="K404">
         <v>75</v>
       </c>
       <c r="L404">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="M404">
-        <v>27</v>
+        <v>281</v>
       </c>
       <c r="P404" s="19">
         <v>46155</v>
@@ -24290,40 +24287,40 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B405" t="s">
         <v>66</v>
       </c>
       <c r="C405" t="s">
-        <v>978</v>
+        <v>906</v>
       </c>
       <c r="D405" t="s">
-        <v>979</v>
+        <v>913</v>
       </c>
       <c r="E405" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F405" t="s">
-        <v>980</v>
-      </c>
-      <c r="G405" t="s">
-        <v>981</v>
+        <v>957</v>
       </c>
       <c r="H405" t="s">
-        <v>982</v>
-      </c>
-      <c r="J405" t="s">
-        <v>339</v>
+        <v>972</v>
+      </c>
+      <c r="I405" t="s">
+        <v>69</v>
+      </c>
+      <c r="J405">
+        <v>2025</v>
       </c>
       <c r="K405">
         <v>75</v>
       </c>
       <c r="L405">
-        <v>3.8</v>
+        <v>12.3</v>
       </c>
       <c r="M405">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="P405" s="19">
         <v>46155</v>
@@ -24331,7 +24328,7 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B406" t="s">
         <v>66</v>
@@ -24349,22 +24346,22 @@
         <v>980</v>
       </c>
       <c r="G406" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H406" t="s">
-        <v>985</v>
-      </c>
-      <c r="J406">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J406" t="s">
+        <v>339</v>
       </c>
       <c r="K406">
         <v>75</v>
       </c>
       <c r="L406">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M406">
-        <v>368</v>
+        <v>60</v>
       </c>
       <c r="P406" s="19">
         <v>46155</v>
@@ -24372,7 +24369,7 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B407" t="s">
         <v>66</v>
@@ -24387,25 +24384,25 @@
         <v>57</v>
       </c>
       <c r="F407" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G407" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="H407" t="s">
-        <v>989</v>
-      </c>
-      <c r="J407" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J407">
+        <v>2025</v>
       </c>
       <c r="K407">
         <v>75</v>
       </c>
       <c r="L407">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M407">
-        <v>152</v>
+        <v>368</v>
       </c>
       <c r="P407" s="19">
         <v>46155</v>
@@ -24413,7 +24410,7 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B408" t="s">
         <v>66</v>
@@ -24428,25 +24425,25 @@
         <v>57</v>
       </c>
       <c r="F408" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G408" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="H408" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="J408" t="s">
-        <v>286</v>
+        <v>564</v>
       </c>
       <c r="K408">
         <v>75</v>
       </c>
       <c r="L408">
-        <v>5.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="M408">
-        <v>693</v>
+        <v>152</v>
       </c>
       <c r="P408" s="19">
         <v>46155</v>
@@ -24454,7 +24451,7 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B409" t="s">
         <v>66</v>
@@ -24472,22 +24469,22 @@
         <v>980</v>
       </c>
       <c r="G409" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="H409" t="s">
-        <v>292</v>
+        <v>992</v>
       </c>
       <c r="J409" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K409">
         <v>75</v>
       </c>
       <c r="L409">
-        <v>4.25</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M409">
-        <v>363</v>
+        <v>693</v>
       </c>
       <c r="P409" s="19">
         <v>46155</v>
@@ -24495,7 +24492,7 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B410" t="s">
         <v>66</v>
@@ -24513,22 +24510,22 @@
         <v>980</v>
       </c>
       <c r="G410" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H410" t="s">
         <v>292</v>
       </c>
-      <c r="J410">
-        <v>2025</v>
+      <c r="J410" t="s">
+        <v>98</v>
       </c>
       <c r="K410">
         <v>75</v>
       </c>
       <c r="L410">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="M410">
-        <v>1425</v>
+        <v>363</v>
       </c>
       <c r="P410" s="19">
         <v>46155</v>
@@ -24536,7 +24533,7 @@
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B411" t="s">
         <v>66</v>
@@ -24554,22 +24551,22 @@
         <v>980</v>
       </c>
       <c r="G411" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H411" t="s">
-        <v>992</v>
-      </c>
-      <c r="J411" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J411">
+        <v>2025</v>
       </c>
       <c r="K411">
         <v>75</v>
       </c>
       <c r="L411">
-        <v>5.25</v>
+        <v>4.05</v>
       </c>
       <c r="M411">
-        <v>84</v>
+        <v>1425</v>
       </c>
       <c r="P411" s="19">
         <v>46155</v>
@@ -24577,7 +24574,7 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B412" t="s">
         <v>66</v>
@@ -24592,13 +24589,13 @@
         <v>57</v>
       </c>
       <c r="F412" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G412" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H412" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="J412" t="s">
         <v>339</v>
@@ -24607,10 +24604,10 @@
         <v>75</v>
       </c>
       <c r="L412">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="M412">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="P412" s="19">
         <v>46155</v>
@@ -24618,7 +24615,7 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B413" t="s">
         <v>66</v>
@@ -24633,16 +24630,16 @@
         <v>57</v>
       </c>
       <c r="F413" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G413" t="s">
-        <v>113</v>
+        <v>1000</v>
       </c>
       <c r="H413" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="J413" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K413">
         <v>75</v>
@@ -24651,7 +24648,7 @@
         <v>5.7</v>
       </c>
       <c r="M413">
-        <v>165</v>
+        <v>42</v>
       </c>
       <c r="P413" s="19">
         <v>46155</v>
@@ -24659,7 +24656,7 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B414" t="s">
         <v>66</v>
@@ -24677,22 +24674,22 @@
         <v>980</v>
       </c>
       <c r="G414" t="s">
-        <v>1005</v>
+        <v>113</v>
       </c>
       <c r="H414" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="J414" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K414">
         <v>75</v>
       </c>
       <c r="L414">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="M414">
-        <v>3214</v>
+        <v>165</v>
       </c>
       <c r="P414" s="19">
         <v>46155</v>
@@ -24700,16 +24697,16 @@
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B415" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C415" t="s">
         <v>978</v>
       </c>
       <c r="D415" t="s">
-        <v>1008</v>
+        <v>979</v>
       </c>
       <c r="E415" t="s">
         <v>57</v>
@@ -24718,7 +24715,7 @@
         <v>980</v>
       </c>
       <c r="G415" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="H415" t="s">
         <v>1006</v>
@@ -24727,13 +24724,13 @@
         <v>339</v>
       </c>
       <c r="K415">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L415">
-        <v>12.9</v>
+        <v>5.85</v>
       </c>
       <c r="M415">
-        <v>0</v>
+        <v>3214</v>
       </c>
       <c r="P415" s="19">
         <v>46155</v>
@@ -24741,16 +24738,16 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="B416" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C416" t="s">
         <v>978</v>
       </c>
       <c r="D416" t="s">
-        <v>979</v>
+        <v>1008</v>
       </c>
       <c r="E416" t="s">
         <v>57</v>
@@ -24759,25 +24756,22 @@
         <v>980</v>
       </c>
       <c r="G416" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H416" t="s">
-        <v>992</v>
-      </c>
-      <c r="I416" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="J416" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K416">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L416">
-        <v>6.05</v>
+        <v>12.9</v>
       </c>
       <c r="M416">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="P416" s="19">
         <v>46155</v>
@@ -24785,7 +24779,7 @@
     </row>
     <row r="417" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="B417" t="s">
         <v>66</v>
@@ -24794,31 +24788,34 @@
         <v>978</v>
       </c>
       <c r="D417" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E417" t="s">
         <v>57</v>
       </c>
       <c r="F417" t="s">
-        <v>1015</v>
+        <v>980</v>
       </c>
       <c r="G417" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="H417" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I417" t="s">
+        <v>1012</v>
       </c>
       <c r="J417" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K417">
         <v>75</v>
       </c>
       <c r="L417">
-        <v>14.5</v>
+        <v>6.05</v>
       </c>
       <c r="M417">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="P417" s="19">
         <v>46155</v>
@@ -24826,7 +24823,7 @@
     </row>
     <row r="418" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B418" t="s">
         <v>66</v>
@@ -24835,34 +24832,31 @@
         <v>978</v>
       </c>
       <c r="D418" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E418" t="s">
         <v>57</v>
       </c>
       <c r="F418" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G418" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="H418" t="s">
-        <v>1021</v>
-      </c>
-      <c r="I418" t="s">
-        <v>777</v>
+        <v>1017</v>
       </c>
       <c r="J418" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="K418">
         <v>75</v>
       </c>
       <c r="L418">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="M418">
-        <v>182</v>
+        <v>24</v>
       </c>
       <c r="P418" s="19">
         <v>46155</v>
@@ -24870,7 +24864,7 @@
     </row>
     <row r="419" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B419" t="s">
         <v>66</v>
@@ -24885,33 +24879,36 @@
         <v>57</v>
       </c>
       <c r="F419" t="s">
-        <v>980</v>
+        <v>1019</v>
       </c>
       <c r="G419" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="H419" t="s">
-        <v>992</v>
+        <v>1021</v>
+      </c>
+      <c r="I419" t="s">
+        <v>777</v>
       </c>
       <c r="J419" t="s">
-        <v>339</v>
+        <v>217</v>
       </c>
       <c r="K419">
         <v>75</v>
       </c>
       <c r="L419">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="M419">
-        <v>357</v>
+        <v>182</v>
       </c>
       <c r="P419" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="420" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A420">
-        <v>13003025</v>
+      <c r="A420" t="s">
+        <v>1022</v>
       </c>
       <c r="B420" t="s">
         <v>66</v>
@@ -24929,33 +24926,30 @@
         <v>980</v>
       </c>
       <c r="G420" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H420" t="s">
         <v>992</v>
       </c>
-      <c r="I420" t="s">
-        <v>1012</v>
-      </c>
-      <c r="J420">
-        <v>2025</v>
+      <c r="J420" t="s">
+        <v>339</v>
       </c>
       <c r="K420">
         <v>75</v>
       </c>
       <c r="L420">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M420">
-        <v>474</v>
+        <v>357</v>
       </c>
       <c r="P420" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="421" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A421" t="s">
-        <v>1025</v>
+      <c r="A421">
+        <v>13003025</v>
       </c>
       <c r="B421" t="s">
         <v>66</v>
@@ -24973,22 +24967,25 @@
         <v>980</v>
       </c>
       <c r="G421" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H421" t="s">
-        <v>589</v>
-      </c>
-      <c r="J421" t="s">
-        <v>339</v>
+        <v>992</v>
+      </c>
+      <c r="I421" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J421">
+        <v>2025</v>
       </c>
       <c r="K421">
         <v>75</v>
       </c>
       <c r="L421">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="M421">
-        <v>321</v>
+        <v>474</v>
       </c>
       <c r="P421" s="19">
         <v>46155</v>
@@ -24996,7 +24993,7 @@
     </row>
     <row r="422" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="B422" t="s">
         <v>66</v>
@@ -25011,33 +25008,36 @@
         <v>57</v>
       </c>
       <c r="F422" t="s">
-        <v>1028</v>
+        <v>980</v>
       </c>
       <c r="G422" t="s">
-        <v>165</v>
+        <v>1026</v>
       </c>
       <c r="H422" t="s">
-        <v>1029</v>
+        <v>589</v>
       </c>
       <c r="J422" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
       <c r="K422">
         <v>75</v>
       </c>
       <c r="L422">
-        <v>37</v>
+        <v>6.4</v>
+      </c>
+      <c r="M422">
+        <v>321</v>
       </c>
       <c r="P422" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="423" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A423">
-        <v>43700425</v>
+      <c r="A423" t="s">
+        <v>1027</v>
       </c>
       <c r="B423" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C423" t="s">
         <v>978</v>
@@ -25052,19 +25052,19 @@
         <v>1028</v>
       </c>
       <c r="G423" t="s">
-        <v>1030</v>
+        <v>165</v>
       </c>
       <c r="H423" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J423">
-        <v>2025</v>
+        <v>1029</v>
+      </c>
+      <c r="J423" t="s">
+        <v>286</v>
       </c>
       <c r="K423">
         <v>75</v>
       </c>
       <c r="L423">
-        <v>10.5</v>
+        <v>37</v>
       </c>
       <c r="P423" s="19">
         <v>46155</v>
@@ -25072,7 +25072,7 @@
     </row>
     <row r="424" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A424">
-        <v>73300125</v>
+        <v>43700425</v>
       </c>
       <c r="B424" t="s">
         <v>55</v>
@@ -25087,13 +25087,13 @@
         <v>57</v>
       </c>
       <c r="F424" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="G424" t="s">
-        <v>113</v>
+        <v>1030</v>
       </c>
       <c r="H424" t="s">
-        <v>2362</v>
+        <v>1031</v>
       </c>
       <c r="J424">
         <v>2025</v>
@@ -25102,10 +25102,7 @@
         <v>75</v>
       </c>
       <c r="L424">
-        <v>4.99</v>
-      </c>
-      <c r="M424">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="P424" s="19">
         <v>46155</v>
@@ -25113,7 +25110,7 @@
     </row>
     <row r="425" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A425">
-        <v>73300225</v>
+        <v>73300125</v>
       </c>
       <c r="B425" t="s">
         <v>55</v>
@@ -25131,7 +25128,7 @@
         <v>1033</v>
       </c>
       <c r="G425" t="s">
-        <v>2364</v>
+        <v>113</v>
       </c>
       <c r="H425" t="s">
         <v>2362</v>
@@ -25154,7 +25151,7 @@
     </row>
     <row r="426" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A426">
-        <v>73300325</v>
+        <v>73300225</v>
       </c>
       <c r="B426" t="s">
         <v>55</v>
@@ -25172,7 +25169,7 @@
         <v>1033</v>
       </c>
       <c r="G426" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="H426" t="s">
         <v>2362</v>
@@ -25184,7 +25181,7 @@
         <v>75</v>
       </c>
       <c r="L426">
-        <v>5.59</v>
+        <v>4.99</v>
       </c>
       <c r="M426">
         <v>12</v>
@@ -25195,7 +25192,7 @@
     </row>
     <row r="427" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A427">
-        <v>73300425</v>
+        <v>73300325</v>
       </c>
       <c r="B427" t="s">
         <v>55</v>
@@ -25207,13 +25204,13 @@
         <v>979</v>
       </c>
       <c r="E427" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F427" t="s">
         <v>1033</v>
       </c>
       <c r="G427" t="s">
-        <v>1135</v>
+        <v>2363</v>
       </c>
       <c r="H427" t="s">
         <v>2362</v>
@@ -25225,7 +25222,7 @@
         <v>75</v>
       </c>
       <c r="L427">
-        <v>4.99</v>
+        <v>5.59</v>
       </c>
       <c r="M427">
         <v>12</v>
@@ -25235,11 +25232,11 @@
       </c>
     </row>
     <row r="428" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A428" t="s">
-        <v>1032</v>
+      <c r="A428">
+        <v>73300425</v>
       </c>
       <c r="B428" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C428" t="s">
         <v>978</v>
@@ -25248,36 +25245,36 @@
         <v>979</v>
       </c>
       <c r="E428" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F428" t="s">
         <v>1033</v>
       </c>
       <c r="G428" t="s">
-        <v>1034</v>
+        <v>1135</v>
       </c>
       <c r="H428" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J428" t="s">
-        <v>98</v>
+        <v>2362</v>
+      </c>
+      <c r="J428">
+        <v>2025</v>
       </c>
       <c r="K428">
         <v>75</v>
       </c>
       <c r="L428">
-        <v>3.95</v>
+        <v>4.99</v>
       </c>
       <c r="M428">
-        <v>351</v>
+        <v>12</v>
       </c>
       <c r="P428" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="429" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A429">
-        <v>13300125</v>
+      <c r="A429" t="s">
+        <v>1032</v>
       </c>
       <c r="B429" t="s">
         <v>66</v>
@@ -25295,33 +25292,33 @@
         <v>1033</v>
       </c>
       <c r="G429" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H429" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J429">
-        <v>2025</v>
+        <v>1035</v>
+      </c>
+      <c r="J429" t="s">
+        <v>98</v>
       </c>
       <c r="K429">
         <v>75</v>
       </c>
       <c r="L429">
-        <v>4.75</v>
+        <v>3.95</v>
       </c>
       <c r="M429">
-        <v>14790</v>
+        <v>351</v>
       </c>
       <c r="P429" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="430" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A430" t="s">
-        <v>1038</v>
+      <c r="A430">
+        <v>13300125</v>
       </c>
       <c r="B430" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C430" t="s">
         <v>978</v>
@@ -25333,33 +25330,33 @@
         <v>57</v>
       </c>
       <c r="F430" t="s">
-        <v>58</v>
+        <v>1033</v>
       </c>
       <c r="G430" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="H430" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J430" t="s">
-        <v>339</v>
+        <v>1037</v>
+      </c>
+      <c r="J430">
+        <v>2025</v>
       </c>
       <c r="K430">
         <v>75</v>
       </c>
       <c r="L430">
-        <v>6.2</v>
+        <v>4.75</v>
       </c>
       <c r="M430">
-        <v>0</v>
+        <v>14790</v>
       </c>
       <c r="P430" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="431" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A431">
-        <v>24003025</v>
+      <c r="A431" t="s">
+        <v>1038</v>
       </c>
       <c r="B431" t="s">
         <v>55</v>
@@ -25368,7 +25365,7 @@
         <v>978</v>
       </c>
       <c r="D431" t="s">
-        <v>1041</v>
+        <v>979</v>
       </c>
       <c r="E431" t="s">
         <v>57</v>
@@ -25377,16 +25374,13 @@
         <v>58</v>
       </c>
       <c r="G431" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="H431" t="s">
-        <v>1043</v>
-      </c>
-      <c r="I431" t="s">
-        <v>69</v>
-      </c>
-      <c r="J431">
-        <v>2025</v>
+        <v>1040</v>
+      </c>
+      <c r="J431" t="s">
+        <v>339</v>
       </c>
       <c r="K431">
         <v>75</v>
@@ -25394,13 +25388,16 @@
       <c r="L431">
         <v>6.2</v>
       </c>
+      <c r="M431">
+        <v>0</v>
+      </c>
       <c r="P431" s="19">
-        <v>46177</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="432" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A432" t="s">
-        <v>1044</v>
+      <c r="A432">
+        <v>24003025</v>
       </c>
       <c r="B432" t="s">
         <v>55</v>
@@ -25409,39 +25406,39 @@
         <v>978</v>
       </c>
       <c r="D432" t="s">
-        <v>1014</v>
+        <v>1041</v>
       </c>
       <c r="E432" t="s">
         <v>57</v>
       </c>
       <c r="F432" t="s">
-        <v>1045</v>
+        <v>58</v>
       </c>
       <c r="G432" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H432" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J432" t="s">
-        <v>87</v>
+        <v>1043</v>
+      </c>
+      <c r="I432" t="s">
+        <v>69</v>
+      </c>
+      <c r="J432">
+        <v>2025</v>
       </c>
       <c r="K432">
         <v>75</v>
       </c>
       <c r="L432">
-        <v>7.55</v>
-      </c>
-      <c r="M432">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="P432" s="19">
-        <v>46155</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="433" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B433" t="s">
         <v>55</v>
@@ -25450,28 +25447,28 @@
         <v>978</v>
       </c>
       <c r="D433" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E433" t="s">
         <v>57</v>
       </c>
       <c r="F433" t="s">
-        <v>58</v>
+        <v>1045</v>
       </c>
       <c r="G433" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="H433" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="J433" t="s">
-        <v>339</v>
+        <v>87</v>
       </c>
       <c r="K433">
         <v>75</v>
       </c>
       <c r="L433">
-        <v>10.5</v>
+        <v>7.55</v>
       </c>
       <c r="M433">
         <v>0</v>
@@ -25482,7 +25479,7 @@
     </row>
     <row r="434" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B434" t="s">
         <v>55</v>
@@ -25491,28 +25488,28 @@
         <v>978</v>
       </c>
       <c r="D434" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E434" t="s">
         <v>57</v>
       </c>
       <c r="F434" t="s">
-        <v>1051</v>
+        <v>58</v>
       </c>
       <c r="G434" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="H434" t="s">
-        <v>1040</v>
+        <v>1049</v>
       </c>
       <c r="J434" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="K434">
         <v>75</v>
       </c>
       <c r="L434">
-        <v>10.65</v>
+        <v>10.5</v>
       </c>
       <c r="M434">
         <v>0</v>
@@ -25523,7 +25520,7 @@
     </row>
     <row r="435" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B435" t="s">
         <v>55</v>
@@ -25532,42 +25529,39 @@
         <v>978</v>
       </c>
       <c r="D435" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E435" t="s">
         <v>57</v>
       </c>
       <c r="F435" t="s">
-        <v>58</v>
+        <v>1051</v>
       </c>
       <c r="G435" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="H435" t="s">
-        <v>1055</v>
-      </c>
-      <c r="I435" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="J435" t="s">
-        <v>286</v>
+        <v>61</v>
       </c>
       <c r="K435">
         <v>75</v>
       </c>
       <c r="L435">
-        <v>11.5</v>
+        <v>10.65</v>
       </c>
       <c r="M435">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P435" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="436" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A436">
-        <v>27701225</v>
+      <c r="A436" t="s">
+        <v>1053</v>
       </c>
       <c r="B436" t="s">
         <v>55</v>
@@ -25576,39 +25570,42 @@
         <v>978</v>
       </c>
       <c r="D436" t="s">
-        <v>1057</v>
+        <v>979</v>
       </c>
       <c r="E436" t="s">
         <v>57</v>
       </c>
       <c r="F436" t="s">
-        <v>1058</v>
+        <v>58</v>
       </c>
       <c r="G436" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="H436" t="s">
         <v>1055</v>
       </c>
-      <c r="J436">
-        <v>2025</v>
+      <c r="I436" t="s">
+        <v>1056</v>
+      </c>
+      <c r="J436" t="s">
+        <v>286</v>
       </c>
       <c r="K436">
         <v>75</v>
       </c>
       <c r="L436">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M436">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P436" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="437" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A437" t="s">
-        <v>1060</v>
+      <c r="A437">
+        <v>27701225</v>
       </c>
       <c r="B437" t="s">
         <v>55</v>
@@ -25617,28 +25614,28 @@
         <v>978</v>
       </c>
       <c r="D437" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E437" t="s">
         <v>57</v>
       </c>
       <c r="F437" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="G437" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="H437" t="s">
-        <v>1040</v>
-      </c>
-      <c r="J437" t="s">
-        <v>132</v>
+        <v>1055</v>
+      </c>
+      <c r="J437">
+        <v>2025</v>
       </c>
       <c r="K437">
         <v>75</v>
       </c>
       <c r="L437">
-        <v>13.95</v>
+        <v>12.2</v>
       </c>
       <c r="M437">
         <v>0</v>
@@ -25649,7 +25646,7 @@
     </row>
     <row r="438" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B438" t="s">
         <v>55</v>
@@ -25658,28 +25655,28 @@
         <v>978</v>
       </c>
       <c r="D438" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E438" t="s">
         <v>57</v>
       </c>
       <c r="F438" t="s">
-        <v>1058</v>
+        <v>1045</v>
       </c>
       <c r="G438" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H438" t="s">
-        <v>1064</v>
+        <v>1040</v>
       </c>
       <c r="J438" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="K438">
         <v>75</v>
       </c>
       <c r="L438">
-        <v>14.8</v>
+        <v>13.95</v>
       </c>
       <c r="M438">
         <v>0</v>
@@ -25690,7 +25687,7 @@
     </row>
     <row r="439" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B439" t="s">
         <v>55</v>
@@ -25705,22 +25702,22 @@
         <v>57</v>
       </c>
       <c r="F439" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G439" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="H439" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="J439" t="s">
-        <v>339</v>
+        <v>106</v>
       </c>
       <c r="K439">
         <v>75</v>
       </c>
       <c r="L439">
-        <v>6.5</v>
+        <v>14.8</v>
       </c>
       <c r="M439">
         <v>0</v>
@@ -25730,8 +25727,8 @@
       </c>
     </row>
     <row r="440" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A440">
-        <v>68002225</v>
+      <c r="A440" t="s">
+        <v>1065</v>
       </c>
       <c r="B440" t="s">
         <v>55</v>
@@ -25743,13 +25740,13 @@
         <v>1057</v>
       </c>
       <c r="E440" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F440" t="s">
         <v>1066</v>
       </c>
       <c r="G440" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H440" t="s">
         <v>1068</v>
@@ -25761,7 +25758,7 @@
         <v>75</v>
       </c>
       <c r="L440">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="M440">
         <v>0</v>
@@ -25772,7 +25769,7 @@
     </row>
     <row r="441" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A441">
-        <v>68002325</v>
+        <v>68002225</v>
       </c>
       <c r="B441" t="s">
         <v>55</v>
@@ -25787,13 +25784,13 @@
         <v>63</v>
       </c>
       <c r="F441" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G441" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H441" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="J441" t="s">
         <v>339</v>
@@ -25802,7 +25799,7 @@
         <v>75</v>
       </c>
       <c r="L441">
-        <v>12.4</v>
+        <v>5.4</v>
       </c>
       <c r="M441">
         <v>0</v>
@@ -25813,7 +25810,7 @@
     </row>
     <row r="442" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A442">
-        <v>68002424</v>
+        <v>68002325</v>
       </c>
       <c r="B442" t="s">
         <v>55</v>
@@ -25831,13 +25828,13 @@
         <v>1070</v>
       </c>
       <c r="G442" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H442" t="s">
-        <v>1074</v>
-      </c>
-      <c r="J442">
-        <v>2024</v>
+        <v>1072</v>
+      </c>
+      <c r="J442" t="s">
+        <v>339</v>
       </c>
       <c r="K442">
         <v>75</v>
@@ -25853,8 +25850,8 @@
       </c>
     </row>
     <row r="443" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A443" t="s">
-        <v>1075</v>
+      <c r="A443">
+        <v>68002424</v>
       </c>
       <c r="B443" t="s">
         <v>55</v>
@@ -25872,19 +25869,19 @@
         <v>1070</v>
       </c>
       <c r="G443" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="H443" t="s">
-        <v>1077</v>
-      </c>
-      <c r="J443" t="s">
-        <v>564</v>
+        <v>1074</v>
+      </c>
+      <c r="J443">
+        <v>2024</v>
       </c>
       <c r="K443">
         <v>75</v>
       </c>
       <c r="L443">
-        <v>10.4</v>
+        <v>12.4</v>
       </c>
       <c r="M443">
         <v>0</v>
@@ -25894,8 +25891,8 @@
       </c>
     </row>
     <row r="444" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A444">
-        <v>68002623</v>
+      <c r="A444" t="s">
+        <v>1075</v>
       </c>
       <c r="B444" t="s">
         <v>55</v>
@@ -25910,25 +25907,22 @@
         <v>63</v>
       </c>
       <c r="F444" t="s">
-        <v>1078</v>
+        <v>1070</v>
       </c>
       <c r="G444" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="H444" t="s">
-        <v>1080</v>
-      </c>
-      <c r="I444" t="s">
-        <v>69</v>
-      </c>
-      <c r="J444">
-        <v>2023</v>
+        <v>1077</v>
+      </c>
+      <c r="J444" t="s">
+        <v>564</v>
       </c>
       <c r="K444">
         <v>75</v>
       </c>
       <c r="L444">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="M444">
         <v>0</v>
@@ -25939,7 +25933,7 @@
     </row>
     <row r="445" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A445">
-        <v>68002825</v>
+        <v>68002623</v>
       </c>
       <c r="B445" t="s">
         <v>55</v>
@@ -25951,28 +25945,28 @@
         <v>1057</v>
       </c>
       <c r="E445" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F445" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="G445" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="H445" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="I445" t="s">
         <v>69</v>
       </c>
       <c r="J445">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="K445">
         <v>75</v>
       </c>
       <c r="L445">
-        <v>9.6999999999999993</v>
+        <v>12.4</v>
       </c>
       <c r="M445">
         <v>0</v>
@@ -25982,8 +25976,8 @@
       </c>
     </row>
     <row r="446" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A446" t="s">
-        <v>1083</v>
+      <c r="A446">
+        <v>68002825</v>
       </c>
       <c r="B446" t="s">
         <v>55</v>
@@ -25998,22 +25992,25 @@
         <v>57</v>
       </c>
       <c r="F446" t="s">
-        <v>1066</v>
+        <v>1058</v>
       </c>
       <c r="G446" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="H446" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J446" t="s">
-        <v>339</v>
+        <v>1082</v>
+      </c>
+      <c r="I446" t="s">
+        <v>69</v>
+      </c>
+      <c r="J446">
+        <v>2025</v>
       </c>
       <c r="K446">
         <v>75</v>
       </c>
       <c r="L446">
-        <v>6.95</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="M446">
         <v>0</v>
@@ -26023,8 +26020,8 @@
       </c>
     </row>
     <row r="447" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A447">
-        <v>68003025</v>
+      <c r="A447" t="s">
+        <v>1083</v>
       </c>
       <c r="B447" t="s">
         <v>55</v>
@@ -26036,13 +26033,13 @@
         <v>1057</v>
       </c>
       <c r="E447" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F447" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
       <c r="G447" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="H447" t="s">
         <v>1085</v>
@@ -26065,7 +26062,7 @@
     </row>
     <row r="448" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A448">
-        <v>680031225</v>
+        <v>68003025</v>
       </c>
       <c r="B448" t="s">
         <v>55</v>
@@ -26083,10 +26080,10 @@
         <v>1078</v>
       </c>
       <c r="G448" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="H448" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="J448" t="s">
         <v>339</v>
@@ -26095,7 +26092,7 @@
         <v>75</v>
       </c>
       <c r="L448">
-        <v>7.95</v>
+        <v>6.95</v>
       </c>
       <c r="M448">
         <v>0</v>
@@ -26105,8 +26102,8 @@
       </c>
     </row>
     <row r="449" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A449" t="s">
-        <v>1089</v>
+      <c r="A449">
+        <v>680031225</v>
       </c>
       <c r="B449" t="s">
         <v>55</v>
@@ -26118,25 +26115,25 @@
         <v>1057</v>
       </c>
       <c r="E449" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F449" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G449" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="H449" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="J449" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K449">
         <v>75</v>
       </c>
       <c r="L449">
-        <v>16.5</v>
+        <v>7.95</v>
       </c>
       <c r="M449">
         <v>0</v>
@@ -26147,10 +26144,10 @@
     </row>
     <row r="450" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B450" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C450" t="s">
         <v>978</v>
@@ -26165,22 +26162,22 @@
         <v>1066</v>
       </c>
       <c r="G450" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="H450" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J450">
-        <v>2025</v>
+        <v>1064</v>
+      </c>
+      <c r="J450" t="s">
+        <v>98</v>
       </c>
       <c r="K450">
         <v>75</v>
       </c>
       <c r="L450">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="M450">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="P450" s="19">
         <v>46155</v>
@@ -26188,7 +26185,7 @@
     </row>
     <row r="451" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B451" t="s">
         <v>66</v>
@@ -26197,31 +26194,31 @@
         <v>978</v>
       </c>
       <c r="D451" t="s">
-        <v>1014</v>
+        <v>1057</v>
       </c>
       <c r="E451" t="s">
         <v>57</v>
       </c>
       <c r="F451" t="s">
-        <v>1033</v>
+        <v>1066</v>
       </c>
       <c r="G451" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="H451" t="s">
-        <v>1017</v>
-      </c>
-      <c r="J451" t="s">
-        <v>98</v>
+        <v>1093</v>
+      </c>
+      <c r="J451">
+        <v>2025</v>
       </c>
       <c r="K451">
         <v>75</v>
       </c>
       <c r="L451">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="M451">
-        <v>539</v>
+        <v>37</v>
       </c>
       <c r="P451" s="19">
         <v>46155</v>
@@ -26229,7 +26226,7 @@
     </row>
     <row r="452" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B452" t="s">
         <v>66</v>
@@ -26247,22 +26244,22 @@
         <v>1033</v>
       </c>
       <c r="G452" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="H452" t="s">
-        <v>1037</v>
-      </c>
-      <c r="J452">
-        <v>2025</v>
+        <v>1017</v>
+      </c>
+      <c r="J452" t="s">
+        <v>98</v>
       </c>
       <c r="K452">
         <v>75</v>
       </c>
       <c r="L452">
-        <v>6.95</v>
+        <v>6.6</v>
       </c>
       <c r="M452">
-        <v>264</v>
+        <v>539</v>
       </c>
       <c r="P452" s="19">
         <v>46155</v>
@@ -26270,7 +26267,7 @@
     </row>
     <row r="453" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B453" t="s">
         <v>66</v>
@@ -26285,22 +26282,25 @@
         <v>57</v>
       </c>
       <c r="F453" t="s">
-        <v>1099</v>
+        <v>1033</v>
       </c>
       <c r="G453" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H453" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J453" t="s">
-        <v>98</v>
+        <v>1037</v>
+      </c>
+      <c r="J453">
+        <v>2025</v>
       </c>
       <c r="K453">
         <v>75</v>
       </c>
       <c r="L453">
-        <v>7.1</v>
+        <v>6.95</v>
+      </c>
+      <c r="M453">
+        <v>264</v>
       </c>
       <c r="P453" s="19">
         <v>46155</v>
@@ -26308,7 +26308,7 @@
     </row>
     <row r="454" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B454" t="s">
         <v>66</v>
@@ -26323,104 +26323,101 @@
         <v>57</v>
       </c>
       <c r="F454" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G454" t="s">
         <v>1100</v>
       </c>
       <c r="H454" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="J454" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="K454">
         <v>75</v>
       </c>
       <c r="L454">
-        <v>8.1999999999999993</v>
+        <v>7.1</v>
       </c>
       <c r="P454" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="455" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A455">
-        <v>53800623</v>
+      <c r="A455" t="s">
+        <v>1102</v>
       </c>
       <c r="B455" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C455" t="s">
         <v>978</v>
       </c>
       <c r="D455" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E455" t="s">
         <v>57</v>
       </c>
       <c r="F455" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G455" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="H455" t="s">
-        <v>1064</v>
+        <v>1104</v>
       </c>
       <c r="J455" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="K455">
         <v>75</v>
       </c>
       <c r="L455">
-        <v>11</v>
-      </c>
-      <c r="M455">
-        <v>0</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="P455" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="456" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>1107</v>
+      <c r="A456">
+        <v>53800623</v>
       </c>
       <c r="B456" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C456" t="s">
         <v>978</v>
       </c>
       <c r="D456" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E456" t="s">
         <v>57</v>
       </c>
       <c r="F456" t="s">
-        <v>980</v>
+        <v>1105</v>
       </c>
       <c r="G456" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="H456" t="s">
-        <v>982</v>
+        <v>1064</v>
       </c>
       <c r="J456" t="s">
-        <v>564</v>
+        <v>61</v>
       </c>
       <c r="K456">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L456">
-        <v>16.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="M456">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P456" s="19">
         <v>46155</v>
@@ -26428,7 +26425,7 @@
     </row>
     <row r="457" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B457" t="s">
         <v>66</v>
@@ -26446,22 +26443,22 @@
         <v>980</v>
       </c>
       <c r="G457" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="H457" t="s">
-        <v>985</v>
-      </c>
-      <c r="J457">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J457" t="s">
+        <v>564</v>
       </c>
       <c r="K457">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L457">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M457">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P457" s="19">
         <v>46155</v>
@@ -26469,7 +26466,7 @@
     </row>
     <row r="458" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B458" t="s">
         <v>66</v>
@@ -26478,75 +26475,72 @@
         <v>978</v>
       </c>
       <c r="D458" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E458" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F458" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="G458" t="s">
-        <v>988</v>
+        <v>1110</v>
       </c>
       <c r="H458" t="s">
-        <v>989</v>
-      </c>
-      <c r="J458" t="s">
-        <v>564</v>
+        <v>985</v>
+      </c>
+      <c r="J458">
+        <v>2025</v>
       </c>
       <c r="K458">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L458">
-        <v>4.8</v>
+        <v>25.5</v>
       </c>
       <c r="M458">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="P458" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="459" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A459">
-        <v>71501125</v>
+      <c r="A459" t="s">
+        <v>1111</v>
       </c>
       <c r="B459" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C459" t="s">
         <v>978</v>
       </c>
       <c r="D459" t="s">
-        <v>979</v>
+        <v>1014</v>
       </c>
       <c r="E459" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F459" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="G459" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="H459" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I459" t="s">
-        <v>69</v>
-      </c>
-      <c r="J459">
-        <v>2025</v>
+        <v>989</v>
+      </c>
+      <c r="J459" t="s">
+        <v>564</v>
       </c>
       <c r="K459">
         <v>75</v>
       </c>
       <c r="L459">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="M459">
-        <v>324</v>
+        <v>152</v>
       </c>
       <c r="P459" s="19">
         <v>46155</v>
@@ -26554,7 +26548,7 @@
     </row>
     <row r="460" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A460">
-        <v>71500125</v>
+        <v>71501125</v>
       </c>
       <c r="B460" t="s">
         <v>55</v>
@@ -26566,17 +26560,20 @@
         <v>979</v>
       </c>
       <c r="E460" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F460" t="s">
         <v>980</v>
       </c>
       <c r="G460" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="H460" t="s">
         <v>1113</v>
       </c>
+      <c r="I460" t="s">
+        <v>69</v>
+      </c>
       <c r="J460">
         <v>2025</v>
       </c>
@@ -26584,7 +26581,7 @@
         <v>75</v>
       </c>
       <c r="L460">
-        <v>4.3499999999999996</v>
+        <v>6.2</v>
       </c>
       <c r="M460">
         <v>324</v>
@@ -26595,7 +26592,7 @@
     </row>
     <row r="461" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A461">
-        <v>71500225</v>
+        <v>71500125</v>
       </c>
       <c r="B461" t="s">
         <v>55</v>
@@ -26613,7 +26610,7 @@
         <v>980</v>
       </c>
       <c r="G461" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="H461" t="s">
         <v>1113</v>
@@ -26636,7 +26633,7 @@
     </row>
     <row r="462" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A462">
-        <v>71500325</v>
+        <v>71500225</v>
       </c>
       <c r="B462" t="s">
         <v>55</v>
@@ -26651,10 +26648,10 @@
         <v>63</v>
       </c>
       <c r="F462" t="s">
-        <v>1051</v>
+        <v>980</v>
       </c>
       <c r="G462" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="H462" t="s">
         <v>1113</v>
@@ -26677,7 +26674,7 @@
     </row>
     <row r="463" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>71500425</v>
+        <v>71500325</v>
       </c>
       <c r="B463" t="s">
         <v>55</v>
@@ -26689,13 +26686,13 @@
         <v>979</v>
       </c>
       <c r="E463" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F463" t="s">
-        <v>980</v>
+        <v>1051</v>
       </c>
       <c r="G463" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="H463" t="s">
         <v>1113</v>
@@ -26718,7 +26715,7 @@
     </row>
     <row r="464" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A464">
-        <v>71500525</v>
+        <v>71500425</v>
       </c>
       <c r="B464" t="s">
         <v>55</v>
@@ -26733,10 +26730,10 @@
         <v>57</v>
       </c>
       <c r="F464" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G464" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H464" t="s">
         <v>1113</v>
@@ -26759,7 +26756,7 @@
     </row>
     <row r="465" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A465">
-        <v>71500625</v>
+        <v>71500525</v>
       </c>
       <c r="B465" t="s">
         <v>55</v>
@@ -26771,13 +26768,13 @@
         <v>979</v>
       </c>
       <c r="E465" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F465" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G465" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="H465" t="s">
         <v>1113</v>
@@ -26789,7 +26786,7 @@
         <v>75</v>
       </c>
       <c r="L465">
-        <v>9.1999999999999993</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="M465">
         <v>324</v>
@@ -26800,7 +26797,7 @@
     </row>
     <row r="466" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A466">
-        <v>71500725</v>
+        <v>71500625</v>
       </c>
       <c r="B466" t="s">
         <v>55</v>
@@ -26815,7 +26812,7 @@
         <v>63</v>
       </c>
       <c r="F466" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G466" t="s">
         <v>1120</v>
@@ -26830,7 +26827,7 @@
         <v>75</v>
       </c>
       <c r="L466">
-        <v>8.5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="M466">
         <v>324</v>
@@ -26841,7 +26838,7 @@
     </row>
     <row r="467" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A467">
-        <v>71500825</v>
+        <v>71500725</v>
       </c>
       <c r="B467" t="s">
         <v>55</v>
@@ -26856,7 +26853,7 @@
         <v>63</v>
       </c>
       <c r="F467" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G467" t="s">
         <v>1120</v>
@@ -26864,9 +26861,6 @@
       <c r="H467" t="s">
         <v>1113</v>
       </c>
-      <c r="I467" t="s">
-        <v>69</v>
-      </c>
       <c r="J467">
         <v>2025</v>
       </c>
@@ -26885,7 +26879,7 @@
     </row>
     <row r="468" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A468">
-        <v>71500925</v>
+        <v>71500825</v>
       </c>
       <c r="B468" t="s">
         <v>55</v>
@@ -26897,10 +26891,10 @@
         <v>979</v>
       </c>
       <c r="E468" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F468" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G468" t="s">
         <v>1120</v>
@@ -26909,7 +26903,7 @@
         <v>1113</v>
       </c>
       <c r="I468" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J468">
         <v>2025</v>
@@ -26918,7 +26912,7 @@
         <v>75</v>
       </c>
       <c r="L468">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="M468">
         <v>324</v>
@@ -26929,7 +26923,7 @@
     </row>
     <row r="469" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A469">
-        <v>71501025</v>
+        <v>71500925</v>
       </c>
       <c r="B469" t="s">
         <v>55</v>
@@ -26944,7 +26938,7 @@
         <v>57</v>
       </c>
       <c r="F469" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G469" t="s">
         <v>1120</v>
@@ -26962,7 +26956,7 @@
         <v>75</v>
       </c>
       <c r="L469">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="M469">
         <v>324</v>
@@ -26973,10 +26967,10 @@
     </row>
     <row r="470" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A470">
-        <v>16000125</v>
+        <v>71501025</v>
       </c>
       <c r="B470" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C470" t="s">
         <v>978</v>
@@ -26985,16 +26979,19 @@
         <v>979</v>
       </c>
       <c r="E470" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F470" t="s">
-        <v>980</v>
+        <v>1124</v>
       </c>
       <c r="G470" t="s">
-        <v>981</v>
+        <v>1120</v>
       </c>
       <c r="H470" t="s">
-        <v>982</v>
+        <v>1113</v>
+      </c>
+      <c r="I470" t="s">
+        <v>175</v>
       </c>
       <c r="J470">
         <v>2025</v>
@@ -27003,7 +27000,7 @@
         <v>75</v>
       </c>
       <c r="L470">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="M470">
         <v>324</v>
@@ -27013,8 +27010,8 @@
       </c>
     </row>
     <row r="471" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A471" t="s">
-        <v>1125</v>
+      <c r="A471">
+        <v>16000125</v>
       </c>
       <c r="B471" t="s">
         <v>66</v>
@@ -27032,22 +27029,22 @@
         <v>980</v>
       </c>
       <c r="G471" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H471" t="s">
-        <v>985</v>
-      </c>
-      <c r="J471" t="s">
-        <v>217</v>
+        <v>982</v>
+      </c>
+      <c r="J471">
+        <v>2025</v>
       </c>
       <c r="K471">
         <v>75</v>
       </c>
       <c r="L471">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M471">
-        <v>99</v>
+        <v>324</v>
       </c>
       <c r="P471" s="19">
         <v>46155</v>
@@ -27055,7 +27052,7 @@
     </row>
     <row r="472" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B472" t="s">
         <v>66</v>
@@ -27073,22 +27070,22 @@
         <v>980</v>
       </c>
       <c r="G472" t="s">
-        <v>1127</v>
+        <v>984</v>
       </c>
       <c r="H472" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J472" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="K472">
         <v>75</v>
       </c>
       <c r="L472">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="M472">
-        <v>915</v>
+        <v>99</v>
       </c>
       <c r="P472" s="19">
         <v>46155</v>
@@ -27096,7 +27093,7 @@
     </row>
     <row r="473" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B473" t="s">
         <v>66</v>
@@ -27114,22 +27111,22 @@
         <v>980</v>
       </c>
       <c r="G473" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="H473" t="s">
-        <v>985</v>
-      </c>
-      <c r="J473">
-        <v>2025</v>
+        <v>292</v>
+      </c>
+      <c r="J473" t="s">
+        <v>286</v>
       </c>
       <c r="K473">
         <v>75</v>
       </c>
       <c r="L473">
-        <v>4.8499999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="M473">
-        <v>219</v>
+        <v>915</v>
       </c>
       <c r="P473" s="19">
         <v>46155</v>
@@ -27137,7 +27134,7 @@
     </row>
     <row r="474" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B474" t="s">
         <v>66</v>
@@ -27152,25 +27149,25 @@
         <v>63</v>
       </c>
       <c r="F474" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G474" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="H474" t="s">
-        <v>1001</v>
-      </c>
-      <c r="J474" t="s">
-        <v>339</v>
+        <v>985</v>
+      </c>
+      <c r="J474">
+        <v>2025</v>
       </c>
       <c r="K474">
         <v>75</v>
       </c>
       <c r="L474">
-        <v>5.7</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M474">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="P474" s="19">
         <v>46155</v>
@@ -27178,7 +27175,7 @@
     </row>
     <row r="475" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B475" t="s">
         <v>66</v>
@@ -27193,25 +27190,25 @@
         <v>63</v>
       </c>
       <c r="F475" t="s">
-        <v>980</v>
+        <v>58</v>
       </c>
       <c r="G475" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="H475" t="s">
-        <v>992</v>
+        <v>1001</v>
       </c>
       <c r="J475" t="s">
-        <v>98</v>
+        <v>339</v>
       </c>
       <c r="K475">
         <v>75</v>
       </c>
       <c r="L475">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="M475">
-        <v>219</v>
+        <v>96</v>
       </c>
       <c r="P475" s="19">
         <v>46155</v>
@@ -27219,7 +27216,7 @@
     </row>
     <row r="476" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B476" t="s">
         <v>66</v>
@@ -27237,22 +27234,22 @@
         <v>980</v>
       </c>
       <c r="G476" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="H476" t="s">
-        <v>1136</v>
+        <v>992</v>
       </c>
       <c r="J476" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K476">
         <v>75</v>
       </c>
       <c r="L476">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="M476">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="P476" s="19">
         <v>46155</v>
@@ -27260,7 +27257,7 @@
     </row>
     <row r="477" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="B477" t="s">
         <v>66</v>
@@ -27278,25 +27275,22 @@
         <v>980</v>
       </c>
       <c r="G477" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="H477" t="s">
-        <v>982</v>
-      </c>
-      <c r="I477" t="s">
-        <v>296</v>
+        <v>1136</v>
       </c>
       <c r="J477" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K477">
         <v>75</v>
       </c>
       <c r="L477">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M477">
-        <v>303</v>
+        <v>27</v>
       </c>
       <c r="P477" s="19">
         <v>46155</v>
@@ -27304,7 +27298,7 @@
     </row>
     <row r="478" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B478" t="s">
         <v>66</v>
@@ -27322,13 +27316,13 @@
         <v>980</v>
       </c>
       <c r="G478" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="H478" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="I478" t="s">
-        <v>1012</v>
+        <v>296</v>
       </c>
       <c r="J478" t="s">
         <v>61</v>
@@ -27337,10 +27331,10 @@
         <v>75</v>
       </c>
       <c r="L478">
-        <v>6.05</v>
+        <v>5.4</v>
       </c>
       <c r="M478">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="P478" s="19">
         <v>46155</v>
@@ -27348,7 +27342,7 @@
     </row>
     <row r="479" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="B479" t="s">
         <v>66</v>
@@ -27363,25 +27357,28 @@
         <v>63</v>
       </c>
       <c r="F479" t="s">
-        <v>58</v>
+        <v>980</v>
       </c>
       <c r="G479" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="H479" t="s">
-        <v>1017</v>
+        <v>992</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1012</v>
       </c>
       <c r="J479" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K479">
         <v>75</v>
       </c>
       <c r="L479">
-        <v>6.35</v>
+        <v>6.05</v>
       </c>
       <c r="M479">
-        <v>340</v>
+        <v>187</v>
       </c>
       <c r="P479" s="19">
         <v>46155</v>
@@ -27389,7 +27386,7 @@
     </row>
     <row r="480" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B480" t="s">
         <v>66</v>
@@ -27398,19 +27395,19 @@
         <v>978</v>
       </c>
       <c r="D480" t="s">
-        <v>1014</v>
+        <v>979</v>
       </c>
       <c r="E480" t="s">
         <v>63</v>
       </c>
       <c r="F480" t="s">
-        <v>1144</v>
+        <v>58</v>
       </c>
       <c r="G480" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="H480" t="s">
-        <v>1101</v>
+        <v>1017</v>
       </c>
       <c r="J480" t="s">
         <v>217</v>
@@ -27419,10 +27416,10 @@
         <v>75</v>
       </c>
       <c r="L480">
-        <v>6.15</v>
+        <v>6.35</v>
       </c>
       <c r="M480">
-        <v>46</v>
+        <v>340</v>
       </c>
       <c r="P480" s="19">
         <v>46155</v>
@@ -27430,7 +27427,7 @@
     </row>
     <row r="481" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="B481" t="s">
         <v>66</v>
@@ -27445,25 +27442,25 @@
         <v>63</v>
       </c>
       <c r="F481" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="G481" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="H481" t="s">
-        <v>1149</v>
+        <v>1101</v>
       </c>
       <c r="J481" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K481">
         <v>75</v>
       </c>
       <c r="L481">
-        <v>9.8000000000000007</v>
+        <v>6.15</v>
       </c>
       <c r="M481">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="P481" s="19">
         <v>46155</v>
@@ -27471,7 +27468,7 @@
     </row>
     <row r="482" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="B482" t="s">
         <v>66</v>
@@ -27489,22 +27486,22 @@
         <v>1147</v>
       </c>
       <c r="G482" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="H482" t="s">
         <v>1149</v>
       </c>
       <c r="J482" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K482">
         <v>75</v>
       </c>
       <c r="L482">
-        <v>18.2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="M482">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="P482" s="19">
         <v>46155</v>
@@ -27512,37 +27509,40 @@
     </row>
     <row r="483" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="B483" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C483" t="s">
         <v>978</v>
       </c>
       <c r="D483" t="s">
-        <v>1057</v>
+        <v>1014</v>
       </c>
       <c r="E483" t="s">
         <v>63</v>
       </c>
       <c r="F483" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="G483" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="H483" t="s">
-        <v>1085</v>
+        <v>1149</v>
       </c>
       <c r="J483" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K483">
         <v>75</v>
       </c>
       <c r="L483">
-        <v>11.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="M483">
+        <v>36</v>
       </c>
       <c r="P483" s="19">
         <v>46155</v>
@@ -27550,7 +27550,7 @@
     </row>
     <row r="484" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B484" t="s">
         <v>55</v>
@@ -27565,25 +27565,22 @@
         <v>63</v>
       </c>
       <c r="F484" t="s">
-        <v>1058</v>
+        <v>1153</v>
       </c>
       <c r="G484" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="H484" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J484" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K484">
         <v>75</v>
       </c>
       <c r="L484">
-        <v>12.5</v>
-      </c>
-      <c r="M484">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="P484" s="19">
         <v>46155</v>
@@ -27591,7 +27588,7 @@
     </row>
     <row r="485" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B485" t="s">
         <v>55</v>
@@ -27606,22 +27603,22 @@
         <v>63</v>
       </c>
       <c r="F485" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="G485" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H485" t="s">
         <v>1064</v>
       </c>
       <c r="J485" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="K485">
         <v>75</v>
       </c>
       <c r="L485">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="M485">
         <v>0</v>
@@ -27632,7 +27629,7 @@
     </row>
     <row r="486" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B486" t="s">
         <v>55</v>
@@ -27650,19 +27647,19 @@
         <v>1078</v>
       </c>
       <c r="G486" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H486" t="s">
-        <v>1161</v>
-      </c>
-      <c r="J486">
-        <v>2014</v>
+        <v>1064</v>
+      </c>
+      <c r="J486" t="s">
+        <v>209</v>
       </c>
       <c r="K486">
         <v>75</v>
       </c>
       <c r="L486">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M486">
         <v>0</v>
@@ -27673,10 +27670,10 @@
     </row>
     <row r="487" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="B487" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C487" t="s">
         <v>978</v>
@@ -27688,25 +27685,25 @@
         <v>63</v>
       </c>
       <c r="F487" t="s">
-        <v>1066</v>
+        <v>1078</v>
       </c>
       <c r="G487" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="H487" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J487" t="s">
-        <v>61</v>
+        <v>1161</v>
+      </c>
+      <c r="J487">
+        <v>2014</v>
       </c>
       <c r="K487">
         <v>75</v>
       </c>
       <c r="L487">
-        <v>4.8499999999999996</v>
+        <v>17</v>
       </c>
       <c r="M487">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="P487" s="19">
         <v>46155</v>
@@ -27714,10 +27711,10 @@
     </row>
     <row r="488" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B488" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C488" t="s">
         <v>978</v>
@@ -27732,13 +27729,10 @@
         <v>1066</v>
       </c>
       <c r="G488" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="H488" t="s">
-        <v>1064</v>
-      </c>
-      <c r="I488" t="s">
-        <v>69</v>
+        <v>1093</v>
       </c>
       <c r="J488" t="s">
         <v>61</v>
@@ -27747,18 +27741,18 @@
         <v>75</v>
       </c>
       <c r="L488">
-        <v>9.9</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="M488">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="P488" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="489" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A489">
-        <v>27701324</v>
+      <c r="A489" t="s">
+        <v>1164</v>
       </c>
       <c r="B489" t="s">
         <v>55</v>
@@ -27776,19 +27770,22 @@
         <v>1066</v>
       </c>
       <c r="G489" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H489" t="s">
-        <v>1055</v>
-      </c>
-      <c r="J489">
-        <v>2024</v>
+        <v>1064</v>
+      </c>
+      <c r="I489" t="s">
+        <v>69</v>
+      </c>
+      <c r="J489" t="s">
+        <v>61</v>
       </c>
       <c r="K489">
         <v>75</v>
       </c>
       <c r="L489">
-        <v>9.9499999999999993</v>
+        <v>9.9</v>
       </c>
       <c r="M489">
         <v>0</v>
@@ -27798,8 +27795,8 @@
       </c>
     </row>
     <row r="490" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A490" t="s">
-        <v>1167</v>
+      <c r="A490">
+        <v>27701324</v>
       </c>
       <c r="B490" t="s">
         <v>55</v>
@@ -27817,22 +27814,19 @@
         <v>1066</v>
       </c>
       <c r="G490" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H490" t="s">
         <v>1055</v>
       </c>
-      <c r="I490" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J490" t="s">
-        <v>98</v>
+      <c r="J490">
+        <v>2024</v>
       </c>
       <c r="K490">
         <v>75</v>
       </c>
       <c r="L490">
-        <v>11.5</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="M490">
         <v>0</v>
@@ -27843,31 +27837,31 @@
     </row>
     <row r="491" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B491" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C491" t="s">
         <v>978</v>
       </c>
       <c r="D491" t="s">
-        <v>979</v>
+        <v>1057</v>
       </c>
       <c r="E491" t="s">
         <v>63</v>
       </c>
       <c r="F491" t="s">
-        <v>1170</v>
+        <v>1066</v>
       </c>
       <c r="G491" t="s">
-        <v>818</v>
+        <v>1168</v>
       </c>
       <c r="H491" t="s">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="I491" t="s">
-        <v>777</v>
+        <v>1056</v>
       </c>
       <c r="J491" t="s">
         <v>98</v>
@@ -27876,10 +27870,10 @@
         <v>75</v>
       </c>
       <c r="L491">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="M491">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="P491" s="19">
         <v>46155</v>
@@ -27887,7 +27881,7 @@
     </row>
     <row r="492" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B492" t="s">
         <v>66</v>
@@ -27902,28 +27896,28 @@
         <v>63</v>
       </c>
       <c r="F492" t="s">
-        <v>980</v>
+        <v>1170</v>
       </c>
       <c r="G492" t="s">
-        <v>1172</v>
+        <v>818</v>
       </c>
       <c r="H492" t="s">
-        <v>1173</v>
+        <v>1021</v>
       </c>
       <c r="I492" t="s">
-        <v>69</v>
+        <v>777</v>
       </c>
       <c r="J492" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="K492">
         <v>75</v>
       </c>
       <c r="L492">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="M492">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="P492" s="19">
         <v>46155</v>
@@ -27931,10 +27925,10 @@
     </row>
     <row r="493" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="B493" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C493" t="s">
         <v>978</v>
@@ -27946,25 +27940,28 @@
         <v>63</v>
       </c>
       <c r="F493" t="s">
-        <v>1175</v>
+        <v>980</v>
       </c>
       <c r="G493" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H493" t="s">
-        <v>1177</v>
+        <v>1173</v>
+      </c>
+      <c r="I493" t="s">
+        <v>69</v>
       </c>
       <c r="J493" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K493">
         <v>75</v>
       </c>
       <c r="L493">
-        <v>9.4</v>
+        <v>16.3</v>
       </c>
       <c r="M493">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P493" s="19">
         <v>46155</v>
@@ -27972,7 +27969,7 @@
     </row>
     <row r="494" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="B494" t="s">
         <v>55</v>
@@ -27990,19 +27987,22 @@
         <v>1175</v>
       </c>
       <c r="G494" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="H494" t="s">
         <v>1177</v>
       </c>
       <c r="J494" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K494">
         <v>75</v>
       </c>
       <c r="L494">
-        <v>31</v>
+        <v>9.4</v>
+      </c>
+      <c r="M494">
+        <v>0</v>
       </c>
       <c r="P494" s="19">
         <v>46155</v>
@@ -28010,10 +28010,10 @@
     </row>
     <row r="495" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B495" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C495" t="s">
         <v>978</v>
@@ -28025,28 +28025,22 @@
         <v>63</v>
       </c>
       <c r="F495" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="G495" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H495" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I495" t="s">
-        <v>69</v>
+        <v>1177</v>
       </c>
       <c r="J495" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="K495">
         <v>75</v>
       </c>
       <c r="L495">
-        <v>7.6</v>
-      </c>
-      <c r="M495">
-        <v>270.39999999999998</v>
+        <v>31</v>
       </c>
       <c r="P495" s="19">
         <v>46155</v>
@@ -28054,10 +28048,10 @@
     </row>
     <row r="496" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B496" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C496" t="s">
         <v>978</v>
@@ -28069,25 +28063,28 @@
         <v>63</v>
       </c>
       <c r="F496" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G496" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="H496" t="s">
-        <v>1049</v>
+        <v>1183</v>
+      </c>
+      <c r="I496" t="s">
+        <v>69</v>
       </c>
       <c r="J496" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K496">
         <v>75</v>
       </c>
       <c r="L496">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="M496">
-        <v>18</v>
+        <v>270.39999999999998</v>
       </c>
       <c r="P496" s="19">
         <v>46155</v>
@@ -28095,7 +28092,7 @@
     </row>
     <row r="497" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="B497" t="s">
         <v>55</v>
@@ -28113,22 +28110,22 @@
         <v>1185</v>
       </c>
       <c r="G497" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="H497" t="s">
         <v>1049</v>
       </c>
       <c r="J497" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="K497">
         <v>75</v>
       </c>
       <c r="L497">
-        <v>8.25</v>
+        <v>6.9</v>
       </c>
       <c r="M497">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="P497" s="19">
         <v>46155</v>
@@ -28136,10 +28133,10 @@
     </row>
     <row r="498" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="B498" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C498" t="s">
         <v>978</v>
@@ -28151,25 +28148,25 @@
         <v>63</v>
       </c>
       <c r="F498" t="s">
-        <v>1193</v>
+        <v>1185</v>
       </c>
       <c r="G498" t="s">
-        <v>165</v>
+        <v>1188</v>
       </c>
       <c r="H498" t="s">
-        <v>1194</v>
-      </c>
-      <c r="I498" t="s">
-        <v>777</v>
+        <v>1049</v>
       </c>
       <c r="J498" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="K498">
         <v>75</v>
       </c>
       <c r="L498">
-        <v>17.8</v>
+        <v>8.25</v>
+      </c>
+      <c r="M498">
+        <v>6</v>
       </c>
       <c r="P498" s="19">
         <v>46155</v>
@@ -28177,7 +28174,7 @@
     </row>
     <row r="499" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="B499" t="s">
         <v>66</v>
@@ -28192,25 +28189,25 @@
         <v>63</v>
       </c>
       <c r="F499" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="G499" t="s">
-        <v>1196</v>
+        <v>165</v>
       </c>
       <c r="H499" t="s">
-        <v>1191</v>
+        <v>1194</v>
+      </c>
+      <c r="I499" t="s">
+        <v>777</v>
       </c>
       <c r="J499" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="K499">
         <v>75</v>
       </c>
       <c r="L499">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="M499">
-        <v>53</v>
+        <v>17.8</v>
       </c>
       <c r="P499" s="19">
         <v>46155</v>
@@ -28218,7 +28215,7 @@
     </row>
     <row r="500" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B500" t="s">
         <v>66</v>
@@ -28233,25 +28230,25 @@
         <v>63</v>
       </c>
       <c r="F500" t="s">
-        <v>1198</v>
+        <v>1185</v>
       </c>
       <c r="G500" t="s">
-        <v>165</v>
+        <v>1196</v>
       </c>
       <c r="H500" t="s">
-        <v>1199</v>
-      </c>
-      <c r="I500" t="s">
-        <v>777</v>
+        <v>1191</v>
       </c>
       <c r="J500" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="K500">
         <v>75</v>
       </c>
       <c r="L500">
-        <v>22.3</v>
+        <v>19.899999999999999</v>
+      </c>
+      <c r="M500">
+        <v>53</v>
       </c>
       <c r="P500" s="19">
         <v>46155</v>
@@ -28259,7 +28256,7 @@
     </row>
     <row r="501" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="B501" t="s">
         <v>66</v>
@@ -28274,28 +28271,25 @@
         <v>63</v>
       </c>
       <c r="F501" t="s">
-        <v>1122</v>
+        <v>1198</v>
       </c>
       <c r="G501" t="s">
-        <v>1201</v>
+        <v>165</v>
       </c>
       <c r="H501" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
       <c r="I501" t="s">
-        <v>175</v>
+        <v>777</v>
       </c>
       <c r="J501" t="s">
-        <v>286</v>
+        <v>87</v>
       </c>
       <c r="K501">
         <v>75</v>
       </c>
       <c r="L501">
-        <v>6.5</v>
-      </c>
-      <c r="M501">
-        <v>42</v>
+        <v>22.3</v>
       </c>
       <c r="P501" s="19">
         <v>46155</v>
@@ -28303,10 +28297,10 @@
     </row>
     <row r="502" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="B502" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C502" t="s">
         <v>978</v>
@@ -28321,30 +28315,33 @@
         <v>1122</v>
       </c>
       <c r="G502" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="H502" t="s">
-        <v>1204</v>
+        <v>1006</v>
+      </c>
+      <c r="I502" t="s">
+        <v>175</v>
       </c>
       <c r="J502" t="s">
-        <v>98</v>
+        <v>286</v>
       </c>
       <c r="K502">
         <v>75</v>
       </c>
       <c r="L502">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="M502">
-        <v>171</v>
+        <v>42</v>
       </c>
       <c r="P502" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="503" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A503">
-        <v>16003124</v>
+      <c r="A503" t="s">
+        <v>1202</v>
       </c>
       <c r="B503" t="s">
         <v>55</v>
@@ -28356,19 +28353,19 @@
         <v>979</v>
       </c>
       <c r="E503" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F503" t="s">
         <v>1122</v>
       </c>
       <c r="G503" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="H503" t="s">
         <v>1204</v>
       </c>
       <c r="J503" t="s">
-        <v>286</v>
+        <v>98</v>
       </c>
       <c r="K503">
         <v>75</v>
@@ -28384,11 +28381,11 @@
       </c>
     </row>
     <row r="504" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A504" t="s">
-        <v>1206</v>
+      <c r="A504">
+        <v>16003124</v>
       </c>
       <c r="B504" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C504" t="s">
         <v>978</v>
@@ -28397,31 +28394,28 @@
         <v>979</v>
       </c>
       <c r="E504" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F504" t="s">
         <v>1122</v>
       </c>
       <c r="G504" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="H504" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I504" t="s">
-        <v>175</v>
+        <v>1204</v>
       </c>
       <c r="J504" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="K504">
         <v>75</v>
       </c>
       <c r="L504">
-        <v>8.61</v>
+        <v>8.4</v>
       </c>
       <c r="M504">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="P504" s="19">
         <v>46155</v>
@@ -28429,10 +28423,10 @@
     </row>
     <row r="505" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B505" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C505" t="s">
         <v>978</v>
@@ -28447,25 +28441,25 @@
         <v>1122</v>
       </c>
       <c r="G505" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="H505" t="s">
-        <v>1204</v>
+        <v>1006</v>
       </c>
       <c r="I505" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="J505" t="s">
-        <v>61</v>
+        <v>217</v>
       </c>
       <c r="K505">
         <v>75</v>
       </c>
       <c r="L505">
-        <v>9.6</v>
+        <v>8.61</v>
       </c>
       <c r="M505">
-        <v>171</v>
+        <v>12</v>
       </c>
       <c r="P505" s="19">
         <v>46155</v>
@@ -28473,10 +28467,10 @@
     </row>
     <row r="506" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B506" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C506" t="s">
         <v>978</v>
@@ -28491,13 +28485,13 @@
         <v>1122</v>
       </c>
       <c r="G506" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="H506" t="s">
-        <v>1006</v>
+        <v>1204</v>
       </c>
       <c r="I506" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J506" t="s">
         <v>61</v>
@@ -28506,7 +28500,7 @@
         <v>75</v>
       </c>
       <c r="L506">
-        <v>13.82</v>
+        <v>9.6</v>
       </c>
       <c r="M506">
         <v>171</v>
@@ -28517,10 +28511,10 @@
     </row>
     <row r="507" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B507" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C507" t="s">
         <v>978</v>
@@ -28535,19 +28529,25 @@
         <v>1122</v>
       </c>
       <c r="G507" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="H507" t="s">
-        <v>1214</v>
+        <v>1006</v>
+      </c>
+      <c r="I507" t="s">
+        <v>175</v>
       </c>
       <c r="J507" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="K507">
         <v>75</v>
       </c>
       <c r="L507">
-        <v>18.3</v>
+        <v>13.82</v>
+      </c>
+      <c r="M507">
+        <v>171</v>
       </c>
       <c r="P507" s="19">
         <v>46155</v>
@@ -28555,10 +28555,10 @@
     </row>
     <row r="508" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B508" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C508" t="s">
         <v>978</v>
@@ -28570,28 +28570,22 @@
         <v>63</v>
       </c>
       <c r="F508" t="s">
-        <v>58</v>
+        <v>1122</v>
       </c>
       <c r="G508" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="H508" t="s">
-        <v>1006</v>
-      </c>
-      <c r="I508" t="s">
-        <v>175</v>
+        <v>1214</v>
       </c>
       <c r="J508" t="s">
-        <v>1217</v>
+        <v>87</v>
       </c>
       <c r="K508">
         <v>75</v>
       </c>
       <c r="L508">
-        <v>24.08</v>
-      </c>
-      <c r="M508">
-        <v>12</v>
+        <v>18.3</v>
       </c>
       <c r="P508" s="19">
         <v>46155</v>
@@ -28599,10 +28593,10 @@
     </row>
     <row r="509" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B509" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C509" t="s">
         <v>978</v>
@@ -28614,19 +28608,28 @@
         <v>63</v>
       </c>
       <c r="F509" t="s">
-        <v>1219</v>
+        <v>58</v>
+      </c>
+      <c r="G509" t="s">
+        <v>1216</v>
       </c>
       <c r="H509" t="s">
-        <v>1220</v>
+        <v>1006</v>
+      </c>
+      <c r="I509" t="s">
+        <v>175</v>
       </c>
       <c r="J509" t="s">
-        <v>61</v>
+        <v>1217</v>
       </c>
       <c r="K509">
         <v>75</v>
       </c>
       <c r="L509">
-        <v>31.7</v>
+        <v>24.08</v>
+      </c>
+      <c r="M509">
+        <v>12</v>
       </c>
       <c r="P509" s="19">
         <v>46155</v>
@@ -28634,10 +28637,10 @@
     </row>
     <row r="510" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="B510" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C510" t="s">
         <v>978</v>
@@ -28649,30 +28652,27 @@
         <v>63</v>
       </c>
       <c r="F510" t="s">
-        <v>1121</v>
+        <v>1219</v>
       </c>
       <c r="H510" t="s">
-        <v>982</v>
+        <v>1220</v>
       </c>
       <c r="J510" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K510">
         <v>75</v>
       </c>
       <c r="L510">
-        <v>7.05</v>
-      </c>
-      <c r="M510">
-        <v>30</v>
+        <v>31.7</v>
       </c>
       <c r="P510" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="511" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A511">
-        <v>27100523</v>
+      <c r="A511" t="s">
+        <v>1221</v>
       </c>
       <c r="B511" t="s">
         <v>66</v>
@@ -28687,36 +28687,33 @@
         <v>63</v>
       </c>
       <c r="F511" t="s">
-        <v>1222</v>
-      </c>
-      <c r="G511" t="s">
-        <v>1223</v>
+        <v>1121</v>
       </c>
       <c r="H511" t="s">
-        <v>1224</v>
-      </c>
-      <c r="I511" t="s">
-        <v>777</v>
-      </c>
-      <c r="J511">
-        <v>2023</v>
+        <v>982</v>
+      </c>
+      <c r="J511" t="s">
+        <v>217</v>
       </c>
       <c r="K511">
         <v>75</v>
       </c>
       <c r="L511">
-        <v>17.8</v>
+        <v>7.05</v>
+      </c>
+      <c r="M511">
+        <v>30</v>
       </c>
       <c r="P511" s="19">
-        <v>46178</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="512" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A512" t="s">
-        <v>1225</v>
+      <c r="A512">
+        <v>27100523</v>
       </c>
       <c r="B512" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C512" t="s">
         <v>978</v>
@@ -28728,33 +28725,36 @@
         <v>63</v>
       </c>
       <c r="F512" t="s">
-        <v>58</v>
+        <v>1222</v>
       </c>
       <c r="G512" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="H512" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J512" t="s">
-        <v>1228</v>
+        <v>1224</v>
+      </c>
+      <c r="I512" t="s">
+        <v>777</v>
+      </c>
+      <c r="J512">
+        <v>2023</v>
       </c>
       <c r="K512">
         <v>75</v>
       </c>
       <c r="L512">
-        <v>95</v>
+        <v>17.8</v>
       </c>
       <c r="P512" s="19">
-        <v>46155</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="513" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B513" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C513" t="s">
         <v>978</v>
@@ -28766,33 +28766,33 @@
         <v>63</v>
       </c>
       <c r="F513" t="s">
-        <v>1119</v>
+        <v>58</v>
       </c>
       <c r="G513" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="H513" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="J513" t="s">
-        <v>98</v>
+        <v>1228</v>
       </c>
       <c r="K513">
         <v>75</v>
       </c>
       <c r="L513">
-        <v>7.35</v>
-      </c>
-      <c r="M513">
-        <v>2215</v>
+        <v>95</v>
       </c>
       <c r="P513" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="514" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A514" t="s">
+        <v>1229</v>
+      </c>
       <c r="B514" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C514" t="s">
         <v>978</v>
@@ -28807,19 +28807,19 @@
         <v>1119</v>
       </c>
       <c r="G514" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="H514" t="s">
         <v>1231</v>
       </c>
       <c r="J514" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K514">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L514">
-        <v>15.95</v>
+        <v>7.35</v>
       </c>
       <c r="M514">
         <v>2215</v>
@@ -28829,11 +28829,8 @@
       </c>
     </row>
     <row r="515" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A515" t="s">
-        <v>1233</v>
-      </c>
       <c r="B515" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C515" t="s">
         <v>978</v>
@@ -28848,22 +28845,22 @@
         <v>1119</v>
       </c>
       <c r="G515" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="H515" t="s">
         <v>1231</v>
       </c>
-      <c r="J515">
-        <v>2023</v>
+      <c r="J515" t="s">
+        <v>61</v>
       </c>
       <c r="K515">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L515">
-        <v>8.35</v>
+        <v>15.95</v>
       </c>
       <c r="M515">
-        <v>279</v>
+        <v>2215</v>
       </c>
       <c r="P515" s="19">
         <v>46155</v>
@@ -28871,7 +28868,7 @@
     </row>
     <row r="516" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B516" t="s">
         <v>66</v>
@@ -28889,25 +28886,22 @@
         <v>1119</v>
       </c>
       <c r="G516" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="H516" t="s">
-        <v>1237</v>
-      </c>
-      <c r="I516" t="s">
-        <v>1238</v>
-      </c>
-      <c r="J516" t="s">
-        <v>61</v>
+        <v>1231</v>
+      </c>
+      <c r="J516">
+        <v>2023</v>
       </c>
       <c r="K516">
         <v>75</v>
       </c>
       <c r="L516">
-        <v>13.5</v>
+        <v>8.35</v>
       </c>
       <c r="M516">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="P516" s="19">
         <v>46155</v>
@@ -28915,10 +28909,10 @@
     </row>
     <row r="517" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B517" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C517" t="s">
         <v>978</v>
@@ -28933,19 +28927,25 @@
         <v>1119</v>
       </c>
       <c r="G517" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="H517" t="s">
-        <v>1241</v>
+        <v>1237</v>
+      </c>
+      <c r="I517" t="s">
+        <v>1238</v>
       </c>
       <c r="J517" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="K517">
         <v>75</v>
       </c>
       <c r="L517">
-        <v>14.5</v>
+        <v>13.5</v>
+      </c>
+      <c r="M517">
+        <v>205</v>
       </c>
       <c r="P517" s="19">
         <v>46155</v>
@@ -28953,7 +28953,7 @@
     </row>
     <row r="518" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="B518" t="s">
         <v>55</v>
@@ -28971,10 +28971,10 @@
         <v>1119</v>
       </c>
       <c r="G518" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="H518" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="J518" t="s">
         <v>98</v>
@@ -28983,21 +28983,18 @@
         <v>75</v>
       </c>
       <c r="L518">
-        <v>14.6</v>
-      </c>
-      <c r="M518">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="P518" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="519" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A519">
-        <v>43700124</v>
+      <c r="A519" t="s">
+        <v>1242</v>
       </c>
       <c r="B519" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C519" t="s">
         <v>978</v>
@@ -29009,22 +29006,25 @@
         <v>63</v>
       </c>
       <c r="F519" t="s">
-        <v>1028</v>
+        <v>1119</v>
       </c>
       <c r="G519" t="s">
-        <v>165</v>
+        <v>1243</v>
       </c>
       <c r="H519" t="s">
-        <v>1029</v>
-      </c>
-      <c r="J519">
-        <v>2024</v>
+        <v>1244</v>
+      </c>
+      <c r="J519" t="s">
+        <v>98</v>
       </c>
       <c r="K519">
         <v>75</v>
       </c>
       <c r="L519">
-        <v>37</v>
+        <v>14.6</v>
+      </c>
+      <c r="M519">
+        <v>0</v>
       </c>
       <c r="P519" s="19">
         <v>46155</v>
@@ -29032,10 +29032,10 @@
     </row>
     <row r="520" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A520">
-        <v>43700325</v>
+        <v>43700124</v>
       </c>
       <c r="B520" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C520" t="s">
         <v>978</v>
@@ -29050,19 +29050,19 @@
         <v>1028</v>
       </c>
       <c r="G520" t="s">
-        <v>1245</v>
+        <v>165</v>
       </c>
       <c r="H520" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J520">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K520">
         <v>75</v>
       </c>
       <c r="L520">
-        <v>7.9</v>
+        <v>37</v>
       </c>
       <c r="P520" s="19">
         <v>46155</v>
@@ -29070,7 +29070,7 @@
     </row>
     <row r="521" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A521">
-        <v>43700524</v>
+        <v>43700325</v>
       </c>
       <c r="B521" t="s">
         <v>55</v>
@@ -29088,30 +29088,30 @@
         <v>1028</v>
       </c>
       <c r="G521" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="H521" t="s">
         <v>1031</v>
       </c>
       <c r="J521">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="K521">
         <v>75</v>
       </c>
       <c r="L521">
-        <v>14.5</v>
+        <v>7.9</v>
       </c>
       <c r="P521" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="522" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A522" t="s">
-        <v>1247</v>
+      <c r="A522">
+        <v>43700524</v>
       </c>
       <c r="B522" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C522" t="s">
         <v>978</v>
@@ -29120,28 +29120,25 @@
         <v>979</v>
       </c>
       <c r="E522" t="s">
-        <v>923</v>
+        <v>63</v>
       </c>
       <c r="F522" t="s">
-        <v>980</v>
+        <v>1028</v>
       </c>
       <c r="G522" t="s">
-        <v>981</v>
+        <v>1246</v>
       </c>
       <c r="H522" t="s">
-        <v>982</v>
-      </c>
-      <c r="J522" t="s">
-        <v>98</v>
+        <v>1031</v>
+      </c>
+      <c r="J522">
+        <v>2024</v>
       </c>
       <c r="K522">
         <v>75</v>
       </c>
       <c r="L522">
-        <v>3.8</v>
-      </c>
-      <c r="M522">
-        <v>324</v>
+        <v>14.5</v>
       </c>
       <c r="P522" s="19">
         <v>46155</v>
@@ -29149,7 +29146,7 @@
     </row>
     <row r="523" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B523" t="s">
         <v>66</v>
@@ -29167,22 +29164,22 @@
         <v>980</v>
       </c>
       <c r="G523" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="H523" t="s">
-        <v>985</v>
-      </c>
-      <c r="J523">
-        <v>2025</v>
+        <v>982</v>
+      </c>
+      <c r="J523" t="s">
+        <v>98</v>
       </c>
       <c r="K523">
         <v>75</v>
       </c>
       <c r="L523">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="M523">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="P523" s="19">
         <v>46155</v>
@@ -29190,7 +29187,7 @@
     </row>
     <row r="524" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B524" t="s">
         <v>66</v>
@@ -29208,10 +29205,10 @@
         <v>980</v>
       </c>
       <c r="G524" t="s">
-        <v>1250</v>
+        <v>984</v>
       </c>
       <c r="H524" t="s">
-        <v>292</v>
+        <v>985</v>
       </c>
       <c r="J524">
         <v>2025</v>
@@ -29220,10 +29217,10 @@
         <v>75</v>
       </c>
       <c r="L524">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M524">
-        <v>969</v>
+        <v>368</v>
       </c>
       <c r="P524" s="19">
         <v>46155</v>
@@ -29231,10 +29228,10 @@
     </row>
     <row r="525" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B525" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C525" t="s">
         <v>978</v>
@@ -29249,22 +29246,22 @@
         <v>980</v>
       </c>
       <c r="G525" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="H525" t="s">
-        <v>1224</v>
-      </c>
-      <c r="J525" t="s">
-        <v>339</v>
+        <v>292</v>
+      </c>
+      <c r="J525">
+        <v>2025</v>
       </c>
       <c r="K525">
         <v>75</v>
       </c>
       <c r="L525">
-        <v>7.2</v>
+        <v>3.99</v>
       </c>
       <c r="M525">
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="P525" s="19">
         <v>46155</v>
@@ -29272,10 +29269,10 @@
     </row>
     <row r="526" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B526" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C526" t="s">
         <v>978</v>
@@ -29290,22 +29287,22 @@
         <v>980</v>
       </c>
       <c r="G526" t="s">
-        <v>1108</v>
+        <v>1252</v>
       </c>
       <c r="H526" t="s">
-        <v>982</v>
+        <v>1224</v>
       </c>
       <c r="J526" t="s">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="K526">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="L526">
-        <v>16.399999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="M526">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="P526" s="19">
         <v>46155</v>
@@ -29313,7 +29310,7 @@
     </row>
     <row r="527" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B527" t="s">
         <v>66</v>
@@ -29331,22 +29328,22 @@
         <v>980</v>
       </c>
       <c r="G527" t="s">
-        <v>1255</v>
+        <v>1108</v>
       </c>
       <c r="H527" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="J527" t="s">
-        <v>98</v>
+        <v>564</v>
       </c>
       <c r="K527">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L527">
-        <v>25.5</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="M527">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="P527" s="19">
         <v>46155</v>
@@ -29354,40 +29351,40 @@
     </row>
     <row r="528" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B528" t="s">
         <v>66</v>
       </c>
       <c r="C528" t="s">
-        <v>1257</v>
+        <v>978</v>
       </c>
       <c r="D528" t="s">
-        <v>1258</v>
+        <v>979</v>
       </c>
       <c r="E528" t="s">
-        <v>57</v>
+        <v>923</v>
       </c>
       <c r="F528" t="s">
-        <v>1259</v>
+        <v>980</v>
       </c>
       <c r="G528" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="H528" t="s">
-        <v>1261</v>
+        <v>985</v>
       </c>
       <c r="J528" t="s">
-        <v>339</v>
+        <v>98</v>
       </c>
       <c r="K528">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="L528">
-        <v>5</v>
+        <v>25.5</v>
       </c>
       <c r="M528">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="P528" s="19">
         <v>46155</v>
@@ -29395,7 +29392,7 @@
     </row>
     <row r="529" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="B529" t="s">
         <v>66</v>
@@ -29410,13 +29407,13 @@
         <v>57</v>
       </c>
       <c r="F529" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G529" t="s">
-        <v>113</v>
+        <v>1260</v>
       </c>
       <c r="H529" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="J529" t="s">
         <v>339</v>
@@ -29425,21 +29422,18 @@
         <v>75</v>
       </c>
       <c r="L529">
-        <v>9.1</v>
+        <v>5</v>
       </c>
       <c r="M529">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="P529" s="19">
         <v>46155</v>
       </c>
-      <c r="R529" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="530" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A530">
-        <v>24000925</v>
+      <c r="A530" t="s">
+        <v>1262</v>
       </c>
       <c r="B530" t="s">
         <v>66</v>
@@ -29451,36 +29445,39 @@
         <v>1258</v>
       </c>
       <c r="E530" t="s">
-        <v>923</v>
+        <v>57</v>
       </c>
       <c r="F530" t="s">
-        <v>1259</v>
+        <v>1263</v>
       </c>
       <c r="G530" t="s">
-        <v>1265</v>
+        <v>113</v>
       </c>
       <c r="H530" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J530">
-        <v>2025</v>
+        <v>1264</v>
+      </c>
+      <c r="J530" t="s">
+        <v>339</v>
       </c>
       <c r="K530">
         <v>75</v>
       </c>
       <c r="L530">
-        <v>5.55</v>
+        <v>9.1</v>
       </c>
       <c r="M530">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="P530" s="19">
         <v>46155</v>
       </c>
+      <c r="R530" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="531" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A531" t="s">
-        <v>1266</v>
+      <c r="A531">
+        <v>24000925</v>
       </c>
       <c r="B531" t="s">
         <v>66</v>
@@ -29492,28 +29489,28 @@
         <v>1258</v>
       </c>
       <c r="E531" t="s">
-        <v>63</v>
+        <v>923</v>
       </c>
       <c r="F531" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="G531" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="H531" t="s">
-        <v>1269</v>
-      </c>
-      <c r="J531" t="s">
-        <v>87</v>
+        <v>1261</v>
+      </c>
+      <c r="J531">
+        <v>2025</v>
       </c>
       <c r="K531">
         <v>75</v>
       </c>
       <c r="L531">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="M531">
-        <v>3</v>
+        <v>549</v>
       </c>
       <c r="P531" s="19">
         <v>46155</v>
@@ -29521,7 +29518,7 @@
     </row>
     <row r="532" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="B532" t="s">
         <v>66</v>
@@ -29536,33 +29533,33 @@
         <v>63</v>
       </c>
       <c r="F532" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G532" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H532" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="J532" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="K532">
         <v>75</v>
       </c>
       <c r="L532">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="M532">
-        <v>288</v>
+        <v>3</v>
       </c>
       <c r="P532" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="533" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A533">
-        <v>24001825</v>
+      <c r="A533" t="s">
+        <v>1270</v>
       </c>
       <c r="B533" t="s">
         <v>66</v>
@@ -29577,33 +29574,33 @@
         <v>63</v>
       </c>
       <c r="F533" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="G533" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="H533" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J533">
-        <v>2025</v>
+        <v>1273</v>
+      </c>
+      <c r="J533" t="s">
+        <v>98</v>
       </c>
       <c r="K533">
         <v>75</v>
       </c>
       <c r="L533">
-        <v>6.75</v>
+        <v>5.4</v>
       </c>
       <c r="M533">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="P533" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="534" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A534" t="s">
-        <v>1275</v>
+      <c r="A534">
+        <v>24001825</v>
       </c>
       <c r="B534" t="s">
         <v>66</v>
@@ -29618,22 +29615,25 @@
         <v>63</v>
       </c>
       <c r="F534" t="s">
-        <v>1276</v>
+        <v>1263</v>
+      </c>
+      <c r="G534" t="s">
+        <v>1274</v>
       </c>
       <c r="H534" t="s">
-        <v>1277</v>
-      </c>
-      <c r="J534" t="s">
-        <v>98</v>
+        <v>1261</v>
+      </c>
+      <c r="J534">
+        <v>2025</v>
       </c>
       <c r="K534">
         <v>75</v>
       </c>
       <c r="L534">
-        <v>6.85</v>
+        <v>6.75</v>
       </c>
       <c r="M534">
-        <v>666</v>
+        <v>54</v>
       </c>
       <c r="P534" s="19">
         <v>46155</v>
@@ -29641,7 +29641,7 @@
     </row>
     <row r="535" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="B535" t="s">
         <v>66</v>
@@ -29656,28 +29656,22 @@
         <v>63</v>
       </c>
       <c r="F535" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G535" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="H535" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I535" t="s">
-        <v>69</v>
+        <v>1277</v>
       </c>
       <c r="J535" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="K535">
         <v>75</v>
       </c>
       <c r="L535">
-        <v>8.25</v>
+        <v>6.85</v>
       </c>
       <c r="M535">
-        <v>318</v>
+        <v>666</v>
       </c>
       <c r="P535" s="19">
         <v>46155</v>
@@ -29685,7 +29679,7 @@
     </row>
     <row r="536" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B536" t="s">
         <v>66</v>
@@ -29694,28 +29688,34 @@
         <v>1257</v>
       </c>
       <c r="D536" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E536" t="s">
         <v>63</v>
       </c>
       <c r="F536" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G536" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="H536" t="s">
-        <v>1286</v>
+        <v>1281</v>
+      </c>
+      <c r="I536" t="s">
+        <v>69</v>
       </c>
       <c r="J536" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="K536">
         <v>75</v>
       </c>
       <c r="L536">
-        <v>4.95</v>
+        <v>8.25</v>
+      </c>
+      <c r="M536">
+        <v>318</v>
       </c>
       <c r="P536" s="19">
         <v>46155</v>
@@ -29723,7 +29723,7 @@
     </row>
     <row r="537" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="B537" t="s">
         <v>66</v>
@@ -29741,22 +29741,19 @@
         <v>1284</v>
       </c>
       <c r="G537" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H537" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="J537" t="s">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="K537">
         <v>75</v>
       </c>
       <c r="L537">
-        <v>6.1</v>
-      </c>
-      <c r="M537">
-        <v>133</v>
+        <v>4.95</v>
       </c>
       <c r="P537" s="19">
         <v>46155</v>
@@ -29764,7 +29761,7 @@
     </row>
     <row r="538" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B538" t="s">
         <v>66</v>
@@ -29787,8 +29784,8 @@
       <c r="H538" t="s">
         <v>1289</v>
       </c>
-      <c r="J538">
-        <v>2024</v>
+      <c r="J538" t="s">
+        <v>87</v>
       </c>
       <c r="K538">
         <v>75</v>
@@ -29796,16 +29793,19 @@
       <c r="L538">
         <v>6.1</v>
       </c>
+      <c r="M538">
+        <v>133</v>
+      </c>
       <c r="P538" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="539" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B539" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C539" t="s">
         <v>1257</v>
@@ -29820,30 +29820,27 @@
         <v>1284</v>
       </c>
       <c r="G539" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H539" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J539" t="s">
-        <v>109</v>
+        <v>1289</v>
+      </c>
+      <c r="J539">
+        <v>2024</v>
       </c>
       <c r="K539">
         <v>75</v>
       </c>
       <c r="L539">
-        <v>13.2</v>
-      </c>
-      <c r="M539">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P539" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="540" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="B540" t="s">
         <v>55</v>
@@ -29861,19 +29858,19 @@
         <v>1284</v>
       </c>
       <c r="G540" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="H540" t="s">
         <v>1293</v>
       </c>
       <c r="J540" t="s">
-        <v>1228</v>
+        <v>109</v>
       </c>
       <c r="K540">
         <v>75</v>
       </c>
       <c r="L540">
-        <v>16.350000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="M540">
         <v>0</v>
@@ -29884,7 +29881,7 @@
     </row>
     <row r="541" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="B541" t="s">
         <v>55</v>
@@ -29899,22 +29896,22 @@
         <v>63</v>
       </c>
       <c r="F541" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G541" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="H541" t="s">
         <v>1293</v>
       </c>
       <c r="J541" t="s">
-        <v>61</v>
+        <v>1228</v>
       </c>
       <c r="K541">
         <v>75</v>
       </c>
       <c r="L541">
-        <v>5.0999999999999996</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M541">
         <v>0</v>
@@ -29924,49 +29921,49 @@
       </c>
     </row>
     <row r="542" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A542">
-        <v>10702526</v>
+      <c r="A542" t="s">
+        <v>1296</v>
       </c>
       <c r="B542" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C542" t="s">
         <v>1257</v>
       </c>
       <c r="D542" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E542" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F542" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G542" t="s">
-        <v>726</v>
+        <v>1298</v>
       </c>
       <c r="H542" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J542">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J542" t="s">
+        <v>61</v>
       </c>
       <c r="K542">
         <v>75</v>
       </c>
       <c r="L542">
-        <v>4.6500000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M542">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P542" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="543" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A543" t="s">
-        <v>1301</v>
+      <c r="A543">
+        <v>10702526</v>
       </c>
       <c r="B543" t="s">
         <v>66</v>
@@ -29975,31 +29972,31 @@
         <v>1257</v>
       </c>
       <c r="D543" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E543" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F543" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G543" t="s">
-        <v>1304</v>
+        <v>726</v>
       </c>
       <c r="H543" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J543" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J543">
+        <v>2026</v>
       </c>
       <c r="K543">
         <v>75</v>
       </c>
       <c r="L543">
-        <v>8.5</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M543">
-        <v>6</v>
+        <v>1327</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -30007,7 +30004,7 @@
     </row>
     <row r="544" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B544" t="s">
         <v>66</v>
@@ -30025,7 +30022,7 @@
         <v>1303</v>
       </c>
       <c r="G544" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="H544" t="s">
         <v>1305</v>
@@ -30037,10 +30034,10 @@
         <v>75</v>
       </c>
       <c r="L544">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M544">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
@@ -30048,7 +30045,7 @@
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -30066,7 +30063,7 @@
         <v>1303</v>
       </c>
       <c r="G545" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="H545" t="s">
         <v>1305</v>
@@ -30081,7 +30078,7 @@
         <v>8.6</v>
       </c>
       <c r="M545">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -30089,7 +30086,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -30107,13 +30104,13 @@
         <v>1303</v>
       </c>
       <c r="G546" t="s">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="H546" t="s">
         <v>1305</v>
       </c>
       <c r="J546" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K546">
         <v>75</v>
@@ -30122,7 +30119,7 @@
         <v>8.6</v>
       </c>
       <c r="M546">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -30130,7 +30127,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -30148,7 +30145,7 @@
         <v>1303</v>
       </c>
       <c r="G547" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="H547" t="s">
         <v>1305</v>
@@ -30163,7 +30160,7 @@
         <v>8.6</v>
       </c>
       <c r="M547">
-        <v>662</v>
+        <v>18</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -30171,7 +30168,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30189,22 +30186,22 @@
         <v>1303</v>
       </c>
       <c r="G548" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="H548" t="s">
         <v>1305</v>
       </c>
       <c r="J548" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K548">
         <v>75</v>
       </c>
       <c r="L548">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M548">
-        <v>64</v>
+        <v>662</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30212,7 +30209,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30230,22 +30227,22 @@
         <v>1303</v>
       </c>
       <c r="G549" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="H549" t="s">
         <v>1305</v>
       </c>
-      <c r="J549">
-        <v>2021</v>
+      <c r="J549" t="s">
+        <v>127</v>
       </c>
       <c r="K549">
         <v>75</v>
       </c>
       <c r="L549">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M549">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30253,7 +30250,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30271,13 +30268,13 @@
         <v>1303</v>
       </c>
       <c r="G550" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="H550" t="s">
         <v>1305</v>
       </c>
-      <c r="J550" t="s">
-        <v>109</v>
+      <c r="J550">
+        <v>2021</v>
       </c>
       <c r="K550">
         <v>75</v>
@@ -30286,7 +30283,7 @@
         <v>13</v>
       </c>
       <c r="M550">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30294,7 +30291,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30312,7 +30309,7 @@
         <v>1303</v>
       </c>
       <c r="G551" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="H551" t="s">
         <v>1305</v>
@@ -30324,7 +30321,7 @@
         <v>75</v>
       </c>
       <c r="L551">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M551">
         <v>36</v>
@@ -30335,7 +30332,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30347,28 +30344,28 @@
         <v>1302</v>
       </c>
       <c r="E552" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F552" t="s">
         <v>1303</v>
       </c>
       <c r="G552" t="s">
-        <v>1042</v>
+        <v>1320</v>
       </c>
       <c r="H552" t="s">
         <v>1305</v>
       </c>
       <c r="J552" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K552">
         <v>75</v>
       </c>
       <c r="L552">
-        <v>8.0500000000000007</v>
+        <v>16</v>
       </c>
       <c r="M552">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30376,40 +30373,40 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
       </c>
       <c r="C553" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D553" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E553" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F553" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G553" t="s">
-        <v>1325</v>
+        <v>1042</v>
       </c>
       <c r="H553" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J553" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K553">
         <v>75</v>
       </c>
       <c r="L553">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="M553">
-        <v>4411</v>
+        <v>55</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30417,7 +30414,7 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
@@ -30425,17 +30422,20 @@
       <c r="C554" t="s">
         <v>1323</v>
       </c>
+      <c r="D554" t="s">
+        <v>1258</v>
+      </c>
       <c r="E554" t="s">
         <v>1323</v>
       </c>
       <c r="F554" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G554" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="H554" t="s">
-        <v>1001</v>
+        <v>1261</v>
       </c>
       <c r="J554" t="s">
         <v>564</v>
@@ -30446,13 +30446,16 @@
       <c r="L554">
         <v>6.2</v>
       </c>
+      <c r="M554">
+        <v>4411</v>
+      </c>
       <c r="P554" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
@@ -30467,10 +30470,10 @@
         <v>58</v>
       </c>
       <c r="G555" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="H555" t="s">
-        <v>1330</v>
+        <v>1001</v>
       </c>
       <c r="J555" t="s">
         <v>564</v>
@@ -30479,7 +30482,7 @@
         <v>75</v>
       </c>
       <c r="L555">
-        <v>8.99</v>
+        <v>6.2</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30487,7 +30490,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30499,25 +30502,22 @@
         <v>1323</v>
       </c>
       <c r="F556" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G556" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="H556" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="J556" t="s">
         <v>564</v>
       </c>
       <c r="K556">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L556">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M556">
-        <v>5</v>
+        <v>8.99</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30525,7 +30525,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30540,22 +30540,22 @@
         <v>1332</v>
       </c>
       <c r="G557" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="H557" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="J557" t="s">
         <v>564</v>
       </c>
       <c r="K557">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L557">
-        <v>16.45</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M557">
-        <v>6532</v>
+        <v>5</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30563,7 +30563,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30578,10 +30578,10 @@
         <v>1332</v>
       </c>
       <c r="G558" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="H558" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="J558" t="s">
         <v>564</v>
@@ -30590,10 +30590,10 @@
         <v>75</v>
       </c>
       <c r="L558">
-        <v>23.5</v>
+        <v>16.45</v>
       </c>
       <c r="M558">
-        <v>418</v>
+        <v>6532</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30601,10 +30601,10 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B559" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C559" t="s">
         <v>1323</v>
@@ -30616,10 +30616,10 @@
         <v>1332</v>
       </c>
       <c r="G559" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="H559" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="J559" t="s">
         <v>564</v>
@@ -30628,7 +30628,10 @@
         <v>75</v>
       </c>
       <c r="L559">
-        <v>23.9</v>
+        <v>23.5</v>
+      </c>
+      <c r="M559">
+        <v>418</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30636,10 +30639,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="B560" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C560" t="s">
         <v>1323</v>
@@ -30651,10 +30654,10 @@
         <v>1332</v>
       </c>
       <c r="G560" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="H560" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="J560" t="s">
         <v>564</v>
@@ -30663,10 +30666,7 @@
         <v>75</v>
       </c>
       <c r="L560">
-        <v>25.8</v>
-      </c>
-      <c r="M560">
-        <v>995</v>
+        <v>23.9</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30674,7 +30674,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30689,10 +30689,10 @@
         <v>1332</v>
       </c>
       <c r="G561" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="H561" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J561" t="s">
         <v>564</v>
@@ -30701,10 +30701,10 @@
         <v>75</v>
       </c>
       <c r="L561">
-        <v>27.5</v>
+        <v>25.8</v>
       </c>
       <c r="M561">
-        <v>31</v>
+        <v>995</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30712,7 +30712,7 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="B562" t="s">
         <v>66</v>
@@ -30727,10 +30727,10 @@
         <v>1332</v>
       </c>
       <c r="G562" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="H562" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J562" t="s">
         <v>564</v>
@@ -30739,10 +30739,10 @@
         <v>75</v>
       </c>
       <c r="L562">
-        <v>29</v>
+        <v>27.5</v>
       </c>
       <c r="M562">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30750,7 +30750,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30765,10 +30765,10 @@
         <v>1332</v>
       </c>
       <c r="G563" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="H563" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J563" t="s">
         <v>564</v>
@@ -30777,10 +30777,10 @@
         <v>75</v>
       </c>
       <c r="L563">
-        <v>29.35</v>
+        <v>29</v>
       </c>
       <c r="M563">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30788,10 +30788,10 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="B564" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C564" t="s">
         <v>1323</v>
@@ -30803,7 +30803,7 @@
         <v>1332</v>
       </c>
       <c r="G564" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="H564" t="s">
         <v>1349</v>
@@ -30812,10 +30812,10 @@
         <v>564</v>
       </c>
       <c r="K564">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L564">
-        <v>63</v>
+        <v>29.35</v>
       </c>
       <c r="M564">
         <v>60</v>
@@ -30826,7 +30826,7 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B565" t="s">
         <v>55</v>
@@ -30841,7 +30841,7 @@
         <v>1332</v>
       </c>
       <c r="G565" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="H565" t="s">
         <v>1349</v>
@@ -30850,10 +30850,10 @@
         <v>564</v>
       </c>
       <c r="K565">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L565">
-        <v>34.5</v>
+        <v>63</v>
       </c>
       <c r="M565">
         <v>60</v>
@@ -30864,7 +30864,7 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="B566" t="s">
         <v>55</v>
@@ -30879,7 +30879,7 @@
         <v>1332</v>
       </c>
       <c r="G566" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="H566" t="s">
         <v>1349</v>
@@ -30891,7 +30891,7 @@
         <v>75</v>
       </c>
       <c r="L566">
-        <v>30.4</v>
+        <v>34.5</v>
       </c>
       <c r="M566">
         <v>60</v>
@@ -30902,10 +30902,10 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="B567" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C567" t="s">
         <v>1323</v>
@@ -30917,10 +30917,10 @@
         <v>1332</v>
       </c>
       <c r="G567" t="s">
-        <v>919</v>
+        <v>1362</v>
       </c>
       <c r="H567" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J567" t="s">
         <v>564</v>
@@ -30929,10 +30929,10 @@
         <v>75</v>
       </c>
       <c r="L567">
-        <v>29.8</v>
+        <v>30.4</v>
       </c>
       <c r="M567">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P567" s="19">
         <v>46155</v>
@@ -30940,7 +30940,7 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B568" t="s">
         <v>66</v>
@@ -30955,10 +30955,10 @@
         <v>1332</v>
       </c>
       <c r="G568" t="s">
-        <v>1368</v>
+        <v>919</v>
       </c>
       <c r="H568" t="s">
-        <v>1369</v>
+        <v>1352</v>
       </c>
       <c r="J568" t="s">
         <v>564</v>
@@ -30967,10 +30967,10 @@
         <v>75</v>
       </c>
       <c r="L568">
-        <v>31</v>
+        <v>29.8</v>
       </c>
       <c r="M568">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="P568" s="19">
         <v>46155</v>
@@ -30978,7 +30978,7 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="B569" t="s">
         <v>66</v>
@@ -30993,10 +30993,10 @@
         <v>1332</v>
       </c>
       <c r="G569" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="H569" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="J569" t="s">
         <v>564</v>
@@ -31005,10 +31005,10 @@
         <v>75</v>
       </c>
       <c r="L569">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M569">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="P569" s="19">
         <v>46155</v>
@@ -31016,7 +31016,7 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
       <c r="B570" t="s">
         <v>66</v>
@@ -31031,10 +31031,10 @@
         <v>1332</v>
       </c>
       <c r="G570" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
       <c r="H570" t="s">
-        <v>1349</v>
+        <v>1372</v>
       </c>
       <c r="J570" t="s">
         <v>564</v>
@@ -31043,10 +31043,10 @@
         <v>75</v>
       </c>
       <c r="L570">
-        <v>34.200000000000003</v>
+        <v>33</v>
       </c>
       <c r="M570">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P570" s="19">
         <v>46155</v>
@@ -31054,7 +31054,7 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B571" t="s">
         <v>66</v>
@@ -31069,10 +31069,10 @@
         <v>1332</v>
       </c>
       <c r="G571" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="H571" t="s">
-        <v>1377</v>
+        <v>1349</v>
       </c>
       <c r="J571" t="s">
         <v>564</v>
@@ -31081,10 +31081,10 @@
         <v>75</v>
       </c>
       <c r="L571">
-        <v>39</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="M571">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="P571" s="19">
         <v>46155</v>
@@ -31092,10 +31092,10 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
       <c r="B572" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C572" t="s">
         <v>1323</v>
@@ -31107,10 +31107,10 @@
         <v>1332</v>
       </c>
       <c r="G572" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
       <c r="H572" t="s">
-        <v>1334</v>
+        <v>1377</v>
       </c>
       <c r="J572" t="s">
         <v>564</v>
@@ -31119,7 +31119,7 @@
         <v>75</v>
       </c>
       <c r="L572">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M572">
         <v>0</v>
@@ -31130,10 +31130,10 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B573" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C573" t="s">
         <v>1323</v>
@@ -31145,10 +31145,10 @@
         <v>1332</v>
       </c>
       <c r="G573" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="H573" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J573" t="s">
         <v>564</v>
@@ -31157,10 +31157,10 @@
         <v>75</v>
       </c>
       <c r="L573">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M573">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P573" s="19">
         <v>46155</v>
@@ -31168,7 +31168,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B574" t="s">
         <v>66</v>
@@ -31183,7 +31183,7 @@
         <v>1332</v>
       </c>
       <c r="G574" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="H574" t="s">
         <v>1352</v>
@@ -31195,10 +31195,10 @@
         <v>75</v>
       </c>
       <c r="L574">
-        <v>47.3</v>
+        <v>41</v>
       </c>
       <c r="M574">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="P574" s="19">
         <v>46155</v>
@@ -31206,7 +31206,7 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B575" t="s">
         <v>66</v>
@@ -31221,10 +31221,10 @@
         <v>1332</v>
       </c>
       <c r="G575" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="H575" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J575" t="s">
         <v>564</v>
@@ -31233,10 +31233,10 @@
         <v>75</v>
       </c>
       <c r="L575">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M575">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P575" s="19">
         <v>46155</v>
@@ -31244,7 +31244,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -31259,10 +31259,10 @@
         <v>1332</v>
       </c>
       <c r="G576" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="H576" t="s">
-        <v>1389</v>
+        <v>1386</v>
       </c>
       <c r="J576" t="s">
         <v>564</v>
@@ -31282,7 +31282,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1390</v>
+        <v>1387</v>
       </c>
       <c r="B577" t="s">
         <v>66</v>
@@ -31297,22 +31297,22 @@
         <v>1332</v>
       </c>
       <c r="G577" t="s">
-        <v>1391</v>
+        <v>1388</v>
       </c>
       <c r="H577" t="s">
-        <v>1334</v>
+        <v>1389</v>
       </c>
       <c r="J577" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K577">
         <v>75</v>
       </c>
       <c r="L577">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M577">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P577" s="19">
         <v>46155</v>
@@ -31320,7 +31320,7 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B578" t="s">
         <v>66</v>
@@ -31335,22 +31335,22 @@
         <v>1332</v>
       </c>
       <c r="G578" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="H578" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J578">
-        <v>2017</v>
+        <v>1334</v>
+      </c>
+      <c r="J578" t="s">
+        <v>167</v>
       </c>
       <c r="K578">
         <v>75</v>
       </c>
       <c r="L578">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="M578">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="P578" s="19">
         <v>46155</v>
@@ -31358,7 +31358,7 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B579" t="s">
         <v>66</v>
@@ -31366,9 +31366,6 @@
       <c r="C579" t="s">
         <v>1323</v>
       </c>
-      <c r="D579" t="s">
-        <v>1008</v>
-      </c>
       <c r="E579" t="s">
         <v>1323</v>
       </c>
@@ -31376,22 +31373,22 @@
         <v>1332</v>
       </c>
       <c r="G579" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="H579" t="s">
-        <v>1352</v>
-      </c>
-      <c r="J579" t="s">
-        <v>564</v>
+        <v>1372</v>
+      </c>
+      <c r="J579">
+        <v>2017</v>
       </c>
       <c r="K579">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L579">
-        <v>65.900000000000006</v>
+        <v>199</v>
       </c>
       <c r="M579">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="P579" s="19">
         <v>46155</v>
@@ -31399,7 +31396,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B580" t="s">
         <v>66</v>
@@ -31417,7 +31414,7 @@
         <v>1332</v>
       </c>
       <c r="G580" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="H580" t="s">
         <v>1352</v>
@@ -31429,10 +31426,10 @@
         <v>150</v>
       </c>
       <c r="L580">
-        <v>54.5</v>
+        <v>65.900000000000006</v>
       </c>
       <c r="M580">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="P580" s="19">
         <v>46155</v>
@@ -31440,10 +31437,10 @@
     </row>
     <row r="581" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B581" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C581" t="s">
         <v>1323</v>
@@ -31458,10 +31455,10 @@
         <v>1332</v>
       </c>
       <c r="G581" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="H581" t="s">
-        <v>1334</v>
+        <v>1352</v>
       </c>
       <c r="J581" t="s">
         <v>564</v>
@@ -31470,10 +31467,10 @@
         <v>150</v>
       </c>
       <c r="L581">
-        <v>59</v>
+        <v>54.5</v>
       </c>
       <c r="M581">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="P581" s="19">
         <v>46155</v>
@@ -31481,7 +31478,7 @@
     </row>
     <row r="582" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="B582" t="s">
         <v>55</v>
@@ -31499,7 +31496,7 @@
         <v>1332</v>
       </c>
       <c r="G582" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="H582" t="s">
         <v>1334</v>
@@ -31508,10 +31505,10 @@
         <v>564</v>
       </c>
       <c r="K582">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L582">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M582">
         <v>5</v>
@@ -31522,7 +31519,7 @@
     </row>
     <row r="583" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="B583" t="s">
         <v>55</v>
@@ -31540,7 +31537,7 @@
         <v>1332</v>
       </c>
       <c r="G583" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="H583" t="s">
         <v>1334</v>
@@ -31549,10 +31546,10 @@
         <v>564</v>
       </c>
       <c r="K583">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="L583">
-        <v>359</v>
+        <v>170</v>
       </c>
       <c r="M583">
         <v>5</v>
@@ -31563,37 +31560,40 @@
     </row>
     <row r="584" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="B584" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C584" t="s">
-        <v>1405</v>
+        <v>1323</v>
+      </c>
+      <c r="D584" t="s">
+        <v>1008</v>
       </c>
       <c r="E584" t="s">
-        <v>1405</v>
+        <v>1323</v>
       </c>
       <c r="F584" t="s">
-        <v>1406</v>
+        <v>1332</v>
       </c>
       <c r="G584" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H584" t="s">
-        <v>1408</v>
+        <v>1334</v>
       </c>
       <c r="J584" t="s">
-        <v>1409</v>
+        <v>564</v>
       </c>
       <c r="K584">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L584">
-        <v>13.8</v>
+        <v>359</v>
       </c>
       <c r="M584">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P584" s="19">
         <v>46155</v>
@@ -31601,7 +31601,7 @@
     </row>
     <row r="585" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="B585" t="s">
         <v>66</v>
@@ -31616,7 +31616,7 @@
         <v>1406</v>
       </c>
       <c r="G585" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="H585" t="s">
         <v>1408</v>
@@ -31628,7 +31628,7 @@
         <v>70</v>
       </c>
       <c r="L585">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="M585">
         <v>6</v>
@@ -31639,7 +31639,7 @@
     </row>
     <row r="586" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B586" t="s">
         <v>66</v>
@@ -31654,19 +31654,22 @@
         <v>1406</v>
       </c>
       <c r="G586" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="H586" t="s">
-        <v>1414</v>
+        <v>1408</v>
       </c>
       <c r="J586" t="s">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="K586">
         <v>70</v>
       </c>
       <c r="L586">
-        <v>14.85</v>
+        <v>14.3</v>
+      </c>
+      <c r="M586">
+        <v>6</v>
       </c>
       <c r="P586" s="19">
         <v>46155</v>
@@ -31674,7 +31677,7 @@
     </row>
     <row r="587" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B587" t="s">
         <v>66</v>
@@ -31689,19 +31692,19 @@
         <v>1406</v>
       </c>
       <c r="G587" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="H587" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="J587" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="K587">
         <v>70</v>
       </c>
       <c r="L587">
-        <v>38.1</v>
+        <v>14.85</v>
       </c>
       <c r="P587" s="19">
         <v>46155</v>
@@ -31709,7 +31712,7 @@
     </row>
     <row r="588" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B588" t="s">
         <v>66</v>
@@ -31724,19 +31727,19 @@
         <v>1406</v>
       </c>
       <c r="G588" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="H588" t="s">
         <v>1418</v>
       </c>
       <c r="J588" t="s">
-        <v>1422</v>
+        <v>1419</v>
       </c>
       <c r="K588">
         <v>70</v>
       </c>
       <c r="L588">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="P588" s="19">
         <v>46155</v>
@@ -31744,7 +31747,7 @@
     </row>
     <row r="589" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
-        <v>1423</v>
+        <v>1420</v>
       </c>
       <c r="B589" t="s">
         <v>66</v>
@@ -31759,19 +31762,19 @@
         <v>1406</v>
       </c>
       <c r="G589" t="s">
-        <v>1424</v>
+        <v>1421</v>
       </c>
       <c r="H589" t="s">
-        <v>1425</v>
+        <v>1418</v>
       </c>
       <c r="J589" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="K589">
         <v>70</v>
       </c>
       <c r="L589">
-        <v>16.149999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="P589" s="19">
         <v>46155</v>
@@ -31779,7 +31782,7 @@
     </row>
     <row r="590" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B590" t="s">
         <v>66</v>
@@ -31787,9 +31790,6 @@
       <c r="C590" t="s">
         <v>1405</v>
       </c>
-      <c r="D590" t="s">
-        <v>1008</v>
-      </c>
       <c r="E590" t="s">
         <v>1405</v>
       </c>
@@ -31797,19 +31797,19 @@
         <v>1406</v>
       </c>
       <c r="G590" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="H590" t="s">
         <v>1425</v>
       </c>
       <c r="J590" t="s">
-        <v>1429</v>
+        <v>1426</v>
       </c>
       <c r="K590">
-        <v>300</v>
+        <v>70</v>
       </c>
       <c r="L590">
-        <v>112</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="P590" s="19">
         <v>46155</v>
@@ -31817,7 +31817,7 @@
     </row>
     <row r="591" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
-        <v>1430</v>
+        <v>1427</v>
       </c>
       <c r="B591" t="s">
         <v>66</v>
@@ -31825,26 +31825,29 @@
       <c r="C591" t="s">
         <v>1405</v>
       </c>
+      <c r="D591" t="s">
+        <v>1008</v>
+      </c>
       <c r="E591" t="s">
         <v>1405</v>
       </c>
       <c r="F591" t="s">
-        <v>1431</v>
+        <v>1406</v>
+      </c>
+      <c r="G591" t="s">
+        <v>1428</v>
       </c>
       <c r="H591" t="s">
-        <v>1432</v>
+        <v>1425</v>
       </c>
       <c r="J591" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="K591">
-        <v>70</v>
+        <v>300</v>
       </c>
       <c r="L591">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="M591">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="P591" s="19">
         <v>46155</v>
@@ -31852,10 +31855,10 @@
     </row>
     <row r="592" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="B592" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C592" t="s">
         <v>1405</v>
@@ -31866,17 +31869,17 @@
       <c r="F592" t="s">
         <v>1431</v>
       </c>
-      <c r="G592" t="s">
-        <v>1435</v>
-      </c>
       <c r="H592" t="s">
-        <v>1436</v>
+        <v>1432</v>
+      </c>
+      <c r="J592" t="s">
+        <v>1433</v>
       </c>
       <c r="K592">
         <v>70</v>
       </c>
       <c r="L592">
-        <v>17.95</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="M592">
         <v>45</v>
@@ -31887,10 +31890,10 @@
     </row>
     <row r="593" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
-        <v>1437</v>
+        <v>1434</v>
       </c>
       <c r="B593" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C593" t="s">
         <v>1405</v>
@@ -31902,22 +31905,19 @@
         <v>1431</v>
       </c>
       <c r="G593" t="s">
-        <v>1438</v>
+        <v>1435</v>
       </c>
       <c r="H593" t="s">
-        <v>1006</v>
-      </c>
-      <c r="J593" t="s">
-        <v>1439</v>
+        <v>1436</v>
       </c>
       <c r="K593">
         <v>70</v>
       </c>
       <c r="L593">
-        <v>20.399999999999999</v>
+        <v>17.95</v>
       </c>
       <c r="M593">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="P593" s="19">
         <v>46155</v>
@@ -31925,7 +31925,7 @@
     </row>
     <row r="594" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
-        <v>1440</v>
+        <v>1437</v>
       </c>
       <c r="B594" t="s">
         <v>66</v>
@@ -31940,22 +31940,22 @@
         <v>1431</v>
       </c>
       <c r="G594" t="s">
-        <v>1441</v>
+        <v>1438</v>
       </c>
       <c r="H594" t="s">
-        <v>1442</v>
+        <v>1006</v>
       </c>
       <c r="J594" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="K594">
         <v>70</v>
       </c>
       <c r="L594">
-        <v>40</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="M594">
-        <v>155</v>
+        <v>68</v>
       </c>
       <c r="P594" s="19">
         <v>46155</v>
@@ -31963,7 +31963,7 @@
     </row>
     <row r="595" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="B595" t="s">
         <v>66</v>
@@ -31975,25 +31975,25 @@
         <v>1405</v>
       </c>
       <c r="F595" t="s">
-        <v>1445</v>
+        <v>1431</v>
       </c>
       <c r="G595" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="H595" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="J595" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="K595">
         <v>70</v>
       </c>
       <c r="L595">
-        <v>36.5</v>
+        <v>40</v>
       </c>
       <c r="M595">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="P595" s="19">
         <v>46155</v>
@@ -32001,7 +32001,7 @@
     </row>
     <row r="596" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="B596" t="s">
         <v>66</v>
@@ -32016,7 +32016,7 @@
         <v>1445</v>
       </c>
       <c r="G596" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="H596" t="s">
         <v>1447</v>
@@ -32028,21 +32028,21 @@
         <v>70</v>
       </c>
       <c r="L596">
-        <v>40.5</v>
+        <v>36.5</v>
       </c>
       <c r="M596">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P596" s="19">
-        <v>46175</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="597" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
-        <v>2365</v>
+        <v>1449</v>
       </c>
       <c r="B597" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C597" t="s">
         <v>1405</v>
@@ -32051,33 +32051,71 @@
         <v>1405</v>
       </c>
       <c r="F597" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G597" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H597" t="s">
+        <v>1447</v>
+      </c>
+      <c r="J597" t="s">
+        <v>1448</v>
+      </c>
+      <c r="K597">
+        <v>70</v>
+      </c>
+      <c r="L597">
+        <v>40.5</v>
+      </c>
+      <c r="M597">
+        <v>5</v>
+      </c>
+      <c r="P597" s="19">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="598" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A598" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B598" t="s">
+        <v>55</v>
+      </c>
+      <c r="C598" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E598" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F598" t="s">
         <v>2366</v>
       </c>
-      <c r="G597" t="s">
+      <c r="G598" t="s">
         <v>2367</v>
       </c>
-      <c r="H597" t="s">
+      <c r="H598" t="s">
         <v>2362</v>
       </c>
-      <c r="J597">
+      <c r="J598">
         <f>5.41+1.74</f>
         <v>7.15</v>
       </c>
-      <c r="K597">
+      <c r="K598">
         <v>70</v>
       </c>
-      <c r="L597">
+      <c r="L598">
         <v>21.95</v>
       </c>
-      <c r="M597">
+      <c r="M598">
         <v>6</v>
       </c>
-      <c r="P597" s="19">
+      <c r="P598" s="19">
         <v>46155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R596" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:R597" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/TarifVinom_Master.xlsx
+++ b/data/TarifVinom_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sfrbt1009862.sharepoint.com/vinom/Shared Documents/TARIF VINOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04391901-AF94-194B-A995-F72457E3C370}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="13_ncr:1_{A968D4B3-F538-6E4D-B999-D2E2C89C0321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6644695-39B6-5D4D-8E3C-D32BD4067EAF}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="27080" windowHeight="14980" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <sheet name="MAJ_Codes" sheetId="6" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$597</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Tarif!$A$1:$R$599</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10591" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10607" uniqueCount="2402">
   <si>
     <t>TARIF VINOM MASTER — Document de pilotage du catalogue automatisé</t>
   </si>
@@ -7248,6 +7248,9 @@
   </si>
   <si>
     <t>Domaine Oddo</t>
+  </si>
+  <si>
+    <t>Serra Ferdiandea</t>
   </si>
 </sst>
 </file>
@@ -8013,7 +8016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R598"/>
+  <dimension ref="A1:R600"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -23786,7 +23789,7 @@
     </row>
     <row r="393" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A393">
-        <v>73900525</v>
+        <v>73900624</v>
       </c>
       <c r="B393" t="s">
         <v>55</v>
@@ -23798,7 +23801,7 @@
         <v>913</v>
       </c>
       <c r="E393" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F393" t="s">
         <v>952</v>
@@ -23810,13 +23813,13 @@
         <v>69</v>
       </c>
       <c r="J393">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="K393">
         <v>75</v>
       </c>
       <c r="L393">
-        <v>7.4</v>
+        <v>7.95</v>
       </c>
       <c r="M393">
         <v>12</v>
@@ -29722,87 +29725,90 @@
       </c>
     </row>
     <row r="537" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A537" t="s">
-        <v>1282</v>
+      <c r="A537">
+        <v>73900824</v>
       </c>
       <c r="B537" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C537" t="s">
         <v>1257</v>
       </c>
       <c r="D537" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E537" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F537" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G537" t="s">
-        <v>1285</v>
+        <v>2401</v>
       </c>
       <c r="H537" t="s">
-        <v>1286</v>
-      </c>
-      <c r="J537" t="s">
-        <v>217</v>
+        <v>2400</v>
+      </c>
+      <c r="I537" t="s">
+        <v>69</v>
+      </c>
+      <c r="J537">
+        <v>2024</v>
       </c>
       <c r="K537">
         <v>75</v>
       </c>
       <c r="L537">
-        <v>4.95</v>
-      </c>
-      <c r="P537" s="19">
-        <v>46155</v>
+        <v>12.6</v>
+      </c>
+      <c r="M537">
+        <v>6</v>
       </c>
     </row>
     <row r="538" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A538" t="s">
-        <v>1287</v>
+      <c r="A538">
+        <v>73900920</v>
       </c>
       <c r="B538" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C538" t="s">
         <v>1257</v>
       </c>
       <c r="D538" t="s">
-        <v>1283</v>
+        <v>1258</v>
       </c>
       <c r="E538" t="s">
         <v>63</v>
       </c>
       <c r="F538" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="G538" t="s">
-        <v>1288</v>
+        <v>2401</v>
       </c>
       <c r="H538" t="s">
-        <v>1289</v>
-      </c>
-      <c r="J538" t="s">
-        <v>87</v>
+        <v>2400</v>
+      </c>
+      <c r="I538" t="s">
+        <v>69</v>
+      </c>
+      <c r="J538">
+        <v>2020</v>
       </c>
       <c r="K538">
         <v>75</v>
       </c>
       <c r="L538">
-        <v>6.1</v>
+        <v>13.95</v>
       </c>
       <c r="M538">
-        <v>133</v>
-      </c>
-      <c r="P538" s="19">
-        <v>46155</v>
+        <v>6</v>
       </c>
     </row>
     <row r="539" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="B539" t="s">
         <v>66</v>
@@ -29820,30 +29826,30 @@
         <v>1284</v>
       </c>
       <c r="G539" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="H539" t="s">
-        <v>1289</v>
-      </c>
-      <c r="J539">
-        <v>2024</v>
+        <v>1286</v>
+      </c>
+      <c r="J539" t="s">
+        <v>217</v>
       </c>
       <c r="K539">
         <v>75</v>
       </c>
       <c r="L539">
-        <v>6.1</v>
+        <v>4.95</v>
       </c>
       <c r="P539" s="19">
-        <v>46275</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="540" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="B540" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C540" t="s">
         <v>1257</v>
@@ -29858,22 +29864,22 @@
         <v>1284</v>
       </c>
       <c r="G540" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="H540" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="J540" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="K540">
         <v>75</v>
       </c>
       <c r="L540">
-        <v>13.2</v>
+        <v>6.1</v>
       </c>
       <c r="M540">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="P540" s="19">
         <v>46155</v>
@@ -29881,10 +29887,10 @@
     </row>
     <row r="541" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="B541" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C541" t="s">
         <v>1257</v>
@@ -29899,30 +29905,27 @@
         <v>1284</v>
       </c>
       <c r="G541" t="s">
-        <v>1295</v>
+        <v>1288</v>
       </c>
       <c r="H541" t="s">
-        <v>1293</v>
-      </c>
-      <c r="J541" t="s">
-        <v>1228</v>
+        <v>1289</v>
+      </c>
+      <c r="J541">
+        <v>2024</v>
       </c>
       <c r="K541">
         <v>75</v>
       </c>
       <c r="L541">
-        <v>16.350000000000001</v>
-      </c>
-      <c r="M541">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P541" s="19">
-        <v>46155</v>
+        <v>46275</v>
       </c>
     </row>
     <row r="542" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="B542" t="s">
         <v>55</v>
@@ -29937,22 +29940,22 @@
         <v>63</v>
       </c>
       <c r="F542" t="s">
-        <v>1297</v>
+        <v>1284</v>
       </c>
       <c r="G542" t="s">
-        <v>1298</v>
+        <v>1292</v>
       </c>
       <c r="H542" t="s">
         <v>1293</v>
       </c>
       <c r="J542" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="K542">
         <v>75</v>
       </c>
       <c r="L542">
-        <v>5.0999999999999996</v>
+        <v>13.2</v>
       </c>
       <c r="M542">
         <v>0</v>
@@ -29962,41 +29965,41 @@
       </c>
     </row>
     <row r="543" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A543">
-        <v>10702526</v>
+      <c r="A543" t="s">
+        <v>1294</v>
       </c>
       <c r="B543" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C543" t="s">
         <v>1257</v>
       </c>
       <c r="D543" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="E543" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F543" t="s">
-        <v>1299</v>
+        <v>1284</v>
       </c>
       <c r="G543" t="s">
-        <v>726</v>
+        <v>1295</v>
       </c>
       <c r="H543" t="s">
-        <v>1300</v>
-      </c>
-      <c r="J543">
-        <v>2026</v>
+        <v>1293</v>
+      </c>
+      <c r="J543" t="s">
+        <v>1228</v>
       </c>
       <c r="K543">
         <v>75</v>
       </c>
       <c r="L543">
-        <v>4.6500000000000004</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="M543">
-        <v>1327</v>
+        <v>0</v>
       </c>
       <c r="P543" s="19">
         <v>46155</v>
@@ -30004,48 +30007,48 @@
     </row>
     <row r="544" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="B544" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C544" t="s">
         <v>1257</v>
       </c>
       <c r="D544" t="s">
-        <v>1302</v>
+        <v>1283</v>
       </c>
       <c r="E544" t="s">
         <v>63</v>
       </c>
       <c r="F544" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="G544" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="H544" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
       <c r="J544" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="K544">
         <v>75</v>
       </c>
       <c r="L544">
-        <v>8.5</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="M544">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P544" s="19">
         <v>46155</v>
       </c>
     </row>
     <row r="545" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A545" t="s">
-        <v>1306</v>
+      <c r="A545">
+        <v>10702526</v>
       </c>
       <c r="B545" t="s">
         <v>66</v>
@@ -30054,31 +30057,31 @@
         <v>1257</v>
       </c>
       <c r="D545" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="E545" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F545" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="G545" t="s">
-        <v>1307</v>
+        <v>726</v>
       </c>
       <c r="H545" t="s">
-        <v>1305</v>
-      </c>
-      <c r="J545" t="s">
-        <v>109</v>
+        <v>1300</v>
+      </c>
+      <c r="J545">
+        <v>2026</v>
       </c>
       <c r="K545">
         <v>75</v>
       </c>
       <c r="L545">
-        <v>8.6</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="M545">
-        <v>30</v>
+        <v>1327</v>
       </c>
       <c r="P545" s="19">
         <v>46155</v>
@@ -30086,7 +30089,7 @@
     </row>
     <row r="546" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
-        <v>1308</v>
+        <v>1301</v>
       </c>
       <c r="B546" t="s">
         <v>66</v>
@@ -30104,7 +30107,7 @@
         <v>1303</v>
       </c>
       <c r="G546" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="H546" t="s">
         <v>1305</v>
@@ -30116,10 +30119,10 @@
         <v>75</v>
       </c>
       <c r="L546">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M546">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="P546" s="19">
         <v>46155</v>
@@ -30127,7 +30130,7 @@
     </row>
     <row r="547" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="B547" t="s">
         <v>66</v>
@@ -30145,13 +30148,13 @@
         <v>1303</v>
       </c>
       <c r="G547" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="H547" t="s">
         <v>1305</v>
       </c>
       <c r="J547" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K547">
         <v>75</v>
@@ -30160,7 +30163,7 @@
         <v>8.6</v>
       </c>
       <c r="M547">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="P547" s="19">
         <v>46155</v>
@@ -30168,7 +30171,7 @@
     </row>
     <row r="548" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="B548" t="s">
         <v>66</v>
@@ -30186,13 +30189,13 @@
         <v>1303</v>
       </c>
       <c r="G548" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="H548" t="s">
         <v>1305</v>
       </c>
       <c r="J548" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="K548">
         <v>75</v>
@@ -30201,7 +30204,7 @@
         <v>8.6</v>
       </c>
       <c r="M548">
-        <v>662</v>
+        <v>36</v>
       </c>
       <c r="P548" s="19">
         <v>46155</v>
@@ -30209,7 +30212,7 @@
     </row>
     <row r="549" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B549" t="s">
         <v>66</v>
@@ -30227,22 +30230,22 @@
         <v>1303</v>
       </c>
       <c r="G549" t="s">
-        <v>1314</v>
+        <v>1304</v>
       </c>
       <c r="H549" t="s">
         <v>1305</v>
       </c>
       <c r="J549" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K549">
         <v>75</v>
       </c>
       <c r="L549">
-        <v>12.05</v>
+        <v>8.6</v>
       </c>
       <c r="M549">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="P549" s="19">
         <v>46155</v>
@@ -30250,7 +30253,7 @@
     </row>
     <row r="550" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B550" t="s">
         <v>66</v>
@@ -30268,22 +30271,22 @@
         <v>1303</v>
       </c>
       <c r="G550" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="H550" t="s">
         <v>1305</v>
       </c>
-      <c r="J550">
-        <v>2021</v>
+      <c r="J550" t="s">
+        <v>132</v>
       </c>
       <c r="K550">
         <v>75</v>
       </c>
       <c r="L550">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="M550">
-        <v>0</v>
+        <v>662</v>
       </c>
       <c r="P550" s="19">
         <v>46155</v>
@@ -30291,7 +30294,7 @@
     </row>
     <row r="551" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="B551" t="s">
         <v>66</v>
@@ -30309,22 +30312,22 @@
         <v>1303</v>
       </c>
       <c r="G551" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="H551" t="s">
         <v>1305</v>
       </c>
       <c r="J551" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="K551">
         <v>75</v>
       </c>
       <c r="L551">
-        <v>13</v>
+        <v>12.05</v>
       </c>
       <c r="M551">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="P551" s="19">
         <v>46155</v>
@@ -30332,7 +30335,7 @@
     </row>
     <row r="552" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="B552" t="s">
         <v>66</v>
@@ -30350,22 +30353,22 @@
         <v>1303</v>
       </c>
       <c r="G552" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="H552" t="s">
         <v>1305</v>
       </c>
-      <c r="J552" t="s">
-        <v>109</v>
+      <c r="J552">
+        <v>2021</v>
       </c>
       <c r="K552">
         <v>75</v>
       </c>
       <c r="L552">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M552">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="P552" s="19">
         <v>46155</v>
@@ -30373,7 +30376,7 @@
     </row>
     <row r="553" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="B553" t="s">
         <v>66</v>
@@ -30385,28 +30388,28 @@
         <v>1302</v>
       </c>
       <c r="E553" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F553" t="s">
         <v>1303</v>
       </c>
       <c r="G553" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="H553" t="s">
         <v>1305</v>
       </c>
       <c r="J553" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="K553">
         <v>75</v>
       </c>
       <c r="L553">
-        <v>8.0500000000000007</v>
+        <v>13</v>
       </c>
       <c r="M553">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="P553" s="19">
         <v>46155</v>
@@ -30414,40 +30417,40 @@
     </row>
     <row r="554" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="B554" t="s">
         <v>66</v>
       </c>
       <c r="C554" t="s">
-        <v>1323</v>
+        <v>1257</v>
       </c>
       <c r="D554" t="s">
-        <v>1258</v>
+        <v>1302</v>
       </c>
       <c r="E554" t="s">
-        <v>1323</v>
+        <v>63</v>
       </c>
       <c r="F554" t="s">
-        <v>1324</v>
+        <v>1303</v>
       </c>
       <c r="G554" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="H554" t="s">
-        <v>1261</v>
+        <v>1305</v>
       </c>
       <c r="J554" t="s">
-        <v>564</v>
+        <v>109</v>
       </c>
       <c r="K554">
         <v>75</v>
       </c>
       <c r="L554">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="M554">
-        <v>4411</v>
+        <v>36</v>
       </c>
       <c r="P554" s="19">
         <v>46155</v>
@@ -30455,34 +30458,40 @@
     </row>
     <row r="555" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="B555" t="s">
         <v>66</v>
       </c>
       <c r="C555" t="s">
-        <v>1323</v>
+        <v>1257</v>
+      </c>
+      <c r="D555" t="s">
+        <v>1302</v>
       </c>
       <c r="E555" t="s">
-        <v>1323</v>
+        <v>57</v>
       </c>
       <c r="F555" t="s">
-        <v>58</v>
+        <v>1303</v>
       </c>
       <c r="G555" t="s">
-        <v>1327</v>
+        <v>1042</v>
       </c>
       <c r="H555" t="s">
-        <v>1001</v>
+        <v>1305</v>
       </c>
       <c r="J555" t="s">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K555">
         <v>75</v>
       </c>
       <c r="L555">
-        <v>6.2</v>
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="M555">
+        <v>55</v>
       </c>
       <c r="P555" s="19">
         <v>46155</v>
@@ -30490,7 +30499,7 @@
     </row>
     <row r="556" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
       <c r="B556" t="s">
         <v>66</v>
@@ -30498,17 +30507,20 @@
       <c r="C556" t="s">
         <v>1323</v>
       </c>
+      <c r="D556" t="s">
+        <v>1258</v>
+      </c>
       <c r="E556" t="s">
         <v>1323</v>
       </c>
       <c r="F556" t="s">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="G556" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="H556" t="s">
-        <v>1330</v>
+        <v>1261</v>
       </c>
       <c r="J556" t="s">
         <v>564</v>
@@ -30517,7 +30529,10 @@
         <v>75</v>
       </c>
       <c r="L556">
-        <v>8.99</v>
+        <v>6.2</v>
+      </c>
+      <c r="M556">
+        <v>4411</v>
       </c>
       <c r="P556" s="19">
         <v>46155</v>
@@ -30525,7 +30540,7 @@
     </row>
     <row r="557" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="B557" t="s">
         <v>66</v>
@@ -30537,25 +30552,22 @@
         <v>1323</v>
       </c>
       <c r="F557" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G557" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="H557" t="s">
-        <v>1334</v>
+        <v>1001</v>
       </c>
       <c r="J557" t="s">
         <v>564</v>
       </c>
       <c r="K557">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="L557">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="M557">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="P557" s="19">
         <v>46155</v>
@@ -30563,7 +30575,7 @@
     </row>
     <row r="558" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
-        <v>1335</v>
+        <v>1328</v>
       </c>
       <c r="B558" t="s">
         <v>66</v>
@@ -30575,13 +30587,13 @@
         <v>1323</v>
       </c>
       <c r="F558" t="s">
-        <v>1332</v>
+        <v>58</v>
       </c>
       <c r="G558" t="s">
-        <v>1336</v>
+        <v>1329</v>
       </c>
       <c r="H558" t="s">
-        <v>1337</v>
+        <v>1330</v>
       </c>
       <c r="J558" t="s">
         <v>564</v>
@@ -30590,10 +30602,7 @@
         <v>75</v>
       </c>
       <c r="L558">
-        <v>16.45</v>
-      </c>
-      <c r="M558">
-        <v>6532</v>
+        <v>8.99</v>
       </c>
       <c r="P558" s="19">
         <v>46155</v>
@@ -30601,7 +30610,7 @@
     </row>
     <row r="559" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
-        <v>1338</v>
+        <v>1331</v>
       </c>
       <c r="B559" t="s">
         <v>66</v>
@@ -30616,22 +30625,22 @@
         <v>1332</v>
       </c>
       <c r="G559" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="H559" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="J559" t="s">
         <v>564</v>
       </c>
       <c r="K559">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="L559">
-        <v>23.5</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="M559">
-        <v>418</v>
+        <v>5</v>
       </c>
       <c r="P559" s="19">
         <v>46155</v>
@@ -30639,10 +30648,10 @@
     </row>
     <row r="560" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="B560" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C560" t="s">
         <v>1323</v>
@@ -30654,10 +30663,10 @@
         <v>1332</v>
       </c>
       <c r="G560" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="H560" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="J560" t="s">
         <v>564</v>
@@ -30666,7 +30675,10 @@
         <v>75</v>
       </c>
       <c r="L560">
-        <v>23.9</v>
+        <v>16.45</v>
+      </c>
+      <c r="M560">
+        <v>6532</v>
       </c>
       <c r="P560" s="19">
         <v>46155</v>
@@ -30674,7 +30686,7 @@
     </row>
     <row r="561" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
-        <v>1347</v>
+        <v>1338</v>
       </c>
       <c r="B561" t="s">
         <v>66</v>
@@ -30689,10 +30701,10 @@
         <v>1332</v>
       </c>
       <c r="G561" t="s">
-        <v>1348</v>
+        <v>1339</v>
       </c>
       <c r="H561" t="s">
-        <v>1349</v>
+        <v>1340</v>
       </c>
       <c r="J561" t="s">
         <v>564</v>
@@ -30701,10 +30713,10 @@
         <v>75</v>
       </c>
       <c r="L561">
-        <v>25.8</v>
+        <v>23.5</v>
       </c>
       <c r="M561">
-        <v>995</v>
+        <v>418</v>
       </c>
       <c r="P561" s="19">
         <v>46155</v>
@@ -30712,10 +30724,10 @@
     </row>
     <row r="562" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
-        <v>1350</v>
+        <v>1341</v>
       </c>
       <c r="B562" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C562" t="s">
         <v>1323</v>
@@ -30727,10 +30739,10 @@
         <v>1332</v>
       </c>
       <c r="G562" t="s">
-        <v>1351</v>
+        <v>1342</v>
       </c>
       <c r="H562" t="s">
-        <v>1352</v>
+        <v>1343</v>
       </c>
       <c r="J562" t="s">
         <v>564</v>
@@ -30739,10 +30751,7 @@
         <v>75</v>
       </c>
       <c r="L562">
-        <v>27.5</v>
-      </c>
-      <c r="M562">
-        <v>31</v>
+        <v>23.9</v>
       </c>
       <c r="P562" s="19">
         <v>46155</v>
@@ -30750,7 +30759,7 @@
     </row>
     <row r="563" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
-        <v>1353</v>
+        <v>1347</v>
       </c>
       <c r="B563" t="s">
         <v>66</v>
@@ -30765,10 +30774,10 @@
         <v>1332</v>
       </c>
       <c r="G563" t="s">
-        <v>1354</v>
+        <v>1348</v>
       </c>
       <c r="H563" t="s">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="J563" t="s">
         <v>564</v>
@@ -30777,10 +30786,10 @@
         <v>75</v>
       </c>
       <c r="L563">
-        <v>29</v>
+        <v>25.8</v>
       </c>
       <c r="M563">
-        <v>5</v>
+        <v>995</v>
       </c>
       <c r="P563" s="19">
         <v>46155</v>
@@ -30788,7 +30797,7 @@
     </row>
     <row r="564" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="B564" t="s">
         <v>66</v>
@@ -30803,10 +30812,10 @@
         <v>1332</v>
       </c>
       <c r="G564" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="H564" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="J564" t="s">
         <v>564</v>
@@ -30815,10 +30824,10 @@
         <v>75</v>
       </c>
       <c r="L564">
-        <v>29.35</v>
+        <v>27.5</v>
       </c>
       <c r="M564">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="P564" s="19">
         <v>46155</v>
@@ -30826,10 +30835,10 @@
     </row>
     <row r="565" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B565" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C565" t="s">
         <v>1323</v>
@@ -30841,22 +30850,22 @@
         <v>1332</v>
       </c>
       <c r="G565" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="H565" t="s">
-        <v>1349</v>
+        <v>1334</v>
       </c>
       <c r="J565" t="s">
         <v>564</v>
       </c>
       <c r="K565">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="L565">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="M565">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="P565" s="19">
         <v>46155</v>
@@ -30864,10 +30873,10 @@
     </row>
     <row r="566" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B566" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C566" t="s">
         <v>1323</v>
@@ -30879,7 +30888,7 @@
         <v>1332</v>
       </c>
       <c r="G566" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="H566" t="s">
         <v>1349</v>
@@ -30891,7 +30900,7 @@
         <v>75</v>
       </c>
       <c r="L566">
-        <v>34.5</v>
+        <v>29.35</v>
       </c>
       <c r="M566">
         <v>60</v>
@@ -30902,7 +30911,7 @@
     </row>
     <row r="567" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="B567" t="s">
         <v>55</v>
@@ -30917,7 +30926,7 @@
         <v>1332</v>
       </c>
       <c r="G567" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="H567" t="s">
         <v>1349</v>
@@ -30926,10 +30935,10 @@
         <v>564</v>
       </c>
       <c r="K567">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="L567">
-        <v>30.4</v>
+        <v>63</v>
       </c>
       <c r="M567">
         <v>60</v>
@@ -30940,10 +30949,10 @@
     </row>
     <row r="568" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="B568" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C568" t="s">
         <v>1323</v>
@@ -30955,10 +30964,10 @@
         <v>1332</v>
       </c>
       <c r="G568" t="s">
-        <v>919</v>
+        <v>1360</v>
       </c>
       <c r="H568" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="J568" t="s">
         <v>564</v>
@@ -30967,10 +30976,10 @@
         <v>75</v>
       </c>
       <c r="L568">
-        <v>29.8</v>
+        <v>34.5</v>
       </c>
       <c r="M568">
-        <v>417</v>
+        <v>60</v>
       </c>
       <c r="P568" s="19">
         <v>46155</v>
@@ -30978,10 +30987,10 @@
     </row>
     <row r="569" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
-        <v>1367</v>
+        <v>1361</v>
       </c>
       <c r="B569" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C569" t="s">
         <v>1323</v>
@@ -30993,10 +31002,10 @@
         <v>1332</v>
       </c>
       <c r="G569" t="s">
-        <v>1368</v>
+        <v>1362</v>
       </c>
       <c r="H569" t="s">
-        <v>1369</v>
+        <v>1349</v>
       </c>
       <c r="J569" t="s">
         <v>564</v>
@@ -31005,10 +31014,10 @@
         <v>75</v>
       </c>
       <c r="L569">
-        <v>31</v>
+        <v>30.4</v>
       </c>
       <c r="M569">
-        <v>428</v>
+        <v>60</v>
       </c>
       <c r="P569" s="19">
         <v>46155</v>
@@ -31016,7 +31025,7 @@
     </row>
     <row r="570" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
-        <v>1370</v>
+        <v>1363</v>
       </c>
       <c r="B570" t="s">
         <v>66</v>
@@ -31031,10 +31040,10 @@
         <v>1332</v>
       </c>
       <c r="G570" t="s">
-        <v>1371</v>
+        <v>919</v>
       </c>
       <c r="H570" t="s">
-        <v>1372</v>
+        <v>1352</v>
       </c>
       <c r="J570" t="s">
         <v>564</v>
@@ -31043,10 +31052,10 @@
         <v>75</v>
       </c>
       <c r="L570">
-        <v>33</v>
+        <v>29.8</v>
       </c>
       <c r="M570">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="P570" s="19">
         <v>46155</v>
@@ -31054,7 +31063,7 @@
     </row>
     <row r="571" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
-        <v>1373</v>
+        <v>1367</v>
       </c>
       <c r="B571" t="s">
         <v>66</v>
@@ -31069,10 +31078,10 @@
         <v>1332</v>
       </c>
       <c r="G571" t="s">
-        <v>1374</v>
+        <v>1368</v>
       </c>
       <c r="H571" t="s">
-        <v>1349</v>
+        <v>1369</v>
       </c>
       <c r="J571" t="s">
         <v>564</v>
@@ -31081,10 +31090,10 @@
         <v>75</v>
       </c>
       <c r="L571">
-        <v>34.200000000000003</v>
+        <v>31</v>
       </c>
       <c r="M571">
-        <v>36</v>
+        <v>428</v>
       </c>
       <c r="P571" s="19">
         <v>46155</v>
@@ -31092,7 +31101,7 @@
     </row>
     <row r="572" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="B572" t="s">
         <v>66</v>
@@ -31107,10 +31116,10 @@
         <v>1332</v>
       </c>
       <c r="G572" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="H572" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="J572" t="s">
         <v>564</v>
@@ -31119,7 +31128,7 @@
         <v>75</v>
       </c>
       <c r="L572">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M572">
         <v>0</v>
@@ -31130,10 +31139,10 @@
     </row>
     <row r="573" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="B573" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C573" t="s">
         <v>1323</v>
@@ -31145,10 +31154,10 @@
         <v>1332</v>
       </c>
       <c r="G573" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="H573" t="s">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="J573" t="s">
         <v>564</v>
@@ -31157,10 +31166,10 @@
         <v>75</v>
       </c>
       <c r="L573">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="M573">
         <v>36</v>
-      </c>
-      <c r="M573">
-        <v>0</v>
       </c>
       <c r="P573" s="19">
         <v>46155</v>
@@ -31168,7 +31177,7 @@
     </row>
     <row r="574" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="B574" t="s">
         <v>66</v>
@@ -31183,10 +31192,10 @@
         <v>1332</v>
       </c>
       <c r="G574" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="H574" t="s">
-        <v>1352</v>
+        <v>1377</v>
       </c>
       <c r="J574" t="s">
         <v>564</v>
@@ -31195,10 +31204,10 @@
         <v>75</v>
       </c>
       <c r="L574">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="M574">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="P574" s="19">
         <v>46155</v>
@@ -31206,10 +31215,10 @@
     </row>
     <row r="575" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="B575" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C575" t="s">
         <v>1323</v>
@@ -31221,10 +31230,10 @@
         <v>1332</v>
       </c>
       <c r="G575" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="H575" t="s">
-        <v>1352</v>
+        <v>1334</v>
       </c>
       <c r="J575" t="s">
         <v>564</v>
@@ -31233,10 +31242,10 @@
         <v>75</v>
       </c>
       <c r="L575">
-        <v>47.3</v>
+        <v>36</v>
       </c>
       <c r="M575">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="P575" s="19">
         <v>46155</v>
@@ -31244,7 +31253,7 @@
     </row>
     <row r="576" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="B576" t="s">
         <v>66</v>
@@ -31259,10 +31268,10 @@
         <v>1332</v>
       </c>
       <c r="G576" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="H576" t="s">
-        <v>1386</v>
+        <v>1352</v>
       </c>
       <c r="J576" t="s">
         <v>564</v>
@@ -31271,10 +31280,10 @@
         <v>75</v>
       </c>
       <c r="L576">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M576">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="P576" s="19">
         <v>46155</v>
@@ -31282,7 +31291,7 @@
     </row>
     <row r="577" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="B577" t="s">
         <v>66</v>
@@ -31297,10 +31306,10 @@
         <v>1332</v>
       </c>
       <c r="G577" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="H577" t="s">
-        <v>1389</v>
+        <v>1352</v>
       </c>
       <c r="J577" t="s">
         <v>564</v>
@@ -31309,10 +31318,10 @@
         <v>75</v>
       </c>
       <c r="L577">
-        <v>49</v>
+        <v>47.3</v>
       </c>
       <c r="M577">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="P577" s="19">
         <v>46155</v>
@@ -31320,7 +31329,7 @@
     </row>
     <row r="578" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
-        <v>1390</v>
+        <v>1384</v>
       </c>
       <c r="B578" t="s">
         <v>66</v>
@@ -31335,22 +31344,22 @@
         <v>1332</v>
       </c>
       <c r="G578" t="s">
-        <v>1391</v>
+        <v>1385</v>
       </c>
       <c r="H578" t="s">
-        <v>1334</v>
+        <v>1386</v>
       </c>
       <c r="J578" t="s">
-        <v>167</v>
+        <v>564</v>
       </c>
       <c r="K578">
         <v>75</v>
       </c>
       <c r="L578">
-        <v>128</v>
+        <v>49</v>
       </c>
       <c r="M578">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P578" s="19">
         <v>46155</v>
@@ -31358,7 +31367,7 @@
     </row>
     <row r="579" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="B579" t="s">
         <v>66</v>
@@ -31373,22 +31382,22 @@
         <v>1332</v>
       </c>
       <c r="G579" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="H579" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J579">
-        <v>2017</v>
+        <v>1389</v>
+      </c>
+      <c r="J579" t="s">
+        <v>564</v>
       </c>
       <c r="K579">
         <v>75</v>
       </c>
       <c r="L579">
-        <v>199</v>
+        <v>49</v>
       </c>
       <c r="M579">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="P579" s="19">
         <v>46155</v>
@@ -31396,7 +31405,7 @@
     </row>
     <row r="580" spans="1:16" x14ac:dyDescent="0.2">
       <c r=